--- a/Backend/output/informe_final.xlsx
+++ b/Backend/output/informe_final.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A589DDF-A1B3-4D04-B0F8-7571B51F8D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7D0C453-1C40-40B5-A102-EF7F24D3B70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="733" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -823,7 +823,7 @@
     <t xml:space="preserve">RESULTADO EX ANTE </t>
   </si>
   <si>
-    <t>DICIEMBRE - 2024</t>
+    <t>ENERO - 2025</t>
   </si>
   <si>
     <t>Gab Subse</t>
@@ -1312,10 +1312,10 @@
     <t>En octubre se envió mediante mail del Jefe del Gabinete del Ministro, el resultado del monitoreo del segundo año de gestión.</t>
   </si>
   <si>
-    <t>Acum diciembre - 2024</t>
-  </si>
-  <si>
-    <t>Hitos ADP ocurridos al 24 de diciembre</t>
+    <t>Acum ENERO - 2025</t>
+  </si>
+  <si>
+    <t>Hitos ADP ocurridos al 19 de ENERO</t>
   </si>
   <si>
     <t>Política de Gestión de Riesgos</t>
@@ -12943,7 +12943,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{34998BFF-D8D2-4A8F-8593-A33373321E10}" type="CELLRANGE">
+                    <a:fld id="{EEC3284A-1D12-4541-B4BD-BC5C0CAAC136}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -12977,7 +12977,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{86CBE627-3C0F-4978-B0DC-4CFA59A5D826}" type="CELLRANGE">
+                    <a:fld id="{3901D9A8-1478-4896-969F-4536D65BC343}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13011,7 +13011,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E2CBA465-4450-4A78-8F16-A8FE2FD1AFED}" type="CELLRANGE">
+                    <a:fld id="{89ABB867-2256-409B-93C2-31E8A17EE74E}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13045,7 +13045,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2B249169-5BD0-4F1B-9198-701BA88C2814}" type="CELLRANGE">
+                    <a:fld id="{D8C0F4C1-2931-4292-91DE-3F3B8AC089FD}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13079,7 +13079,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A09EECD4-3F58-4FD5-87A0-EC873ED0D5A8}" type="CELLRANGE">
+                    <a:fld id="{6A19137B-2D14-4005-A000-15DCB4EFC1C2}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13113,7 +13113,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BF31348A-2324-42F9-A2F5-A5A3192E1D50}" type="CELLRANGE">
+                    <a:fld id="{277E8A87-E022-4A06-9D64-3F5FBEEEC105}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13147,7 +13147,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EFE3E381-F170-4180-AA96-5A4F340894B7}" type="CELLRANGE">
+                    <a:fld id="{CC6CF608-F57F-4350-99EA-68DF58399C14}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13181,7 +13181,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DB9DF5BE-AE12-4AB0-868D-263C01483CD3}" type="CELLRANGE">
+                    <a:fld id="{6918DFEB-DF5D-412E-BE16-08E4231F8D56}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13215,7 +13215,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2C1DB71A-F76F-4960-AF58-51177E7FD95F}" type="CELLRANGE">
+                    <a:fld id="{B1D51C0B-F48B-4E2D-821E-FE94A8716AD4}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13249,7 +13249,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0FF58543-30B4-4B02-83DA-D9E978168D83}" type="CELLRANGE">
+                    <a:fld id="{8845C194-D043-44F6-A8D1-0DF940D3D360}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13283,7 +13283,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6EA55170-8142-482D-90DE-A1EE59C7E261}" type="CELLRANGE">
+                    <a:fld id="{C73A5DF3-B07C-4689-B046-EBAAB7944AFF}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13317,7 +13317,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DA8A8286-A200-4A63-947D-9969200E2BF2}" type="CELLRANGE">
+                    <a:fld id="{2855ABBC-6F3F-4CD1-BB59-F28358BC5072}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13694,7 +13694,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{31A588B1-9C89-493D-AF7D-F2A84DDEC711}" type="CELLRANGE">
+                    <a:fld id="{C0487E3F-585E-455E-B519-817CFBD4B253}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14418,7 +14418,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{31FBFC7A-C227-44A6-B6E5-9F1BF52B6A97}" type="CELLRANGE">
+                    <a:fld id="{DA9C1530-8952-40FB-B247-F96B093B8736}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr>
                         <a:defRPr sz="1400">
@@ -14499,7 +14499,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{74D90ABB-66FC-41FE-9269-A82190059F92}" type="CELLRANGE">
+                    <a:fld id="{C03A957D-69DF-4E86-96F4-5067CAF52B61}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -27083,7 +27083,7 @@
         <v>193</v>
       </c>
       <c r="G11" s="458">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H11" s="458"/>
       <c r="I11" s="125"/>
@@ -33327,7 +33327,7 @@
       <c r="A8" s="44"/>
       <c r="C8" s="473" t="str">
         <f>_xlfn.CONCAT("PERIODO ", N5)</f>
-        <v>PERIODO DICIEMBRE - 2024</v>
+        <v>PERIODO ENERO - 2025</v>
       </c>
       <c r="D8" s="474"/>
       <c r="E8" s="475"/>

--- a/Backend/output/informe_final.xlsx
+++ b/Backend/output/informe_final.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7D0C453-1C40-40B5-A102-EF7F24D3B70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{470DA3BE-9FF1-4DB0-9528-6D2DD5B5084A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="733" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="733" firstSheet="4" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -426,9 +426,6 @@
     <t>Acum oct - 24</t>
   </si>
   <si>
-    <t xml:space="preserve"> - Representa los Hitos acumulados que han sido ejecutados al año 2024. ​</t>
-  </si>
-  <si>
     <t xml:space="preserve"> - Todos los Convenios de Alta Dirección Pública (CADP) expuestos, se encuentran vigentes a la fecha del reporte.​</t>
   </si>
   <si>
@@ -823,7 +820,10 @@
     <t xml:space="preserve">RESULTADO EX ANTE </t>
   </si>
   <si>
-    <t>ENERO - 2025</t>
+    <t xml:space="preserve"> - Representa los Hitos acumulados que han sido ejecutados al año 2025. ​</t>
+  </si>
+  <si>
+    <t>FEBRERO - 2025</t>
   </si>
   <si>
     <t>Gab Subse</t>
@@ -1312,10 +1312,10 @@
     <t>En octubre se envió mediante mail del Jefe del Gabinete del Ministro, el resultado del monitoreo del segundo año de gestión.</t>
   </si>
   <si>
-    <t>Acum ENERO - 2025</t>
-  </si>
-  <si>
-    <t>Hitos ADP ocurridos al 19 de ENERO</t>
+    <t>Acum FEBRERO - 2025</t>
+  </si>
+  <si>
+    <t>Hitos ADP ocurridos al 19 de FEBRERO</t>
   </si>
   <si>
     <t>Política de Gestión de Riesgos</t>
@@ -6475,15 +6475,42 @@
     <xf numFmtId="0" fontId="71" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="79" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6493,36 +6520,9 @@
     <xf numFmtId="0" fontId="35" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="81" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -6640,21 +6640,27 @@
     <xf numFmtId="0" fontId="32" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="243" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="149" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="150" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="70" fillId="0" borderId="123" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="124" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="243" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="149" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="150" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6682,23 +6688,266 @@
     <xf numFmtId="0" fontId="70" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="144" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="145" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="120" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="175" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="142" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="143" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="173" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="174" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="15" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="15" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="15" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -6706,9 +6955,6 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6760,9 +7006,6 @@
     <xf numFmtId="0" fontId="43" fillId="12" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="50" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -6787,249 +7030,6 @@
     <xf numFmtId="0" fontId="53" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="15" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="15" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="15" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="175" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="142" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="143" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="173" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="174" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="144" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="145" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="120" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -7042,6 +7042,111 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="205" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="236" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="195" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="202" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="200" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="199" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="219" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="190" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="218" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="220" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="204" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="197" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="21" borderId="185" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="200" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="199" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="164" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="198" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="201" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="55" fillId="20" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7072,115 +7177,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="197" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="67" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="21" borderId="185" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="200" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="199" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="164" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="198" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="201" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="202" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="204" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="219" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="220" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="205" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="236" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="195" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="200" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="199" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="190" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="218" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12943,7 +12943,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EEC3284A-1D12-4541-B4BD-BC5C0CAAC136}" type="CELLRANGE">
+                    <a:fld id="{D2661E06-3F77-4FAC-A8A7-CF9B9C10EF69}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -12977,7 +12977,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3901D9A8-1478-4896-969F-4536D65BC343}" type="CELLRANGE">
+                    <a:fld id="{CAE0097E-7DAA-4E9D-9BEC-B3A5B62944EE}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13011,7 +13011,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{89ABB867-2256-409B-93C2-31E8A17EE74E}" type="CELLRANGE">
+                    <a:fld id="{099923D3-2D7E-465A-B7B2-DEF25AC595C4}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13045,7 +13045,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D8C0F4C1-2931-4292-91DE-3F3B8AC089FD}" type="CELLRANGE">
+                    <a:fld id="{7DF0810F-2DEC-447F-B655-DEF29D3830FE}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13079,7 +13079,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6A19137B-2D14-4005-A000-15DCB4EFC1C2}" type="CELLRANGE">
+                    <a:fld id="{E795BBD4-5136-4809-8B44-29CEC985D5AB}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13113,7 +13113,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{277E8A87-E022-4A06-9D64-3F5FBEEEC105}" type="CELLRANGE">
+                    <a:fld id="{43D1785F-A299-4BC9-8EAC-D65E8B93E892}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13147,7 +13147,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CC6CF608-F57F-4350-99EA-68DF58399C14}" type="CELLRANGE">
+                    <a:fld id="{EC7B2C24-C212-4D79-A016-BDA9D27D99FD}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13181,7 +13181,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6918DFEB-DF5D-412E-BE16-08E4231F8D56}" type="CELLRANGE">
+                    <a:fld id="{39B2D2E8-ECA1-47C1-B195-F0BB1B02BD29}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13215,7 +13215,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B1D51C0B-F48B-4E2D-821E-FE94A8716AD4}" type="CELLRANGE">
+                    <a:fld id="{A6AC6F43-139A-446B-B2EE-C4379C106670}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13249,7 +13249,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8845C194-D043-44F6-A8D1-0DF940D3D360}" type="CELLRANGE">
+                    <a:fld id="{B77455C1-D810-4DDB-9F1B-74BBCCD3A107}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13283,7 +13283,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C73A5DF3-B07C-4689-B046-EBAAB7944AFF}" type="CELLRANGE">
+                    <a:fld id="{63366F18-2EA9-4853-A4BA-5EA60FD69657}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13317,7 +13317,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2855ABBC-6F3F-4CD1-BB59-F28358BC5072}" type="CELLRANGE">
+                    <a:fld id="{F1B882B2-36B1-4EC5-ACBF-FE14554D37CA}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13694,7 +13694,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C0487E3F-585E-455E-B519-817CFBD4B253}" type="CELLRANGE">
+                    <a:fld id="{D93D1446-274D-4BCD-B83E-64A4D75820E5}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14418,7 +14418,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{DA9C1530-8952-40FB-B247-F96B093B8736}" type="CELLRANGE">
+                    <a:fld id="{A070C695-F9A9-410E-A7E2-7E0B5577E904}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr>
                         <a:defRPr sz="1400">
@@ -14499,7 +14499,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C03A957D-69DF-4E86-96F4-5067CAF52B61}" type="CELLRANGE">
+                    <a:fld id="{399870C1-1BC3-4CBA-9F8E-E76AB3F525F2}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -23252,7 +23252,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C3:D5" spid="_x0000_s286601"/>
+                  <a14:cameraTool cellRange="data_status_NC!C3:D5" spid="_x0000_s286609"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23308,7 +23308,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C20:D24" spid="_x0000_s286602"/>
+                  <a14:cameraTool cellRange="data_status_NC!C20:D24" spid="_x0000_s286610"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23373,7 +23373,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C7:D13" spid="_x0000_s286603"/>
+                  <a14:cameraTool cellRange="data_status_NC!C7:D13" spid="_x0000_s286611"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23438,7 +23438,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C15:D18" spid="_x0000_s286604"/>
+                  <a14:cameraTool cellRange="data_status_NC!C15:D18" spid="_x0000_s286612"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23503,7 +23503,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C26:D33" spid="_x0000_s286605"/>
+                  <a14:cameraTool cellRange="data_status_NC!C26:D33" spid="_x0000_s286613"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23568,7 +23568,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C35:D39" spid="_x0000_s286606"/>
+                  <a14:cameraTool cellRange="data_status_NC!C35:D39" spid="_x0000_s286614"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23633,7 +23633,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C41:D46" spid="_x0000_s286607"/>
+                  <a14:cameraTool cellRange="data_status_NC!C41:D46" spid="_x0000_s286615"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23698,7 +23698,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C48:D54" spid="_x0000_s286608"/>
+                  <a14:cameraTool cellRange="data_status_NC!C48:D54" spid="_x0000_s286616"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -27080,7 +27080,7 @@
       <c r="D11" s="298"/>
       <c r="E11" s="303"/>
       <c r="F11" s="304" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G11" s="458">
         <v>2025</v>
@@ -27190,7 +27190,7 @@
       <c r="D15" s="125"/>
       <c r="E15" s="302"/>
       <c r="F15" s="456" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G15" s="456"/>
       <c r="H15" s="125"/>
@@ -27218,7 +27218,7 @@
       <c r="D16" s="125"/>
       <c r="E16" s="302"/>
       <c r="F16" s="456" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G16" s="456"/>
       <c r="H16" s="125"/>
@@ -27272,7 +27272,7 @@
       <c r="D18" s="125"/>
       <c r="E18" s="301"/>
       <c r="F18" s="457" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G18" s="457"/>
       <c r="H18" s="125"/>
@@ -27917,32 +27917,32 @@
   <sheetData>
     <row r="1" spans="1:28" ht="29.25" customHeight="1" thickBot="1">
       <c r="A1" s="233"/>
-      <c r="B1" s="541" t="s">
+      <c r="B1" s="623" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="542"/>
-      <c r="D1" s="542"/>
-      <c r="E1" s="542"/>
-      <c r="F1" s="542"/>
-      <c r="G1" s="542"/>
-      <c r="H1" s="542"/>
-      <c r="I1" s="542"/>
-      <c r="J1" s="542"/>
-      <c r="K1" s="542"/>
-      <c r="L1" s="542"/>
-      <c r="M1" s="542"/>
-      <c r="N1" s="542"/>
-      <c r="O1" s="542"/>
-      <c r="P1" s="542"/>
-      <c r="Q1" s="542"/>
-      <c r="R1" s="542"/>
-      <c r="S1" s="542"/>
-      <c r="T1" s="542"/>
-      <c r="U1" s="542"/>
-      <c r="V1" s="542"/>
-      <c r="W1" s="542"/>
-      <c r="X1" s="542"/>
-      <c r="Y1" s="543"/>
+      <c r="C1" s="624"/>
+      <c r="D1" s="624"/>
+      <c r="E1" s="624"/>
+      <c r="F1" s="624"/>
+      <c r="G1" s="624"/>
+      <c r="H1" s="624"/>
+      <c r="I1" s="624"/>
+      <c r="J1" s="624"/>
+      <c r="K1" s="624"/>
+      <c r="L1" s="624"/>
+      <c r="M1" s="624"/>
+      <c r="N1" s="624"/>
+      <c r="O1" s="624"/>
+      <c r="P1" s="624"/>
+      <c r="Q1" s="624"/>
+      <c r="R1" s="624"/>
+      <c r="S1" s="624"/>
+      <c r="T1" s="624"/>
+      <c r="U1" s="624"/>
+      <c r="V1" s="624"/>
+      <c r="W1" s="624"/>
+      <c r="X1" s="624"/>
+      <c r="Y1" s="625"/>
       <c r="Z1" s="228"/>
     </row>
     <row r="2" spans="1:28" ht="9" customHeight="1" thickBot="1">
@@ -27976,67 +27976,67 @@
     </row>
     <row r="3" spans="1:28" ht="24.75" customHeight="1" thickBot="1">
       <c r="A3" s="234" t="s">
-        <v>174</v>
-      </c>
-      <c r="B3" s="544" t="s">
-        <v>214</v>
-      </c>
-      <c r="C3" s="545"/>
-      <c r="D3" s="545"/>
-      <c r="E3" s="545"/>
-      <c r="F3" s="545"/>
-      <c r="G3" s="545"/>
-      <c r="H3" s="545"/>
-      <c r="I3" s="545"/>
-      <c r="J3" s="545"/>
-      <c r="K3" s="545"/>
-      <c r="L3" s="545"/>
-      <c r="M3" s="545"/>
-      <c r="N3" s="545"/>
-      <c r="O3" s="545"/>
-      <c r="P3" s="545"/>
-      <c r="Q3" s="545"/>
-      <c r="R3" s="545"/>
-      <c r="S3" s="545"/>
-      <c r="T3" s="545"/>
-      <c r="U3" s="545"/>
-      <c r="V3" s="545"/>
-      <c r="W3" s="545"/>
-      <c r="X3" s="545"/>
-      <c r="Y3" s="546"/>
+        <v>173</v>
+      </c>
+      <c r="B3" s="626" t="s">
+        <v>213</v>
+      </c>
+      <c r="C3" s="627"/>
+      <c r="D3" s="627"/>
+      <c r="E3" s="627"/>
+      <c r="F3" s="627"/>
+      <c r="G3" s="627"/>
+      <c r="H3" s="627"/>
+      <c r="I3" s="627"/>
+      <c r="J3" s="627"/>
+      <c r="K3" s="627"/>
+      <c r="L3" s="627"/>
+      <c r="M3" s="627"/>
+      <c r="N3" s="627"/>
+      <c r="O3" s="627"/>
+      <c r="P3" s="627"/>
+      <c r="Q3" s="627"/>
+      <c r="R3" s="627"/>
+      <c r="S3" s="627"/>
+      <c r="T3" s="627"/>
+      <c r="U3" s="627"/>
+      <c r="V3" s="627"/>
+      <c r="W3" s="627"/>
+      <c r="X3" s="627"/>
+      <c r="Y3" s="628"/>
       <c r="Z3" s="229"/>
       <c r="AA3" s="146"/>
     </row>
     <row r="4" spans="1:28" ht="23.25" customHeight="1" thickBot="1">
       <c r="A4" s="235" t="s">
-        <v>175</v>
-      </c>
-      <c r="B4" s="547" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4" s="629" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="548"/>
-      <c r="D4" s="548"/>
-      <c r="E4" s="548"/>
-      <c r="F4" s="548"/>
-      <c r="G4" s="548"/>
-      <c r="H4" s="548"/>
-      <c r="I4" s="548"/>
-      <c r="J4" s="548"/>
-      <c r="K4" s="548"/>
-      <c r="L4" s="548"/>
-      <c r="M4" s="548"/>
-      <c r="N4" s="548"/>
-      <c r="O4" s="548"/>
-      <c r="P4" s="548"/>
-      <c r="Q4" s="548"/>
-      <c r="R4" s="548"/>
-      <c r="S4" s="548"/>
-      <c r="T4" s="548"/>
-      <c r="U4" s="548"/>
-      <c r="V4" s="548"/>
-      <c r="W4" s="548"/>
-      <c r="X4" s="548"/>
-      <c r="Y4" s="549"/>
+      <c r="C4" s="630"/>
+      <c r="D4" s="630"/>
+      <c r="E4" s="630"/>
+      <c r="F4" s="630"/>
+      <c r="G4" s="630"/>
+      <c r="H4" s="630"/>
+      <c r="I4" s="630"/>
+      <c r="J4" s="630"/>
+      <c r="K4" s="630"/>
+      <c r="L4" s="630"/>
+      <c r="M4" s="630"/>
+      <c r="N4" s="630"/>
+      <c r="O4" s="630"/>
+      <c r="P4" s="630"/>
+      <c r="Q4" s="630"/>
+      <c r="R4" s="630"/>
+      <c r="S4" s="630"/>
+      <c r="T4" s="630"/>
+      <c r="U4" s="630"/>
+      <c r="V4" s="630"/>
+      <c r="W4" s="630"/>
+      <c r="X4" s="630"/>
+      <c r="Y4" s="631"/>
       <c r="Z4" s="230"/>
       <c r="AA4" s="146"/>
     </row>
@@ -28071,89 +28071,89 @@
     </row>
     <row r="6" spans="1:28" ht="24.75" customHeight="1" thickBot="1">
       <c r="A6" s="236"/>
-      <c r="B6" s="553" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="554"/>
-      <c r="D6" s="554"/>
-      <c r="E6" s="555"/>
+      <c r="B6" s="635" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" s="636"/>
+      <c r="D6" s="636"/>
+      <c r="E6" s="637"/>
       <c r="F6" s="132"/>
       <c r="G6" s="195"/>
-      <c r="H6" s="573" t="s">
-        <v>136</v>
-      </c>
-      <c r="I6" s="574"/>
-      <c r="J6" s="574"/>
-      <c r="K6" s="575"/>
+      <c r="H6" s="601" t="s">
+        <v>135</v>
+      </c>
+      <c r="I6" s="602"/>
+      <c r="J6" s="602"/>
+      <c r="K6" s="603"/>
       <c r="L6" s="132"/>
       <c r="M6" s="195"/>
-      <c r="N6" s="581" t="s">
-        <v>155</v>
-      </c>
-      <c r="O6" s="582"/>
-      <c r="P6" s="583"/>
+      <c r="N6" s="613" t="s">
+        <v>154</v>
+      </c>
+      <c r="O6" s="614"/>
+      <c r="P6" s="615"/>
       <c r="Q6" s="202"/>
       <c r="R6" s="204"/>
-      <c r="S6" s="533" t="s">
-        <v>137</v>
-      </c>
-      <c r="T6" s="534"/>
+      <c r="S6" s="608" t="s">
+        <v>136</v>
+      </c>
+      <c r="T6" s="609"/>
       <c r="U6" s="205"/>
       <c r="V6" s="209"/>
       <c r="W6" s="196"/>
-      <c r="X6" s="533" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y6" s="534"/>
+      <c r="X6" s="608" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y6" s="609"/>
       <c r="Z6" s="123"/>
       <c r="AA6" s="146"/>
     </row>
     <row r="7" spans="1:28" ht="30.75" customHeight="1" thickBot="1">
       <c r="A7" s="236"/>
       <c r="B7" s="246" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="238" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="238" t="s">
+      <c r="D7" s="239" t="s">
         <v>133</v>
       </c>
-      <c r="D7" s="239" t="s">
+      <c r="E7" s="240" t="s">
         <v>134</v>
-      </c>
-      <c r="E7" s="240" t="s">
-        <v>135</v>
       </c>
       <c r="F7" s="132"/>
       <c r="G7" s="162"/>
-      <c r="H7" s="569">
+      <c r="H7" s="610">
         <f>I23</f>
         <v>68</v>
       </c>
-      <c r="I7" s="580"/>
-      <c r="J7" s="580"/>
-      <c r="K7" s="570"/>
+      <c r="I7" s="612"/>
+      <c r="J7" s="612"/>
+      <c r="K7" s="611"/>
       <c r="L7" s="132"/>
       <c r="M7" s="162"/>
-      <c r="N7" s="565">
+      <c r="N7" s="616">
         <f>L23</f>
         <v>187</v>
       </c>
-      <c r="O7" s="566"/>
-      <c r="P7" s="567"/>
+      <c r="O7" s="617"/>
+      <c r="P7" s="618"/>
       <c r="Q7" s="203"/>
       <c r="R7" s="205"/>
-      <c r="S7" s="569">
+      <c r="S7" s="610">
         <f>O23</f>
         <v>473</v>
       </c>
-      <c r="T7" s="570"/>
+      <c r="T7" s="611"/>
       <c r="U7" s="132"/>
       <c r="V7" s="208"/>
       <c r="W7" s="125"/>
-      <c r="X7" s="569">
+      <c r="X7" s="610">
         <f>R23</f>
         <v>526</v>
       </c>
-      <c r="Y7" s="570"/>
+      <c r="Y7" s="611"/>
       <c r="Z7" s="194"/>
       <c r="AA7" s="146"/>
     </row>
@@ -28240,27 +28240,27 @@
       </c>
       <c r="E10" s="258"/>
       <c r="F10" s="132"/>
-      <c r="G10" s="561" t="s">
-        <v>139</v>
-      </c>
-      <c r="H10" s="562"/>
-      <c r="I10" s="562"/>
-      <c r="J10" s="562"/>
-      <c r="K10" s="562"/>
-      <c r="L10" s="562"/>
-      <c r="M10" s="562"/>
-      <c r="N10" s="562"/>
-      <c r="O10" s="562"/>
-      <c r="P10" s="562"/>
-      <c r="Q10" s="562"/>
-      <c r="R10" s="562"/>
-      <c r="S10" s="562"/>
-      <c r="T10" s="562"/>
-      <c r="U10" s="562"/>
-      <c r="V10" s="562"/>
-      <c r="W10" s="562"/>
-      <c r="X10" s="562"/>
-      <c r="Y10" s="563"/>
+      <c r="G10" s="642" t="s">
+        <v>138</v>
+      </c>
+      <c r="H10" s="643"/>
+      <c r="I10" s="643"/>
+      <c r="J10" s="643"/>
+      <c r="K10" s="643"/>
+      <c r="L10" s="643"/>
+      <c r="M10" s="643"/>
+      <c r="N10" s="643"/>
+      <c r="O10" s="643"/>
+      <c r="P10" s="643"/>
+      <c r="Q10" s="643"/>
+      <c r="R10" s="643"/>
+      <c r="S10" s="643"/>
+      <c r="T10" s="643"/>
+      <c r="U10" s="643"/>
+      <c r="V10" s="643"/>
+      <c r="W10" s="643"/>
+      <c r="X10" s="643"/>
+      <c r="Y10" s="644"/>
       <c r="Z10" s="123"/>
       <c r="AA10" s="146"/>
     </row>
@@ -28277,35 +28277,35 @@
       </c>
       <c r="E11" s="258"/>
       <c r="F11" s="132"/>
-      <c r="G11" s="564" t="s">
+      <c r="G11" s="645" t="s">
+        <v>139</v>
+      </c>
+      <c r="H11" s="640"/>
+      <c r="I11" s="640" t="s">
         <v>140</v>
       </c>
-      <c r="H11" s="559"/>
-      <c r="I11" s="559" t="s">
+      <c r="J11" s="640"/>
+      <c r="K11" s="640"/>
+      <c r="L11" s="640" t="s">
         <v>141</v>
       </c>
-      <c r="J11" s="559"/>
-      <c r="K11" s="559"/>
-      <c r="L11" s="559" t="s">
+      <c r="M11" s="640"/>
+      <c r="N11" s="640"/>
+      <c r="O11" s="640" t="s">
         <v>142</v>
       </c>
-      <c r="M11" s="559"/>
-      <c r="N11" s="559"/>
-      <c r="O11" s="559" t="s">
-        <v>143</v>
-      </c>
-      <c r="P11" s="559"/>
-      <c r="Q11" s="559"/>
-      <c r="R11" s="559" t="s">
-        <v>138</v>
-      </c>
-      <c r="S11" s="559"/>
-      <c r="T11" s="559"/>
-      <c r="U11" s="559"/>
-      <c r="V11" s="559"/>
-      <c r="W11" s="559"/>
-      <c r="X11" s="559"/>
-      <c r="Y11" s="560"/>
+      <c r="P11" s="640"/>
+      <c r="Q11" s="640"/>
+      <c r="R11" s="640" t="s">
+        <v>137</v>
+      </c>
+      <c r="S11" s="640"/>
+      <c r="T11" s="640"/>
+      <c r="U11" s="640"/>
+      <c r="V11" s="640"/>
+      <c r="W11" s="640"/>
+      <c r="X11" s="640"/>
+      <c r="Y11" s="641"/>
       <c r="Z11" s="123"/>
       <c r="AA11" s="146"/>
     </row>
@@ -28322,33 +28322,33 @@
       </c>
       <c r="E12" s="258"/>
       <c r="F12" s="132"/>
-      <c r="G12" s="564"/>
-      <c r="H12" s="559"/>
-      <c r="I12" s="559"/>
-      <c r="J12" s="559"/>
-      <c r="K12" s="559"/>
-      <c r="L12" s="559"/>
-      <c r="M12" s="559"/>
-      <c r="N12" s="559"/>
-      <c r="O12" s="559"/>
-      <c r="P12" s="559"/>
-      <c r="Q12" s="559"/>
-      <c r="R12" s="535" t="s">
+      <c r="G12" s="645"/>
+      <c r="H12" s="640"/>
+      <c r="I12" s="640"/>
+      <c r="J12" s="640"/>
+      <c r="K12" s="640"/>
+      <c r="L12" s="640"/>
+      <c r="M12" s="640"/>
+      <c r="N12" s="640"/>
+      <c r="O12" s="640"/>
+      <c r="P12" s="640"/>
+      <c r="Q12" s="640"/>
+      <c r="R12" s="567" t="s">
+        <v>143</v>
+      </c>
+      <c r="S12" s="567"/>
+      <c r="T12" s="567" t="s">
         <v>144</v>
       </c>
-      <c r="S12" s="535"/>
-      <c r="T12" s="535" t="s">
+      <c r="U12" s="567"/>
+      <c r="V12" s="567" t="s">
         <v>145</v>
       </c>
-      <c r="U12" s="535"/>
-      <c r="V12" s="535" t="s">
+      <c r="W12" s="567"/>
+      <c r="X12" s="567" t="s">
         <v>146</v>
       </c>
-      <c r="W12" s="535"/>
-      <c r="X12" s="535" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y12" s="556"/>
+      <c r="Y12" s="598"/>
       <c r="Z12" s="123"/>
       <c r="AA12" s="122"/>
     </row>
@@ -28365,25 +28365,25 @@
       </c>
       <c r="E13" s="258"/>
       <c r="F13" s="132"/>
-      <c r="G13" s="564"/>
-      <c r="H13" s="559"/>
-      <c r="I13" s="559"/>
-      <c r="J13" s="559"/>
-      <c r="K13" s="559"/>
-      <c r="L13" s="559"/>
-      <c r="M13" s="559"/>
-      <c r="N13" s="559"/>
-      <c r="O13" s="559"/>
-      <c r="P13" s="559"/>
-      <c r="Q13" s="559"/>
-      <c r="R13" s="535"/>
-      <c r="S13" s="535"/>
-      <c r="T13" s="535"/>
-      <c r="U13" s="535"/>
-      <c r="V13" s="535"/>
-      <c r="W13" s="535"/>
-      <c r="X13" s="557"/>
-      <c r="Y13" s="558"/>
+      <c r="G13" s="645"/>
+      <c r="H13" s="640"/>
+      <c r="I13" s="640"/>
+      <c r="J13" s="640"/>
+      <c r="K13" s="640"/>
+      <c r="L13" s="640"/>
+      <c r="M13" s="640"/>
+      <c r="N13" s="640"/>
+      <c r="O13" s="640"/>
+      <c r="P13" s="640"/>
+      <c r="Q13" s="640"/>
+      <c r="R13" s="567"/>
+      <c r="S13" s="567"/>
+      <c r="T13" s="567"/>
+      <c r="U13" s="567"/>
+      <c r="V13" s="567"/>
+      <c r="W13" s="567"/>
+      <c r="X13" s="638"/>
+      <c r="Y13" s="639"/>
       <c r="Z13" s="123"/>
       <c r="AA13" s="124"/>
     </row>
@@ -28400,41 +28400,41 @@
       </c>
       <c r="E14" s="258"/>
       <c r="F14" s="132"/>
-      <c r="G14" s="536" t="s">
+      <c r="G14" s="619" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="537"/>
-      <c r="I14" s="538">
+      <c r="H14" s="620"/>
+      <c r="I14" s="597">
         <v>4</v>
       </c>
-      <c r="J14" s="539"/>
-      <c r="K14" s="540"/>
-      <c r="L14" s="532">
+      <c r="J14" s="621"/>
+      <c r="K14" s="622"/>
+      <c r="L14" s="595">
         <v>8</v>
       </c>
-      <c r="M14" s="532"/>
-      <c r="N14" s="532"/>
-      <c r="O14" s="532">
+      <c r="M14" s="595"/>
+      <c r="N14" s="595"/>
+      <c r="O14" s="595">
         <v>30</v>
       </c>
-      <c r="P14" s="532"/>
-      <c r="Q14" s="532"/>
-      <c r="R14" s="532">
+      <c r="P14" s="595"/>
+      <c r="Q14" s="595"/>
+      <c r="R14" s="595">
         <v>53</v>
       </c>
-      <c r="S14" s="532"/>
-      <c r="T14" s="532">
+      <c r="S14" s="595"/>
+      <c r="T14" s="595">
         <v>0</v>
       </c>
-      <c r="U14" s="532"/>
-      <c r="V14" s="532">
+      <c r="U14" s="595"/>
+      <c r="V14" s="595">
         <v>8</v>
       </c>
-      <c r="W14" s="538"/>
-      <c r="X14" s="532">
+      <c r="W14" s="597"/>
+      <c r="X14" s="595">
         <v>2</v>
       </c>
-      <c r="Y14" s="568"/>
+      <c r="Y14" s="596"/>
       <c r="Z14" s="123"/>
     </row>
     <row r="15" spans="1:28" ht="19.5" customHeight="1" thickBot="1">
@@ -28450,41 +28450,41 @@
       </c>
       <c r="E15" s="259"/>
       <c r="F15" s="132"/>
-      <c r="G15" s="536" t="s">
+      <c r="G15" s="619" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="537"/>
-      <c r="I15" s="538">
+      <c r="H15" s="620"/>
+      <c r="I15" s="597">
         <v>11</v>
       </c>
-      <c r="J15" s="539"/>
-      <c r="K15" s="540"/>
-      <c r="L15" s="532">
+      <c r="J15" s="621"/>
+      <c r="K15" s="622"/>
+      <c r="L15" s="595">
         <v>30</v>
       </c>
-      <c r="M15" s="532"/>
-      <c r="N15" s="532"/>
-      <c r="O15" s="532">
+      <c r="M15" s="595"/>
+      <c r="N15" s="595"/>
+      <c r="O15" s="595">
         <v>105</v>
       </c>
-      <c r="P15" s="532"/>
-      <c r="Q15" s="532"/>
-      <c r="R15" s="532">
+      <c r="P15" s="595"/>
+      <c r="Q15" s="595"/>
+      <c r="R15" s="595">
         <v>105</v>
       </c>
-      <c r="S15" s="532"/>
-      <c r="T15" s="532">
+      <c r="S15" s="595"/>
+      <c r="T15" s="595">
         <v>8</v>
       </c>
-      <c r="U15" s="532"/>
-      <c r="V15" s="532">
+      <c r="U15" s="595"/>
+      <c r="V15" s="595">
         <v>0</v>
       </c>
-      <c r="W15" s="538"/>
-      <c r="X15" s="532">
+      <c r="W15" s="597"/>
+      <c r="X15" s="595">
         <v>4</v>
       </c>
-      <c r="Y15" s="568"/>
+      <c r="Y15" s="596"/>
       <c r="Z15" s="123"/>
       <c r="AA15" s="146"/>
     </row>
@@ -28495,149 +28495,149 @@
       <c r="D16" s="152"/>
       <c r="E16" s="152"/>
       <c r="F16" s="122"/>
-      <c r="G16" s="536" t="s">
+      <c r="G16" s="619" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="537"/>
-      <c r="I16" s="538">
+      <c r="H16" s="620"/>
+      <c r="I16" s="597">
         <v>19</v>
       </c>
-      <c r="J16" s="539"/>
-      <c r="K16" s="540"/>
-      <c r="L16" s="532">
+      <c r="J16" s="621"/>
+      <c r="K16" s="622"/>
+      <c r="L16" s="595">
         <v>58</v>
       </c>
-      <c r="M16" s="532"/>
-      <c r="N16" s="532"/>
-      <c r="O16" s="532">
+      <c r="M16" s="595"/>
+      <c r="N16" s="595"/>
+      <c r="O16" s="595">
         <v>99</v>
       </c>
-      <c r="P16" s="532"/>
-      <c r="Q16" s="532"/>
-      <c r="R16" s="532">
+      <c r="P16" s="595"/>
+      <c r="Q16" s="595"/>
+      <c r="R16" s="595">
         <v>107</v>
       </c>
-      <c r="S16" s="532"/>
-      <c r="T16" s="532">
+      <c r="S16" s="595"/>
+      <c r="T16" s="595">
         <v>8</v>
       </c>
-      <c r="U16" s="532"/>
-      <c r="V16" s="532">
+      <c r="U16" s="595"/>
+      <c r="V16" s="595">
         <v>6</v>
       </c>
-      <c r="W16" s="538"/>
-      <c r="X16" s="532">
+      <c r="W16" s="597"/>
+      <c r="X16" s="595">
         <v>7</v>
       </c>
-      <c r="Y16" s="568"/>
+      <c r="Y16" s="596"/>
       <c r="Z16" s="123"/>
       <c r="AA16" s="146"/>
       <c r="AB16" s="253"/>
     </row>
     <row r="17" spans="1:27" ht="21" customHeight="1">
       <c r="A17" s="122"/>
-      <c r="B17" s="550" t="s">
-        <v>149</v>
-      </c>
-      <c r="C17" s="551"/>
-      <c r="D17" s="551"/>
-      <c r="E17" s="552"/>
+      <c r="B17" s="632" t="s">
+        <v>148</v>
+      </c>
+      <c r="C17" s="633"/>
+      <c r="D17" s="633"/>
+      <c r="E17" s="634"/>
       <c r="F17" s="132"/>
-      <c r="G17" s="536" t="s">
+      <c r="G17" s="619" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="537"/>
-      <c r="I17" s="538">
+      <c r="H17" s="620"/>
+      <c r="I17" s="597">
         <v>15</v>
       </c>
-      <c r="J17" s="539"/>
-      <c r="K17" s="540"/>
-      <c r="L17" s="532">
+      <c r="J17" s="621"/>
+      <c r="K17" s="622"/>
+      <c r="L17" s="595">
         <v>49</v>
       </c>
-      <c r="M17" s="532"/>
-      <c r="N17" s="532"/>
-      <c r="O17" s="532">
+      <c r="M17" s="595"/>
+      <c r="N17" s="595"/>
+      <c r="O17" s="595">
         <v>127</v>
       </c>
-      <c r="P17" s="532"/>
-      <c r="Q17" s="532"/>
-      <c r="R17" s="532">
+      <c r="P17" s="595"/>
+      <c r="Q17" s="595"/>
+      <c r="R17" s="595">
         <v>134</v>
       </c>
-      <c r="S17" s="532"/>
-      <c r="T17" s="532">
+      <c r="S17" s="595"/>
+      <c r="T17" s="595">
         <v>12</v>
       </c>
-      <c r="U17" s="532"/>
-      <c r="V17" s="532">
+      <c r="U17" s="595"/>
+      <c r="V17" s="595">
         <v>5</v>
       </c>
-      <c r="W17" s="538"/>
-      <c r="X17" s="532">
+      <c r="W17" s="597"/>
+      <c r="X17" s="595">
         <v>7</v>
       </c>
-      <c r="Y17" s="568"/>
+      <c r="Y17" s="596"/>
       <c r="Z17" s="123"/>
       <c r="AA17" s="146"/>
     </row>
     <row r="18" spans="1:27" ht="34.5" customHeight="1">
       <c r="A18" s="122"/>
       <c r="B18" s="210" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" s="186" t="s">
+        <v>143</v>
+      </c>
+      <c r="D18" s="185" t="s">
+        <v>129</v>
+      </c>
+      <c r="E18" s="211" t="s">
         <v>150</v>
       </c>
-      <c r="C18" s="186" t="s">
-        <v>144</v>
-      </c>
-      <c r="D18" s="185" t="s">
-        <v>130</v>
-      </c>
-      <c r="E18" s="211" t="s">
-        <v>151</v>
-      </c>
       <c r="F18" s="132"/>
-      <c r="G18" s="536" t="s">
+      <c r="G18" s="619" t="s">
         <v>399</v>
       </c>
-      <c r="H18" s="537"/>
-      <c r="I18" s="538">
+      <c r="H18" s="620"/>
+      <c r="I18" s="597">
         <v>1</v>
       </c>
-      <c r="J18" s="539"/>
-      <c r="K18" s="540"/>
-      <c r="L18" s="532">
+      <c r="J18" s="621"/>
+      <c r="K18" s="622"/>
+      <c r="L18" s="595">
         <v>2</v>
       </c>
-      <c r="M18" s="532"/>
-      <c r="N18" s="532"/>
-      <c r="O18" s="532">
+      <c r="M18" s="595"/>
+      <c r="N18" s="595"/>
+      <c r="O18" s="595">
         <v>4</v>
       </c>
-      <c r="P18" s="532"/>
-      <c r="Q18" s="532"/>
-      <c r="R18" s="532">
+      <c r="P18" s="595"/>
+      <c r="Q18" s="595"/>
+      <c r="R18" s="595">
         <v>4</v>
       </c>
-      <c r="S18" s="532"/>
-      <c r="T18" s="532">
+      <c r="S18" s="595"/>
+      <c r="T18" s="595">
         <v>0</v>
       </c>
-      <c r="U18" s="532"/>
-      <c r="V18" s="532">
+      <c r="U18" s="595"/>
+      <c r="V18" s="595">
         <v>2</v>
       </c>
-      <c r="W18" s="538"/>
-      <c r="X18" s="532">
+      <c r="W18" s="597"/>
+      <c r="X18" s="595">
         <v>2</v>
       </c>
-      <c r="Y18" s="568"/>
+      <c r="Y18" s="596"/>
       <c r="Z18" s="123"/>
       <c r="AA18" s="146"/>
     </row>
     <row r="19" spans="1:27" ht="30.75" customHeight="1">
       <c r="A19" s="122"/>
       <c r="B19" s="212" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C19" s="187">
         <v>16</v>
@@ -28647,48 +28647,48 @@
       </c>
       <c r="E19" s="260"/>
       <c r="F19" s="132"/>
-      <c r="G19" s="536" t="s">
+      <c r="G19" s="619" t="s">
         <v>400</v>
       </c>
-      <c r="H19" s="537"/>
-      <c r="I19" s="538">
+      <c r="H19" s="620"/>
+      <c r="I19" s="597">
         <v>5</v>
       </c>
-      <c r="J19" s="539"/>
-      <c r="K19" s="540"/>
-      <c r="L19" s="532">
+      <c r="J19" s="621"/>
+      <c r="K19" s="622"/>
+      <c r="L19" s="595">
         <v>8</v>
       </c>
-      <c r="M19" s="532"/>
-      <c r="N19" s="532"/>
-      <c r="O19" s="532">
+      <c r="M19" s="595"/>
+      <c r="N19" s="595"/>
+      <c r="O19" s="595">
         <v>22</v>
       </c>
-      <c r="P19" s="532"/>
-      <c r="Q19" s="532"/>
-      <c r="R19" s="532">
+      <c r="P19" s="595"/>
+      <c r="Q19" s="595"/>
+      <c r="R19" s="595">
         <v>22</v>
       </c>
-      <c r="S19" s="532"/>
-      <c r="T19" s="532">
+      <c r="S19" s="595"/>
+      <c r="T19" s="595">
         <v>0</v>
       </c>
-      <c r="U19" s="532"/>
-      <c r="V19" s="532">
+      <c r="U19" s="595"/>
+      <c r="V19" s="595">
         <v>2</v>
       </c>
-      <c r="W19" s="538"/>
-      <c r="X19" s="532">
+      <c r="W19" s="597"/>
+      <c r="X19" s="595">
         <v>0</v>
       </c>
-      <c r="Y19" s="568"/>
+      <c r="Y19" s="596"/>
       <c r="Z19" s="123"/>
       <c r="AA19" s="146"/>
     </row>
     <row r="20" spans="1:27" ht="30" customHeight="1">
       <c r="A20" s="122"/>
       <c r="B20" s="212" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C20" s="192">
         <v>10</v>
@@ -28698,41 +28698,41 @@
       </c>
       <c r="E20" s="260"/>
       <c r="F20" s="132"/>
-      <c r="G20" s="536" t="s">
+      <c r="G20" s="619" t="s">
         <v>22</v>
       </c>
-      <c r="H20" s="537"/>
-      <c r="I20" s="538">
+      <c r="H20" s="620"/>
+      <c r="I20" s="597">
         <v>9</v>
       </c>
-      <c r="J20" s="539"/>
-      <c r="K20" s="540"/>
-      <c r="L20" s="532">
+      <c r="J20" s="621"/>
+      <c r="K20" s="622"/>
+      <c r="L20" s="595">
         <v>22</v>
       </c>
-      <c r="M20" s="532"/>
-      <c r="N20" s="532"/>
-      <c r="O20" s="532">
+      <c r="M20" s="595"/>
+      <c r="N20" s="595"/>
+      <c r="O20" s="595">
         <v>32</v>
       </c>
-      <c r="P20" s="532"/>
-      <c r="Q20" s="532"/>
-      <c r="R20" s="532">
+      <c r="P20" s="595"/>
+      <c r="Q20" s="595"/>
+      <c r="R20" s="595">
         <v>33</v>
       </c>
-      <c r="S20" s="532"/>
-      <c r="T20" s="532">
+      <c r="S20" s="595"/>
+      <c r="T20" s="595">
         <v>0</v>
       </c>
-      <c r="U20" s="532"/>
-      <c r="V20" s="532">
+      <c r="U20" s="595"/>
+      <c r="V20" s="595">
         <v>0</v>
       </c>
-      <c r="W20" s="538"/>
-      <c r="X20" s="532">
+      <c r="W20" s="597"/>
+      <c r="X20" s="595">
         <v>0</v>
       </c>
-      <c r="Y20" s="568"/>
+      <c r="Y20" s="596"/>
       <c r="Z20" s="123"/>
       <c r="AA20" s="146"/>
     </row>
@@ -28749,48 +28749,48 @@
       </c>
       <c r="E21" s="260"/>
       <c r="F21" s="132"/>
-      <c r="G21" s="536" t="s">
+      <c r="G21" s="619" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="537"/>
-      <c r="I21" s="538">
+      <c r="H21" s="620"/>
+      <c r="I21" s="597">
         <v>3</v>
       </c>
-      <c r="J21" s="539"/>
-      <c r="K21" s="540"/>
-      <c r="L21" s="532">
+      <c r="J21" s="621"/>
+      <c r="K21" s="622"/>
+      <c r="L21" s="595">
         <v>8</v>
       </c>
-      <c r="M21" s="532"/>
-      <c r="N21" s="532"/>
-      <c r="O21" s="532">
+      <c r="M21" s="595"/>
+      <c r="N21" s="595"/>
+      <c r="O21" s="595">
         <v>50</v>
       </c>
-      <c r="P21" s="532"/>
-      <c r="Q21" s="532"/>
-      <c r="R21" s="532">
+      <c r="P21" s="595"/>
+      <c r="Q21" s="595"/>
+      <c r="R21" s="595">
         <v>62</v>
       </c>
-      <c r="S21" s="532"/>
-      <c r="T21" s="532">
+      <c r="S21" s="595"/>
+      <c r="T21" s="595">
         <v>0</v>
       </c>
-      <c r="U21" s="532"/>
-      <c r="V21" s="532">
+      <c r="U21" s="595"/>
+      <c r="V21" s="595">
         <v>10</v>
       </c>
-      <c r="W21" s="538"/>
-      <c r="X21" s="532">
+      <c r="W21" s="597"/>
+      <c r="X21" s="595">
         <v>11</v>
       </c>
-      <c r="Y21" s="568"/>
+      <c r="Y21" s="596"/>
       <c r="Z21" s="123"/>
       <c r="AA21" s="146"/>
     </row>
     <row r="22" spans="1:27" ht="32.25" customHeight="1">
       <c r="A22" s="122"/>
       <c r="B22" s="212" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C22" s="192">
         <v>20</v>
@@ -28800,41 +28800,41 @@
       </c>
       <c r="E22" s="260"/>
       <c r="F22" s="132"/>
-      <c r="G22" s="536" t="s">
+      <c r="G22" s="619" t="s">
         <v>401</v>
       </c>
-      <c r="H22" s="537"/>
-      <c r="I22" s="538">
+      <c r="H22" s="620"/>
+      <c r="I22" s="597">
         <v>1</v>
       </c>
-      <c r="J22" s="539"/>
-      <c r="K22" s="540"/>
-      <c r="L22" s="532">
+      <c r="J22" s="621"/>
+      <c r="K22" s="622"/>
+      <c r="L22" s="595">
         <v>2</v>
       </c>
-      <c r="M22" s="532"/>
-      <c r="N22" s="532"/>
-      <c r="O22" s="532">
+      <c r="M22" s="595"/>
+      <c r="N22" s="595"/>
+      <c r="O22" s="595">
         <v>4</v>
       </c>
-      <c r="P22" s="532"/>
-      <c r="Q22" s="532"/>
-      <c r="R22" s="532">
+      <c r="P22" s="595"/>
+      <c r="Q22" s="595"/>
+      <c r="R22" s="595">
         <v>6</v>
       </c>
-      <c r="S22" s="532"/>
-      <c r="T22" s="532">
+      <c r="S22" s="595"/>
+      <c r="T22" s="595">
         <v>0</v>
       </c>
-      <c r="U22" s="532"/>
-      <c r="V22" s="532">
+      <c r="U22" s="595"/>
+      <c r="V22" s="595">
         <v>0</v>
       </c>
-      <c r="W22" s="538"/>
-      <c r="X22" s="532">
+      <c r="W22" s="597"/>
+      <c r="X22" s="595">
         <v>3</v>
       </c>
-      <c r="Y22" s="568"/>
+      <c r="Y22" s="596"/>
       <c r="Z22" s="123"/>
       <c r="AA22" s="146"/>
     </row>
@@ -28851,48 +28851,48 @@
       </c>
       <c r="E23" s="261"/>
       <c r="F23" s="132"/>
-      <c r="G23" s="579" t="s">
-        <v>148</v>
-      </c>
-      <c r="H23" s="571"/>
-      <c r="I23" s="571">
+      <c r="G23" s="607" t="s">
+        <v>147</v>
+      </c>
+      <c r="H23" s="599"/>
+      <c r="I23" s="599">
         <f>SUM(I14:K22)</f>
         <v>68</v>
       </c>
-      <c r="J23" s="571"/>
-      <c r="K23" s="571"/>
-      <c r="L23" s="571">
+      <c r="J23" s="599"/>
+      <c r="K23" s="599"/>
+      <c r="L23" s="599">
         <f>SUM(L14:N22)</f>
         <v>187</v>
       </c>
-      <c r="M23" s="571"/>
-      <c r="N23" s="571"/>
-      <c r="O23" s="576">
+      <c r="M23" s="599"/>
+      <c r="N23" s="599"/>
+      <c r="O23" s="604">
         <f>SUM(O14:Q22)</f>
         <v>473</v>
       </c>
-      <c r="P23" s="577"/>
-      <c r="Q23" s="578"/>
-      <c r="R23" s="576">
+      <c r="P23" s="605"/>
+      <c r="Q23" s="606"/>
+      <c r="R23" s="604">
         <f>SUM(R14:S22)</f>
         <v>526</v>
       </c>
-      <c r="S23" s="578"/>
-      <c r="T23" s="576">
+      <c r="S23" s="606"/>
+      <c r="T23" s="604">
         <f>SUM(T14:U22)</f>
         <v>28</v>
       </c>
-      <c r="U23" s="578"/>
-      <c r="V23" s="576">
+      <c r="U23" s="606"/>
+      <c r="V23" s="604">
         <f>SUM(V14:W22)</f>
         <v>33</v>
       </c>
-      <c r="W23" s="577"/>
-      <c r="X23" s="571">
+      <c r="W23" s="605"/>
+      <c r="X23" s="599">
         <f>SUM(X14:Y22)</f>
         <v>36</v>
       </c>
-      <c r="Y23" s="572"/>
+      <c r="Y23" s="600"/>
       <c r="Z23" s="123"/>
       <c r="AA23" s="146"/>
     </row>
@@ -28962,28 +28962,28 @@
       <c r="E26" s="125"/>
       <c r="F26" s="122"/>
       <c r="G26" s="188"/>
-      <c r="H26" s="616" t="s">
-        <v>163</v>
-      </c>
-      <c r="I26" s="617"/>
-      <c r="J26" s="618"/>
+      <c r="H26" s="562" t="s">
+        <v>162</v>
+      </c>
+      <c r="I26" s="563"/>
+      <c r="J26" s="564"/>
       <c r="K26" s="132"/>
-      <c r="L26" s="622" t="s">
-        <v>156</v>
-      </c>
-      <c r="M26" s="623"/>
-      <c r="N26" s="623"/>
-      <c r="O26" s="623"/>
-      <c r="P26" s="623"/>
-      <c r="Q26" s="623"/>
-      <c r="R26" s="623"/>
-      <c r="S26" s="623"/>
-      <c r="T26" s="623"/>
-      <c r="U26" s="623"/>
-      <c r="V26" s="623"/>
-      <c r="W26" s="623"/>
-      <c r="X26" s="623"/>
-      <c r="Y26" s="624"/>
+      <c r="L26" s="571" t="s">
+        <v>155</v>
+      </c>
+      <c r="M26" s="572"/>
+      <c r="N26" s="572"/>
+      <c r="O26" s="572"/>
+      <c r="P26" s="572"/>
+      <c r="Q26" s="572"/>
+      <c r="R26" s="572"/>
+      <c r="S26" s="572"/>
+      <c r="T26" s="572"/>
+      <c r="U26" s="572"/>
+      <c r="V26" s="572"/>
+      <c r="W26" s="572"/>
+      <c r="X26" s="572"/>
+      <c r="Y26" s="573"/>
       <c r="Z26" s="123"/>
       <c r="AA26" s="146"/>
     </row>
@@ -28995,42 +28995,42 @@
       <c r="E27" s="125"/>
       <c r="F27" s="122"/>
       <c r="G27" s="189"/>
-      <c r="H27" s="613">
+      <c r="H27" s="544">
         <f>Y38</f>
         <v>64</v>
       </c>
-      <c r="I27" s="614"/>
-      <c r="J27" s="615"/>
+      <c r="I27" s="545"/>
+      <c r="J27" s="546"/>
       <c r="K27" s="132"/>
-      <c r="L27" s="587" t="s">
-        <v>140</v>
-      </c>
-      <c r="M27" s="535"/>
-      <c r="N27" s="535"/>
-      <c r="O27" s="535" t="s">
+      <c r="L27" s="593" t="s">
+        <v>139</v>
+      </c>
+      <c r="M27" s="567"/>
+      <c r="N27" s="567"/>
+      <c r="O27" s="567" t="s">
+        <v>156</v>
+      </c>
+      <c r="P27" s="567"/>
+      <c r="Q27" s="567" t="s">
         <v>157</v>
       </c>
-      <c r="P27" s="535"/>
-      <c r="Q27" s="535" t="s">
+      <c r="R27" s="567"/>
+      <c r="S27" s="567" t="s">
         <v>158</v>
       </c>
-      <c r="R27" s="535"/>
-      <c r="S27" s="535" t="s">
+      <c r="T27" s="567" t="s">
         <v>159</v>
       </c>
-      <c r="T27" s="535" t="s">
+      <c r="U27" s="567"/>
+      <c r="V27" s="567" t="s">
         <v>160</v>
       </c>
-      <c r="U27" s="535"/>
-      <c r="V27" s="535" t="s">
+      <c r="W27" s="567" t="s">
         <v>161</v>
       </c>
-      <c r="W27" s="535" t="s">
-        <v>162</v>
-      </c>
-      <c r="X27" s="535"/>
-      <c r="Y27" s="556" t="s">
-        <v>148</v>
+      <c r="X27" s="567"/>
+      <c r="Y27" s="598" t="s">
+        <v>147</v>
       </c>
       <c r="Z27" s="123"/>
       <c r="AA27" s="122"/>
@@ -29047,20 +29047,20 @@
       <c r="I28" s="125"/>
       <c r="J28" s="220"/>
       <c r="K28" s="132"/>
-      <c r="L28" s="587"/>
-      <c r="M28" s="535"/>
-      <c r="N28" s="535"/>
-      <c r="O28" s="535"/>
-      <c r="P28" s="535"/>
-      <c r="Q28" s="535"/>
-      <c r="R28" s="535"/>
-      <c r="S28" s="535"/>
-      <c r="T28" s="535"/>
-      <c r="U28" s="535"/>
-      <c r="V28" s="535"/>
-      <c r="W28" s="535"/>
-      <c r="X28" s="535"/>
-      <c r="Y28" s="556"/>
+      <c r="L28" s="593"/>
+      <c r="M28" s="567"/>
+      <c r="N28" s="567"/>
+      <c r="O28" s="567"/>
+      <c r="P28" s="567"/>
+      <c r="Q28" s="567"/>
+      <c r="R28" s="567"/>
+      <c r="S28" s="567"/>
+      <c r="T28" s="567"/>
+      <c r="U28" s="567"/>
+      <c r="V28" s="567"/>
+      <c r="W28" s="567"/>
+      <c r="X28" s="567"/>
+      <c r="Y28" s="598"/>
       <c r="Z28" s="123"/>
       <c r="AA28" s="146"/>
     </row>
@@ -29076,33 +29076,33 @@
       <c r="I29" s="221"/>
       <c r="J29" s="191"/>
       <c r="K29" s="132"/>
-      <c r="L29" s="584" t="s">
+      <c r="L29" s="579" t="s">
         <v>18</v>
       </c>
-      <c r="M29" s="585"/>
-      <c r="N29" s="585"/>
-      <c r="O29" s="585">
+      <c r="M29" s="547"/>
+      <c r="N29" s="547"/>
+      <c r="O29" s="547">
         <v>3</v>
       </c>
-      <c r="P29" s="585"/>
-      <c r="Q29" s="585">
+      <c r="P29" s="547"/>
+      <c r="Q29" s="547">
         <v>1</v>
       </c>
-      <c r="R29" s="585"/>
+      <c r="R29" s="547"/>
       <c r="S29" s="113">
         <v>0</v>
       </c>
-      <c r="T29" s="585">
+      <c r="T29" s="547">
         <v>0</v>
       </c>
-      <c r="U29" s="585"/>
+      <c r="U29" s="547"/>
       <c r="V29" s="113">
         <v>3</v>
       </c>
-      <c r="W29" s="585">
+      <c r="W29" s="547">
         <v>0</v>
       </c>
-      <c r="X29" s="586"/>
+      <c r="X29" s="548"/>
       <c r="Y29" s="254">
         <v>6</v>
       </c>
@@ -29121,33 +29121,33 @@
       <c r="I30" s="152"/>
       <c r="J30" s="152"/>
       <c r="K30" s="122"/>
-      <c r="L30" s="584" t="s">
+      <c r="L30" s="579" t="s">
         <v>16</v>
       </c>
-      <c r="M30" s="585"/>
-      <c r="N30" s="585"/>
-      <c r="O30" s="585">
+      <c r="M30" s="547"/>
+      <c r="N30" s="547"/>
+      <c r="O30" s="547">
         <v>0</v>
       </c>
-      <c r="P30" s="585"/>
-      <c r="Q30" s="585">
+      <c r="P30" s="547"/>
+      <c r="Q30" s="547">
         <v>0</v>
       </c>
-      <c r="R30" s="585"/>
+      <c r="R30" s="547"/>
       <c r="S30" s="113">
         <v>9</v>
       </c>
-      <c r="T30" s="585">
+      <c r="T30" s="547">
         <v>3</v>
       </c>
-      <c r="U30" s="585"/>
+      <c r="U30" s="547"/>
       <c r="V30" s="113">
         <v>2</v>
       </c>
-      <c r="W30" s="585">
+      <c r="W30" s="547">
         <v>1</v>
       </c>
-      <c r="X30" s="586"/>
+      <c r="X30" s="548"/>
       <c r="Y30" s="254">
         <v>11</v>
       </c>
@@ -29162,39 +29162,39 @@
       <c r="E31" s="125"/>
       <c r="F31" s="122"/>
       <c r="G31" s="188"/>
-      <c r="H31" s="619" t="s">
-        <v>153</v>
-      </c>
-      <c r="I31" s="620"/>
-      <c r="J31" s="621"/>
+      <c r="H31" s="568" t="s">
+        <v>152</v>
+      </c>
+      <c r="I31" s="569"/>
+      <c r="J31" s="570"/>
       <c r="K31" s="132"/>
-      <c r="L31" s="584" t="s">
+      <c r="L31" s="579" t="s">
         <v>19</v>
       </c>
-      <c r="M31" s="585"/>
-      <c r="N31" s="585"/>
-      <c r="O31" s="585">
+      <c r="M31" s="547"/>
+      <c r="N31" s="547"/>
+      <c r="O31" s="547">
         <v>1</v>
       </c>
-      <c r="P31" s="585"/>
-      <c r="Q31" s="585">
+      <c r="P31" s="547"/>
+      <c r="Q31" s="547">
         <v>0</v>
       </c>
-      <c r="R31" s="585"/>
+      <c r="R31" s="547"/>
       <c r="S31" s="113">
         <v>3</v>
       </c>
-      <c r="T31" s="585">
+      <c r="T31" s="547">
         <v>4</v>
       </c>
-      <c r="U31" s="585"/>
+      <c r="U31" s="547"/>
       <c r="V31" s="113">
         <v>2</v>
       </c>
-      <c r="W31" s="585">
+      <c r="W31" s="547">
         <v>0</v>
       </c>
-      <c r="X31" s="586"/>
+      <c r="X31" s="548"/>
       <c r="Y31" s="254">
         <v>6</v>
       </c>
@@ -29213,33 +29213,33 @@
       <c r="I32" s="125"/>
       <c r="J32" s="220"/>
       <c r="K32" s="132"/>
-      <c r="L32" s="584" t="s">
+      <c r="L32" s="579" t="s">
         <v>17</v>
       </c>
-      <c r="M32" s="585"/>
-      <c r="N32" s="585"/>
-      <c r="O32" s="585">
+      <c r="M32" s="547"/>
+      <c r="N32" s="547"/>
+      <c r="O32" s="547">
         <v>2</v>
       </c>
-      <c r="P32" s="585"/>
-      <c r="Q32" s="585">
+      <c r="P32" s="547"/>
+      <c r="Q32" s="547">
         <v>0</v>
       </c>
-      <c r="R32" s="585"/>
+      <c r="R32" s="547"/>
       <c r="S32" s="113">
         <v>4</v>
       </c>
-      <c r="T32" s="585">
+      <c r="T32" s="547">
         <v>2</v>
       </c>
-      <c r="U32" s="585"/>
+      <c r="U32" s="547"/>
       <c r="V32" s="113">
         <v>9</v>
       </c>
-      <c r="W32" s="585">
+      <c r="W32" s="547">
         <v>2</v>
       </c>
-      <c r="X32" s="586"/>
+      <c r="X32" s="548"/>
       <c r="Y32" s="254">
         <v>15</v>
       </c>
@@ -29254,40 +29254,40 @@
       <c r="E33" s="125"/>
       <c r="F33" s="122"/>
       <c r="G33" s="189"/>
-      <c r="H33" s="613">
+      <c r="H33" s="544">
         <f>O38</f>
         <v>13</v>
       </c>
-      <c r="I33" s="614"/>
-      <c r="J33" s="615"/>
+      <c r="I33" s="545"/>
+      <c r="J33" s="546"/>
       <c r="K33" s="132"/>
-      <c r="L33" s="584" t="s">
+      <c r="L33" s="579" t="s">
         <v>399</v>
       </c>
-      <c r="M33" s="585"/>
-      <c r="N33" s="585"/>
-      <c r="O33" s="585">
+      <c r="M33" s="547"/>
+      <c r="N33" s="547"/>
+      <c r="O33" s="547">
         <v>2</v>
       </c>
-      <c r="P33" s="585"/>
-      <c r="Q33" s="585">
+      <c r="P33" s="547"/>
+      <c r="Q33" s="547">
         <v>2</v>
       </c>
-      <c r="R33" s="585"/>
+      <c r="R33" s="547"/>
       <c r="S33" s="113">
         <v>0</v>
       </c>
-      <c r="T33" s="585">
+      <c r="T33" s="547">
         <v>0</v>
       </c>
-      <c r="U33" s="585"/>
+      <c r="U33" s="547"/>
       <c r="V33" s="113">
         <v>1</v>
       </c>
-      <c r="W33" s="585">
+      <c r="W33" s="547">
         <v>1</v>
       </c>
-      <c r="X33" s="586"/>
+      <c r="X33" s="548"/>
       <c r="Y33" s="254">
         <v>3</v>
       </c>
@@ -29306,33 +29306,33 @@
       <c r="I34" s="125"/>
       <c r="J34" s="220"/>
       <c r="K34" s="132"/>
-      <c r="L34" s="584" t="s">
+      <c r="L34" s="579" t="s">
         <v>400</v>
       </c>
-      <c r="M34" s="585"/>
-      <c r="N34" s="585"/>
-      <c r="O34" s="585">
+      <c r="M34" s="547"/>
+      <c r="N34" s="547"/>
+      <c r="O34" s="547">
         <v>1</v>
       </c>
-      <c r="P34" s="585"/>
-      <c r="Q34" s="585">
+      <c r="P34" s="547"/>
+      <c r="Q34" s="547">
         <v>0</v>
       </c>
-      <c r="R34" s="585"/>
+      <c r="R34" s="547"/>
       <c r="S34" s="113">
         <v>0</v>
       </c>
-      <c r="T34" s="585">
+      <c r="T34" s="547">
         <v>0</v>
       </c>
-      <c r="U34" s="585"/>
+      <c r="U34" s="547"/>
       <c r="V34" s="113">
         <v>4</v>
       </c>
-      <c r="W34" s="585">
+      <c r="W34" s="547">
         <v>0</v>
       </c>
-      <c r="X34" s="586"/>
+      <c r="X34" s="548"/>
       <c r="Y34" s="254">
         <v>5</v>
       </c>
@@ -29351,33 +29351,33 @@
       <c r="I35" s="221"/>
       <c r="J35" s="191"/>
       <c r="K35" s="132"/>
-      <c r="L35" s="584" t="s">
+      <c r="L35" s="579" t="s">
         <v>22</v>
       </c>
-      <c r="M35" s="585"/>
-      <c r="N35" s="585"/>
-      <c r="O35" s="588">
+      <c r="M35" s="547"/>
+      <c r="N35" s="547"/>
+      <c r="O35" s="574">
         <v>0</v>
       </c>
-      <c r="P35" s="588"/>
-      <c r="Q35" s="588">
+      <c r="P35" s="574"/>
+      <c r="Q35" s="574">
         <v>0</v>
       </c>
-      <c r="R35" s="588"/>
+      <c r="R35" s="574"/>
       <c r="S35" s="217">
         <v>0</v>
       </c>
-      <c r="T35" s="588">
+      <c r="T35" s="574">
         <v>0</v>
       </c>
-      <c r="U35" s="588"/>
+      <c r="U35" s="574"/>
       <c r="V35" s="217">
         <v>5</v>
       </c>
-      <c r="W35" s="588">
+      <c r="W35" s="574">
         <v>0</v>
       </c>
-      <c r="X35" s="589"/>
+      <c r="X35" s="594"/>
       <c r="Y35" s="254">
         <v>5</v>
       </c>
@@ -29396,33 +29396,33 @@
       <c r="I36" s="152"/>
       <c r="J36" s="152"/>
       <c r="K36" s="122"/>
-      <c r="L36" s="584" t="s">
+      <c r="L36" s="579" t="s">
         <v>20</v>
       </c>
-      <c r="M36" s="585"/>
-      <c r="N36" s="586"/>
-      <c r="O36" s="590">
+      <c r="M36" s="547"/>
+      <c r="N36" s="548"/>
+      <c r="O36" s="551">
         <v>4</v>
       </c>
-      <c r="P36" s="590"/>
-      <c r="Q36" s="590">
+      <c r="P36" s="551"/>
+      <c r="Q36" s="551">
         <v>1</v>
       </c>
-      <c r="R36" s="590"/>
+      <c r="R36" s="551"/>
       <c r="S36" s="218">
         <v>0</v>
       </c>
-      <c r="T36" s="590">
+      <c r="T36" s="551">
         <v>0</v>
       </c>
-      <c r="U36" s="590"/>
+      <c r="U36" s="551"/>
       <c r="V36" s="218">
         <v>6</v>
       </c>
-      <c r="W36" s="590">
+      <c r="W36" s="551">
         <v>1</v>
       </c>
-      <c r="X36" s="591"/>
+      <c r="X36" s="575"/>
       <c r="Y36" s="254">
         <v>10</v>
       </c>
@@ -29437,39 +29437,39 @@
       <c r="E37" s="125"/>
       <c r="F37" s="122"/>
       <c r="G37" s="188"/>
-      <c r="H37" s="619" t="s">
-        <v>152</v>
-      </c>
-      <c r="I37" s="620"/>
-      <c r="J37" s="621"/>
+      <c r="H37" s="568" t="s">
+        <v>151</v>
+      </c>
+      <c r="I37" s="569"/>
+      <c r="J37" s="570"/>
       <c r="K37" s="132"/>
-      <c r="L37" s="584" t="s">
+      <c r="L37" s="579" t="s">
         <v>401</v>
       </c>
-      <c r="M37" s="585"/>
-      <c r="N37" s="586"/>
-      <c r="O37" s="590">
+      <c r="M37" s="547"/>
+      <c r="N37" s="548"/>
+      <c r="O37" s="551">
         <v>0</v>
       </c>
-      <c r="P37" s="590"/>
-      <c r="Q37" s="590">
+      <c r="P37" s="551"/>
+      <c r="Q37" s="551">
         <v>0</v>
       </c>
-      <c r="R37" s="590"/>
+      <c r="R37" s="551"/>
       <c r="S37" s="218">
         <v>0</v>
       </c>
-      <c r="T37" s="590">
+      <c r="T37" s="551">
         <v>0</v>
       </c>
-      <c r="U37" s="590"/>
+      <c r="U37" s="551"/>
       <c r="V37" s="218">
         <v>3</v>
       </c>
-      <c r="W37" s="590">
+      <c r="W37" s="551">
         <v>3</v>
       </c>
-      <c r="X37" s="591"/>
+      <c r="X37" s="575"/>
       <c r="Y37" s="254">
         <v>3</v>
       </c>
@@ -29487,39 +29487,39 @@
       <c r="I38" s="125"/>
       <c r="J38" s="220"/>
       <c r="K38" s="132"/>
-      <c r="L38" s="603" t="s">
-        <v>148</v>
-      </c>
-      <c r="M38" s="604"/>
-      <c r="N38" s="605"/>
-      <c r="O38" s="592">
+      <c r="L38" s="587" t="s">
+        <v>147</v>
+      </c>
+      <c r="M38" s="588"/>
+      <c r="N38" s="589"/>
+      <c r="O38" s="552">
         <f>SUM(O29:P37)</f>
         <v>13</v>
       </c>
-      <c r="P38" s="592"/>
-      <c r="Q38" s="592">
+      <c r="P38" s="552"/>
+      <c r="Q38" s="552">
         <f>SUM(Q29:R37)</f>
         <v>4</v>
       </c>
-      <c r="R38" s="592"/>
+      <c r="R38" s="552"/>
       <c r="S38" s="255">
         <f>SUM(S29:S37)</f>
         <v>16</v>
       </c>
-      <c r="T38" s="592">
+      <c r="T38" s="552">
         <f>SUM(T29:U37)</f>
         <v>9</v>
       </c>
-      <c r="U38" s="592"/>
+      <c r="U38" s="552"/>
       <c r="V38" s="255">
         <f>SUM(V29:V37)</f>
         <v>35</v>
       </c>
-      <c r="W38" s="592">
+      <c r="W38" s="552">
         <f>SUM(W29:X37)</f>
         <v>8</v>
       </c>
-      <c r="X38" s="592"/>
+      <c r="X38" s="552"/>
       <c r="Y38" s="256">
         <f>SUM(Y29:Y37)</f>
         <v>64</v>
@@ -29535,26 +29535,26 @@
       <c r="E39" s="125"/>
       <c r="F39" s="122"/>
       <c r="G39" s="189"/>
-      <c r="H39" s="613">
+      <c r="H39" s="544">
         <f>S38</f>
         <v>16</v>
       </c>
-      <c r="I39" s="614"/>
-      <c r="J39" s="615"/>
+      <c r="I39" s="545"/>
+      <c r="J39" s="546"/>
       <c r="K39" s="132"/>
-      <c r="L39" s="598"/>
-      <c r="M39" s="606"/>
-      <c r="N39" s="607"/>
-      <c r="O39" s="598"/>
-      <c r="P39" s="599"/>
-      <c r="Q39" s="611"/>
-      <c r="R39" s="612"/>
+      <c r="L39" s="582"/>
+      <c r="M39" s="590"/>
+      <c r="N39" s="591"/>
+      <c r="O39" s="582"/>
+      <c r="P39" s="583"/>
+      <c r="Q39" s="565"/>
+      <c r="R39" s="566"/>
       <c r="S39" s="150"/>
-      <c r="T39" s="639"/>
-      <c r="U39" s="639"/>
+      <c r="T39" s="553"/>
+      <c r="U39" s="553"/>
       <c r="V39" s="150"/>
-      <c r="W39" s="639"/>
-      <c r="X39" s="639"/>
+      <c r="W39" s="553"/>
+      <c r="X39" s="553"/>
       <c r="Y39" s="181"/>
       <c r="Z39" s="125"/>
       <c r="AA39" s="122"/>
@@ -29571,19 +29571,19 @@
       <c r="I40" s="125"/>
       <c r="J40" s="220"/>
       <c r="K40" s="132"/>
-      <c r="L40" s="608"/>
-      <c r="M40" s="609"/>
-      <c r="N40" s="610"/>
-      <c r="O40" s="600"/>
-      <c r="P40" s="597"/>
-      <c r="Q40" s="596"/>
-      <c r="R40" s="597"/>
+      <c r="L40" s="555"/>
+      <c r="M40" s="592"/>
+      <c r="N40" s="556"/>
+      <c r="O40" s="584"/>
+      <c r="P40" s="581"/>
+      <c r="Q40" s="580"/>
+      <c r="R40" s="581"/>
       <c r="S40" s="125"/>
-      <c r="T40" s="640"/>
-      <c r="U40" s="640"/>
+      <c r="T40" s="554"/>
+      <c r="U40" s="554"/>
       <c r="V40" s="125"/>
-      <c r="W40" s="640"/>
-      <c r="X40" s="640"/>
+      <c r="W40" s="554"/>
+      <c r="X40" s="554"/>
       <c r="Y40" s="193"/>
       <c r="Z40" s="125"/>
     </row>
@@ -29599,19 +29599,19 @@
       <c r="I41" s="221"/>
       <c r="J41" s="191"/>
       <c r="K41" s="132"/>
-      <c r="L41" s="608"/>
-      <c r="M41" s="609"/>
-      <c r="N41" s="610"/>
-      <c r="O41" s="601"/>
-      <c r="P41" s="602"/>
-      <c r="Q41" s="608"/>
-      <c r="R41" s="610"/>
+      <c r="L41" s="555"/>
+      <c r="M41" s="592"/>
+      <c r="N41" s="556"/>
+      <c r="O41" s="585"/>
+      <c r="P41" s="586"/>
+      <c r="Q41" s="555"/>
+      <c r="R41" s="556"/>
       <c r="S41" s="125"/>
-      <c r="T41" s="608"/>
-      <c r="U41" s="610"/>
+      <c r="T41" s="555"/>
+      <c r="U41" s="556"/>
       <c r="V41" s="125"/>
-      <c r="W41" s="608"/>
-      <c r="X41" s="610"/>
+      <c r="W41" s="555"/>
+      <c r="X41" s="556"/>
       <c r="Y41" s="193"/>
       <c r="Z41" s="125"/>
       <c r="AA41" s="146"/>
@@ -29628,21 +29628,21 @@
       <c r="I42" s="152"/>
       <c r="J42" s="152"/>
       <c r="K42" s="122"/>
-      <c r="L42" s="593"/>
-      <c r="M42" s="594"/>
-      <c r="N42" s="595"/>
-      <c r="O42" s="611"/>
-      <c r="P42" s="612"/>
+      <c r="L42" s="576"/>
+      <c r="M42" s="577"/>
+      <c r="N42" s="578"/>
+      <c r="O42" s="565"/>
+      <c r="P42" s="566"/>
       <c r="Q42" s="125"/>
-      <c r="R42" s="637" t="s">
-        <v>207</v>
-      </c>
-      <c r="S42" s="638"/>
+      <c r="R42" s="549" t="s">
+        <v>206</v>
+      </c>
+      <c r="S42" s="550"/>
       <c r="T42" s="151"/>
-      <c r="U42" s="641"/>
-      <c r="V42" s="642"/>
-      <c r="W42" s="641"/>
-      <c r="X42" s="642"/>
+      <c r="U42" s="557"/>
+      <c r="V42" s="558"/>
+      <c r="W42" s="557"/>
+      <c r="X42" s="558"/>
       <c r="Y42" s="193"/>
       <c r="Z42" s="125"/>
       <c r="AA42" s="122"/>
@@ -29655,26 +29655,26 @@
       <c r="E43" s="125"/>
       <c r="F43" s="122"/>
       <c r="G43" s="188"/>
-      <c r="H43" s="644" t="s">
-        <v>164</v>
-      </c>
-      <c r="I43" s="644"/>
-      <c r="J43" s="645"/>
+      <c r="H43" s="560" t="s">
+        <v>163</v>
+      </c>
+      <c r="I43" s="560"/>
+      <c r="J43" s="561"/>
       <c r="K43" s="132"/>
       <c r="L43" s="188"/>
       <c r="M43" s="219"/>
-      <c r="N43" s="628" t="s">
-        <v>154</v>
-      </c>
-      <c r="O43" s="629"/>
-      <c r="P43" s="630"/>
+      <c r="N43" s="535" t="s">
+        <v>153</v>
+      </c>
+      <c r="O43" s="536"/>
+      <c r="P43" s="537"/>
       <c r="Q43" s="189"/>
       <c r="R43" s="387" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S43" s="400"/>
       <c r="T43" s="397" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="U43" s="388"/>
       <c r="V43" s="388"/>
@@ -29721,28 +29721,28 @@
       <c r="E45" s="125"/>
       <c r="F45" s="122"/>
       <c r="G45" s="189"/>
-      <c r="H45" s="613">
+      <c r="H45" s="544">
         <f>SUM(V38)</f>
         <v>35</v>
       </c>
-      <c r="I45" s="614"/>
-      <c r="J45" s="615"/>
+      <c r="I45" s="545"/>
+      <c r="J45" s="546"/>
       <c r="K45" s="132"/>
       <c r="L45" s="189"/>
       <c r="M45" s="125"/>
       <c r="N45" s="125"/>
-      <c r="O45" s="631">
+      <c r="O45" s="538">
         <f>SUM(Q38,T38,W38)</f>
         <v>21</v>
       </c>
-      <c r="P45" s="632"/>
+      <c r="P45" s="539"/>
       <c r="Q45" s="189"/>
       <c r="R45" s="388" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="S45" s="398"/>
       <c r="T45" s="396" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="U45" s="397"/>
       <c r="V45" s="390"/>
@@ -29767,8 +29767,8 @@
       <c r="L46" s="189"/>
       <c r="M46" s="125"/>
       <c r="N46" s="125"/>
-      <c r="O46" s="633"/>
-      <c r="P46" s="634"/>
+      <c r="O46" s="540"/>
+      <c r="P46" s="541"/>
       <c r="Q46" s="189"/>
       <c r="R46" s="389"/>
       <c r="S46" s="404"/>
@@ -29799,11 +29799,11 @@
       <c r="O47" s="221"/>
       <c r="P47" s="191"/>
       <c r="R47" s="396" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S47" s="395"/>
       <c r="T47" s="396" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="U47" s="397"/>
       <c r="V47" s="390"/>
@@ -29879,9 +29879,9 @@
       <c r="E50" s="125"/>
       <c r="F50" s="122"/>
       <c r="G50" s="222"/>
-      <c r="H50" s="635"/>
-      <c r="I50" s="635"/>
-      <c r="J50" s="636"/>
+      <c r="H50" s="542"/>
+      <c r="I50" s="542"/>
+      <c r="J50" s="543"/>
       <c r="K50" s="123"/>
       <c r="L50" s="150"/>
       <c r="M50" s="150"/>
@@ -29936,9 +29936,9 @@
       <c r="E52" s="125"/>
       <c r="F52" s="125"/>
       <c r="G52" s="125"/>
-      <c r="H52" s="643"/>
-      <c r="I52" s="643"/>
-      <c r="J52" s="643"/>
+      <c r="H52" s="559"/>
+      <c r="I52" s="559"/>
+      <c r="J52" s="559"/>
       <c r="K52" s="125"/>
       <c r="L52" s="125"/>
       <c r="M52" s="125"/>
@@ -30039,11 +30039,11 @@
       <c r="U55" s="122"/>
       <c r="V55" s="125"/>
       <c r="W55" s="125"/>
-      <c r="X55" s="625"/>
-      <c r="Y55" s="626"/>
-      <c r="Z55" s="626"/>
-      <c r="AA55" s="626"/>
-      <c r="AB55" s="627"/>
+      <c r="X55" s="532"/>
+      <c r="Y55" s="533"/>
+      <c r="Z55" s="533"/>
+      <c r="AA55" s="533"/>
+      <c r="AB55" s="534"/>
     </row>
     <row r="56" spans="1:28" ht="23.25" hidden="1">
       <c r="A56" s="125"/>
@@ -30259,11 +30259,11 @@
       <c r="P63" s="125"/>
       <c r="Q63" s="122"/>
       <c r="R63" s="122"/>
-      <c r="U63" s="625"/>
-      <c r="V63" s="626"/>
-      <c r="W63" s="626"/>
-      <c r="X63" s="626"/>
-      <c r="Y63" s="627"/>
+      <c r="U63" s="532"/>
+      <c r="V63" s="533"/>
+      <c r="W63" s="533"/>
+      <c r="X63" s="533"/>
+      <c r="Y63" s="534"/>
       <c r="Z63" s="125"/>
     </row>
     <row r="64" spans="1:28" ht="23.25">
@@ -30699,6 +30699,178 @@
     </row>
   </sheetData>
   <mergeCells count="196">
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="V12:W13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="B1:Y1"/>
+    <mergeCell ref="B3:Y3"/>
+    <mergeCell ref="B4:Y4"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="X12:Y13"/>
+    <mergeCell ref="R11:Y11"/>
+    <mergeCell ref="G10:Y10"/>
+    <mergeCell ref="G11:H13"/>
+    <mergeCell ref="I11:K13"/>
+    <mergeCell ref="L11:N13"/>
+    <mergeCell ref="O11:Q13"/>
+    <mergeCell ref="R12:S13"/>
+    <mergeCell ref="T12:U13"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="W27:X28"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="V27:V28"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Y27:Y28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="W29:X29"/>
+    <mergeCell ref="T27:U28"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="L27:N28"/>
+    <mergeCell ref="W31:X31"/>
+    <mergeCell ref="W32:X32"/>
+    <mergeCell ref="W33:X33"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="W35:X35"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="W38:X38"/>
+    <mergeCell ref="L42:N42"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="L40:N40"/>
+    <mergeCell ref="L41:N41"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="O27:P28"/>
+    <mergeCell ref="Q27:R28"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="L26:Y26"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="T32:U32"/>
+    <mergeCell ref="T33:U33"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="Q36:R36"/>
     <mergeCell ref="U63:Y63"/>
     <mergeCell ref="X55:AB55"/>
     <mergeCell ref="N43:P43"/>
@@ -30723,178 +30895,6 @@
     <mergeCell ref="W41:X41"/>
     <mergeCell ref="W42:X42"/>
     <mergeCell ref="H43:J43"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="O42:P42"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="O27:P28"/>
-    <mergeCell ref="Q27:R28"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="L26:Y26"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="T32:U32"/>
-    <mergeCell ref="T33:U33"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="W37:X37"/>
-    <mergeCell ref="W38:X38"/>
-    <mergeCell ref="L42:N42"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="L40:N40"/>
-    <mergeCell ref="L41:N41"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="W29:X29"/>
-    <mergeCell ref="T27:U28"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="L27:N28"/>
-    <mergeCell ref="W31:X31"/>
-    <mergeCell ref="W32:X32"/>
-    <mergeCell ref="W33:X33"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="W35:X35"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Y27:Y28"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="V27:V28"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="W27:X28"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="X15:Y15"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="V12:W13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="B1:Y1"/>
-    <mergeCell ref="B3:Y3"/>
-    <mergeCell ref="B4:Y4"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="X12:Y13"/>
-    <mergeCell ref="R11:Y11"/>
-    <mergeCell ref="G10:Y10"/>
-    <mergeCell ref="G11:H13"/>
-    <mergeCell ref="I11:K13"/>
-    <mergeCell ref="L11:N13"/>
-    <mergeCell ref="O11:Q13"/>
-    <mergeCell ref="R12:S13"/>
-    <mergeCell ref="T12:U13"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="T16:U16"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:E15">
     <cfRule type="expression" dxfId="5" priority="10">
@@ -30935,7 +30935,7 @@
   <sheetData>
     <row r="2" spans="1:6">
       <c r="B2" s="648" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C2" s="648"/>
       <c r="D2" s="648"/>
@@ -30944,7 +30944,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="B3" s="649" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C3" s="649"/>
       <c r="D3" s="649"/>
@@ -30953,19 +30953,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="B4" s="115" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="115" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="D4" s="115" t="s">
         <v>168</v>
       </c>
-      <c r="D4" s="115" t="s">
+      <c r="E4" s="115" t="s">
         <v>169</v>
       </c>
-      <c r="E4" s="115" t="s">
+      <c r="F4" s="115" t="s">
         <v>170</v>
-      </c>
-      <c r="F4" s="115" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -31088,13 +31088,13 @@
     </row>
     <row r="14" spans="1:6" ht="15.75">
       <c r="C14" s="293" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D14" s="293" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E14" s="294" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -31229,7 +31229,7 @@
         <v>72</v>
       </c>
       <c r="G26" s="646" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H26" s="647">
         <v>5</v>
@@ -31536,7 +31536,7 @@
       <c r="I70" s="647"/>
       <c r="J70" s="646"/>
       <c r="K70" s="646" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="71" spans="8:11">
@@ -31689,23 +31689,23 @@
   <sheetData>
     <row r="1" spans="1:21" ht="21">
       <c r="A1" s="125"/>
-      <c r="B1" s="650" t="s">
-        <v>179</v>
-      </c>
-      <c r="C1" s="651"/>
-      <c r="D1" s="651"/>
-      <c r="E1" s="651"/>
-      <c r="F1" s="651"/>
-      <c r="G1" s="651"/>
-      <c r="H1" s="651"/>
-      <c r="I1" s="651"/>
-      <c r="J1" s="651"/>
-      <c r="K1" s="651"/>
-      <c r="L1" s="651"/>
-      <c r="M1" s="651"/>
-      <c r="N1" s="651"/>
-      <c r="O1" s="651"/>
-      <c r="P1" s="652"/>
+      <c r="B1" s="685" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="686"/>
+      <c r="D1" s="686"/>
+      <c r="E1" s="686"/>
+      <c r="F1" s="686"/>
+      <c r="G1" s="686"/>
+      <c r="H1" s="686"/>
+      <c r="I1" s="686"/>
+      <c r="J1" s="686"/>
+      <c r="K1" s="686"/>
+      <c r="L1" s="686"/>
+      <c r="M1" s="686"/>
+      <c r="N1" s="686"/>
+      <c r="O1" s="686"/>
+      <c r="P1" s="687"/>
       <c r="Q1" s="125"/>
       <c r="R1" s="125"/>
       <c r="S1" s="125"/>
@@ -31714,23 +31714,23 @@
     </row>
     <row r="2" spans="1:21" ht="18" customHeight="1">
       <c r="A2" s="125"/>
-      <c r="B2" s="653" t="s">
-        <v>180</v>
-      </c>
-      <c r="C2" s="654"/>
-      <c r="D2" s="654"/>
-      <c r="E2" s="654"/>
-      <c r="F2" s="654"/>
-      <c r="G2" s="654"/>
-      <c r="H2" s="654"/>
-      <c r="I2" s="654"/>
-      <c r="J2" s="654"/>
-      <c r="K2" s="654"/>
-      <c r="L2" s="654"/>
-      <c r="M2" s="654"/>
-      <c r="N2" s="654"/>
-      <c r="O2" s="654"/>
-      <c r="P2" s="655"/>
+      <c r="B2" s="688" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2" s="689"/>
+      <c r="D2" s="689"/>
+      <c r="E2" s="689"/>
+      <c r="F2" s="689"/>
+      <c r="G2" s="689"/>
+      <c r="H2" s="689"/>
+      <c r="I2" s="689"/>
+      <c r="J2" s="689"/>
+      <c r="K2" s="689"/>
+      <c r="L2" s="689"/>
+      <c r="M2" s="689"/>
+      <c r="N2" s="689"/>
+      <c r="O2" s="689"/>
+      <c r="P2" s="690"/>
       <c r="Q2" s="125"/>
       <c r="R2" s="125"/>
       <c r="S2" s="125"/>
@@ -31771,14 +31771,14 @@
       <c r="H4" s="123"/>
       <c r="I4" s="131"/>
       <c r="J4" s="278"/>
-      <c r="K4" s="668" t="s">
-        <v>220</v>
-      </c>
-      <c r="L4" s="668"/>
-      <c r="M4" s="668"/>
-      <c r="N4" s="668"/>
-      <c r="O4" s="668"/>
-      <c r="P4" s="668"/>
+      <c r="K4" s="678" t="s">
+        <v>219</v>
+      </c>
+      <c r="L4" s="678"/>
+      <c r="M4" s="678"/>
+      <c r="N4" s="678"/>
+      <c r="O4" s="678"/>
+      <c r="P4" s="678"/>
       <c r="Q4" s="125"/>
       <c r="R4" s="125"/>
       <c r="S4" s="125"/>
@@ -31791,18 +31791,18 @@
       <c r="H5" s="122"/>
       <c r="I5" s="125"/>
       <c r="J5" s="279"/>
-      <c r="K5" s="664" t="s">
-        <v>182</v>
-      </c>
-      <c r="L5" s="664"/>
-      <c r="M5" s="664" t="s">
+      <c r="K5" s="695" t="s">
+        <v>181</v>
+      </c>
+      <c r="L5" s="695"/>
+      <c r="M5" s="695" t="s">
+        <v>184</v>
+      </c>
+      <c r="N5" s="695"/>
+      <c r="O5" s="695" t="s">
         <v>185</v>
       </c>
-      <c r="N5" s="664"/>
-      <c r="O5" s="664" t="s">
-        <v>186</v>
-      </c>
-      <c r="P5" s="664"/>
+      <c r="P5" s="695"/>
       <c r="Q5" s="123"/>
       <c r="R5" s="125"/>
       <c r="S5" s="125"/>
@@ -31815,18 +31815,18 @@
       <c r="H6" s="122"/>
       <c r="I6" s="125"/>
       <c r="J6" s="122"/>
-      <c r="K6" s="679" t="s">
-        <v>197</v>
-      </c>
-      <c r="L6" s="660"/>
-      <c r="M6" s="659" t="s">
+      <c r="K6" s="674" t="s">
+        <v>196</v>
+      </c>
+      <c r="L6" s="675"/>
+      <c r="M6" s="694" t="s">
         <v>404</v>
       </c>
-      <c r="N6" s="660"/>
-      <c r="O6" s="659" t="s">
-        <v>159</v>
-      </c>
-      <c r="P6" s="665"/>
+      <c r="N6" s="675"/>
+      <c r="O6" s="694" t="s">
+        <v>158</v>
+      </c>
+      <c r="P6" s="696"/>
       <c r="Q6" s="123"/>
       <c r="R6" s="125"/>
       <c r="S6" s="125"/>
@@ -31837,24 +31837,24 @@
       <c r="A7" s="125"/>
       <c r="C7" s="125"/>
       <c r="D7" s="125"/>
-      <c r="E7" s="666"/>
-      <c r="F7" s="667"/>
-      <c r="G7" s="667"/>
-      <c r="H7" s="667"/>
+      <c r="E7" s="676"/>
+      <c r="F7" s="677"/>
+      <c r="G7" s="677"/>
+      <c r="H7" s="677"/>
       <c r="I7" s="125"/>
       <c r="J7" s="146"/>
-      <c r="K7" s="669" t="s">
-        <v>197</v>
-      </c>
-      <c r="L7" s="662"/>
-      <c r="M7" s="661" t="s">
+      <c r="K7" s="670" t="s">
+        <v>196</v>
+      </c>
+      <c r="L7" s="667"/>
+      <c r="M7" s="666" t="s">
         <v>405</v>
       </c>
-      <c r="N7" s="662"/>
-      <c r="O7" s="661" t="s">
-        <v>159</v>
-      </c>
-      <c r="P7" s="663"/>
+      <c r="N7" s="667"/>
+      <c r="O7" s="666" t="s">
+        <v>158</v>
+      </c>
+      <c r="P7" s="673"/>
       <c r="Q7" s="123"/>
       <c r="R7" s="125"/>
       <c r="S7" s="125"/>
@@ -31868,18 +31868,18 @@
       <c r="D8" s="125"/>
       <c r="I8" s="125"/>
       <c r="J8" s="122"/>
-      <c r="K8" s="669" t="s">
-        <v>196</v>
-      </c>
-      <c r="L8" s="662"/>
-      <c r="M8" s="661" t="s">
+      <c r="K8" s="670" t="s">
+        <v>195</v>
+      </c>
+      <c r="L8" s="667"/>
+      <c r="M8" s="666" t="s">
         <v>406</v>
       </c>
-      <c r="N8" s="662"/>
-      <c r="O8" s="661" t="s">
-        <v>159</v>
-      </c>
-      <c r="P8" s="663"/>
+      <c r="N8" s="667"/>
+      <c r="O8" s="666" t="s">
+        <v>158</v>
+      </c>
+      <c r="P8" s="673"/>
       <c r="Q8" s="123"/>
       <c r="R8" s="125"/>
       <c r="S8" s="125"/>
@@ -31893,18 +31893,18 @@
       <c r="D9" s="125"/>
       <c r="I9" s="125"/>
       <c r="J9" s="146"/>
-      <c r="K9" s="669" t="s">
-        <v>196</v>
-      </c>
-      <c r="L9" s="662"/>
-      <c r="M9" s="661" t="s">
+      <c r="K9" s="670" t="s">
+        <v>195</v>
+      </c>
+      <c r="L9" s="667"/>
+      <c r="M9" s="666" t="s">
         <v>407</v>
       </c>
-      <c r="N9" s="662"/>
-      <c r="O9" s="661" t="s">
-        <v>159</v>
-      </c>
-      <c r="P9" s="663"/>
+      <c r="N9" s="667"/>
+      <c r="O9" s="666" t="s">
+        <v>158</v>
+      </c>
+      <c r="P9" s="673"/>
       <c r="Q9" s="123"/>
       <c r="R9" s="125"/>
       <c r="S9" s="125"/>
@@ -31918,18 +31918,18 @@
       <c r="D10" s="125"/>
       <c r="I10" s="125"/>
       <c r="J10" s="122"/>
-      <c r="K10" s="669" t="s">
-        <v>196</v>
-      </c>
-      <c r="L10" s="662"/>
-      <c r="M10" s="661" t="s">
+      <c r="K10" s="670" t="s">
+        <v>195</v>
+      </c>
+      <c r="L10" s="667"/>
+      <c r="M10" s="666" t="s">
         <v>408</v>
       </c>
-      <c r="N10" s="662"/>
-      <c r="O10" s="661" t="s">
-        <v>159</v>
-      </c>
-      <c r="P10" s="663"/>
+      <c r="N10" s="667"/>
+      <c r="O10" s="666" t="s">
+        <v>158</v>
+      </c>
+      <c r="P10" s="673"/>
       <c r="Q10" s="123"/>
       <c r="R10" s="125"/>
       <c r="S10" s="125"/>
@@ -31941,26 +31941,26 @@
       <c r="B11" s="125"/>
       <c r="C11" s="125"/>
       <c r="D11" s="122"/>
-      <c r="E11" s="656" t="s">
-        <v>184</v>
-      </c>
-      <c r="F11" s="657"/>
-      <c r="G11" s="657"/>
-      <c r="H11" s="658"/>
+      <c r="E11" s="691" t="s">
+        <v>183</v>
+      </c>
+      <c r="F11" s="692"/>
+      <c r="G11" s="692"/>
+      <c r="H11" s="693"/>
       <c r="I11" s="123"/>
       <c r="J11" s="146"/>
-      <c r="K11" s="669" t="s">
+      <c r="K11" s="670" t="s">
         <v>402</v>
       </c>
-      <c r="L11" s="662"/>
-      <c r="M11" s="661" t="s">
+      <c r="L11" s="667"/>
+      <c r="M11" s="666" t="s">
         <v>409</v>
       </c>
-      <c r="N11" s="662"/>
-      <c r="O11" s="661" t="s">
-        <v>159</v>
-      </c>
-      <c r="P11" s="663"/>
+      <c r="N11" s="667"/>
+      <c r="O11" s="666" t="s">
+        <v>158</v>
+      </c>
+      <c r="P11" s="673"/>
       <c r="Q11" s="123"/>
       <c r="R11" s="125"/>
       <c r="S11" s="125"/>
@@ -31972,28 +31972,28 @@
       <c r="B12" s="125"/>
       <c r="C12" s="125"/>
       <c r="D12" s="122"/>
-      <c r="E12" s="670" t="s">
+      <c r="E12" s="679" t="s">
+        <v>181</v>
+      </c>
+      <c r="F12" s="680"/>
+      <c r="G12" s="681"/>
+      <c r="H12" s="288" t="s">
         <v>182</v>
-      </c>
-      <c r="F12" s="671"/>
-      <c r="G12" s="672"/>
-      <c r="H12" s="288" t="s">
-        <v>183</v>
       </c>
       <c r="I12" s="123"/>
       <c r="J12" s="146"/>
-      <c r="K12" s="669" t="s">
+      <c r="K12" s="670" t="s">
         <v>402</v>
       </c>
-      <c r="L12" s="662"/>
-      <c r="M12" s="661" t="s">
+      <c r="L12" s="667"/>
+      <c r="M12" s="666" t="s">
         <v>410</v>
       </c>
-      <c r="N12" s="662"/>
-      <c r="O12" s="661" t="s">
+      <c r="N12" s="667"/>
+      <c r="O12" s="666" t="s">
         <v>417</v>
       </c>
-      <c r="P12" s="663"/>
+      <c r="P12" s="673"/>
       <c r="Q12" s="123"/>
       <c r="R12" s="125"/>
       <c r="S12" s="125"/>
@@ -32005,28 +32005,28 @@
       <c r="B13" s="125"/>
       <c r="C13" s="125"/>
       <c r="D13" s="122"/>
-      <c r="E13" s="673" t="s">
-        <v>199</v>
-      </c>
-      <c r="F13" s="674"/>
-      <c r="G13" s="675"/>
+      <c r="E13" s="682" t="s">
+        <v>198</v>
+      </c>
+      <c r="F13" s="683"/>
+      <c r="G13" s="684"/>
       <c r="H13" s="343">
         <v>2</v>
       </c>
       <c r="I13" s="123"/>
       <c r="J13" s="122"/>
-      <c r="K13" s="669" t="s">
+      <c r="K13" s="670" t="s">
         <v>403</v>
       </c>
-      <c r="L13" s="662"/>
-      <c r="M13" s="661" t="s">
+      <c r="L13" s="667"/>
+      <c r="M13" s="666" t="s">
         <v>411</v>
       </c>
-      <c r="N13" s="662"/>
-      <c r="O13" s="661" t="s">
-        <v>159</v>
-      </c>
-      <c r="P13" s="663"/>
+      <c r="N13" s="667"/>
+      <c r="O13" s="666" t="s">
+        <v>158</v>
+      </c>
+      <c r="P13" s="673"/>
       <c r="Q13" s="123"/>
       <c r="R13" s="125"/>
       <c r="S13" s="125"/>
@@ -32038,28 +32038,28 @@
       <c r="B14" s="125"/>
       <c r="C14" s="125"/>
       <c r="D14" s="122"/>
-      <c r="E14" s="676" t="s">
-        <v>197</v>
-      </c>
-      <c r="F14" s="677"/>
-      <c r="G14" s="678"/>
+      <c r="E14" s="656" t="s">
+        <v>196</v>
+      </c>
+      <c r="F14" s="657"/>
+      <c r="G14" s="658"/>
       <c r="H14" s="344">
         <v>26</v>
       </c>
       <c r="I14" s="123"/>
       <c r="J14" s="130"/>
-      <c r="K14" s="669" t="s">
+      <c r="K14" s="670" t="s">
         <v>403</v>
       </c>
-      <c r="L14" s="662"/>
-      <c r="M14" s="661" t="s">
+      <c r="L14" s="667"/>
+      <c r="M14" s="666" t="s">
         <v>412</v>
       </c>
-      <c r="N14" s="662"/>
-      <c r="O14" s="661" t="s">
-        <v>159</v>
-      </c>
-      <c r="P14" s="663"/>
+      <c r="N14" s="667"/>
+      <c r="O14" s="666" t="s">
+        <v>158</v>
+      </c>
+      <c r="P14" s="673"/>
       <c r="Q14" s="123"/>
       <c r="R14" s="125"/>
       <c r="S14" s="125"/>
@@ -32071,28 +32071,28 @@
       <c r="B15" s="125"/>
       <c r="C15" s="125"/>
       <c r="D15" s="122"/>
-      <c r="E15" s="676" t="s">
-        <v>198</v>
-      </c>
-      <c r="F15" s="677"/>
-      <c r="G15" s="678"/>
+      <c r="E15" s="656" t="s">
+        <v>197</v>
+      </c>
+      <c r="F15" s="657"/>
+      <c r="G15" s="658"/>
       <c r="H15" s="344">
         <v>5</v>
       </c>
       <c r="I15" s="123"/>
       <c r="J15" s="122"/>
-      <c r="K15" s="669" t="s">
-        <v>196</v>
-      </c>
-      <c r="L15" s="662"/>
-      <c r="M15" s="661" t="s">
+      <c r="K15" s="670" t="s">
+        <v>195</v>
+      </c>
+      <c r="L15" s="667"/>
+      <c r="M15" s="666" t="s">
         <v>413</v>
       </c>
-      <c r="N15" s="662"/>
-      <c r="O15" s="661" t="s">
-        <v>159</v>
-      </c>
-      <c r="P15" s="663"/>
+      <c r="N15" s="667"/>
+      <c r="O15" s="666" t="s">
+        <v>158</v>
+      </c>
+      <c r="P15" s="673"/>
       <c r="Q15" s="123"/>
       <c r="R15" s="125"/>
       <c r="S15" s="125"/>
@@ -32104,28 +32104,28 @@
       <c r="B16" s="125"/>
       <c r="C16" s="125"/>
       <c r="D16" s="122"/>
-      <c r="E16" s="676" t="s">
-        <v>200</v>
-      </c>
-      <c r="F16" s="677"/>
-      <c r="G16" s="678"/>
+      <c r="E16" s="656" t="s">
+        <v>199</v>
+      </c>
+      <c r="F16" s="657"/>
+      <c r="G16" s="658"/>
       <c r="H16" s="344">
         <v>29</v>
       </c>
       <c r="I16" s="123"/>
       <c r="J16" s="146"/>
-      <c r="K16" s="669" t="s">
-        <v>196</v>
-      </c>
-      <c r="L16" s="662"/>
-      <c r="M16" s="661" t="s">
+      <c r="K16" s="670" t="s">
+        <v>195</v>
+      </c>
+      <c r="L16" s="667"/>
+      <c r="M16" s="666" t="s">
         <v>414</v>
       </c>
-      <c r="N16" s="662"/>
-      <c r="O16" s="661" t="s">
-        <v>159</v>
-      </c>
-      <c r="P16" s="663"/>
+      <c r="N16" s="667"/>
+      <c r="O16" s="666" t="s">
+        <v>158</v>
+      </c>
+      <c r="P16" s="673"/>
       <c r="Q16" s="123"/>
       <c r="R16" s="125"/>
       <c r="S16" s="125"/>
@@ -32135,28 +32135,28 @@
     <row r="17" spans="1:21" ht="66" customHeight="1">
       <c r="A17" s="122"/>
       <c r="D17" s="141"/>
-      <c r="E17" s="676" t="s">
-        <v>201</v>
-      </c>
-      <c r="F17" s="677"/>
-      <c r="G17" s="678"/>
+      <c r="E17" s="656" t="s">
+        <v>200</v>
+      </c>
+      <c r="F17" s="657"/>
+      <c r="G17" s="658"/>
       <c r="H17" s="344">
         <v>6</v>
       </c>
       <c r="I17" s="123"/>
       <c r="J17" s="146"/>
-      <c r="K17" s="669" t="s">
-        <v>198</v>
-      </c>
-      <c r="L17" s="662"/>
-      <c r="M17" s="661" t="s">
+      <c r="K17" s="670" t="s">
+        <v>197</v>
+      </c>
+      <c r="L17" s="667"/>
+      <c r="M17" s="666" t="s">
         <v>415</v>
       </c>
-      <c r="N17" s="662"/>
-      <c r="O17" s="661" t="s">
+      <c r="N17" s="667"/>
+      <c r="O17" s="666" t="s">
         <v>417</v>
       </c>
-      <c r="P17" s="663"/>
+      <c r="P17" s="673"/>
       <c r="Q17" s="123"/>
       <c r="R17" s="125"/>
       <c r="S17" s="125"/>
@@ -32167,28 +32167,28 @@
       <c r="A18" s="122"/>
       <c r="C18" s="150"/>
       <c r="D18" s="122"/>
-      <c r="E18" s="688" t="s">
-        <v>202</v>
-      </c>
-      <c r="F18" s="689"/>
-      <c r="G18" s="690"/>
+      <c r="E18" s="659" t="s">
+        <v>201</v>
+      </c>
+      <c r="F18" s="660"/>
+      <c r="G18" s="661"/>
       <c r="H18" s="345">
         <v>25</v>
       </c>
       <c r="I18" s="123"/>
       <c r="J18" s="122"/>
-      <c r="K18" s="696" t="s">
-        <v>198</v>
-      </c>
-      <c r="L18" s="695"/>
-      <c r="M18" s="680" t="s">
+      <c r="K18" s="671" t="s">
+        <v>197</v>
+      </c>
+      <c r="L18" s="669"/>
+      <c r="M18" s="668" t="s">
         <v>416</v>
       </c>
-      <c r="N18" s="695"/>
-      <c r="O18" s="680" t="s">
+      <c r="N18" s="669"/>
+      <c r="O18" s="668" t="s">
         <v>417</v>
       </c>
-      <c r="P18" s="681"/>
+      <c r="P18" s="672"/>
       <c r="Q18" s="123"/>
       <c r="R18" s="125"/>
       <c r="S18" s="122"/>
@@ -32220,10 +32220,10 @@
     <row r="20" spans="1:21" ht="56.25" customHeight="1" thickBot="1">
       <c r="A20" s="122"/>
       <c r="B20" s="332" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C20" s="282" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D20" s="281"/>
       <c r="E20" s="133"/>
@@ -32268,7 +32268,7 @@
     <row r="22" spans="1:21" ht="35.25" customHeight="1" thickBot="1">
       <c r="A22" s="122"/>
       <c r="B22" s="331" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C22" s="334">
         <v>2</v>
@@ -32276,13 +32276,13 @@
       <c r="D22" s="311"/>
       <c r="E22" s="320"/>
       <c r="F22" s="342" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G22" s="319"/>
-      <c r="H22" s="691" t="s">
-        <v>187</v>
-      </c>
-      <c r="I22" s="692"/>
+      <c r="H22" s="662" t="s">
+        <v>186</v>
+      </c>
+      <c r="I22" s="663"/>
       <c r="J22" s="328"/>
       <c r="K22" s="338"/>
       <c r="L22" s="316"/>
@@ -32298,7 +32298,7 @@
     <row r="23" spans="1:21" ht="35.25" customHeight="1" thickBot="1">
       <c r="A23" s="122"/>
       <c r="B23" s="284" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C23" s="285">
         <v>26</v>
@@ -32330,7 +32330,7 @@
     <row r="24" spans="1:21" ht="35.25" customHeight="1" thickBot="1">
       <c r="A24" s="122"/>
       <c r="B24" s="286" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C24" s="287">
         <v>5</v>
@@ -32356,7 +32356,7 @@
     <row r="25" spans="1:21" ht="33" customHeight="1" thickBot="1">
       <c r="A25" s="122"/>
       <c r="B25" s="286" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C25" s="287">
         <v>29</v>
@@ -32368,7 +32368,7 @@
       <c r="I25" s="201"/>
       <c r="J25" s="122"/>
       <c r="K25" s="429" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L25" s="219"/>
       <c r="M25" s="428"/>
@@ -32383,7 +32383,7 @@
     <row r="26" spans="1:21" ht="44.25" customHeight="1">
       <c r="A26" s="122"/>
       <c r="B26" s="286" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C26" s="287">
         <v>6</v>
@@ -32391,19 +32391,19 @@
       <c r="D26" s="311"/>
       <c r="E26" s="325"/>
       <c r="F26" s="341" t="s">
-        <v>188</v>
-      </c>
-      <c r="H26" s="693" t="s">
-        <v>216</v>
-      </c>
-      <c r="I26" s="694"/>
+        <v>187</v>
+      </c>
+      <c r="H26" s="664" t="s">
+        <v>215</v>
+      </c>
+      <c r="I26" s="665"/>
       <c r="J26" s="427"/>
-      <c r="K26" s="682" t="s">
-        <v>219</v>
-      </c>
-      <c r="L26" s="683"/>
-      <c r="M26" s="683"/>
-      <c r="N26" s="684"/>
+      <c r="K26" s="650" t="s">
+        <v>218</v>
+      </c>
+      <c r="L26" s="651"/>
+      <c r="M26" s="651"/>
+      <c r="N26" s="652"/>
       <c r="O26" s="123"/>
       <c r="P26" s="220"/>
       <c r="Q26" s="123"/>
@@ -32414,7 +32414,7 @@
     <row r="27" spans="1:21" ht="36.75" customHeight="1" thickBot="1">
       <c r="A27" s="122"/>
       <c r="B27" s="290" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C27" s="291">
         <v>25</v>
@@ -32431,12 +32431,12 @@
       </c>
       <c r="I27" s="283"/>
       <c r="J27" s="280"/>
-      <c r="K27" s="685" t="s">
-        <v>218</v>
-      </c>
-      <c r="L27" s="686"/>
-      <c r="M27" s="686"/>
-      <c r="N27" s="687"/>
+      <c r="K27" s="653" t="s">
+        <v>217</v>
+      </c>
+      <c r="L27" s="654"/>
+      <c r="M27" s="654"/>
+      <c r="N27" s="655"/>
       <c r="O27" s="221"/>
       <c r="P27" s="191"/>
       <c r="Q27" s="123"/>
@@ -32883,32 +32883,22 @@
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="K4:P4"/>
     <mergeCell ref="M15:N15"/>
@@ -32925,22 +32915,32 @@
     <mergeCell ref="K13:L13"/>
     <mergeCell ref="K14:L14"/>
     <mergeCell ref="K15:L15"/>
-    <mergeCell ref="B1:P1"/>
-    <mergeCell ref="B2:P2"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K18:L18"/>
   </mergeCells>
   <phoneticPr fontId="33" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -32964,16 +32964,16 @@
   <sheetData>
     <row r="2" spans="1:4" ht="18.75">
       <c r="A2" s="346" t="s">
+        <v>188</v>
+      </c>
+      <c r="B2" s="346" t="s">
         <v>189</v>
       </c>
-      <c r="B2" s="346" t="s">
+      <c r="C2" s="346" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="346" t="s">
+      <c r="D2" s="346" t="s">
         <v>191</v>
-      </c>
-      <c r="D2" s="346" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="27.75" customHeight="1">
@@ -33213,14 +33213,14 @@
       <c r="G2" s="351"/>
       <c r="H2" s="351"/>
       <c r="I2" s="351"/>
-      <c r="J2" s="462" t="s">
-        <v>206</v>
-      </c>
-      <c r="K2" s="462"/>
-      <c r="L2" s="462"/>
-      <c r="M2" s="462"/>
-      <c r="N2" s="462"/>
-      <c r="O2" s="462"/>
+      <c r="J2" s="472" t="s">
+        <v>205</v>
+      </c>
+      <c r="K2" s="472"/>
+      <c r="L2" s="472"/>
+      <c r="M2" s="472"/>
+      <c r="N2" s="472"/>
+      <c r="O2" s="472"/>
       <c r="P2" s="351"/>
       <c r="Q2" s="351"/>
       <c r="R2" s="351"/>
@@ -33250,7 +33250,7 @@
     <row r="4" spans="1:19" ht="33" customHeight="1">
       <c r="A4" s="44"/>
       <c r="B4" s="352" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C4" s="352"/>
       <c r="D4" s="352"/>
@@ -33259,16 +33259,16 @@
       <c r="G4" s="352"/>
       <c r="H4" s="352"/>
       <c r="I4" s="352" t="s">
+        <v>203</v>
+      </c>
+      <c r="J4" s="471" t="s">
         <v>204</v>
       </c>
-      <c r="J4" s="461" t="s">
-        <v>205</v>
-      </c>
-      <c r="K4" s="461"/>
-      <c r="L4" s="461"/>
-      <c r="M4" s="461"/>
-      <c r="N4" s="461"/>
-      <c r="O4" s="461"/>
+      <c r="K4" s="471"/>
+      <c r="L4" s="471"/>
+      <c r="M4" s="471"/>
+      <c r="N4" s="471"/>
+      <c r="O4" s="471"/>
       <c r="P4" s="262"/>
       <c r="Q4" s="262"/>
       <c r="R4" s="263"/>
@@ -33284,17 +33284,17 @@
       <c r="G5" s="353"/>
       <c r="H5" s="353"/>
       <c r="I5" s="355"/>
-      <c r="J5" s="472" t="s">
-        <v>177</v>
-      </c>
-      <c r="K5" s="472"/>
-      <c r="L5" s="472"/>
-      <c r="M5" s="472"/>
-      <c r="N5" s="469" t="s">
+      <c r="J5" s="464" t="s">
+        <v>176</v>
+      </c>
+      <c r="K5" s="464"/>
+      <c r="L5" s="464"/>
+      <c r="M5" s="464"/>
+      <c r="N5" s="476" t="s">
         <v>221</v>
       </c>
-      <c r="O5" s="469"/>
-      <c r="P5" s="469"/>
+      <c r="O5" s="476"/>
+      <c r="P5" s="476"/>
       <c r="Q5" s="354"/>
       <c r="R5" s="354"/>
       <c r="S5" s="43"/>
@@ -33325,12 +33325,12 @@
     </row>
     <row r="8" spans="1:19" ht="45.75" customHeight="1" thickBot="1">
       <c r="A8" s="44"/>
-      <c r="C8" s="473" t="str">
+      <c r="C8" s="467" t="str">
         <f>_xlfn.CONCAT("PERIODO ", N5)</f>
-        <v>PERIODO ENERO - 2025</v>
-      </c>
-      <c r="D8" s="474"/>
-      <c r="E8" s="475"/>
+        <v>PERIODO FEBRERO - 2025</v>
+      </c>
+      <c r="D8" s="468"/>
+      <c r="E8" s="469"/>
       <c r="G8" s="92" t="s">
         <v>1</v>
       </c>
@@ -33373,11 +33373,11 @@
     </row>
     <row r="10" spans="1:19" ht="42" customHeight="1">
       <c r="A10" s="44"/>
-      <c r="C10" s="476" t="s">
+      <c r="C10" s="470" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="476"/>
-      <c r="E10" s="476"/>
+      <c r="D10" s="470"/>
+      <c r="E10" s="470"/>
       <c r="G10" s="119" t="s">
         <v>8</v>
       </c>
@@ -33551,11 +33551,11 @@
       <c r="C15" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="471">
+      <c r="D15" s="462">
         <f>R14</f>
         <v>107</v>
       </c>
-      <c r="E15" s="471"/>
+      <c r="E15" s="462"/>
       <c r="H15" s="71"/>
       <c r="M15" s="71"/>
       <c r="N15" s="71"/>
@@ -33598,11 +33598,11 @@
     </row>
     <row r="24" spans="1:19" ht="50.25" customHeight="1">
       <c r="A24" s="44"/>
-      <c r="C24" s="464" t="s">
+      <c r="C24" s="473" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="465"/>
-      <c r="E24" s="466"/>
+      <c r="D24" s="474"/>
+      <c r="E24" s="475"/>
       <c r="S24" s="43"/>
     </row>
     <row r="25" spans="1:19" ht="32.25" customHeight="1">
@@ -33610,11 +33610,11 @@
       <c r="C25" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="467">
+      <c r="D25" s="465">
         <f>SUM(M13:O13)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="468"/>
+      <c r="E25" s="466"/>
       <c r="S25" s="43"/>
     </row>
     <row r="26" spans="1:19" ht="33.75" customHeight="1">
@@ -33622,11 +33622,11 @@
       <c r="C26" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="467">
+      <c r="D26" s="465">
         <f>SUM(M12:O12)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="468"/>
+      <c r="E26" s="466"/>
       <c r="S26" s="43"/>
     </row>
     <row r="27" spans="1:19" ht="38.25" customHeight="1">
@@ -33658,11 +33658,11 @@
       <c r="C29" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="470">
+      <c r="D29" s="461">
         <f>SUM(M14:O14)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="470"/>
+      <c r="E29" s="461"/>
       <c r="S29" s="43"/>
     </row>
     <row r="30" spans="1:19">
@@ -33776,6 +33776,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="J4:O4"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="N5:P5"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D27:E27"/>
@@ -33787,12 +33793,6 @@
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="D11:E11"/>
-    <mergeCell ref="J4:O4"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="N5:P5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -34391,7 +34391,7 @@
     </row>
     <row r="2" spans="1:27" ht="37.15" customHeight="1">
       <c r="A2" s="477" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B2" s="478"/>
       <c r="C2" s="478"/>
@@ -38164,10 +38164,10 @@
         <v>39</v>
       </c>
       <c r="D3" s="114" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="114" t="s">
         <v>129</v>
-      </c>
-      <c r="E3" s="114" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -40036,9 +40036,9 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27" customHeight="1">
       <c r="A1" s="141"/>
-      <c r="B1" s="521"/>
-      <c r="C1" s="522"/>
-      <c r="D1" s="523"/>
+      <c r="B1" s="523"/>
+      <c r="C1" s="524"/>
+      <c r="D1" s="525"/>
       <c r="E1" s="122"/>
       <c r="F1" s="125"/>
       <c r="G1" s="123"/>
@@ -40062,10 +40062,10 @@
       <c r="H2" s="125" t="s">
         <v>384</v>
       </c>
-      <c r="I2" s="530" t="s">
+      <c r="I2" s="519" t="s">
         <v>123</v>
       </c>
-      <c r="J2" s="531"/>
+      <c r="J2" s="520"/>
       <c r="K2" s="136"/>
       <c r="L2" s="125"/>
       <c r="M2" s="133"/>
@@ -40118,10 +40118,10 @@
       <c r="B5" s="184" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="524" t="s">
+      <c r="C5" s="526" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="525"/>
+      <c r="D5" s="527"/>
       <c r="E5" s="266" t="s">
         <v>110</v>
       </c>
@@ -40132,7 +40132,7 @@
         <v>111</v>
       </c>
       <c r="H5" s="267" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I5" s="267" t="s">
         <v>112</v>
@@ -40151,10 +40151,10 @@
       <c r="B6" s="295" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="526">
+      <c r="C6" s="528">
         <v>44725</v>
       </c>
-      <c r="D6" s="527"/>
+      <c r="D6" s="529"/>
       <c r="E6" s="450">
         <v>44908</v>
       </c>
@@ -40186,10 +40186,10 @@
       <c r="B7" s="296" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="528">
+      <c r="C7" s="530">
         <v>37484</v>
       </c>
-      <c r="D7" s="529"/>
+      <c r="D7" s="531"/>
       <c r="E7" s="451">
         <v>44608</v>
       </c>
@@ -40219,10 +40219,10 @@
       <c r="B8" s="296" t="s">
         <v>116</v>
       </c>
-      <c r="C8" s="528">
+      <c r="C8" s="530">
         <v>44868</v>
       </c>
-      <c r="D8" s="529"/>
+      <c r="D8" s="531"/>
       <c r="E8" s="451">
         <v>45049</v>
       </c>
@@ -40253,10 +40253,10 @@
       <c r="B9" s="296" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="528">
+      <c r="C9" s="530">
         <v>45439</v>
       </c>
-      <c r="D9" s="529"/>
+      <c r="D9" s="531"/>
       <c r="E9" s="451">
         <v>45623</v>
       </c>
@@ -40288,10 +40288,10 @@
       <c r="B10" s="296" t="s">
         <v>118</v>
       </c>
-      <c r="C10" s="528">
+      <c r="C10" s="530">
         <v>44900</v>
       </c>
-      <c r="D10" s="529"/>
+      <c r="D10" s="531"/>
       <c r="E10" s="451">
         <v>45082</v>
       </c>
@@ -40322,10 +40322,10 @@
       <c r="B11" s="296" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="528">
+      <c r="C11" s="530">
         <v>44930</v>
       </c>
-      <c r="D11" s="529"/>
+      <c r="D11" s="531"/>
       <c r="E11" s="451">
         <v>45111</v>
       </c>
@@ -40356,10 +40356,10 @@
       <c r="B12" s="297" t="s">
         <v>120</v>
       </c>
-      <c r="C12" s="516">
+      <c r="C12" s="521">
         <v>44958</v>
       </c>
-      <c r="D12" s="517"/>
+      <c r="D12" s="522"/>
       <c r="E12" s="452">
         <v>45139</v>
       </c>
@@ -40405,11 +40405,11 @@
     <row r="14" spans="1:17" ht="30.75" customHeight="1">
       <c r="A14" s="147"/>
       <c r="B14" s="413" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C14" s="433"/>
       <c r="D14" s="412" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E14" s="175"/>
       <c r="F14" s="176"/>
@@ -40444,20 +40444,20 @@
     <row r="16" spans="1:17" ht="74.25" customHeight="1" thickBot="1">
       <c r="A16" s="147"/>
       <c r="B16" s="415" t="s">
-        <v>124</v>
+        <v>220</v>
       </c>
       <c r="C16" s="435"/>
       <c r="D16" s="421" t="s">
         <v>114</v>
       </c>
-      <c r="E16" s="518" t="s">
+      <c r="E16" s="516" t="s">
         <v>378</v>
       </c>
-      <c r="F16" s="519"/>
-      <c r="G16" s="519"/>
-      <c r="H16" s="519"/>
-      <c r="I16" s="519"/>
-      <c r="J16" s="520"/>
+      <c r="F16" s="517"/>
+      <c r="G16" s="517"/>
+      <c r="H16" s="517"/>
+      <c r="I16" s="517"/>
+      <c r="J16" s="518"/>
       <c r="K16" s="438"/>
       <c r="L16" s="161"/>
       <c r="M16" s="159"/>
@@ -40467,20 +40467,20 @@
     <row r="17" spans="1:16" ht="108.75" customHeight="1" thickBot="1">
       <c r="A17" s="130"/>
       <c r="B17" s="416" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C17" s="436"/>
       <c r="D17" s="421" t="s">
         <v>115</v>
       </c>
-      <c r="E17" s="518" t="s">
+      <c r="E17" s="516" t="s">
         <v>379</v>
       </c>
-      <c r="F17" s="519"/>
-      <c r="G17" s="519"/>
-      <c r="H17" s="519"/>
-      <c r="I17" s="519"/>
-      <c r="J17" s="520"/>
+      <c r="F17" s="517"/>
+      <c r="G17" s="517"/>
+      <c r="H17" s="517"/>
+      <c r="I17" s="517"/>
+      <c r="J17" s="518"/>
       <c r="K17" s="189"/>
       <c r="L17" s="172"/>
       <c r="M17" s="161"/>
@@ -40491,20 +40491,20 @@
     <row r="18" spans="1:16" ht="87" customHeight="1" thickBot="1">
       <c r="A18" s="148"/>
       <c r="B18" s="416" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C18" s="436"/>
       <c r="D18" s="422" t="s">
         <v>116</v>
       </c>
-      <c r="E18" s="518" t="s">
+      <c r="E18" s="516" t="s">
         <v>380</v>
       </c>
-      <c r="F18" s="519"/>
-      <c r="G18" s="519"/>
-      <c r="H18" s="519"/>
-      <c r="I18" s="519"/>
-      <c r="J18" s="520"/>
+      <c r="F18" s="517"/>
+      <c r="G18" s="517"/>
+      <c r="H18" s="517"/>
+      <c r="I18" s="517"/>
+      <c r="J18" s="518"/>
       <c r="L18" s="161"/>
       <c r="M18" s="157"/>
       <c r="N18" s="156"/>
@@ -40518,14 +40518,14 @@
       <c r="D19" s="423" t="s">
         <v>117</v>
       </c>
-      <c r="E19" s="518" t="s">
+      <c r="E19" s="516" t="s">
         <v>381</v>
       </c>
-      <c r="F19" s="519"/>
-      <c r="G19" s="519"/>
-      <c r="H19" s="519"/>
-      <c r="I19" s="519"/>
-      <c r="J19" s="520"/>
+      <c r="F19" s="517"/>
+      <c r="G19" s="517"/>
+      <c r="H19" s="517"/>
+      <c r="I19" s="517"/>
+      <c r="J19" s="518"/>
       <c r="K19" s="189"/>
       <c r="L19" s="172"/>
       <c r="M19" s="157"/>
@@ -40539,14 +40539,14 @@
       <c r="D20" s="422" t="s">
         <v>118</v>
       </c>
-      <c r="E20" s="518" t="s">
+      <c r="E20" s="516" t="s">
         <v>378</v>
       </c>
-      <c r="F20" s="519"/>
-      <c r="G20" s="519"/>
-      <c r="H20" s="519"/>
-      <c r="I20" s="519"/>
-      <c r="J20" s="520"/>
+      <c r="F20" s="517"/>
+      <c r="G20" s="517"/>
+      <c r="H20" s="517"/>
+      <c r="I20" s="517"/>
+      <c r="J20" s="518"/>
       <c r="K20" s="439"/>
       <c r="L20" s="424"/>
       <c r="M20" s="160"/>
@@ -40559,14 +40559,14 @@
       <c r="D21" s="425" t="s">
         <v>119</v>
       </c>
-      <c r="E21" s="518" t="s">
+      <c r="E21" s="516" t="s">
         <v>382</v>
       </c>
-      <c r="F21" s="519"/>
-      <c r="G21" s="519"/>
-      <c r="H21" s="519"/>
-      <c r="I21" s="519"/>
-      <c r="J21" s="520"/>
+      <c r="F21" s="517"/>
+      <c r="G21" s="517"/>
+      <c r="H21" s="517"/>
+      <c r="I21" s="517"/>
+      <c r="J21" s="518"/>
       <c r="K21" s="440"/>
       <c r="L21" s="94"/>
       <c r="M21" s="158"/>
@@ -40580,14 +40580,14 @@
       <c r="D22" s="441" t="s">
         <v>120</v>
       </c>
-      <c r="E22" s="518" t="s">
+      <c r="E22" s="516" t="s">
         <v>383</v>
       </c>
-      <c r="F22" s="519"/>
-      <c r="G22" s="519"/>
-      <c r="H22" s="519"/>
-      <c r="I22" s="519"/>
-      <c r="J22" s="520"/>
+      <c r="F22" s="517"/>
+      <c r="G22" s="517"/>
+      <c r="H22" s="517"/>
+      <c r="I22" s="517"/>
+      <c r="J22" s="518"/>
       <c r="L22" s="158"/>
       <c r="M22" s="161"/>
       <c r="N22" s="161"/>
@@ -41005,11 +41005,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="E21:J21"/>
-    <mergeCell ref="E16:J16"/>
-    <mergeCell ref="E17:J17"/>
-    <mergeCell ref="I2:J2"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="E20:J20"/>
     <mergeCell ref="E19:J19"/>
@@ -41022,6 +41017,11 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="E21:J21"/>
+    <mergeCell ref="E16:J16"/>
+    <mergeCell ref="E17:J17"/>
+    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="5" scale="47" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -41039,17 +41039,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010039E554BA5E2FA5449283D399C0FD5B7C" ma:contentTypeVersion="18" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="dd0678842d65e4207392abd035356b9c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xmlns:ns3="954542bb-2825-439d-9db6-a5c04d3b21fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d84746cc30da1fe182e7a313d44b54c" ns2:_="" ns3:_="">
     <xsd:import namespace="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
@@ -41304,6 +41293,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6AC9645-B568-450E-BF2C-C54CDA88D1C4}">
   <ds:schemaRefs>
@@ -41313,23 +41313,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83E8CA1-0683-49D4-9501-EE88776F2630}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
-    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE64779-B9F2-4AEC-A5E9-E8076DA89A71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41346,4 +41329,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83E8CA1-0683-49D4-9501-EE88776F2630}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
+    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Backend/output/informe_final.xlsx
+++ b/Backend/output/informe_final.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1A5CD4-4EA1-46E0-92E7-6C3E5ACCAEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8BDD170-A9EF-41E2-8339-2798E0624F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="733" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="733" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -13,8 +13,8 @@
     <sheet name="data_panel" sheetId="36" state="hidden" r:id="rId3"/>
     <sheet name="02-ESTADO NC" sheetId="20" r:id="rId4"/>
     <sheet name="03-  ESTADO REGIONES" sheetId="32" r:id="rId5"/>
-    <sheet name="data_status_NC" sheetId="33" r:id="rId6"/>
-    <sheet name="data_status_reg" sheetId="46" r:id="rId7"/>
+    <sheet name="data_status_NC" sheetId="33" state="hidden" r:id="rId6"/>
+    <sheet name="data_status_reg" sheetId="46" state="hidden" r:id="rId7"/>
     <sheet name="Ev Proveedores" sheetId="43" r:id="rId8"/>
     <sheet name="Convenios ADP" sheetId="45" r:id="rId9"/>
     <sheet name="Gestión de riesgos" sheetId="48" r:id="rId10"/>
@@ -1283,7 +1283,7 @@
     <t>Acum FEBRERO - 2025</t>
   </si>
   <si>
-    <t>Hitos ADP ocurridos al 20 de FEBRERO</t>
+    <t>Hitos ADP ocurridos al 21 de FEBRERO</t>
   </si>
   <si>
     <t>Política de Gestión de Riesgos</t>
@@ -1435,7 +1435,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="90">
+  <fonts count="89">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2072,12 +2072,6 @@
     <font>
       <b/>
       <sz val="16"/>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri Light"/>
       <family val="2"/>
     </font>
@@ -5490,7 +5484,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="703">
+  <cellXfs count="701">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -6399,7 +6393,13 @@
     <xf numFmtId="49" fontId="20" fillId="24" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="20" fillId="24" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="20" fillId="24" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="24" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6528,15 +6528,42 @@
     <xf numFmtId="0" fontId="70" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="78" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6546,36 +6573,9 @@
     <xf numFmtId="0" fontId="34" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="80" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -6693,21 +6693,27 @@
     <xf numFmtId="0" fontId="31" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="243" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="149" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="150" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="69" fillId="0" borderId="123" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="124" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="243" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="149" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="150" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6735,23 +6741,266 @@
     <xf numFmtId="0" fontId="69" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="144" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="145" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="120" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="15" borderId="175" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="142" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="143" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="15" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="173" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="174" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -6759,9 +7008,6 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6813,9 +7059,6 @@
     <xf numFmtId="0" fontId="42" fillId="12" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="49" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -6840,249 +7083,6 @@
     <xf numFmtId="0" fontId="52" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="15" borderId="175" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="142" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="143" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="15" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="173" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="174" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="144" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="145" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="120" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -7095,6 +7095,111 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="205" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="236" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="195" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="202" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="200" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="199" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="219" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="190" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="218" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="220" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="204" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="197" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="21" borderId="185" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="200" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="199" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="164" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="198" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="201" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="20" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7125,128 +7230,11 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="197" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="66" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="21" borderId="185" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="200" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="199" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="164" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="198" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="201" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="202" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="204" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="219" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="220" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="205" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="236" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="195" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="200" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="199" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="190" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="218" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="89" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="89" fillId="24" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="89" fillId="24" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="89" fillId="24" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -7257,17 +7245,7 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Porcentual 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <fill>
         <patternFill>
@@ -13000,7 +12978,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5D69A2AC-88B2-4715-AE75-26FC2580BC0A}" type="CELLRANGE">
+                    <a:fld id="{3175E1D9-2D5D-4C98-A330-AE0EF765B1FB}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13034,7 +13012,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{011955F1-6C67-4173-9CC8-34C073FFEB61}" type="CELLRANGE">
+                    <a:fld id="{A15D19F6-B3A8-42D4-9634-38BB377AB6AA}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13068,7 +13046,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3DFB889F-CC5C-496F-B10A-1B4C90F45E4C}" type="CELLRANGE">
+                    <a:fld id="{29E652C9-5A2E-4A1C-A4F3-AAEAE0F28D73}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13102,7 +13080,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{51525CDF-E966-469D-B63F-55D58F13C69E}" type="CELLRANGE">
+                    <a:fld id="{25E5A8A0-1677-430D-9D51-A0D4F3E53949}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13136,7 +13114,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5EAB0635-B315-4386-8176-E4F4B21F3E89}" type="CELLRANGE">
+                    <a:fld id="{AB18087C-B0B4-4FDA-B8D3-97E1A4C7F925}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13170,7 +13148,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B7D6BEF4-6CE1-4394-9F9E-3506A6E5906C}" type="CELLRANGE">
+                    <a:fld id="{5A8A8B55-3E58-4904-B1FF-D5B4C278A9CD}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13204,7 +13182,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CF7A05E7-B9B3-4501-93FA-4F83C350E91F}" type="CELLRANGE">
+                    <a:fld id="{74C8F4BF-18EC-4703-A454-CD4C9BCB682C}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13238,7 +13216,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{73A60FF0-ECC9-4B5C-BDEE-DAD2961125CA}" type="CELLRANGE">
+                    <a:fld id="{1677952B-0432-4CAD-909C-7909772240D4}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13272,7 +13250,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BDB7C72F-D8C6-4FBA-B91D-789CDB9748D2}" type="CELLRANGE">
+                    <a:fld id="{5B3C83E3-6461-45E8-B140-8A63C65E3081}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13306,7 +13284,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E4F57A9B-32BD-455D-B750-0B548BEC7531}" type="CELLRANGE">
+                    <a:fld id="{5B33D0CF-087A-405F-A2C3-C5F8DA68EED1}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13340,7 +13318,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{93E71F48-A884-4C17-B4AF-D0BB2AFBDF59}" type="CELLRANGE">
+                    <a:fld id="{7A9CB30D-2948-4BA6-8522-35849B103305}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13374,7 +13352,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{819B6384-932E-4F67-9BAE-063F79CEB93C}" type="CELLRANGE">
+                    <a:fld id="{3962EFBA-CD79-4E74-B811-50A0C808E94E}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13751,7 +13729,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E5854460-5BFF-4708-BF2A-DAA2D43576D2}" type="CELLRANGE">
+                    <a:fld id="{FBA4F8E7-DEBE-4EA4-8C13-5B51D231F7D4}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14475,7 +14453,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{E549B68B-5F96-4F05-A39A-60FA391015FD}" type="CELLRANGE">
+                    <a:fld id="{EC229AEE-9755-41C2-8D28-EA5B2D1F5154}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr>
                         <a:defRPr sz="1400">
@@ -14556,7 +14534,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6E1271F6-C0C5-42EF-B13F-E71CD331C6F3}" type="CELLRANGE">
+                    <a:fld id="{2C8E3F93-9497-42E9-8E23-FADEAA05BDD0}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -23309,7 +23287,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C3:D5" spid="_x0000_s286641"/>
+                  <a14:cameraTool cellRange="data_status_NC!C3:D5" spid="_x0000_s286633"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23365,7 +23343,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C20:D24" spid="_x0000_s286642"/>
+                  <a14:cameraTool cellRange="data_status_NC!C20:D24" spid="_x0000_s286634"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23430,7 +23408,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C7:D13" spid="_x0000_s286643"/>
+                  <a14:cameraTool cellRange="data_status_NC!C7:D13" spid="_x0000_s286635"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23495,7 +23473,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C15:D18" spid="_x0000_s286644"/>
+                  <a14:cameraTool cellRange="data_status_NC!C15:D18" spid="_x0000_s286636"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23560,7 +23538,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C26:D33" spid="_x0000_s286645"/>
+                  <a14:cameraTool cellRange="data_status_NC!C26:D33" spid="_x0000_s286637"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23625,7 +23603,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C35:D39" spid="_x0000_s286646"/>
+                  <a14:cameraTool cellRange="data_status_NC!C35:D39" spid="_x0000_s286638"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23690,7 +23668,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C41:D46" spid="_x0000_s286647"/>
+                  <a14:cameraTool cellRange="data_status_NC!C41:D46" spid="_x0000_s286639"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23755,7 +23733,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C48:D54" spid="_x0000_s286648"/>
+                  <a14:cameraTool cellRange="data_status_NC!C48:D54" spid="_x0000_s286640"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -26564,10 +26542,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{842C5F27-4ECE-41D4-B69D-721F29C3337F}" name="Tabla3" displayName="Tabla3" ref="B20:C27" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" totalsRowDxfId="15" headerRowBorderDxfId="18" tableBorderDxfId="16" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{842C5F27-4ECE-41D4-B69D-721F29C3337F}" name="Tabla3" displayName="Tabla3" ref="B20:C27" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" totalsRowDxfId="13" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="12">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{59BD1EC2-C3BB-43E8-A6F6-E914B455E7BB}" name="SUBSECRETARÍA/SERVICIO" dataDxfId="13" totalsRowDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{DF4BB275-2D51-45F7-8197-42C7331CDF0B}" name="NÚMERO DE PROGRAMAS 2024" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{59BD1EC2-C3BB-43E8-A6F6-E914B455E7BB}" name="SUBSECRETARÍA/SERVICIO" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{DF4BB275-2D51-45F7-8197-42C7331CDF0B}" name="NÚMERO DE PROGRAMAS 2024" dataDxfId="9" totalsRowDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -27139,10 +27117,10 @@
       <c r="F11" s="277" t="s">
         <v>192</v>
       </c>
-      <c r="G11" s="460">
+      <c r="G11" s="462">
         <v>2025</v>
       </c>
-      <c r="H11" s="460"/>
+      <c r="H11" s="462"/>
       <c r="I11" s="98"/>
       <c r="J11" s="98"/>
       <c r="K11" s="98"/>
@@ -27166,10 +27144,10 @@
       <c r="C12" s="98"/>
       <c r="D12" s="98"/>
       <c r="E12" s="278"/>
-      <c r="F12" s="461" t="s">
+      <c r="F12" s="463" t="s">
         <v>223</v>
       </c>
-      <c r="G12" s="462"/>
+      <c r="G12" s="464"/>
       <c r="H12" s="98"/>
       <c r="I12" s="98"/>
       <c r="J12" s="98"/>
@@ -27246,10 +27224,10 @@
       <c r="C15" s="98"/>
       <c r="D15" s="98"/>
       <c r="E15" s="275"/>
-      <c r="F15" s="458" t="s">
+      <c r="F15" s="460" t="s">
         <v>193</v>
       </c>
-      <c r="G15" s="458"/>
+      <c r="G15" s="460"/>
       <c r="H15" s="98"/>
       <c r="I15" s="98"/>
       <c r="J15" s="98"/>
@@ -27274,10 +27252,10 @@
       <c r="C16" s="98"/>
       <c r="D16" s="98"/>
       <c r="E16" s="275"/>
-      <c r="F16" s="458" t="s">
+      <c r="F16" s="460" t="s">
         <v>194</v>
       </c>
-      <c r="G16" s="458"/>
+      <c r="G16" s="460"/>
       <c r="H16" s="98"/>
       <c r="I16" s="98"/>
       <c r="J16" s="98"/>
@@ -27328,10 +27306,10 @@
       <c r="C18" s="98"/>
       <c r="D18" s="98"/>
       <c r="E18" s="274"/>
-      <c r="F18" s="459" t="s">
+      <c r="F18" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="G18" s="459"/>
+      <c r="G18" s="461"/>
       <c r="H18" s="98"/>
       <c r="I18" s="98"/>
       <c r="J18" s="98"/>
@@ -27974,32 +27952,32 @@
   <sheetData>
     <row r="1" spans="1:28" ht="29.25" customHeight="1" thickBot="1">
       <c r="A1" s="206"/>
-      <c r="B1" s="543" t="s">
+      <c r="B1" s="627" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="544"/>
-      <c r="D1" s="544"/>
-      <c r="E1" s="544"/>
-      <c r="F1" s="544"/>
-      <c r="G1" s="544"/>
-      <c r="H1" s="544"/>
-      <c r="I1" s="544"/>
-      <c r="J1" s="544"/>
-      <c r="K1" s="544"/>
-      <c r="L1" s="544"/>
-      <c r="M1" s="544"/>
-      <c r="N1" s="544"/>
-      <c r="O1" s="544"/>
-      <c r="P1" s="544"/>
-      <c r="Q1" s="544"/>
-      <c r="R1" s="544"/>
-      <c r="S1" s="544"/>
-      <c r="T1" s="544"/>
-      <c r="U1" s="544"/>
-      <c r="V1" s="544"/>
-      <c r="W1" s="544"/>
-      <c r="X1" s="544"/>
-      <c r="Y1" s="545"/>
+      <c r="C1" s="628"/>
+      <c r="D1" s="628"/>
+      <c r="E1" s="628"/>
+      <c r="F1" s="628"/>
+      <c r="G1" s="628"/>
+      <c r="H1" s="628"/>
+      <c r="I1" s="628"/>
+      <c r="J1" s="628"/>
+      <c r="K1" s="628"/>
+      <c r="L1" s="628"/>
+      <c r="M1" s="628"/>
+      <c r="N1" s="628"/>
+      <c r="O1" s="628"/>
+      <c r="P1" s="628"/>
+      <c r="Q1" s="628"/>
+      <c r="R1" s="628"/>
+      <c r="S1" s="628"/>
+      <c r="T1" s="628"/>
+      <c r="U1" s="628"/>
+      <c r="V1" s="628"/>
+      <c r="W1" s="628"/>
+      <c r="X1" s="628"/>
+      <c r="Y1" s="629"/>
       <c r="Z1" s="201"/>
     </row>
     <row r="2" spans="1:28" ht="9" customHeight="1" thickBot="1">
@@ -28035,32 +28013,32 @@
       <c r="A3" s="207" t="s">
         <v>173</v>
       </c>
-      <c r="B3" s="546" t="s">
+      <c r="B3" s="630" t="s">
         <v>213</v>
       </c>
-      <c r="C3" s="547"/>
-      <c r="D3" s="547"/>
-      <c r="E3" s="547"/>
-      <c r="F3" s="547"/>
-      <c r="G3" s="547"/>
-      <c r="H3" s="547"/>
-      <c r="I3" s="547"/>
-      <c r="J3" s="547"/>
-      <c r="K3" s="547"/>
-      <c r="L3" s="547"/>
-      <c r="M3" s="547"/>
-      <c r="N3" s="547"/>
-      <c r="O3" s="547"/>
-      <c r="P3" s="547"/>
-      <c r="Q3" s="547"/>
-      <c r="R3" s="547"/>
-      <c r="S3" s="547"/>
-      <c r="T3" s="547"/>
-      <c r="U3" s="547"/>
-      <c r="V3" s="547"/>
-      <c r="W3" s="547"/>
-      <c r="X3" s="547"/>
-      <c r="Y3" s="548"/>
+      <c r="C3" s="631"/>
+      <c r="D3" s="631"/>
+      <c r="E3" s="631"/>
+      <c r="F3" s="631"/>
+      <c r="G3" s="631"/>
+      <c r="H3" s="631"/>
+      <c r="I3" s="631"/>
+      <c r="J3" s="631"/>
+      <c r="K3" s="631"/>
+      <c r="L3" s="631"/>
+      <c r="M3" s="631"/>
+      <c r="N3" s="631"/>
+      <c r="O3" s="631"/>
+      <c r="P3" s="631"/>
+      <c r="Q3" s="631"/>
+      <c r="R3" s="631"/>
+      <c r="S3" s="631"/>
+      <c r="T3" s="631"/>
+      <c r="U3" s="631"/>
+      <c r="V3" s="631"/>
+      <c r="W3" s="631"/>
+      <c r="X3" s="631"/>
+      <c r="Y3" s="632"/>
       <c r="Z3" s="202"/>
       <c r="AA3" s="119"/>
     </row>
@@ -28068,32 +28046,32 @@
       <c r="A4" s="208" t="s">
         <v>174</v>
       </c>
-      <c r="B4" s="549" t="s">
+      <c r="B4" s="633" t="s">
         <v>223</v>
       </c>
-      <c r="C4" s="550"/>
-      <c r="D4" s="550"/>
-      <c r="E4" s="550"/>
-      <c r="F4" s="550"/>
-      <c r="G4" s="550"/>
-      <c r="H4" s="550"/>
-      <c r="I4" s="550"/>
-      <c r="J4" s="550"/>
-      <c r="K4" s="550"/>
-      <c r="L4" s="550"/>
-      <c r="M4" s="550"/>
-      <c r="N4" s="550"/>
-      <c r="O4" s="550"/>
-      <c r="P4" s="550"/>
-      <c r="Q4" s="550"/>
-      <c r="R4" s="550"/>
-      <c r="S4" s="550"/>
-      <c r="T4" s="550"/>
-      <c r="U4" s="550"/>
-      <c r="V4" s="550"/>
-      <c r="W4" s="550"/>
-      <c r="X4" s="550"/>
-      <c r="Y4" s="551"/>
+      <c r="C4" s="634"/>
+      <c r="D4" s="634"/>
+      <c r="E4" s="634"/>
+      <c r="F4" s="634"/>
+      <c r="G4" s="634"/>
+      <c r="H4" s="634"/>
+      <c r="I4" s="634"/>
+      <c r="J4" s="634"/>
+      <c r="K4" s="634"/>
+      <c r="L4" s="634"/>
+      <c r="M4" s="634"/>
+      <c r="N4" s="634"/>
+      <c r="O4" s="634"/>
+      <c r="P4" s="634"/>
+      <c r="Q4" s="634"/>
+      <c r="R4" s="634"/>
+      <c r="S4" s="634"/>
+      <c r="T4" s="634"/>
+      <c r="U4" s="634"/>
+      <c r="V4" s="634"/>
+      <c r="W4" s="634"/>
+      <c r="X4" s="634"/>
+      <c r="Y4" s="635"/>
       <c r="Z4" s="203"/>
       <c r="AA4" s="119"/>
     </row>
@@ -28128,40 +28106,40 @@
     </row>
     <row r="6" spans="1:28" ht="24.75" customHeight="1" thickBot="1">
       <c r="A6" s="209"/>
-      <c r="B6" s="555" t="s">
+      <c r="B6" s="639" t="s">
         <v>130</v>
       </c>
-      <c r="C6" s="556"/>
-      <c r="D6" s="556"/>
-      <c r="E6" s="557"/>
+      <c r="C6" s="640"/>
+      <c r="D6" s="640"/>
+      <c r="E6" s="641"/>
       <c r="F6" s="105"/>
       <c r="G6" s="168"/>
-      <c r="H6" s="575" t="s">
+      <c r="H6" s="605" t="s">
         <v>135</v>
       </c>
-      <c r="I6" s="576"/>
-      <c r="J6" s="576"/>
-      <c r="K6" s="577"/>
+      <c r="I6" s="606"/>
+      <c r="J6" s="606"/>
+      <c r="K6" s="607"/>
       <c r="L6" s="105"/>
       <c r="M6" s="168"/>
-      <c r="N6" s="583" t="s">
+      <c r="N6" s="617" t="s">
         <v>154</v>
       </c>
-      <c r="O6" s="584"/>
-      <c r="P6" s="585"/>
+      <c r="O6" s="618"/>
+      <c r="P6" s="619"/>
       <c r="Q6" s="175"/>
       <c r="R6" s="177"/>
-      <c r="S6" s="535" t="s">
+      <c r="S6" s="612" t="s">
         <v>136</v>
       </c>
-      <c r="T6" s="536"/>
+      <c r="T6" s="613"/>
       <c r="U6" s="178"/>
       <c r="V6" s="182"/>
       <c r="W6" s="169"/>
-      <c r="X6" s="535" t="s">
+      <c r="X6" s="612" t="s">
         <v>137</v>
       </c>
-      <c r="Y6" s="536"/>
+      <c r="Y6" s="613"/>
       <c r="Z6" s="96"/>
       <c r="AA6" s="119"/>
     </row>
@@ -28181,36 +28159,36 @@
       </c>
       <c r="F7" s="105"/>
       <c r="G7" s="135"/>
-      <c r="H7" s="571">
+      <c r="H7" s="614">
         <f>I23</f>
         <v>68</v>
       </c>
-      <c r="I7" s="582"/>
-      <c r="J7" s="582"/>
-      <c r="K7" s="572"/>
+      <c r="I7" s="616"/>
+      <c r="J7" s="616"/>
+      <c r="K7" s="615"/>
       <c r="L7" s="105"/>
       <c r="M7" s="135"/>
-      <c r="N7" s="567">
+      <c r="N7" s="620">
         <f>L23</f>
         <v>187</v>
       </c>
-      <c r="O7" s="568"/>
-      <c r="P7" s="569"/>
+      <c r="O7" s="621"/>
+      <c r="P7" s="622"/>
       <c r="Q7" s="176"/>
       <c r="R7" s="178"/>
-      <c r="S7" s="571">
+      <c r="S7" s="614">
         <f>O23</f>
         <v>473</v>
       </c>
-      <c r="T7" s="572"/>
+      <c r="T7" s="615"/>
       <c r="U7" s="105"/>
       <c r="V7" s="181"/>
       <c r="W7" s="98"/>
-      <c r="X7" s="571">
+      <c r="X7" s="614">
         <f>R23</f>
         <v>526</v>
       </c>
-      <c r="Y7" s="572"/>
+      <c r="Y7" s="615"/>
       <c r="Z7" s="167"/>
       <c r="AA7" s="119"/>
     </row>
@@ -28297,27 +28275,27 @@
       </c>
       <c r="E10" s="231"/>
       <c r="F10" s="105"/>
-      <c r="G10" s="563" t="s">
+      <c r="G10" s="646" t="s">
         <v>138</v>
       </c>
-      <c r="H10" s="564"/>
-      <c r="I10" s="564"/>
-      <c r="J10" s="564"/>
-      <c r="K10" s="564"/>
-      <c r="L10" s="564"/>
-      <c r="M10" s="564"/>
-      <c r="N10" s="564"/>
-      <c r="O10" s="564"/>
-      <c r="P10" s="564"/>
-      <c r="Q10" s="564"/>
-      <c r="R10" s="564"/>
-      <c r="S10" s="564"/>
-      <c r="T10" s="564"/>
-      <c r="U10" s="564"/>
-      <c r="V10" s="564"/>
-      <c r="W10" s="564"/>
-      <c r="X10" s="564"/>
-      <c r="Y10" s="565"/>
+      <c r="H10" s="647"/>
+      <c r="I10" s="647"/>
+      <c r="J10" s="647"/>
+      <c r="K10" s="647"/>
+      <c r="L10" s="647"/>
+      <c r="M10" s="647"/>
+      <c r="N10" s="647"/>
+      <c r="O10" s="647"/>
+      <c r="P10" s="647"/>
+      <c r="Q10" s="647"/>
+      <c r="R10" s="647"/>
+      <c r="S10" s="647"/>
+      <c r="T10" s="647"/>
+      <c r="U10" s="647"/>
+      <c r="V10" s="647"/>
+      <c r="W10" s="647"/>
+      <c r="X10" s="647"/>
+      <c r="Y10" s="648"/>
       <c r="Z10" s="96"/>
       <c r="AA10" s="119"/>
     </row>
@@ -28334,35 +28312,35 @@
       </c>
       <c r="E11" s="231"/>
       <c r="F11" s="105"/>
-      <c r="G11" s="566" t="s">
+      <c r="G11" s="649" t="s">
         <v>139</v>
       </c>
-      <c r="H11" s="561"/>
-      <c r="I11" s="561" t="s">
+      <c r="H11" s="644"/>
+      <c r="I11" s="644" t="s">
         <v>140</v>
       </c>
-      <c r="J11" s="561"/>
-      <c r="K11" s="561"/>
-      <c r="L11" s="561" t="s">
+      <c r="J11" s="644"/>
+      <c r="K11" s="644"/>
+      <c r="L11" s="644" t="s">
         <v>141</v>
       </c>
-      <c r="M11" s="561"/>
-      <c r="N11" s="561"/>
-      <c r="O11" s="561" t="s">
+      <c r="M11" s="644"/>
+      <c r="N11" s="644"/>
+      <c r="O11" s="644" t="s">
         <v>142</v>
       </c>
-      <c r="P11" s="561"/>
-      <c r="Q11" s="561"/>
-      <c r="R11" s="561" t="s">
+      <c r="P11" s="644"/>
+      <c r="Q11" s="644"/>
+      <c r="R11" s="644" t="s">
         <v>137</v>
       </c>
-      <c r="S11" s="561"/>
-      <c r="T11" s="561"/>
-      <c r="U11" s="561"/>
-      <c r="V11" s="561"/>
-      <c r="W11" s="561"/>
-      <c r="X11" s="561"/>
-      <c r="Y11" s="562"/>
+      <c r="S11" s="644"/>
+      <c r="T11" s="644"/>
+      <c r="U11" s="644"/>
+      <c r="V11" s="644"/>
+      <c r="W11" s="644"/>
+      <c r="X11" s="644"/>
+      <c r="Y11" s="645"/>
       <c r="Z11" s="96"/>
       <c r="AA11" s="119"/>
     </row>
@@ -28379,33 +28357,33 @@
       </c>
       <c r="E12" s="231"/>
       <c r="F12" s="105"/>
-      <c r="G12" s="566"/>
-      <c r="H12" s="561"/>
-      <c r="I12" s="561"/>
-      <c r="J12" s="561"/>
-      <c r="K12" s="561"/>
-      <c r="L12" s="561"/>
-      <c r="M12" s="561"/>
-      <c r="N12" s="561"/>
-      <c r="O12" s="561"/>
-      <c r="P12" s="561"/>
-      <c r="Q12" s="561"/>
-      <c r="R12" s="537" t="s">
+      <c r="G12" s="649"/>
+      <c r="H12" s="644"/>
+      <c r="I12" s="644"/>
+      <c r="J12" s="644"/>
+      <c r="K12" s="644"/>
+      <c r="L12" s="644"/>
+      <c r="M12" s="644"/>
+      <c r="N12" s="644"/>
+      <c r="O12" s="644"/>
+      <c r="P12" s="644"/>
+      <c r="Q12" s="644"/>
+      <c r="R12" s="571" t="s">
         <v>143</v>
       </c>
-      <c r="S12" s="537"/>
-      <c r="T12" s="537" t="s">
+      <c r="S12" s="571"/>
+      <c r="T12" s="571" t="s">
         <v>144</v>
       </c>
-      <c r="U12" s="537"/>
-      <c r="V12" s="537" t="s">
+      <c r="U12" s="571"/>
+      <c r="V12" s="571" t="s">
         <v>145</v>
       </c>
-      <c r="W12" s="537"/>
-      <c r="X12" s="537" t="s">
+      <c r="W12" s="571"/>
+      <c r="X12" s="571" t="s">
         <v>146</v>
       </c>
-      <c r="Y12" s="558"/>
+      <c r="Y12" s="602"/>
       <c r="Z12" s="96"/>
       <c r="AA12" s="95"/>
     </row>
@@ -28422,25 +28400,25 @@
       </c>
       <c r="E13" s="231"/>
       <c r="F13" s="105"/>
-      <c r="G13" s="566"/>
-      <c r="H13" s="561"/>
-      <c r="I13" s="561"/>
-      <c r="J13" s="561"/>
-      <c r="K13" s="561"/>
-      <c r="L13" s="561"/>
-      <c r="M13" s="561"/>
-      <c r="N13" s="561"/>
-      <c r="O13" s="561"/>
-      <c r="P13" s="561"/>
-      <c r="Q13" s="561"/>
-      <c r="R13" s="537"/>
-      <c r="S13" s="537"/>
-      <c r="T13" s="537"/>
-      <c r="U13" s="537"/>
-      <c r="V13" s="537"/>
-      <c r="W13" s="537"/>
-      <c r="X13" s="559"/>
-      <c r="Y13" s="560"/>
+      <c r="G13" s="649"/>
+      <c r="H13" s="644"/>
+      <c r="I13" s="644"/>
+      <c r="J13" s="644"/>
+      <c r="K13" s="644"/>
+      <c r="L13" s="644"/>
+      <c r="M13" s="644"/>
+      <c r="N13" s="644"/>
+      <c r="O13" s="644"/>
+      <c r="P13" s="644"/>
+      <c r="Q13" s="644"/>
+      <c r="R13" s="571"/>
+      <c r="S13" s="571"/>
+      <c r="T13" s="571"/>
+      <c r="U13" s="571"/>
+      <c r="V13" s="571"/>
+      <c r="W13" s="571"/>
+      <c r="X13" s="642"/>
+      <c r="Y13" s="643"/>
       <c r="Z13" s="96"/>
       <c r="AA13" s="97"/>
     </row>
@@ -28457,41 +28435,41 @@
       </c>
       <c r="E14" s="231"/>
       <c r="F14" s="105"/>
-      <c r="G14" s="538" t="s">
+      <c r="G14" s="623" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="539"/>
-      <c r="I14" s="540">
+      <c r="H14" s="624"/>
+      <c r="I14" s="601">
         <v>4</v>
       </c>
-      <c r="J14" s="541"/>
-      <c r="K14" s="542"/>
-      <c r="L14" s="534">
+      <c r="J14" s="625"/>
+      <c r="K14" s="626"/>
+      <c r="L14" s="599">
         <v>8</v>
       </c>
-      <c r="M14" s="534"/>
-      <c r="N14" s="534"/>
-      <c r="O14" s="534">
+      <c r="M14" s="599"/>
+      <c r="N14" s="599"/>
+      <c r="O14" s="599">
         <v>30</v>
       </c>
-      <c r="P14" s="534"/>
-      <c r="Q14" s="534"/>
-      <c r="R14" s="534">
+      <c r="P14" s="599"/>
+      <c r="Q14" s="599"/>
+      <c r="R14" s="599">
         <v>53</v>
       </c>
-      <c r="S14" s="534"/>
-      <c r="T14" s="534">
+      <c r="S14" s="599"/>
+      <c r="T14" s="599">
         <v>0</v>
       </c>
-      <c r="U14" s="534"/>
-      <c r="V14" s="534">
+      <c r="U14" s="599"/>
+      <c r="V14" s="599">
         <v>8</v>
       </c>
-      <c r="W14" s="540"/>
-      <c r="X14" s="534">
+      <c r="W14" s="601"/>
+      <c r="X14" s="599">
         <v>2</v>
       </c>
-      <c r="Y14" s="570"/>
+      <c r="Y14" s="600"/>
       <c r="Z14" s="96"/>
     </row>
     <row r="15" spans="1:28" ht="19.5" customHeight="1" thickBot="1">
@@ -28507,41 +28485,41 @@
       </c>
       <c r="E15" s="232"/>
       <c r="F15" s="105"/>
-      <c r="G15" s="538" t="s">
+      <c r="G15" s="623" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="539"/>
-      <c r="I15" s="540">
+      <c r="H15" s="624"/>
+      <c r="I15" s="601">
         <v>11</v>
       </c>
-      <c r="J15" s="541"/>
-      <c r="K15" s="542"/>
-      <c r="L15" s="534">
+      <c r="J15" s="625"/>
+      <c r="K15" s="626"/>
+      <c r="L15" s="599">
         <v>30</v>
       </c>
-      <c r="M15" s="534"/>
-      <c r="N15" s="534"/>
-      <c r="O15" s="534">
+      <c r="M15" s="599"/>
+      <c r="N15" s="599"/>
+      <c r="O15" s="599">
         <v>105</v>
       </c>
-      <c r="P15" s="534"/>
-      <c r="Q15" s="534"/>
-      <c r="R15" s="534">
+      <c r="P15" s="599"/>
+      <c r="Q15" s="599"/>
+      <c r="R15" s="599">
         <v>105</v>
       </c>
-      <c r="S15" s="534"/>
-      <c r="T15" s="534">
+      <c r="S15" s="599"/>
+      <c r="T15" s="599">
         <v>8</v>
       </c>
-      <c r="U15" s="534"/>
-      <c r="V15" s="534">
+      <c r="U15" s="599"/>
+      <c r="V15" s="599">
         <v>0</v>
       </c>
-      <c r="W15" s="540"/>
-      <c r="X15" s="534">
+      <c r="W15" s="601"/>
+      <c r="X15" s="599">
         <v>4</v>
       </c>
-      <c r="Y15" s="570"/>
+      <c r="Y15" s="600"/>
       <c r="Z15" s="96"/>
       <c r="AA15" s="119"/>
     </row>
@@ -28552,89 +28530,89 @@
       <c r="D16" s="125"/>
       <c r="E16" s="125"/>
       <c r="F16" s="95"/>
-      <c r="G16" s="538" t="s">
+      <c r="G16" s="623" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="539"/>
-      <c r="I16" s="540">
+      <c r="H16" s="624"/>
+      <c r="I16" s="601">
         <v>19</v>
       </c>
-      <c r="J16" s="541"/>
-      <c r="K16" s="542"/>
-      <c r="L16" s="534">
+      <c r="J16" s="625"/>
+      <c r="K16" s="626"/>
+      <c r="L16" s="599">
         <v>58</v>
       </c>
-      <c r="M16" s="534"/>
-      <c r="N16" s="534"/>
-      <c r="O16" s="534">
+      <c r="M16" s="599"/>
+      <c r="N16" s="599"/>
+      <c r="O16" s="599">
         <v>99</v>
       </c>
-      <c r="P16" s="534"/>
-      <c r="Q16" s="534"/>
-      <c r="R16" s="534">
+      <c r="P16" s="599"/>
+      <c r="Q16" s="599"/>
+      <c r="R16" s="599">
         <v>107</v>
       </c>
-      <c r="S16" s="534"/>
-      <c r="T16" s="534">
+      <c r="S16" s="599"/>
+      <c r="T16" s="599">
         <v>8</v>
       </c>
-      <c r="U16" s="534"/>
-      <c r="V16" s="534">
+      <c r="U16" s="599"/>
+      <c r="V16" s="599">
         <v>6</v>
       </c>
-      <c r="W16" s="540"/>
-      <c r="X16" s="534">
+      <c r="W16" s="601"/>
+      <c r="X16" s="599">
         <v>7</v>
       </c>
-      <c r="Y16" s="570"/>
+      <c r="Y16" s="600"/>
       <c r="Z16" s="96"/>
       <c r="AA16" s="119"/>
       <c r="AB16" s="226"/>
     </row>
     <row r="17" spans="1:27" ht="21" customHeight="1">
       <c r="A17" s="95"/>
-      <c r="B17" s="552" t="s">
+      <c r="B17" s="636" t="s">
         <v>148</v>
       </c>
-      <c r="C17" s="553"/>
-      <c r="D17" s="553"/>
-      <c r="E17" s="554"/>
+      <c r="C17" s="637"/>
+      <c r="D17" s="637"/>
+      <c r="E17" s="638"/>
       <c r="F17" s="105"/>
-      <c r="G17" s="538" t="s">
+      <c r="G17" s="623" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="539"/>
-      <c r="I17" s="540">
+      <c r="H17" s="624"/>
+      <c r="I17" s="601">
         <v>15</v>
       </c>
-      <c r="J17" s="541"/>
-      <c r="K17" s="542"/>
-      <c r="L17" s="534">
+      <c r="J17" s="625"/>
+      <c r="K17" s="626"/>
+      <c r="L17" s="599">
         <v>49</v>
       </c>
-      <c r="M17" s="534"/>
-      <c r="N17" s="534"/>
-      <c r="O17" s="534">
+      <c r="M17" s="599"/>
+      <c r="N17" s="599"/>
+      <c r="O17" s="599">
         <v>127</v>
       </c>
-      <c r="P17" s="534"/>
-      <c r="Q17" s="534"/>
-      <c r="R17" s="534">
+      <c r="P17" s="599"/>
+      <c r="Q17" s="599"/>
+      <c r="R17" s="599">
         <v>134</v>
       </c>
-      <c r="S17" s="534"/>
-      <c r="T17" s="534">
+      <c r="S17" s="599"/>
+      <c r="T17" s="599">
         <v>12</v>
       </c>
-      <c r="U17" s="534"/>
-      <c r="V17" s="534">
+      <c r="U17" s="599"/>
+      <c r="V17" s="599">
         <v>5</v>
       </c>
-      <c r="W17" s="540"/>
-      <c r="X17" s="534">
+      <c r="W17" s="601"/>
+      <c r="X17" s="599">
         <v>7</v>
       </c>
-      <c r="Y17" s="570"/>
+      <c r="Y17" s="600"/>
       <c r="Z17" s="96"/>
       <c r="AA17" s="119"/>
     </row>
@@ -28653,41 +28631,41 @@
         <v>150</v>
       </c>
       <c r="F18" s="105"/>
-      <c r="G18" s="538" t="s">
+      <c r="G18" s="623" t="s">
         <v>388</v>
       </c>
-      <c r="H18" s="539"/>
-      <c r="I18" s="540">
+      <c r="H18" s="624"/>
+      <c r="I18" s="601">
         <v>1</v>
       </c>
-      <c r="J18" s="541"/>
-      <c r="K18" s="542"/>
-      <c r="L18" s="534">
+      <c r="J18" s="625"/>
+      <c r="K18" s="626"/>
+      <c r="L18" s="599">
         <v>2</v>
       </c>
-      <c r="M18" s="534"/>
-      <c r="N18" s="534"/>
-      <c r="O18" s="534">
+      <c r="M18" s="599"/>
+      <c r="N18" s="599"/>
+      <c r="O18" s="599">
         <v>4</v>
       </c>
-      <c r="P18" s="534"/>
-      <c r="Q18" s="534"/>
-      <c r="R18" s="534">
+      <c r="P18" s="599"/>
+      <c r="Q18" s="599"/>
+      <c r="R18" s="599">
         <v>4</v>
       </c>
-      <c r="S18" s="534"/>
-      <c r="T18" s="534">
+      <c r="S18" s="599"/>
+      <c r="T18" s="599">
         <v>0</v>
       </c>
-      <c r="U18" s="534"/>
-      <c r="V18" s="534">
+      <c r="U18" s="599"/>
+      <c r="V18" s="599">
         <v>2</v>
       </c>
-      <c r="W18" s="540"/>
-      <c r="X18" s="534">
+      <c r="W18" s="601"/>
+      <c r="X18" s="599">
         <v>2</v>
       </c>
-      <c r="Y18" s="570"/>
+      <c r="Y18" s="600"/>
       <c r="Z18" s="96"/>
       <c r="AA18" s="119"/>
     </row>
@@ -28704,41 +28682,41 @@
       </c>
       <c r="E19" s="233"/>
       <c r="F19" s="105"/>
-      <c r="G19" s="538" t="s">
+      <c r="G19" s="623" t="s">
         <v>389</v>
       </c>
-      <c r="H19" s="539"/>
-      <c r="I19" s="540">
+      <c r="H19" s="624"/>
+      <c r="I19" s="601">
         <v>5</v>
       </c>
-      <c r="J19" s="541"/>
-      <c r="K19" s="542"/>
-      <c r="L19" s="534">
+      <c r="J19" s="625"/>
+      <c r="K19" s="626"/>
+      <c r="L19" s="599">
         <v>8</v>
       </c>
-      <c r="M19" s="534"/>
-      <c r="N19" s="534"/>
-      <c r="O19" s="534">
+      <c r="M19" s="599"/>
+      <c r="N19" s="599"/>
+      <c r="O19" s="599">
         <v>22</v>
       </c>
-      <c r="P19" s="534"/>
-      <c r="Q19" s="534"/>
-      <c r="R19" s="534">
+      <c r="P19" s="599"/>
+      <c r="Q19" s="599"/>
+      <c r="R19" s="599">
         <v>22</v>
       </c>
-      <c r="S19" s="534"/>
-      <c r="T19" s="534">
+      <c r="S19" s="599"/>
+      <c r="T19" s="599">
         <v>0</v>
       </c>
-      <c r="U19" s="534"/>
-      <c r="V19" s="534">
+      <c r="U19" s="599"/>
+      <c r="V19" s="599">
         <v>2</v>
       </c>
-      <c r="W19" s="540"/>
-      <c r="X19" s="534">
+      <c r="W19" s="601"/>
+      <c r="X19" s="599">
         <v>0</v>
       </c>
-      <c r="Y19" s="570"/>
+      <c r="Y19" s="600"/>
       <c r="Z19" s="96"/>
       <c r="AA19" s="119"/>
     </row>
@@ -28755,41 +28733,41 @@
       </c>
       <c r="E20" s="233"/>
       <c r="F20" s="105"/>
-      <c r="G20" s="538" t="s">
+      <c r="G20" s="623" t="s">
         <v>22</v>
       </c>
-      <c r="H20" s="539"/>
-      <c r="I20" s="540">
+      <c r="H20" s="624"/>
+      <c r="I20" s="601">
         <v>9</v>
       </c>
-      <c r="J20" s="541"/>
-      <c r="K20" s="542"/>
-      <c r="L20" s="534">
+      <c r="J20" s="625"/>
+      <c r="K20" s="626"/>
+      <c r="L20" s="599">
         <v>22</v>
       </c>
-      <c r="M20" s="534"/>
-      <c r="N20" s="534"/>
-      <c r="O20" s="534">
+      <c r="M20" s="599"/>
+      <c r="N20" s="599"/>
+      <c r="O20" s="599">
         <v>32</v>
       </c>
-      <c r="P20" s="534"/>
-      <c r="Q20" s="534"/>
-      <c r="R20" s="534">
+      <c r="P20" s="599"/>
+      <c r="Q20" s="599"/>
+      <c r="R20" s="599">
         <v>33</v>
       </c>
-      <c r="S20" s="534"/>
-      <c r="T20" s="534">
+      <c r="S20" s="599"/>
+      <c r="T20" s="599">
         <v>0</v>
       </c>
-      <c r="U20" s="534"/>
-      <c r="V20" s="534">
+      <c r="U20" s="599"/>
+      <c r="V20" s="599">
         <v>0</v>
       </c>
-      <c r="W20" s="540"/>
-      <c r="X20" s="534">
+      <c r="W20" s="601"/>
+      <c r="X20" s="599">
         <v>0</v>
       </c>
-      <c r="Y20" s="570"/>
+      <c r="Y20" s="600"/>
       <c r="Z20" s="96"/>
       <c r="AA20" s="119"/>
     </row>
@@ -28806,41 +28784,41 @@
       </c>
       <c r="E21" s="233"/>
       <c r="F21" s="105"/>
-      <c r="G21" s="538" t="s">
+      <c r="G21" s="623" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="539"/>
-      <c r="I21" s="540">
+      <c r="H21" s="624"/>
+      <c r="I21" s="601">
         <v>3</v>
       </c>
-      <c r="J21" s="541"/>
-      <c r="K21" s="542"/>
-      <c r="L21" s="534">
+      <c r="J21" s="625"/>
+      <c r="K21" s="626"/>
+      <c r="L21" s="599">
         <v>8</v>
       </c>
-      <c r="M21" s="534"/>
-      <c r="N21" s="534"/>
-      <c r="O21" s="534">
+      <c r="M21" s="599"/>
+      <c r="N21" s="599"/>
+      <c r="O21" s="599">
         <v>50</v>
       </c>
-      <c r="P21" s="534"/>
-      <c r="Q21" s="534"/>
-      <c r="R21" s="534">
+      <c r="P21" s="599"/>
+      <c r="Q21" s="599"/>
+      <c r="R21" s="599">
         <v>62</v>
       </c>
-      <c r="S21" s="534"/>
-      <c r="T21" s="534">
+      <c r="S21" s="599"/>
+      <c r="T21" s="599">
         <v>0</v>
       </c>
-      <c r="U21" s="534"/>
-      <c r="V21" s="534">
+      <c r="U21" s="599"/>
+      <c r="V21" s="599">
         <v>10</v>
       </c>
-      <c r="W21" s="540"/>
-      <c r="X21" s="534">
+      <c r="W21" s="601"/>
+      <c r="X21" s="599">
         <v>11</v>
       </c>
-      <c r="Y21" s="570"/>
+      <c r="Y21" s="600"/>
       <c r="Z21" s="96"/>
       <c r="AA21" s="119"/>
     </row>
@@ -28857,41 +28835,41 @@
       </c>
       <c r="E22" s="233"/>
       <c r="F22" s="105"/>
-      <c r="G22" s="538" t="s">
+      <c r="G22" s="623" t="s">
         <v>390</v>
       </c>
-      <c r="H22" s="539"/>
-      <c r="I22" s="540">
+      <c r="H22" s="624"/>
+      <c r="I22" s="601">
         <v>1</v>
       </c>
-      <c r="J22" s="541"/>
-      <c r="K22" s="542"/>
-      <c r="L22" s="534">
+      <c r="J22" s="625"/>
+      <c r="K22" s="626"/>
+      <c r="L22" s="599">
         <v>2</v>
       </c>
-      <c r="M22" s="534"/>
-      <c r="N22" s="534"/>
-      <c r="O22" s="534">
+      <c r="M22" s="599"/>
+      <c r="N22" s="599"/>
+      <c r="O22" s="599">
         <v>4</v>
       </c>
-      <c r="P22" s="534"/>
-      <c r="Q22" s="534"/>
-      <c r="R22" s="534">
+      <c r="P22" s="599"/>
+      <c r="Q22" s="599"/>
+      <c r="R22" s="599">
         <v>6</v>
       </c>
-      <c r="S22" s="534"/>
-      <c r="T22" s="534">
+      <c r="S22" s="599"/>
+      <c r="T22" s="599">
         <v>0</v>
       </c>
-      <c r="U22" s="534"/>
-      <c r="V22" s="534">
+      <c r="U22" s="599"/>
+      <c r="V22" s="599">
         <v>0</v>
       </c>
-      <c r="W22" s="540"/>
-      <c r="X22" s="534">
+      <c r="W22" s="601"/>
+      <c r="X22" s="599">
         <v>3</v>
       </c>
-      <c r="Y22" s="570"/>
+      <c r="Y22" s="600"/>
       <c r="Z22" s="96"/>
       <c r="AA22" s="119"/>
     </row>
@@ -28908,48 +28886,48 @@
       </c>
       <c r="E23" s="234"/>
       <c r="F23" s="105"/>
-      <c r="G23" s="581" t="s">
+      <c r="G23" s="611" t="s">
         <v>147</v>
       </c>
-      <c r="H23" s="573"/>
-      <c r="I23" s="573">
+      <c r="H23" s="603"/>
+      <c r="I23" s="603">
         <f>SUM(I14:K22)</f>
         <v>68</v>
       </c>
-      <c r="J23" s="573"/>
-      <c r="K23" s="573"/>
-      <c r="L23" s="573">
+      <c r="J23" s="603"/>
+      <c r="K23" s="603"/>
+      <c r="L23" s="603">
         <f>SUM(L14:N22)</f>
         <v>187</v>
       </c>
-      <c r="M23" s="573"/>
-      <c r="N23" s="573"/>
-      <c r="O23" s="578">
+      <c r="M23" s="603"/>
+      <c r="N23" s="603"/>
+      <c r="O23" s="608">
         <f>SUM(O14:Q22)</f>
         <v>473</v>
       </c>
-      <c r="P23" s="579"/>
-      <c r="Q23" s="580"/>
-      <c r="R23" s="578">
+      <c r="P23" s="609"/>
+      <c r="Q23" s="610"/>
+      <c r="R23" s="608">
         <f>SUM(R14:S22)</f>
         <v>526</v>
       </c>
-      <c r="S23" s="580"/>
-      <c r="T23" s="578">
+      <c r="S23" s="610"/>
+      <c r="T23" s="608">
         <f>SUM(T14:U22)</f>
         <v>28</v>
       </c>
-      <c r="U23" s="580"/>
-      <c r="V23" s="578">
+      <c r="U23" s="610"/>
+      <c r="V23" s="608">
         <f>SUM(V14:W22)</f>
         <v>33</v>
       </c>
-      <c r="W23" s="579"/>
-      <c r="X23" s="573">
+      <c r="W23" s="609"/>
+      <c r="X23" s="603">
         <f>SUM(X14:Y22)</f>
         <v>36</v>
       </c>
-      <c r="Y23" s="574"/>
+      <c r="Y23" s="604"/>
       <c r="Z23" s="96"/>
       <c r="AA23" s="119"/>
     </row>
@@ -29019,28 +28997,28 @@
       <c r="E26" s="98"/>
       <c r="F26" s="95"/>
       <c r="G26" s="161"/>
-      <c r="H26" s="618" t="s">
+      <c r="H26" s="566" t="s">
         <v>162</v>
       </c>
-      <c r="I26" s="619"/>
-      <c r="J26" s="620"/>
+      <c r="I26" s="567"/>
+      <c r="J26" s="568"/>
       <c r="K26" s="105"/>
-      <c r="L26" s="624" t="s">
+      <c r="L26" s="575" t="s">
         <v>155</v>
       </c>
-      <c r="M26" s="625"/>
-      <c r="N26" s="625"/>
-      <c r="O26" s="625"/>
-      <c r="P26" s="625"/>
-      <c r="Q26" s="625"/>
-      <c r="R26" s="625"/>
-      <c r="S26" s="625"/>
-      <c r="T26" s="625"/>
-      <c r="U26" s="625"/>
-      <c r="V26" s="625"/>
-      <c r="W26" s="625"/>
-      <c r="X26" s="625"/>
-      <c r="Y26" s="626"/>
+      <c r="M26" s="576"/>
+      <c r="N26" s="576"/>
+      <c r="O26" s="576"/>
+      <c r="P26" s="576"/>
+      <c r="Q26" s="576"/>
+      <c r="R26" s="576"/>
+      <c r="S26" s="576"/>
+      <c r="T26" s="576"/>
+      <c r="U26" s="576"/>
+      <c r="V26" s="576"/>
+      <c r="W26" s="576"/>
+      <c r="X26" s="576"/>
+      <c r="Y26" s="577"/>
       <c r="Z26" s="96"/>
       <c r="AA26" s="119"/>
     </row>
@@ -29052,41 +29030,41 @@
       <c r="E27" s="98"/>
       <c r="F27" s="95"/>
       <c r="G27" s="162"/>
-      <c r="H27" s="615">
+      <c r="H27" s="548">
         <f>Y38</f>
         <v>64</v>
       </c>
-      <c r="I27" s="616"/>
-      <c r="J27" s="617"/>
+      <c r="I27" s="549"/>
+      <c r="J27" s="550"/>
       <c r="K27" s="105"/>
-      <c r="L27" s="589" t="s">
+      <c r="L27" s="597" t="s">
         <v>139</v>
       </c>
-      <c r="M27" s="537"/>
-      <c r="N27" s="537"/>
-      <c r="O27" s="537" t="s">
+      <c r="M27" s="571"/>
+      <c r="N27" s="571"/>
+      <c r="O27" s="571" t="s">
         <v>156</v>
       </c>
-      <c r="P27" s="537"/>
-      <c r="Q27" s="537" t="s">
+      <c r="P27" s="571"/>
+      <c r="Q27" s="571" t="s">
         <v>157</v>
       </c>
-      <c r="R27" s="537"/>
-      <c r="S27" s="537" t="s">
+      <c r="R27" s="571"/>
+      <c r="S27" s="571" t="s">
         <v>158</v>
       </c>
-      <c r="T27" s="537" t="s">
+      <c r="T27" s="571" t="s">
         <v>159</v>
       </c>
-      <c r="U27" s="537"/>
-      <c r="V27" s="537" t="s">
+      <c r="U27" s="571"/>
+      <c r="V27" s="571" t="s">
         <v>160</v>
       </c>
-      <c r="W27" s="537" t="s">
+      <c r="W27" s="571" t="s">
         <v>161</v>
       </c>
-      <c r="X27" s="537"/>
-      <c r="Y27" s="558" t="s">
+      <c r="X27" s="571"/>
+      <c r="Y27" s="602" t="s">
         <v>147</v>
       </c>
       <c r="Z27" s="96"/>
@@ -29104,20 +29082,20 @@
       <c r="I28" s="98"/>
       <c r="J28" s="193"/>
       <c r="K28" s="105"/>
-      <c r="L28" s="589"/>
-      <c r="M28" s="537"/>
-      <c r="N28" s="537"/>
-      <c r="O28" s="537"/>
-      <c r="P28" s="537"/>
-      <c r="Q28" s="537"/>
-      <c r="R28" s="537"/>
-      <c r="S28" s="537"/>
-      <c r="T28" s="537"/>
-      <c r="U28" s="537"/>
-      <c r="V28" s="537"/>
-      <c r="W28" s="537"/>
-      <c r="X28" s="537"/>
-      <c r="Y28" s="558"/>
+      <c r="L28" s="597"/>
+      <c r="M28" s="571"/>
+      <c r="N28" s="571"/>
+      <c r="O28" s="571"/>
+      <c r="P28" s="571"/>
+      <c r="Q28" s="571"/>
+      <c r="R28" s="571"/>
+      <c r="S28" s="571"/>
+      <c r="T28" s="571"/>
+      <c r="U28" s="571"/>
+      <c r="V28" s="571"/>
+      <c r="W28" s="571"/>
+      <c r="X28" s="571"/>
+      <c r="Y28" s="602"/>
       <c r="Z28" s="96"/>
       <c r="AA28" s="119"/>
     </row>
@@ -29133,33 +29111,33 @@
       <c r="I29" s="194"/>
       <c r="J29" s="164"/>
       <c r="K29" s="105"/>
-      <c r="L29" s="586" t="s">
+      <c r="L29" s="583" t="s">
         <v>18</v>
       </c>
-      <c r="M29" s="587"/>
-      <c r="N29" s="587"/>
-      <c r="O29" s="587">
+      <c r="M29" s="551"/>
+      <c r="N29" s="551"/>
+      <c r="O29" s="551">
         <v>3</v>
       </c>
-      <c r="P29" s="587"/>
-      <c r="Q29" s="587">
+      <c r="P29" s="551"/>
+      <c r="Q29" s="551">
         <v>1</v>
       </c>
-      <c r="R29" s="587"/>
+      <c r="R29" s="551"/>
       <c r="S29" s="87">
         <v>0</v>
       </c>
-      <c r="T29" s="587">
+      <c r="T29" s="551">
         <v>0</v>
       </c>
-      <c r="U29" s="587"/>
+      <c r="U29" s="551"/>
       <c r="V29" s="87">
         <v>3</v>
       </c>
-      <c r="W29" s="587">
+      <c r="W29" s="551">
         <v>0</v>
       </c>
-      <c r="X29" s="588"/>
+      <c r="X29" s="552"/>
       <c r="Y29" s="227">
         <v>6</v>
       </c>
@@ -29178,33 +29156,33 @@
       <c r="I30" s="125"/>
       <c r="J30" s="125"/>
       <c r="K30" s="95"/>
-      <c r="L30" s="586" t="s">
+      <c r="L30" s="583" t="s">
         <v>16</v>
       </c>
-      <c r="M30" s="587"/>
-      <c r="N30" s="587"/>
-      <c r="O30" s="587">
+      <c r="M30" s="551"/>
+      <c r="N30" s="551"/>
+      <c r="O30" s="551">
         <v>0</v>
       </c>
-      <c r="P30" s="587"/>
-      <c r="Q30" s="587">
+      <c r="P30" s="551"/>
+      <c r="Q30" s="551">
         <v>0</v>
       </c>
-      <c r="R30" s="587"/>
+      <c r="R30" s="551"/>
       <c r="S30" s="87">
         <v>9</v>
       </c>
-      <c r="T30" s="587">
+      <c r="T30" s="551">
         <v>3</v>
       </c>
-      <c r="U30" s="587"/>
+      <c r="U30" s="551"/>
       <c r="V30" s="87">
         <v>2</v>
       </c>
-      <c r="W30" s="587">
+      <c r="W30" s="551">
         <v>1</v>
       </c>
-      <c r="X30" s="588"/>
+      <c r="X30" s="552"/>
       <c r="Y30" s="227">
         <v>11</v>
       </c>
@@ -29219,39 +29197,39 @@
       <c r="E31" s="98"/>
       <c r="F31" s="95"/>
       <c r="G31" s="161"/>
-      <c r="H31" s="621" t="s">
+      <c r="H31" s="572" t="s">
         <v>152</v>
       </c>
-      <c r="I31" s="622"/>
-      <c r="J31" s="623"/>
+      <c r="I31" s="573"/>
+      <c r="J31" s="574"/>
       <c r="K31" s="105"/>
-      <c r="L31" s="586" t="s">
+      <c r="L31" s="583" t="s">
         <v>19</v>
       </c>
-      <c r="M31" s="587"/>
-      <c r="N31" s="587"/>
-      <c r="O31" s="587">
+      <c r="M31" s="551"/>
+      <c r="N31" s="551"/>
+      <c r="O31" s="551">
         <v>1</v>
       </c>
-      <c r="P31" s="587"/>
-      <c r="Q31" s="587">
+      <c r="P31" s="551"/>
+      <c r="Q31" s="551">
         <v>0</v>
       </c>
-      <c r="R31" s="587"/>
+      <c r="R31" s="551"/>
       <c r="S31" s="87">
         <v>3</v>
       </c>
-      <c r="T31" s="587">
+      <c r="T31" s="551">
         <v>4</v>
       </c>
-      <c r="U31" s="587"/>
+      <c r="U31" s="551"/>
       <c r="V31" s="87">
         <v>2</v>
       </c>
-      <c r="W31" s="587">
+      <c r="W31" s="551">
         <v>0</v>
       </c>
-      <c r="X31" s="588"/>
+      <c r="X31" s="552"/>
       <c r="Y31" s="227">
         <v>6</v>
       </c>
@@ -29270,33 +29248,33 @@
       <c r="I32" s="98"/>
       <c r="J32" s="193"/>
       <c r="K32" s="105"/>
-      <c r="L32" s="586" t="s">
+      <c r="L32" s="583" t="s">
         <v>17</v>
       </c>
-      <c r="M32" s="587"/>
-      <c r="N32" s="587"/>
-      <c r="O32" s="587">
+      <c r="M32" s="551"/>
+      <c r="N32" s="551"/>
+      <c r="O32" s="551">
         <v>2</v>
       </c>
-      <c r="P32" s="587"/>
-      <c r="Q32" s="587">
+      <c r="P32" s="551"/>
+      <c r="Q32" s="551">
         <v>0</v>
       </c>
-      <c r="R32" s="587"/>
+      <c r="R32" s="551"/>
       <c r="S32" s="87">
         <v>4</v>
       </c>
-      <c r="T32" s="587">
+      <c r="T32" s="551">
         <v>2</v>
       </c>
-      <c r="U32" s="587"/>
+      <c r="U32" s="551"/>
       <c r="V32" s="87">
         <v>9</v>
       </c>
-      <c r="W32" s="587">
+      <c r="W32" s="551">
         <v>2</v>
       </c>
-      <c r="X32" s="588"/>
+      <c r="X32" s="552"/>
       <c r="Y32" s="227">
         <v>15</v>
       </c>
@@ -29311,40 +29289,40 @@
       <c r="E33" s="98"/>
       <c r="F33" s="95"/>
       <c r="G33" s="162"/>
-      <c r="H33" s="615">
+      <c r="H33" s="548">
         <f>O38</f>
         <v>13</v>
       </c>
-      <c r="I33" s="616"/>
-      <c r="J33" s="617"/>
+      <c r="I33" s="549"/>
+      <c r="J33" s="550"/>
       <c r="K33" s="105"/>
-      <c r="L33" s="586" t="s">
+      <c r="L33" s="583" t="s">
         <v>388</v>
       </c>
-      <c r="M33" s="587"/>
-      <c r="N33" s="587"/>
-      <c r="O33" s="587">
+      <c r="M33" s="551"/>
+      <c r="N33" s="551"/>
+      <c r="O33" s="551">
         <v>2</v>
       </c>
-      <c r="P33" s="587"/>
-      <c r="Q33" s="587">
+      <c r="P33" s="551"/>
+      <c r="Q33" s="551">
         <v>2</v>
       </c>
-      <c r="R33" s="587"/>
+      <c r="R33" s="551"/>
       <c r="S33" s="87">
         <v>0</v>
       </c>
-      <c r="T33" s="587">
+      <c r="T33" s="551">
         <v>0</v>
       </c>
-      <c r="U33" s="587"/>
+      <c r="U33" s="551"/>
       <c r="V33" s="87">
         <v>1</v>
       </c>
-      <c r="W33" s="587">
+      <c r="W33" s="551">
         <v>1</v>
       </c>
-      <c r="X33" s="588"/>
+      <c r="X33" s="552"/>
       <c r="Y33" s="227">
         <v>3</v>
       </c>
@@ -29363,33 +29341,33 @@
       <c r="I34" s="98"/>
       <c r="J34" s="193"/>
       <c r="K34" s="105"/>
-      <c r="L34" s="586" t="s">
+      <c r="L34" s="583" t="s">
         <v>389</v>
       </c>
-      <c r="M34" s="587"/>
-      <c r="N34" s="587"/>
-      <c r="O34" s="587">
+      <c r="M34" s="551"/>
+      <c r="N34" s="551"/>
+      <c r="O34" s="551">
         <v>1</v>
       </c>
-      <c r="P34" s="587"/>
-      <c r="Q34" s="587">
+      <c r="P34" s="551"/>
+      <c r="Q34" s="551">
         <v>0</v>
       </c>
-      <c r="R34" s="587"/>
+      <c r="R34" s="551"/>
       <c r="S34" s="87">
         <v>0</v>
       </c>
-      <c r="T34" s="587">
+      <c r="T34" s="551">
         <v>0</v>
       </c>
-      <c r="U34" s="587"/>
+      <c r="U34" s="551"/>
       <c r="V34" s="87">
         <v>4</v>
       </c>
-      <c r="W34" s="587">
+      <c r="W34" s="551">
         <v>0</v>
       </c>
-      <c r="X34" s="588"/>
+      <c r="X34" s="552"/>
       <c r="Y34" s="227">
         <v>5</v>
       </c>
@@ -29408,33 +29386,33 @@
       <c r="I35" s="194"/>
       <c r="J35" s="164"/>
       <c r="K35" s="105"/>
-      <c r="L35" s="586" t="s">
+      <c r="L35" s="583" t="s">
         <v>22</v>
       </c>
-      <c r="M35" s="587"/>
-      <c r="N35" s="587"/>
-      <c r="O35" s="590">
+      <c r="M35" s="551"/>
+      <c r="N35" s="551"/>
+      <c r="O35" s="578">
         <v>0</v>
       </c>
-      <c r="P35" s="590"/>
-      <c r="Q35" s="590">
+      <c r="P35" s="578"/>
+      <c r="Q35" s="578">
         <v>0</v>
       </c>
-      <c r="R35" s="590"/>
+      <c r="R35" s="578"/>
       <c r="S35" s="190">
         <v>0</v>
       </c>
-      <c r="T35" s="590">
+      <c r="T35" s="578">
         <v>0</v>
       </c>
-      <c r="U35" s="590"/>
+      <c r="U35" s="578"/>
       <c r="V35" s="190">
         <v>5</v>
       </c>
-      <c r="W35" s="590">
+      <c r="W35" s="578">
         <v>0</v>
       </c>
-      <c r="X35" s="591"/>
+      <c r="X35" s="598"/>
       <c r="Y35" s="227">
         <v>5</v>
       </c>
@@ -29453,33 +29431,33 @@
       <c r="I36" s="125"/>
       <c r="J36" s="125"/>
       <c r="K36" s="95"/>
-      <c r="L36" s="586" t="s">
+      <c r="L36" s="583" t="s">
         <v>20</v>
       </c>
-      <c r="M36" s="587"/>
-      <c r="N36" s="588"/>
-      <c r="O36" s="592">
+      <c r="M36" s="551"/>
+      <c r="N36" s="552"/>
+      <c r="O36" s="555">
         <v>4</v>
       </c>
-      <c r="P36" s="592"/>
-      <c r="Q36" s="592">
+      <c r="P36" s="555"/>
+      <c r="Q36" s="555">
         <v>1</v>
       </c>
-      <c r="R36" s="592"/>
+      <c r="R36" s="555"/>
       <c r="S36" s="191">
         <v>0</v>
       </c>
-      <c r="T36" s="592">
+      <c r="T36" s="555">
         <v>0</v>
       </c>
-      <c r="U36" s="592"/>
+      <c r="U36" s="555"/>
       <c r="V36" s="191">
         <v>6</v>
       </c>
-      <c r="W36" s="592">
+      <c r="W36" s="555">
         <v>1</v>
       </c>
-      <c r="X36" s="593"/>
+      <c r="X36" s="579"/>
       <c r="Y36" s="227">
         <v>10</v>
       </c>
@@ -29494,39 +29472,39 @@
       <c r="E37" s="98"/>
       <c r="F37" s="95"/>
       <c r="G37" s="161"/>
-      <c r="H37" s="621" t="s">
+      <c r="H37" s="572" t="s">
         <v>151</v>
       </c>
-      <c r="I37" s="622"/>
-      <c r="J37" s="623"/>
+      <c r="I37" s="573"/>
+      <c r="J37" s="574"/>
       <c r="K37" s="105"/>
-      <c r="L37" s="586" t="s">
+      <c r="L37" s="583" t="s">
         <v>390</v>
       </c>
-      <c r="M37" s="587"/>
-      <c r="N37" s="588"/>
-      <c r="O37" s="592">
+      <c r="M37" s="551"/>
+      <c r="N37" s="552"/>
+      <c r="O37" s="555">
         <v>0</v>
       </c>
-      <c r="P37" s="592"/>
-      <c r="Q37" s="592">
+      <c r="P37" s="555"/>
+      <c r="Q37" s="555">
         <v>0</v>
       </c>
-      <c r="R37" s="592"/>
+      <c r="R37" s="555"/>
       <c r="S37" s="191">
         <v>0</v>
       </c>
-      <c r="T37" s="592">
+      <c r="T37" s="555">
         <v>0</v>
       </c>
-      <c r="U37" s="592"/>
+      <c r="U37" s="555"/>
       <c r="V37" s="191">
         <v>3</v>
       </c>
-      <c r="W37" s="592">
+      <c r="W37" s="555">
         <v>3</v>
       </c>
-      <c r="X37" s="593"/>
+      <c r="X37" s="579"/>
       <c r="Y37" s="227">
         <v>3</v>
       </c>
@@ -29544,39 +29522,39 @@
       <c r="I38" s="98"/>
       <c r="J38" s="193"/>
       <c r="K38" s="105"/>
-      <c r="L38" s="605" t="s">
+      <c r="L38" s="591" t="s">
         <v>147</v>
       </c>
-      <c r="M38" s="606"/>
-      <c r="N38" s="607"/>
-      <c r="O38" s="594">
+      <c r="M38" s="592"/>
+      <c r="N38" s="593"/>
+      <c r="O38" s="556">
         <f>SUM(O29:P37)</f>
         <v>13</v>
       </c>
-      <c r="P38" s="594"/>
-      <c r="Q38" s="594">
+      <c r="P38" s="556"/>
+      <c r="Q38" s="556">
         <f>SUM(Q29:R37)</f>
         <v>4</v>
       </c>
-      <c r="R38" s="594"/>
+      <c r="R38" s="556"/>
       <c r="S38" s="228">
         <f>SUM(S29:S37)</f>
         <v>16</v>
       </c>
-      <c r="T38" s="594">
+      <c r="T38" s="556">
         <f>SUM(T29:U37)</f>
         <v>9</v>
       </c>
-      <c r="U38" s="594"/>
+      <c r="U38" s="556"/>
       <c r="V38" s="228">
         <f>SUM(V29:V37)</f>
         <v>35</v>
       </c>
-      <c r="W38" s="594">
+      <c r="W38" s="556">
         <f>SUM(W29:X37)</f>
         <v>8</v>
       </c>
-      <c r="X38" s="594"/>
+      <c r="X38" s="556"/>
       <c r="Y38" s="229">
         <f>SUM(Y29:Y37)</f>
         <v>64</v>
@@ -29592,26 +29570,26 @@
       <c r="E39" s="98"/>
       <c r="F39" s="95"/>
       <c r="G39" s="162"/>
-      <c r="H39" s="615">
+      <c r="H39" s="548">
         <f>S38</f>
         <v>16</v>
       </c>
-      <c r="I39" s="616"/>
-      <c r="J39" s="617"/>
+      <c r="I39" s="549"/>
+      <c r="J39" s="550"/>
       <c r="K39" s="105"/>
-      <c r="L39" s="600"/>
-      <c r="M39" s="608"/>
-      <c r="N39" s="609"/>
-      <c r="O39" s="600"/>
-      <c r="P39" s="601"/>
-      <c r="Q39" s="613"/>
-      <c r="R39" s="614"/>
+      <c r="L39" s="586"/>
+      <c r="M39" s="594"/>
+      <c r="N39" s="595"/>
+      <c r="O39" s="586"/>
+      <c r="P39" s="587"/>
+      <c r="Q39" s="569"/>
+      <c r="R39" s="570"/>
       <c r="S39" s="123"/>
-      <c r="T39" s="641"/>
-      <c r="U39" s="641"/>
+      <c r="T39" s="557"/>
+      <c r="U39" s="557"/>
       <c r="V39" s="123"/>
-      <c r="W39" s="641"/>
-      <c r="X39" s="641"/>
+      <c r="W39" s="557"/>
+      <c r="X39" s="557"/>
       <c r="Y39" s="154"/>
       <c r="Z39" s="98"/>
       <c r="AA39" s="95"/>
@@ -29628,19 +29606,19 @@
       <c r="I40" s="98"/>
       <c r="J40" s="193"/>
       <c r="K40" s="105"/>
-      <c r="L40" s="610"/>
-      <c r="M40" s="611"/>
-      <c r="N40" s="612"/>
-      <c r="O40" s="602"/>
-      <c r="P40" s="599"/>
-      <c r="Q40" s="598"/>
-      <c r="R40" s="599"/>
+      <c r="L40" s="559"/>
+      <c r="M40" s="596"/>
+      <c r="N40" s="560"/>
+      <c r="O40" s="588"/>
+      <c r="P40" s="585"/>
+      <c r="Q40" s="584"/>
+      <c r="R40" s="585"/>
       <c r="S40" s="98"/>
-      <c r="T40" s="642"/>
-      <c r="U40" s="642"/>
+      <c r="T40" s="558"/>
+      <c r="U40" s="558"/>
       <c r="V40" s="98"/>
-      <c r="W40" s="642"/>
-      <c r="X40" s="642"/>
+      <c r="W40" s="558"/>
+      <c r="X40" s="558"/>
       <c r="Y40" s="166"/>
       <c r="Z40" s="98"/>
     </row>
@@ -29656,19 +29634,19 @@
       <c r="I41" s="194"/>
       <c r="J41" s="164"/>
       <c r="K41" s="105"/>
-      <c r="L41" s="610"/>
-      <c r="M41" s="611"/>
-      <c r="N41" s="612"/>
-      <c r="O41" s="603"/>
-      <c r="P41" s="604"/>
-      <c r="Q41" s="610"/>
-      <c r="R41" s="612"/>
+      <c r="L41" s="559"/>
+      <c r="M41" s="596"/>
+      <c r="N41" s="560"/>
+      <c r="O41" s="589"/>
+      <c r="P41" s="590"/>
+      <c r="Q41" s="559"/>
+      <c r="R41" s="560"/>
       <c r="S41" s="98"/>
-      <c r="T41" s="610"/>
-      <c r="U41" s="612"/>
+      <c r="T41" s="559"/>
+      <c r="U41" s="560"/>
       <c r="V41" s="98"/>
-      <c r="W41" s="610"/>
-      <c r="X41" s="612"/>
+      <c r="W41" s="559"/>
+      <c r="X41" s="560"/>
       <c r="Y41" s="166"/>
       <c r="Z41" s="98"/>
       <c r="AA41" s="119"/>
@@ -29685,21 +29663,21 @@
       <c r="I42" s="125"/>
       <c r="J42" s="125"/>
       <c r="K42" s="95"/>
-      <c r="L42" s="595"/>
-      <c r="M42" s="596"/>
-      <c r="N42" s="597"/>
-      <c r="O42" s="613"/>
-      <c r="P42" s="614"/>
+      <c r="L42" s="580"/>
+      <c r="M42" s="581"/>
+      <c r="N42" s="582"/>
+      <c r="O42" s="569"/>
+      <c r="P42" s="570"/>
       <c r="Q42" s="98"/>
-      <c r="R42" s="639" t="s">
+      <c r="R42" s="553" t="s">
         <v>206</v>
       </c>
-      <c r="S42" s="640"/>
+      <c r="S42" s="554"/>
       <c r="T42" s="124"/>
-      <c r="U42" s="643"/>
-      <c r="V42" s="644"/>
-      <c r="W42" s="643"/>
-      <c r="X42" s="644"/>
+      <c r="U42" s="561"/>
+      <c r="V42" s="562"/>
+      <c r="W42" s="561"/>
+      <c r="X42" s="562"/>
       <c r="Y42" s="166"/>
       <c r="Z42" s="98"/>
       <c r="AA42" s="95"/>
@@ -29712,19 +29690,19 @@
       <c r="E43" s="98"/>
       <c r="F43" s="95"/>
       <c r="G43" s="161"/>
-      <c r="H43" s="646" t="s">
+      <c r="H43" s="564" t="s">
         <v>163</v>
       </c>
-      <c r="I43" s="646"/>
-      <c r="J43" s="647"/>
+      <c r="I43" s="564"/>
+      <c r="J43" s="565"/>
       <c r="K43" s="105"/>
       <c r="L43" s="161"/>
       <c r="M43" s="192"/>
-      <c r="N43" s="630" t="s">
+      <c r="N43" s="539" t="s">
         <v>153</v>
       </c>
-      <c r="O43" s="631"/>
-      <c r="P43" s="632"/>
+      <c r="O43" s="540"/>
+      <c r="P43" s="541"/>
       <c r="Q43" s="162"/>
       <c r="R43" s="356" t="s">
         <v>207</v>
@@ -29778,21 +29756,21 @@
       <c r="E45" s="98"/>
       <c r="F45" s="95"/>
       <c r="G45" s="162"/>
-      <c r="H45" s="615">
+      <c r="H45" s="548">
         <f>SUM(V38)</f>
         <v>35</v>
       </c>
-      <c r="I45" s="616"/>
-      <c r="J45" s="617"/>
+      <c r="I45" s="549"/>
+      <c r="J45" s="550"/>
       <c r="K45" s="105"/>
       <c r="L45" s="162"/>
       <c r="M45" s="98"/>
       <c r="N45" s="98"/>
-      <c r="O45" s="633">
+      <c r="O45" s="542">
         <f>SUM(Q38,T38,W38)</f>
         <v>21</v>
       </c>
-      <c r="P45" s="634"/>
+      <c r="P45" s="543"/>
       <c r="Q45" s="162"/>
       <c r="R45" s="357" t="s">
         <v>208</v>
@@ -29824,8 +29802,8 @@
       <c r="L46" s="162"/>
       <c r="M46" s="98"/>
       <c r="N46" s="98"/>
-      <c r="O46" s="635"/>
-      <c r="P46" s="636"/>
+      <c r="O46" s="544"/>
+      <c r="P46" s="545"/>
       <c r="Q46" s="162"/>
       <c r="R46" s="358"/>
       <c r="S46" s="373"/>
@@ -29936,9 +29914,9 @@
       <c r="E50" s="98"/>
       <c r="F50" s="95"/>
       <c r="G50" s="195"/>
-      <c r="H50" s="637"/>
-      <c r="I50" s="637"/>
-      <c r="J50" s="638"/>
+      <c r="H50" s="546"/>
+      <c r="I50" s="546"/>
+      <c r="J50" s="547"/>
       <c r="K50" s="96"/>
       <c r="L50" s="123"/>
       <c r="M50" s="123"/>
@@ -29993,9 +29971,9 @@
       <c r="E52" s="98"/>
       <c r="F52" s="98"/>
       <c r="G52" s="98"/>
-      <c r="H52" s="645"/>
-      <c r="I52" s="645"/>
-      <c r="J52" s="645"/>
+      <c r="H52" s="563"/>
+      <c r="I52" s="563"/>
+      <c r="J52" s="563"/>
       <c r="K52" s="98"/>
       <c r="L52" s="98"/>
       <c r="M52" s="98"/>
@@ -30096,11 +30074,11 @@
       <c r="U55" s="95"/>
       <c r="V55" s="98"/>
       <c r="W55" s="98"/>
-      <c r="X55" s="627"/>
-      <c r="Y55" s="628"/>
-      <c r="Z55" s="628"/>
-      <c r="AA55" s="628"/>
-      <c r="AB55" s="629"/>
+      <c r="X55" s="536"/>
+      <c r="Y55" s="537"/>
+      <c r="Z55" s="537"/>
+      <c r="AA55" s="537"/>
+      <c r="AB55" s="538"/>
     </row>
     <row r="56" spans="1:28" ht="23.25" hidden="1">
       <c r="A56" s="98"/>
@@ -30316,11 +30294,11 @@
       <c r="P63" s="98"/>
       <c r="Q63" s="95"/>
       <c r="R63" s="95"/>
-      <c r="U63" s="627"/>
-      <c r="V63" s="628"/>
-      <c r="W63" s="628"/>
-      <c r="X63" s="628"/>
-      <c r="Y63" s="629"/>
+      <c r="U63" s="536"/>
+      <c r="V63" s="537"/>
+      <c r="W63" s="537"/>
+      <c r="X63" s="537"/>
+      <c r="Y63" s="538"/>
       <c r="Z63" s="98"/>
     </row>
     <row r="64" spans="1:28" ht="23.25">
@@ -30756,6 +30734,178 @@
     </row>
   </sheetData>
   <mergeCells count="196">
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="V12:W13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="B1:Y1"/>
+    <mergeCell ref="B3:Y3"/>
+    <mergeCell ref="B4:Y4"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="X12:Y13"/>
+    <mergeCell ref="R11:Y11"/>
+    <mergeCell ref="G10:Y10"/>
+    <mergeCell ref="G11:H13"/>
+    <mergeCell ref="I11:K13"/>
+    <mergeCell ref="L11:N13"/>
+    <mergeCell ref="O11:Q13"/>
+    <mergeCell ref="R12:S13"/>
+    <mergeCell ref="T12:U13"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="W27:X28"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="V27:V28"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Y27:Y28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="W29:X29"/>
+    <mergeCell ref="T27:U28"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="L27:N28"/>
+    <mergeCell ref="W31:X31"/>
+    <mergeCell ref="W32:X32"/>
+    <mergeCell ref="W33:X33"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="W35:X35"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="W38:X38"/>
+    <mergeCell ref="L42:N42"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="L40:N40"/>
+    <mergeCell ref="L41:N41"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="O27:P28"/>
+    <mergeCell ref="Q27:R28"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="L26:Y26"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="T32:U32"/>
+    <mergeCell ref="T33:U33"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="Q36:R36"/>
     <mergeCell ref="U63:Y63"/>
     <mergeCell ref="X55:AB55"/>
     <mergeCell ref="N43:P43"/>
@@ -30780,198 +30930,26 @@
     <mergeCell ref="W41:X41"/>
     <mergeCell ref="W42:X42"/>
     <mergeCell ref="H43:J43"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="O42:P42"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="O27:P28"/>
-    <mergeCell ref="Q27:R28"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="L26:Y26"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="T32:U32"/>
-    <mergeCell ref="T33:U33"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="W37:X37"/>
-    <mergeCell ref="W38:X38"/>
-    <mergeCell ref="L42:N42"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="L40:N40"/>
-    <mergeCell ref="L41:N41"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="W29:X29"/>
-    <mergeCell ref="T27:U28"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="L27:N28"/>
-    <mergeCell ref="W31:X31"/>
-    <mergeCell ref="W32:X32"/>
-    <mergeCell ref="W33:X33"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="W35:X35"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Y27:Y28"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="V27:V28"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="W27:X28"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="X15:Y15"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="V12:W13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="B1:Y1"/>
-    <mergeCell ref="B3:Y3"/>
-    <mergeCell ref="B4:Y4"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="X12:Y13"/>
-    <mergeCell ref="R11:Y11"/>
-    <mergeCell ref="G10:Y10"/>
-    <mergeCell ref="G11:H13"/>
-    <mergeCell ref="I11:K13"/>
-    <mergeCell ref="L11:N13"/>
-    <mergeCell ref="O11:Q13"/>
-    <mergeCell ref="R12:S13"/>
-    <mergeCell ref="T12:U13"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="T16:U16"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:E15">
-    <cfRule type="expression" dxfId="7" priority="10">
+    <cfRule type="expression" dxfId="5" priority="10">
       <formula>SEARCH("No actualizado",$C8)&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="11">
+    <cfRule type="expression" dxfId="4" priority="11">
       <formula>SEARCH("Actualizado",$C8)&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="12">
+    <cfRule type="expression" dxfId="3" priority="12">
       <formula>SEARCH("Pendiente Actualizar",$C8)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19:E23">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>SEARCH("No monitoreado",$D19)&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>SEARCH("Monitoreo pendiente",$D19)&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>SEARCH("Monitoreado",$D19)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30991,22 +30969,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6">
-      <c r="B2" s="650" t="s">
+      <c r="B2" s="652" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="650"/>
-      <c r="D2" s="650"/>
-      <c r="E2" s="650"/>
-      <c r="F2" s="650"/>
+      <c r="C2" s="652"/>
+      <c r="D2" s="652"/>
+      <c r="E2" s="652"/>
+      <c r="F2" s="652"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="B3" s="651" t="s">
+      <c r="B3" s="653" t="s">
         <v>165</v>
       </c>
-      <c r="C3" s="651"/>
-      <c r="D3" s="651"/>
-      <c r="E3" s="651"/>
-      <c r="F3" s="651"/>
+      <c r="C3" s="653"/>
+      <c r="D3" s="653"/>
+      <c r="E3" s="653"/>
+      <c r="F3" s="653"/>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" s="89" t="s">
@@ -31285,10 +31263,10 @@
       <c r="E26" s="2">
         <v>72</v>
       </c>
-      <c r="G26" s="648" t="s">
+      <c r="G26" s="650" t="s">
         <v>171</v>
       </c>
-      <c r="H26" s="649">
+      <c r="H26" s="651">
         <v>5</v>
       </c>
     </row>
@@ -31302,8 +31280,8 @@
       <c r="E27" s="2">
         <v>96</v>
       </c>
-      <c r="G27" s="648"/>
-      <c r="H27" s="649"/>
+      <c r="G27" s="650"/>
+      <c r="H27" s="651"/>
     </row>
     <row r="28" spans="3:8">
       <c r="C28" s="89">
@@ -31315,8 +31293,8 @@
       <c r="E28" s="2">
         <v>21</v>
       </c>
-      <c r="G28" s="648"/>
-      <c r="H28" s="649"/>
+      <c r="G28" s="650"/>
+      <c r="H28" s="651"/>
     </row>
     <row r="29" spans="3:8">
       <c r="C29" s="89">
@@ -31328,8 +31306,8 @@
       <c r="E29" s="2">
         <v>2</v>
       </c>
-      <c r="G29" s="648"/>
-      <c r="H29" s="649"/>
+      <c r="G29" s="650"/>
+      <c r="H29" s="651"/>
     </row>
     <row r="30" spans="3:8">
       <c r="C30" s="89">
@@ -31341,8 +31319,8 @@
       <c r="E30" s="2">
         <v>22</v>
       </c>
-      <c r="G30" s="648"/>
-      <c r="H30" s="649"/>
+      <c r="G30" s="650"/>
+      <c r="H30" s="651"/>
     </row>
     <row r="31" spans="3:8">
       <c r="C31" s="89">
@@ -31354,8 +31332,8 @@
       <c r="E31" s="2">
         <v>31</v>
       </c>
-      <c r="G31" s="648"/>
-      <c r="H31" s="649">
+      <c r="G31" s="650"/>
+      <c r="H31" s="651">
         <v>4</v>
       </c>
     </row>
@@ -31369,8 +31347,8 @@
       <c r="E32" s="2">
         <v>45</v>
       </c>
-      <c r="G32" s="648"/>
-      <c r="H32" s="649"/>
+      <c r="G32" s="650"/>
+      <c r="H32" s="651"/>
     </row>
     <row r="33" spans="3:8">
       <c r="C33" s="89">
@@ -31382,8 +31360,8 @@
       <c r="E33" s="2">
         <v>18</v>
       </c>
-      <c r="G33" s="648"/>
-      <c r="H33" s="649"/>
+      <c r="G33" s="650"/>
+      <c r="H33" s="651"/>
     </row>
     <row r="34" spans="3:8">
       <c r="C34" s="89">
@@ -31395,8 +31373,8 @@
       <c r="E34" s="2">
         <v>0</v>
       </c>
-      <c r="G34" s="648"/>
-      <c r="H34" s="649"/>
+      <c r="G34" s="650"/>
+      <c r="H34" s="651"/>
     </row>
     <row r="35" spans="3:8">
       <c r="C35" s="89">
@@ -31408,8 +31386,8 @@
       <c r="E35" s="2">
         <v>14</v>
       </c>
-      <c r="G35" s="648"/>
-      <c r="H35" s="649"/>
+      <c r="G35" s="650"/>
+      <c r="H35" s="651"/>
     </row>
     <row r="36" spans="3:8">
       <c r="C36" s="89">
@@ -31421,8 +31399,8 @@
       <c r="E36" s="2">
         <v>10</v>
       </c>
-      <c r="G36" s="648"/>
-      <c r="H36" s="649">
+      <c r="G36" s="650"/>
+      <c r="H36" s="651">
         <v>3</v>
       </c>
     </row>
@@ -31436,8 +31414,8 @@
       <c r="E37" s="2">
         <v>2</v>
       </c>
-      <c r="G37" s="648"/>
-      <c r="H37" s="649"/>
+      <c r="G37" s="650"/>
+      <c r="H37" s="651"/>
     </row>
     <row r="38" spans="3:8">
       <c r="C38" s="89">
@@ -31449,8 +31427,8 @@
       <c r="E38" s="2">
         <v>0</v>
       </c>
-      <c r="G38" s="648"/>
-      <c r="H38" s="649"/>
+      <c r="G38" s="650"/>
+      <c r="H38" s="651"/>
     </row>
     <row r="39" spans="3:8">
       <c r="C39" s="89">
@@ -31462,238 +31440,238 @@
       <c r="E39" s="2">
         <v>0</v>
       </c>
-      <c r="G39" s="648"/>
-      <c r="H39" s="649"/>
+      <c r="G39" s="650"/>
+      <c r="H39" s="651"/>
     </row>
     <row r="40" spans="3:8">
-      <c r="G40" s="648"/>
-      <c r="H40" s="649"/>
+      <c r="G40" s="650"/>
+      <c r="H40" s="651"/>
     </row>
     <row r="41" spans="3:8">
-      <c r="G41" s="648"/>
-      <c r="H41" s="649">
+      <c r="G41" s="650"/>
+      <c r="H41" s="651">
         <v>2</v>
       </c>
     </row>
     <row r="42" spans="3:8">
-      <c r="G42" s="648"/>
-      <c r="H42" s="649"/>
+      <c r="G42" s="650"/>
+      <c r="H42" s="651"/>
     </row>
     <row r="43" spans="3:8">
-      <c r="G43" s="648"/>
-      <c r="H43" s="649"/>
+      <c r="G43" s="650"/>
+      <c r="H43" s="651"/>
     </row>
     <row r="44" spans="3:8">
-      <c r="G44" s="648"/>
-      <c r="H44" s="649"/>
+      <c r="G44" s="650"/>
+      <c r="H44" s="651"/>
     </row>
     <row r="45" spans="3:8">
-      <c r="G45" s="648"/>
-      <c r="H45" s="649"/>
+      <c r="G45" s="650"/>
+      <c r="H45" s="651"/>
     </row>
     <row r="46" spans="3:8">
-      <c r="G46" s="648"/>
-      <c r="H46" s="649">
+      <c r="G46" s="650"/>
+      <c r="H46" s="651">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="3:8">
-      <c r="G47" s="648"/>
-      <c r="H47" s="649"/>
+      <c r="G47" s="650"/>
+      <c r="H47" s="651"/>
     </row>
     <row r="48" spans="3:8">
-      <c r="G48" s="648"/>
-      <c r="H48" s="649"/>
+      <c r="G48" s="650"/>
+      <c r="H48" s="651"/>
     </row>
     <row r="49" spans="7:10">
-      <c r="G49" s="648"/>
-      <c r="H49" s="649"/>
+      <c r="G49" s="650"/>
+      <c r="H49" s="651"/>
     </row>
     <row r="50" spans="7:10">
-      <c r="G50" s="648"/>
-      <c r="H50" s="649"/>
+      <c r="G50" s="650"/>
+      <c r="H50" s="651"/>
     </row>
     <row r="55" spans="7:10">
       <c r="H55" s="200"/>
-      <c r="I55" s="649"/>
-      <c r="J55" s="648"/>
+      <c r="I55" s="651"/>
+      <c r="J55" s="650"/>
     </row>
     <row r="56" spans="7:10">
       <c r="H56" s="200"/>
-      <c r="I56" s="649"/>
-      <c r="J56" s="648"/>
+      <c r="I56" s="651"/>
+      <c r="J56" s="650"/>
     </row>
     <row r="57" spans="7:10">
       <c r="H57" s="200"/>
-      <c r="I57" s="649"/>
-      <c r="J57" s="648"/>
+      <c r="I57" s="651"/>
+      <c r="J57" s="650"/>
     </row>
     <row r="58" spans="7:10">
       <c r="H58" s="200"/>
-      <c r="I58" s="649"/>
-      <c r="J58" s="648"/>
+      <c r="I58" s="651"/>
+      <c r="J58" s="650"/>
     </row>
     <row r="59" spans="7:10">
       <c r="H59" s="200"/>
-      <c r="I59" s="649"/>
-      <c r="J59" s="648"/>
+      <c r="I59" s="651"/>
+      <c r="J59" s="650"/>
     </row>
     <row r="60" spans="7:10">
       <c r="H60" s="200"/>
-      <c r="I60" s="649"/>
-      <c r="J60" s="648"/>
+      <c r="I60" s="651"/>
+      <c r="J60" s="650"/>
     </row>
     <row r="61" spans="7:10">
       <c r="H61" s="200"/>
-      <c r="I61" s="649"/>
-      <c r="J61" s="648"/>
+      <c r="I61" s="651"/>
+      <c r="J61" s="650"/>
     </row>
     <row r="62" spans="7:10">
       <c r="H62" s="200"/>
-      <c r="I62" s="649"/>
-      <c r="J62" s="648"/>
+      <c r="I62" s="651"/>
+      <c r="J62" s="650"/>
     </row>
     <row r="63" spans="7:10">
       <c r="H63" s="200"/>
-      <c r="I63" s="649"/>
-      <c r="J63" s="648"/>
+      <c r="I63" s="651"/>
+      <c r="J63" s="650"/>
     </row>
     <row r="64" spans="7:10">
       <c r="H64" s="200"/>
-      <c r="I64" s="649"/>
-      <c r="J64" s="648"/>
+      <c r="I64" s="651"/>
+      <c r="J64" s="650"/>
     </row>
     <row r="65" spans="8:11">
       <c r="H65" s="200"/>
-      <c r="I65" s="649"/>
-      <c r="J65" s="648"/>
+      <c r="I65" s="651"/>
+      <c r="J65" s="650"/>
     </row>
     <row r="66" spans="8:11">
       <c r="H66" s="200"/>
-      <c r="I66" s="649"/>
-      <c r="J66" s="648"/>
+      <c r="I66" s="651"/>
+      <c r="J66" s="650"/>
     </row>
     <row r="67" spans="8:11">
       <c r="H67" s="200"/>
-      <c r="I67" s="649"/>
-      <c r="J67" s="648"/>
+      <c r="I67" s="651"/>
+      <c r="J67" s="650"/>
     </row>
     <row r="68" spans="8:11">
       <c r="H68" s="200"/>
-      <c r="I68" s="649"/>
-      <c r="J68" s="648"/>
+      <c r="I68" s="651"/>
+      <c r="J68" s="650"/>
     </row>
     <row r="69" spans="8:11">
       <c r="H69" s="200"/>
-      <c r="I69" s="649"/>
-      <c r="J69" s="648"/>
+      <c r="I69" s="651"/>
+      <c r="J69" s="650"/>
     </row>
     <row r="70" spans="8:11">
       <c r="H70" s="200"/>
-      <c r="I70" s="649"/>
-      <c r="J70" s="648"/>
-      <c r="K70" s="648" t="s">
+      <c r="I70" s="651"/>
+      <c r="J70" s="650"/>
+      <c r="K70" s="650" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="71" spans="8:11">
       <c r="H71" s="200"/>
-      <c r="I71" s="649"/>
-      <c r="J71" s="648"/>
-      <c r="K71" s="648"/>
+      <c r="I71" s="651"/>
+      <c r="J71" s="650"/>
+      <c r="K71" s="650"/>
     </row>
     <row r="72" spans="8:11">
       <c r="H72" s="200"/>
-      <c r="I72" s="649"/>
-      <c r="J72" s="648"/>
-      <c r="K72" s="648"/>
+      <c r="I72" s="651"/>
+      <c r="J72" s="650"/>
+      <c r="K72" s="650"/>
     </row>
     <row r="73" spans="8:11">
       <c r="H73" s="200"/>
-      <c r="I73" s="649"/>
-      <c r="J73" s="648"/>
-      <c r="K73" s="648"/>
+      <c r="I73" s="651"/>
+      <c r="J73" s="650"/>
+      <c r="K73" s="650"/>
     </row>
     <row r="74" spans="8:11">
       <c r="H74" s="200"/>
-      <c r="I74" s="649"/>
-      <c r="J74" s="648"/>
-      <c r="K74" s="648"/>
+      <c r="I74" s="651"/>
+      <c r="J74" s="650"/>
+      <c r="K74" s="650"/>
     </row>
     <row r="75" spans="8:11">
       <c r="H75" s="200"/>
-      <c r="I75" s="649"/>
-      <c r="J75" s="648"/>
-      <c r="K75" s="648"/>
+      <c r="I75" s="651"/>
+      <c r="J75" s="650"/>
+      <c r="K75" s="650"/>
     </row>
     <row r="76" spans="8:11">
       <c r="H76" s="200"/>
-      <c r="I76" s="649"/>
-      <c r="J76" s="648"/>
-      <c r="K76" s="648"/>
+      <c r="I76" s="651"/>
+      <c r="J76" s="650"/>
+      <c r="K76" s="650"/>
     </row>
     <row r="77" spans="8:11">
       <c r="H77" s="200"/>
-      <c r="I77" s="649"/>
-      <c r="J77" s="648"/>
-      <c r="K77" s="648"/>
+      <c r="I77" s="651"/>
+      <c r="J77" s="650"/>
+      <c r="K77" s="650"/>
     </row>
     <row r="78" spans="8:11">
       <c r="H78" s="200"/>
-      <c r="I78" s="649"/>
-      <c r="J78" s="648"/>
-      <c r="K78" s="648"/>
+      <c r="I78" s="651"/>
+      <c r="J78" s="650"/>
+      <c r="K78" s="650"/>
     </row>
     <row r="79" spans="8:11">
       <c r="H79" s="200"/>
-      <c r="I79" s="649"/>
-      <c r="J79" s="648"/>
-      <c r="K79" s="648"/>
+      <c r="I79" s="651"/>
+      <c r="J79" s="650"/>
+      <c r="K79" s="650"/>
     </row>
     <row r="80" spans="8:11">
-      <c r="K80" s="648"/>
+      <c r="K80" s="650"/>
     </row>
     <row r="81" spans="11:11">
-      <c r="K81" s="648"/>
+      <c r="K81" s="650"/>
     </row>
     <row r="82" spans="11:11">
-      <c r="K82" s="648"/>
+      <c r="K82" s="650"/>
     </row>
     <row r="83" spans="11:11">
-      <c r="K83" s="648"/>
+      <c r="K83" s="650"/>
     </row>
     <row r="84" spans="11:11">
-      <c r="K84" s="648"/>
+      <c r="K84" s="650"/>
     </row>
     <row r="85" spans="11:11">
-      <c r="K85" s="648"/>
+      <c r="K85" s="650"/>
     </row>
     <row r="86" spans="11:11">
-      <c r="K86" s="648"/>
+      <c r="K86" s="650"/>
     </row>
     <row r="87" spans="11:11">
-      <c r="K87" s="648"/>
+      <c r="K87" s="650"/>
     </row>
     <row r="88" spans="11:11">
-      <c r="K88" s="648"/>
+      <c r="K88" s="650"/>
     </row>
     <row r="89" spans="11:11">
-      <c r="K89" s="648"/>
+      <c r="K89" s="650"/>
     </row>
     <row r="90" spans="11:11">
-      <c r="K90" s="648"/>
+      <c r="K90" s="650"/>
     </row>
     <row r="91" spans="11:11">
-      <c r="K91" s="648"/>
+      <c r="K91" s="650"/>
     </row>
     <row r="92" spans="11:11">
-      <c r="K92" s="648"/>
+      <c r="K92" s="650"/>
     </row>
     <row r="93" spans="11:11">
-      <c r="K93" s="648"/>
+      <c r="K93" s="650"/>
     </row>
     <row r="94" spans="11:11">
-      <c r="K94" s="648"/>
+      <c r="K94" s="650"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -31746,23 +31724,23 @@
   <sheetData>
     <row r="1" spans="1:21" ht="21">
       <c r="A1" s="98"/>
-      <c r="B1" s="652" t="s">
+      <c r="B1" s="689" t="s">
         <v>178</v>
       </c>
-      <c r="C1" s="653"/>
-      <c r="D1" s="653"/>
-      <c r="E1" s="653"/>
-      <c r="F1" s="653"/>
-      <c r="G1" s="653"/>
-      <c r="H1" s="653"/>
-      <c r="I1" s="653"/>
-      <c r="J1" s="653"/>
-      <c r="K1" s="653"/>
-      <c r="L1" s="653"/>
-      <c r="M1" s="653"/>
-      <c r="N1" s="653"/>
-      <c r="O1" s="653"/>
-      <c r="P1" s="654"/>
+      <c r="C1" s="690"/>
+      <c r="D1" s="690"/>
+      <c r="E1" s="690"/>
+      <c r="F1" s="690"/>
+      <c r="G1" s="690"/>
+      <c r="H1" s="690"/>
+      <c r="I1" s="690"/>
+      <c r="J1" s="690"/>
+      <c r="K1" s="690"/>
+      <c r="L1" s="690"/>
+      <c r="M1" s="690"/>
+      <c r="N1" s="690"/>
+      <c r="O1" s="690"/>
+      <c r="P1" s="691"/>
       <c r="Q1" s="98"/>
       <c r="R1" s="98"/>
       <c r="S1" s="98"/>
@@ -31771,23 +31749,23 @@
     </row>
     <row r="2" spans="1:21" ht="18" customHeight="1">
       <c r="A2" s="98"/>
-      <c r="B2" s="655" t="s">
+      <c r="B2" s="692" t="s">
         <v>179</v>
       </c>
-      <c r="C2" s="656"/>
-      <c r="D2" s="656"/>
-      <c r="E2" s="656"/>
-      <c r="F2" s="656"/>
-      <c r="G2" s="656"/>
-      <c r="H2" s="656"/>
-      <c r="I2" s="656"/>
-      <c r="J2" s="656"/>
-      <c r="K2" s="656"/>
-      <c r="L2" s="656"/>
-      <c r="M2" s="656"/>
-      <c r="N2" s="656"/>
-      <c r="O2" s="656"/>
-      <c r="P2" s="657"/>
+      <c r="C2" s="693"/>
+      <c r="D2" s="693"/>
+      <c r="E2" s="693"/>
+      <c r="F2" s="693"/>
+      <c r="G2" s="693"/>
+      <c r="H2" s="693"/>
+      <c r="I2" s="693"/>
+      <c r="J2" s="693"/>
+      <c r="K2" s="693"/>
+      <c r="L2" s="693"/>
+      <c r="M2" s="693"/>
+      <c r="N2" s="693"/>
+      <c r="O2" s="693"/>
+      <c r="P2" s="694"/>
       <c r="Q2" s="98"/>
       <c r="R2" s="98"/>
       <c r="S2" s="98"/>
@@ -31828,14 +31806,14 @@
       <c r="H4" s="96"/>
       <c r="I4" s="104"/>
       <c r="J4" s="251"/>
-      <c r="K4" s="670" t="s">
+      <c r="K4" s="682" t="s">
         <v>219</v>
       </c>
-      <c r="L4" s="670"/>
-      <c r="M4" s="670"/>
-      <c r="N4" s="670"/>
-      <c r="O4" s="670"/>
-      <c r="P4" s="670"/>
+      <c r="L4" s="682"/>
+      <c r="M4" s="682"/>
+      <c r="N4" s="682"/>
+      <c r="O4" s="682"/>
+      <c r="P4" s="682"/>
       <c r="Q4" s="98"/>
       <c r="R4" s="98"/>
       <c r="S4" s="98"/>
@@ -31848,18 +31826,18 @@
       <c r="H5" s="95"/>
       <c r="I5" s="98"/>
       <c r="J5" s="252"/>
-      <c r="K5" s="666" t="s">
+      <c r="K5" s="699" t="s">
         <v>181</v>
       </c>
-      <c r="L5" s="666"/>
-      <c r="M5" s="666" t="s">
+      <c r="L5" s="699"/>
+      <c r="M5" s="699" t="s">
         <v>184</v>
       </c>
-      <c r="N5" s="666"/>
-      <c r="O5" s="666" t="s">
+      <c r="N5" s="699"/>
+      <c r="O5" s="699" t="s">
         <v>185</v>
       </c>
-      <c r="P5" s="666"/>
+      <c r="P5" s="699"/>
       <c r="Q5" s="96"/>
       <c r="R5" s="98"/>
       <c r="S5" s="98"/>
@@ -31872,18 +31850,18 @@
       <c r="H6" s="95"/>
       <c r="I6" s="98"/>
       <c r="J6" s="95"/>
-      <c r="K6" s="681" t="s">
+      <c r="K6" s="678" t="s">
         <v>196</v>
       </c>
-      <c r="L6" s="662"/>
-      <c r="M6" s="661" t="s">
+      <c r="L6" s="679"/>
+      <c r="M6" s="698" t="s">
         <v>393</v>
       </c>
-      <c r="N6" s="662"/>
-      <c r="O6" s="661" t="s">
+      <c r="N6" s="679"/>
+      <c r="O6" s="698" t="s">
         <v>158</v>
       </c>
-      <c r="P6" s="667"/>
+      <c r="P6" s="700"/>
       <c r="Q6" s="96"/>
       <c r="R6" s="98"/>
       <c r="S6" s="98"/>
@@ -31894,24 +31872,24 @@
       <c r="A7" s="98"/>
       <c r="C7" s="98"/>
       <c r="D7" s="98"/>
-      <c r="E7" s="668"/>
-      <c r="F7" s="669"/>
-      <c r="G7" s="669"/>
-      <c r="H7" s="669"/>
+      <c r="E7" s="680"/>
+      <c r="F7" s="681"/>
+      <c r="G7" s="681"/>
+      <c r="H7" s="681"/>
       <c r="I7" s="98"/>
       <c r="J7" s="119"/>
-      <c r="K7" s="671" t="s">
+      <c r="K7" s="674" t="s">
         <v>196</v>
       </c>
-      <c r="L7" s="664"/>
-      <c r="M7" s="663" t="s">
+      <c r="L7" s="671"/>
+      <c r="M7" s="670" t="s">
         <v>394</v>
       </c>
-      <c r="N7" s="664"/>
-      <c r="O7" s="663" t="s">
+      <c r="N7" s="671"/>
+      <c r="O7" s="670" t="s">
         <v>158</v>
       </c>
-      <c r="P7" s="665"/>
+      <c r="P7" s="677"/>
       <c r="Q7" s="96"/>
       <c r="R7" s="98"/>
       <c r="S7" s="98"/>
@@ -31925,18 +31903,18 @@
       <c r="D8" s="98"/>
       <c r="I8" s="98"/>
       <c r="J8" s="95"/>
-      <c r="K8" s="671" t="s">
+      <c r="K8" s="674" t="s">
         <v>195</v>
       </c>
-      <c r="L8" s="664"/>
-      <c r="M8" s="663" t="s">
+      <c r="L8" s="671"/>
+      <c r="M8" s="670" t="s">
         <v>395</v>
       </c>
-      <c r="N8" s="664"/>
-      <c r="O8" s="663" t="s">
+      <c r="N8" s="671"/>
+      <c r="O8" s="670" t="s">
         <v>158</v>
       </c>
-      <c r="P8" s="665"/>
+      <c r="P8" s="677"/>
       <c r="Q8" s="96"/>
       <c r="R8" s="98"/>
       <c r="S8" s="98"/>
@@ -31950,18 +31928,18 @@
       <c r="D9" s="98"/>
       <c r="I9" s="98"/>
       <c r="J9" s="119"/>
-      <c r="K9" s="671" t="s">
+      <c r="K9" s="674" t="s">
         <v>195</v>
       </c>
-      <c r="L9" s="664"/>
-      <c r="M9" s="663" t="s">
+      <c r="L9" s="671"/>
+      <c r="M9" s="670" t="s">
         <v>396</v>
       </c>
-      <c r="N9" s="664"/>
-      <c r="O9" s="663" t="s">
+      <c r="N9" s="671"/>
+      <c r="O9" s="670" t="s">
         <v>158</v>
       </c>
-      <c r="P9" s="665"/>
+      <c r="P9" s="677"/>
       <c r="Q9" s="96"/>
       <c r="R9" s="98"/>
       <c r="S9" s="98"/>
@@ -31975,18 +31953,18 @@
       <c r="D10" s="98"/>
       <c r="I10" s="98"/>
       <c r="J10" s="95"/>
-      <c r="K10" s="671" t="s">
+      <c r="K10" s="674" t="s">
         <v>195</v>
       </c>
-      <c r="L10" s="664"/>
-      <c r="M10" s="663" t="s">
+      <c r="L10" s="671"/>
+      <c r="M10" s="670" t="s">
         <v>397</v>
       </c>
-      <c r="N10" s="664"/>
-      <c r="O10" s="663" t="s">
+      <c r="N10" s="671"/>
+      <c r="O10" s="670" t="s">
         <v>158</v>
       </c>
-      <c r="P10" s="665"/>
+      <c r="P10" s="677"/>
       <c r="Q10" s="96"/>
       <c r="R10" s="98"/>
       <c r="S10" s="98"/>
@@ -31998,26 +31976,26 @@
       <c r="B11" s="98"/>
       <c r="C11" s="98"/>
       <c r="D11" s="95"/>
-      <c r="E11" s="658" t="s">
+      <c r="E11" s="695" t="s">
         <v>183</v>
       </c>
-      <c r="F11" s="659"/>
-      <c r="G11" s="659"/>
-      <c r="H11" s="660"/>
+      <c r="F11" s="696"/>
+      <c r="G11" s="696"/>
+      <c r="H11" s="697"/>
       <c r="I11" s="96"/>
       <c r="J11" s="119"/>
-      <c r="K11" s="671" t="s">
+      <c r="K11" s="674" t="s">
         <v>391</v>
       </c>
-      <c r="L11" s="664"/>
-      <c r="M11" s="663" t="s">
+      <c r="L11" s="671"/>
+      <c r="M11" s="670" t="s">
         <v>398</v>
       </c>
-      <c r="N11" s="664"/>
-      <c r="O11" s="663" t="s">
+      <c r="N11" s="671"/>
+      <c r="O11" s="670" t="s">
         <v>158</v>
       </c>
-      <c r="P11" s="665"/>
+      <c r="P11" s="677"/>
       <c r="Q11" s="96"/>
       <c r="R11" s="98"/>
       <c r="S11" s="98"/>
@@ -32029,28 +32007,28 @@
       <c r="B12" s="98"/>
       <c r="C12" s="98"/>
       <c r="D12" s="95"/>
-      <c r="E12" s="672" t="s">
+      <c r="E12" s="683" t="s">
         <v>181</v>
       </c>
-      <c r="F12" s="673"/>
-      <c r="G12" s="674"/>
+      <c r="F12" s="684"/>
+      <c r="G12" s="685"/>
       <c r="H12" s="261" t="s">
         <v>182</v>
       </c>
       <c r="I12" s="96"/>
       <c r="J12" s="119"/>
-      <c r="K12" s="671" t="s">
+      <c r="K12" s="674" t="s">
         <v>391</v>
       </c>
-      <c r="L12" s="664"/>
-      <c r="M12" s="663" t="s">
+      <c r="L12" s="671"/>
+      <c r="M12" s="670" t="s">
         <v>399</v>
       </c>
-      <c r="N12" s="664"/>
-      <c r="O12" s="663" t="s">
+      <c r="N12" s="671"/>
+      <c r="O12" s="670" t="s">
         <v>406</v>
       </c>
-      <c r="P12" s="665"/>
+      <c r="P12" s="677"/>
       <c r="Q12" s="96"/>
       <c r="R12" s="98"/>
       <c r="S12" s="98"/>
@@ -32062,28 +32040,28 @@
       <c r="B13" s="98"/>
       <c r="C13" s="98"/>
       <c r="D13" s="95"/>
-      <c r="E13" s="675" t="s">
+      <c r="E13" s="686" t="s">
         <v>198</v>
       </c>
-      <c r="F13" s="676"/>
-      <c r="G13" s="677"/>
+      <c r="F13" s="687"/>
+      <c r="G13" s="688"/>
       <c r="H13" s="316">
         <v>2</v>
       </c>
       <c r="I13" s="96"/>
       <c r="J13" s="95"/>
-      <c r="K13" s="671" t="s">
+      <c r="K13" s="674" t="s">
         <v>392</v>
       </c>
-      <c r="L13" s="664"/>
-      <c r="M13" s="663" t="s">
+      <c r="L13" s="671"/>
+      <c r="M13" s="670" t="s">
         <v>400</v>
       </c>
-      <c r="N13" s="664"/>
-      <c r="O13" s="663" t="s">
+      <c r="N13" s="671"/>
+      <c r="O13" s="670" t="s">
         <v>158</v>
       </c>
-      <c r="P13" s="665"/>
+      <c r="P13" s="677"/>
       <c r="Q13" s="96"/>
       <c r="R13" s="98"/>
       <c r="S13" s="98"/>
@@ -32095,28 +32073,28 @@
       <c r="B14" s="98"/>
       <c r="C14" s="98"/>
       <c r="D14" s="95"/>
-      <c r="E14" s="678" t="s">
+      <c r="E14" s="660" t="s">
         <v>196</v>
       </c>
-      <c r="F14" s="679"/>
-      <c r="G14" s="680"/>
+      <c r="F14" s="661"/>
+      <c r="G14" s="662"/>
       <c r="H14" s="317">
         <v>26</v>
       </c>
       <c r="I14" s="96"/>
       <c r="J14" s="103"/>
-      <c r="K14" s="671" t="s">
+      <c r="K14" s="674" t="s">
         <v>392</v>
       </c>
-      <c r="L14" s="664"/>
-      <c r="M14" s="663" t="s">
+      <c r="L14" s="671"/>
+      <c r="M14" s="670" t="s">
         <v>401</v>
       </c>
-      <c r="N14" s="664"/>
-      <c r="O14" s="663" t="s">
+      <c r="N14" s="671"/>
+      <c r="O14" s="670" t="s">
         <v>158</v>
       </c>
-      <c r="P14" s="665"/>
+      <c r="P14" s="677"/>
       <c r="Q14" s="96"/>
       <c r="R14" s="98"/>
       <c r="S14" s="98"/>
@@ -32128,28 +32106,28 @@
       <c r="B15" s="98"/>
       <c r="C15" s="98"/>
       <c r="D15" s="95"/>
-      <c r="E15" s="678" t="s">
+      <c r="E15" s="660" t="s">
         <v>197</v>
       </c>
-      <c r="F15" s="679"/>
-      <c r="G15" s="680"/>
+      <c r="F15" s="661"/>
+      <c r="G15" s="662"/>
       <c r="H15" s="317">
         <v>5</v>
       </c>
       <c r="I15" s="96"/>
       <c r="J15" s="95"/>
-      <c r="K15" s="671" t="s">
+      <c r="K15" s="674" t="s">
         <v>195</v>
       </c>
-      <c r="L15" s="664"/>
-      <c r="M15" s="663" t="s">
+      <c r="L15" s="671"/>
+      <c r="M15" s="670" t="s">
         <v>402</v>
       </c>
-      <c r="N15" s="664"/>
-      <c r="O15" s="663" t="s">
+      <c r="N15" s="671"/>
+      <c r="O15" s="670" t="s">
         <v>158</v>
       </c>
-      <c r="P15" s="665"/>
+      <c r="P15" s="677"/>
       <c r="Q15" s="96"/>
       <c r="R15" s="98"/>
       <c r="S15" s="98"/>
@@ -32161,28 +32139,28 @@
       <c r="B16" s="98"/>
       <c r="C16" s="98"/>
       <c r="D16" s="95"/>
-      <c r="E16" s="678" t="s">
+      <c r="E16" s="660" t="s">
         <v>199</v>
       </c>
-      <c r="F16" s="679"/>
-      <c r="G16" s="680"/>
+      <c r="F16" s="661"/>
+      <c r="G16" s="662"/>
       <c r="H16" s="317">
         <v>29</v>
       </c>
       <c r="I16" s="96"/>
       <c r="J16" s="119"/>
-      <c r="K16" s="671" t="s">
+      <c r="K16" s="674" t="s">
         <v>195</v>
       </c>
-      <c r="L16" s="664"/>
-      <c r="M16" s="663" t="s">
+      <c r="L16" s="671"/>
+      <c r="M16" s="670" t="s">
         <v>403</v>
       </c>
-      <c r="N16" s="664"/>
-      <c r="O16" s="663" t="s">
+      <c r="N16" s="671"/>
+      <c r="O16" s="670" t="s">
         <v>158</v>
       </c>
-      <c r="P16" s="665"/>
+      <c r="P16" s="677"/>
       <c r="Q16" s="96"/>
       <c r="R16" s="98"/>
       <c r="S16" s="98"/>
@@ -32192,28 +32170,28 @@
     <row r="17" spans="1:21" ht="66" customHeight="1">
       <c r="A17" s="95"/>
       <c r="D17" s="114"/>
-      <c r="E17" s="678" t="s">
+      <c r="E17" s="660" t="s">
         <v>200</v>
       </c>
-      <c r="F17" s="679"/>
-      <c r="G17" s="680"/>
+      <c r="F17" s="661"/>
+      <c r="G17" s="662"/>
       <c r="H17" s="317">
         <v>6</v>
       </c>
       <c r="I17" s="96"/>
       <c r="J17" s="119"/>
-      <c r="K17" s="671" t="s">
+      <c r="K17" s="674" t="s">
         <v>197</v>
       </c>
-      <c r="L17" s="664"/>
-      <c r="M17" s="663" t="s">
+      <c r="L17" s="671"/>
+      <c r="M17" s="670" t="s">
         <v>404</v>
       </c>
-      <c r="N17" s="664"/>
-      <c r="O17" s="663" t="s">
+      <c r="N17" s="671"/>
+      <c r="O17" s="670" t="s">
         <v>406</v>
       </c>
-      <c r="P17" s="665"/>
+      <c r="P17" s="677"/>
       <c r="Q17" s="96"/>
       <c r="R17" s="98"/>
       <c r="S17" s="98"/>
@@ -32224,28 +32202,28 @@
       <c r="A18" s="95"/>
       <c r="C18" s="123"/>
       <c r="D18" s="95"/>
-      <c r="E18" s="690" t="s">
+      <c r="E18" s="663" t="s">
         <v>201</v>
       </c>
-      <c r="F18" s="691"/>
-      <c r="G18" s="692"/>
+      <c r="F18" s="664"/>
+      <c r="G18" s="665"/>
       <c r="H18" s="318">
         <v>25</v>
       </c>
       <c r="I18" s="96"/>
       <c r="J18" s="95"/>
-      <c r="K18" s="698" t="s">
+      <c r="K18" s="675" t="s">
         <v>197</v>
       </c>
-      <c r="L18" s="697"/>
-      <c r="M18" s="682" t="s">
+      <c r="L18" s="673"/>
+      <c r="M18" s="672" t="s">
         <v>405</v>
       </c>
-      <c r="N18" s="697"/>
-      <c r="O18" s="682" t="s">
+      <c r="N18" s="673"/>
+      <c r="O18" s="672" t="s">
         <v>406</v>
       </c>
-      <c r="P18" s="683"/>
+      <c r="P18" s="676"/>
       <c r="Q18" s="96"/>
       <c r="R18" s="98"/>
       <c r="S18" s="95"/>
@@ -32336,10 +32314,10 @@
         <v>183</v>
       </c>
       <c r="G22" s="292"/>
-      <c r="H22" s="693" t="s">
+      <c r="H22" s="666" t="s">
         <v>186</v>
       </c>
-      <c r="I22" s="694"/>
+      <c r="I22" s="667"/>
       <c r="J22" s="301"/>
       <c r="K22" s="311"/>
       <c r="L22" s="289"/>
@@ -32450,17 +32428,17 @@
       <c r="F26" s="314" t="s">
         <v>187</v>
       </c>
-      <c r="H26" s="695" t="s">
+      <c r="H26" s="668" t="s">
         <v>215</v>
       </c>
-      <c r="I26" s="696"/>
+      <c r="I26" s="669"/>
       <c r="J26" s="396"/>
-      <c r="K26" s="684" t="s">
+      <c r="K26" s="654" t="s">
         <v>218</v>
       </c>
-      <c r="L26" s="685"/>
-      <c r="M26" s="685"/>
-      <c r="N26" s="686"/>
+      <c r="L26" s="655"/>
+      <c r="M26" s="655"/>
+      <c r="N26" s="656"/>
       <c r="O26" s="96"/>
       <c r="P26" s="193"/>
       <c r="Q26" s="96"/>
@@ -32488,12 +32466,12 @@
       </c>
       <c r="I27" s="256"/>
       <c r="J27" s="253"/>
-      <c r="K27" s="687" t="s">
+      <c r="K27" s="657" t="s">
         <v>217</v>
       </c>
-      <c r="L27" s="688"/>
-      <c r="M27" s="688"/>
-      <c r="N27" s="689"/>
+      <c r="L27" s="658"/>
+      <c r="M27" s="658"/>
+      <c r="N27" s="659"/>
       <c r="O27" s="194"/>
       <c r="P27" s="164"/>
       <c r="Q27" s="96"/>
@@ -32940,32 +32918,22 @@
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="K4:P4"/>
     <mergeCell ref="M15:N15"/>
@@ -32982,22 +32950,32 @@
     <mergeCell ref="K13:L13"/>
     <mergeCell ref="K14:L14"/>
     <mergeCell ref="K15:L15"/>
-    <mergeCell ref="B1:P1"/>
-    <mergeCell ref="B2:P2"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K18:L18"/>
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -33270,14 +33248,14 @@
       <c r="G2" s="324"/>
       <c r="H2" s="324"/>
       <c r="I2" s="324"/>
-      <c r="J2" s="464" t="s">
+      <c r="J2" s="476" t="s">
         <v>205</v>
       </c>
-      <c r="K2" s="464"/>
-      <c r="L2" s="464"/>
-      <c r="M2" s="464"/>
-      <c r="N2" s="464"/>
-      <c r="O2" s="464"/>
+      <c r="K2" s="476"/>
+      <c r="L2" s="476"/>
+      <c r="M2" s="476"/>
+      <c r="N2" s="476"/>
+      <c r="O2" s="476"/>
       <c r="P2" s="324"/>
       <c r="Q2" s="324"/>
       <c r="R2" s="324"/>
@@ -33318,14 +33296,14 @@
       <c r="I4" s="325" t="s">
         <v>203</v>
       </c>
-      <c r="J4" s="463" t="s">
+      <c r="J4" s="475" t="s">
         <v>204</v>
       </c>
-      <c r="K4" s="463"/>
-      <c r="L4" s="463"/>
-      <c r="M4" s="463"/>
-      <c r="N4" s="463"/>
-      <c r="O4" s="463"/>
+      <c r="K4" s="475"/>
+      <c r="L4" s="475"/>
+      <c r="M4" s="475"/>
+      <c r="N4" s="475"/>
+      <c r="O4" s="475"/>
       <c r="P4" s="235"/>
       <c r="Q4" s="235"/>
       <c r="R4" s="236"/>
@@ -33341,17 +33319,17 @@
       <c r="G5" s="326"/>
       <c r="H5" s="326"/>
       <c r="I5" s="328"/>
-      <c r="J5" s="474" t="s">
+      <c r="J5" s="468" t="s">
         <v>176</v>
       </c>
-      <c r="K5" s="474"/>
-      <c r="L5" s="474"/>
-      <c r="M5" s="474"/>
-      <c r="N5" s="471" t="s">
+      <c r="K5" s="468"/>
+      <c r="L5" s="468"/>
+      <c r="M5" s="468"/>
+      <c r="N5" s="480" t="s">
         <v>223</v>
       </c>
-      <c r="O5" s="471"/>
-      <c r="P5" s="471"/>
+      <c r="O5" s="480"/>
+      <c r="P5" s="480"/>
       <c r="Q5" s="327"/>
       <c r="R5" s="327"/>
       <c r="S5" s="28"/>
@@ -33382,12 +33360,12 @@
     </row>
     <row r="8" spans="1:19" ht="45.75" customHeight="1" thickBot="1">
       <c r="A8" s="29"/>
-      <c r="C8" s="475" t="str">
+      <c r="C8" s="471" t="str">
         <f>_xlfn.CONCAT("PERIODO ", N5)</f>
         <v>PERIODO FEBRERO - 2025</v>
       </c>
-      <c r="D8" s="476"/>
-      <c r="E8" s="477"/>
+      <c r="D8" s="472"/>
+      <c r="E8" s="473"/>
       <c r="G8" s="66" t="s">
         <v>1</v>
       </c>
@@ -33430,11 +33408,11 @@
     </row>
     <row r="10" spans="1:19" ht="42" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="C10" s="478" t="s">
+      <c r="C10" s="474" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="478"/>
-      <c r="E10" s="478"/>
+      <c r="D10" s="474"/>
+      <c r="E10" s="474"/>
       <c r="G10" s="92" t="s">
         <v>8</v>
       </c>
@@ -33465,11 +33443,11 @@
       <c r="C11" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="465">
+      <c r="D11" s="467">
         <f>R13</f>
         <v>6</v>
       </c>
-      <c r="E11" s="465"/>
+      <c r="E11" s="467"/>
       <c r="G11" s="58" t="s">
         <v>9</v>
       </c>
@@ -33500,11 +33478,11 @@
       <c r="C12" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="465">
+      <c r="D12" s="467">
         <f>R12</f>
         <v>4</v>
       </c>
-      <c r="E12" s="465"/>
+      <c r="E12" s="467"/>
       <c r="G12" s="58" t="s">
         <v>7</v>
       </c>
@@ -33535,11 +33513,11 @@
       <c r="C13" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="465">
+      <c r="D13" s="467">
         <f>R10</f>
         <v>33</v>
       </c>
-      <c r="E13" s="465"/>
+      <c r="E13" s="467"/>
       <c r="G13" s="93" t="s">
         <v>6</v>
       </c>
@@ -33570,11 +33548,11 @@
       <c r="C14" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="465">
+      <c r="D14" s="467">
         <f>R11</f>
         <v>78</v>
       </c>
-      <c r="E14" s="465"/>
+      <c r="E14" s="467"/>
       <c r="G14" s="64" t="s">
         <v>10</v>
       </c>
@@ -33608,11 +33586,11 @@
       <c r="C15" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="473">
+      <c r="D15" s="466">
         <f>R14</f>
         <v>121</v>
       </c>
-      <c r="E15" s="473"/>
+      <c r="E15" s="466"/>
       <c r="H15" s="45"/>
       <c r="M15" s="45"/>
       <c r="N15" s="45"/>
@@ -33655,11 +33633,11 @@
     </row>
     <row r="24" spans="1:19" ht="50.25" customHeight="1">
       <c r="A24" s="29"/>
-      <c r="C24" s="466" t="s">
+      <c r="C24" s="477" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="467"/>
-      <c r="E24" s="468"/>
+      <c r="D24" s="478"/>
+      <c r="E24" s="479"/>
       <c r="S24" s="28"/>
     </row>
     <row r="25" spans="1:19" ht="32.25" customHeight="1">
@@ -33691,11 +33669,11 @@
       <c r="C27" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="465">
+      <c r="D27" s="467">
         <f>SUM(M10:O10)</f>
         <v>0</v>
       </c>
-      <c r="E27" s="465"/>
+      <c r="E27" s="467"/>
       <c r="S27" s="28"/>
     </row>
     <row r="28" spans="1:19" ht="25.5" customHeight="1">
@@ -33703,11 +33681,11 @@
       <c r="C28" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D28" s="465">
+      <c r="D28" s="467">
         <f>SUM(M11:O11)</f>
         <v>0</v>
       </c>
-      <c r="E28" s="465"/>
+      <c r="E28" s="467"/>
       <c r="S28" s="28"/>
     </row>
     <row r="29" spans="1:19" ht="33" customHeight="1">
@@ -33715,11 +33693,11 @@
       <c r="C29" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="472">
+      <c r="D29" s="465">
         <f>SUM(M14:O14)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="472"/>
+      <c r="E29" s="465"/>
       <c r="S29" s="28"/>
     </row>
     <row r="30" spans="1:19">
@@ -33833,6 +33811,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="J4:O4"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="N5:P5"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D27:E27"/>
@@ -33844,12 +33828,6 @@
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="D11:E11"/>
-    <mergeCell ref="J4:O4"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="N5:P5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -34439,37 +34417,37 @@
       <c r="AA1" s="21"/>
     </row>
     <row r="2" spans="1:27" ht="37.15" customHeight="1">
-      <c r="A2" s="479" t="s">
+      <c r="A2" s="481" t="s">
         <v>175</v>
       </c>
-      <c r="B2" s="480"/>
-      <c r="C2" s="480"/>
-      <c r="D2" s="480"/>
-      <c r="E2" s="480"/>
-      <c r="F2" s="480"/>
-      <c r="G2" s="480"/>
-      <c r="H2" s="480"/>
-      <c r="I2" s="480"/>
-      <c r="J2" s="480"/>
-      <c r="K2" s="480"/>
-      <c r="L2" s="480"/>
-      <c r="M2" s="480"/>
-      <c r="N2" s="480"/>
-      <c r="O2" s="480"/>
-      <c r="P2" s="480"/>
-      <c r="Q2" s="480"/>
-      <c r="R2" s="480"/>
-      <c r="S2" s="480"/>
-      <c r="T2" s="481" t="s">
+      <c r="B2" s="482"/>
+      <c r="C2" s="482"/>
+      <c r="D2" s="482"/>
+      <c r="E2" s="482"/>
+      <c r="F2" s="482"/>
+      <c r="G2" s="482"/>
+      <c r="H2" s="482"/>
+      <c r="I2" s="482"/>
+      <c r="J2" s="482"/>
+      <c r="K2" s="482"/>
+      <c r="L2" s="482"/>
+      <c r="M2" s="482"/>
+      <c r="N2" s="482"/>
+      <c r="O2" s="482"/>
+      <c r="P2" s="482"/>
+      <c r="Q2" s="482"/>
+      <c r="R2" s="482"/>
+      <c r="S2" s="482"/>
+      <c r="T2" s="483" t="s">
         <v>223</v>
       </c>
-      <c r="U2" s="481"/>
-      <c r="V2" s="481"/>
-      <c r="W2" s="481"/>
-      <c r="X2" s="481"/>
-      <c r="Y2" s="481"/>
-      <c r="Z2" s="481"/>
-      <c r="AA2" s="482"/>
+      <c r="U2" s="483"/>
+      <c r="V2" s="483"/>
+      <c r="W2" s="483"/>
+      <c r="X2" s="483"/>
+      <c r="Y2" s="483"/>
+      <c r="Z2" s="483"/>
+      <c r="AA2" s="484"/>
     </row>
     <row r="3" spans="1:27" ht="2.4500000000000002" customHeight="1">
       <c r="A3" s="22"/>
@@ -36228,51 +36206,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="18.75">
-      <c r="A1" s="483" t="s">
+      <c r="A1" s="485" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="484"/>
-      <c r="C1" s="484"/>
-      <c r="D1" s="484"/>
-      <c r="E1" s="484"/>
-      <c r="F1" s="484"/>
-      <c r="G1" s="484"/>
-      <c r="H1" s="484"/>
-      <c r="I1" s="484"/>
-      <c r="J1" s="484"/>
-      <c r="K1" s="484"/>
-      <c r="L1" s="484"/>
-      <c r="M1" s="484"/>
-      <c r="N1" s="484"/>
-      <c r="O1" s="484"/>
-      <c r="P1" s="484"/>
-      <c r="Q1" s="484"/>
-      <c r="R1" s="484"/>
+      <c r="B1" s="486"/>
+      <c r="C1" s="486"/>
+      <c r="D1" s="486"/>
+      <c r="E1" s="486"/>
+      <c r="F1" s="486"/>
+      <c r="G1" s="486"/>
+      <c r="H1" s="486"/>
+      <c r="I1" s="486"/>
+      <c r="J1" s="486"/>
+      <c r="K1" s="486"/>
+      <c r="L1" s="486"/>
+      <c r="M1" s="486"/>
+      <c r="N1" s="486"/>
+      <c r="O1" s="486"/>
+      <c r="P1" s="486"/>
+      <c r="Q1" s="486"/>
+      <c r="R1" s="486"/>
     </row>
     <row r="2" spans="1:21" ht="19.5" thickBot="1">
-      <c r="A2" s="485" t="s">
+      <c r="A2" s="487" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="486"/>
-      <c r="C2" s="486"/>
-      <c r="D2" s="486"/>
-      <c r="E2" s="486"/>
-      <c r="F2" s="486"/>
-      <c r="G2" s="486"/>
-      <c r="H2" s="486"/>
-      <c r="I2" s="486"/>
-      <c r="J2" s="486"/>
-      <c r="K2" s="486"/>
-      <c r="L2" s="486"/>
-      <c r="M2" s="486"/>
-      <c r="N2" s="486"/>
-      <c r="O2" s="486"/>
-      <c r="P2" s="486"/>
-      <c r="Q2" s="486"/>
-      <c r="R2" s="486"/>
+      <c r="B2" s="488"/>
+      <c r="C2" s="488"/>
+      <c r="D2" s="488"/>
+      <c r="E2" s="488"/>
+      <c r="F2" s="488"/>
+      <c r="G2" s="488"/>
+      <c r="H2" s="488"/>
+      <c r="I2" s="488"/>
+      <c r="J2" s="488"/>
+      <c r="K2" s="488"/>
+      <c r="L2" s="488"/>
+      <c r="M2" s="488"/>
+      <c r="N2" s="488"/>
+      <c r="O2" s="488"/>
+      <c r="P2" s="488"/>
+      <c r="Q2" s="488"/>
+      <c r="R2" s="488"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="425"/>
+      <c r="A3" s="427"/>
       <c r="B3" s="3" t="s">
         <v>223</v>
       </c>
@@ -36294,9 +36272,9 @@
       <c r="R3" s="3"/>
     </row>
     <row r="4" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A4" s="425"/>
-      <c r="B4" s="426"/>
-      <c r="C4" s="426"/>
+      <c r="A4" s="427"/>
+      <c r="B4" s="428"/>
+      <c r="C4" s="428"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -36314,632 +36292,632 @@
       <c r="R4" s="3"/>
     </row>
     <row r="5" spans="1:21" ht="88.5" customHeight="1" thickBot="1">
-      <c r="A5" s="425"/>
-      <c r="B5" s="443" t="s">
+      <c r="A5" s="427"/>
+      <c r="B5" s="445" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="487" t="s">
+      <c r="C5" s="489" t="s">
         <v>91</v>
       </c>
-      <c r="D5" s="487"/>
-      <c r="E5" s="487"/>
-      <c r="F5" s="487" t="s">
+      <c r="D5" s="489"/>
+      <c r="E5" s="489"/>
+      <c r="F5" s="489" t="s">
         <v>92</v>
       </c>
-      <c r="G5" s="487"/>
-      <c r="H5" s="487"/>
-      <c r="I5" s="487" t="s">
+      <c r="G5" s="489"/>
+      <c r="H5" s="489"/>
+      <c r="I5" s="489" t="s">
         <v>221</v>
       </c>
-      <c r="J5" s="487"/>
-      <c r="K5" s="487"/>
-      <c r="L5" s="487" t="s">
+      <c r="J5" s="489"/>
+      <c r="K5" s="489"/>
+      <c r="L5" s="489" t="s">
         <v>93</v>
       </c>
-      <c r="M5" s="487"/>
-      <c r="N5" s="487"/>
-      <c r="O5" s="487" t="s">
+      <c r="M5" s="489"/>
+      <c r="N5" s="489"/>
+      <c r="O5" s="489" t="s">
         <v>222</v>
       </c>
-      <c r="P5" s="487"/>
-      <c r="Q5" s="488"/>
-      <c r="R5" s="423"/>
-      <c r="S5" s="422"/>
+      <c r="P5" s="489"/>
+      <c r="Q5" s="490"/>
+      <c r="R5" s="425"/>
+      <c r="S5" s="424"/>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
     </row>
     <row r="6" spans="1:21" ht="21">
-      <c r="A6" s="425"/>
-      <c r="B6" s="444" t="s">
+      <c r="A6" s="427"/>
+      <c r="B6" s="446" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="429"/>
-      <c r="D6" s="430">
+      <c r="C6" s="431"/>
+      <c r="D6" s="432">
         <f>IF(data_status_reg!$E4="bajo",0,IF(data_status_reg!$E4="medio",0.5,IF(data_status_reg!$E4="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E6" s="431"/>
-      <c r="F6" s="431"/>
-      <c r="G6" s="430">
+      <c r="E6" s="433"/>
+      <c r="F6" s="433"/>
+      <c r="G6" s="432">
         <f>IF(data_status_reg!$E20="bajo",0,IF(data_status_reg!$E20="medio",0.5,IF(data_status_reg!$E20="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H6" s="431"/>
-      <c r="I6" s="431"/>
-      <c r="J6" s="430">
+      <c r="H6" s="433"/>
+      <c r="I6" s="433"/>
+      <c r="J6" s="432">
         <f>IF(data_status_reg!$E36="bajo",0,IF(data_status_reg!$E36="medio",0.5,IF(data_status_reg!$E36="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K6" s="431"/>
-      <c r="L6" s="431"/>
-      <c r="M6" s="430">
+      <c r="K6" s="433"/>
+      <c r="L6" s="433"/>
+      <c r="M6" s="432">
         <f>IF(data_status_reg!$E52="bajo",0,IF(data_status_reg!$E52="medio",0.5,IF(data_status_reg!$E52="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N6" s="432"/>
-      <c r="O6" s="446"/>
-      <c r="P6" s="430">
+      <c r="N6" s="434"/>
+      <c r="O6" s="448"/>
+      <c r="P6" s="432">
         <f>IF(data_status_reg!$E68="bajo",0,IF(data_status_reg!$E68="medio",0.5,IF(data_status_reg!$E68="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="433"/>
-      <c r="R6" s="424"/>
+      <c r="Q6" s="435"/>
+      <c r="R6" s="426"/>
     </row>
     <row r="7" spans="1:21" ht="21">
-      <c r="A7" s="425"/>
-      <c r="B7" s="444" t="s">
+      <c r="A7" s="427"/>
+      <c r="B7" s="446" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="434"/>
-      <c r="D7" s="419">
+      <c r="C7" s="436"/>
+      <c r="D7" s="421">
         <f>IF(data_status_reg!$E5="bajo",0,IF(data_status_reg!$E5="medio",0.5,IF(data_status_reg!$E5="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E7" s="420"/>
-      <c r="F7" s="420"/>
-      <c r="G7" s="419">
+      <c r="E7" s="422"/>
+      <c r="F7" s="422"/>
+      <c r="G7" s="421">
         <f>IF(data_status_reg!$E21="bajo",0,IF(data_status_reg!$E21="medio",0.5,IF(data_status_reg!$E21="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H7" s="420"/>
-      <c r="I7" s="420"/>
-      <c r="J7" s="419">
+      <c r="H7" s="422"/>
+      <c r="I7" s="422"/>
+      <c r="J7" s="421">
         <f>IF(data_status_reg!$E37="bajo",0,IF(data_status_reg!$E37="medio",0.5,IF(data_status_reg!$E37="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="420"/>
-      <c r="L7" s="420"/>
-      <c r="M7" s="419">
+      <c r="K7" s="422"/>
+      <c r="L7" s="422"/>
+      <c r="M7" s="421">
         <f>IF(data_status_reg!$E53="bajo",0,IF(data_status_reg!$E53="medio",0.5,IF(data_status_reg!$E53="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N7" s="417"/>
-      <c r="O7" s="447"/>
-      <c r="P7" s="419">
+      <c r="N7" s="419"/>
+      <c r="O7" s="449"/>
+      <c r="P7" s="421">
         <f>IF(data_status_reg!$E69="bajo",0,IF(data_status_reg!$E69="medio",0.5,IF(data_status_reg!$E69="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="435"/>
+      <c r="Q7" s="437"/>
       <c r="R7" s="3"/>
     </row>
     <row r="8" spans="1:21" ht="21">
-      <c r="A8" s="425"/>
-      <c r="B8" s="444" t="s">
+      <c r="A8" s="427"/>
+      <c r="B8" s="446" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="434"/>
-      <c r="D8" s="419">
+      <c r="C8" s="436"/>
+      <c r="D8" s="421">
         <f>IF(data_status_reg!$E6="bajo",0,IF(data_status_reg!$E6="medio",0.5,IF(data_status_reg!$E6="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E8" s="420"/>
-      <c r="F8" s="420"/>
-      <c r="G8" s="419">
+      <c r="E8" s="422"/>
+      <c r="F8" s="422"/>
+      <c r="G8" s="421">
         <f>IF(data_status_reg!$E22="bajo",0,IF(data_status_reg!$E22="medio",0.5,IF(data_status_reg!$E22="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H8" s="420"/>
-      <c r="I8" s="420"/>
-      <c r="J8" s="419">
+      <c r="H8" s="422"/>
+      <c r="I8" s="422"/>
+      <c r="J8" s="421">
         <f>IF(data_status_reg!$E38="bajo",0,IF(data_status_reg!$E38="medio",0.5,IF(data_status_reg!$E38="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="420"/>
-      <c r="L8" s="420"/>
-      <c r="M8" s="419">
+      <c r="K8" s="422"/>
+      <c r="L8" s="422"/>
+      <c r="M8" s="421">
         <f>IF(data_status_reg!$E54="bajo",0,IF(data_status_reg!$E54="medio",0.5,IF(data_status_reg!$E54="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N8" s="417"/>
-      <c r="O8" s="447"/>
-      <c r="P8" s="419">
+      <c r="N8" s="419"/>
+      <c r="O8" s="449"/>
+      <c r="P8" s="421">
         <f>IF(data_status_reg!$E70="bajo",0,IF(data_status_reg!$E70="medio",0.5,IF(data_status_reg!$E70="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="435"/>
+      <c r="Q8" s="437"/>
       <c r="R8" s="3"/>
     </row>
     <row r="9" spans="1:21" ht="21">
-      <c r="A9" s="425"/>
-      <c r="B9" s="444" t="s">
+      <c r="A9" s="427"/>
+      <c r="B9" s="446" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="434"/>
-      <c r="D9" s="419">
+      <c r="C9" s="436"/>
+      <c r="D9" s="421">
         <f>IF(data_status_reg!$E7="bajo",0,IF(data_status_reg!$E7="medio",0.5,IF(data_status_reg!$E7="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E9" s="420"/>
-      <c r="F9" s="420"/>
-      <c r="G9" s="419">
+      <c r="E9" s="422"/>
+      <c r="F9" s="422"/>
+      <c r="G9" s="421">
         <f>IF(data_status_reg!$E23="bajo",0,IF(data_status_reg!$E23="medio",0.5,IF(data_status_reg!$E23="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H9" s="420"/>
-      <c r="I9" s="420"/>
-      <c r="J9" s="419">
+      <c r="H9" s="422"/>
+      <c r="I9" s="422"/>
+      <c r="J9" s="421">
         <f>IF(data_status_reg!$E39="bajo",0,IF(data_status_reg!$E39="medio",0.5,IF(data_status_reg!$E39="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="420"/>
-      <c r="L9" s="420"/>
-      <c r="M9" s="419">
+      <c r="K9" s="422"/>
+      <c r="L9" s="422"/>
+      <c r="M9" s="421">
         <f>IF(data_status_reg!$E55="bajo",0,IF(data_status_reg!$E55="medio",0.5,IF(data_status_reg!$E55="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N9" s="417"/>
-      <c r="O9" s="447"/>
-      <c r="P9" s="419">
+      <c r="N9" s="419"/>
+      <c r="O9" s="449"/>
+      <c r="P9" s="421">
         <f>IF(data_status_reg!$E71="bajo",0,IF(data_status_reg!$E71="medio",0.5,IF(data_status_reg!$E71="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="435"/>
+      <c r="Q9" s="437"/>
       <c r="R9" s="3"/>
     </row>
     <row r="10" spans="1:21" ht="21">
-      <c r="A10" s="425"/>
-      <c r="B10" s="444" t="s">
+      <c r="A10" s="427"/>
+      <c r="B10" s="446" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="434"/>
-      <c r="D10" s="419">
+      <c r="C10" s="436"/>
+      <c r="D10" s="421">
         <f>IF(data_status_reg!$E8="bajo",0,IF(data_status_reg!$E8="medio",0.5,IF(data_status_reg!$E8="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E10" s="420"/>
-      <c r="F10" s="420"/>
-      <c r="G10" s="419">
+      <c r="E10" s="422"/>
+      <c r="F10" s="422"/>
+      <c r="G10" s="421">
         <f>IF(data_status_reg!$E24="bajo",0,IF(data_status_reg!$E24="medio",0.5,IF(data_status_reg!$E24="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H10" s="420"/>
-      <c r="I10" s="420"/>
-      <c r="J10" s="419">
+      <c r="H10" s="422"/>
+      <c r="I10" s="422"/>
+      <c r="J10" s="421">
         <f>IF(data_status_reg!$E40="bajo",0,IF(data_status_reg!$E40="medio",0.5,IF(data_status_reg!$E40="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="420"/>
-      <c r="L10" s="420"/>
-      <c r="M10" s="419">
+      <c r="K10" s="422"/>
+      <c r="L10" s="422"/>
+      <c r="M10" s="421">
         <f>IF(data_status_reg!$E56="bajo",0,IF(data_status_reg!$E56="medio",0.5,IF(data_status_reg!$E56="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N10" s="417"/>
-      <c r="O10" s="447"/>
-      <c r="P10" s="419">
+      <c r="N10" s="419"/>
+      <c r="O10" s="449"/>
+      <c r="P10" s="421">
         <f>IF(data_status_reg!$E72="bajo",0,IF(data_status_reg!$E72="medio",0.5,IF(data_status_reg!$E72="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="435"/>
+      <c r="Q10" s="437"/>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:21" ht="21">
-      <c r="A11" s="425"/>
-      <c r="B11" s="444" t="s">
+      <c r="A11" s="427"/>
+      <c r="B11" s="446" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="434"/>
-      <c r="D11" s="419">
+      <c r="C11" s="436"/>
+      <c r="D11" s="421">
         <f>IF(data_status_reg!$E9="bajo",0,IF(data_status_reg!$E9="medio",0.5,IF(data_status_reg!$E9="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E11" s="420"/>
-      <c r="F11" s="420"/>
-      <c r="G11" s="419">
+      <c r="E11" s="422"/>
+      <c r="F11" s="422"/>
+      <c r="G11" s="421">
         <f>IF(data_status_reg!$E25="bajo",0,IF(data_status_reg!$E25="medio",0.5,IF(data_status_reg!$E25="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H11" s="420"/>
-      <c r="I11" s="420"/>
-      <c r="J11" s="419">
+      <c r="H11" s="422"/>
+      <c r="I11" s="422"/>
+      <c r="J11" s="421">
         <f>IF(data_status_reg!$E41="bajo",0,IF(data_status_reg!$E41="medio",0.5,IF(data_status_reg!$E41="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="420"/>
-      <c r="L11" s="420"/>
-      <c r="M11" s="419">
+      <c r="K11" s="422"/>
+      <c r="L11" s="422"/>
+      <c r="M11" s="421">
         <f>IF(data_status_reg!$E57="bajo",0,IF(data_status_reg!$E57="medio",0.5,IF(data_status_reg!$E57="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N11" s="417"/>
-      <c r="O11" s="447"/>
-      <c r="P11" s="419">
+      <c r="N11" s="419"/>
+      <c r="O11" s="449"/>
+      <c r="P11" s="421">
         <f>IF(data_status_reg!$E73="bajo",0,IF(data_status_reg!$E73="medio",0.5,IF(data_status_reg!$E73="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="435"/>
+      <c r="Q11" s="437"/>
       <c r="R11" s="3"/>
     </row>
     <row r="12" spans="1:21" ht="21">
-      <c r="A12" s="425"/>
-      <c r="B12" s="444" t="s">
+      <c r="A12" s="427"/>
+      <c r="B12" s="446" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="434"/>
-      <c r="D12" s="419">
+      <c r="C12" s="436"/>
+      <c r="D12" s="421">
         <f>IF(data_status_reg!$E10="bajo",0,IF(data_status_reg!$E10="medio",0.5,IF(data_status_reg!$E10="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E12" s="420"/>
-      <c r="F12" s="420"/>
-      <c r="G12" s="419">
+      <c r="E12" s="422"/>
+      <c r="F12" s="422"/>
+      <c r="G12" s="421">
         <f>IF(data_status_reg!$E26="bajo",0,IF(data_status_reg!$E26="medio",0.5,IF(data_status_reg!$E26="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H12" s="420"/>
-      <c r="I12" s="421"/>
-      <c r="J12" s="419">
+      <c r="H12" s="422"/>
+      <c r="I12" s="423"/>
+      <c r="J12" s="421">
         <f>IF(data_status_reg!$E42="bajo",0,IF(data_status_reg!$E42="medio",0.5,IF(data_status_reg!$E42="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="421"/>
-      <c r="L12" s="421"/>
-      <c r="M12" s="419">
+      <c r="K12" s="423"/>
+      <c r="L12" s="423"/>
+      <c r="M12" s="421">
         <f>IF(data_status_reg!$E58="bajo",0,IF(data_status_reg!$E58="medio",0.5,IF(data_status_reg!$E58="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N12" s="418"/>
-      <c r="O12" s="448"/>
-      <c r="P12" s="419">
+      <c r="N12" s="420"/>
+      <c r="O12" s="450"/>
+      <c r="P12" s="421">
         <f>IF(data_status_reg!$E74="bajo",0,IF(data_status_reg!$E74="medio",0.5,IF(data_status_reg!$E74="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="435"/>
+      <c r="Q12" s="437"/>
       <c r="R12" s="3"/>
     </row>
     <row r="13" spans="1:21" ht="21">
-      <c r="A13" s="425"/>
-      <c r="B13" s="444" t="s">
+      <c r="A13" s="427"/>
+      <c r="B13" s="446" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="434"/>
-      <c r="D13" s="419">
+      <c r="C13" s="436"/>
+      <c r="D13" s="421">
         <f>IF(data_status_reg!$E11="bajo",0,IF(data_status_reg!$E11="medio",0.5,IF(data_status_reg!$E11="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E13" s="420"/>
-      <c r="F13" s="420"/>
-      <c r="G13" s="419">
+      <c r="E13" s="422"/>
+      <c r="F13" s="422"/>
+      <c r="G13" s="421">
         <f>IF(data_status_reg!$E27="bajo",0,IF(data_status_reg!$E27="medio",0.5,IF(data_status_reg!$E27="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H13" s="420"/>
-      <c r="I13" s="420"/>
-      <c r="J13" s="419">
+      <c r="H13" s="422"/>
+      <c r="I13" s="422"/>
+      <c r="J13" s="421">
         <f>IF(data_status_reg!$E43="bajo",0,IF(data_status_reg!$E43="medio",0.5,IF(data_status_reg!$E43="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="420"/>
-      <c r="L13" s="420"/>
-      <c r="M13" s="419">
+      <c r="K13" s="422"/>
+      <c r="L13" s="422"/>
+      <c r="M13" s="421">
         <f>IF(data_status_reg!$E59="bajo",0,IF(data_status_reg!$E59="medio",0.5,IF(data_status_reg!$E59="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N13" s="417"/>
-      <c r="O13" s="447"/>
-      <c r="P13" s="419">
+      <c r="N13" s="419"/>
+      <c r="O13" s="449"/>
+      <c r="P13" s="421">
         <f>IF(data_status_reg!$E75="bajo",0,IF(data_status_reg!$E75="medio",0.5,IF(data_status_reg!$E75="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q13" s="435"/>
+      <c r="Q13" s="437"/>
       <c r="R13" s="3"/>
       <c r="U13" s="16"/>
     </row>
     <row r="14" spans="1:21" ht="21">
-      <c r="A14" s="425"/>
-      <c r="B14" s="444" t="s">
+      <c r="A14" s="427"/>
+      <c r="B14" s="446" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="434"/>
-      <c r="D14" s="419">
+      <c r="C14" s="436"/>
+      <c r="D14" s="421">
         <f>IF(data_status_reg!$E12="bajo",0,IF(data_status_reg!$E12="medio",0.5,IF(data_status_reg!$E12="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E14" s="420"/>
-      <c r="F14" s="420"/>
-      <c r="G14" s="419">
+      <c r="E14" s="422"/>
+      <c r="F14" s="422"/>
+      <c r="G14" s="421">
         <f>IF(data_status_reg!$E28="bajo",0,IF(data_status_reg!$E28="medio",0.5,IF(data_status_reg!$E28="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H14" s="420"/>
-      <c r="I14" s="420"/>
-      <c r="J14" s="419">
+      <c r="H14" s="422"/>
+      <c r="I14" s="422"/>
+      <c r="J14" s="421">
         <f>IF(data_status_reg!$E44="bajo",0,IF(data_status_reg!$E44="medio",0.5,IF(data_status_reg!$E44="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K14" s="420"/>
-      <c r="L14" s="420"/>
-      <c r="M14" s="419">
+      <c r="K14" s="422"/>
+      <c r="L14" s="422"/>
+      <c r="M14" s="421">
         <f>IF(data_status_reg!$E60="bajo",0,IF(data_status_reg!$E60="medio",0.5,IF(data_status_reg!$E60="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N14" s="417"/>
-      <c r="O14" s="447"/>
-      <c r="P14" s="419">
+      <c r="N14" s="419"/>
+      <c r="O14" s="449"/>
+      <c r="P14" s="421">
         <f>IF(data_status_reg!$E76="bajo",0,IF(data_status_reg!$E76="medio",0.5,IF(data_status_reg!$E76="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q14" s="435"/>
+      <c r="Q14" s="437"/>
       <c r="R14" s="3"/>
     </row>
     <row r="15" spans="1:21" ht="21">
-      <c r="A15" s="425"/>
-      <c r="B15" s="444" t="s">
+      <c r="A15" s="427"/>
+      <c r="B15" s="446" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="434"/>
-      <c r="D15" s="419">
+      <c r="C15" s="436"/>
+      <c r="D15" s="421">
         <f>IF(data_status_reg!$E13="bajo",0,IF(data_status_reg!$E13="medio",0.5,IF(data_status_reg!$E13="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E15" s="420"/>
-      <c r="F15" s="420"/>
-      <c r="G15" s="419">
+      <c r="E15" s="422"/>
+      <c r="F15" s="422"/>
+      <c r="G15" s="421">
         <f>IF(data_status_reg!$E29="bajo",0,IF(data_status_reg!$E29="medio",0.5,IF(data_status_reg!$E29="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H15" s="420"/>
-      <c r="I15" s="421"/>
-      <c r="J15" s="419">
+      <c r="H15" s="422"/>
+      <c r="I15" s="423"/>
+      <c r="J15" s="421">
         <f>IF(data_status_reg!$E45="bajo",0,IF(data_status_reg!$E45="medio",0.5,IF(data_status_reg!$E45="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K15" s="421"/>
-      <c r="L15" s="421"/>
-      <c r="M15" s="419">
+      <c r="K15" s="423"/>
+      <c r="L15" s="423"/>
+      <c r="M15" s="421">
         <f>IF(data_status_reg!$E61="bajo",0,IF(data_status_reg!$E61="medio",0.5,IF(data_status_reg!$E61="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N15" s="418"/>
-      <c r="O15" s="448"/>
-      <c r="P15" s="419">
+      <c r="N15" s="420"/>
+      <c r="O15" s="450"/>
+      <c r="P15" s="421">
         <f>IF(data_status_reg!$E77="bajo",0,IF(data_status_reg!$E77="medio",0.5,IF(data_status_reg!$E77="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q15" s="435"/>
+      <c r="Q15" s="437"/>
       <c r="R15" s="3"/>
     </row>
     <row r="16" spans="1:21" ht="21">
-      <c r="A16" s="425"/>
-      <c r="B16" s="444" t="s">
+      <c r="A16" s="427"/>
+      <c r="B16" s="446" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="434"/>
-      <c r="D16" s="419">
+      <c r="C16" s="436"/>
+      <c r="D16" s="421">
         <f>IF(data_status_reg!$E14="bajo",0,IF(data_status_reg!$E14="medio",0.5,IF(data_status_reg!$E14="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E16" s="420"/>
-      <c r="F16" s="420"/>
-      <c r="G16" s="419">
+      <c r="E16" s="422"/>
+      <c r="F16" s="422"/>
+      <c r="G16" s="421">
         <f>IF(data_status_reg!$E30="bajo",0,IF(data_status_reg!$E30="medio",0.5,IF(data_status_reg!$E30="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H16" s="420"/>
-      <c r="I16" s="420"/>
-      <c r="J16" s="419">
+      <c r="H16" s="422"/>
+      <c r="I16" s="422"/>
+      <c r="J16" s="421">
         <f>IF(data_status_reg!$E46="bajo",0,IF(data_status_reg!$E46="medio",0.5,IF(data_status_reg!$E46="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K16" s="420"/>
-      <c r="L16" s="420"/>
-      <c r="M16" s="419">
+      <c r="K16" s="422"/>
+      <c r="L16" s="422"/>
+      <c r="M16" s="421">
         <f>IF(data_status_reg!$E62="bajo",0,IF(data_status_reg!$E62="medio",0.5,IF(data_status_reg!$E62="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N16" s="417"/>
-      <c r="O16" s="447"/>
-      <c r="P16" s="419">
+      <c r="N16" s="419"/>
+      <c r="O16" s="449"/>
+      <c r="P16" s="421">
         <f>IF(data_status_reg!$E78="bajo",0,IF(data_status_reg!$E78="medio",0.5,IF(data_status_reg!$E78="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q16" s="435"/>
+      <c r="Q16" s="437"/>
       <c r="R16" s="3"/>
     </row>
     <row r="17" spans="1:18" ht="21">
-      <c r="A17" s="425"/>
-      <c r="B17" s="444" t="s">
+      <c r="A17" s="427"/>
+      <c r="B17" s="446" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="434"/>
-      <c r="D17" s="419">
+      <c r="C17" s="436"/>
+      <c r="D17" s="421">
         <f>IF(data_status_reg!$E15="bajo",0,IF(data_status_reg!$E15="medio",0.5,IF(data_status_reg!$E15="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E17" s="420"/>
-      <c r="F17" s="420"/>
-      <c r="G17" s="419">
+      <c r="E17" s="422"/>
+      <c r="F17" s="422"/>
+      <c r="G17" s="421">
         <f>IF(data_status_reg!$E31="bajo",0,IF(data_status_reg!$E31="medio",0.5,IF(data_status_reg!$E31="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H17" s="420"/>
-      <c r="I17" s="420"/>
-      <c r="J17" s="419">
+      <c r="H17" s="422"/>
+      <c r="I17" s="422"/>
+      <c r="J17" s="421">
         <f>IF(data_status_reg!$E47="bajo",0,IF(data_status_reg!$E47="medio",0.5,IF(data_status_reg!$E47="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K17" s="420"/>
-      <c r="L17" s="420"/>
-      <c r="M17" s="419">
+      <c r="K17" s="422"/>
+      <c r="L17" s="422"/>
+      <c r="M17" s="421">
         <f>IF(data_status_reg!$E63="bajo",0,IF(data_status_reg!$E63="medio",0.5,IF(data_status_reg!$E63="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N17" s="417"/>
-      <c r="O17" s="447"/>
-      <c r="P17" s="419">
+      <c r="N17" s="419"/>
+      <c r="O17" s="449"/>
+      <c r="P17" s="421">
         <f>IF(data_status_reg!$E79="bajo",0,IF(data_status_reg!$E79="medio",0.5,IF(data_status_reg!$E79="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q17" s="435"/>
+      <c r="Q17" s="437"/>
       <c r="R17" s="3"/>
     </row>
     <row r="18" spans="1:18" ht="21">
-      <c r="A18" s="425"/>
-      <c r="B18" s="444" t="s">
+      <c r="A18" s="427"/>
+      <c r="B18" s="446" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="434"/>
-      <c r="D18" s="419">
+      <c r="C18" s="436"/>
+      <c r="D18" s="421">
         <f>IF(data_status_reg!$E16="bajo",0,IF(data_status_reg!$E16="medio",0.5,IF(data_status_reg!$E16="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E18" s="420"/>
-      <c r="F18" s="420"/>
-      <c r="G18" s="450" t="s">
+      <c r="E18" s="422"/>
+      <c r="F18" s="422"/>
+      <c r="G18" s="452" t="s">
         <v>94</v>
       </c>
-      <c r="H18" s="420"/>
-      <c r="I18" s="420"/>
-      <c r="J18" s="419">
+      <c r="H18" s="422"/>
+      <c r="I18" s="422"/>
+      <c r="J18" s="421">
         <f>IF(data_status_reg!$E48="bajo",0,IF(data_status_reg!$E48="medio",0.5,IF(data_status_reg!$E48="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K18" s="420"/>
-      <c r="M18" s="419">
+      <c r="K18" s="422"/>
+      <c r="M18" s="421">
         <f>IF(data_status_reg!$E64="bajo",0,IF(data_status_reg!$E64="medio",0.5,IF(data_status_reg!$E64="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N18" s="418"/>
-      <c r="O18" s="448"/>
-      <c r="P18" s="419">
+      <c r="N18" s="420"/>
+      <c r="O18" s="450"/>
+      <c r="P18" s="421">
         <f>IF(data_status_reg!$E80="bajo",0,IF(data_status_reg!$E80="medio",0.5,IF(data_status_reg!$E80="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q18" s="435"/>
+      <c r="Q18" s="437"/>
       <c r="R18" s="3"/>
     </row>
     <row r="19" spans="1:18" ht="21">
-      <c r="A19" s="425"/>
-      <c r="B19" s="444" t="s">
+      <c r="A19" s="427"/>
+      <c r="B19" s="446" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="434"/>
-      <c r="D19" s="419">
+      <c r="C19" s="436"/>
+      <c r="D19" s="421">
         <f>IF(data_status_reg!$E17="bajo",0,IF(data_status_reg!$E17="medio",0.5,IF(data_status_reg!$E17="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E19" s="420"/>
-      <c r="F19" s="420"/>
-      <c r="G19" s="419">
+      <c r="E19" s="422"/>
+      <c r="F19" s="422"/>
+      <c r="G19" s="421">
         <f>IF(data_status_reg!$E33="bajo",0,IF(data_status_reg!$E33="medio",0.5,IF(data_status_reg!$E33="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H19" s="420"/>
-      <c r="I19" s="420"/>
-      <c r="J19" s="419">
+      <c r="H19" s="422"/>
+      <c r="I19" s="422"/>
+      <c r="J19" s="421">
         <f>IF(data_status_reg!$E49="bajo",0,IF(data_status_reg!$E49="medio",0.5,IF(data_status_reg!$E49="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K19" s="420"/>
-      <c r="L19" s="420"/>
-      <c r="M19" s="419">
+      <c r="K19" s="422"/>
+      <c r="L19" s="422"/>
+      <c r="M19" s="421">
         <f>IF(data_status_reg!$E65="bajo",0,IF(data_status_reg!$E65="medio",0.5,IF(data_status_reg!$E65="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N19" s="417"/>
-      <c r="O19" s="447"/>
-      <c r="P19" s="419">
+      <c r="N19" s="419"/>
+      <c r="O19" s="449"/>
+      <c r="P19" s="421">
         <f>IF(data_status_reg!$E81="bajo",0,IF(data_status_reg!$E81="medio",0.5,IF(data_status_reg!$E81="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="435"/>
+      <c r="Q19" s="437"/>
       <c r="R19" s="3"/>
     </row>
     <row r="20" spans="1:18" ht="21">
-      <c r="A20" s="425"/>
-      <c r="B20" s="444" t="s">
+      <c r="A20" s="427"/>
+      <c r="B20" s="446" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="434"/>
-      <c r="D20" s="419">
+      <c r="C20" s="436"/>
+      <c r="D20" s="421">
         <f>IF(data_status_reg!$E18="bajo",0,IF(data_status_reg!$E18="medio",0.5,IF(data_status_reg!$E18="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E20" s="420"/>
-      <c r="F20" s="420"/>
-      <c r="G20" s="419">
+      <c r="E20" s="422"/>
+      <c r="F20" s="422"/>
+      <c r="G20" s="421">
         <f>IF(data_status_reg!$E34="bajo",0,IF(data_status_reg!$E34="medio",0.5,IF(data_status_reg!$E34="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H20" s="420"/>
-      <c r="I20" s="420"/>
-      <c r="J20" s="419">
+      <c r="H20" s="422"/>
+      <c r="I20" s="422"/>
+      <c r="J20" s="421">
         <f>IF(data_status_reg!$E50="bajo",0,IF(data_status_reg!$E50="medio",0.5,IF(data_status_reg!$E50="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K20" s="420"/>
-      <c r="L20" s="420"/>
-      <c r="M20" s="419">
+      <c r="K20" s="422"/>
+      <c r="L20" s="422"/>
+      <c r="M20" s="421">
         <f>IF(data_status_reg!$E66="bajo",0,IF(data_status_reg!$E66="medio",0.5,IF(data_status_reg!$E66="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N20" s="417"/>
-      <c r="O20" s="447"/>
-      <c r="P20" s="419">
+      <c r="N20" s="419"/>
+      <c r="O20" s="449"/>
+      <c r="P20" s="421">
         <f>IF(data_status_reg!$E82="bajo",0,IF(data_status_reg!$E82="medio",0.5,IF(data_status_reg!$E82="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q20" s="435"/>
+      <c r="Q20" s="437"/>
       <c r="R20" s="3"/>
     </row>
     <row r="21" spans="1:18" ht="21.75" thickBot="1">
-      <c r="A21" s="425"/>
-      <c r="B21" s="445" t="s">
+      <c r="A21" s="427"/>
+      <c r="B21" s="447" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="436"/>
-      <c r="D21" s="437">
+      <c r="C21" s="438"/>
+      <c r="D21" s="439">
         <f>IF(data_status_reg!$E19="bajo",0,IF(data_status_reg!$E19="medio",0.5,IF(data_status_reg!$E19="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E21" s="438"/>
-      <c r="F21" s="438"/>
-      <c r="G21" s="451" t="s">
+      <c r="E21" s="440"/>
+      <c r="F21" s="440"/>
+      <c r="G21" s="453" t="s">
         <v>94</v>
       </c>
-      <c r="H21" s="438"/>
-      <c r="I21" s="438"/>
-      <c r="J21" s="437">
+      <c r="H21" s="440"/>
+      <c r="I21" s="440"/>
+      <c r="J21" s="439">
         <f>IF(data_status_reg!$E51="bajo",0,IF(data_status_reg!$E51="medio",0.5,IF(data_status_reg!$E51="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K21" s="438"/>
-      <c r="L21" s="439"/>
-      <c r="M21" s="440">
+      <c r="K21" s="440"/>
+      <c r="L21" s="441"/>
+      <c r="M21" s="442">
         <f>IF(data_status_reg!$E67="bajo",0,IF(data_status_reg!$E67="medio",0.5,IF(data_status_reg!$E67="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N21" s="441"/>
-      <c r="O21" s="449"/>
-      <c r="P21" s="437">
+      <c r="N21" s="443"/>
+      <c r="O21" s="451"/>
+      <c r="P21" s="439">
         <f>IF(data_status_reg!$E83="bajo",0,IF(data_status_reg!$E83="medio",0.5,IF(data_status_reg!$E83="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q21" s="442"/>
+      <c r="Q21" s="444"/>
       <c r="R21" s="3"/>
     </row>
     <row r="22" spans="1:18">
-      <c r="A22" s="425"/>
+      <c r="A22" s="427"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -36959,24 +36937,24 @@
       <c r="R22" s="3"/>
     </row>
     <row r="23" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A23" s="427"/>
-      <c r="B23" s="428"/>
-      <c r="C23" s="428"/>
-      <c r="D23" s="428"/>
-      <c r="E23" s="428"/>
-      <c r="F23" s="428"/>
-      <c r="G23" s="428"/>
-      <c r="H23" s="428"/>
-      <c r="I23" s="428"/>
-      <c r="J23" s="428"/>
-      <c r="K23" s="428"/>
-      <c r="L23" s="428"/>
-      <c r="M23" s="428"/>
-      <c r="N23" s="428"/>
-      <c r="O23" s="428"/>
-      <c r="P23" s="428"/>
-      <c r="Q23" s="428"/>
-      <c r="R23" s="428"/>
+      <c r="A23" s="429"/>
+      <c r="B23" s="430"/>
+      <c r="C23" s="430"/>
+      <c r="D23" s="430"/>
+      <c r="E23" s="430"/>
+      <c r="F23" s="430"/>
+      <c r="G23" s="430"/>
+      <c r="H23" s="430"/>
+      <c r="I23" s="430"/>
+      <c r="J23" s="430"/>
+      <c r="K23" s="430"/>
+      <c r="L23" s="430"/>
+      <c r="M23" s="430"/>
+      <c r="N23" s="430"/>
+      <c r="O23" s="430"/>
+      <c r="P23" s="430"/>
+      <c r="Q23" s="430"/>
+      <c r="R23" s="430"/>
     </row>
     <row r="26" spans="1:18" outlineLevel="1"/>
     <row r="27" spans="1:18" outlineLevel="1">
@@ -39401,74 +39379,74 @@
     </row>
     <row r="3" spans="1:16" ht="37.35" customHeight="1">
       <c r="A3" s="37"/>
-      <c r="B3" s="489" t="s">
+      <c r="B3" s="491" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="490"/>
-      <c r="D3" s="490"/>
-      <c r="E3" s="490"/>
-      <c r="F3" s="490"/>
-      <c r="G3" s="490"/>
-      <c r="H3" s="490"/>
-      <c r="I3" s="490"/>
-      <c r="J3" s="490"/>
-      <c r="K3" s="490"/>
-      <c r="L3" s="490"/>
-      <c r="M3" s="490"/>
-      <c r="N3" s="490"/>
-      <c r="O3" s="491"/>
+      <c r="C3" s="492"/>
+      <c r="D3" s="492"/>
+      <c r="E3" s="492"/>
+      <c r="F3" s="492"/>
+      <c r="G3" s="492"/>
+      <c r="H3" s="492"/>
+      <c r="I3" s="492"/>
+      <c r="J3" s="492"/>
+      <c r="K3" s="492"/>
+      <c r="L3" s="492"/>
+      <c r="M3" s="492"/>
+      <c r="N3" s="492"/>
+      <c r="O3" s="493"/>
     </row>
     <row r="4" spans="1:16" ht="7.35" customHeight="1">
       <c r="A4" s="38"/>
-      <c r="B4" s="496" t="s">
+      <c r="B4" s="498" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="497"/>
-      <c r="D4" s="497"/>
-      <c r="E4" s="497"/>
-      <c r="F4" s="497"/>
-      <c r="G4" s="497"/>
-      <c r="H4" s="497"/>
-      <c r="I4" s="497"/>
-      <c r="J4" s="497"/>
-      <c r="K4" s="497"/>
-      <c r="L4" s="497"/>
-      <c r="M4" s="497"/>
-      <c r="N4" s="497"/>
+      <c r="C4" s="499"/>
+      <c r="D4" s="499"/>
+      <c r="E4" s="499"/>
+      <c r="F4" s="499"/>
+      <c r="G4" s="499"/>
+      <c r="H4" s="499"/>
+      <c r="I4" s="499"/>
+      <c r="J4" s="499"/>
+      <c r="K4" s="499"/>
+      <c r="L4" s="499"/>
+      <c r="M4" s="499"/>
+      <c r="N4" s="499"/>
       <c r="O4" s="348"/>
     </row>
     <row r="5" spans="1:16" ht="43.5" customHeight="1">
       <c r="A5" s="38"/>
-      <c r="B5" s="496"/>
-      <c r="C5" s="497"/>
-      <c r="D5" s="497"/>
-      <c r="E5" s="497"/>
-      <c r="F5" s="497"/>
-      <c r="G5" s="497"/>
-      <c r="H5" s="497"/>
-      <c r="I5" s="497"/>
-      <c r="J5" s="497"/>
-      <c r="K5" s="497"/>
-      <c r="L5" s="497"/>
-      <c r="M5" s="497"/>
-      <c r="N5" s="497"/>
+      <c r="B5" s="498"/>
+      <c r="C5" s="499"/>
+      <c r="D5" s="499"/>
+      <c r="E5" s="499"/>
+      <c r="F5" s="499"/>
+      <c r="G5" s="499"/>
+      <c r="H5" s="499"/>
+      <c r="I5" s="499"/>
+      <c r="J5" s="499"/>
+      <c r="K5" s="499"/>
+      <c r="L5" s="499"/>
+      <c r="M5" s="499"/>
+      <c r="N5" s="499"/>
       <c r="O5" s="348"/>
     </row>
     <row r="6" spans="1:16" ht="43.5" customHeight="1">
       <c r="A6" s="38"/>
-      <c r="B6" s="496"/>
-      <c r="C6" s="497"/>
-      <c r="D6" s="497"/>
-      <c r="E6" s="497"/>
-      <c r="F6" s="497"/>
-      <c r="G6" s="497"/>
-      <c r="H6" s="497"/>
-      <c r="I6" s="497"/>
-      <c r="J6" s="497"/>
-      <c r="K6" s="497"/>
-      <c r="L6" s="497"/>
-      <c r="M6" s="497"/>
-      <c r="N6" s="497"/>
+      <c r="B6" s="498"/>
+      <c r="C6" s="499"/>
+      <c r="D6" s="499"/>
+      <c r="E6" s="499"/>
+      <c r="F6" s="499"/>
+      <c r="G6" s="499"/>
+      <c r="H6" s="499"/>
+      <c r="I6" s="499"/>
+      <c r="J6" s="499"/>
+      <c r="K6" s="499"/>
+      <c r="L6" s="499"/>
+      <c r="M6" s="499"/>
+      <c r="N6" s="499"/>
       <c r="O6" s="348"/>
     </row>
     <row r="7" spans="1:16" ht="8.1" customHeight="1">
@@ -39497,19 +39475,19 @@
       <c r="A9" s="332"/>
       <c r="B9" s="339"/>
       <c r="C9" s="330"/>
-      <c r="D9" s="500" t="s">
+      <c r="D9" s="502" t="s">
         <v>98</v>
       </c>
-      <c r="E9" s="498"/>
-      <c r="F9" s="498"/>
-      <c r="G9" s="499"/>
+      <c r="E9" s="500"/>
+      <c r="F9" s="500"/>
+      <c r="G9" s="501"/>
       <c r="I9" s="330"/>
-      <c r="J9" s="505" t="s">
+      <c r="J9" s="507" t="s">
         <v>98</v>
       </c>
-      <c r="K9" s="502"/>
-      <c r="L9" s="503"/>
-      <c r="M9" s="504"/>
+      <c r="K9" s="504"/>
+      <c r="L9" s="505"/>
+      <c r="M9" s="506"/>
       <c r="O9" s="348"/>
     </row>
     <row r="10" spans="1:16" ht="37.5" customHeight="1" thickBot="1">
@@ -39518,7 +39496,7 @@
       <c r="C10" s="75" t="s">
         <v>99</v>
       </c>
-      <c r="D10" s="501"/>
+      <c r="D10" s="503"/>
       <c r="E10" s="76" t="s">
         <v>100</v>
       </c>
@@ -39531,7 +39509,7 @@
       <c r="I10" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="J10" s="506"/>
+      <c r="J10" s="508"/>
       <c r="K10" s="82" t="s">
         <v>100</v>
       </c>
@@ -39599,16 +39577,16 @@
       <c r="I12" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="699" t="s">
+      <c r="J12" s="414" t="s">
         <v>362</v>
       </c>
       <c r="K12" s="414" t="s">
         <v>357</v>
       </c>
-      <c r="L12" s="699" t="s">
+      <c r="L12" s="414" t="s">
         <v>364</v>
       </c>
-      <c r="M12" s="701" t="s">
+      <c r="M12" s="416" t="s">
         <v>364</v>
       </c>
       <c r="N12" s="349"/>
@@ -39635,16 +39613,16 @@
       <c r="I13" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="J13" s="699" t="s">
+      <c r="J13" s="414" t="s">
         <v>362</v>
       </c>
       <c r="K13" s="414" t="s">
         <v>357</v>
       </c>
-      <c r="L13" s="699" t="s">
+      <c r="L13" s="414" t="s">
         <v>364</v>
       </c>
-      <c r="M13" s="701" t="s">
+      <c r="M13" s="416" t="s">
         <v>364</v>
       </c>
       <c r="N13" s="349"/>
@@ -39671,16 +39649,16 @@
       <c r="I14" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="699" t="s">
+      <c r="J14" s="414" t="s">
         <v>362</v>
       </c>
       <c r="K14" s="414" t="s">
         <v>357</v>
       </c>
-      <c r="L14" s="699" t="s">
+      <c r="L14" s="414" t="s">
         <v>364</v>
       </c>
-      <c r="M14" s="701" t="s">
+      <c r="M14" s="416" t="s">
         <v>364</v>
       </c>
       <c r="N14" s="349"/>
@@ -39707,16 +39685,16 @@
       <c r="I15" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="J15" s="699" t="s">
+      <c r="J15" s="414" t="s">
         <v>362</v>
       </c>
       <c r="K15" s="414" t="s">
         <v>357</v>
       </c>
-      <c r="L15" s="699" t="s">
+      <c r="L15" s="414" t="s">
         <v>364</v>
       </c>
-      <c r="M15" s="701" t="s">
+      <c r="M15" s="416" t="s">
         <v>364</v>
       </c>
       <c r="N15" s="349"/>
@@ -39743,16 +39721,16 @@
       <c r="I16" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="J16" s="699" t="s">
+      <c r="J16" s="414" t="s">
         <v>362</v>
       </c>
       <c r="K16" s="414" t="s">
         <v>357</v>
       </c>
-      <c r="L16" s="699" t="s">
+      <c r="L16" s="414" t="s">
         <v>364</v>
       </c>
-      <c r="M16" s="701" t="s">
+      <c r="M16" s="416" t="s">
         <v>364</v>
       </c>
       <c r="N16" s="349"/>
@@ -39779,16 +39757,16 @@
       <c r="I17" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="J17" s="699" t="s">
+      <c r="J17" s="414" t="s">
         <v>362</v>
       </c>
       <c r="K17" s="414" t="s">
         <v>357</v>
       </c>
-      <c r="L17" s="699" t="s">
+      <c r="L17" s="414" t="s">
         <v>364</v>
       </c>
-      <c r="M17" s="701" t="s">
+      <c r="M17" s="416" t="s">
         <v>364</v>
       </c>
       <c r="N17" s="349"/>
@@ -39815,16 +39793,16 @@
       <c r="I18" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="J18" s="699" t="s">
+      <c r="J18" s="414" t="s">
         <v>362</v>
       </c>
       <c r="K18" s="414" t="s">
         <v>357</v>
       </c>
-      <c r="L18" s="699" t="s">
+      <c r="L18" s="414" t="s">
         <v>364</v>
       </c>
-      <c r="M18" s="701" t="s">
+      <c r="M18" s="416" t="s">
         <v>364</v>
       </c>
       <c r="N18" s="349"/>
@@ -39851,16 +39829,16 @@
       <c r="I19" s="41" t="s">
         <v>226</v>
       </c>
-      <c r="J19" s="699" t="s">
+      <c r="J19" s="414" t="s">
         <v>362</v>
       </c>
       <c r="K19" s="414" t="s">
         <v>357</v>
       </c>
-      <c r="L19" s="699" t="s">
+      <c r="L19" s="414" t="s">
         <v>364</v>
       </c>
-      <c r="M19" s="701" t="s">
+      <c r="M19" s="416" t="s">
         <v>364</v>
       </c>
       <c r="N19" s="349"/>
@@ -39887,16 +39865,16 @@
       <c r="I20" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="J20" s="699" t="s">
+      <c r="J20" s="414" t="s">
         <v>362</v>
       </c>
       <c r="K20" s="414" t="s">
         <v>357</v>
       </c>
-      <c r="L20" s="699" t="s">
+      <c r="L20" s="414" t="s">
         <v>364</v>
       </c>
-      <c r="M20" s="701" t="s">
+      <c r="M20" s="416" t="s">
         <v>364</v>
       </c>
       <c r="N20" s="349"/>
@@ -39923,16 +39901,16 @@
       <c r="I21" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J21" s="699" t="s">
+      <c r="J21" s="414" t="s">
         <v>362</v>
       </c>
       <c r="K21" s="414" t="s">
         <v>357</v>
       </c>
-      <c r="L21" s="699" t="s">
+      <c r="L21" s="414" t="s">
         <v>364</v>
       </c>
-      <c r="M21" s="701" t="s">
+      <c r="M21" s="416" t="s">
         <v>364</v>
       </c>
       <c r="N21" s="349"/>
@@ -39959,16 +39937,16 @@
       <c r="I22" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="J22" s="699" t="s">
+      <c r="J22" s="414" t="s">
         <v>362</v>
       </c>
       <c r="K22" s="414" t="s">
         <v>357</v>
       </c>
-      <c r="L22" s="699" t="s">
+      <c r="L22" s="414" t="s">
         <v>364</v>
       </c>
-      <c r="M22" s="701" t="s">
+      <c r="M22" s="416" t="s">
         <v>364</v>
       </c>
       <c r="N22" s="349"/>
@@ -39995,16 +39973,16 @@
       <c r="I23" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="J23" s="699" t="s">
+      <c r="J23" s="414" t="s">
         <v>363</v>
       </c>
       <c r="K23" s="414" t="s">
         <v>357</v>
       </c>
-      <c r="L23" s="699" t="s">
+      <c r="L23" s="414" t="s">
         <v>365</v>
       </c>
-      <c r="M23" s="701" t="s">
+      <c r="M23" s="416" t="s">
         <v>365</v>
       </c>
       <c r="N23" s="349"/>
@@ -40031,16 +40009,16 @@
       <c r="I24" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="J24" s="699" t="s">
+      <c r="J24" s="414" t="s">
         <v>362</v>
       </c>
       <c r="K24" s="414" t="s">
         <v>357</v>
       </c>
-      <c r="L24" s="699" t="s">
+      <c r="L24" s="414" t="s">
         <v>364</v>
       </c>
-      <c r="M24" s="701" t="s">
+      <c r="M24" s="416" t="s">
         <v>364</v>
       </c>
       <c r="N24" s="349"/>
@@ -40057,16 +40035,16 @@
       <c r="I25" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="J25" s="699" t="s">
+      <c r="J25" s="414" t="s">
         <v>362</v>
       </c>
       <c r="K25" s="414" t="s">
         <v>357</v>
       </c>
-      <c r="L25" s="699" t="s">
+      <c r="L25" s="414" t="s">
         <v>364</v>
       </c>
-      <c r="M25" s="701" t="s">
+      <c r="M25" s="416" t="s">
         <v>364</v>
       </c>
       <c r="N25" s="349"/>
@@ -40083,16 +40061,16 @@
       <c r="I26" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="J26" s="700" t="s">
+      <c r="J26" s="417" t="s">
         <v>363</v>
       </c>
-      <c r="K26" s="416" t="s">
+      <c r="K26" s="417" t="s">
         <v>357</v>
       </c>
-      <c r="L26" s="700" t="s">
+      <c r="L26" s="417" t="s">
         <v>365</v>
       </c>
-      <c r="M26" s="702" t="s">
+      <c r="M26" s="418" t="s">
         <v>365</v>
       </c>
       <c r="N26" s="349"/>
@@ -40128,58 +40106,58 @@
     <row r="30" spans="1:15" ht="42" customHeight="1" thickBot="1">
       <c r="A30" s="38"/>
       <c r="B30" s="341"/>
-      <c r="C30" s="515" t="s">
+      <c r="C30" s="517" t="s">
         <v>103</v>
       </c>
-      <c r="D30" s="516"/>
-      <c r="E30" s="516"/>
-      <c r="F30" s="516"/>
-      <c r="G30" s="517"/>
+      <c r="D30" s="518"/>
+      <c r="E30" s="518"/>
+      <c r="F30" s="518"/>
+      <c r="G30" s="519"/>
       <c r="N30" s="349"/>
       <c r="O30" s="340"/>
     </row>
     <row r="31" spans="1:15" ht="49.5" customHeight="1">
       <c r="A31" s="38"/>
       <c r="B31" s="339"/>
-      <c r="C31" s="507" t="s">
+      <c r="C31" s="509" t="s">
         <v>100</v>
       </c>
-      <c r="D31" s="508"/>
-      <c r="E31" s="509" t="s">
+      <c r="D31" s="510"/>
+      <c r="E31" s="511" t="s">
         <v>104</v>
       </c>
-      <c r="F31" s="509"/>
-      <c r="G31" s="510"/>
+      <c r="F31" s="511"/>
+      <c r="G31" s="512"/>
       <c r="N31" s="349"/>
       <c r="O31" s="340"/>
     </row>
     <row r="32" spans="1:15" ht="60" customHeight="1">
       <c r="A32" s="38"/>
       <c r="B32" s="339"/>
-      <c r="C32" s="511" t="s">
+      <c r="C32" s="513" t="s">
         <v>101</v>
       </c>
-      <c r="D32" s="512"/>
-      <c r="E32" s="513" t="s">
+      <c r="D32" s="514"/>
+      <c r="E32" s="515" t="s">
         <v>105</v>
       </c>
-      <c r="F32" s="513"/>
-      <c r="G32" s="514"/>
+      <c r="F32" s="515"/>
+      <c r="G32" s="516"/>
       <c r="N32" s="349"/>
       <c r="O32" s="340"/>
     </row>
     <row r="33" spans="1:15" ht="66.75" customHeight="1" thickBot="1">
       <c r="A33" s="38"/>
       <c r="B33" s="341"/>
-      <c r="C33" s="492" t="s">
+      <c r="C33" s="494" t="s">
         <v>102</v>
       </c>
-      <c r="D33" s="493"/>
-      <c r="E33" s="494" t="s">
+      <c r="D33" s="495"/>
+      <c r="E33" s="496" t="s">
         <v>106</v>
       </c>
-      <c r="F33" s="494"/>
-      <c r="G33" s="495"/>
+      <c r="F33" s="496"/>
+      <c r="G33" s="497"/>
       <c r="H33" s="345"/>
       <c r="J33" s="347"/>
       <c r="K33" s="347"/>
@@ -40234,8 +40212,13 @@
     <mergeCell ref="C30:G30"/>
   </mergeCells>
   <conditionalFormatting sqref="D11:G28">
-    <cfRule type="expression" dxfId="9" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>$D11&lt;&gt;"100%"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J11:M26">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>$J11&lt;&gt;"100%"</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -40272,9 +40255,9 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27" customHeight="1">
       <c r="A1" s="114"/>
-      <c r="B1" s="523"/>
-      <c r="C1" s="524"/>
-      <c r="D1" s="525"/>
+      <c r="B1" s="527"/>
+      <c r="C1" s="528"/>
+      <c r="D1" s="529"/>
       <c r="E1" s="95"/>
       <c r="F1" s="98"/>
       <c r="G1" s="96"/>
@@ -40298,10 +40281,10 @@
       <c r="H2" s="98" t="s">
         <v>373</v>
       </c>
-      <c r="I2" s="532" t="s">
+      <c r="I2" s="523" t="s">
         <v>123</v>
       </c>
-      <c r="J2" s="533"/>
+      <c r="J2" s="524"/>
       <c r="K2" s="109"/>
       <c r="L2" s="98"/>
       <c r="M2" s="106"/>
@@ -40354,10 +40337,10 @@
       <c r="B5" s="157" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="526" t="s">
+      <c r="C5" s="530" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="527"/>
+      <c r="D5" s="531"/>
       <c r="E5" s="239" t="s">
         <v>110</v>
       </c>
@@ -40387,26 +40370,26 @@
       <c r="B6" s="268" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="528">
+      <c r="C6" s="532">
         <v>44728</v>
       </c>
-      <c r="D6" s="529"/>
-      <c r="E6" s="452">
+      <c r="D6" s="533"/>
+      <c r="E6" s="454">
         <v>44908</v>
       </c>
-      <c r="F6" s="452">
+      <c r="F6" s="454">
         <v>45090</v>
       </c>
-      <c r="G6" s="452">
+      <c r="G6" s="454">
         <v>45273</v>
       </c>
-      <c r="H6" s="452">
+      <c r="H6" s="454">
         <v>45456</v>
       </c>
-      <c r="I6" s="452">
+      <c r="I6" s="454">
         <v>45639</v>
       </c>
-      <c r="J6" s="455">
+      <c r="J6" s="457">
         <v>45821</v>
       </c>
       <c r="K6" s="135"/>
@@ -40422,26 +40405,26 @@
       <c r="B7" s="269" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="530">
+      <c r="C7" s="534">
         <v>44789</v>
       </c>
-      <c r="D7" s="531"/>
-      <c r="E7" s="453">
+      <c r="D7" s="535"/>
+      <c r="E7" s="455">
         <v>44608</v>
       </c>
-      <c r="F7" s="453">
+      <c r="F7" s="455">
         <v>45154</v>
       </c>
-      <c r="G7" s="453">
+      <c r="G7" s="455">
         <v>45338</v>
       </c>
-      <c r="H7" s="453">
+      <c r="H7" s="455">
         <v>45520</v>
       </c>
-      <c r="I7" s="453">
+      <c r="I7" s="455">
         <v>45704</v>
       </c>
-      <c r="J7" s="456">
+      <c r="J7" s="458">
         <v>45885</v>
       </c>
       <c r="L7" s="98"/>
@@ -40455,26 +40438,26 @@
       <c r="B8" s="269" t="s">
         <v>116</v>
       </c>
-      <c r="C8" s="530">
+      <c r="C8" s="534">
         <v>44868</v>
       </c>
-      <c r="D8" s="531"/>
-      <c r="E8" s="453">
+      <c r="D8" s="535"/>
+      <c r="E8" s="455">
         <v>45049</v>
       </c>
-      <c r="F8" s="453">
+      <c r="F8" s="455">
         <v>45233</v>
       </c>
-      <c r="G8" s="453">
+      <c r="G8" s="455">
         <v>45415</v>
       </c>
-      <c r="H8" s="453">
+      <c r="H8" s="455">
         <v>45599</v>
       </c>
-      <c r="I8" s="453">
+      <c r="I8" s="455">
         <v>45780</v>
       </c>
-      <c r="J8" s="456">
+      <c r="J8" s="458">
         <v>45964</v>
       </c>
       <c r="K8" s="243"/>
@@ -40489,26 +40472,26 @@
       <c r="B9" s="269" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="530">
+      <c r="C9" s="534">
         <v>45439</v>
       </c>
-      <c r="D9" s="531"/>
-      <c r="E9" s="453">
+      <c r="D9" s="535"/>
+      <c r="E9" s="455">
         <v>45623</v>
       </c>
-      <c r="F9" s="453">
+      <c r="F9" s="455">
         <v>45804</v>
       </c>
-      <c r="G9" s="453">
+      <c r="G9" s="455">
         <v>45988</v>
       </c>
-      <c r="H9" s="453">
+      <c r="H9" s="455">
         <v>46169</v>
       </c>
-      <c r="I9" s="453">
+      <c r="I9" s="455">
         <v>46353</v>
       </c>
-      <c r="J9" s="456">
+      <c r="J9" s="458">
         <v>46534</v>
       </c>
       <c r="K9" s="178"/>
@@ -40524,26 +40507,26 @@
       <c r="B10" s="269" t="s">
         <v>118</v>
       </c>
-      <c r="C10" s="530">
+      <c r="C10" s="534">
         <v>44900</v>
       </c>
-      <c r="D10" s="531"/>
-      <c r="E10" s="453">
+      <c r="D10" s="535"/>
+      <c r="E10" s="455">
         <v>45082</v>
       </c>
-      <c r="F10" s="453">
+      <c r="F10" s="455">
         <v>45265</v>
       </c>
-      <c r="G10" s="453">
+      <c r="G10" s="455">
         <v>45448</v>
       </c>
-      <c r="H10" s="453">
+      <c r="H10" s="455">
         <v>45631</v>
       </c>
-      <c r="I10" s="453">
+      <c r="I10" s="455">
         <v>45813</v>
       </c>
-      <c r="J10" s="456">
+      <c r="J10" s="458">
         <v>45813</v>
       </c>
       <c r="K10" s="135"/>
@@ -40558,26 +40541,26 @@
       <c r="B11" s="269" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="530">
+      <c r="C11" s="534">
         <v>44930</v>
       </c>
-      <c r="D11" s="531"/>
-      <c r="E11" s="453">
+      <c r="D11" s="535"/>
+      <c r="E11" s="455">
         <v>45111</v>
       </c>
-      <c r="F11" s="453">
+      <c r="F11" s="455">
         <v>45295</v>
       </c>
-      <c r="G11" s="453">
+      <c r="G11" s="455">
         <v>45477</v>
       </c>
-      <c r="H11" s="453">
+      <c r="H11" s="455">
         <v>45661</v>
       </c>
-      <c r="I11" s="453">
+      <c r="I11" s="455">
         <v>45842</v>
       </c>
-      <c r="J11" s="456">
+      <c r="J11" s="458">
         <v>46026</v>
       </c>
       <c r="L11" s="98"/>
@@ -40592,26 +40575,26 @@
       <c r="B12" s="270" t="s">
         <v>120</v>
       </c>
-      <c r="C12" s="518">
+      <c r="C12" s="525">
         <v>44958</v>
       </c>
-      <c r="D12" s="519"/>
-      <c r="E12" s="454">
+      <c r="D12" s="526"/>
+      <c r="E12" s="456">
         <v>45139</v>
       </c>
-      <c r="F12" s="454">
+      <c r="F12" s="456">
         <v>45323</v>
       </c>
-      <c r="G12" s="454">
+      <c r="G12" s="456">
         <v>45505</v>
       </c>
-      <c r="H12" s="454">
+      <c r="H12" s="456">
         <v>45689</v>
       </c>
-      <c r="I12" s="454">
+      <c r="I12" s="456">
         <v>45870</v>
       </c>
-      <c r="J12" s="457">
+      <c r="J12" s="459">
         <v>46054</v>
       </c>
       <c r="K12" s="243"/>
@@ -41241,11 +41224,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="E21:J21"/>
-    <mergeCell ref="E16:J16"/>
-    <mergeCell ref="E17:J17"/>
-    <mergeCell ref="I2:J2"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="E20:J20"/>
     <mergeCell ref="E19:J19"/>
@@ -41258,6 +41236,11 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="E21:J21"/>
+    <mergeCell ref="E16:J16"/>
+    <mergeCell ref="E17:J17"/>
+    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="5" scale="47" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -41266,6 +41249,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010039E554BA5E2FA5449283D399C0FD5B7C" ma:contentTypeVersion="18" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="dd0678842d65e4207392abd035356b9c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xmlns:ns3="954542bb-2825-439d-9db6-a5c04d3b21fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d84746cc30da1fe182e7a313d44b54c" ns2:_="" ns3:_="">
     <xsd:import namespace="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
@@ -41520,27 +41523,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83E8CA1-0683-49D4-9501-EE88776F2630}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
+    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6AC9645-B568-450E-BF2C-C54CDA88D1C4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE64779-B9F2-4AEC-A5E9-E8076DA89A71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41557,29 +41565,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6AC9645-B568-450E-BF2C-C54CDA88D1C4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83E8CA1-0683-49D4-9501-EE88776F2630}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Backend/output/informe_final.xlsx
+++ b/Backend/output/informe_final.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8BDD170-A9EF-41E2-8339-2798E0624F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D85C889-B46F-47A7-9122-354427E1C8F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="733" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1283,7 +1283,7 @@
     <t>Acum FEBRERO - 2025</t>
   </si>
   <si>
-    <t>Hitos ADP ocurridos al 21 de FEBRERO</t>
+    <t>Hitos ADP ocurridos al 24 de FEBRERO</t>
   </si>
   <si>
     <t>Política de Gestión de Riesgos</t>
@@ -12978,7 +12978,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3175E1D9-2D5D-4C98-A330-AE0EF765B1FB}" type="CELLRANGE">
+                    <a:fld id="{79B59CAE-E957-4DB4-A03E-A3EE21D9F64F}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13012,7 +13012,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A15D19F6-B3A8-42D4-9634-38BB377AB6AA}" type="CELLRANGE">
+                    <a:fld id="{E8770FB4-C04F-416A-96BB-97FEC533CD48}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13046,7 +13046,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{29E652C9-5A2E-4A1C-A4F3-AAEAE0F28D73}" type="CELLRANGE">
+                    <a:fld id="{D17A1A71-7EA6-4C96-80A3-F5A7805C2BEF}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13080,7 +13080,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{25E5A8A0-1677-430D-9D51-A0D4F3E53949}" type="CELLRANGE">
+                    <a:fld id="{3F104E5E-D0D6-44EE-9E91-54EFC0A0BE7B}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13114,7 +13114,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AB18087C-B0B4-4FDA-B8D3-97E1A4C7F925}" type="CELLRANGE">
+                    <a:fld id="{C889C164-6AEA-4671-8BBC-6DB2F3607B95}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13148,7 +13148,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5A8A8B55-3E58-4904-B1FF-D5B4C278A9CD}" type="CELLRANGE">
+                    <a:fld id="{ADE2AA2F-A697-4162-856B-43AFA0CBAB2E}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13182,7 +13182,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{74C8F4BF-18EC-4703-A454-CD4C9BCB682C}" type="CELLRANGE">
+                    <a:fld id="{AEE85172-3D79-4A05-A699-0FAB2EE80C9C}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13216,7 +13216,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1677952B-0432-4CAD-909C-7909772240D4}" type="CELLRANGE">
+                    <a:fld id="{DC14568C-9879-4365-B22E-164EB210BF5B}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13250,7 +13250,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5B3C83E3-6461-45E8-B140-8A63C65E3081}" type="CELLRANGE">
+                    <a:fld id="{9422167C-3C91-4C25-805D-0245CE8E921F}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13284,7 +13284,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5B33D0CF-087A-405F-A2C3-C5F8DA68EED1}" type="CELLRANGE">
+                    <a:fld id="{84FC4139-BE11-4712-BFE8-04AB590DD951}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13318,7 +13318,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7A9CB30D-2948-4BA6-8522-35849B103305}" type="CELLRANGE">
+                    <a:fld id="{03A51483-CE80-4FF0-945E-DEA92855A65E}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13352,7 +13352,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3962EFBA-CD79-4E74-B811-50A0C808E94E}" type="CELLRANGE">
+                    <a:fld id="{CAFC47C8-942C-494C-8F8A-0DF2225280BD}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13729,7 +13729,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FBA4F8E7-DEBE-4EA4-8C13-5B51D231F7D4}" type="CELLRANGE">
+                    <a:fld id="{6D2371AD-21AA-4185-BF32-E016B0499682}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14453,7 +14453,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{EC229AEE-9755-41C2-8D28-EA5B2D1F5154}" type="CELLRANGE">
+                    <a:fld id="{1EA9646C-584E-4176-BC78-1B3D073BBEED}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr>
                         <a:defRPr sz="1400">
@@ -14534,7 +14534,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2C8E3F93-9497-42E9-8E23-FADEAA05BDD0}" type="CELLRANGE">
+                    <a:fld id="{F1714C22-BDEE-449A-A289-3803D3E1DFFD}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>

--- a/Backend/output/informe_final.xlsx
+++ b/Backend/output/informe_final.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D85C889-B46F-47A7-9122-354427E1C8F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BB42F77-4B96-4773-A06C-0B978915D389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="733" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="15375" windowHeight="7785" tabRatio="733" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="426">
   <si>
     <t>SUBSECRETARÍA DE EDUCACIÓN</t>
   </si>
@@ -851,45 +851,12 @@
     <t>I20_014-Gabinete Ministerio</t>
   </si>
   <si>
-    <t>PTR25_040-Gabinete Ministerio</t>
-  </si>
-  <si>
-    <t>PTR25_041-Gabinete Ministerio</t>
-  </si>
-  <si>
-    <t>PTR25_042-Gabinete Ministerio</t>
-  </si>
-  <si>
-    <t>PTR25_043-Gabinete Ministerio</t>
-  </si>
-  <si>
-    <t>PTR25_044-Gabinete Ministerio</t>
-  </si>
-  <si>
-    <t>PTR25_053-Gabinete Ministerio</t>
-  </si>
-  <si>
-    <t>PTR25_054-Gabinete Ministerio</t>
-  </si>
-  <si>
-    <t>PTR25_055-Gabinete Ministerio</t>
-  </si>
-  <si>
     <t>I19_026-Gabinete Subsecretaría</t>
   </si>
   <si>
     <t>I23_015-Gabinete Subsecretaría</t>
   </si>
   <si>
-    <t>PTR25_045-Gabinete Subsecretaría</t>
-  </si>
-  <si>
-    <t>PTR25_046-Gabinete Subsecretaría</t>
-  </si>
-  <si>
-    <t>PTR25_047-Gabinete Subsecretaría</t>
-  </si>
-  <si>
     <t>I21_001-Gabinete Subsecretaría</t>
   </si>
   <si>
@@ -905,24 +872,6 @@
     <t>I23_018-CPEIP</t>
   </si>
   <si>
-    <t>PTR25_001-CPEIP</t>
-  </si>
-  <si>
-    <t>PTR25_002-CPEIP</t>
-  </si>
-  <si>
-    <t>PTR25_003-CPEIP</t>
-  </si>
-  <si>
-    <t>PTR25_004-CPEIP</t>
-  </si>
-  <si>
-    <t>PTR25_005-CPEIP</t>
-  </si>
-  <si>
-    <t>PTR25_006-CPEIP</t>
-  </si>
-  <si>
     <t>I25_003-CPEIP</t>
   </si>
   <si>
@@ -932,25 +881,97 @@
     <t>I25_011-DEG</t>
   </si>
   <si>
-    <t>PTR25_015-DEG</t>
-  </si>
-  <si>
-    <t>PTR25_016-DEG</t>
-  </si>
-  <si>
-    <t>PTR25_017-DEG</t>
-  </si>
-  <si>
-    <t>PTR25_018-DEG</t>
-  </si>
-  <si>
-    <t>PTR25_019-DEG</t>
-  </si>
-  <si>
-    <t>PTR25_020-DEG</t>
-  </si>
-  <si>
-    <t>PTR25_021-DEG</t>
+    <t>I17_001-DEG</t>
+  </si>
+  <si>
+    <t>I23_004-DEG</t>
+  </si>
+  <si>
+    <t>I24_009-DEG</t>
+  </si>
+  <si>
+    <t>I16_043-División de Planificación y Presupuesto</t>
+  </si>
+  <si>
+    <t>I20_011-División de Planificación y Presupuesto</t>
+  </si>
+  <si>
+    <t>I20_012-División de Planificación y Presupuesto</t>
+  </si>
+  <si>
+    <t>I25_012-División de Planificación y Presupuesto</t>
+  </si>
+  <si>
+    <t>I21_002-División de Planificación y Presupuesto</t>
+  </si>
+  <si>
+    <t>I16_054-División de Planificación y Presupuesto</t>
+  </si>
+  <si>
+    <t>I19_012-División de Planificación y Presupuesto</t>
+  </si>
+  <si>
+    <t>I25_005-División de Planificación y Presupuesto</t>
+  </si>
+  <si>
+    <t>I21_007-DAG</t>
+  </si>
+  <si>
+    <t>I25_004-DAG</t>
+  </si>
+  <si>
+    <t>I23_019-DAG</t>
+  </si>
+  <si>
+    <t>I25_013-DAG</t>
+  </si>
+  <si>
+    <t>I20_006-DAG</t>
+  </si>
+  <si>
+    <t>I20_005-DAG</t>
+  </si>
+  <si>
+    <t>I19_020-UCE</t>
+  </si>
+  <si>
+    <t>I21_011-UCE</t>
+  </si>
+  <si>
+    <t>I21_012-UCE</t>
+  </si>
+  <si>
+    <t>I22_006-UCE</t>
+  </si>
+  <si>
+    <t>I19_019-UCE</t>
+  </si>
+  <si>
+    <t>I16_062-UCE</t>
+  </si>
+  <si>
+    <t>I25_010-UCE</t>
+  </si>
+  <si>
+    <t>I16_052-División Jurídica</t>
+  </si>
+  <si>
+    <t>I24_004-División Jurídica</t>
+  </si>
+  <si>
+    <t>I23_007-División Jurídica</t>
+  </si>
+  <si>
+    <t>I22_008-División Jurídica</t>
+  </si>
+  <si>
+    <t>I24_011-División Jurídica</t>
+  </si>
+  <si>
+    <t>I24_003-División Jurídica</t>
+  </si>
+  <si>
+    <t>I16_053-División Jurídica</t>
   </si>
   <si>
     <t>Sin dato</t>
@@ -1283,7 +1304,7 @@
     <t>Acum FEBRERO - 2025</t>
   </si>
   <si>
-    <t>Hitos ADP ocurridos al 24 de FEBRERO</t>
+    <t>Hitos ADP ocurridos al 26 de FEBRERO</t>
   </si>
   <si>
     <t>Política de Gestión de Riesgos</t>
@@ -12978,7 +12999,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{79B59CAE-E957-4DB4-A03E-A3EE21D9F64F}" type="CELLRANGE">
+                    <a:fld id="{5B07F8DF-8178-4A03-A2B6-C18807156040}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13012,7 +13033,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E8770FB4-C04F-416A-96BB-97FEC533CD48}" type="CELLRANGE">
+                    <a:fld id="{67C5E621-8048-4CC9-B507-8CF5753626C5}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13046,7 +13067,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D17A1A71-7EA6-4C96-80A3-F5A7805C2BEF}" type="CELLRANGE">
+                    <a:fld id="{AB6BEC96-EE4D-48CA-88A5-6EF718249E2D}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13080,7 +13101,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3F104E5E-D0D6-44EE-9E91-54EFC0A0BE7B}" type="CELLRANGE">
+                    <a:fld id="{9E4C2A99-CF5A-41E8-97A7-83E2C3F39317}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13114,7 +13135,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C889C164-6AEA-4671-8BBC-6DB2F3607B95}" type="CELLRANGE">
+                    <a:fld id="{5378AA3C-52DC-4ADE-9928-1EB2C6FC1D90}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13148,7 +13169,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{ADE2AA2F-A697-4162-856B-43AFA0CBAB2E}" type="CELLRANGE">
+                    <a:fld id="{7F2B2987-2056-4900-B547-FCF4720D72CE}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13182,7 +13203,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AEE85172-3D79-4A05-A699-0FAB2EE80C9C}" type="CELLRANGE">
+                    <a:fld id="{F1DD95AE-F0D5-4125-AAE6-273816F56566}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13216,7 +13237,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DC14568C-9879-4365-B22E-164EB210BF5B}" type="CELLRANGE">
+                    <a:fld id="{F7FC12B3-95C8-410F-8401-C49B73A1CB61}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13250,7 +13271,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9422167C-3C91-4C25-805D-0245CE8E921F}" type="CELLRANGE">
+                    <a:fld id="{1A582626-5512-4C00-81D9-B3C20FAA95CB}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13284,7 +13305,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{84FC4139-BE11-4712-BFE8-04AB590DD951}" type="CELLRANGE">
+                    <a:fld id="{48838F0F-4E8E-449F-AA01-B17679F72977}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13318,7 +13339,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{03A51483-CE80-4FF0-945E-DEA92855A65E}" type="CELLRANGE">
+                    <a:fld id="{559B87D9-0052-41DE-A66D-638DB3F8626B}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13352,7 +13373,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CAFC47C8-942C-494C-8F8A-0DF2225280BD}" type="CELLRANGE">
+                    <a:fld id="{1598D04A-8C0F-488C-A87D-F7DC68393B39}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13729,7 +13750,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6D2371AD-21AA-4185-BF32-E016B0499682}" type="CELLRANGE">
+                    <a:fld id="{3B5E661A-7FAA-4F8D-8BA9-AF3A173149C2}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14453,7 +14474,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{1EA9646C-584E-4176-BC78-1B3D073BBEED}" type="CELLRANGE">
+                    <a:fld id="{9225CDDF-8E27-4A2E-BB9F-DAB4EC5C1D8D}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr>
                         <a:defRPr sz="1400">
@@ -14534,7 +14555,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F1714C22-BDEE-449A-A289-3803D3E1DFFD}" type="CELLRANGE">
+                    <a:fld id="{ED06BA52-1CFC-42CC-8BB9-F8F874D9BD1A}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -28195,10 +28216,10 @@
     <row r="8" spans="1:28" ht="21.75" customHeight="1" thickBot="1">
       <c r="A8" s="209"/>
       <c r="B8" s="221" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="C8" s="215" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="D8" s="210">
         <v>2019</v>
@@ -28230,10 +28251,10 @@
     <row r="9" spans="1:28" ht="18" customHeight="1" thickBot="1">
       <c r="A9" s="214"/>
       <c r="B9" s="221" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="C9" s="216" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="D9" s="160">
         <v>2024</v>
@@ -28265,10 +28286,10 @@
     <row r="10" spans="1:28" ht="21" customHeight="1">
       <c r="A10" s="97"/>
       <c r="B10" s="221" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C10" s="216" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="D10" s="160">
         <v>2024</v>
@@ -28302,10 +28323,10 @@
     <row r="11" spans="1:28" ht="19.5" customHeight="1">
       <c r="A11" s="95"/>
       <c r="B11" s="221" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C11" s="220" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="D11" s="160">
         <v>2024</v>
@@ -28347,10 +28368,10 @@
     <row r="12" spans="1:28" ht="17.25" customHeight="1">
       <c r="A12" s="95"/>
       <c r="B12" s="222" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="C12" s="224" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="D12" s="216">
         <v>2024</v>
@@ -28390,10 +28411,10 @@
     <row r="13" spans="1:28" ht="18.75" customHeight="1">
       <c r="A13" s="95"/>
       <c r="B13" s="221" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="C13" s="215" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="D13" s="160">
         <v>2024</v>
@@ -28425,10 +28446,10 @@
     <row r="14" spans="1:28" ht="18.75" customHeight="1">
       <c r="A14" s="95"/>
       <c r="B14" s="221" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="C14" s="216" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="D14" s="160">
         <v>2024</v>
@@ -28475,10 +28496,10 @@
     <row r="15" spans="1:28" ht="19.5" customHeight="1" thickBot="1">
       <c r="A15" s="95"/>
       <c r="B15" s="223" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="C15" s="218" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="D15" s="217">
         <v>2024</v>
@@ -28632,7 +28653,7 @@
       </c>
       <c r="F18" s="105"/>
       <c r="G18" s="623" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="H18" s="624"/>
       <c r="I18" s="601">
@@ -28678,12 +28699,12 @@
         <v>16</v>
       </c>
       <c r="D19" s="165" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="E19" s="233"/>
       <c r="F19" s="105"/>
       <c r="G19" s="623" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="H19" s="624"/>
       <c r="I19" s="601">
@@ -28729,7 +28750,7 @@
         <v>13</v>
       </c>
       <c r="D20" s="165" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="E20" s="233"/>
       <c r="F20" s="105"/>
@@ -28774,13 +28795,13 @@
     <row r="21" spans="1:27" ht="30" customHeight="1">
       <c r="A21" s="95"/>
       <c r="B21" s="185" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C21" s="165">
         <v>35</v>
       </c>
       <c r="D21" s="165" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="E21" s="233"/>
       <c r="F21" s="105"/>
@@ -28831,12 +28852,12 @@
         <v>21</v>
       </c>
       <c r="D22" s="165" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="E22" s="233"/>
       <c r="F22" s="105"/>
       <c r="G22" s="623" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="H22" s="624"/>
       <c r="I22" s="601">
@@ -28876,13 +28897,13 @@
     <row r="23" spans="1:27" ht="30.75" customHeight="1" thickBot="1">
       <c r="A23" s="95"/>
       <c r="B23" s="186" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="C23" s="187">
         <v>2</v>
       </c>
       <c r="D23" s="187" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="E23" s="234"/>
       <c r="F23" s="105"/>
@@ -29297,7 +29318,7 @@
       <c r="J33" s="550"/>
       <c r="K33" s="105"/>
       <c r="L33" s="583" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="M33" s="551"/>
       <c r="N33" s="551"/>
@@ -29342,7 +29363,7 @@
       <c r="J34" s="193"/>
       <c r="K34" s="105"/>
       <c r="L34" s="583" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="M34" s="551"/>
       <c r="N34" s="551"/>
@@ -29479,7 +29500,7 @@
       <c r="J37" s="574"/>
       <c r="K37" s="105"/>
       <c r="L37" s="583" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="M37" s="551"/>
       <c r="N37" s="552"/>
@@ -31855,7 +31876,7 @@
       </c>
       <c r="L6" s="679"/>
       <c r="M6" s="698" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="N6" s="679"/>
       <c r="O6" s="698" t="s">
@@ -31883,7 +31904,7 @@
       </c>
       <c r="L7" s="671"/>
       <c r="M7" s="670" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="N7" s="671"/>
       <c r="O7" s="670" t="s">
@@ -31908,7 +31929,7 @@
       </c>
       <c r="L8" s="671"/>
       <c r="M8" s="670" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="N8" s="671"/>
       <c r="O8" s="670" t="s">
@@ -31933,7 +31954,7 @@
       </c>
       <c r="L9" s="671"/>
       <c r="M9" s="670" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="N9" s="671"/>
       <c r="O9" s="670" t="s">
@@ -31958,7 +31979,7 @@
       </c>
       <c r="L10" s="671"/>
       <c r="M10" s="670" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="N10" s="671"/>
       <c r="O10" s="670" t="s">
@@ -31985,11 +32006,11 @@
       <c r="I11" s="96"/>
       <c r="J11" s="119"/>
       <c r="K11" s="674" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="L11" s="671"/>
       <c r="M11" s="670" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="N11" s="671"/>
       <c r="O11" s="670" t="s">
@@ -32018,15 +32039,15 @@
       <c r="I12" s="96"/>
       <c r="J12" s="119"/>
       <c r="K12" s="674" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="L12" s="671"/>
       <c r="M12" s="670" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="N12" s="671"/>
       <c r="O12" s="670" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="P12" s="677"/>
       <c r="Q12" s="96"/>
@@ -32051,11 +32072,11 @@
       <c r="I13" s="96"/>
       <c r="J13" s="95"/>
       <c r="K13" s="674" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="L13" s="671"/>
       <c r="M13" s="670" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="N13" s="671"/>
       <c r="O13" s="670" t="s">
@@ -32084,11 +32105,11 @@
       <c r="I14" s="96"/>
       <c r="J14" s="103"/>
       <c r="K14" s="674" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="L14" s="671"/>
       <c r="M14" s="670" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="N14" s="671"/>
       <c r="O14" s="670" t="s">
@@ -32121,7 +32142,7 @@
       </c>
       <c r="L15" s="671"/>
       <c r="M15" s="670" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="N15" s="671"/>
       <c r="O15" s="670" t="s">
@@ -32154,7 +32175,7 @@
       </c>
       <c r="L16" s="671"/>
       <c r="M16" s="670" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="N16" s="671"/>
       <c r="O16" s="670" t="s">
@@ -32185,11 +32206,11 @@
       </c>
       <c r="L17" s="671"/>
       <c r="M17" s="670" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="N17" s="671"/>
       <c r="O17" s="670" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="P17" s="677"/>
       <c r="Q17" s="96"/>
@@ -32217,11 +32238,11 @@
       </c>
       <c r="L18" s="673"/>
       <c r="M18" s="672" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="N18" s="673"/>
       <c r="O18" s="672" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="P18" s="676"/>
       <c r="Q18" s="96"/>
@@ -33016,7 +33037,7 @@
         <v>45646</v>
       </c>
       <c r="B3" s="320" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C3" s="191">
         <v>2</v>
@@ -33030,7 +33051,7 @@
         <v>45294</v>
       </c>
       <c r="B4" s="320" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="C4" s="191">
         <v>-1</v>
@@ -33044,7 +33065,7 @@
         <v>45317</v>
       </c>
       <c r="B5" s="320" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="C5" s="191">
         <v>1.5</v>
@@ -33058,7 +33079,7 @@
         <v>45677</v>
       </c>
       <c r="B6" s="320" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="C6" s="191">
         <v>-1</v>
@@ -33072,7 +33093,7 @@
         <v>45748</v>
       </c>
       <c r="B7" s="320" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="C7" s="191">
         <v>1</v>
@@ -33086,7 +33107,7 @@
         <v>45796</v>
       </c>
       <c r="B8" s="320" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="C8" s="191">
         <v>2</v>
@@ -33100,7 +33121,7 @@
         <v>45432</v>
       </c>
       <c r="B9" s="320" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="C9" s="191">
         <v>1</v>
@@ -33114,7 +33135,7 @@
         <v>45435</v>
       </c>
       <c r="B10" s="320" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="C10" s="191">
         <v>-1</v>
@@ -33128,7 +33149,7 @@
         <v>45442</v>
       </c>
       <c r="B11" s="320" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C11" s="191">
         <v>-1</v>
@@ -33142,7 +33163,7 @@
         <v>45449</v>
       </c>
       <c r="B12" s="320" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C12" s="191">
         <v>-1</v>
@@ -33156,7 +33177,7 @@
         <v>45456</v>
       </c>
       <c r="B13" s="320" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C13" s="191">
         <v>-1</v>
@@ -33170,7 +33191,7 @@
         <v>45463</v>
       </c>
       <c r="B14" s="320" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C14" s="191">
         <v>1</v>
@@ -37304,10 +37325,10 @@
       <c r="D6" s="5"/>
       <c r="E6" s="4"/>
       <c r="I6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="18" customHeight="1">
@@ -37318,16 +37339,16 @@
       <c r="C7" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="5" t="str">
+      <c r="D7" s="5">
         <f>IF(J9="bajo",0,IF(J9="medio",0.5,IF(J9="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E7" s="4"/>
       <c r="I7" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1">
@@ -37342,10 +37363,10 @@
       </c>
       <c r="E8" s="4"/>
       <c r="I8" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="18" customHeight="1">
@@ -37360,10 +37381,10 @@
       </c>
       <c r="E9" s="4"/>
       <c r="I9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="18" customHeight="1">
@@ -37372,16 +37393,16 @@
       <c r="C10" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="5" t="str">
+      <c r="D10" s="5">
         <f>IF(J10="bajo",0,IF(J10="medio",0.5,IF(J10="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E10" s="4"/>
       <c r="I10" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="18" customHeight="1">
@@ -37390,16 +37411,16 @@
       <c r="C11" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="5" t="str">
+      <c r="D11" s="5">
         <f>IF(J12="bajo",0,IF(J12="medio",0.5,IF(J12="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E11" s="4"/>
       <c r="I11" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="18" customHeight="1">
@@ -37408,16 +37429,16 @@
       <c r="C12" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="5" t="str">
+      <c r="D12" s="5">
         <f>IF(J13="bajo",0,IF(J13="medio",0.5,IF(J13="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E12" s="4"/>
       <c r="I12" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="18" customHeight="1">
@@ -37426,16 +37447,16 @@
       <c r="C13" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="5" t="str">
+      <c r="D13" s="5">
         <f>IF(J11="bajo",0,IF(J11="medio",0.5,IF(J11="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E13" s="4"/>
       <c r="I13" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="18" customHeight="1">
@@ -37445,7 +37466,7 @@
       <c r="D14" s="5"/>
       <c r="E14" s="4"/>
       <c r="I14" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>13</v>
@@ -37459,13 +37480,13 @@
       <c r="C15" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="5" t="str">
+      <c r="D15" s="5">
         <f>IF(J18="bajo",0,IF(J18="medio",0.5,IF(J18="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E15" s="4"/>
       <c r="I15" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>13</v>
@@ -37477,13 +37498,13 @@
       <c r="C16" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="5" t="str">
+      <c r="D16" s="5">
         <f>IF(J17="bajo",0,IF(J17="medio",0.5,IF(J17="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E16" s="4"/>
       <c r="I16" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>13</v>
@@ -37495,16 +37516,16 @@
       <c r="C17" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="5" t="str">
+      <c r="D17" s="5">
         <f>IF(J19="bajo",0,IF(J19="medio",0.5,IF(J19="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E17" s="4"/>
       <c r="I17" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="21">
@@ -37519,10 +37540,10 @@
       </c>
       <c r="E18" s="4"/>
       <c r="I18" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="18" customHeight="1">
@@ -37532,10 +37553,10 @@
       <c r="D19" s="5"/>
       <c r="E19" s="4"/>
       <c r="I19" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="18" customHeight="1">
@@ -37546,16 +37567,16 @@
       <c r="C20" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="5" t="str">
+      <c r="D20" s="5">
         <f>IF(J22="bajo",0,IF(J22="medio",0.5,IF(J22="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E20" s="4"/>
       <c r="I20" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="18" customHeight="1">
@@ -37564,16 +37585,16 @@
       <c r="C21" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="5" t="str">
+      <c r="D21" s="5">
         <f>IF(J24="bajo",0,IF(J24="medio",0.5,IF(J24="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E21" s="4"/>
       <c r="I21" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="18" customHeight="1">
@@ -37582,16 +37603,16 @@
       <c r="C22" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="5" t="str">
+      <c r="D22" s="5">
         <f>IF(J23="bajo",0,IF(J23="medio",0.5,IF(J23="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E22" s="4"/>
       <c r="I22" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="18" customHeight="1">
@@ -37600,16 +37621,16 @@
       <c r="C23" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="D23" s="5" t="str">
+      <c r="D23" s="5">
         <f>IF(J21="bajo",0,IF(J21="medio",0.5,IF(J21="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E23" s="4"/>
       <c r="I23" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="18" customHeight="1">
@@ -37618,16 +37639,16 @@
       <c r="C24" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="5" t="str">
+      <c r="D24" s="5">
         <f>IF(J20="bajo",0,IF(J20="medio",0.5,IF(J20="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E24" s="4"/>
       <c r="I24" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="18" customHeight="1">
@@ -37637,7 +37658,7 @@
       <c r="D25" s="5"/>
       <c r="E25" s="4"/>
       <c r="I25" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>13</v>
@@ -37651,13 +37672,13 @@
       <c r="C26" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="5" t="str">
+      <c r="D26" s="5">
         <f>IF(J27="bajo",0,IF(J27="medio",0.5,IF(J27="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E26" s="4"/>
       <c r="I26" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>13</v>
@@ -37675,10 +37696,10 @@
       </c>
       <c r="E27" s="4"/>
       <c r="I27" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="18" customHeight="1">
@@ -37693,10 +37714,10 @@
       </c>
       <c r="E28" s="4"/>
       <c r="I28" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="18" customHeight="1">
@@ -37711,10 +37732,10 @@
       </c>
       <c r="E29" s="4"/>
       <c r="I29" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="18" customHeight="1">
@@ -37729,7 +37750,7 @@
       </c>
       <c r="E30" s="4"/>
       <c r="I30" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="J30" s="6" t="s">
         <v>13</v>
@@ -37747,7 +37768,7 @@
       </c>
       <c r="E31" s="4"/>
       <c r="I31" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>13</v>
@@ -37759,13 +37780,13 @@
       <c r="C32" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="5" t="str">
+      <c r="D32" s="5">
         <f>IF(J28="bajo",0,IF(J28="medio",0.5,IF(J28="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E32" s="4"/>
       <c r="I32" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="J32" s="6" t="s">
         <v>13</v>
@@ -37783,7 +37804,7 @@
       </c>
       <c r="E33" s="4"/>
       <c r="I33" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="J33" s="6" t="s">
         <v>13</v>
@@ -37796,7 +37817,7 @@
       <c r="D34" s="5"/>
       <c r="E34" s="4"/>
       <c r="I34" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="J34" s="6" t="s">
         <v>13</v>
@@ -37816,10 +37837,10 @@
       </c>
       <c r="E35" s="4"/>
       <c r="I35" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="18" customHeight="1">
@@ -37834,10 +37855,10 @@
       </c>
       <c r="E36" s="4"/>
       <c r="I36" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="18" customHeight="1">
@@ -37846,16 +37867,16 @@
       <c r="C37" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="D37" s="5" t="str">
+      <c r="D37" s="5">
         <f>IF(J36="bajo",0,IF(J36="medio",0.5,IF(J36="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E37" s="4"/>
       <c r="I37" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="18" customHeight="1">
@@ -37864,16 +37885,16 @@
       <c r="C38" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="D38" s="5" t="str">
+      <c r="D38" s="5">
         <f>IF(J37="bajo",0,IF(J37="medio",0.5,IF(J37="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E38" s="4"/>
       <c r="I38" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="18" customHeight="1">
@@ -37882,16 +37903,16 @@
       <c r="C39" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="D39" s="5" t="str">
+      <c r="D39" s="5">
         <f>IF(J35="bajo",0,IF(J35="medio",0.5,IF(J35="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E39" s="4"/>
       <c r="I39" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="18" customHeight="1">
@@ -37901,10 +37922,10 @@
       <c r="D40" s="5"/>
       <c r="E40" s="4"/>
       <c r="I40" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="18" customHeight="1">
@@ -37915,13 +37936,13 @@
       <c r="C41" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="D41" s="5" t="str">
+      <c r="D41" s="5">
         <f>IF(J38="bajo",0,IF(J38="medio",0.5,IF(J38="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E41" s="4"/>
       <c r="I41" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="J41" s="6" t="s">
         <v>13</v>
@@ -37933,13 +37954,13 @@
       <c r="C42" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="D42" s="5" t="str">
+      <c r="D42" s="5">
         <f>IF(J39="bajo",0,IF(J39="medio",0.5,IF(J39="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E42" s="4"/>
       <c r="I42" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="J42" s="6" t="s">
         <v>13</v>
@@ -37951,13 +37972,13 @@
       <c r="C43" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="D43" s="5" t="str">
+      <c r="D43" s="5">
         <f>IF(J40="bajo",0,IF(J40="medio",0.5,IF(J40="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E43" s="4"/>
       <c r="I43" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="J43" s="6" t="s">
         <v>13</v>
@@ -37975,10 +37996,10 @@
       </c>
       <c r="E44" s="4"/>
       <c r="I44" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="18" customHeight="1">
@@ -37993,10 +38014,10 @@
       </c>
       <c r="E45" s="4"/>
       <c r="I45" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="20.25" customHeight="1">
@@ -38011,10 +38032,10 @@
       </c>
       <c r="E46" s="4"/>
       <c r="I46" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="18" customHeight="1">
@@ -38024,10 +38045,10 @@
       <c r="D47" s="5"/>
       <c r="E47" s="4"/>
       <c r="I47" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="18" customHeight="1">
@@ -38038,16 +38059,16 @@
       <c r="C48" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="D48" s="5" t="str">
+      <c r="D48" s="5">
         <f>IF(J49="bajo",0,IF(J49="medio",0.5,IF(J49="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E48" s="4"/>
       <c r="I48" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="18" customHeight="1">
@@ -38056,16 +38077,16 @@
       <c r="C49" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="D49" s="5" t="str">
+      <c r="D49" s="5">
         <f>IF(J44="bajo",0,IF(J44="medio",0.5,IF(J44="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E49" s="4"/>
       <c r="I49" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="18" customHeight="1">
@@ -38074,17 +38095,11 @@
       <c r="C50" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="D50" s="5" t="str">
+      <c r="D50" s="5">
         <f>IF(J46="bajo",0,IF(J46="medio",0.5,IF(J46="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E50" s="4"/>
-      <c r="I50" t="s">
-        <v>263</v>
-      </c>
-      <c r="J50" s="6" t="s">
-        <v>264</v>
-      </c>
     </row>
     <row r="51" spans="1:10" ht="18" customHeight="1">
       <c r="A51" s="15"/>
@@ -38092,9 +38107,9 @@
       <c r="C51" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="D51" s="5" t="str">
+      <c r="D51" s="5">
         <f>IF(J47="bajo",0,IF(J47="medio",0.5,IF(J47="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E51" s="4"/>
     </row>
@@ -38104,9 +38119,9 @@
       <c r="C52" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="D52" s="5" t="str">
+      <c r="D52" s="5">
         <f>IF(J48="bajo",0,IF(J48="medio",0.5,IF(J48="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E52" s="4"/>
     </row>
@@ -38116,9 +38131,9 @@
       <c r="C53" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="D53" s="5" t="str">
+      <c r="D53" s="5">
         <f>IF(J45="bajo",0,IF(J45="medio",0.5,IF(J45="alto",1,"falta riesgo")))</f>
-        <v>falta riesgo</v>
+        <v>0</v>
       </c>
       <c r="E53" s="4"/>
     </row>
@@ -38206,10 +38221,10 @@
     </row>
     <row r="4" spans="2:5">
       <c r="B4" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>23</v>
@@ -38220,10 +38235,10 @@
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>24</v>
@@ -38234,10 +38249,10 @@
     </row>
     <row r="6" spans="2:5">
       <c r="B6" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>25</v>
@@ -38248,10 +38263,10 @@
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>26</v>
@@ -38262,10 +38277,10 @@
     </row>
     <row r="8" spans="2:5">
       <c r="B8" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>27</v>
@@ -38276,10 +38291,10 @@
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>28</v>
@@ -38290,10 +38305,10 @@
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>29</v>
@@ -38304,10 +38319,10 @@
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>30</v>
@@ -38318,10 +38333,10 @@
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>226</v>
@@ -38332,10 +38347,10 @@
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>32</v>
@@ -38346,10 +38361,10 @@
     </row>
     <row r="14" spans="2:5">
       <c r="B14" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>33</v>
@@ -38360,10 +38375,10 @@
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>34</v>
@@ -38374,10 +38389,10 @@
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>35</v>
@@ -38388,10 +38403,10 @@
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>36</v>
@@ -38402,10 +38417,10 @@
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>37</v>
@@ -38416,10 +38431,10 @@
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>38</v>
@@ -38430,10 +38445,10 @@
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="90" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C20" s="90" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="D20" s="90" t="s">
         <v>23</v>
@@ -38444,10 +38459,10 @@
     </row>
     <row r="21" spans="2:5">
       <c r="B21" s="90" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C21" s="90" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D21" s="90" t="s">
         <v>24</v>
@@ -38458,10 +38473,10 @@
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="90" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C22" s="90" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="D22" s="90" t="s">
         <v>25</v>
@@ -38472,10 +38487,10 @@
     </row>
     <row r="23" spans="2:5">
       <c r="B23" s="90" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C23" s="90" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="D23" s="90" t="s">
         <v>26</v>
@@ -38486,10 +38501,10 @@
     </row>
     <row r="24" spans="2:5">
       <c r="B24" s="90" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C24" s="90" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="D24" s="90" t="s">
         <v>27</v>
@@ -38500,10 +38515,10 @@
     </row>
     <row r="25" spans="2:5">
       <c r="B25" s="90" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C25" s="90" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D25" s="90" t="s">
         <v>28</v>
@@ -38514,10 +38529,10 @@
     </row>
     <row r="26" spans="2:5">
       <c r="B26" s="90" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C26" s="90" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="D26" s="90" t="s">
         <v>29</v>
@@ -38528,10 +38543,10 @@
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="90" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C27" s="90" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="D27" s="90" t="s">
         <v>30</v>
@@ -38542,10 +38557,10 @@
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="90" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C28" s="90" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D28" s="90" t="s">
         <v>226</v>
@@ -38556,10 +38571,10 @@
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="90" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C29" s="90" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="D29" s="90" t="s">
         <v>32</v>
@@ -38570,10 +38585,10 @@
     </row>
     <row r="30" spans="2:5">
       <c r="B30" s="90" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C30" s="90" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="D30" s="90" t="s">
         <v>33</v>
@@ -38584,10 +38599,10 @@
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="90" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C31" s="90" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="D31" s="90" t="s">
         <v>34</v>
@@ -38598,10 +38613,10 @@
     </row>
     <row r="32" spans="2:5">
       <c r="B32" s="90" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C32" s="90" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D32" s="90" t="s">
         <v>35</v>
@@ -38612,10 +38627,10 @@
     </row>
     <row r="33" spans="2:5">
       <c r="B33" s="90" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C33" s="90" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="D33" s="90" t="s">
         <v>36</v>
@@ -38626,10 +38641,10 @@
     </row>
     <row r="34" spans="2:5">
       <c r="B34" s="90" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C34" s="90" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="D34" s="90" t="s">
         <v>37</v>
@@ -38640,10 +38655,10 @@
     </row>
     <row r="35" spans="2:5">
       <c r="B35" s="90" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C35" s="90" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="D35" s="90" t="s">
         <v>38</v>
@@ -38654,10 +38669,10 @@
     </row>
     <row r="36" spans="2:5">
       <c r="B36" s="87" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>23</v>
@@ -38668,10 +38683,10 @@
     </row>
     <row r="37" spans="2:5">
       <c r="B37" s="87" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>24</v>
@@ -38682,10 +38697,10 @@
     </row>
     <row r="38" spans="2:5">
       <c r="B38" s="87" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>25</v>
@@ -38696,10 +38711,10 @@
     </row>
     <row r="39" spans="2:5">
       <c r="B39" s="87" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>26</v>
@@ -38710,10 +38725,10 @@
     </row>
     <row r="40" spans="2:5">
       <c r="B40" s="87" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>27</v>
@@ -38724,10 +38739,10 @@
     </row>
     <row r="41" spans="2:5">
       <c r="B41" s="87" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>28</v>
@@ -38738,10 +38753,10 @@
     </row>
     <row r="42" spans="2:5">
       <c r="B42" s="87" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>29</v>
@@ -38752,10 +38767,10 @@
     </row>
     <row r="43" spans="2:5">
       <c r="B43" s="87" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>30</v>
@@ -38766,10 +38781,10 @@
     </row>
     <row r="44" spans="2:5">
       <c r="B44" s="87" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>226</v>
@@ -38780,10 +38795,10 @@
     </row>
     <row r="45" spans="2:5">
       <c r="B45" s="87" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>32</v>
@@ -38794,10 +38809,10 @@
     </row>
     <row r="46" spans="2:5">
       <c r="B46" s="87" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>33</v>
@@ -38808,10 +38823,10 @@
     </row>
     <row r="47" spans="2:5">
       <c r="B47" s="87" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>34</v>
@@ -38822,10 +38837,10 @@
     </row>
     <row r="48" spans="2:5">
       <c r="B48" s="87" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>35</v>
@@ -38836,10 +38851,10 @@
     </row>
     <row r="49" spans="2:5">
       <c r="B49" s="87" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>36</v>
@@ -38850,10 +38865,10 @@
     </row>
     <row r="50" spans="2:5">
       <c r="B50" s="87" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>37</v>
@@ -38864,10 +38879,10 @@
     </row>
     <row r="51" spans="2:5">
       <c r="B51" s="87" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>38</v>
@@ -38878,10 +38893,10 @@
     </row>
     <row r="52" spans="2:5">
       <c r="B52" s="87" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="D52" s="91" t="s">
         <v>23</v>
@@ -38892,10 +38907,10 @@
     </row>
     <row r="53" spans="2:5">
       <c r="B53" s="87" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="D53" s="91" t="s">
         <v>24</v>
@@ -38906,10 +38921,10 @@
     </row>
     <row r="54" spans="2:5">
       <c r="B54" s="87" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="D54" s="91" t="s">
         <v>25</v>
@@ -38920,10 +38935,10 @@
     </row>
     <row r="55" spans="2:5">
       <c r="B55" s="87" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="D55" s="91" t="s">
         <v>26</v>
@@ -38934,10 +38949,10 @@
     </row>
     <row r="56" spans="2:5">
       <c r="B56" s="87" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="D56" s="91" t="s">
         <v>27</v>
@@ -38948,10 +38963,10 @@
     </row>
     <row r="57" spans="2:5">
       <c r="B57" s="87" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="D57" s="91" t="s">
         <v>28</v>
@@ -38962,10 +38977,10 @@
     </row>
     <row r="58" spans="2:5">
       <c r="B58" s="87" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="D58" s="91" t="s">
         <v>29</v>
@@ -38976,10 +38991,10 @@
     </row>
     <row r="59" spans="2:5">
       <c r="B59" s="87" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="D59" s="91" t="s">
         <v>30</v>
@@ -38990,10 +39005,10 @@
     </row>
     <row r="60" spans="2:5">
       <c r="B60" s="87" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="D60" s="91" t="s">
         <v>226</v>
@@ -39004,10 +39019,10 @@
     </row>
     <row r="61" spans="2:5">
       <c r="B61" s="87" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="D61" s="91" t="s">
         <v>32</v>
@@ -39018,10 +39033,10 @@
     </row>
     <row r="62" spans="2:5">
       <c r="B62" s="87" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="D62" s="91" t="s">
         <v>33</v>
@@ -39032,10 +39047,10 @@
     </row>
     <row r="63" spans="2:5">
       <c r="B63" s="87" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="D63" s="91" t="s">
         <v>34</v>
@@ -39046,10 +39061,10 @@
     </row>
     <row r="64" spans="2:5">
       <c r="B64" s="87" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D64" s="91" t="s">
         <v>35</v>
@@ -39060,10 +39075,10 @@
     </row>
     <row r="65" spans="2:5">
       <c r="B65" s="87" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="D65" s="91" t="s">
         <v>36</v>
@@ -39074,10 +39089,10 @@
     </row>
     <row r="66" spans="2:5">
       <c r="B66" s="87" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="D66" s="91" t="s">
         <v>37</v>
@@ -39088,10 +39103,10 @@
     </row>
     <row r="67" spans="2:5">
       <c r="B67" s="87" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="D67" s="91" t="s">
         <v>38</v>
@@ -39102,10 +39117,10 @@
     </row>
     <row r="68" spans="2:5">
       <c r="B68" s="87" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="D68" s="91" t="s">
         <v>23</v>
@@ -39116,10 +39131,10 @@
     </row>
     <row r="69" spans="2:5">
       <c r="B69" s="87" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="D69" s="91" t="s">
         <v>24</v>
@@ -39130,10 +39145,10 @@
     </row>
     <row r="70" spans="2:5">
       <c r="B70" s="87" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="D70" s="91" t="s">
         <v>25</v>
@@ -39144,10 +39159,10 @@
     </row>
     <row r="71" spans="2:5">
       <c r="B71" s="87" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="D71" s="91" t="s">
         <v>26</v>
@@ -39158,10 +39173,10 @@
     </row>
     <row r="72" spans="2:5">
       <c r="B72" s="87" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="D72" s="91" t="s">
         <v>27</v>
@@ -39172,10 +39187,10 @@
     </row>
     <row r="73" spans="2:5">
       <c r="B73" s="87" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="D73" s="91" t="s">
         <v>28</v>
@@ -39186,10 +39201,10 @@
     </row>
     <row r="74" spans="2:5">
       <c r="B74" s="87" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="D74" s="91" t="s">
         <v>29</v>
@@ -39200,10 +39215,10 @@
     </row>
     <row r="75" spans="2:5">
       <c r="B75" s="87" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="D75" s="91" t="s">
         <v>30</v>
@@ -39214,10 +39229,10 @@
     </row>
     <row r="76" spans="2:5">
       <c r="B76" s="87" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="D76" s="91" t="s">
         <v>226</v>
@@ -39228,10 +39243,10 @@
     </row>
     <row r="77" spans="2:5">
       <c r="B77" s="87" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="D77" s="91" t="s">
         <v>32</v>
@@ -39242,10 +39257,10 @@
     </row>
     <row r="78" spans="2:5">
       <c r="B78" s="87" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="D78" s="91" t="s">
         <v>33</v>
@@ -39256,10 +39271,10 @@
     </row>
     <row r="79" spans="2:5">
       <c r="B79" s="87" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="D79" s="91" t="s">
         <v>34</v>
@@ -39270,10 +39285,10 @@
     </row>
     <row r="80" spans="2:5">
       <c r="B80" s="87" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="D80" s="91" t="s">
         <v>35</v>
@@ -39284,10 +39299,10 @@
     </row>
     <row r="81" spans="2:5">
       <c r="B81" s="87" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="D81" s="91" t="s">
         <v>36</v>
@@ -39298,10 +39313,10 @@
     </row>
     <row r="82" spans="2:5">
       <c r="B82" s="87" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="D82" s="91" t="s">
         <v>37</v>
@@ -39312,10 +39327,10 @@
     </row>
     <row r="83" spans="2:5">
       <c r="B83" s="87" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="D83" s="91" t="s">
         <v>38</v>
@@ -39528,31 +39543,31 @@
         <v>18</v>
       </c>
       <c r="D11" s="79" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E11" s="79" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="F11" s="79" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="G11" s="80" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="I11" s="84" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="413" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="K11" s="413" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="L11" s="413" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="M11" s="415" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="O11" s="348"/>
     </row>
@@ -39563,31 +39578,31 @@
         <v>16</v>
       </c>
       <c r="D12" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E12" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="F12" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="G12" s="72" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="I12" s="41" t="s">
         <v>24</v>
       </c>
       <c r="J12" s="414" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="K12" s="414" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="L12" s="414" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="M12" s="416" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="N12" s="349"/>
       <c r="O12" s="340"/>
@@ -39599,31 +39614,31 @@
         <v>19</v>
       </c>
       <c r="D13" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E13" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="F13" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="G13" s="72" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="I13" s="41" t="s">
         <v>25</v>
       </c>
       <c r="J13" s="414" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="K13" s="414" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="L13" s="414" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="M13" s="416" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="N13" s="349"/>
       <c r="O13" s="340"/>
@@ -39635,31 +39650,31 @@
         <v>17</v>
       </c>
       <c r="D14" s="71" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="E14" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="F14" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="G14" s="72" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="I14" s="41" t="s">
         <v>26</v>
       </c>
       <c r="J14" s="414" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="K14" s="414" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="L14" s="414" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="M14" s="416" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="N14" s="349"/>
       <c r="O14" s="340"/>
@@ -39668,34 +39683,34 @@
       <c r="A15" s="38"/>
       <c r="B15" s="339"/>
       <c r="C15" s="67" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="D15" s="71" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="E15" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="F15" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="G15" s="72" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="I15" s="41" t="s">
         <v>27</v>
       </c>
       <c r="J15" s="414" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="K15" s="414" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="L15" s="414" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="M15" s="416" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="N15" s="349"/>
       <c r="O15" s="340"/>
@@ -39704,34 +39719,34 @@
       <c r="A16" s="38"/>
       <c r="B16" s="339"/>
       <c r="C16" s="67" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="D16" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E16" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="F16" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="G16" s="72" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="I16" s="41" t="s">
         <v>28</v>
       </c>
       <c r="J16" s="414" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="K16" s="414" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="L16" s="414" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="M16" s="416" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="N16" s="349"/>
       <c r="O16" s="340"/>
@@ -39740,34 +39755,34 @@
       <c r="A17" s="38"/>
       <c r="B17" s="339"/>
       <c r="C17" s="67" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="D17" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E17" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="F17" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="G17" s="72" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="I17" s="41" t="s">
         <v>29</v>
       </c>
       <c r="J17" s="414" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="K17" s="414" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="L17" s="414" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="M17" s="416" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="N17" s="349"/>
       <c r="O17" s="340"/>
@@ -39776,34 +39791,34 @@
       <c r="A18" s="38"/>
       <c r="B18" s="339"/>
       <c r="C18" s="67" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="D18" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E18" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="F18" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="G18" s="72" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="I18" s="41" t="s">
         <v>30</v>
       </c>
       <c r="J18" s="414" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="K18" s="414" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="L18" s="414" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="M18" s="416" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="N18" s="349"/>
       <c r="O18" s="340"/>
@@ -39815,31 +39830,31 @@
         <v>17</v>
       </c>
       <c r="D19" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E19" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="F19" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="G19" s="72" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="I19" s="41" t="s">
         <v>226</v>
       </c>
       <c r="J19" s="414" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="K19" s="414" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="L19" s="414" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="M19" s="416" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="N19" s="349"/>
       <c r="O19" s="340"/>
@@ -39848,34 +39863,34 @@
       <c r="A20" s="38"/>
       <c r="B20" s="339"/>
       <c r="C20" s="40" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="D20" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E20" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="F20" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="G20" s="72" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="I20" s="41" t="s">
         <v>32</v>
       </c>
       <c r="J20" s="414" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="K20" s="414" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="L20" s="414" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="M20" s="416" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="N20" s="349"/>
       <c r="O20" s="340"/>
@@ -39884,34 +39899,34 @@
       <c r="A21" s="38"/>
       <c r="B21" s="339"/>
       <c r="C21" s="39" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="D21" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E21" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="F21" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="G21" s="72" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="I21" s="41" t="s">
         <v>33</v>
       </c>
       <c r="J21" s="414" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="K21" s="414" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="L21" s="414" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="M21" s="416" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="N21" s="349"/>
       <c r="O21" s="340"/>
@@ -39920,34 +39935,34 @@
       <c r="A22" s="38"/>
       <c r="B22" s="339"/>
       <c r="C22" s="39" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D22" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E22" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="F22" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="G22" s="72" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="I22" s="41" t="s">
         <v>34</v>
       </c>
       <c r="J22" s="414" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="K22" s="414" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="L22" s="414" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="M22" s="416" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="N22" s="349"/>
       <c r="O22" s="340"/>
@@ -39956,34 +39971,34 @@
       <c r="A23" s="38"/>
       <c r="B23" s="339"/>
       <c r="C23" s="40" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="D23" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E23" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="F23" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="G23" s="72" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="I23" s="41" t="s">
         <v>35</v>
       </c>
       <c r="J23" s="414" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="K23" s="414" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="L23" s="414" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="M23" s="416" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="N23" s="349"/>
       <c r="O23" s="340"/>
@@ -39995,31 +40010,31 @@
         <v>20</v>
       </c>
       <c r="D24" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E24" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="F24" s="71" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="G24" s="72" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="I24" s="41" t="s">
         <v>36</v>
       </c>
       <c r="J24" s="414" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="K24" s="414" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="L24" s="414" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="M24" s="416" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="N24" s="349"/>
       <c r="O24" s="340"/>
@@ -40036,16 +40051,16 @@
         <v>37</v>
       </c>
       <c r="J25" s="414" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="K25" s="414" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="L25" s="414" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="M25" s="416" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="N25" s="349"/>
       <c r="O25" s="340"/>
@@ -40062,16 +40077,16 @@
         <v>38</v>
       </c>
       <c r="J26" s="417" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="K26" s="417" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="L26" s="417" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="M26" s="418" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="N26" s="349"/>
       <c r="O26" s="340"/>
@@ -40279,7 +40294,7 @@
       <c r="E2" s="104"/>
       <c r="G2" s="106"/>
       <c r="H2" s="98" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="I2" s="523" t="s">
         <v>123</v>
@@ -40296,7 +40311,7 @@
     <row r="3" spans="1:17" s="69" customFormat="1" ht="22.5" customHeight="1">
       <c r="A3" s="101"/>
       <c r="B3" s="69" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="D3" s="107"/>
       <c r="E3" s="100"/>
@@ -40670,7 +40685,7 @@
         <v>115</v>
       </c>
       <c r="E16" s="520" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="F16" s="521"/>
       <c r="G16" s="521"/>
@@ -40693,7 +40708,7 @@
         <v>116</v>
       </c>
       <c r="E17" s="520" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="F17" s="521"/>
       <c r="G17" s="521"/>
@@ -40717,7 +40732,7 @@
         <v>117</v>
       </c>
       <c r="E18" s="520" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="F18" s="521"/>
       <c r="G18" s="521"/>
@@ -40738,7 +40753,7 @@
         <v>118</v>
       </c>
       <c r="E19" s="520" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="F19" s="521"/>
       <c r="G19" s="521"/>
@@ -40759,7 +40774,7 @@
         <v>119</v>
       </c>
       <c r="E20" s="520" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="F20" s="521"/>
       <c r="G20" s="521"/>
@@ -40779,7 +40794,7 @@
         <v>120</v>
       </c>
       <c r="E21" s="520" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="F21" s="521"/>
       <c r="G21" s="521"/>
@@ -40797,10 +40812,10 @@
       <c r="B22" s="125"/>
       <c r="C22" s="103"/>
       <c r="D22" s="410" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="E22" s="520" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="F22" s="521"/>
       <c r="G22" s="521"/>

--- a/Backend/output/informe_final.xlsx
+++ b/Backend/output/informe_final.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{755CB9DE-4E18-4544-88C0-E024EF50EE1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D42A5960-DF64-402B-8948-C0845645106D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="15375" windowHeight="7785" tabRatio="733" firstSheet="11" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="733" firstSheet="4" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="433">
   <si>
     <t>SUBSECRETARÍA DE EDUCACIÓN</t>
   </si>
@@ -319,9 +319,6 @@
   </si>
   <si>
     <t>REGIONES : ESTADO RIESGO INDICADORES POR CR AL CIERRE:</t>
-  </si>
-  <si>
-    <t>OCTUBRE 2024</t>
   </si>
   <si>
     <t>REGIÓN</t>
@@ -827,7 +824,7 @@
 través del SAE</t>
   </si>
   <si>
-    <t>MARZO - 2025</t>
+    <t>ABRIL - 2025</t>
   </si>
   <si>
     <t>Gab Subse</t>
@@ -1307,9 +1304,6 @@
     <t>50%</t>
   </si>
   <si>
-    <t>Comentarios</t>
-  </si>
-  <si>
     <t>En enero 2025 se envió mediante mail del Jefe del Gabinete del Ministro, el resultado del monitoreo del tercer año de gestión.</t>
   </si>
   <si>
@@ -1325,10 +1319,13 @@
     <t>En febrero 2025 se tramitó totalmente el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio del 2do año de gestión.</t>
   </si>
   <si>
-    <t>Acum MARZO - 2025</t>
-  </si>
-  <si>
-    <t>Hitos ADP ocurridos al 22 de MARZO</t>
+    <t>En marzo 2025 se enviaron los antecedentes a la División Jurídica para la elaboración del acto administrativo de la evaluación del segundo año de gestión.</t>
+  </si>
+  <si>
+    <t>Acum ABRIL - 2025</t>
+  </si>
+  <si>
+    <t>Hitos ADP ocurridos al 8 de ABRIL</t>
   </si>
   <si>
     <t>Política de Gestión de Riesgos</t>
@@ -1480,7 +1477,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="90">
+  <fonts count="91">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2126,8 +2123,16 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFF4EE00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2232,30 +2237,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF008080"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="3" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2270,6 +2251,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor theme="7"/>
       </patternFill>
     </fill>
   </fills>
@@ -5587,7 +5574,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="705">
+  <cellXfs count="706">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -6133,9 +6120,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="186" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6151,9 +6135,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="157" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6166,10 +6147,10 @@
     <xf numFmtId="0" fontId="65" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6255,16 +6236,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="209" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="211" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="80" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="212" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="213" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6291,7 +6263,7 @@
     <xf numFmtId="0" fontId="76" fillId="0" borderId="223" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="23" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="19" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="224" xfId="0" applyBorder="1"/>
@@ -6478,22 +6450,22 @@
     <xf numFmtId="49" fontId="20" fillId="9" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="24" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="24" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="24" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="24" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="24" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6610,6 +6582,21 @@
     <xf numFmtId="0" fontId="89" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="157" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="80" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="186" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="212" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="69" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7210,31 +7197,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="20" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="4" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="90" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="90" fillId="4" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="4" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="20" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="4" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="19" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="4" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="4" borderId="198" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="19" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="21" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="21" borderId="198" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="21" borderId="192" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="4" borderId="192" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7252,7 +7242,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7264,19 +7254,19 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="21" borderId="185" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="4" borderId="185" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="200" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="200" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="199" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="199" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="164" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="164" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7564,7 +7554,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
+          <bgColor rgb="FF002060"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -7583,8 +7573,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFF4EE00"/>
       <color rgb="FF008080"/>
-      <color rgb="FFF4EE00"/>
       <color rgb="FFCCFF66"/>
     </mruColors>
   </colors>
@@ -13093,7 +13083,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2F4094B4-43C7-471D-B2FF-D7AD7B066C3F}" type="CELLRANGE">
+                    <a:fld id="{CB06C2E6-1E7D-4A4D-AB80-B09E852CEF0C}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13127,7 +13117,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AE7C6B00-604D-4DFF-AD4A-2E90A4C65424}" type="CELLRANGE">
+                    <a:fld id="{87BAEF73-8224-4BA1-A227-D9D2BBFFC837}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13161,7 +13151,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E710295C-061A-4015-941E-33F664AC57BD}" type="CELLRANGE">
+                    <a:fld id="{976CF574-3B49-4C8B-B8B0-89A85371BEF8}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13195,7 +13185,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{24B38E6A-FF20-4839-9BA6-DB983D8A1DF9}" type="CELLRANGE">
+                    <a:fld id="{30AA0A42-41AC-4566-887A-2ACE757A0C9B}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13229,7 +13219,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0382C5B7-02F3-453F-8FB7-3D1A0B7DB327}" type="CELLRANGE">
+                    <a:fld id="{553D689C-50F4-496B-BBF5-0619F37B8A4F}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13263,7 +13253,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BADEB7AA-FFEE-4627-BE6B-B2A951165B8B}" type="CELLRANGE">
+                    <a:fld id="{B72AF6A3-3CF1-48DB-A02E-3575F5AF4027}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13297,7 +13287,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6AFDC4B6-402E-4D0F-8B54-E94D2F9C4B30}" type="CELLRANGE">
+                    <a:fld id="{43DB766B-FB6B-423E-9913-FF5982720AA9}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13331,7 +13321,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F8FEB8B5-C24D-4128-AB9E-10525F180D60}" type="CELLRANGE">
+                    <a:fld id="{98535E82-2BEE-4694-BE9C-9ECB12567F2F}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13365,7 +13355,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CE5AB509-186E-49BB-9530-65F73D8B12D7}" type="CELLRANGE">
+                    <a:fld id="{ACE6F29D-CF83-43B1-BCA7-E9A677E4D13F}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13399,7 +13389,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2CFDED36-7704-487C-88B8-AFFF463D6F67}" type="CELLRANGE">
+                    <a:fld id="{13D106E3-9DA2-48E0-815A-20118F4C71B6}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13433,7 +13423,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{55B5E600-DADB-4C58-A53B-F39675DBB83F}" type="CELLRANGE">
+                    <a:fld id="{8CA606A2-FEA6-4F03-833C-83BF173C37B9}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13467,7 +13457,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B8D8CE1D-C42C-49BC-AC48-0421D41FD08C}" type="CELLRANGE">
+                    <a:fld id="{CE7D12D1-E966-4DFE-A925-C49FA33487C4}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13850,7 +13840,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FFF2036E-637C-4AA8-A457-10508741B0D3}" type="CELLRANGE">
+                    <a:fld id="{9544A587-8AF7-4128-897B-A054C1528D37}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14567,7 +14557,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{02C2305A-B617-4845-AEFE-459413F438E1}" type="CELLRANGE">
+                    <a:fld id="{8D4BF037-6365-4A02-9B44-3D5C8A287B38}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr>
                         <a:defRPr sz="1400">
@@ -14647,7 +14637,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{34DF82A1-5D2E-4C01-BDAA-BBD1CB2A21BA}" type="CELLRANGE">
+                    <a:fld id="{12940128-3CD8-4C53-8407-27EE0764C40F}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -23400,7 +23390,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C3:D5" spid="_x0000_s286649"/>
+                  <a14:cameraTool cellRange="data_status_NC!C3:D5" spid="_x0000_s286673"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23456,7 +23446,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C20:D24" spid="_x0000_s286650"/>
+                  <a14:cameraTool cellRange="data_status_NC!C20:D24" spid="_x0000_s286674"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23521,7 +23511,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C7:D13" spid="_x0000_s286651"/>
+                  <a14:cameraTool cellRange="data_status_NC!C7:D13" spid="_x0000_s286675"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23586,7 +23576,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C15:D18" spid="_x0000_s286652"/>
+                  <a14:cameraTool cellRange="data_status_NC!C15:D18" spid="_x0000_s286676"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23651,7 +23641,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C26:D33" spid="_x0000_s286653"/>
+                  <a14:cameraTool cellRange="data_status_NC!C26:D33" spid="_x0000_s286677"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23716,7 +23706,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C35:D39" spid="_x0000_s286654"/>
+                  <a14:cameraTool cellRange="data_status_NC!C35:D39" spid="_x0000_s286678"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23781,7 +23771,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C41:D46" spid="_x0000_s286655"/>
+                  <a14:cameraTool cellRange="data_status_NC!C41:D46" spid="_x0000_s286679"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23846,7 +23836,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C48:D54" spid="_x0000_s286656"/>
+                  <a14:cameraTool cellRange="data_status_NC!C48:D54" spid="_x0000_s286680"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -26418,7 +26408,7 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>1147440</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>441107</xdr:rowOff>
+      <xdr:rowOff>441108</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -26479,7 +26469,7 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>672354</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>311726</xdr:rowOff>
+      <xdr:rowOff>311727</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -27224,11 +27214,11 @@
     <row r="11" spans="1:24" ht="39.75" customHeight="1">
       <c r="A11" s="98"/>
       <c r="B11" s="95"/>
-      <c r="C11" s="271"/>
-      <c r="D11" s="271"/>
-      <c r="E11" s="276"/>
-      <c r="F11" s="277" t="s">
-        <v>191</v>
+      <c r="C11" s="269"/>
+      <c r="D11" s="269"/>
+      <c r="E11" s="274"/>
+      <c r="F11" s="275" t="s">
+        <v>190</v>
       </c>
       <c r="G11" s="466">
         <v>2025</v>
@@ -27256,9 +27246,9 @@
       <c r="B12" s="95"/>
       <c r="C12" s="98"/>
       <c r="D12" s="98"/>
-      <c r="E12" s="278"/>
+      <c r="E12" s="276"/>
       <c r="F12" s="467" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G12" s="468"/>
       <c r="H12" s="98"/>
@@ -27336,9 +27326,9 @@
       <c r="B15" s="95"/>
       <c r="C15" s="98"/>
       <c r="D15" s="98"/>
-      <c r="E15" s="275"/>
+      <c r="E15" s="273"/>
       <c r="F15" s="464" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G15" s="464"/>
       <c r="H15" s="98"/>
@@ -27364,9 +27354,9 @@
       <c r="B16" s="95"/>
       <c r="C16" s="98"/>
       <c r="D16" s="98"/>
-      <c r="E16" s="275"/>
+      <c r="E16" s="273"/>
       <c r="F16" s="464" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G16" s="464"/>
       <c r="H16" s="98"/>
@@ -27392,9 +27382,9 @@
       <c r="B17" s="95"/>
       <c r="C17" s="98"/>
       <c r="D17" s="98"/>
-      <c r="E17" s="272"/>
-      <c r="F17" s="273"/>
-      <c r="G17" s="273"/>
+      <c r="E17" s="270"/>
+      <c r="F17" s="271"/>
+      <c r="G17" s="271"/>
       <c r="H17" s="98"/>
       <c r="I17" s="98"/>
       <c r="J17" s="98"/>
@@ -27418,9 +27408,9 @@
       <c r="B18" s="95"/>
       <c r="C18" s="98"/>
       <c r="D18" s="98"/>
-      <c r="E18" s="274"/>
+      <c r="E18" s="272"/>
       <c r="F18" s="465" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G18" s="465"/>
       <c r="H18" s="98"/>
@@ -28124,10 +28114,10 @@
     </row>
     <row r="3" spans="1:28" ht="24.75" customHeight="1" thickBot="1">
       <c r="A3" s="207" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B3" s="552" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C3" s="553"/>
       <c r="D3" s="553"/>
@@ -28157,10 +28147,10 @@
     </row>
     <row r="4" spans="1:28" ht="23.25" customHeight="1" thickBot="1">
       <c r="A4" s="208" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B4" s="555" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C4" s="556"/>
       <c r="D4" s="556"/>
@@ -28220,7 +28210,7 @@
     <row r="6" spans="1:28" ht="24.75" customHeight="1" thickBot="1">
       <c r="A6" s="209"/>
       <c r="B6" s="561" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C6" s="562"/>
       <c r="D6" s="562"/>
@@ -28228,7 +28218,7 @@
       <c r="F6" s="105"/>
       <c r="G6" s="168"/>
       <c r="H6" s="581" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I6" s="582"/>
       <c r="J6" s="582"/>
@@ -28236,21 +28226,21 @@
       <c r="L6" s="105"/>
       <c r="M6" s="168"/>
       <c r="N6" s="589" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O6" s="590"/>
       <c r="P6" s="591"/>
       <c r="Q6" s="175"/>
       <c r="R6" s="177"/>
       <c r="S6" s="541" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T6" s="542"/>
       <c r="U6" s="178"/>
       <c r="V6" s="182"/>
       <c r="W6" s="169"/>
       <c r="X6" s="541" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Y6" s="542"/>
       <c r="Z6" s="96"/>
@@ -28259,16 +28249,16 @@
     <row r="7" spans="1:28" ht="30.75" customHeight="1" thickBot="1">
       <c r="A7" s="209"/>
       <c r="B7" s="219" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="211" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="211" t="s">
+      <c r="D7" s="212" t="s">
         <v>131</v>
       </c>
-      <c r="D7" s="212" t="s">
+      <c r="E7" s="213" t="s">
         <v>132</v>
-      </c>
-      <c r="E7" s="213" t="s">
-        <v>133</v>
       </c>
       <c r="F7" s="105"/>
       <c r="G7" s="135"/>
@@ -28308,10 +28298,10 @@
     <row r="8" spans="1:28" ht="21.75" customHeight="1" thickBot="1">
       <c r="A8" s="209"/>
       <c r="B8" s="221" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C8" s="215" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D8" s="210">
         <v>2019</v>
@@ -28343,10 +28333,10 @@
     <row r="9" spans="1:28" ht="18" customHeight="1" thickBot="1">
       <c r="A9" s="214"/>
       <c r="B9" s="221" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C9" s="216" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D9" s="160">
         <v>2024</v>
@@ -28378,10 +28368,10 @@
     <row r="10" spans="1:28" ht="21" customHeight="1">
       <c r="A10" s="97"/>
       <c r="B10" s="221" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C10" s="216" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D10" s="160">
         <v>2024</v>
@@ -28389,7 +28379,7 @@
       <c r="E10" s="231"/>
       <c r="F10" s="105"/>
       <c r="G10" s="569" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H10" s="570"/>
       <c r="I10" s="570"/>
@@ -28415,10 +28405,10 @@
     <row r="11" spans="1:28" ht="19.5" customHeight="1">
       <c r="A11" s="95"/>
       <c r="B11" s="221" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C11" s="220" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D11" s="160">
         <v>2024</v>
@@ -28426,26 +28416,26 @@
       <c r="E11" s="231"/>
       <c r="F11" s="105"/>
       <c r="G11" s="572" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H11" s="567"/>
       <c r="I11" s="567" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J11" s="567"/>
       <c r="K11" s="567"/>
       <c r="L11" s="567" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M11" s="567"/>
       <c r="N11" s="567"/>
       <c r="O11" s="567" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P11" s="567"/>
       <c r="Q11" s="567"/>
       <c r="R11" s="567" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="S11" s="567"/>
       <c r="T11" s="567"/>
@@ -28460,10 +28450,10 @@
     <row r="12" spans="1:28" ht="17.25" customHeight="1">
       <c r="A12" s="95"/>
       <c r="B12" s="222" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C12" s="224" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D12" s="216">
         <v>2024</v>
@@ -28482,19 +28472,19 @@
       <c r="P12" s="567"/>
       <c r="Q12" s="567"/>
       <c r="R12" s="543" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S12" s="543"/>
       <c r="T12" s="543" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="U12" s="543"/>
       <c r="V12" s="543" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="W12" s="543"/>
       <c r="X12" s="543" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Y12" s="564"/>
       <c r="Z12" s="96"/>
@@ -28503,10 +28493,10 @@
     <row r="13" spans="1:28" ht="18.75" customHeight="1">
       <c r="A13" s="95"/>
       <c r="B13" s="221" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C13" s="215" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D13" s="160">
         <v>2024</v>
@@ -28538,10 +28528,10 @@
     <row r="14" spans="1:28" ht="18.75" customHeight="1">
       <c r="A14" s="95"/>
       <c r="B14" s="221" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C14" s="216" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D14" s="160">
         <v>2024</v>
@@ -28588,10 +28578,10 @@
     <row r="15" spans="1:28" ht="19.5" customHeight="1" thickBot="1">
       <c r="A15" s="95"/>
       <c r="B15" s="223" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C15" s="218" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D15" s="217">
         <v>2024</v>
@@ -28685,7 +28675,7 @@
     <row r="17" spans="1:27" ht="21" customHeight="1">
       <c r="A17" s="95"/>
       <c r="B17" s="558" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C17" s="559"/>
       <c r="D17" s="559"/>
@@ -28732,20 +28722,20 @@
     <row r="18" spans="1:27" ht="34.5" customHeight="1">
       <c r="A18" s="95"/>
       <c r="B18" s="183" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="159" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="158" t="s">
+        <v>127</v>
+      </c>
+      <c r="E18" s="184" t="s">
         <v>148</v>
-      </c>
-      <c r="C18" s="159" t="s">
-        <v>142</v>
-      </c>
-      <c r="D18" s="158" t="s">
-        <v>128</v>
-      </c>
-      <c r="E18" s="184" t="s">
-        <v>149</v>
       </c>
       <c r="F18" s="105"/>
       <c r="G18" s="544" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H18" s="545"/>
       <c r="I18" s="546">
@@ -28785,18 +28775,18 @@
     <row r="19" spans="1:27" ht="30.75" customHeight="1">
       <c r="A19" s="95"/>
       <c r="B19" s="185" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C19" s="160">
         <v>16</v>
       </c>
       <c r="D19" s="165" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E19" s="233"/>
       <c r="F19" s="105"/>
       <c r="G19" s="544" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H19" s="545"/>
       <c r="I19" s="546">
@@ -28836,13 +28826,13 @@
     <row r="20" spans="1:27" ht="30" customHeight="1">
       <c r="A20" s="95"/>
       <c r="B20" s="185" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C20" s="165">
         <v>13</v>
       </c>
       <c r="D20" s="165" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E20" s="233"/>
       <c r="F20" s="105"/>
@@ -28887,13 +28877,13 @@
     <row r="21" spans="1:27" ht="30" customHeight="1">
       <c r="A21" s="95"/>
       <c r="B21" s="185" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C21" s="165">
         <v>35</v>
       </c>
       <c r="D21" s="165" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E21" s="233"/>
       <c r="F21" s="105"/>
@@ -28938,18 +28928,18 @@
     <row r="22" spans="1:27" ht="32.25" customHeight="1">
       <c r="A22" s="95"/>
       <c r="B22" s="185" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C22" s="165">
         <v>21</v>
       </c>
       <c r="D22" s="165" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E22" s="233"/>
       <c r="F22" s="105"/>
       <c r="G22" s="544" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H22" s="545"/>
       <c r="I22" s="546">
@@ -28989,18 +28979,18 @@
     <row r="23" spans="1:27" ht="30.75" customHeight="1" thickBot="1">
       <c r="A23" s="95"/>
       <c r="B23" s="186" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C23" s="187">
         <v>2</v>
       </c>
       <c r="D23" s="187" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E23" s="234"/>
       <c r="F23" s="105"/>
       <c r="G23" s="587" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H23" s="579"/>
       <c r="I23" s="579">
@@ -29111,13 +29101,13 @@
       <c r="F26" s="95"/>
       <c r="G26" s="161"/>
       <c r="H26" s="624" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I26" s="625"/>
       <c r="J26" s="626"/>
       <c r="K26" s="105"/>
       <c r="L26" s="630" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M26" s="631"/>
       <c r="N26" s="631"/>
@@ -29151,34 +29141,34 @@
       <c r="J27" s="623"/>
       <c r="K27" s="105"/>
       <c r="L27" s="595" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M27" s="543"/>
       <c r="N27" s="543"/>
       <c r="O27" s="543" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P27" s="543"/>
       <c r="Q27" s="543" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R27" s="543"/>
       <c r="S27" s="543" t="s">
+        <v>156</v>
+      </c>
+      <c r="T27" s="543" t="s">
         <v>157</v>
-      </c>
-      <c r="T27" s="543" t="s">
-        <v>158</v>
       </c>
       <c r="U27" s="543"/>
       <c r="V27" s="543" t="s">
+        <v>158</v>
+      </c>
+      <c r="W27" s="543" t="s">
         <v>159</v>
-      </c>
-      <c r="W27" s="543" t="s">
-        <v>160</v>
       </c>
       <c r="X27" s="543"/>
       <c r="Y27" s="564" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Z27" s="96"/>
       <c r="AA27" s="95"/>
@@ -29311,7 +29301,7 @@
       <c r="F31" s="95"/>
       <c r="G31" s="161"/>
       <c r="H31" s="627" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I31" s="628"/>
       <c r="J31" s="629"/>
@@ -29410,7 +29400,7 @@
       <c r="J33" s="623"/>
       <c r="K33" s="105"/>
       <c r="L33" s="592" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="M33" s="593"/>
       <c r="N33" s="593"/>
@@ -29455,7 +29445,7 @@
       <c r="J34" s="193"/>
       <c r="K34" s="105"/>
       <c r="L34" s="592" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M34" s="593"/>
       <c r="N34" s="593"/>
@@ -29586,13 +29576,13 @@
       <c r="F37" s="95"/>
       <c r="G37" s="161"/>
       <c r="H37" s="627" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I37" s="628"/>
       <c r="J37" s="629"/>
       <c r="K37" s="105"/>
       <c r="L37" s="592" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M37" s="593"/>
       <c r="N37" s="594"/>
@@ -29636,7 +29626,7 @@
       <c r="J38" s="193"/>
       <c r="K38" s="105"/>
       <c r="L38" s="611" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M38" s="612"/>
       <c r="N38" s="613"/>
@@ -29783,7 +29773,7 @@
       <c r="P42" s="620"/>
       <c r="Q42" s="98"/>
       <c r="R42" s="645" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S42" s="646"/>
       <c r="T42" s="124"/>
@@ -29804,7 +29794,7 @@
       <c r="F43" s="95"/>
       <c r="G43" s="161"/>
       <c r="H43" s="652" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I43" s="652"/>
       <c r="J43" s="653"/>
@@ -29812,25 +29802,25 @@
       <c r="L43" s="161"/>
       <c r="M43" s="192"/>
       <c r="N43" s="636" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O43" s="637"/>
       <c r="P43" s="638"/>
       <c r="Q43" s="162"/>
-      <c r="R43" s="353" t="s">
-        <v>206</v>
-      </c>
-      <c r="S43" s="366"/>
-      <c r="T43" s="363" t="s">
-        <v>209</v>
-      </c>
-      <c r="U43" s="354"/>
-      <c r="V43" s="354"/>
-      <c r="W43" s="354"/>
-      <c r="X43" s="367"/>
-      <c r="Y43" s="360"/>
-      <c r="Z43" s="356"/>
-      <c r="AA43" s="361"/>
+      <c r="R43" s="348" t="s">
+        <v>205</v>
+      </c>
+      <c r="S43" s="361"/>
+      <c r="T43" s="358" t="s">
+        <v>208</v>
+      </c>
+      <c r="U43" s="349"/>
+      <c r="V43" s="349"/>
+      <c r="W43" s="349"/>
+      <c r="X43" s="362"/>
+      <c r="Y43" s="355"/>
+      <c r="Z43" s="351"/>
+      <c r="AA43" s="356"/>
     </row>
     <row r="44" spans="1:27" ht="12" customHeight="1">
       <c r="A44" s="98"/>
@@ -29849,17 +29839,17 @@
       <c r="N44" s="98"/>
       <c r="O44" s="98"/>
       <c r="P44" s="193"/>
-      <c r="Q44" s="373"/>
-      <c r="R44" s="355"/>
-      <c r="S44" s="370"/>
-      <c r="T44" s="371"/>
-      <c r="U44" s="368"/>
-      <c r="V44" s="369"/>
-      <c r="W44" s="369"/>
-      <c r="X44" s="369"/>
-      <c r="Y44" s="375"/>
-      <c r="Z44" s="369"/>
-      <c r="AA44" s="370"/>
+      <c r="Q44" s="368"/>
+      <c r="R44" s="350"/>
+      <c r="S44" s="365"/>
+      <c r="T44" s="366"/>
+      <c r="U44" s="363"/>
+      <c r="V44" s="364"/>
+      <c r="W44" s="364"/>
+      <c r="X44" s="364"/>
+      <c r="Y44" s="370"/>
+      <c r="Z44" s="364"/>
+      <c r="AA44" s="365"/>
     </row>
     <row r="45" spans="1:27" ht="27" customHeight="1">
       <c r="A45" s="98"/>
@@ -29885,20 +29875,20 @@
       </c>
       <c r="P45" s="640"/>
       <c r="Q45" s="162"/>
-      <c r="R45" s="354" t="s">
-        <v>207</v>
-      </c>
-      <c r="S45" s="364"/>
-      <c r="T45" s="362" t="s">
-        <v>210</v>
-      </c>
-      <c r="U45" s="363"/>
-      <c r="V45" s="356"/>
-      <c r="W45" s="356"/>
-      <c r="X45" s="361"/>
-      <c r="Y45" s="374"/>
-      <c r="Z45" s="356"/>
-      <c r="AA45" s="361"/>
+      <c r="R45" s="349" t="s">
+        <v>206</v>
+      </c>
+      <c r="S45" s="359"/>
+      <c r="T45" s="357" t="s">
+        <v>209</v>
+      </c>
+      <c r="U45" s="358"/>
+      <c r="V45" s="351"/>
+      <c r="W45" s="351"/>
+      <c r="X45" s="356"/>
+      <c r="Y45" s="369"/>
+      <c r="Z45" s="351"/>
+      <c r="AA45" s="356"/>
     </row>
     <row r="46" spans="1:27" ht="17.25" customHeight="1">
       <c r="A46" s="98"/>
@@ -29918,16 +29908,16 @@
       <c r="O46" s="641"/>
       <c r="P46" s="642"/>
       <c r="Q46" s="162"/>
-      <c r="R46" s="355"/>
-      <c r="S46" s="370"/>
-      <c r="T46" s="371"/>
-      <c r="U46" s="368"/>
-      <c r="V46" s="369"/>
-      <c r="W46" s="369"/>
-      <c r="X46" s="369"/>
-      <c r="Y46" s="376"/>
-      <c r="Z46" s="369"/>
-      <c r="AA46" s="372"/>
+      <c r="R46" s="350"/>
+      <c r="S46" s="365"/>
+      <c r="T46" s="366"/>
+      <c r="U46" s="363"/>
+      <c r="V46" s="364"/>
+      <c r="W46" s="364"/>
+      <c r="X46" s="364"/>
+      <c r="Y46" s="371"/>
+      <c r="Z46" s="364"/>
+      <c r="AA46" s="367"/>
     </row>
     <row r="47" spans="1:27" ht="19.5" customHeight="1" thickBot="1">
       <c r="A47" s="98"/>
@@ -29946,20 +29936,20 @@
       <c r="N47" s="194"/>
       <c r="O47" s="194"/>
       <c r="P47" s="164"/>
-      <c r="R47" s="362" t="s">
-        <v>208</v>
-      </c>
-      <c r="S47" s="361"/>
-      <c r="T47" s="362" t="s">
-        <v>211</v>
-      </c>
-      <c r="U47" s="363"/>
-      <c r="V47" s="356"/>
-      <c r="W47" s="356"/>
-      <c r="X47" s="361"/>
-      <c r="Y47" s="377"/>
-      <c r="Z47" s="356"/>
-      <c r="AA47" s="365"/>
+      <c r="R47" s="357" t="s">
+        <v>207</v>
+      </c>
+      <c r="S47" s="356"/>
+      <c r="T47" s="357" t="s">
+        <v>210</v>
+      </c>
+      <c r="U47" s="358"/>
+      <c r="V47" s="351"/>
+      <c r="W47" s="351"/>
+      <c r="X47" s="356"/>
+      <c r="Y47" s="372"/>
+      <c r="Z47" s="351"/>
+      <c r="AA47" s="360"/>
     </row>
     <row r="48" spans="1:27" ht="18.75" customHeight="1">
       <c r="A48" s="98"/>
@@ -30217,8 +30207,8 @@
       <c r="U56" s="95"/>
       <c r="V56" s="98"/>
       <c r="W56" s="98"/>
-      <c r="X56" s="357"/>
-      <c r="Y56" s="358"/>
+      <c r="X56" s="352"/>
+      <c r="Y56" s="353"/>
       <c r="Z56" s="98"/>
       <c r="AA56" s="98"/>
       <c r="AB56" s="95"/>
@@ -30247,8 +30237,8 @@
       <c r="U57" s="95"/>
       <c r="V57" s="98"/>
       <c r="W57" s="98"/>
-      <c r="X57" s="359"/>
-      <c r="Y57" s="358"/>
+      <c r="X57" s="354"/>
+      <c r="Y57" s="353"/>
       <c r="Z57" s="98"/>
       <c r="AA57" s="98"/>
       <c r="AB57" s="95"/>
@@ -30277,8 +30267,8 @@
       <c r="U58" s="95"/>
       <c r="V58" s="98"/>
       <c r="W58" s="98"/>
-      <c r="X58" s="357"/>
-      <c r="Y58" s="358"/>
+      <c r="X58" s="352"/>
+      <c r="Y58" s="353"/>
       <c r="Z58" s="98"/>
       <c r="AA58" s="98"/>
       <c r="AB58" s="95"/>
@@ -30307,8 +30297,8 @@
       <c r="U59" s="95"/>
       <c r="V59" s="98"/>
       <c r="W59" s="98"/>
-      <c r="X59" s="359"/>
-      <c r="Y59" s="358"/>
+      <c r="X59" s="354"/>
+      <c r="Y59" s="353"/>
       <c r="Z59" s="98"/>
       <c r="AA59" s="98"/>
       <c r="AB59" s="95"/>
@@ -30433,8 +30423,8 @@
       <c r="P64" s="98"/>
       <c r="Q64" s="95"/>
       <c r="R64" s="95"/>
-      <c r="U64" s="357"/>
-      <c r="V64" s="358"/>
+      <c r="U64" s="352"/>
+      <c r="V64" s="353"/>
       <c r="W64" s="98"/>
       <c r="X64" s="98"/>
       <c r="Y64" s="95"/>
@@ -30459,8 +30449,8 @@
       <c r="P65" s="98"/>
       <c r="Q65" s="95"/>
       <c r="R65" s="95"/>
-      <c r="U65" s="359"/>
-      <c r="V65" s="358"/>
+      <c r="U65" s="354"/>
+      <c r="V65" s="353"/>
       <c r="W65" s="98"/>
       <c r="X65" s="98"/>
       <c r="Y65" s="95"/>
@@ -30485,8 +30475,8 @@
       <c r="P66" s="98"/>
       <c r="Q66" s="95"/>
       <c r="R66" s="95"/>
-      <c r="U66" s="357"/>
-      <c r="V66" s="358"/>
+      <c r="U66" s="352"/>
+      <c r="V66" s="353"/>
       <c r="W66" s="98"/>
       <c r="X66" s="98"/>
       <c r="Y66" s="95"/>
@@ -30513,8 +30503,8 @@
       <c r="R67" s="95"/>
       <c r="S67" s="98"/>
       <c r="T67" s="98"/>
-      <c r="U67" s="359"/>
-      <c r="V67" s="358"/>
+      <c r="U67" s="354"/>
+      <c r="V67" s="353"/>
       <c r="W67" s="98"/>
       <c r="X67" s="98"/>
       <c r="Y67" s="95"/>
@@ -31083,7 +31073,7 @@
   <sheetData>
     <row r="2" spans="1:6">
       <c r="B2" s="656" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C2" s="656"/>
       <c r="D2" s="656"/>
@@ -31092,7 +31082,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="B3" s="657" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C3" s="657"/>
       <c r="D3" s="657"/>
@@ -31101,19 +31091,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="B4" s="89" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="89" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="89" t="s">
+      <c r="D4" s="89" t="s">
         <v>166</v>
       </c>
-      <c r="D4" s="89" t="s">
+      <c r="E4" s="89" t="s">
         <v>167</v>
       </c>
-      <c r="E4" s="89" t="s">
+      <c r="F4" s="89" t="s">
         <v>168</v>
-      </c>
-      <c r="F4" s="89" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -31235,14 +31225,14 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75">
-      <c r="C14" s="266" t="s">
-        <v>170</v>
-      </c>
-      <c r="D14" s="266" t="s">
-        <v>164</v>
-      </c>
-      <c r="E14" s="267" t="s">
-        <v>146</v>
+      <c r="C14" s="264" t="s">
+        <v>169</v>
+      </c>
+      <c r="D14" s="264" t="s">
+        <v>163</v>
+      </c>
+      <c r="E14" s="265" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -31377,7 +31367,7 @@
         <v>72</v>
       </c>
       <c r="G26" s="654" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H26" s="655">
         <v>5</v>
@@ -31684,7 +31674,7 @@
       <c r="I70" s="655"/>
       <c r="J70" s="654"/>
       <c r="K70" s="654" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="71" spans="8:11">
@@ -31837,55 +31827,57 @@
   <sheetData>
     <row r="1" spans="1:21" ht="21">
       <c r="A1" s="98"/>
-      <c r="B1" s="658" t="s">
-        <v>177</v>
-      </c>
-      <c r="C1" s="659"/>
-      <c r="D1" s="659"/>
-      <c r="E1" s="659"/>
-      <c r="F1" s="659"/>
-      <c r="G1" s="659"/>
-      <c r="H1" s="659"/>
-      <c r="I1" s="659"/>
-      <c r="J1" s="659"/>
-      <c r="K1" s="659"/>
-      <c r="L1" s="659"/>
-      <c r="M1" s="659"/>
-      <c r="N1" s="659"/>
-      <c r="O1" s="659"/>
-      <c r="P1" s="660"/>
+      <c r="B1" s="662" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1" s="663"/>
+      <c r="D1" s="663"/>
+      <c r="E1" s="663"/>
+      <c r="F1" s="663"/>
+      <c r="G1" s="663"/>
+      <c r="H1" s="663"/>
+      <c r="I1" s="663"/>
+      <c r="J1" s="663"/>
+      <c r="K1" s="663"/>
+      <c r="L1" s="663"/>
+      <c r="M1" s="663"/>
+      <c r="N1" s="663"/>
+      <c r="O1" s="663"/>
+      <c r="P1" s="664"/>
       <c r="Q1" s="98"/>
       <c r="R1" s="98"/>
       <c r="S1" s="98"/>
       <c r="T1" s="98"/>
       <c r="U1" s="98"/>
     </row>
-    <row r="2" spans="1:21" ht="18" customHeight="1">
+    <row r="2" spans="1:21" ht="30.75" customHeight="1">
       <c r="A2" s="98"/>
-      <c r="B2" s="661" t="s">
-        <v>178</v>
-      </c>
-      <c r="C2" s="662"/>
-      <c r="D2" s="662"/>
-      <c r="E2" s="662"/>
-      <c r="F2" s="662"/>
-      <c r="G2" s="662"/>
-      <c r="H2" s="662"/>
-      <c r="I2" s="662"/>
-      <c r="J2" s="662"/>
-      <c r="K2" s="662"/>
-      <c r="L2" s="662"/>
-      <c r="M2" s="662"/>
-      <c r="N2" s="662"/>
-      <c r="O2" s="662"/>
-      <c r="P2" s="663"/>
+      <c r="B2" s="658" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="659"/>
+      <c r="D2" s="659"/>
+      <c r="E2" s="659"/>
+      <c r="F2" s="659"/>
+      <c r="G2" s="660" t="s">
+        <v>221</v>
+      </c>
+      <c r="H2" s="660"/>
+      <c r="I2" s="660"/>
+      <c r="J2" s="660"/>
+      <c r="K2" s="660"/>
+      <c r="L2" s="660"/>
+      <c r="M2" s="660"/>
+      <c r="N2" s="660"/>
+      <c r="O2" s="660"/>
+      <c r="P2" s="661"/>
       <c r="Q2" s="98"/>
       <c r="R2" s="98"/>
       <c r="S2" s="98"/>
       <c r="T2" s="98"/>
       <c r="U2" s="98"/>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1">
+    <row r="3" spans="1:21" ht="18.75" customHeight="1">
       <c r="A3" s="98"/>
       <c r="B3" s="245"/>
       <c r="C3" s="249"/>
@@ -31919,14 +31911,14 @@
       <c r="H4" s="96"/>
       <c r="I4" s="104"/>
       <c r="J4" s="251"/>
-      <c r="K4" s="676" t="s">
-        <v>218</v>
-      </c>
-      <c r="L4" s="676"/>
-      <c r="M4" s="676"/>
-      <c r="N4" s="676"/>
-      <c r="O4" s="676"/>
-      <c r="P4" s="676"/>
+      <c r="K4" s="677" t="s">
+        <v>217</v>
+      </c>
+      <c r="L4" s="677"/>
+      <c r="M4" s="677"/>
+      <c r="N4" s="677"/>
+      <c r="O4" s="677"/>
+      <c r="P4" s="677"/>
       <c r="Q4" s="98"/>
       <c r="R4" s="98"/>
       <c r="S4" s="98"/>
@@ -31939,18 +31931,18 @@
       <c r="H5" s="95"/>
       <c r="I5" s="98"/>
       <c r="J5" s="252"/>
-      <c r="K5" s="672" t="s">
-        <v>180</v>
-      </c>
-      <c r="L5" s="672"/>
-      <c r="M5" s="672" t="s">
+      <c r="K5" s="673" t="s">
+        <v>179</v>
+      </c>
+      <c r="L5" s="673"/>
+      <c r="M5" s="673" t="s">
+        <v>182</v>
+      </c>
+      <c r="N5" s="673"/>
+      <c r="O5" s="673" t="s">
         <v>183</v>
       </c>
-      <c r="N5" s="672"/>
-      <c r="O5" s="672" t="s">
-        <v>184</v>
-      </c>
-      <c r="P5" s="672"/>
+      <c r="P5" s="673"/>
       <c r="Q5" s="96"/>
       <c r="R5" s="98"/>
       <c r="S5" s="98"/>
@@ -31963,18 +31955,18 @@
       <c r="H6" s="95"/>
       <c r="I6" s="98"/>
       <c r="J6" s="95"/>
-      <c r="K6" s="687" t="s">
-        <v>195</v>
-      </c>
-      <c r="L6" s="668"/>
-      <c r="M6" s="667" t="s">
-        <v>408</v>
-      </c>
-      <c r="N6" s="668"/>
-      <c r="O6" s="667" t="s">
-        <v>157</v>
-      </c>
-      <c r="P6" s="673"/>
+      <c r="K6" s="688" t="s">
+        <v>194</v>
+      </c>
+      <c r="L6" s="669"/>
+      <c r="M6" s="668" t="s">
+        <v>407</v>
+      </c>
+      <c r="N6" s="669"/>
+      <c r="O6" s="668" t="s">
+        <v>156</v>
+      </c>
+      <c r="P6" s="674"/>
       <c r="Q6" s="96"/>
       <c r="R6" s="98"/>
       <c r="S6" s="98"/>
@@ -31985,24 +31977,24 @@
       <c r="A7" s="98"/>
       <c r="C7" s="98"/>
       <c r="D7" s="98"/>
-      <c r="E7" s="674"/>
-      <c r="F7" s="675"/>
-      <c r="G7" s="675"/>
-      <c r="H7" s="675"/>
+      <c r="E7" s="675"/>
+      <c r="F7" s="676"/>
+      <c r="G7" s="676"/>
+      <c r="H7" s="676"/>
       <c r="I7" s="98"/>
       <c r="J7" s="119"/>
-      <c r="K7" s="677" t="s">
-        <v>195</v>
-      </c>
-      <c r="L7" s="670"/>
-      <c r="M7" s="669" t="s">
-        <v>409</v>
-      </c>
-      <c r="N7" s="670"/>
-      <c r="O7" s="669" t="s">
-        <v>157</v>
-      </c>
-      <c r="P7" s="671"/>
+      <c r="K7" s="678" t="s">
+        <v>194</v>
+      </c>
+      <c r="L7" s="671"/>
+      <c r="M7" s="670" t="s">
+        <v>408</v>
+      </c>
+      <c r="N7" s="671"/>
+      <c r="O7" s="670" t="s">
+        <v>156</v>
+      </c>
+      <c r="P7" s="672"/>
       <c r="Q7" s="96"/>
       <c r="R7" s="98"/>
       <c r="S7" s="98"/>
@@ -32016,18 +32008,18 @@
       <c r="D8" s="98"/>
       <c r="I8" s="98"/>
       <c r="J8" s="95"/>
-      <c r="K8" s="677" t="s">
-        <v>194</v>
-      </c>
-      <c r="L8" s="670"/>
-      <c r="M8" s="669" t="s">
-        <v>410</v>
-      </c>
-      <c r="N8" s="670"/>
-      <c r="O8" s="669" t="s">
-        <v>157</v>
-      </c>
-      <c r="P8" s="671"/>
+      <c r="K8" s="678" t="s">
+        <v>193</v>
+      </c>
+      <c r="L8" s="671"/>
+      <c r="M8" s="670" t="s">
+        <v>409</v>
+      </c>
+      <c r="N8" s="671"/>
+      <c r="O8" s="670" t="s">
+        <v>156</v>
+      </c>
+      <c r="P8" s="672"/>
       <c r="Q8" s="96"/>
       <c r="R8" s="98"/>
       <c r="S8" s="98"/>
@@ -32041,18 +32033,18 @@
       <c r="D9" s="98"/>
       <c r="I9" s="98"/>
       <c r="J9" s="119"/>
-      <c r="K9" s="677" t="s">
-        <v>194</v>
-      </c>
-      <c r="L9" s="670"/>
-      <c r="M9" s="669" t="s">
-        <v>411</v>
-      </c>
-      <c r="N9" s="670"/>
-      <c r="O9" s="669" t="s">
-        <v>157</v>
-      </c>
-      <c r="P9" s="671"/>
+      <c r="K9" s="678" t="s">
+        <v>193</v>
+      </c>
+      <c r="L9" s="671"/>
+      <c r="M9" s="670" t="s">
+        <v>410</v>
+      </c>
+      <c r="N9" s="671"/>
+      <c r="O9" s="670" t="s">
+        <v>156</v>
+      </c>
+      <c r="P9" s="672"/>
       <c r="Q9" s="96"/>
       <c r="R9" s="98"/>
       <c r="S9" s="98"/>
@@ -32066,18 +32058,18 @@
       <c r="D10" s="98"/>
       <c r="I10" s="98"/>
       <c r="J10" s="95"/>
-      <c r="K10" s="677" t="s">
-        <v>194</v>
-      </c>
-      <c r="L10" s="670"/>
-      <c r="M10" s="669" t="s">
-        <v>412</v>
-      </c>
-      <c r="N10" s="670"/>
-      <c r="O10" s="669" t="s">
-        <v>157</v>
-      </c>
-      <c r="P10" s="671"/>
+      <c r="K10" s="678" t="s">
+        <v>193</v>
+      </c>
+      <c r="L10" s="671"/>
+      <c r="M10" s="670" t="s">
+        <v>411</v>
+      </c>
+      <c r="N10" s="671"/>
+      <c r="O10" s="670" t="s">
+        <v>156</v>
+      </c>
+      <c r="P10" s="672"/>
       <c r="Q10" s="96"/>
       <c r="R10" s="98"/>
       <c r="S10" s="98"/>
@@ -32089,26 +32081,26 @@
       <c r="B11" s="98"/>
       <c r="C11" s="98"/>
       <c r="D11" s="95"/>
-      <c r="E11" s="664" t="s">
-        <v>182</v>
-      </c>
-      <c r="F11" s="665"/>
-      <c r="G11" s="665"/>
-      <c r="H11" s="666"/>
+      <c r="E11" s="665" t="s">
+        <v>181</v>
+      </c>
+      <c r="F11" s="666"/>
+      <c r="G11" s="666"/>
+      <c r="H11" s="667"/>
       <c r="I11" s="96"/>
       <c r="J11" s="119"/>
-      <c r="K11" s="677" t="s">
-        <v>406</v>
-      </c>
-      <c r="L11" s="670"/>
-      <c r="M11" s="669" t="s">
-        <v>413</v>
-      </c>
-      <c r="N11" s="670"/>
-      <c r="O11" s="669" t="s">
-        <v>157</v>
-      </c>
-      <c r="P11" s="671"/>
+      <c r="K11" s="678" t="s">
+        <v>405</v>
+      </c>
+      <c r="L11" s="671"/>
+      <c r="M11" s="670" t="s">
+        <v>412</v>
+      </c>
+      <c r="N11" s="671"/>
+      <c r="O11" s="670" t="s">
+        <v>156</v>
+      </c>
+      <c r="P11" s="672"/>
       <c r="Q11" s="96"/>
       <c r="R11" s="98"/>
       <c r="S11" s="98"/>
@@ -32120,28 +32112,28 @@
       <c r="B12" s="98"/>
       <c r="C12" s="98"/>
       <c r="D12" s="95"/>
-      <c r="E12" s="678" t="s">
+      <c r="E12" s="679" t="s">
+        <v>179</v>
+      </c>
+      <c r="F12" s="680"/>
+      <c r="G12" s="681"/>
+      <c r="H12" s="453" t="s">
         <v>180</v>
-      </c>
-      <c r="F12" s="679"/>
-      <c r="G12" s="680"/>
-      <c r="H12" s="261" t="s">
-        <v>181</v>
       </c>
       <c r="I12" s="96"/>
       <c r="J12" s="119"/>
-      <c r="K12" s="677" t="s">
-        <v>406</v>
-      </c>
-      <c r="L12" s="670"/>
-      <c r="M12" s="669" t="s">
-        <v>414</v>
-      </c>
-      <c r="N12" s="670"/>
-      <c r="O12" s="669" t="s">
-        <v>421</v>
-      </c>
-      <c r="P12" s="671"/>
+      <c r="K12" s="678" t="s">
+        <v>405</v>
+      </c>
+      <c r="L12" s="671"/>
+      <c r="M12" s="670" t="s">
+        <v>413</v>
+      </c>
+      <c r="N12" s="671"/>
+      <c r="O12" s="670" t="s">
+        <v>420</v>
+      </c>
+      <c r="P12" s="672"/>
       <c r="Q12" s="96"/>
       <c r="R12" s="98"/>
       <c r="S12" s="98"/>
@@ -32153,28 +32145,28 @@
       <c r="B13" s="98"/>
       <c r="C13" s="98"/>
       <c r="D13" s="95"/>
-      <c r="E13" s="681" t="s">
-        <v>197</v>
-      </c>
-      <c r="F13" s="682"/>
-      <c r="G13" s="683"/>
-      <c r="H13" s="316">
+      <c r="E13" s="682" t="s">
+        <v>196</v>
+      </c>
+      <c r="F13" s="683"/>
+      <c r="G13" s="684"/>
+      <c r="H13" s="311">
         <v>2</v>
       </c>
       <c r="I13" s="96"/>
       <c r="J13" s="95"/>
-      <c r="K13" s="677" t="s">
-        <v>407</v>
-      </c>
-      <c r="L13" s="670"/>
-      <c r="M13" s="669" t="s">
-        <v>415</v>
-      </c>
-      <c r="N13" s="670"/>
-      <c r="O13" s="669" t="s">
-        <v>157</v>
-      </c>
-      <c r="P13" s="671"/>
+      <c r="K13" s="678" t="s">
+        <v>406</v>
+      </c>
+      <c r="L13" s="671"/>
+      <c r="M13" s="670" t="s">
+        <v>414</v>
+      </c>
+      <c r="N13" s="671"/>
+      <c r="O13" s="670" t="s">
+        <v>156</v>
+      </c>
+      <c r="P13" s="672"/>
       <c r="Q13" s="96"/>
       <c r="R13" s="98"/>
       <c r="S13" s="98"/>
@@ -32186,28 +32178,28 @@
       <c r="B14" s="98"/>
       <c r="C14" s="98"/>
       <c r="D14" s="95"/>
-      <c r="E14" s="684" t="s">
-        <v>195</v>
-      </c>
-      <c r="F14" s="685"/>
-      <c r="G14" s="686"/>
-      <c r="H14" s="317">
+      <c r="E14" s="685" t="s">
+        <v>194</v>
+      </c>
+      <c r="F14" s="686"/>
+      <c r="G14" s="687"/>
+      <c r="H14" s="312">
         <v>26</v>
       </c>
       <c r="I14" s="96"/>
       <c r="J14" s="103"/>
-      <c r="K14" s="677" t="s">
-        <v>407</v>
-      </c>
-      <c r="L14" s="670"/>
-      <c r="M14" s="669" t="s">
-        <v>416</v>
-      </c>
-      <c r="N14" s="670"/>
-      <c r="O14" s="669" t="s">
-        <v>157</v>
-      </c>
-      <c r="P14" s="671"/>
+      <c r="K14" s="678" t="s">
+        <v>406</v>
+      </c>
+      <c r="L14" s="671"/>
+      <c r="M14" s="670" t="s">
+        <v>415</v>
+      </c>
+      <c r="N14" s="671"/>
+      <c r="O14" s="670" t="s">
+        <v>156</v>
+      </c>
+      <c r="P14" s="672"/>
       <c r="Q14" s="96"/>
       <c r="R14" s="98"/>
       <c r="S14" s="98"/>
@@ -32219,28 +32211,28 @@
       <c r="B15" s="98"/>
       <c r="C15" s="98"/>
       <c r="D15" s="95"/>
-      <c r="E15" s="684" t="s">
-        <v>196</v>
-      </c>
-      <c r="F15" s="685"/>
-      <c r="G15" s="686"/>
-      <c r="H15" s="317">
+      <c r="E15" s="685" t="s">
+        <v>195</v>
+      </c>
+      <c r="F15" s="686"/>
+      <c r="G15" s="687"/>
+      <c r="H15" s="312">
         <v>5</v>
       </c>
       <c r="I15" s="96"/>
       <c r="J15" s="95"/>
-      <c r="K15" s="677" t="s">
-        <v>194</v>
-      </c>
-      <c r="L15" s="670"/>
-      <c r="M15" s="669" t="s">
-        <v>417</v>
-      </c>
-      <c r="N15" s="670"/>
-      <c r="O15" s="669" t="s">
-        <v>157</v>
-      </c>
-      <c r="P15" s="671"/>
+      <c r="K15" s="678" t="s">
+        <v>193</v>
+      </c>
+      <c r="L15" s="671"/>
+      <c r="M15" s="670" t="s">
+        <v>416</v>
+      </c>
+      <c r="N15" s="671"/>
+      <c r="O15" s="670" t="s">
+        <v>156</v>
+      </c>
+      <c r="P15" s="672"/>
       <c r="Q15" s="96"/>
       <c r="R15" s="98"/>
       <c r="S15" s="98"/>
@@ -32252,28 +32244,28 @@
       <c r="B16" s="98"/>
       <c r="C16" s="98"/>
       <c r="D16" s="95"/>
-      <c r="E16" s="684" t="s">
-        <v>198</v>
-      </c>
-      <c r="F16" s="685"/>
-      <c r="G16" s="686"/>
-      <c r="H16" s="317">
+      <c r="E16" s="685" t="s">
+        <v>197</v>
+      </c>
+      <c r="F16" s="686"/>
+      <c r="G16" s="687"/>
+      <c r="H16" s="312">
         <v>29</v>
       </c>
       <c r="I16" s="96"/>
       <c r="J16" s="119"/>
-      <c r="K16" s="677" t="s">
-        <v>194</v>
-      </c>
-      <c r="L16" s="670"/>
-      <c r="M16" s="669" t="s">
-        <v>418</v>
-      </c>
-      <c r="N16" s="670"/>
-      <c r="O16" s="669" t="s">
-        <v>157</v>
-      </c>
-      <c r="P16" s="671"/>
+      <c r="K16" s="678" t="s">
+        <v>193</v>
+      </c>
+      <c r="L16" s="671"/>
+      <c r="M16" s="670" t="s">
+        <v>417</v>
+      </c>
+      <c r="N16" s="671"/>
+      <c r="O16" s="670" t="s">
+        <v>156</v>
+      </c>
+      <c r="P16" s="672"/>
       <c r="Q16" s="96"/>
       <c r="R16" s="98"/>
       <c r="S16" s="98"/>
@@ -32283,28 +32275,28 @@
     <row r="17" spans="1:21" ht="66" customHeight="1">
       <c r="A17" s="95"/>
       <c r="D17" s="114"/>
-      <c r="E17" s="684" t="s">
-        <v>199</v>
-      </c>
-      <c r="F17" s="685"/>
-      <c r="G17" s="686"/>
-      <c r="H17" s="317">
+      <c r="E17" s="685" t="s">
+        <v>198</v>
+      </c>
+      <c r="F17" s="686"/>
+      <c r="G17" s="687"/>
+      <c r="H17" s="312">
         <v>6</v>
       </c>
       <c r="I17" s="96"/>
       <c r="J17" s="119"/>
-      <c r="K17" s="677" t="s">
-        <v>196</v>
-      </c>
-      <c r="L17" s="670"/>
-      <c r="M17" s="669" t="s">
-        <v>419</v>
-      </c>
-      <c r="N17" s="670"/>
-      <c r="O17" s="669" t="s">
-        <v>421</v>
-      </c>
-      <c r="P17" s="671"/>
+      <c r="K17" s="678" t="s">
+        <v>195</v>
+      </c>
+      <c r="L17" s="671"/>
+      <c r="M17" s="670" t="s">
+        <v>418</v>
+      </c>
+      <c r="N17" s="671"/>
+      <c r="O17" s="670" t="s">
+        <v>420</v>
+      </c>
+      <c r="P17" s="672"/>
       <c r="Q17" s="96"/>
       <c r="R17" s="98"/>
       <c r="S17" s="98"/>
@@ -32315,28 +32307,28 @@
       <c r="A18" s="95"/>
       <c r="C18" s="123"/>
       <c r="D18" s="95"/>
-      <c r="E18" s="696" t="s">
-        <v>200</v>
-      </c>
-      <c r="F18" s="697"/>
-      <c r="G18" s="698"/>
-      <c r="H18" s="318">
+      <c r="E18" s="697" t="s">
+        <v>199</v>
+      </c>
+      <c r="F18" s="698"/>
+      <c r="G18" s="699"/>
+      <c r="H18" s="313">
         <v>25</v>
       </c>
       <c r="I18" s="96"/>
       <c r="J18" s="95"/>
-      <c r="K18" s="704" t="s">
-        <v>196</v>
-      </c>
-      <c r="L18" s="703"/>
-      <c r="M18" s="688" t="s">
+      <c r="K18" s="705" t="s">
+        <v>195</v>
+      </c>
+      <c r="L18" s="704"/>
+      <c r="M18" s="689" t="s">
+        <v>419</v>
+      </c>
+      <c r="N18" s="704"/>
+      <c r="O18" s="689" t="s">
         <v>420</v>
       </c>
-      <c r="N18" s="703"/>
-      <c r="O18" s="688" t="s">
-        <v>421</v>
-      </c>
-      <c r="P18" s="689"/>
+      <c r="P18" s="690"/>
       <c r="Q18" s="96"/>
       <c r="R18" s="98"/>
       <c r="S18" s="95"/>
@@ -32348,17 +32340,17 @@
       <c r="B19" s="99"/>
       <c r="C19" s="119"/>
       <c r="D19" s="106"/>
-      <c r="E19" s="262"/>
+      <c r="E19" s="260"/>
       <c r="F19" s="244"/>
       <c r="G19" s="244"/>
       <c r="H19" s="244"/>
       <c r="I19" s="106"/>
       <c r="J19" s="95"/>
-      <c r="K19" s="283"/>
+      <c r="K19" s="281"/>
       <c r="L19" s="103"/>
       <c r="M19" s="125"/>
       <c r="O19" s="123"/>
-      <c r="P19" s="308"/>
+      <c r="P19" s="303"/>
       <c r="Q19" s="96"/>
       <c r="R19" s="98"/>
       <c r="S19" s="95"/>
@@ -32367,11 +32359,11 @@
     </row>
     <row r="20" spans="1:21" ht="56.25" customHeight="1" thickBot="1">
       <c r="A20" s="95"/>
-      <c r="B20" s="305" t="s">
-        <v>179</v>
-      </c>
-      <c r="C20" s="255" t="s">
-        <v>213</v>
+      <c r="B20" s="454" t="s">
+        <v>178</v>
+      </c>
+      <c r="C20" s="455" t="s">
+        <v>212</v>
       </c>
       <c r="D20" s="254"/>
       <c r="E20" s="106"/>
@@ -32380,8 +32372,8 @@
       <c r="H20" s="106"/>
       <c r="I20" s="106"/>
       <c r="J20" s="103"/>
-      <c r="K20" s="309"/>
-      <c r="L20" s="302"/>
+      <c r="K20" s="304"/>
+      <c r="L20" s="300"/>
       <c r="M20" s="98"/>
       <c r="N20" s="98"/>
       <c r="O20" s="96"/>
@@ -32393,17 +32385,17 @@
     </row>
     <row r="21" spans="1:21" ht="3.75" customHeight="1" thickBot="1">
       <c r="A21" s="95"/>
-      <c r="B21" s="306"/>
-      <c r="C21" s="303"/>
-      <c r="D21" s="284"/>
-      <c r="E21" s="282"/>
-      <c r="F21" s="294"/>
-      <c r="G21" s="291"/>
-      <c r="H21" s="282"/>
-      <c r="I21" s="288"/>
-      <c r="J21" s="300"/>
-      <c r="K21" s="310"/>
-      <c r="L21" s="289"/>
+      <c r="B21" s="456"/>
+      <c r="C21" s="457"/>
+      <c r="D21" s="282"/>
+      <c r="E21" s="280"/>
+      <c r="F21" s="292"/>
+      <c r="G21" s="289"/>
+      <c r="H21" s="280"/>
+      <c r="I21" s="286"/>
+      <c r="J21" s="298"/>
+      <c r="K21" s="305"/>
+      <c r="L21" s="287"/>
       <c r="M21" s="95"/>
       <c r="N21" s="98"/>
       <c r="O21" s="96"/>
@@ -32415,25 +32407,25 @@
     </row>
     <row r="22" spans="1:21" ht="35.25" customHeight="1" thickBot="1">
       <c r="A22" s="95"/>
-      <c r="B22" s="304" t="s">
-        <v>197</v>
-      </c>
-      <c r="C22" s="307">
+      <c r="B22" s="301" t="s">
+        <v>196</v>
+      </c>
+      <c r="C22" s="302">
         <v>2</v>
       </c>
-      <c r="D22" s="284"/>
-      <c r="E22" s="293"/>
-      <c r="F22" s="315" t="s">
-        <v>182</v>
-      </c>
-      <c r="G22" s="292"/>
-      <c r="H22" s="699" t="s">
-        <v>185</v>
-      </c>
-      <c r="I22" s="700"/>
-      <c r="J22" s="301"/>
-      <c r="K22" s="311"/>
-      <c r="L22" s="289"/>
+      <c r="D22" s="282"/>
+      <c r="E22" s="291"/>
+      <c r="F22" s="310" t="s">
+        <v>181</v>
+      </c>
+      <c r="G22" s="290"/>
+      <c r="H22" s="700" t="s">
+        <v>184</v>
+      </c>
+      <c r="I22" s="701"/>
+      <c r="J22" s="299"/>
+      <c r="K22" s="306"/>
+      <c r="L22" s="287"/>
       <c r="M22" s="123"/>
       <c r="N22" s="98"/>
       <c r="O22" s="96"/>
@@ -32445,29 +32437,29 @@
     </row>
     <row r="23" spans="1:21" ht="35.25" customHeight="1" thickBot="1">
       <c r="A23" s="95"/>
-      <c r="B23" s="257" t="s">
-        <v>195</v>
-      </c>
-      <c r="C23" s="258">
+      <c r="B23" s="256" t="s">
+        <v>194</v>
+      </c>
+      <c r="C23" s="257">
         <v>26</v>
       </c>
-      <c r="D23" s="284"/>
-      <c r="E23" s="286"/>
-      <c r="F23" s="295">
+      <c r="D23" s="282"/>
+      <c r="E23" s="284"/>
+      <c r="F23" s="293">
         <f>SUM(H13:H18)</f>
         <v>93</v>
       </c>
-      <c r="G23" s="285"/>
-      <c r="H23" s="296">
+      <c r="G23" s="283"/>
+      <c r="H23" s="294">
         <f>SUM(C22:C27)</f>
         <v>93</v>
       </c>
-      <c r="I23" s="287"/>
-      <c r="J23" s="301"/>
-      <c r="K23" s="312"/>
-      <c r="L23" s="290"/>
-      <c r="M23" s="313"/>
-      <c r="N23" s="313"/>
+      <c r="I23" s="285"/>
+      <c r="J23" s="299"/>
+      <c r="K23" s="307"/>
+      <c r="L23" s="288"/>
+      <c r="M23" s="308"/>
+      <c r="N23" s="308"/>
       <c r="O23" s="96"/>
       <c r="P23" s="193"/>
       <c r="Q23" s="96"/>
@@ -32477,10 +32469,10 @@
     </row>
     <row r="24" spans="1:21" ht="35.25" customHeight="1" thickBot="1">
       <c r="A24" s="95"/>
-      <c r="B24" s="259" t="s">
-        <v>196</v>
-      </c>
-      <c r="C24" s="260">
+      <c r="B24" s="258" t="s">
+        <v>195</v>
+      </c>
+      <c r="C24" s="259">
         <v>5</v>
       </c>
       <c r="D24" s="254"/>
@@ -32490,12 +32482,12 @@
       <c r="H24" s="123"/>
       <c r="I24" s="123"/>
       <c r="J24" s="97"/>
-      <c r="K24" s="283"/>
+      <c r="K24" s="281"/>
       <c r="L24" s="143"/>
       <c r="M24" s="144"/>
       <c r="N24" s="142"/>
       <c r="O24" s="99"/>
-      <c r="P24" s="392"/>
+      <c r="P24" s="387"/>
       <c r="Q24" s="96"/>
       <c r="R24" s="98"/>
       <c r="T24" s="98"/>
@@ -32503,26 +32495,26 @@
     </row>
     <row r="25" spans="1:21" ht="33" customHeight="1" thickBot="1">
       <c r="A25" s="95"/>
-      <c r="B25" s="259" t="s">
-        <v>198</v>
-      </c>
-      <c r="C25" s="260">
+      <c r="B25" s="258" t="s">
+        <v>197</v>
+      </c>
+      <c r="C25" s="259">
         <v>29</v>
       </c>
-      <c r="D25" s="284"/>
+      <c r="D25" s="282"/>
       <c r="E25" s="194"/>
       <c r="F25" s="194"/>
       <c r="G25" s="106"/>
       <c r="I25" s="174"/>
       <c r="J25" s="95"/>
-      <c r="K25" s="395" t="s">
-        <v>215</v>
+      <c r="K25" s="390" t="s">
+        <v>214</v>
       </c>
       <c r="L25" s="192"/>
-      <c r="M25" s="394"/>
-      <c r="N25" s="397"/>
-      <c r="O25" s="396"/>
-      <c r="P25" s="288"/>
+      <c r="M25" s="389"/>
+      <c r="N25" s="392"/>
+      <c r="O25" s="391"/>
+      <c r="P25" s="286"/>
       <c r="Q25" s="96"/>
       <c r="R25" s="98"/>
       <c r="T25" s="98"/>
@@ -32530,28 +32522,28 @@
     </row>
     <row r="26" spans="1:21" ht="44.25" customHeight="1">
       <c r="A26" s="95"/>
-      <c r="B26" s="259" t="s">
-        <v>199</v>
-      </c>
-      <c r="C26" s="260">
+      <c r="B26" s="258" t="s">
+        <v>198</v>
+      </c>
+      <c r="C26" s="259">
         <v>6</v>
       </c>
-      <c r="D26" s="284"/>
-      <c r="E26" s="298"/>
-      <c r="F26" s="314" t="s">
-        <v>186</v>
-      </c>
-      <c r="H26" s="701" t="s">
-        <v>214</v>
-      </c>
-      <c r="I26" s="702"/>
-      <c r="J26" s="393"/>
-      <c r="K26" s="690" t="s">
-        <v>217</v>
-      </c>
-      <c r="L26" s="691"/>
-      <c r="M26" s="691"/>
-      <c r="N26" s="692"/>
+      <c r="D26" s="282"/>
+      <c r="E26" s="296"/>
+      <c r="F26" s="309" t="s">
+        <v>185</v>
+      </c>
+      <c r="H26" s="702" t="s">
+        <v>213</v>
+      </c>
+      <c r="I26" s="703"/>
+      <c r="J26" s="388"/>
+      <c r="K26" s="691" t="s">
+        <v>216</v>
+      </c>
+      <c r="L26" s="692"/>
+      <c r="M26" s="692"/>
+      <c r="N26" s="693"/>
       <c r="O26" s="96"/>
       <c r="P26" s="193"/>
       <c r="Q26" s="96"/>
@@ -32561,30 +32553,30 @@
     </row>
     <row r="27" spans="1:21" ht="36.75" customHeight="1" thickBot="1">
       <c r="A27" s="95"/>
-      <c r="B27" s="263" t="s">
-        <v>200</v>
-      </c>
-      <c r="C27" s="264">
+      <c r="B27" s="261" t="s">
+        <v>199</v>
+      </c>
+      <c r="C27" s="262">
         <v>25</v>
       </c>
       <c r="D27" s="254"/>
-      <c r="E27" s="297"/>
-      <c r="F27" s="299">
+      <c r="E27" s="295"/>
+      <c r="F27" s="297">
         <v>45657</v>
       </c>
       <c r="G27" s="94"/>
-      <c r="H27" s="265">
+      <c r="H27" s="263">
         <f>COUNTA(O6:P27)</f>
         <v>13</v>
       </c>
-      <c r="I27" s="256"/>
+      <c r="I27" s="255"/>
       <c r="J27" s="253"/>
-      <c r="K27" s="693" t="s">
-        <v>216</v>
-      </c>
-      <c r="L27" s="694"/>
-      <c r="M27" s="694"/>
-      <c r="N27" s="695"/>
+      <c r="K27" s="694" t="s">
+        <v>215</v>
+      </c>
+      <c r="L27" s="695"/>
+      <c r="M27" s="695"/>
+      <c r="N27" s="696"/>
       <c r="O27" s="194"/>
       <c r="P27" s="164"/>
       <c r="Q27" s="96"/>
@@ -32606,7 +32598,7 @@
       <c r="K28" s="143"/>
       <c r="L28" s="125"/>
       <c r="M28" s="125"/>
-      <c r="N28" s="320"/>
+      <c r="N28" s="315"/>
       <c r="O28" s="104"/>
       <c r="P28" s="123"/>
       <c r="Q28" s="98"/>
@@ -33030,7 +33022,7 @@
       <c r="U46" s="98"/>
     </row>
   </sheetData>
-  <mergeCells count="58">
+  <mergeCells count="59">
     <mergeCell ref="K26:N26"/>
     <mergeCell ref="K27:N27"/>
     <mergeCell ref="E17:G17"/>
@@ -33042,6 +33034,7 @@
     <mergeCell ref="M18:N18"/>
     <mergeCell ref="K17:L17"/>
     <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K15:L15"/>
     <mergeCell ref="O18:P18"/>
     <mergeCell ref="O17:P17"/>
     <mergeCell ref="O16:P16"/>
@@ -33057,6 +33050,7 @@
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M11:N11"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="K4:P4"/>
     <mergeCell ref="M15:N15"/>
@@ -33072,9 +33066,9 @@
     <mergeCell ref="K12:L12"/>
     <mergeCell ref="K13:L13"/>
     <mergeCell ref="K14:L14"/>
-    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:P2"/>
     <mergeCell ref="B1:P1"/>
-    <mergeCell ref="B2:P2"/>
     <mergeCell ref="E11:H11"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="M7:N7"/>
@@ -33088,7 +33082,6 @@
     <mergeCell ref="O8:P8"/>
     <mergeCell ref="O9:P9"/>
     <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -33111,184 +33104,184 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:4" ht="18.75">
-      <c r="A2" s="319" t="s">
+      <c r="A2" s="314" t="s">
+        <v>186</v>
+      </c>
+      <c r="B2" s="314" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="319" t="s">
+      <c r="C2" s="314" t="s">
         <v>188</v>
       </c>
-      <c r="C2" s="319" t="s">
+      <c r="D2" s="314" t="s">
         <v>189</v>
       </c>
-      <c r="D2" s="319" t="s">
-        <v>190</v>
-      </c>
     </row>
     <row r="3" spans="1:4" ht="58.5" customHeight="1">
-      <c r="A3" s="455">
+      <c r="A3" s="450">
         <v>45646</v>
       </c>
-      <c r="B3" s="451" t="s">
+      <c r="B3" s="446" t="s">
+        <v>421</v>
+      </c>
+      <c r="C3" s="452">
+        <v>2</v>
+      </c>
+      <c r="D3" s="452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="68.25" customHeight="1">
+      <c r="A4" s="451">
+        <v>45294</v>
+      </c>
+      <c r="B4" s="447" t="s">
         <v>422</v>
       </c>
-      <c r="C3" s="457">
+      <c r="C4" s="452">
+        <v>-1</v>
+      </c>
+      <c r="D4" s="452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="47.25" customHeight="1">
+      <c r="A5" s="451">
+        <v>45317</v>
+      </c>
+      <c r="B5" s="446" t="s">
+        <v>423</v>
+      </c>
+      <c r="C5" s="452">
+        <v>1.5</v>
+      </c>
+      <c r="D5" s="452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="45" customHeight="1">
+      <c r="A6" s="451">
+        <v>45677</v>
+      </c>
+      <c r="B6" s="447" t="s">
+        <v>424</v>
+      </c>
+      <c r="C6" s="452">
+        <v>-1</v>
+      </c>
+      <c r="D6" s="452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="66" customHeight="1">
+      <c r="A7" s="451">
+        <v>45748</v>
+      </c>
+      <c r="B7" s="446" t="s">
+        <v>425</v>
+      </c>
+      <c r="C7" s="452">
+        <v>1</v>
+      </c>
+      <c r="D7" s="452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="48.75" customHeight="1">
+      <c r="A8" s="451">
+        <v>45796</v>
+      </c>
+      <c r="B8" s="447" t="s">
+        <v>426</v>
+      </c>
+      <c r="C8" s="452">
         <v>2</v>
       </c>
-      <c r="D3" s="457">
+      <c r="D8" s="452">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="68.25" customHeight="1">
-      <c r="A4" s="456">
-        <v>45294</v>
-      </c>
-      <c r="B4" s="452" t="s">
-        <v>423</v>
-      </c>
-      <c r="C4" s="457">
+    <row r="9" spans="1:4" ht="52.5" customHeight="1">
+      <c r="A9" s="451">
+        <v>45432</v>
+      </c>
+      <c r="B9" s="446" t="s">
+        <v>427</v>
+      </c>
+      <c r="C9" s="452">
+        <v>1</v>
+      </c>
+      <c r="D9" s="452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="32.25" customHeight="1">
+      <c r="A10" s="451">
+        <v>45435</v>
+      </c>
+      <c r="B10" s="447" t="s">
+        <v>428</v>
+      </c>
+      <c r="C10" s="452">
         <v>-1</v>
       </c>
-      <c r="D4" s="457">
+      <c r="D10" s="452">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="47.25" customHeight="1">
-      <c r="A5" s="456">
-        <v>45317</v>
-      </c>
-      <c r="B5" s="451" t="s">
-        <v>424</v>
-      </c>
-      <c r="C5" s="457">
-        <v>1.5</v>
-      </c>
-      <c r="D5" s="457">
+    <row r="11" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A11" s="451">
+        <v>45442</v>
+      </c>
+      <c r="B11" s="446" t="s">
+        <v>429</v>
+      </c>
+      <c r="C11" s="452">
+        <v>-1</v>
+      </c>
+      <c r="D11" s="452">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="45" customHeight="1">
-      <c r="A6" s="456">
-        <v>45677</v>
-      </c>
-      <c r="B6" s="452" t="s">
-        <v>425</v>
-      </c>
-      <c r="C6" s="457">
+    <row r="12" spans="1:4">
+      <c r="A12" s="451">
+        <v>45449</v>
+      </c>
+      <c r="B12" s="448" t="s">
+        <v>430</v>
+      </c>
+      <c r="C12" s="452">
         <v>-1</v>
       </c>
-      <c r="D6" s="457">
+      <c r="D12" s="452">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="66" customHeight="1">
-      <c r="A7" s="456">
-        <v>45748</v>
-      </c>
-      <c r="B7" s="451" t="s">
-        <v>426</v>
-      </c>
-      <c r="C7" s="457">
+    <row r="13" spans="1:4">
+      <c r="A13" s="451">
+        <v>45456</v>
+      </c>
+      <c r="B13" s="447" t="s">
+        <v>431</v>
+      </c>
+      <c r="C13" s="452">
+        <v>-1</v>
+      </c>
+      <c r="D13" s="452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="30">
+      <c r="A14" s="451">
+        <v>45463</v>
+      </c>
+      <c r="B14" s="449" t="s">
+        <v>432</v>
+      </c>
+      <c r="C14" s="452">
         <v>1</v>
       </c>
-      <c r="D7" s="457">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="48.75" customHeight="1">
-      <c r="A8" s="456">
-        <v>45796</v>
-      </c>
-      <c r="B8" s="452" t="s">
-        <v>427</v>
-      </c>
-      <c r="C8" s="457">
-        <v>2</v>
-      </c>
-      <c r="D8" s="457">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="52.5" customHeight="1">
-      <c r="A9" s="456">
-        <v>45432</v>
-      </c>
-      <c r="B9" s="451" t="s">
-        <v>428</v>
-      </c>
-      <c r="C9" s="457">
-        <v>1</v>
-      </c>
-      <c r="D9" s="457">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="32.25" customHeight="1">
-      <c r="A10" s="456">
-        <v>45435</v>
-      </c>
-      <c r="B10" s="452" t="s">
-        <v>429</v>
-      </c>
-      <c r="C10" s="457">
-        <v>-1</v>
-      </c>
-      <c r="D10" s="457">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A11" s="456">
-        <v>45442</v>
-      </c>
-      <c r="B11" s="451" t="s">
-        <v>430</v>
-      </c>
-      <c r="C11" s="457">
-        <v>-1</v>
-      </c>
-      <c r="D11" s="457">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="456">
-        <v>45449</v>
-      </c>
-      <c r="B12" s="453" t="s">
-        <v>431</v>
-      </c>
-      <c r="C12" s="457">
-        <v>-1</v>
-      </c>
-      <c r="D12" s="457">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="456">
-        <v>45456</v>
-      </c>
-      <c r="B13" s="452" t="s">
-        <v>432</v>
-      </c>
-      <c r="C13" s="457">
-        <v>-1</v>
-      </c>
-      <c r="D13" s="457">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="30">
-      <c r="A14" s="456">
-        <v>45463</v>
-      </c>
-      <c r="B14" s="454" t="s">
-        <v>433</v>
-      </c>
-      <c r="C14" s="457">
-        <v>1</v>
-      </c>
-      <c r="D14" s="457">
+      <c r="D14" s="452">
         <v>0</v>
       </c>
     </row>
@@ -33354,25 +33347,25 @@
     </row>
     <row r="2" spans="1:19" ht="37.35" customHeight="1">
       <c r="A2" s="29"/>
-      <c r="B2" s="321"/>
-      <c r="C2" s="321"/>
-      <c r="D2" s="321"/>
-      <c r="E2" s="321"/>
-      <c r="F2" s="321"/>
-      <c r="G2" s="321"/>
-      <c r="H2" s="321"/>
-      <c r="I2" s="321"/>
+      <c r="B2" s="316"/>
+      <c r="C2" s="316"/>
+      <c r="D2" s="316"/>
+      <c r="E2" s="316"/>
+      <c r="F2" s="316"/>
+      <c r="G2" s="316"/>
+      <c r="H2" s="316"/>
+      <c r="I2" s="316"/>
       <c r="J2" s="470" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K2" s="470"/>
       <c r="L2" s="470"/>
       <c r="M2" s="470"/>
       <c r="N2" s="470"/>
       <c r="O2" s="470"/>
-      <c r="P2" s="321"/>
-      <c r="Q2" s="321"/>
-      <c r="R2" s="321"/>
+      <c r="P2" s="316"/>
+      <c r="Q2" s="316"/>
+      <c r="R2" s="316"/>
       <c r="S2" s="28"/>
     </row>
     <row r="3" spans="1:19" ht="7.35" customHeight="1">
@@ -33398,20 +33391,20 @@
     </row>
     <row r="4" spans="1:19" ht="33" customHeight="1">
       <c r="A4" s="29"/>
-      <c r="B4" s="322" t="s">
+      <c r="B4" s="317" t="s">
+        <v>200</v>
+      </c>
+      <c r="C4" s="317"/>
+      <c r="D4" s="317"/>
+      <c r="E4" s="317"/>
+      <c r="F4" s="317"/>
+      <c r="G4" s="317"/>
+      <c r="H4" s="317"/>
+      <c r="I4" s="317" t="s">
         <v>201</v>
       </c>
-      <c r="C4" s="322"/>
-      <c r="D4" s="322"/>
-      <c r="E4" s="322"/>
-      <c r="F4" s="322"/>
-      <c r="G4" s="322"/>
-      <c r="H4" s="322"/>
-      <c r="I4" s="322" t="s">
+      <c r="J4" s="469" t="s">
         <v>202</v>
-      </c>
-      <c r="J4" s="469" t="s">
-        <v>203</v>
       </c>
       <c r="K4" s="469"/>
       <c r="L4" s="469"/>
@@ -33425,27 +33418,27 @@
     </row>
     <row r="5" spans="1:19" ht="29.25" customHeight="1">
       <c r="A5" s="29"/>
-      <c r="B5" s="323"/>
-      <c r="C5" s="323"/>
-      <c r="D5" s="323"/>
-      <c r="E5" s="323"/>
-      <c r="F5" s="323"/>
-      <c r="G5" s="323"/>
-      <c r="H5" s="323"/>
-      <c r="I5" s="325"/>
+      <c r="B5" s="318"/>
+      <c r="C5" s="318"/>
+      <c r="D5" s="318"/>
+      <c r="E5" s="318"/>
+      <c r="F5" s="318"/>
+      <c r="G5" s="318"/>
+      <c r="H5" s="318"/>
+      <c r="I5" s="320"/>
       <c r="J5" s="480" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K5" s="480"/>
       <c r="L5" s="480"/>
       <c r="M5" s="480"/>
       <c r="N5" s="477" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O5" s="477"/>
       <c r="P5" s="477"/>
-      <c r="Q5" s="324"/>
-      <c r="R5" s="324"/>
+      <c r="Q5" s="319"/>
+      <c r="R5" s="319"/>
       <c r="S5" s="28"/>
     </row>
     <row r="6" spans="1:19" ht="23.25" customHeight="1" thickBot="1">
@@ -33476,7 +33469,7 @@
       <c r="A8" s="29"/>
       <c r="C8" s="481" t="str">
         <f>_xlfn.CONCAT("PERIODO ", N5)</f>
-        <v>PERIODO MARZO - 2025</v>
+        <v>PERIODO ABRIL - 2025</v>
       </c>
       <c r="D8" s="482"/>
       <c r="E8" s="483"/>
@@ -33510,7 +33503,7 @@
       <c r="H9" s="53"/>
       <c r="I9" s="53"/>
       <c r="J9" s="53"/>
-      <c r="K9" s="352"/>
+      <c r="K9" s="347"/>
       <c r="L9" s="53"/>
       <c r="M9" s="53"/>
       <c r="N9" s="53"/>
@@ -34015,7 +34008,7 @@
     </row>
     <row r="6" spans="2:5">
       <c r="B6" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C6" s="12">
         <v>2</v>
@@ -34159,7 +34152,7 @@
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C18" s="12">
         <v>3</v>
@@ -34173,7 +34166,7 @@
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C19" s="12">
         <v>3</v>
@@ -34300,7 +34293,7 @@
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="86" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C31" s="12">
         <v>5</v>
@@ -34532,7 +34525,7 @@
     </row>
     <row r="2" spans="1:27" ht="37.15" customHeight="1">
       <c r="A2" s="485" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B2" s="486"/>
       <c r="C2" s="486"/>
@@ -34553,7 +34546,7 @@
       <c r="R2" s="486"/>
       <c r="S2" s="486"/>
       <c r="T2" s="487" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U2" s="487"/>
       <c r="V2" s="487"/>
@@ -36343,7 +36336,7 @@
     </row>
     <row r="2" spans="1:21" ht="19.5" thickBot="1">
       <c r="A2" s="491" t="s">
-        <v>89</v>
+        <v>221</v>
       </c>
       <c r="B2" s="492"/>
       <c r="C2" s="492"/>
@@ -36364,10 +36357,8 @@
       <c r="R2" s="492"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="424"/>
-      <c r="B3" s="3" t="s">
-        <v>222</v>
-      </c>
+      <c r="A3" s="419"/>
+      <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -36386,9 +36377,9 @@
       <c r="R3" s="3"/>
     </row>
     <row r="4" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A4" s="424"/>
-      <c r="B4" s="425"/>
-      <c r="C4" s="425"/>
+      <c r="A4" s="419"/>
+      <c r="B4" s="420"/>
+      <c r="C4" s="420"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -36406,632 +36397,632 @@
       <c r="R4" s="3"/>
     </row>
     <row r="5" spans="1:21" ht="88.5" customHeight="1" thickBot="1">
-      <c r="A5" s="424"/>
-      <c r="B5" s="442" t="s">
+      <c r="A5" s="419"/>
+      <c r="B5" s="437" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="493" t="s">
         <v>90</v>
-      </c>
-      <c r="C5" s="493" t="s">
-        <v>91</v>
       </c>
       <c r="D5" s="493"/>
       <c r="E5" s="493"/>
       <c r="F5" s="493" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G5" s="493"/>
       <c r="H5" s="493"/>
       <c r="I5" s="493" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J5" s="493"/>
       <c r="K5" s="493"/>
       <c r="L5" s="493" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M5" s="493"/>
       <c r="N5" s="493"/>
       <c r="O5" s="493" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P5" s="493"/>
       <c r="Q5" s="494"/>
-      <c r="R5" s="422"/>
-      <c r="S5" s="421"/>
+      <c r="R5" s="417"/>
+      <c r="S5" s="416"/>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
     </row>
     <row r="6" spans="1:21" ht="21">
-      <c r="A6" s="424"/>
-      <c r="B6" s="443" t="s">
+      <c r="A6" s="419"/>
+      <c r="B6" s="438" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="428"/>
-      <c r="D6" s="429">
+      <c r="C6" s="423"/>
+      <c r="D6" s="424">
         <f>IF(data_status_reg!$E4="bajo",0,IF(data_status_reg!$E4="medio",0.5,IF(data_status_reg!$E4="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E6" s="430"/>
-      <c r="F6" s="430"/>
-      <c r="G6" s="429">
+      <c r="E6" s="425"/>
+      <c r="F6" s="425"/>
+      <c r="G6" s="424">
         <f>IF(data_status_reg!$E20="bajo",0,IF(data_status_reg!$E20="medio",0.5,IF(data_status_reg!$E20="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H6" s="430"/>
-      <c r="I6" s="430"/>
-      <c r="J6" s="429">
+      <c r="H6" s="425"/>
+      <c r="I6" s="425"/>
+      <c r="J6" s="424">
         <f>IF(data_status_reg!$E36="bajo",0,IF(data_status_reg!$E36="medio",0.5,IF(data_status_reg!$E36="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K6" s="430"/>
-      <c r="L6" s="430"/>
-      <c r="M6" s="429">
+      <c r="K6" s="425"/>
+      <c r="L6" s="425"/>
+      <c r="M6" s="424">
         <f>IF(data_status_reg!$E52="bajo",0,IF(data_status_reg!$E52="medio",0.5,IF(data_status_reg!$E52="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N6" s="431"/>
-      <c r="O6" s="445"/>
-      <c r="P6" s="429">
+      <c r="N6" s="426"/>
+      <c r="O6" s="440"/>
+      <c r="P6" s="424">
         <f>IF(data_status_reg!$E68="bajo",0,IF(data_status_reg!$E68="medio",0.5,IF(data_status_reg!$E68="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="432"/>
-      <c r="R6" s="423"/>
+      <c r="Q6" s="427"/>
+      <c r="R6" s="418"/>
     </row>
     <row r="7" spans="1:21" ht="21">
-      <c r="A7" s="424"/>
-      <c r="B7" s="443" t="s">
+      <c r="A7" s="419"/>
+      <c r="B7" s="438" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="433"/>
-      <c r="D7" s="418">
+      <c r="C7" s="428"/>
+      <c r="D7" s="413">
         <f>IF(data_status_reg!$E5="bajo",0,IF(data_status_reg!$E5="medio",0.5,IF(data_status_reg!$E5="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E7" s="419"/>
-      <c r="F7" s="419"/>
-      <c r="G7" s="418">
+      <c r="E7" s="414"/>
+      <c r="F7" s="414"/>
+      <c r="G7" s="413">
         <f>IF(data_status_reg!$E21="bajo",0,IF(data_status_reg!$E21="medio",0.5,IF(data_status_reg!$E21="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H7" s="419"/>
-      <c r="I7" s="419"/>
-      <c r="J7" s="418">
+      <c r="H7" s="414"/>
+      <c r="I7" s="414"/>
+      <c r="J7" s="413">
         <f>IF(data_status_reg!$E37="bajo",0,IF(data_status_reg!$E37="medio",0.5,IF(data_status_reg!$E37="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="419"/>
-      <c r="L7" s="419"/>
-      <c r="M7" s="418">
+      <c r="K7" s="414"/>
+      <c r="L7" s="414"/>
+      <c r="M7" s="413">
         <f>IF(data_status_reg!$E53="bajo",0,IF(data_status_reg!$E53="medio",0.5,IF(data_status_reg!$E53="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N7" s="416"/>
-      <c r="O7" s="446"/>
-      <c r="P7" s="418">
+      <c r="N7" s="411"/>
+      <c r="O7" s="441"/>
+      <c r="P7" s="413">
         <f>IF(data_status_reg!$E69="bajo",0,IF(data_status_reg!$E69="medio",0.5,IF(data_status_reg!$E69="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="434"/>
+      <c r="Q7" s="429"/>
       <c r="R7" s="3"/>
     </row>
     <row r="8" spans="1:21" ht="21">
-      <c r="A8" s="424"/>
-      <c r="B8" s="443" t="s">
+      <c r="A8" s="419"/>
+      <c r="B8" s="438" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="433"/>
-      <c r="D8" s="418">
+      <c r="C8" s="428"/>
+      <c r="D8" s="413">
         <f>IF(data_status_reg!$E6="bajo",0,IF(data_status_reg!$E6="medio",0.5,IF(data_status_reg!$E6="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E8" s="419"/>
-      <c r="F8" s="419"/>
-      <c r="G8" s="418">
+      <c r="E8" s="414"/>
+      <c r="F8" s="414"/>
+      <c r="G8" s="413">
         <f>IF(data_status_reg!$E22="bajo",0,IF(data_status_reg!$E22="medio",0.5,IF(data_status_reg!$E22="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H8" s="419"/>
-      <c r="I8" s="419"/>
-      <c r="J8" s="418">
+      <c r="H8" s="414"/>
+      <c r="I8" s="414"/>
+      <c r="J8" s="413">
         <f>IF(data_status_reg!$E38="bajo",0,IF(data_status_reg!$E38="medio",0.5,IF(data_status_reg!$E38="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="419"/>
-      <c r="L8" s="419"/>
-      <c r="M8" s="418">
+      <c r="K8" s="414"/>
+      <c r="L8" s="414"/>
+      <c r="M8" s="413">
         <f>IF(data_status_reg!$E54="bajo",0,IF(data_status_reg!$E54="medio",0.5,IF(data_status_reg!$E54="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N8" s="416"/>
-      <c r="O8" s="446"/>
-      <c r="P8" s="418">
+      <c r="N8" s="411"/>
+      <c r="O8" s="441"/>
+      <c r="P8" s="413">
         <f>IF(data_status_reg!$E70="bajo",0,IF(data_status_reg!$E70="medio",0.5,IF(data_status_reg!$E70="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="434"/>
+      <c r="Q8" s="429"/>
       <c r="R8" s="3"/>
     </row>
     <row r="9" spans="1:21" ht="21">
-      <c r="A9" s="424"/>
-      <c r="B9" s="443" t="s">
+      <c r="A9" s="419"/>
+      <c r="B9" s="438" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="433"/>
-      <c r="D9" s="418">
+      <c r="C9" s="428"/>
+      <c r="D9" s="413">
         <f>IF(data_status_reg!$E7="bajo",0,IF(data_status_reg!$E7="medio",0.5,IF(data_status_reg!$E7="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E9" s="419"/>
-      <c r="F9" s="419"/>
-      <c r="G9" s="418">
+      <c r="E9" s="414"/>
+      <c r="F9" s="414"/>
+      <c r="G9" s="413">
         <f>IF(data_status_reg!$E23="bajo",0,IF(data_status_reg!$E23="medio",0.5,IF(data_status_reg!$E23="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H9" s="419"/>
-      <c r="I9" s="419"/>
-      <c r="J9" s="418">
+      <c r="H9" s="414"/>
+      <c r="I9" s="414"/>
+      <c r="J9" s="413">
         <f>IF(data_status_reg!$E39="bajo",0,IF(data_status_reg!$E39="medio",0.5,IF(data_status_reg!$E39="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="419"/>
-      <c r="L9" s="419"/>
-      <c r="M9" s="418">
+      <c r="K9" s="414"/>
+      <c r="L9" s="414"/>
+      <c r="M9" s="413">
         <f>IF(data_status_reg!$E55="bajo",0,IF(data_status_reg!$E55="medio",0.5,IF(data_status_reg!$E55="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N9" s="416"/>
-      <c r="O9" s="446"/>
-      <c r="P9" s="418">
+      <c r="N9" s="411"/>
+      <c r="O9" s="441"/>
+      <c r="P9" s="413">
         <f>IF(data_status_reg!$E71="bajo",0,IF(data_status_reg!$E71="medio",0.5,IF(data_status_reg!$E71="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="434"/>
+      <c r="Q9" s="429"/>
       <c r="R9" s="3"/>
     </row>
     <row r="10" spans="1:21" ht="21">
-      <c r="A10" s="424"/>
-      <c r="B10" s="443" t="s">
+      <c r="A10" s="419"/>
+      <c r="B10" s="438" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="433"/>
-      <c r="D10" s="418">
+      <c r="C10" s="428"/>
+      <c r="D10" s="413">
         <f>IF(data_status_reg!$E8="bajo",0,IF(data_status_reg!$E8="medio",0.5,IF(data_status_reg!$E8="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E10" s="419"/>
-      <c r="F10" s="419"/>
-      <c r="G10" s="418">
+      <c r="E10" s="414"/>
+      <c r="F10" s="414"/>
+      <c r="G10" s="413">
         <f>IF(data_status_reg!$E24="bajo",0,IF(data_status_reg!$E24="medio",0.5,IF(data_status_reg!$E24="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H10" s="419"/>
-      <c r="I10" s="419"/>
-      <c r="J10" s="418">
+      <c r="H10" s="414"/>
+      <c r="I10" s="414"/>
+      <c r="J10" s="413">
         <f>IF(data_status_reg!$E40="bajo",0,IF(data_status_reg!$E40="medio",0.5,IF(data_status_reg!$E40="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="419"/>
-      <c r="L10" s="419"/>
-      <c r="M10" s="418">
+      <c r="K10" s="414"/>
+      <c r="L10" s="414"/>
+      <c r="M10" s="413">
         <f>IF(data_status_reg!$E56="bajo",0,IF(data_status_reg!$E56="medio",0.5,IF(data_status_reg!$E56="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N10" s="416"/>
-      <c r="O10" s="446"/>
-      <c r="P10" s="418">
+      <c r="N10" s="411"/>
+      <c r="O10" s="441"/>
+      <c r="P10" s="413">
         <f>IF(data_status_reg!$E72="bajo",0,IF(data_status_reg!$E72="medio",0.5,IF(data_status_reg!$E72="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="434"/>
+      <c r="Q10" s="429"/>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:21" ht="21">
-      <c r="A11" s="424"/>
-      <c r="B11" s="443" t="s">
+      <c r="A11" s="419"/>
+      <c r="B11" s="438" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="433"/>
-      <c r="D11" s="418">
+      <c r="C11" s="428"/>
+      <c r="D11" s="413">
         <f>IF(data_status_reg!$E9="bajo",0,IF(data_status_reg!$E9="medio",0.5,IF(data_status_reg!$E9="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E11" s="419"/>
-      <c r="F11" s="419"/>
-      <c r="G11" s="418">
+      <c r="E11" s="414"/>
+      <c r="F11" s="414"/>
+      <c r="G11" s="413">
         <f>IF(data_status_reg!$E25="bajo",0,IF(data_status_reg!$E25="medio",0.5,IF(data_status_reg!$E25="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H11" s="419"/>
-      <c r="I11" s="419"/>
-      <c r="J11" s="418">
+      <c r="H11" s="414"/>
+      <c r="I11" s="414"/>
+      <c r="J11" s="413">
         <f>IF(data_status_reg!$E41="bajo",0,IF(data_status_reg!$E41="medio",0.5,IF(data_status_reg!$E41="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="419"/>
-      <c r="L11" s="419"/>
-      <c r="M11" s="418">
+      <c r="K11" s="414"/>
+      <c r="L11" s="414"/>
+      <c r="M11" s="413">
         <f>IF(data_status_reg!$E57="bajo",0,IF(data_status_reg!$E57="medio",0.5,IF(data_status_reg!$E57="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N11" s="416"/>
-      <c r="O11" s="446"/>
-      <c r="P11" s="418">
+      <c r="N11" s="411"/>
+      <c r="O11" s="441"/>
+      <c r="P11" s="413">
         <f>IF(data_status_reg!$E73="bajo",0,IF(data_status_reg!$E73="medio",0.5,IF(data_status_reg!$E73="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="434"/>
+      <c r="Q11" s="429"/>
       <c r="R11" s="3"/>
     </row>
     <row r="12" spans="1:21" ht="21">
-      <c r="A12" s="424"/>
-      <c r="B12" s="443" t="s">
+      <c r="A12" s="419"/>
+      <c r="B12" s="438" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="433"/>
-      <c r="D12" s="418">
+      <c r="C12" s="428"/>
+      <c r="D12" s="413">
         <f>IF(data_status_reg!$E10="bajo",0,IF(data_status_reg!$E10="medio",0.5,IF(data_status_reg!$E10="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E12" s="419"/>
-      <c r="F12" s="419"/>
-      <c r="G12" s="418">
+      <c r="E12" s="414"/>
+      <c r="F12" s="414"/>
+      <c r="G12" s="413">
         <f>IF(data_status_reg!$E26="bajo",0,IF(data_status_reg!$E26="medio",0.5,IF(data_status_reg!$E26="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H12" s="419"/>
-      <c r="I12" s="420"/>
-      <c r="J12" s="418">
+      <c r="H12" s="414"/>
+      <c r="I12" s="415"/>
+      <c r="J12" s="413">
         <f>IF(data_status_reg!$E42="bajo",0,IF(data_status_reg!$E42="medio",0.5,IF(data_status_reg!$E42="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="420"/>
-      <c r="L12" s="420"/>
-      <c r="M12" s="418">
+      <c r="K12" s="415"/>
+      <c r="L12" s="415"/>
+      <c r="M12" s="413">
         <f>IF(data_status_reg!$E58="bajo",0,IF(data_status_reg!$E58="medio",0.5,IF(data_status_reg!$E58="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N12" s="417"/>
-      <c r="O12" s="447"/>
-      <c r="P12" s="418">
+      <c r="N12" s="412"/>
+      <c r="O12" s="442"/>
+      <c r="P12" s="413">
         <f>IF(data_status_reg!$E74="bajo",0,IF(data_status_reg!$E74="medio",0.5,IF(data_status_reg!$E74="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="434"/>
+      <c r="Q12" s="429"/>
       <c r="R12" s="3"/>
     </row>
     <row r="13" spans="1:21" ht="21">
-      <c r="A13" s="424"/>
-      <c r="B13" s="443" t="s">
+      <c r="A13" s="419"/>
+      <c r="B13" s="438" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="433"/>
-      <c r="D13" s="418">
+      <c r="C13" s="428"/>
+      <c r="D13" s="413">
         <f>IF(data_status_reg!$E11="bajo",0,IF(data_status_reg!$E11="medio",0.5,IF(data_status_reg!$E11="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E13" s="419"/>
-      <c r="F13" s="419"/>
-      <c r="G13" s="418">
+      <c r="E13" s="414"/>
+      <c r="F13" s="414"/>
+      <c r="G13" s="413">
         <f>IF(data_status_reg!$E27="bajo",0,IF(data_status_reg!$E27="medio",0.5,IF(data_status_reg!$E27="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H13" s="419"/>
-      <c r="I13" s="419"/>
-      <c r="J13" s="418">
+      <c r="H13" s="414"/>
+      <c r="I13" s="414"/>
+      <c r="J13" s="413">
         <f>IF(data_status_reg!$E43="bajo",0,IF(data_status_reg!$E43="medio",0.5,IF(data_status_reg!$E43="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="419"/>
-      <c r="L13" s="419"/>
-      <c r="M13" s="418">
+      <c r="K13" s="414"/>
+      <c r="L13" s="414"/>
+      <c r="M13" s="413">
         <f>IF(data_status_reg!$E59="bajo",0,IF(data_status_reg!$E59="medio",0.5,IF(data_status_reg!$E59="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N13" s="416"/>
-      <c r="O13" s="446"/>
-      <c r="P13" s="418">
+      <c r="N13" s="411"/>
+      <c r="O13" s="441"/>
+      <c r="P13" s="413">
         <f>IF(data_status_reg!$E75="bajo",0,IF(data_status_reg!$E75="medio",0.5,IF(data_status_reg!$E75="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q13" s="434"/>
+      <c r="Q13" s="429"/>
       <c r="R13" s="3"/>
       <c r="U13" s="16"/>
     </row>
     <row r="14" spans="1:21" ht="21">
-      <c r="A14" s="424"/>
-      <c r="B14" s="443" t="s">
+      <c r="A14" s="419"/>
+      <c r="B14" s="438" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="433"/>
-      <c r="D14" s="418">
+      <c r="C14" s="428"/>
+      <c r="D14" s="413">
         <f>IF(data_status_reg!$E12="bajo",0,IF(data_status_reg!$E12="medio",0.5,IF(data_status_reg!$E12="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E14" s="419"/>
-      <c r="F14" s="419"/>
-      <c r="G14" s="418">
+      <c r="E14" s="414"/>
+      <c r="F14" s="414"/>
+      <c r="G14" s="413">
         <f>IF(data_status_reg!$E28="bajo",0,IF(data_status_reg!$E28="medio",0.5,IF(data_status_reg!$E28="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H14" s="419"/>
-      <c r="I14" s="419"/>
-      <c r="J14" s="418">
+      <c r="H14" s="414"/>
+      <c r="I14" s="414"/>
+      <c r="J14" s="413">
         <f>IF(data_status_reg!$E44="bajo",0,IF(data_status_reg!$E44="medio",0.5,IF(data_status_reg!$E44="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K14" s="419"/>
-      <c r="L14" s="419"/>
-      <c r="M14" s="418">
+      <c r="K14" s="414"/>
+      <c r="L14" s="414"/>
+      <c r="M14" s="413">
         <f>IF(data_status_reg!$E60="bajo",0,IF(data_status_reg!$E60="medio",0.5,IF(data_status_reg!$E60="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N14" s="416"/>
-      <c r="O14" s="446"/>
-      <c r="P14" s="418">
+      <c r="N14" s="411"/>
+      <c r="O14" s="441"/>
+      <c r="P14" s="413">
         <f>IF(data_status_reg!$E76="bajo",0,IF(data_status_reg!$E76="medio",0.5,IF(data_status_reg!$E76="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q14" s="434"/>
+      <c r="Q14" s="429"/>
       <c r="R14" s="3"/>
     </row>
     <row r="15" spans="1:21" ht="21">
-      <c r="A15" s="424"/>
-      <c r="B15" s="443" t="s">
+      <c r="A15" s="419"/>
+      <c r="B15" s="438" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="433"/>
-      <c r="D15" s="418">
+      <c r="C15" s="428"/>
+      <c r="D15" s="413">
         <f>IF(data_status_reg!$E13="bajo",0,IF(data_status_reg!$E13="medio",0.5,IF(data_status_reg!$E13="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E15" s="419"/>
-      <c r="F15" s="419"/>
-      <c r="G15" s="418">
+      <c r="E15" s="414"/>
+      <c r="F15" s="414"/>
+      <c r="G15" s="413">
         <f>IF(data_status_reg!$E29="bajo",0,IF(data_status_reg!$E29="medio",0.5,IF(data_status_reg!$E29="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H15" s="419"/>
-      <c r="I15" s="420"/>
-      <c r="J15" s="418">
+      <c r="H15" s="414"/>
+      <c r="I15" s="415"/>
+      <c r="J15" s="413">
         <f>IF(data_status_reg!$E45="bajo",0,IF(data_status_reg!$E45="medio",0.5,IF(data_status_reg!$E45="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K15" s="420"/>
-      <c r="L15" s="420"/>
-      <c r="M15" s="418">
+      <c r="K15" s="415"/>
+      <c r="L15" s="415"/>
+      <c r="M15" s="413">
         <f>IF(data_status_reg!$E61="bajo",0,IF(data_status_reg!$E61="medio",0.5,IF(data_status_reg!$E61="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N15" s="417"/>
-      <c r="O15" s="447"/>
-      <c r="P15" s="418">
+      <c r="N15" s="412"/>
+      <c r="O15" s="442"/>
+      <c r="P15" s="413">
         <f>IF(data_status_reg!$E77="bajo",0,IF(data_status_reg!$E77="medio",0.5,IF(data_status_reg!$E77="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q15" s="434"/>
+      <c r="Q15" s="429"/>
       <c r="R15" s="3"/>
     </row>
     <row r="16" spans="1:21" ht="21">
-      <c r="A16" s="424"/>
-      <c r="B16" s="443" t="s">
+      <c r="A16" s="419"/>
+      <c r="B16" s="438" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="433"/>
-      <c r="D16" s="418">
+      <c r="C16" s="428"/>
+      <c r="D16" s="413">
         <f>IF(data_status_reg!$E14="bajo",0,IF(data_status_reg!$E14="medio",0.5,IF(data_status_reg!$E14="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E16" s="419"/>
-      <c r="F16" s="419"/>
-      <c r="G16" s="418">
+      <c r="E16" s="414"/>
+      <c r="F16" s="414"/>
+      <c r="G16" s="413">
         <f>IF(data_status_reg!$E30="bajo",0,IF(data_status_reg!$E30="medio",0.5,IF(data_status_reg!$E30="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H16" s="419"/>
-      <c r="I16" s="419"/>
-      <c r="J16" s="418">
+      <c r="H16" s="414"/>
+      <c r="I16" s="414"/>
+      <c r="J16" s="413">
         <f>IF(data_status_reg!$E46="bajo",0,IF(data_status_reg!$E46="medio",0.5,IF(data_status_reg!$E46="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K16" s="419"/>
-      <c r="L16" s="419"/>
-      <c r="M16" s="418">
+      <c r="K16" s="414"/>
+      <c r="L16" s="414"/>
+      <c r="M16" s="413">
         <f>IF(data_status_reg!$E62="bajo",0,IF(data_status_reg!$E62="medio",0.5,IF(data_status_reg!$E62="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N16" s="416"/>
-      <c r="O16" s="446"/>
-      <c r="P16" s="418">
+      <c r="N16" s="411"/>
+      <c r="O16" s="441"/>
+      <c r="P16" s="413">
         <f>IF(data_status_reg!$E78="bajo",0,IF(data_status_reg!$E78="medio",0.5,IF(data_status_reg!$E78="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q16" s="434"/>
+      <c r="Q16" s="429"/>
       <c r="R16" s="3"/>
     </row>
     <row r="17" spans="1:18" ht="21">
-      <c r="A17" s="424"/>
-      <c r="B17" s="443" t="s">
+      <c r="A17" s="419"/>
+      <c r="B17" s="438" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="433"/>
-      <c r="D17" s="418">
+      <c r="C17" s="428"/>
+      <c r="D17" s="413">
         <f>IF(data_status_reg!$E15="bajo",0,IF(data_status_reg!$E15="medio",0.5,IF(data_status_reg!$E15="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E17" s="419"/>
-      <c r="F17" s="419"/>
-      <c r="G17" s="418">
+      <c r="E17" s="414"/>
+      <c r="F17" s="414"/>
+      <c r="G17" s="413">
         <f>IF(data_status_reg!$E31="bajo",0,IF(data_status_reg!$E31="medio",0.5,IF(data_status_reg!$E31="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H17" s="419"/>
-      <c r="I17" s="419"/>
-      <c r="J17" s="418">
+      <c r="H17" s="414"/>
+      <c r="I17" s="414"/>
+      <c r="J17" s="413">
         <f>IF(data_status_reg!$E47="bajo",0,IF(data_status_reg!$E47="medio",0.5,IF(data_status_reg!$E47="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K17" s="419"/>
-      <c r="L17" s="419"/>
-      <c r="M17" s="418">
+      <c r="K17" s="414"/>
+      <c r="L17" s="414"/>
+      <c r="M17" s="413">
         <f>IF(data_status_reg!$E63="bajo",0,IF(data_status_reg!$E63="medio",0.5,IF(data_status_reg!$E63="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N17" s="416"/>
-      <c r="O17" s="446"/>
-      <c r="P17" s="418">
+      <c r="N17" s="411"/>
+      <c r="O17" s="441"/>
+      <c r="P17" s="413">
         <f>IF(data_status_reg!$E79="bajo",0,IF(data_status_reg!$E79="medio",0.5,IF(data_status_reg!$E79="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q17" s="434"/>
+      <c r="Q17" s="429"/>
       <c r="R17" s="3"/>
     </row>
     <row r="18" spans="1:18" ht="21">
-      <c r="A18" s="424"/>
-      <c r="B18" s="443" t="s">
+      <c r="A18" s="419"/>
+      <c r="B18" s="438" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="433"/>
-      <c r="D18" s="418">
+      <c r="C18" s="428"/>
+      <c r="D18" s="413">
         <f>IF(data_status_reg!$E16="bajo",0,IF(data_status_reg!$E16="medio",0.5,IF(data_status_reg!$E16="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E18" s="419"/>
-      <c r="F18" s="419"/>
-      <c r="G18" s="449" t="s">
-        <v>94</v>
-      </c>
-      <c r="H18" s="419"/>
-      <c r="I18" s="419"/>
-      <c r="J18" s="418">
+      <c r="E18" s="414"/>
+      <c r="F18" s="414"/>
+      <c r="G18" s="444" t="s">
+        <v>93</v>
+      </c>
+      <c r="H18" s="414"/>
+      <c r="I18" s="414"/>
+      <c r="J18" s="413">
         <f>IF(data_status_reg!$E48="bajo",0,IF(data_status_reg!$E48="medio",0.5,IF(data_status_reg!$E48="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K18" s="419"/>
-      <c r="M18" s="418">
+      <c r="K18" s="414"/>
+      <c r="M18" s="413">
         <f>IF(data_status_reg!$E64="bajo",0,IF(data_status_reg!$E64="medio",0.5,IF(data_status_reg!$E64="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N18" s="417"/>
-      <c r="O18" s="447"/>
-      <c r="P18" s="418">
+      <c r="N18" s="412"/>
+      <c r="O18" s="442"/>
+      <c r="P18" s="413">
         <f>IF(data_status_reg!$E80="bajo",0,IF(data_status_reg!$E80="medio",0.5,IF(data_status_reg!$E80="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q18" s="434"/>
+      <c r="Q18" s="429"/>
       <c r="R18" s="3"/>
     </row>
     <row r="19" spans="1:18" ht="21">
-      <c r="A19" s="424"/>
-      <c r="B19" s="443" t="s">
+      <c r="A19" s="419"/>
+      <c r="B19" s="438" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="433"/>
-      <c r="D19" s="418">
+      <c r="C19" s="428"/>
+      <c r="D19" s="413">
         <f>IF(data_status_reg!$E17="bajo",0,IF(data_status_reg!$E17="medio",0.5,IF(data_status_reg!$E17="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E19" s="419"/>
-      <c r="F19" s="419"/>
-      <c r="G19" s="418">
+      <c r="E19" s="414"/>
+      <c r="F19" s="414"/>
+      <c r="G19" s="413">
         <f>IF(data_status_reg!$E33="bajo",0,IF(data_status_reg!$E33="medio",0.5,IF(data_status_reg!$E33="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H19" s="419"/>
-      <c r="I19" s="419"/>
-      <c r="J19" s="418">
+      <c r="H19" s="414"/>
+      <c r="I19" s="414"/>
+      <c r="J19" s="413">
         <f>IF(data_status_reg!$E49="bajo",0,IF(data_status_reg!$E49="medio",0.5,IF(data_status_reg!$E49="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K19" s="419"/>
-      <c r="L19" s="419"/>
-      <c r="M19" s="418">
+      <c r="K19" s="414"/>
+      <c r="L19" s="414"/>
+      <c r="M19" s="413">
         <f>IF(data_status_reg!$E65="bajo",0,IF(data_status_reg!$E65="medio",0.5,IF(data_status_reg!$E65="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N19" s="416"/>
-      <c r="O19" s="446"/>
-      <c r="P19" s="418">
+      <c r="N19" s="411"/>
+      <c r="O19" s="441"/>
+      <c r="P19" s="413">
         <f>IF(data_status_reg!$E81="bajo",0,IF(data_status_reg!$E81="medio",0.5,IF(data_status_reg!$E81="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="434"/>
+      <c r="Q19" s="429"/>
       <c r="R19" s="3"/>
     </row>
     <row r="20" spans="1:18" ht="21">
-      <c r="A20" s="424"/>
-      <c r="B20" s="443" t="s">
+      <c r="A20" s="419"/>
+      <c r="B20" s="438" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="433"/>
-      <c r="D20" s="418">
+      <c r="C20" s="428"/>
+      <c r="D20" s="413">
         <f>IF(data_status_reg!$E18="bajo",0,IF(data_status_reg!$E18="medio",0.5,IF(data_status_reg!$E18="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E20" s="419"/>
-      <c r="F20" s="419"/>
-      <c r="G20" s="418">
+      <c r="E20" s="414"/>
+      <c r="F20" s="414"/>
+      <c r="G20" s="413">
         <f>IF(data_status_reg!$E34="bajo",0,IF(data_status_reg!$E34="medio",0.5,IF(data_status_reg!$E34="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="H20" s="419"/>
-      <c r="I20" s="419"/>
-      <c r="J20" s="418">
+      <c r="H20" s="414"/>
+      <c r="I20" s="414"/>
+      <c r="J20" s="413">
         <f>IF(data_status_reg!$E50="bajo",0,IF(data_status_reg!$E50="medio",0.5,IF(data_status_reg!$E50="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K20" s="419"/>
-      <c r="L20" s="419"/>
-      <c r="M20" s="418">
+      <c r="K20" s="414"/>
+      <c r="L20" s="414"/>
+      <c r="M20" s="413">
         <f>IF(data_status_reg!$E66="bajo",0,IF(data_status_reg!$E66="medio",0.5,IF(data_status_reg!$E66="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N20" s="416"/>
-      <c r="O20" s="446"/>
-      <c r="P20" s="418">
+      <c r="N20" s="411"/>
+      <c r="O20" s="441"/>
+      <c r="P20" s="413">
         <f>IF(data_status_reg!$E82="bajo",0,IF(data_status_reg!$E82="medio",0.5,IF(data_status_reg!$E82="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q20" s="434"/>
+      <c r="Q20" s="429"/>
       <c r="R20" s="3"/>
     </row>
     <row r="21" spans="1:18" ht="21.75" thickBot="1">
-      <c r="A21" s="424"/>
-      <c r="B21" s="444" t="s">
+      <c r="A21" s="419"/>
+      <c r="B21" s="439" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="435"/>
-      <c r="D21" s="436">
+      <c r="C21" s="430"/>
+      <c r="D21" s="431">
         <f>IF(data_status_reg!$E19="bajo",0,IF(data_status_reg!$E19="medio",0.5,IF(data_status_reg!$E19="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="E21" s="437"/>
-      <c r="F21" s="437"/>
-      <c r="G21" s="450" t="s">
-        <v>94</v>
-      </c>
-      <c r="H21" s="437"/>
-      <c r="I21" s="437"/>
-      <c r="J21" s="436">
+      <c r="E21" s="432"/>
+      <c r="F21" s="432"/>
+      <c r="G21" s="445" t="s">
+        <v>93</v>
+      </c>
+      <c r="H21" s="432"/>
+      <c r="I21" s="432"/>
+      <c r="J21" s="431">
         <f>IF(data_status_reg!$E51="bajo",0,IF(data_status_reg!$E51="medio",0.5,IF(data_status_reg!$E51="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="K21" s="437"/>
-      <c r="L21" s="438"/>
-      <c r="M21" s="439">
+      <c r="K21" s="432"/>
+      <c r="L21" s="433"/>
+      <c r="M21" s="434">
         <f>IF(data_status_reg!$E67="bajo",0,IF(data_status_reg!$E67="medio",0.5,IF(data_status_reg!$E67="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="N21" s="440"/>
-      <c r="O21" s="448"/>
-      <c r="P21" s="436">
+      <c r="N21" s="435"/>
+      <c r="O21" s="443"/>
+      <c r="P21" s="431">
         <f>IF(data_status_reg!$E83="bajo",0,IF(data_status_reg!$E83="medio",0.5,IF(data_status_reg!$E83="alto",1,"falta riesgo")))</f>
         <v>0</v>
       </c>
-      <c r="Q21" s="441"/>
+      <c r="Q21" s="436"/>
       <c r="R21" s="3"/>
     </row>
     <row r="22" spans="1:18">
-      <c r="A22" s="424"/>
+      <c r="A22" s="419"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -37051,24 +37042,24 @@
       <c r="R22" s="3"/>
     </row>
     <row r="23" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A23" s="426"/>
-      <c r="B23" s="427"/>
-      <c r="C23" s="427"/>
-      <c r="D23" s="427"/>
-      <c r="E23" s="427"/>
-      <c r="F23" s="427"/>
-      <c r="G23" s="427"/>
-      <c r="H23" s="427"/>
-      <c r="I23" s="427"/>
-      <c r="J23" s="427"/>
-      <c r="K23" s="427"/>
-      <c r="L23" s="427"/>
-      <c r="M23" s="427"/>
-      <c r="N23" s="427"/>
-      <c r="O23" s="427"/>
-      <c r="P23" s="427"/>
-      <c r="Q23" s="427"/>
-      <c r="R23" s="427"/>
+      <c r="A23" s="421"/>
+      <c r="B23" s="422"/>
+      <c r="C23" s="422"/>
+      <c r="D23" s="422"/>
+      <c r="E23" s="422"/>
+      <c r="F23" s="422"/>
+      <c r="G23" s="422"/>
+      <c r="H23" s="422"/>
+      <c r="I23" s="422"/>
+      <c r="J23" s="422"/>
+      <c r="K23" s="422"/>
+      <c r="L23" s="422"/>
+      <c r="M23" s="422"/>
+      <c r="N23" s="422"/>
+      <c r="O23" s="422"/>
+      <c r="P23" s="422"/>
+      <c r="Q23" s="422"/>
+      <c r="R23" s="422"/>
     </row>
     <row r="26" spans="1:18" outlineLevel="1"/>
     <row r="27" spans="1:18" outlineLevel="1">
@@ -37369,7 +37360,7 @@
       </c>
       <c r="E3" s="4"/>
       <c r="I3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>13</v>
@@ -37387,7 +37378,7 @@
       </c>
       <c r="E4" s="4"/>
       <c r="I4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J4" s="6" t="s">
         <v>13</v>
@@ -37405,7 +37396,7 @@
       </c>
       <c r="E5" s="4"/>
       <c r="I5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>13</v>
@@ -37418,7 +37409,7 @@
       <c r="D6" s="5"/>
       <c r="E6" s="4"/>
       <c r="I6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>13</v>
@@ -37438,7 +37429,7 @@
       </c>
       <c r="E7" s="4"/>
       <c r="I7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>13</v>
@@ -37456,7 +37447,7 @@
       </c>
       <c r="E8" s="4"/>
       <c r="I8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>13</v>
@@ -37474,7 +37465,7 @@
       </c>
       <c r="E9" s="4"/>
       <c r="I9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>13</v>
@@ -37492,7 +37483,7 @@
       </c>
       <c r="E10" s="4"/>
       <c r="I10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>13</v>
@@ -37510,7 +37501,7 @@
       </c>
       <c r="E11" s="4"/>
       <c r="I11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>13</v>
@@ -37528,7 +37519,7 @@
       </c>
       <c r="E12" s="4"/>
       <c r="I12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>13</v>
@@ -37546,7 +37537,7 @@
       </c>
       <c r="E13" s="4"/>
       <c r="I13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>13</v>
@@ -37559,7 +37550,7 @@
       <c r="D14" s="5"/>
       <c r="E14" s="4"/>
       <c r="I14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>13</v>
@@ -37579,7 +37570,7 @@
       </c>
       <c r="E15" s="4"/>
       <c r="I15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>13</v>
@@ -37597,7 +37588,7 @@
       </c>
       <c r="E16" s="4"/>
       <c r="I16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>13</v>
@@ -37615,7 +37606,7 @@
       </c>
       <c r="E17" s="4"/>
       <c r="I17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>13</v>
@@ -37633,7 +37624,7 @@
       </c>
       <c r="E18" s="4"/>
       <c r="I18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>13</v>
@@ -37646,7 +37637,7 @@
       <c r="D19" s="5"/>
       <c r="E19" s="4"/>
       <c r="I19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>13</v>
@@ -37666,7 +37657,7 @@
       </c>
       <c r="E20" s="4"/>
       <c r="I20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>13</v>
@@ -37684,7 +37675,7 @@
       </c>
       <c r="E21" s="4"/>
       <c r="I21" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>13</v>
@@ -37702,7 +37693,7 @@
       </c>
       <c r="E22" s="4"/>
       <c r="I22" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>13</v>
@@ -37720,7 +37711,7 @@
       </c>
       <c r="E23" s="4"/>
       <c r="I23" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>13</v>
@@ -37738,7 +37729,7 @@
       </c>
       <c r="E24" s="4"/>
       <c r="I24" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>13</v>
@@ -37751,7 +37742,7 @@
       <c r="D25" s="5"/>
       <c r="E25" s="4"/>
       <c r="I25" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>13</v>
@@ -37771,7 +37762,7 @@
       </c>
       <c r="E26" s="4"/>
       <c r="I26" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>13</v>
@@ -37789,7 +37780,7 @@
       </c>
       <c r="E27" s="4"/>
       <c r="I27" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J27" s="6" t="s">
         <v>13</v>
@@ -37807,7 +37798,7 @@
       </c>
       <c r="E28" s="4"/>
       <c r="I28" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J28" s="6" t="s">
         <v>13</v>
@@ -37825,7 +37816,7 @@
       </c>
       <c r="E29" s="4"/>
       <c r="I29" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J29" s="6" t="s">
         <v>13</v>
@@ -37843,7 +37834,7 @@
       </c>
       <c r="E30" s="4"/>
       <c r="I30" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J30" s="6" t="s">
         <v>13</v>
@@ -37861,7 +37852,7 @@
       </c>
       <c r="E31" s="4"/>
       <c r="I31" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>13</v>
@@ -37879,7 +37870,7 @@
       </c>
       <c r="E32" s="4"/>
       <c r="I32" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J32" s="6" t="s">
         <v>13</v>
@@ -37897,7 +37888,7 @@
       </c>
       <c r="E33" s="4"/>
       <c r="I33" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J33" s="6" t="s">
         <v>13</v>
@@ -37910,7 +37901,7 @@
       <c r="D34" s="5"/>
       <c r="E34" s="4"/>
       <c r="I34" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J34" s="6" t="s">
         <v>13</v>
@@ -37930,7 +37921,7 @@
       </c>
       <c r="E35" s="4"/>
       <c r="I35" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J35" s="6" t="s">
         <v>13</v>
@@ -37948,7 +37939,7 @@
       </c>
       <c r="E36" s="4"/>
       <c r="I36" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J36" s="6" t="s">
         <v>13</v>
@@ -37966,7 +37957,7 @@
       </c>
       <c r="E37" s="4"/>
       <c r="I37" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J37" s="6" t="s">
         <v>13</v>
@@ -37984,7 +37975,7 @@
       </c>
       <c r="E38" s="4"/>
       <c r="I38" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J38" s="6" t="s">
         <v>13</v>
@@ -38002,7 +37993,7 @@
       </c>
       <c r="E39" s="4"/>
       <c r="I39" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J39" s="6" t="s">
         <v>13</v>
@@ -38015,7 +38006,7 @@
       <c r="D40" s="5"/>
       <c r="E40" s="4"/>
       <c r="I40" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J40" s="6" t="s">
         <v>13</v>
@@ -38035,7 +38026,7 @@
       </c>
       <c r="E41" s="4"/>
       <c r="I41" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J41" s="6" t="s">
         <v>13</v>
@@ -38053,7 +38044,7 @@
       </c>
       <c r="E42" s="4"/>
       <c r="I42" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J42" s="6" t="s">
         <v>13</v>
@@ -38071,7 +38062,7 @@
       </c>
       <c r="E43" s="4"/>
       <c r="I43" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J43" s="6" t="s">
         <v>13</v>
@@ -38089,7 +38080,7 @@
       </c>
       <c r="E44" s="4"/>
       <c r="I44" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J44" s="6" t="s">
         <v>13</v>
@@ -38107,7 +38098,7 @@
       </c>
       <c r="E45" s="4"/>
       <c r="I45" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J45" s="6" t="s">
         <v>13</v>
@@ -38125,7 +38116,7 @@
       </c>
       <c r="E46" s="4"/>
       <c r="I46" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>13</v>
@@ -38138,7 +38129,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="4"/>
       <c r="I47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J47" s="6" t="s">
         <v>13</v>
@@ -38158,7 +38149,7 @@
       </c>
       <c r="E48" s="4"/>
       <c r="I48" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>13</v>
@@ -38176,7 +38167,7 @@
       </c>
       <c r="E49" s="4"/>
       <c r="I49" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J49" s="6" t="s">
         <v>13</v>
@@ -38300,24 +38291,24 @@
   <sheetData>
     <row r="3" spans="2:5" ht="18.75" customHeight="1">
       <c r="B3" s="88" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C3" s="88" t="s">
         <v>39</v>
       </c>
       <c r="D3" s="88" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="88" t="s">
         <v>127</v>
-      </c>
-      <c r="E3" s="88" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="B4" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>23</v>
@@ -38328,10 +38319,10 @@
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>24</v>
@@ -38342,10 +38333,10 @@
     </row>
     <row r="6" spans="2:5">
       <c r="B6" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>25</v>
@@ -38356,10 +38347,10 @@
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>26</v>
@@ -38370,10 +38361,10 @@
     </row>
     <row r="8" spans="2:5">
       <c r="B8" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>27</v>
@@ -38384,10 +38375,10 @@
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>28</v>
@@ -38398,10 +38389,10 @@
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>29</v>
@@ -38412,10 +38403,10 @@
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>30</v>
@@ -38426,13 +38417,13 @@
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E12" s="89" t="s">
         <v>13</v>
@@ -38440,10 +38431,10 @@
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>32</v>
@@ -38454,10 +38445,10 @@
     </row>
     <row r="14" spans="2:5">
       <c r="B14" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>33</v>
@@ -38468,10 +38459,10 @@
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>34</v>
@@ -38482,10 +38473,10 @@
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>35</v>
@@ -38496,10 +38487,10 @@
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>36</v>
@@ -38510,10 +38501,10 @@
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>37</v>
@@ -38524,10 +38515,10 @@
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>38</v>
@@ -38538,10 +38529,10 @@
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="90" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C20" s="90" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D20" s="90" t="s">
         <v>23</v>
@@ -38552,10 +38543,10 @@
     </row>
     <row r="21" spans="2:5">
       <c r="B21" s="90" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C21" s="90" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D21" s="90" t="s">
         <v>24</v>
@@ -38566,10 +38557,10 @@
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="90" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C22" s="90" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D22" s="90" t="s">
         <v>25</v>
@@ -38580,10 +38571,10 @@
     </row>
     <row r="23" spans="2:5">
       <c r="B23" s="90" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C23" s="90" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D23" s="90" t="s">
         <v>26</v>
@@ -38594,10 +38585,10 @@
     </row>
     <row r="24" spans="2:5">
       <c r="B24" s="90" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C24" s="90" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D24" s="90" t="s">
         <v>27</v>
@@ -38608,10 +38599,10 @@
     </row>
     <row r="25" spans="2:5">
       <c r="B25" s="90" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C25" s="90" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D25" s="90" t="s">
         <v>28</v>
@@ -38622,10 +38613,10 @@
     </row>
     <row r="26" spans="2:5">
       <c r="B26" s="90" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C26" s="90" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D26" s="90" t="s">
         <v>29</v>
@@ -38636,10 +38627,10 @@
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="90" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C27" s="90" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D27" s="90" t="s">
         <v>30</v>
@@ -38650,13 +38641,13 @@
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="90" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C28" s="90" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D28" s="90" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E28" s="89" t="s">
         <v>13</v>
@@ -38664,10 +38655,10 @@
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="90" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C29" s="90" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D29" s="90" t="s">
         <v>32</v>
@@ -38678,10 +38669,10 @@
     </row>
     <row r="30" spans="2:5">
       <c r="B30" s="90" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C30" s="90" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D30" s="90" t="s">
         <v>33</v>
@@ -38692,10 +38683,10 @@
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="90" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C31" s="90" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D31" s="90" t="s">
         <v>34</v>
@@ -38706,24 +38697,24 @@
     </row>
     <row r="32" spans="2:5">
       <c r="B32" s="90" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C32" s="90" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D32" s="90" t="s">
         <v>35</v>
       </c>
       <c r="E32" s="89" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="2:5">
       <c r="B33" s="90" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C33" s="90" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D33" s="90" t="s">
         <v>36</v>
@@ -38734,10 +38725,10 @@
     </row>
     <row r="34" spans="2:5">
       <c r="B34" s="90" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C34" s="90" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D34" s="90" t="s">
         <v>37</v>
@@ -38748,24 +38739,24 @@
     </row>
     <row r="35" spans="2:5">
       <c r="B35" s="90" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C35" s="90" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D35" s="90" t="s">
         <v>38</v>
       </c>
       <c r="E35" s="89" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36" spans="2:5">
       <c r="B36" s="87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>23</v>
@@ -38776,10 +38767,10 @@
     </row>
     <row r="37" spans="2:5">
       <c r="B37" s="87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>24</v>
@@ -38790,10 +38781,10 @@
     </row>
     <row r="38" spans="2:5">
       <c r="B38" s="87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>25</v>
@@ -38804,10 +38795,10 @@
     </row>
     <row r="39" spans="2:5">
       <c r="B39" s="87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>26</v>
@@ -38818,10 +38809,10 @@
     </row>
     <row r="40" spans="2:5">
       <c r="B40" s="87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>27</v>
@@ -38832,10 +38823,10 @@
     </row>
     <row r="41" spans="2:5">
       <c r="B41" s="87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>28</v>
@@ -38846,10 +38837,10 @@
     </row>
     <row r="42" spans="2:5">
       <c r="B42" s="87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>29</v>
@@ -38860,10 +38851,10 @@
     </row>
     <row r="43" spans="2:5">
       <c r="B43" s="87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>30</v>
@@ -38874,13 +38865,13 @@
     </row>
     <row r="44" spans="2:5">
       <c r="B44" s="87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E44" s="89" t="s">
         <v>13</v>
@@ -38888,10 +38879,10 @@
     </row>
     <row r="45" spans="2:5">
       <c r="B45" s="87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>32</v>
@@ -38902,10 +38893,10 @@
     </row>
     <row r="46" spans="2:5">
       <c r="B46" s="87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>33</v>
@@ -38916,10 +38907,10 @@
     </row>
     <row r="47" spans="2:5">
       <c r="B47" s="87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>34</v>
@@ -38930,10 +38921,10 @@
     </row>
     <row r="48" spans="2:5">
       <c r="B48" s="87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>35</v>
@@ -38944,10 +38935,10 @@
     </row>
     <row r="49" spans="2:5">
       <c r="B49" s="87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>36</v>
@@ -38958,10 +38949,10 @@
     </row>
     <row r="50" spans="2:5">
       <c r="B50" s="87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>37</v>
@@ -38972,10 +38963,10 @@
     </row>
     <row r="51" spans="2:5">
       <c r="B51" s="87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>38</v>
@@ -38986,10 +38977,10 @@
     </row>
     <row r="52" spans="2:5">
       <c r="B52" s="87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D52" s="91" t="s">
         <v>23</v>
@@ -39000,10 +38991,10 @@
     </row>
     <row r="53" spans="2:5">
       <c r="B53" s="87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D53" s="91" t="s">
         <v>24</v>
@@ -39014,10 +39005,10 @@
     </row>
     <row r="54" spans="2:5">
       <c r="B54" s="87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D54" s="91" t="s">
         <v>25</v>
@@ -39028,10 +39019,10 @@
     </row>
     <row r="55" spans="2:5">
       <c r="B55" s="87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D55" s="91" t="s">
         <v>26</v>
@@ -39042,10 +39033,10 @@
     </row>
     <row r="56" spans="2:5">
       <c r="B56" s="87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D56" s="91" t="s">
         <v>27</v>
@@ -39056,10 +39047,10 @@
     </row>
     <row r="57" spans="2:5">
       <c r="B57" s="87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D57" s="91" t="s">
         <v>28</v>
@@ -39070,10 +39061,10 @@
     </row>
     <row r="58" spans="2:5">
       <c r="B58" s="87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D58" s="91" t="s">
         <v>29</v>
@@ -39084,10 +39075,10 @@
     </row>
     <row r="59" spans="2:5">
       <c r="B59" s="87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D59" s="91" t="s">
         <v>30</v>
@@ -39098,13 +39089,13 @@
     </row>
     <row r="60" spans="2:5">
       <c r="B60" s="87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D60" s="91" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E60" s="89" t="s">
         <v>13</v>
@@ -39112,10 +39103,10 @@
     </row>
     <row r="61" spans="2:5">
       <c r="B61" s="87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D61" s="91" t="s">
         <v>32</v>
@@ -39126,10 +39117,10 @@
     </row>
     <row r="62" spans="2:5">
       <c r="B62" s="87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D62" s="91" t="s">
         <v>33</v>
@@ -39140,10 +39131,10 @@
     </row>
     <row r="63" spans="2:5">
       <c r="B63" s="87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D63" s="91" t="s">
         <v>34</v>
@@ -39154,10 +39145,10 @@
     </row>
     <row r="64" spans="2:5">
       <c r="B64" s="87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D64" s="91" t="s">
         <v>35</v>
@@ -39168,10 +39159,10 @@
     </row>
     <row r="65" spans="2:5">
       <c r="B65" s="87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D65" s="91" t="s">
         <v>36</v>
@@ -39182,10 +39173,10 @@
     </row>
     <row r="66" spans="2:5">
       <c r="B66" s="87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D66" s="91" t="s">
         <v>37</v>
@@ -39196,10 +39187,10 @@
     </row>
     <row r="67" spans="2:5">
       <c r="B67" s="87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D67" s="91" t="s">
         <v>38</v>
@@ -39210,10 +39201,10 @@
     </row>
     <row r="68" spans="2:5">
       <c r="B68" s="87" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D68" s="91" t="s">
         <v>23</v>
@@ -39224,10 +39215,10 @@
     </row>
     <row r="69" spans="2:5">
       <c r="B69" s="87" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D69" s="91" t="s">
         <v>24</v>
@@ -39238,10 +39229,10 @@
     </row>
     <row r="70" spans="2:5">
       <c r="B70" s="87" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D70" s="91" t="s">
         <v>25</v>
@@ -39252,10 +39243,10 @@
     </row>
     <row r="71" spans="2:5">
       <c r="B71" s="87" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D71" s="91" t="s">
         <v>26</v>
@@ -39266,10 +39257,10 @@
     </row>
     <row r="72" spans="2:5">
       <c r="B72" s="87" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D72" s="91" t="s">
         <v>27</v>
@@ -39280,10 +39271,10 @@
     </row>
     <row r="73" spans="2:5">
       <c r="B73" s="87" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D73" s="91" t="s">
         <v>28</v>
@@ -39294,10 +39285,10 @@
     </row>
     <row r="74" spans="2:5">
       <c r="B74" s="87" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D74" s="91" t="s">
         <v>29</v>
@@ -39308,10 +39299,10 @@
     </row>
     <row r="75" spans="2:5">
       <c r="B75" s="87" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D75" s="91" t="s">
         <v>30</v>
@@ -39322,13 +39313,13 @@
     </row>
     <row r="76" spans="2:5">
       <c r="B76" s="87" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D76" s="91" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E76" s="89" t="s">
         <v>13</v>
@@ -39336,10 +39327,10 @@
     </row>
     <row r="77" spans="2:5">
       <c r="B77" s="87" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D77" s="91" t="s">
         <v>32</v>
@@ -39350,10 +39341,10 @@
     </row>
     <row r="78" spans="2:5">
       <c r="B78" s="87" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D78" s="91" t="s">
         <v>33</v>
@@ -39364,10 +39355,10 @@
     </row>
     <row r="79" spans="2:5">
       <c r="B79" s="87" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D79" s="91" t="s">
         <v>34</v>
@@ -39378,10 +39369,10 @@
     </row>
     <row r="80" spans="2:5">
       <c r="B80" s="87" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D80" s="91" t="s">
         <v>35</v>
@@ -39392,10 +39383,10 @@
     </row>
     <row r="81" spans="2:5">
       <c r="B81" s="87" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D81" s="91" t="s">
         <v>36</v>
@@ -39406,10 +39397,10 @@
     </row>
     <row r="82" spans="2:5">
       <c r="B82" s="87" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D82" s="91" t="s">
         <v>37</v>
@@ -39420,10 +39411,10 @@
     </row>
     <row r="83" spans="2:5">
       <c r="B83" s="87" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D83" s="91" t="s">
         <v>38</v>
@@ -39461,34 +39452,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="330"/>
-      <c r="B1" s="350"/>
-      <c r="C1" s="344"/>
-      <c r="D1" s="344"/>
-      <c r="E1" s="344"/>
-      <c r="F1" s="344"/>
-      <c r="G1" s="344"/>
-      <c r="H1" s="344"/>
-      <c r="I1" s="344"/>
-      <c r="J1" s="344"/>
-      <c r="K1" s="344"/>
-      <c r="L1" s="344"/>
-      <c r="M1" s="344"/>
-      <c r="N1" s="344"/>
-      <c r="O1" s="344"/>
-      <c r="P1" s="344"/>
+      <c r="A1" s="325"/>
+      <c r="B1" s="345"/>
+      <c r="C1" s="339"/>
+      <c r="D1" s="339"/>
+      <c r="E1" s="339"/>
+      <c r="F1" s="339"/>
+      <c r="G1" s="339"/>
+      <c r="H1" s="339"/>
+      <c r="I1" s="339"/>
+      <c r="J1" s="339"/>
+      <c r="K1" s="339"/>
+      <c r="L1" s="339"/>
+      <c r="M1" s="339"/>
+      <c r="N1" s="339"/>
+      <c r="O1" s="339"/>
+      <c r="P1" s="339"/>
     </row>
     <row r="2" spans="1:16" ht="13.5" customHeight="1">
-      <c r="A2" s="348"/>
-      <c r="B2" s="349"/>
-      <c r="N2" s="346"/>
-      <c r="O2" s="351"/>
-      <c r="P2" s="349"/>
+      <c r="A2" s="343"/>
+      <c r="B2" s="344"/>
+      <c r="N2" s="341"/>
+      <c r="O2" s="346"/>
+      <c r="P2" s="344"/>
     </row>
     <row r="3" spans="1:16" ht="37.35" customHeight="1">
       <c r="A3" s="37"/>
       <c r="B3" s="495" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C3" s="496"/>
       <c r="D3" s="496"/>
@@ -39507,7 +39498,7 @@
     <row r="4" spans="1:16" ht="7.35" customHeight="1">
       <c r="A4" s="38"/>
       <c r="B4" s="502" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="503"/>
       <c r="D4" s="503"/>
@@ -39521,7 +39512,7 @@
       <c r="L4" s="503"/>
       <c r="M4" s="503"/>
       <c r="N4" s="503"/>
-      <c r="O4" s="345"/>
+      <c r="O4" s="340"/>
     </row>
     <row r="5" spans="1:16" ht="43.5" customHeight="1">
       <c r="A5" s="38"/>
@@ -39538,7 +39529,7 @@
       <c r="L5" s="503"/>
       <c r="M5" s="503"/>
       <c r="N5" s="503"/>
-      <c r="O5" s="345"/>
+      <c r="O5" s="340"/>
     </row>
     <row r="6" spans="1:16" ht="43.5" customHeight="1">
       <c r="A6" s="38"/>
@@ -39555,793 +39546,793 @@
       <c r="L6" s="503"/>
       <c r="M6" s="503"/>
       <c r="N6" s="503"/>
-      <c r="O6" s="345"/>
+      <c r="O6" s="340"/>
     </row>
     <row r="7" spans="1:16" ht="8.1" customHeight="1">
       <c r="A7" s="38"/>
-      <c r="B7" s="335"/>
-      <c r="C7" s="326"/>
-      <c r="D7" s="326"/>
-      <c r="E7" s="326"/>
-      <c r="F7" s="326"/>
-      <c r="G7" s="326"/>
-      <c r="H7" s="326"/>
-      <c r="I7" s="326"/>
-      <c r="J7" s="326"/>
-      <c r="K7" s="326"/>
-      <c r="L7" s="326"/>
-      <c r="M7" s="326"/>
-      <c r="N7" s="326"/>
-      <c r="O7" s="345"/>
+      <c r="B7" s="330"/>
+      <c r="C7" s="321"/>
+      <c r="D7" s="321"/>
+      <c r="E7" s="321"/>
+      <c r="F7" s="321"/>
+      <c r="G7" s="321"/>
+      <c r="H7" s="321"/>
+      <c r="I7" s="321"/>
+      <c r="J7" s="321"/>
+      <c r="K7" s="321"/>
+      <c r="L7" s="321"/>
+      <c r="M7" s="321"/>
+      <c r="N7" s="321"/>
+      <c r="O7" s="340"/>
     </row>
     <row r="8" spans="1:16" ht="32.25" customHeight="1" thickBot="1">
-      <c r="A8" s="334"/>
-      <c r="B8" s="336"/>
-      <c r="O8" s="345"/>
+      <c r="A8" s="329"/>
+      <c r="B8" s="331"/>
+      <c r="O8" s="340"/>
     </row>
     <row r="9" spans="1:16" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A9" s="329"/>
-      <c r="B9" s="336"/>
-      <c r="C9" s="327"/>
+      <c r="A9" s="324"/>
+      <c r="B9" s="331"/>
+      <c r="C9" s="322"/>
       <c r="D9" s="506" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E9" s="504"/>
       <c r="F9" s="504"/>
       <c r="G9" s="505"/>
-      <c r="I9" s="327"/>
+      <c r="I9" s="322"/>
       <c r="J9" s="511" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K9" s="508"/>
       <c r="L9" s="509"/>
       <c r="M9" s="510"/>
-      <c r="O9" s="345"/>
+      <c r="O9" s="340"/>
     </row>
     <row r="10" spans="1:16" ht="37.5" customHeight="1" thickBot="1">
-      <c r="A10" s="329"/>
-      <c r="B10" s="338"/>
+      <c r="A10" s="324"/>
+      <c r="B10" s="333"/>
       <c r="C10" s="75" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D10" s="507"/>
       <c r="E10" s="76" t="s">
+        <v>99</v>
+      </c>
+      <c r="F10" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="F10" s="76" t="s">
+      <c r="G10" s="77" t="s">
         <v>101</v>
       </c>
-      <c r="G10" s="77" t="s">
-        <v>102</v>
-      </c>
       <c r="I10" s="81" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J10" s="512"/>
       <c r="K10" s="82" t="s">
+        <v>99</v>
+      </c>
+      <c r="L10" s="82" t="s">
         <v>100</v>
       </c>
-      <c r="L10" s="82" t="s">
+      <c r="M10" s="83" t="s">
         <v>101</v>
       </c>
-      <c r="M10" s="83" t="s">
-        <v>102</v>
-      </c>
-      <c r="O10" s="345"/>
+      <c r="O10" s="340"/>
     </row>
     <row r="11" spans="1:16" ht="18.75">
-      <c r="A11" s="331"/>
-      <c r="B11" s="336"/>
+      <c r="A11" s="326"/>
+      <c r="B11" s="331"/>
       <c r="C11" s="78" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="79" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E11" s="79" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F11" s="79" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G11" s="80" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I11" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="J11" s="410" t="s">
-        <v>368</v>
-      </c>
-      <c r="K11" s="410" t="s">
-        <v>368</v>
-      </c>
-      <c r="L11" s="410" t="s">
-        <v>368</v>
-      </c>
-      <c r="M11" s="412" t="s">
-        <v>368</v>
-      </c>
-      <c r="O11" s="345"/>
+      <c r="J11" s="405" t="s">
+        <v>367</v>
+      </c>
+      <c r="K11" s="405" t="s">
+        <v>367</v>
+      </c>
+      <c r="L11" s="405" t="s">
+        <v>367</v>
+      </c>
+      <c r="M11" s="407" t="s">
+        <v>367</v>
+      </c>
+      <c r="O11" s="340"/>
     </row>
     <row r="12" spans="1:16" ht="18.75">
       <c r="A12" s="38"/>
-      <c r="B12" s="336"/>
+      <c r="B12" s="331"/>
       <c r="C12" s="40" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E12" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F12" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G12" s="72" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I12" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="411" t="s">
-        <v>377</v>
-      </c>
-      <c r="K12" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="L12" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="M12" s="413" t="s">
-        <v>380</v>
-      </c>
-      <c r="N12" s="346"/>
-      <c r="O12" s="337"/>
+      <c r="J12" s="406" t="s">
+        <v>376</v>
+      </c>
+      <c r="K12" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="L12" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="M12" s="408" t="s">
+        <v>379</v>
+      </c>
+      <c r="N12" s="341"/>
+      <c r="O12" s="332"/>
     </row>
     <row r="13" spans="1:16" ht="18.75">
       <c r="A13" s="38"/>
-      <c r="B13" s="336"/>
+      <c r="B13" s="331"/>
       <c r="C13" s="40" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E13" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F13" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G13" s="72" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I13" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="J13" s="411" t="s">
-        <v>377</v>
-      </c>
-      <c r="K13" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="L13" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="M13" s="413" t="s">
-        <v>380</v>
-      </c>
-      <c r="N13" s="346"/>
-      <c r="O13" s="337"/>
+      <c r="J13" s="406" t="s">
+        <v>376</v>
+      </c>
+      <c r="K13" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="L13" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="M13" s="408" t="s">
+        <v>379</v>
+      </c>
+      <c r="N13" s="341"/>
+      <c r="O13" s="332"/>
     </row>
     <row r="14" spans="1:16" ht="18.75">
-      <c r="A14" s="332"/>
-      <c r="B14" s="336"/>
+      <c r="A14" s="327"/>
+      <c r="B14" s="331"/>
       <c r="C14" s="40" t="s">
         <v>17</v>
       </c>
       <c r="D14" s="71" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E14" s="71" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F14" s="71" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G14" s="72" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I14" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="K14" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="L14" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="M14" s="413" t="s">
-        <v>368</v>
-      </c>
-      <c r="N14" s="346"/>
-      <c r="O14" s="337"/>
+      <c r="J14" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="K14" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="L14" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="M14" s="408" t="s">
+        <v>367</v>
+      </c>
+      <c r="N14" s="341"/>
+      <c r="O14" s="332"/>
     </row>
     <row r="15" spans="1:16" ht="18.75">
       <c r="A15" s="38"/>
-      <c r="B15" s="336"/>
+      <c r="B15" s="331"/>
       <c r="C15" s="67" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D15" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E15" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F15" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G15" s="72" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I15" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="J15" s="411" t="s">
-        <v>377</v>
-      </c>
-      <c r="K15" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="L15" s="411" t="s">
-        <v>380</v>
-      </c>
-      <c r="M15" s="413" t="s">
-        <v>368</v>
-      </c>
-      <c r="N15" s="346"/>
-      <c r="O15" s="337"/>
+      <c r="J15" s="406" t="s">
+        <v>376</v>
+      </c>
+      <c r="K15" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="L15" s="406" t="s">
+        <v>379</v>
+      </c>
+      <c r="M15" s="408" t="s">
+        <v>367</v>
+      </c>
+      <c r="N15" s="341"/>
+      <c r="O15" s="332"/>
     </row>
     <row r="16" spans="1:16" ht="18.75">
       <c r="A16" s="38"/>
-      <c r="B16" s="336"/>
+      <c r="B16" s="331"/>
       <c r="C16" s="67" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D16" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E16" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F16" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G16" s="72" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I16" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="J16" s="411" t="s">
-        <v>378</v>
-      </c>
-      <c r="K16" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="L16" s="411" t="s">
-        <v>376</v>
-      </c>
-      <c r="M16" s="413" t="s">
-        <v>376</v>
-      </c>
-      <c r="N16" s="346"/>
-      <c r="O16" s="337"/>
+      <c r="J16" s="406" t="s">
+        <v>377</v>
+      </c>
+      <c r="K16" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="L16" s="406" t="s">
+        <v>375</v>
+      </c>
+      <c r="M16" s="408" t="s">
+        <v>375</v>
+      </c>
+      <c r="N16" s="341"/>
+      <c r="O16" s="332"/>
     </row>
     <row r="17" spans="1:15" ht="18.75">
       <c r="A17" s="38"/>
-      <c r="B17" s="336"/>
+      <c r="B17" s="331"/>
       <c r="C17" s="67" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D17" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E17" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F17" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G17" s="72" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I17" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="J17" s="411" t="s">
-        <v>378</v>
-      </c>
-      <c r="K17" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="L17" s="411" t="s">
-        <v>376</v>
-      </c>
-      <c r="M17" s="413" t="s">
-        <v>376</v>
-      </c>
-      <c r="N17" s="346"/>
-      <c r="O17" s="337"/>
+      <c r="J17" s="406" t="s">
+        <v>377</v>
+      </c>
+      <c r="K17" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="L17" s="406" t="s">
+        <v>375</v>
+      </c>
+      <c r="M17" s="408" t="s">
+        <v>375</v>
+      </c>
+      <c r="N17" s="341"/>
+      <c r="O17" s="332"/>
     </row>
     <row r="18" spans="1:15" ht="18.75">
       <c r="A18" s="38"/>
-      <c r="B18" s="336"/>
+      <c r="B18" s="331"/>
       <c r="C18" s="67" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D18" s="71" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E18" s="71" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F18" s="71" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G18" s="72" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I18" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="J18" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="K18" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="L18" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="M18" s="413" t="s">
-        <v>368</v>
-      </c>
-      <c r="N18" s="346"/>
-      <c r="O18" s="337"/>
+      <c r="J18" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="K18" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="L18" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="M18" s="408" t="s">
+        <v>367</v>
+      </c>
+      <c r="N18" s="341"/>
+      <c r="O18" s="332"/>
     </row>
     <row r="19" spans="1:15" ht="18.75">
       <c r="A19" s="38"/>
-      <c r="B19" s="336"/>
+      <c r="B19" s="331"/>
       <c r="C19" s="40" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D19" s="71" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E19" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F19" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G19" s="72" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I19" s="41" t="s">
-        <v>225</v>
-      </c>
-      <c r="J19" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="K19" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="L19" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="M19" s="413" t="s">
-        <v>368</v>
-      </c>
-      <c r="N19" s="346"/>
-      <c r="O19" s="337"/>
+        <v>224</v>
+      </c>
+      <c r="J19" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="K19" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="L19" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="M19" s="408" t="s">
+        <v>367</v>
+      </c>
+      <c r="N19" s="341"/>
+      <c r="O19" s="332"/>
     </row>
     <row r="20" spans="1:15" ht="18.75">
       <c r="A20" s="38"/>
-      <c r="B20" s="336"/>
+      <c r="B20" s="331"/>
       <c r="C20" s="40" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D20" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E20" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F20" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G20" s="72" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I20" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="J20" s="411" t="s">
-        <v>373</v>
-      </c>
-      <c r="K20" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="L20" s="411" t="s">
-        <v>380</v>
-      </c>
-      <c r="M20" s="413" t="s">
-        <v>380</v>
-      </c>
-      <c r="N20" s="346"/>
-      <c r="O20" s="337"/>
+      <c r="J20" s="406" t="s">
+        <v>372</v>
+      </c>
+      <c r="K20" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="L20" s="406" t="s">
+        <v>379</v>
+      </c>
+      <c r="M20" s="408" t="s">
+        <v>379</v>
+      </c>
+      <c r="N20" s="341"/>
+      <c r="O20" s="332"/>
     </row>
     <row r="21" spans="1:15" ht="18.75">
       <c r="A21" s="38"/>
-      <c r="B21" s="336"/>
+      <c r="B21" s="331"/>
       <c r="C21" s="39" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D21" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E21" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F21" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G21" s="72" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I21" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="J21" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="K21" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="L21" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="M21" s="413" t="s">
-        <v>368</v>
-      </c>
-      <c r="N21" s="346"/>
-      <c r="O21" s="337"/>
+      <c r="J21" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="K21" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="L21" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="M21" s="408" t="s">
+        <v>367</v>
+      </c>
+      <c r="N21" s="341"/>
+      <c r="O21" s="332"/>
     </row>
     <row r="22" spans="1:15" ht="18.75">
       <c r="A22" s="38"/>
-      <c r="B22" s="336"/>
+      <c r="B22" s="331"/>
       <c r="C22" s="39" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D22" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E22" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F22" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G22" s="72" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I22" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="J22" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="K22" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="L22" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="M22" s="413" t="s">
-        <v>368</v>
-      </c>
-      <c r="N22" s="346"/>
-      <c r="O22" s="337"/>
+      <c r="J22" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="K22" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="L22" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="M22" s="408" t="s">
+        <v>367</v>
+      </c>
+      <c r="N22" s="341"/>
+      <c r="O22" s="332"/>
     </row>
     <row r="23" spans="1:15" ht="18.75">
       <c r="A23" s="38"/>
-      <c r="B23" s="336"/>
+      <c r="B23" s="331"/>
       <c r="C23" s="40" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D23" s="71" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E23" s="71" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F23" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G23" s="72" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I23" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="J23" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="K23" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="L23" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="M23" s="413" t="s">
-        <v>368</v>
-      </c>
-      <c r="N23" s="346"/>
-      <c r="O23" s="337"/>
+      <c r="J23" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="K23" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="L23" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="M23" s="408" t="s">
+        <v>367</v>
+      </c>
+      <c r="N23" s="341"/>
+      <c r="O23" s="332"/>
     </row>
     <row r="24" spans="1:15" ht="18.75">
       <c r="A24" s="38"/>
-      <c r="B24" s="336"/>
+      <c r="B24" s="331"/>
       <c r="C24" s="39" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D24" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E24" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F24" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G24" s="72" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I24" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="J24" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="K24" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="L24" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="M24" s="413" t="s">
-        <v>368</v>
-      </c>
-      <c r="N24" s="346"/>
-      <c r="O24" s="337"/>
+      <c r="J24" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="K24" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="L24" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="M24" s="408" t="s">
+        <v>367</v>
+      </c>
+      <c r="N24" s="341"/>
+      <c r="O24" s="332"/>
     </row>
     <row r="25" spans="1:15" ht="18.75">
       <c r="A25" s="38"/>
-      <c r="B25" s="336"/>
+      <c r="B25" s="331"/>
       <c r="C25" s="39" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D25" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E25" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F25" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G25" s="72" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I25" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="J25" s="411" t="s">
-        <v>373</v>
-      </c>
-      <c r="K25" s="411" t="s">
-        <v>368</v>
-      </c>
-      <c r="L25" s="411" t="s">
-        <v>376</v>
-      </c>
-      <c r="M25" s="413" t="s">
-        <v>368</v>
-      </c>
-      <c r="N25" s="346"/>
-      <c r="O25" s="337"/>
+      <c r="J25" s="406" t="s">
+        <v>372</v>
+      </c>
+      <c r="K25" s="406" t="s">
+        <v>367</v>
+      </c>
+      <c r="L25" s="406" t="s">
+        <v>375</v>
+      </c>
+      <c r="M25" s="408" t="s">
+        <v>367</v>
+      </c>
+      <c r="N25" s="341"/>
+      <c r="O25" s="332"/>
     </row>
     <row r="26" spans="1:15" ht="19.5" thickBot="1">
       <c r="A26" s="38"/>
-      <c r="B26" s="336"/>
+      <c r="B26" s="331"/>
       <c r="C26" s="39" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D26" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E26" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F26" s="71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G26" s="72" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I26" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="J26" s="414" t="s">
-        <v>379</v>
-      </c>
-      <c r="K26" s="414" t="s">
-        <v>368</v>
-      </c>
-      <c r="L26" s="414" t="s">
-        <v>381</v>
-      </c>
-      <c r="M26" s="415" t="s">
-        <v>368</v>
-      </c>
-      <c r="N26" s="346"/>
-      <c r="O26" s="337"/>
+      <c r="J26" s="409" t="s">
+        <v>378</v>
+      </c>
+      <c r="K26" s="409" t="s">
+        <v>367</v>
+      </c>
+      <c r="L26" s="409" t="s">
+        <v>380</v>
+      </c>
+      <c r="M26" s="410" t="s">
+        <v>367</v>
+      </c>
+      <c r="N26" s="341"/>
+      <c r="O26" s="332"/>
     </row>
     <row r="27" spans="1:15" ht="23.25" customHeight="1">
       <c r="A27" s="38"/>
-      <c r="B27" s="336"/>
+      <c r="B27" s="331"/>
       <c r="C27" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="D27" s="71" t="s">
+        <v>371</v>
+      </c>
+      <c r="E27" s="71" t="s">
+        <v>369</v>
+      </c>
+      <c r="F27" s="71" t="s">
         <v>367</v>
       </c>
-      <c r="D27" s="71" t="s">
-        <v>372</v>
-      </c>
-      <c r="E27" s="71" t="s">
-        <v>370</v>
-      </c>
-      <c r="F27" s="71" t="s">
-        <v>368</v>
-      </c>
       <c r="G27" s="72" t="s">
-        <v>370</v>
-      </c>
-      <c r="N27" s="346"/>
-      <c r="O27" s="337"/>
+        <v>369</v>
+      </c>
+      <c r="N27" s="341"/>
+      <c r="O27" s="332"/>
     </row>
     <row r="28" spans="1:15" ht="23.25" customHeight="1" thickBot="1">
       <c r="A28" s="38"/>
-      <c r="B28" s="336"/>
-      <c r="C28" s="408" t="s">
+      <c r="B28" s="331"/>
+      <c r="C28" s="403" t="s">
         <v>20</v>
       </c>
       <c r="D28" s="73" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E28" s="73" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F28" s="73" t="s">
-        <v>368</v>
-      </c>
-      <c r="G28" s="409" t="s">
-        <v>376</v>
-      </c>
-      <c r="N28" s="346"/>
-      <c r="O28" s="337"/>
+        <v>367</v>
+      </c>
+      <c r="G28" s="404" t="s">
+        <v>375</v>
+      </c>
+      <c r="N28" s="341"/>
+      <c r="O28" s="332"/>
     </row>
     <row r="29" spans="1:15" ht="28.5" customHeight="1" thickBot="1">
-      <c r="B29" s="336"/>
-      <c r="N29" s="346"/>
-      <c r="O29" s="337"/>
+      <c r="B29" s="331"/>
+      <c r="N29" s="341"/>
+      <c r="O29" s="332"/>
     </row>
     <row r="30" spans="1:15" ht="42" customHeight="1" thickBot="1">
       <c r="A30" s="38"/>
-      <c r="B30" s="338"/>
+      <c r="B30" s="333"/>
       <c r="C30" s="521" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D30" s="522"/>
       <c r="E30" s="522"/>
       <c r="F30" s="522"/>
       <c r="G30" s="523"/>
-      <c r="N30" s="346"/>
-      <c r="O30" s="337"/>
+      <c r="N30" s="341"/>
+      <c r="O30" s="332"/>
     </row>
     <row r="31" spans="1:15" ht="49.5" customHeight="1">
       <c r="A31" s="38"/>
-      <c r="B31" s="336"/>
+      <c r="B31" s="331"/>
       <c r="C31" s="513" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D31" s="514"/>
       <c r="E31" s="515" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F31" s="515"/>
       <c r="G31" s="516"/>
-      <c r="N31" s="346"/>
-      <c r="O31" s="337"/>
+      <c r="N31" s="341"/>
+      <c r="O31" s="332"/>
     </row>
     <row r="32" spans="1:15" ht="60" customHeight="1">
       <c r="A32" s="38"/>
-      <c r="B32" s="336"/>
+      <c r="B32" s="331"/>
       <c r="C32" s="517" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D32" s="518"/>
       <c r="E32" s="519" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F32" s="519"/>
       <c r="G32" s="520"/>
-      <c r="N32" s="346"/>
-      <c r="O32" s="337"/>
+      <c r="N32" s="341"/>
+      <c r="O32" s="332"/>
     </row>
     <row r="33" spans="1:15" ht="66.75" customHeight="1" thickBot="1">
       <c r="A33" s="38"/>
-      <c r="B33" s="338"/>
+      <c r="B33" s="333"/>
       <c r="C33" s="498" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D33" s="499"/>
       <c r="E33" s="500" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F33" s="500"/>
       <c r="G33" s="501"/>
-      <c r="H33" s="342"/>
-      <c r="J33" s="344"/>
-      <c r="K33" s="344"/>
-      <c r="L33" s="344"/>
-      <c r="M33" s="344"/>
-      <c r="N33" s="344"/>
-      <c r="O33" s="345"/>
+      <c r="H33" s="337"/>
+      <c r="J33" s="339"/>
+      <c r="K33" s="339"/>
+      <c r="L33" s="339"/>
+      <c r="M33" s="339"/>
+      <c r="N33" s="339"/>
+      <c r="O33" s="340"/>
     </row>
     <row r="34" spans="1:15" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A34" s="341"/>
-      <c r="B34" s="347"/>
-      <c r="C34" s="339"/>
-      <c r="D34" s="339"/>
-      <c r="E34" s="339"/>
-      <c r="F34" s="339"/>
-      <c r="G34" s="339"/>
-      <c r="H34" s="339"/>
-      <c r="I34" s="343"/>
-      <c r="J34" s="339"/>
-      <c r="K34" s="339"/>
-      <c r="L34" s="339"/>
-      <c r="M34" s="339"/>
-      <c r="N34" s="339"/>
-      <c r="O34" s="340"/>
+      <c r="A34" s="336"/>
+      <c r="B34" s="342"/>
+      <c r="C34" s="334"/>
+      <c r="D34" s="334"/>
+      <c r="E34" s="334"/>
+      <c r="F34" s="334"/>
+      <c r="G34" s="334"/>
+      <c r="H34" s="334"/>
+      <c r="I34" s="338"/>
+      <c r="J34" s="334"/>
+      <c r="K34" s="334"/>
+      <c r="L34" s="334"/>
+      <c r="M34" s="334"/>
+      <c r="N34" s="334"/>
+      <c r="O34" s="335"/>
     </row>
     <row r="35" spans="1:15" ht="12" customHeight="1">
-      <c r="A35" s="328"/>
+      <c r="A35" s="323"/>
     </row>
     <row r="36" spans="1:15" ht="8.25" customHeight="1"/>
     <row r="38" spans="1:15" ht="3" customHeight="1">
-      <c r="C38" s="333"/>
-      <c r="D38" s="333"/>
-      <c r="E38" s="333"/>
-      <c r="F38" s="333"/>
-      <c r="G38" s="333"/>
-      <c r="H38" s="333"/>
+      <c r="C38" s="328"/>
+      <c r="D38" s="328"/>
+      <c r="E38" s="328"/>
+      <c r="F38" s="328"/>
+      <c r="G38" s="328"/>
+      <c r="H38" s="328"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -40420,7 +40411,7 @@
     </row>
     <row r="2" spans="1:17" ht="36">
       <c r="B2" s="139" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C2" s="139"/>
       <c r="D2" s="98"/>
@@ -40428,7 +40419,7 @@
       <c r="G2" s="106"/>
       <c r="H2" s="98"/>
       <c r="I2" s="538" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J2" s="539"/>
       <c r="K2" s="109"/>
@@ -40442,7 +40433,7 @@
     <row r="3" spans="1:17" s="69" customFormat="1" ht="22.5" customHeight="1">
       <c r="A3" s="101"/>
       <c r="B3" s="69" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D3" s="107"/>
       <c r="E3" s="100"/>
@@ -40461,9 +40452,9 @@
     </row>
     <row r="4" spans="1:17" s="70" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
       <c r="B4" s="156" t="s">
-        <v>122</v>
-      </c>
-      <c r="C4" s="398"/>
+        <v>121</v>
+      </c>
+      <c r="C4" s="393"/>
       <c r="D4" s="238"/>
       <c r="F4" s="237"/>
       <c r="G4" s="127"/>
@@ -40481,29 +40472,29 @@
     <row r="5" spans="1:17" ht="78" customHeight="1" thickBot="1">
       <c r="A5" s="105"/>
       <c r="B5" s="157" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="532" t="s">
         <v>107</v>
-      </c>
-      <c r="C5" s="532" t="s">
-        <v>108</v>
       </c>
       <c r="D5" s="533"/>
       <c r="E5" s="239" t="s">
+        <v>109</v>
+      </c>
+      <c r="F5" s="239" t="s">
+        <v>108</v>
+      </c>
+      <c r="G5" s="239" t="s">
         <v>110</v>
       </c>
-      <c r="F5" s="239" t="s">
-        <v>109</v>
-      </c>
-      <c r="G5" s="239" t="s">
+      <c r="H5" s="240" t="s">
+        <v>175</v>
+      </c>
+      <c r="I5" s="240" t="s">
         <v>111</v>
       </c>
-      <c r="H5" s="240" t="s">
-        <v>176</v>
-      </c>
-      <c r="I5" s="240" t="s">
+      <c r="J5" s="241" t="s">
         <v>112</v>
-      </c>
-      <c r="J5" s="241" t="s">
-        <v>113</v>
       </c>
       <c r="K5" s="242"/>
       <c r="L5" s="98"/>
@@ -40513,8 +40504,8 @@
       <c r="P5" s="123"/>
     </row>
     <row r="6" spans="1:17" ht="51" customHeight="1">
-      <c r="B6" s="268" t="s">
-        <v>114</v>
+      <c r="B6" s="266" t="s">
+        <v>113</v>
       </c>
       <c r="C6" s="534">
         <v>44725</v>
@@ -40548,8 +40539,8 @@
     </row>
     <row r="7" spans="1:17" ht="45.75" customHeight="1">
       <c r="A7" s="115"/>
-      <c r="B7" s="269" t="s">
-        <v>115</v>
+      <c r="B7" s="267" t="s">
+        <v>114</v>
       </c>
       <c r="C7" s="536">
         <v>44789</v>
@@ -40581,8 +40572,8 @@
     </row>
     <row r="8" spans="1:17" ht="44.25" customHeight="1">
       <c r="A8" s="116"/>
-      <c r="B8" s="269" t="s">
-        <v>116</v>
+      <c r="B8" s="267" t="s">
+        <v>115</v>
       </c>
       <c r="C8" s="536">
         <v>44868</v>
@@ -40615,8 +40606,8 @@
     </row>
     <row r="9" spans="1:17" ht="39.75" customHeight="1">
       <c r="A9" s="116"/>
-      <c r="B9" s="269" t="s">
-        <v>117</v>
+      <c r="B9" s="267" t="s">
+        <v>116</v>
       </c>
       <c r="C9" s="536">
         <v>45439</v>
@@ -40650,8 +40641,8 @@
     </row>
     <row r="10" spans="1:17" ht="55.5" customHeight="1">
       <c r="A10" s="118"/>
-      <c r="B10" s="269" t="s">
-        <v>118</v>
+      <c r="B10" s="267" t="s">
+        <v>117</v>
       </c>
       <c r="C10" s="536">
         <v>44900</v>
@@ -40684,8 +40675,8 @@
     </row>
     <row r="11" spans="1:17" ht="44.25" customHeight="1">
       <c r="A11" s="117"/>
-      <c r="B11" s="269" t="s">
-        <v>119</v>
+      <c r="B11" s="267" t="s">
+        <v>118</v>
       </c>
       <c r="C11" s="536">
         <v>44930</v>
@@ -40718,8 +40709,8 @@
     </row>
     <row r="12" spans="1:17" ht="66.75" customHeight="1" thickBot="1">
       <c r="A12" s="116"/>
-      <c r="B12" s="270" t="s">
-        <v>120</v>
+      <c r="B12" s="268" t="s">
+        <v>119</v>
       </c>
       <c r="C12" s="524">
         <v>44958</v>
@@ -40769,12 +40760,12 @@
     </row>
     <row r="14" spans="1:17" ht="30.75" customHeight="1">
       <c r="A14" s="120"/>
-      <c r="B14" s="379" t="s">
+      <c r="B14" s="374" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="394"/>
+      <c r="D14" s="373" t="s">
         <v>125</v>
-      </c>
-      <c r="C14" s="399"/>
-      <c r="D14" s="378" t="s">
-        <v>126</v>
       </c>
       <c r="E14" s="148"/>
       <c r="F14" s="149"/>
@@ -40782,7 +40773,7 @@
       <c r="H14" s="151"/>
       <c r="I14" s="152"/>
       <c r="J14" s="153"/>
-      <c r="K14" s="403"/>
+      <c r="K14" s="398"/>
       <c r="L14" s="98"/>
       <c r="M14" s="98"/>
       <c r="N14" s="125"/>
@@ -40791,15 +40782,15 @@
     </row>
     <row r="15" spans="1:17" ht="8.25" customHeight="1" thickBot="1">
       <c r="A15" s="103"/>
-      <c r="B15" s="380"/>
-      <c r="C15" s="400"/>
-      <c r="D15" s="383"/>
-      <c r="E15" s="384"/>
-      <c r="F15" s="384"/>
-      <c r="G15" s="385"/>
-      <c r="H15" s="384"/>
-      <c r="I15" s="385"/>
-      <c r="J15" s="386"/>
+      <c r="B15" s="375"/>
+      <c r="C15" s="395"/>
+      <c r="D15" s="378"/>
+      <c r="E15" s="379"/>
+      <c r="F15" s="379"/>
+      <c r="G15" s="380"/>
+      <c r="H15" s="379"/>
+      <c r="I15" s="380"/>
+      <c r="J15" s="381"/>
       <c r="L15" s="98"/>
       <c r="M15" s="123"/>
       <c r="N15" s="98"/>
@@ -40808,18 +40799,22 @@
     </row>
     <row r="16" spans="1:17" ht="74.25" customHeight="1" thickBot="1">
       <c r="A16" s="120"/>
-      <c r="B16" s="381" t="s">
-        <v>219</v>
-      </c>
-      <c r="C16" s="401"/>
-      <c r="D16" s="387"/>
-      <c r="E16" s="526"/>
+      <c r="B16" s="376" t="s">
+        <v>218</v>
+      </c>
+      <c r="C16" s="396"/>
+      <c r="D16" s="382" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" s="526" t="s">
+        <v>381</v>
+      </c>
       <c r="F16" s="527"/>
       <c r="G16" s="527"/>
       <c r="H16" s="527"/>
       <c r="I16" s="527"/>
       <c r="J16" s="528"/>
-      <c r="K16" s="404"/>
+      <c r="K16" s="399"/>
       <c r="L16" s="134"/>
       <c r="M16" s="132"/>
       <c r="N16" s="131"/>
@@ -40827,12 +40822,12 @@
     </row>
     <row r="17" spans="1:16" ht="108.75" customHeight="1" thickBot="1">
       <c r="A17" s="103"/>
-      <c r="B17" s="382" t="s">
-        <v>123</v>
-      </c>
-      <c r="C17" s="402"/>
-      <c r="D17" s="387" t="s">
-        <v>107</v>
+      <c r="B17" s="377" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="397"/>
+      <c r="D17" s="382" t="s">
+        <v>114</v>
       </c>
       <c r="E17" s="526" t="s">
         <v>382</v>
@@ -40851,12 +40846,12 @@
     </row>
     <row r="18" spans="1:16" ht="87" customHeight="1" thickBot="1">
       <c r="A18" s="121"/>
-      <c r="B18" s="382" t="s">
-        <v>124</v>
-      </c>
-      <c r="C18" s="402"/>
-      <c r="D18" s="388" t="s">
-        <v>114</v>
+      <c r="B18" s="377" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" s="397"/>
+      <c r="D18" s="383" t="s">
+        <v>115</v>
       </c>
       <c r="E18" s="526" t="s">
         <v>383</v>
@@ -40876,8 +40871,8 @@
       <c r="A19" s="98"/>
       <c r="B19" s="122"/>
       <c r="C19" s="103"/>
-      <c r="D19" s="389" t="s">
-        <v>115</v>
+      <c r="D19" s="384" t="s">
+        <v>116</v>
       </c>
       <c r="E19" s="526" t="s">
         <v>384</v>
@@ -40897,8 +40892,8 @@
     <row r="20" spans="1:16" ht="108" customHeight="1" thickBot="1">
       <c r="A20" s="95"/>
       <c r="B20" s="106"/>
-      <c r="D20" s="388" t="s">
-        <v>116</v>
+      <c r="D20" s="383" t="s">
+        <v>117</v>
       </c>
       <c r="E20" s="526" t="s">
         <v>385</v>
@@ -40908,27 +40903,27 @@
       <c r="H20" s="527"/>
       <c r="I20" s="527"/>
       <c r="J20" s="528"/>
-      <c r="K20" s="405"/>
-      <c r="L20" s="390"/>
+      <c r="K20" s="400"/>
+      <c r="L20" s="385"/>
       <c r="M20" s="133"/>
       <c r="N20" s="131"/>
       <c r="O20" s="129"/>
     </row>
-    <row r="21" spans="1:16" s="279" customFormat="1" ht="81.75" customHeight="1" thickBot="1">
-      <c r="B21" s="280"/>
-      <c r="C21" s="281"/>
-      <c r="D21" s="391" t="s">
-        <v>117</v>
+    <row r="21" spans="1:16" s="277" customFormat="1" ht="81.75" customHeight="1" thickBot="1">
+      <c r="B21" s="278"/>
+      <c r="C21" s="279"/>
+      <c r="D21" s="386" t="s">
+        <v>118</v>
       </c>
       <c r="E21" s="526" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F21" s="527"/>
       <c r="G21" s="527"/>
       <c r="H21" s="527"/>
       <c r="I21" s="527"/>
       <c r="J21" s="528"/>
-      <c r="K21" s="406"/>
+      <c r="K21" s="401"/>
       <c r="L21" s="68"/>
       <c r="M21" s="131"/>
       <c r="N21" s="131"/>
@@ -40938,11 +40933,11 @@
       <c r="A22" s="99"/>
       <c r="B22" s="125"/>
       <c r="C22" s="103"/>
-      <c r="D22" s="407" t="s">
-        <v>118</v>
+      <c r="D22" s="402" t="s">
+        <v>119</v>
       </c>
       <c r="E22" s="526" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F22" s="527"/>
       <c r="G22" s="527"/>

--- a/Backend/output/informe_final.xlsx
+++ b/Backend/output/informe_final.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D42A5960-DF64-402B-8948-C0845645106D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{50F531A4-57E4-4E08-B6EE-DA81EF3F054D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="733" firstSheet="4" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="733" firstSheet="11" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -1325,7 +1325,7 @@
     <t>Acum ABRIL - 2025</t>
   </si>
   <si>
-    <t>Hitos ADP ocurridos al 8 de ABRIL</t>
+    <t>Hitos ADP ocurridos al 9 de ABRIL</t>
   </si>
   <si>
     <t>Política de Gestión de Riesgos</t>
@@ -6630,15 +6630,42 @@
     <xf numFmtId="0" fontId="70" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="78" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6648,36 +6675,9 @@
     <xf numFmtId="0" fontId="34" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="80" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -6795,21 +6795,27 @@
     <xf numFmtId="0" fontId="31" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="243" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="149" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="150" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="69" fillId="0" borderId="123" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="124" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="243" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="149" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="150" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6837,23 +6843,266 @@
     <xf numFmtId="0" fontId="69" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="144" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="145" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="120" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="15" borderId="175" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="142" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="143" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="15" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="173" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="174" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -6861,9 +7110,6 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6915,9 +7161,6 @@
     <xf numFmtId="0" fontId="42" fillId="12" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="49" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -6942,249 +7185,6 @@
     <xf numFmtId="0" fontId="52" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="15" borderId="175" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="142" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="143" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="15" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="173" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="174" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="144" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="145" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="120" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -7197,6 +7197,111 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="205" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="236" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="195" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="202" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="200" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="199" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="219" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="190" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="218" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="220" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="204" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="197" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="4" borderId="185" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="200" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="199" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="164" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="198" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="201" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="4" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -7230,115 +7335,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="197" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="66" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="4" borderId="185" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="200" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="199" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="164" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="198" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="201" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="202" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="204" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="219" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="220" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="205" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="236" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="195" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="200" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="199" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="190" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="218" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -13083,7 +13083,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CB06C2E6-1E7D-4A4D-AB80-B09E852CEF0C}" type="CELLRANGE">
+                    <a:fld id="{2D9496E2-8B54-410D-B43B-EC89CAC64382}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13117,7 +13117,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{87BAEF73-8224-4BA1-A227-D9D2BBFFC837}" type="CELLRANGE">
+                    <a:fld id="{8873FA30-3BC9-4E58-83A2-A8C4C691EFDF}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13151,7 +13151,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{976CF574-3B49-4C8B-B8B0-89A85371BEF8}" type="CELLRANGE">
+                    <a:fld id="{11947890-B2A4-4D78-952F-13A1FBB9DE42}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13185,7 +13185,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{30AA0A42-41AC-4566-887A-2ACE757A0C9B}" type="CELLRANGE">
+                    <a:fld id="{F9AD79E8-6A0F-4699-9A6B-48E691122336}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13219,7 +13219,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{553D689C-50F4-496B-BBF5-0619F37B8A4F}" type="CELLRANGE">
+                    <a:fld id="{B77911A2-55C5-4A35-8592-8F37BED85D22}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13253,7 +13253,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B72AF6A3-3CF1-48DB-A02E-3575F5AF4027}" type="CELLRANGE">
+                    <a:fld id="{093A43F7-F642-46E7-A1D2-9D00F218B30D}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13287,7 +13287,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{43DB766B-FB6B-423E-9913-FF5982720AA9}" type="CELLRANGE">
+                    <a:fld id="{3115F790-5A34-4D1B-B505-31D790AE6C2D}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13321,7 +13321,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{98535E82-2BEE-4694-BE9C-9ECB12567F2F}" type="CELLRANGE">
+                    <a:fld id="{FB9E8F68-FEC4-4167-8035-5364047EFFA5}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13355,7 +13355,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{ACE6F29D-CF83-43B1-BCA7-E9A677E4D13F}" type="CELLRANGE">
+                    <a:fld id="{EF6AECF0-07E8-4CEF-97DF-5CDDCD079C7B}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13389,7 +13389,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{13D106E3-9DA2-48E0-815A-20118F4C71B6}" type="CELLRANGE">
+                    <a:fld id="{388531D0-D152-494C-9878-EB3251A7E288}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13423,7 +13423,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8CA606A2-FEA6-4F03-833C-83BF173C37B9}" type="CELLRANGE">
+                    <a:fld id="{9381E986-76A2-4BF1-BA3F-6F7B458E2D1C}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13457,7 +13457,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CE7D12D1-E966-4DFE-A925-C49FA33487C4}" type="CELLRANGE">
+                    <a:fld id="{683F0BDD-38F1-4929-8DA9-81441535400B}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13840,7 +13840,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9544A587-8AF7-4128-897B-A054C1528D37}" type="CELLRANGE">
+                    <a:fld id="{6FACC62E-2DD8-481F-9050-ED16B70F26A1}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14557,7 +14557,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{8D4BF037-6365-4A02-9B44-3D5C8A287B38}" type="CELLRANGE">
+                    <a:fld id="{C99019EA-68C2-47F9-88D9-7E1332B9E9B2}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr>
                         <a:defRPr sz="1400">
@@ -14637,7 +14637,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{12940128-3CD8-4C53-8407-27EE0764C40F}" type="CELLRANGE">
+                    <a:fld id="{4379CD8A-3DA2-49F6-A5F1-86A3EB5FC8AD}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -23390,7 +23390,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C3:D5" spid="_x0000_s286673"/>
+                  <a14:cameraTool cellRange="data_status_NC!C3:D5" spid="_x0000_s286681"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23446,7 +23446,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C20:D24" spid="_x0000_s286674"/>
+                  <a14:cameraTool cellRange="data_status_NC!C20:D24" spid="_x0000_s286682"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23511,7 +23511,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C7:D13" spid="_x0000_s286675"/>
+                  <a14:cameraTool cellRange="data_status_NC!C7:D13" spid="_x0000_s286683"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23576,7 +23576,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C15:D18" spid="_x0000_s286676"/>
+                  <a14:cameraTool cellRange="data_status_NC!C15:D18" spid="_x0000_s286684"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23641,7 +23641,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C26:D33" spid="_x0000_s286677"/>
+                  <a14:cameraTool cellRange="data_status_NC!C26:D33" spid="_x0000_s286685"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23706,7 +23706,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C35:D39" spid="_x0000_s286678"/>
+                  <a14:cameraTool cellRange="data_status_NC!C35:D39" spid="_x0000_s286686"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23771,7 +23771,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C41:D46" spid="_x0000_s286679"/>
+                  <a14:cameraTool cellRange="data_status_NC!C41:D46" spid="_x0000_s286687"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -23836,7 +23836,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C48:D54" spid="_x0000_s286680"/>
+                  <a14:cameraTool cellRange="data_status_NC!C48:D54" spid="_x0000_s286688"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -26469,7 +26469,7 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>672354</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>311727</xdr:rowOff>
+      <xdr:rowOff>311728</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -28055,32 +28055,32 @@
   <sheetData>
     <row r="1" spans="1:28" ht="29.25" customHeight="1" thickBot="1">
       <c r="A1" s="206"/>
-      <c r="B1" s="549" t="s">
+      <c r="B1" s="631" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="550"/>
-      <c r="D1" s="550"/>
-      <c r="E1" s="550"/>
-      <c r="F1" s="550"/>
-      <c r="G1" s="550"/>
-      <c r="H1" s="550"/>
-      <c r="I1" s="550"/>
-      <c r="J1" s="550"/>
-      <c r="K1" s="550"/>
-      <c r="L1" s="550"/>
-      <c r="M1" s="550"/>
-      <c r="N1" s="550"/>
-      <c r="O1" s="550"/>
-      <c r="P1" s="550"/>
-      <c r="Q1" s="550"/>
-      <c r="R1" s="550"/>
-      <c r="S1" s="550"/>
-      <c r="T1" s="550"/>
-      <c r="U1" s="550"/>
-      <c r="V1" s="550"/>
-      <c r="W1" s="550"/>
-      <c r="X1" s="550"/>
-      <c r="Y1" s="551"/>
+      <c r="C1" s="632"/>
+      <c r="D1" s="632"/>
+      <c r="E1" s="632"/>
+      <c r="F1" s="632"/>
+      <c r="G1" s="632"/>
+      <c r="H1" s="632"/>
+      <c r="I1" s="632"/>
+      <c r="J1" s="632"/>
+      <c r="K1" s="632"/>
+      <c r="L1" s="632"/>
+      <c r="M1" s="632"/>
+      <c r="N1" s="632"/>
+      <c r="O1" s="632"/>
+      <c r="P1" s="632"/>
+      <c r="Q1" s="632"/>
+      <c r="R1" s="632"/>
+      <c r="S1" s="632"/>
+      <c r="T1" s="632"/>
+      <c r="U1" s="632"/>
+      <c r="V1" s="632"/>
+      <c r="W1" s="632"/>
+      <c r="X1" s="632"/>
+      <c r="Y1" s="633"/>
       <c r="Z1" s="201"/>
     </row>
     <row r="2" spans="1:28" ht="9" customHeight="1" thickBot="1">
@@ -28116,32 +28116,32 @@
       <c r="A3" s="207" t="s">
         <v>171</v>
       </c>
-      <c r="B3" s="552" t="s">
+      <c r="B3" s="634" t="s">
         <v>211</v>
       </c>
-      <c r="C3" s="553"/>
-      <c r="D3" s="553"/>
-      <c r="E3" s="553"/>
-      <c r="F3" s="553"/>
-      <c r="G3" s="553"/>
-      <c r="H3" s="553"/>
-      <c r="I3" s="553"/>
-      <c r="J3" s="553"/>
-      <c r="K3" s="553"/>
-      <c r="L3" s="553"/>
-      <c r="M3" s="553"/>
-      <c r="N3" s="553"/>
-      <c r="O3" s="553"/>
-      <c r="P3" s="553"/>
-      <c r="Q3" s="553"/>
-      <c r="R3" s="553"/>
-      <c r="S3" s="553"/>
-      <c r="T3" s="553"/>
-      <c r="U3" s="553"/>
-      <c r="V3" s="553"/>
-      <c r="W3" s="553"/>
-      <c r="X3" s="553"/>
-      <c r="Y3" s="554"/>
+      <c r="C3" s="635"/>
+      <c r="D3" s="635"/>
+      <c r="E3" s="635"/>
+      <c r="F3" s="635"/>
+      <c r="G3" s="635"/>
+      <c r="H3" s="635"/>
+      <c r="I3" s="635"/>
+      <c r="J3" s="635"/>
+      <c r="K3" s="635"/>
+      <c r="L3" s="635"/>
+      <c r="M3" s="635"/>
+      <c r="N3" s="635"/>
+      <c r="O3" s="635"/>
+      <c r="P3" s="635"/>
+      <c r="Q3" s="635"/>
+      <c r="R3" s="635"/>
+      <c r="S3" s="635"/>
+      <c r="T3" s="635"/>
+      <c r="U3" s="635"/>
+      <c r="V3" s="635"/>
+      <c r="W3" s="635"/>
+      <c r="X3" s="635"/>
+      <c r="Y3" s="636"/>
       <c r="Z3" s="202"/>
       <c r="AA3" s="119"/>
     </row>
@@ -28149,32 +28149,32 @@
       <c r="A4" s="208" t="s">
         <v>172</v>
       </c>
-      <c r="B4" s="555" t="s">
+      <c r="B4" s="637" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="556"/>
-      <c r="D4" s="556"/>
-      <c r="E4" s="556"/>
-      <c r="F4" s="556"/>
-      <c r="G4" s="556"/>
-      <c r="H4" s="556"/>
-      <c r="I4" s="556"/>
-      <c r="J4" s="556"/>
-      <c r="K4" s="556"/>
-      <c r="L4" s="556"/>
-      <c r="M4" s="556"/>
-      <c r="N4" s="556"/>
-      <c r="O4" s="556"/>
-      <c r="P4" s="556"/>
-      <c r="Q4" s="556"/>
-      <c r="R4" s="556"/>
-      <c r="S4" s="556"/>
-      <c r="T4" s="556"/>
-      <c r="U4" s="556"/>
-      <c r="V4" s="556"/>
-      <c r="W4" s="556"/>
-      <c r="X4" s="556"/>
-      <c r="Y4" s="557"/>
+      <c r="C4" s="638"/>
+      <c r="D4" s="638"/>
+      <c r="E4" s="638"/>
+      <c r="F4" s="638"/>
+      <c r="G4" s="638"/>
+      <c r="H4" s="638"/>
+      <c r="I4" s="638"/>
+      <c r="J4" s="638"/>
+      <c r="K4" s="638"/>
+      <c r="L4" s="638"/>
+      <c r="M4" s="638"/>
+      <c r="N4" s="638"/>
+      <c r="O4" s="638"/>
+      <c r="P4" s="638"/>
+      <c r="Q4" s="638"/>
+      <c r="R4" s="638"/>
+      <c r="S4" s="638"/>
+      <c r="T4" s="638"/>
+      <c r="U4" s="638"/>
+      <c r="V4" s="638"/>
+      <c r="W4" s="638"/>
+      <c r="X4" s="638"/>
+      <c r="Y4" s="639"/>
       <c r="Z4" s="203"/>
       <c r="AA4" s="119"/>
     </row>
@@ -28209,40 +28209,40 @@
     </row>
     <row r="6" spans="1:28" ht="24.75" customHeight="1" thickBot="1">
       <c r="A6" s="209"/>
-      <c r="B6" s="561" t="s">
+      <c r="B6" s="643" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="562"/>
-      <c r="D6" s="562"/>
-      <c r="E6" s="563"/>
+      <c r="C6" s="644"/>
+      <c r="D6" s="644"/>
+      <c r="E6" s="645"/>
       <c r="F6" s="105"/>
       <c r="G6" s="168"/>
-      <c r="H6" s="581" t="s">
+      <c r="H6" s="609" t="s">
         <v>133</v>
       </c>
-      <c r="I6" s="582"/>
-      <c r="J6" s="582"/>
-      <c r="K6" s="583"/>
+      <c r="I6" s="610"/>
+      <c r="J6" s="610"/>
+      <c r="K6" s="611"/>
       <c r="L6" s="105"/>
       <c r="M6" s="168"/>
-      <c r="N6" s="589" t="s">
+      <c r="N6" s="621" t="s">
         <v>152</v>
       </c>
-      <c r="O6" s="590"/>
-      <c r="P6" s="591"/>
+      <c r="O6" s="622"/>
+      <c r="P6" s="623"/>
       <c r="Q6" s="175"/>
       <c r="R6" s="177"/>
-      <c r="S6" s="541" t="s">
+      <c r="S6" s="616" t="s">
         <v>134</v>
       </c>
-      <c r="T6" s="542"/>
+      <c r="T6" s="617"/>
       <c r="U6" s="178"/>
       <c r="V6" s="182"/>
       <c r="W6" s="169"/>
-      <c r="X6" s="541" t="s">
+      <c r="X6" s="616" t="s">
         <v>135</v>
       </c>
-      <c r="Y6" s="542"/>
+      <c r="Y6" s="617"/>
       <c r="Z6" s="96"/>
       <c r="AA6" s="119"/>
     </row>
@@ -28262,36 +28262,36 @@
       </c>
       <c r="F7" s="105"/>
       <c r="G7" s="135"/>
-      <c r="H7" s="577">
+      <c r="H7" s="618">
         <f>I23</f>
         <v>68</v>
       </c>
-      <c r="I7" s="588"/>
-      <c r="J7" s="588"/>
-      <c r="K7" s="578"/>
+      <c r="I7" s="620"/>
+      <c r="J7" s="620"/>
+      <c r="K7" s="619"/>
       <c r="L7" s="105"/>
       <c r="M7" s="135"/>
-      <c r="N7" s="573">
+      <c r="N7" s="624">
         <f>L23</f>
         <v>187</v>
       </c>
-      <c r="O7" s="574"/>
-      <c r="P7" s="575"/>
+      <c r="O7" s="625"/>
+      <c r="P7" s="626"/>
       <c r="Q7" s="176"/>
       <c r="R7" s="178"/>
-      <c r="S7" s="577">
+      <c r="S7" s="618">
         <f>O23</f>
         <v>473</v>
       </c>
-      <c r="T7" s="578"/>
+      <c r="T7" s="619"/>
       <c r="U7" s="105"/>
       <c r="V7" s="181"/>
       <c r="W7" s="98"/>
-      <c r="X7" s="577">
+      <c r="X7" s="618">
         <f>R23</f>
         <v>526</v>
       </c>
-      <c r="Y7" s="578"/>
+      <c r="Y7" s="619"/>
       <c r="Z7" s="167"/>
       <c r="AA7" s="119"/>
     </row>
@@ -28378,27 +28378,27 @@
       </c>
       <c r="E10" s="231"/>
       <c r="F10" s="105"/>
-      <c r="G10" s="569" t="s">
+      <c r="G10" s="650" t="s">
         <v>136</v>
       </c>
-      <c r="H10" s="570"/>
-      <c r="I10" s="570"/>
-      <c r="J10" s="570"/>
-      <c r="K10" s="570"/>
-      <c r="L10" s="570"/>
-      <c r="M10" s="570"/>
-      <c r="N10" s="570"/>
-      <c r="O10" s="570"/>
-      <c r="P10" s="570"/>
-      <c r="Q10" s="570"/>
-      <c r="R10" s="570"/>
-      <c r="S10" s="570"/>
-      <c r="T10" s="570"/>
-      <c r="U10" s="570"/>
-      <c r="V10" s="570"/>
-      <c r="W10" s="570"/>
-      <c r="X10" s="570"/>
-      <c r="Y10" s="571"/>
+      <c r="H10" s="651"/>
+      <c r="I10" s="651"/>
+      <c r="J10" s="651"/>
+      <c r="K10" s="651"/>
+      <c r="L10" s="651"/>
+      <c r="M10" s="651"/>
+      <c r="N10" s="651"/>
+      <c r="O10" s="651"/>
+      <c r="P10" s="651"/>
+      <c r="Q10" s="651"/>
+      <c r="R10" s="651"/>
+      <c r="S10" s="651"/>
+      <c r="T10" s="651"/>
+      <c r="U10" s="651"/>
+      <c r="V10" s="651"/>
+      <c r="W10" s="651"/>
+      <c r="X10" s="651"/>
+      <c r="Y10" s="652"/>
       <c r="Z10" s="96"/>
       <c r="AA10" s="119"/>
     </row>
@@ -28415,35 +28415,35 @@
       </c>
       <c r="E11" s="231"/>
       <c r="F11" s="105"/>
-      <c r="G11" s="572" t="s">
+      <c r="G11" s="653" t="s">
         <v>137</v>
       </c>
-      <c r="H11" s="567"/>
-      <c r="I11" s="567" t="s">
+      <c r="H11" s="648"/>
+      <c r="I11" s="648" t="s">
         <v>138</v>
       </c>
-      <c r="J11" s="567"/>
-      <c r="K11" s="567"/>
-      <c r="L11" s="567" t="s">
+      <c r="J11" s="648"/>
+      <c r="K11" s="648"/>
+      <c r="L11" s="648" t="s">
         <v>139</v>
       </c>
-      <c r="M11" s="567"/>
-      <c r="N11" s="567"/>
-      <c r="O11" s="567" t="s">
+      <c r="M11" s="648"/>
+      <c r="N11" s="648"/>
+      <c r="O11" s="648" t="s">
         <v>140</v>
       </c>
-      <c r="P11" s="567"/>
-      <c r="Q11" s="567"/>
-      <c r="R11" s="567" t="s">
+      <c r="P11" s="648"/>
+      <c r="Q11" s="648"/>
+      <c r="R11" s="648" t="s">
         <v>135</v>
       </c>
-      <c r="S11" s="567"/>
-      <c r="T11" s="567"/>
-      <c r="U11" s="567"/>
-      <c r="V11" s="567"/>
-      <c r="W11" s="567"/>
-      <c r="X11" s="567"/>
-      <c r="Y11" s="568"/>
+      <c r="S11" s="648"/>
+      <c r="T11" s="648"/>
+      <c r="U11" s="648"/>
+      <c r="V11" s="648"/>
+      <c r="W11" s="648"/>
+      <c r="X11" s="648"/>
+      <c r="Y11" s="649"/>
       <c r="Z11" s="96"/>
       <c r="AA11" s="119"/>
     </row>
@@ -28460,33 +28460,33 @@
       </c>
       <c r="E12" s="231"/>
       <c r="F12" s="105"/>
-      <c r="G12" s="572"/>
-      <c r="H12" s="567"/>
-      <c r="I12" s="567"/>
-      <c r="J12" s="567"/>
-      <c r="K12" s="567"/>
-      <c r="L12" s="567"/>
-      <c r="M12" s="567"/>
-      <c r="N12" s="567"/>
-      <c r="O12" s="567"/>
-      <c r="P12" s="567"/>
-      <c r="Q12" s="567"/>
-      <c r="R12" s="543" t="s">
+      <c r="G12" s="653"/>
+      <c r="H12" s="648"/>
+      <c r="I12" s="648"/>
+      <c r="J12" s="648"/>
+      <c r="K12" s="648"/>
+      <c r="L12" s="648"/>
+      <c r="M12" s="648"/>
+      <c r="N12" s="648"/>
+      <c r="O12" s="648"/>
+      <c r="P12" s="648"/>
+      <c r="Q12" s="648"/>
+      <c r="R12" s="575" t="s">
         <v>141</v>
       </c>
-      <c r="S12" s="543"/>
-      <c r="T12" s="543" t="s">
+      <c r="S12" s="575"/>
+      <c r="T12" s="575" t="s">
         <v>142</v>
       </c>
-      <c r="U12" s="543"/>
-      <c r="V12" s="543" t="s">
+      <c r="U12" s="575"/>
+      <c r="V12" s="575" t="s">
         <v>143</v>
       </c>
-      <c r="W12" s="543"/>
-      <c r="X12" s="543" t="s">
+      <c r="W12" s="575"/>
+      <c r="X12" s="575" t="s">
         <v>144</v>
       </c>
-      <c r="Y12" s="564"/>
+      <c r="Y12" s="606"/>
       <c r="Z12" s="96"/>
       <c r="AA12" s="95"/>
     </row>
@@ -28503,25 +28503,25 @@
       </c>
       <c r="E13" s="231"/>
       <c r="F13" s="105"/>
-      <c r="G13" s="572"/>
-      <c r="H13" s="567"/>
-      <c r="I13" s="567"/>
-      <c r="J13" s="567"/>
-      <c r="K13" s="567"/>
-      <c r="L13" s="567"/>
-      <c r="M13" s="567"/>
-      <c r="N13" s="567"/>
-      <c r="O13" s="567"/>
-      <c r="P13" s="567"/>
-      <c r="Q13" s="567"/>
-      <c r="R13" s="543"/>
-      <c r="S13" s="543"/>
-      <c r="T13" s="543"/>
-      <c r="U13" s="543"/>
-      <c r="V13" s="543"/>
-      <c r="W13" s="543"/>
-      <c r="X13" s="565"/>
-      <c r="Y13" s="566"/>
+      <c r="G13" s="653"/>
+      <c r="H13" s="648"/>
+      <c r="I13" s="648"/>
+      <c r="J13" s="648"/>
+      <c r="K13" s="648"/>
+      <c r="L13" s="648"/>
+      <c r="M13" s="648"/>
+      <c r="N13" s="648"/>
+      <c r="O13" s="648"/>
+      <c r="P13" s="648"/>
+      <c r="Q13" s="648"/>
+      <c r="R13" s="575"/>
+      <c r="S13" s="575"/>
+      <c r="T13" s="575"/>
+      <c r="U13" s="575"/>
+      <c r="V13" s="575"/>
+      <c r="W13" s="575"/>
+      <c r="X13" s="646"/>
+      <c r="Y13" s="647"/>
       <c r="Z13" s="96"/>
       <c r="AA13" s="97"/>
     </row>
@@ -28538,41 +28538,41 @@
       </c>
       <c r="E14" s="231"/>
       <c r="F14" s="105"/>
-      <c r="G14" s="544" t="s">
+      <c r="G14" s="627" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="545"/>
-      <c r="I14" s="546">
+      <c r="H14" s="628"/>
+      <c r="I14" s="605">
         <v>4</v>
       </c>
-      <c r="J14" s="547"/>
-      <c r="K14" s="548"/>
-      <c r="L14" s="540">
+      <c r="J14" s="629"/>
+      <c r="K14" s="630"/>
+      <c r="L14" s="603">
         <v>8</v>
       </c>
-      <c r="M14" s="540"/>
-      <c r="N14" s="540"/>
-      <c r="O14" s="540">
+      <c r="M14" s="603"/>
+      <c r="N14" s="603"/>
+      <c r="O14" s="603">
         <v>30</v>
       </c>
-      <c r="P14" s="540"/>
-      <c r="Q14" s="540"/>
-      <c r="R14" s="540">
+      <c r="P14" s="603"/>
+      <c r="Q14" s="603"/>
+      <c r="R14" s="603">
         <v>53</v>
       </c>
-      <c r="S14" s="540"/>
-      <c r="T14" s="540">
+      <c r="S14" s="603"/>
+      <c r="T14" s="603">
         <v>0</v>
       </c>
-      <c r="U14" s="540"/>
-      <c r="V14" s="540">
+      <c r="U14" s="603"/>
+      <c r="V14" s="603">
         <v>8</v>
       </c>
-      <c r="W14" s="546"/>
-      <c r="X14" s="540">
+      <c r="W14" s="605"/>
+      <c r="X14" s="603">
         <v>2</v>
       </c>
-      <c r="Y14" s="576"/>
+      <c r="Y14" s="604"/>
       <c r="Z14" s="96"/>
     </row>
     <row r="15" spans="1:28" ht="19.5" customHeight="1" thickBot="1">
@@ -28588,41 +28588,41 @@
       </c>
       <c r="E15" s="232"/>
       <c r="F15" s="105"/>
-      <c r="G15" s="544" t="s">
+      <c r="G15" s="627" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="545"/>
-      <c r="I15" s="546">
+      <c r="H15" s="628"/>
+      <c r="I15" s="605">
         <v>11</v>
       </c>
-      <c r="J15" s="547"/>
-      <c r="K15" s="548"/>
-      <c r="L15" s="540">
+      <c r="J15" s="629"/>
+      <c r="K15" s="630"/>
+      <c r="L15" s="603">
         <v>30</v>
       </c>
-      <c r="M15" s="540"/>
-      <c r="N15" s="540"/>
-      <c r="O15" s="540">
+      <c r="M15" s="603"/>
+      <c r="N15" s="603"/>
+      <c r="O15" s="603">
         <v>105</v>
       </c>
-      <c r="P15" s="540"/>
-      <c r="Q15" s="540"/>
-      <c r="R15" s="540">
+      <c r="P15" s="603"/>
+      <c r="Q15" s="603"/>
+      <c r="R15" s="603">
         <v>105</v>
       </c>
-      <c r="S15" s="540"/>
-      <c r="T15" s="540">
+      <c r="S15" s="603"/>
+      <c r="T15" s="603">
         <v>8</v>
       </c>
-      <c r="U15" s="540"/>
-      <c r="V15" s="540">
+      <c r="U15" s="603"/>
+      <c r="V15" s="603">
         <v>0</v>
       </c>
-      <c r="W15" s="546"/>
-      <c r="X15" s="540">
+      <c r="W15" s="605"/>
+      <c r="X15" s="603">
         <v>4</v>
       </c>
-      <c r="Y15" s="576"/>
+      <c r="Y15" s="604"/>
       <c r="Z15" s="96"/>
       <c r="AA15" s="119"/>
     </row>
@@ -28633,89 +28633,89 @@
       <c r="D16" s="125"/>
       <c r="E16" s="125"/>
       <c r="F16" s="95"/>
-      <c r="G16" s="544" t="s">
+      <c r="G16" s="627" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="545"/>
-      <c r="I16" s="546">
+      <c r="H16" s="628"/>
+      <c r="I16" s="605">
         <v>19</v>
       </c>
-      <c r="J16" s="547"/>
-      <c r="K16" s="548"/>
-      <c r="L16" s="540">
+      <c r="J16" s="629"/>
+      <c r="K16" s="630"/>
+      <c r="L16" s="603">
         <v>58</v>
       </c>
-      <c r="M16" s="540"/>
-      <c r="N16" s="540"/>
-      <c r="O16" s="540">
+      <c r="M16" s="603"/>
+      <c r="N16" s="603"/>
+      <c r="O16" s="603">
         <v>99</v>
       </c>
-      <c r="P16" s="540"/>
-      <c r="Q16" s="540"/>
-      <c r="R16" s="540">
+      <c r="P16" s="603"/>
+      <c r="Q16" s="603"/>
+      <c r="R16" s="603">
         <v>107</v>
       </c>
-      <c r="S16" s="540"/>
-      <c r="T16" s="540">
+      <c r="S16" s="603"/>
+      <c r="T16" s="603">
         <v>8</v>
       </c>
-      <c r="U16" s="540"/>
-      <c r="V16" s="540">
+      <c r="U16" s="603"/>
+      <c r="V16" s="603">
         <v>6</v>
       </c>
-      <c r="W16" s="546"/>
-      <c r="X16" s="540">
+      <c r="W16" s="605"/>
+      <c r="X16" s="603">
         <v>7</v>
       </c>
-      <c r="Y16" s="576"/>
+      <c r="Y16" s="604"/>
       <c r="Z16" s="96"/>
       <c r="AA16" s="119"/>
       <c r="AB16" s="226"/>
     </row>
     <row r="17" spans="1:27" ht="21" customHeight="1">
       <c r="A17" s="95"/>
-      <c r="B17" s="558" t="s">
+      <c r="B17" s="640" t="s">
         <v>146</v>
       </c>
-      <c r="C17" s="559"/>
-      <c r="D17" s="559"/>
-      <c r="E17" s="560"/>
+      <c r="C17" s="641"/>
+      <c r="D17" s="641"/>
+      <c r="E17" s="642"/>
       <c r="F17" s="105"/>
-      <c r="G17" s="544" t="s">
+      <c r="G17" s="627" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="545"/>
-      <c r="I17" s="546">
+      <c r="H17" s="628"/>
+      <c r="I17" s="605">
         <v>15</v>
       </c>
-      <c r="J17" s="547"/>
-      <c r="K17" s="548"/>
-      <c r="L17" s="540">
+      <c r="J17" s="629"/>
+      <c r="K17" s="630"/>
+      <c r="L17" s="603">
         <v>49</v>
       </c>
-      <c r="M17" s="540"/>
-      <c r="N17" s="540"/>
-      <c r="O17" s="540">
+      <c r="M17" s="603"/>
+      <c r="N17" s="603"/>
+      <c r="O17" s="603">
         <v>127</v>
       </c>
-      <c r="P17" s="540"/>
-      <c r="Q17" s="540"/>
-      <c r="R17" s="540">
+      <c r="P17" s="603"/>
+      <c r="Q17" s="603"/>
+      <c r="R17" s="603">
         <v>134</v>
       </c>
-      <c r="S17" s="540"/>
-      <c r="T17" s="540">
+      <c r="S17" s="603"/>
+      <c r="T17" s="603">
         <v>12</v>
       </c>
-      <c r="U17" s="540"/>
-      <c r="V17" s="540">
+      <c r="U17" s="603"/>
+      <c r="V17" s="603">
         <v>5</v>
       </c>
-      <c r="W17" s="546"/>
-      <c r="X17" s="540">
+      <c r="W17" s="605"/>
+      <c r="X17" s="603">
         <v>7</v>
       </c>
-      <c r="Y17" s="576"/>
+      <c r="Y17" s="604"/>
       <c r="Z17" s="96"/>
       <c r="AA17" s="119"/>
     </row>
@@ -28734,41 +28734,41 @@
         <v>148</v>
       </c>
       <c r="F18" s="105"/>
-      <c r="G18" s="544" t="s">
+      <c r="G18" s="627" t="s">
         <v>402</v>
       </c>
-      <c r="H18" s="545"/>
-      <c r="I18" s="546">
+      <c r="H18" s="628"/>
+      <c r="I18" s="605">
         <v>1</v>
       </c>
-      <c r="J18" s="547"/>
-      <c r="K18" s="548"/>
-      <c r="L18" s="540">
+      <c r="J18" s="629"/>
+      <c r="K18" s="630"/>
+      <c r="L18" s="603">
         <v>2</v>
       </c>
-      <c r="M18" s="540"/>
-      <c r="N18" s="540"/>
-      <c r="O18" s="540">
+      <c r="M18" s="603"/>
+      <c r="N18" s="603"/>
+      <c r="O18" s="603">
         <v>4</v>
       </c>
-      <c r="P18" s="540"/>
-      <c r="Q18" s="540"/>
-      <c r="R18" s="540">
+      <c r="P18" s="603"/>
+      <c r="Q18" s="603"/>
+      <c r="R18" s="603">
         <v>4</v>
       </c>
-      <c r="S18" s="540"/>
-      <c r="T18" s="540">
+      <c r="S18" s="603"/>
+      <c r="T18" s="603">
         <v>0</v>
       </c>
-      <c r="U18" s="540"/>
-      <c r="V18" s="540">
+      <c r="U18" s="603"/>
+      <c r="V18" s="603">
         <v>2</v>
       </c>
-      <c r="W18" s="546"/>
-      <c r="X18" s="540">
+      <c r="W18" s="605"/>
+      <c r="X18" s="603">
         <v>2</v>
       </c>
-      <c r="Y18" s="576"/>
+      <c r="Y18" s="604"/>
       <c r="Z18" s="96"/>
       <c r="AA18" s="119"/>
     </row>
@@ -28785,41 +28785,41 @@
       </c>
       <c r="E19" s="233"/>
       <c r="F19" s="105"/>
-      <c r="G19" s="544" t="s">
+      <c r="G19" s="627" t="s">
         <v>403</v>
       </c>
-      <c r="H19" s="545"/>
-      <c r="I19" s="546">
+      <c r="H19" s="628"/>
+      <c r="I19" s="605">
         <v>5</v>
       </c>
-      <c r="J19" s="547"/>
-      <c r="K19" s="548"/>
-      <c r="L19" s="540">
+      <c r="J19" s="629"/>
+      <c r="K19" s="630"/>
+      <c r="L19" s="603">
         <v>8</v>
       </c>
-      <c r="M19" s="540"/>
-      <c r="N19" s="540"/>
-      <c r="O19" s="540">
+      <c r="M19" s="603"/>
+      <c r="N19" s="603"/>
+      <c r="O19" s="603">
         <v>22</v>
       </c>
-      <c r="P19" s="540"/>
-      <c r="Q19" s="540"/>
-      <c r="R19" s="540">
+      <c r="P19" s="603"/>
+      <c r="Q19" s="603"/>
+      <c r="R19" s="603">
         <v>22</v>
       </c>
-      <c r="S19" s="540"/>
-      <c r="T19" s="540">
+      <c r="S19" s="603"/>
+      <c r="T19" s="603">
         <v>0</v>
       </c>
-      <c r="U19" s="540"/>
-      <c r="V19" s="540">
+      <c r="U19" s="603"/>
+      <c r="V19" s="603">
         <v>2</v>
       </c>
-      <c r="W19" s="546"/>
-      <c r="X19" s="540">
+      <c r="W19" s="605"/>
+      <c r="X19" s="603">
         <v>0</v>
       </c>
-      <c r="Y19" s="576"/>
+      <c r="Y19" s="604"/>
       <c r="Z19" s="96"/>
       <c r="AA19" s="119"/>
     </row>
@@ -28836,41 +28836,41 @@
       </c>
       <c r="E20" s="233"/>
       <c r="F20" s="105"/>
-      <c r="G20" s="544" t="s">
+      <c r="G20" s="627" t="s">
         <v>22</v>
       </c>
-      <c r="H20" s="545"/>
-      <c r="I20" s="546">
+      <c r="H20" s="628"/>
+      <c r="I20" s="605">
         <v>9</v>
       </c>
-      <c r="J20" s="547"/>
-      <c r="K20" s="548"/>
-      <c r="L20" s="540">
+      <c r="J20" s="629"/>
+      <c r="K20" s="630"/>
+      <c r="L20" s="603">
         <v>22</v>
       </c>
-      <c r="M20" s="540"/>
-      <c r="N20" s="540"/>
-      <c r="O20" s="540">
+      <c r="M20" s="603"/>
+      <c r="N20" s="603"/>
+      <c r="O20" s="603">
         <v>32</v>
       </c>
-      <c r="P20" s="540"/>
-      <c r="Q20" s="540"/>
-      <c r="R20" s="540">
+      <c r="P20" s="603"/>
+      <c r="Q20" s="603"/>
+      <c r="R20" s="603">
         <v>33</v>
       </c>
-      <c r="S20" s="540"/>
-      <c r="T20" s="540">
+      <c r="S20" s="603"/>
+      <c r="T20" s="603">
         <v>0</v>
       </c>
-      <c r="U20" s="540"/>
-      <c r="V20" s="540">
+      <c r="U20" s="603"/>
+      <c r="V20" s="603">
         <v>0</v>
       </c>
-      <c r="W20" s="546"/>
-      <c r="X20" s="540">
+      <c r="W20" s="605"/>
+      <c r="X20" s="603">
         <v>0</v>
       </c>
-      <c r="Y20" s="576"/>
+      <c r="Y20" s="604"/>
       <c r="Z20" s="96"/>
       <c r="AA20" s="119"/>
     </row>
@@ -28887,41 +28887,41 @@
       </c>
       <c r="E21" s="233"/>
       <c r="F21" s="105"/>
-      <c r="G21" s="544" t="s">
+      <c r="G21" s="627" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="545"/>
-      <c r="I21" s="546">
+      <c r="H21" s="628"/>
+      <c r="I21" s="605">
         <v>3</v>
       </c>
-      <c r="J21" s="547"/>
-      <c r="K21" s="548"/>
-      <c r="L21" s="540">
+      <c r="J21" s="629"/>
+      <c r="K21" s="630"/>
+      <c r="L21" s="603">
         <v>8</v>
       </c>
-      <c r="M21" s="540"/>
-      <c r="N21" s="540"/>
-      <c r="O21" s="540">
+      <c r="M21" s="603"/>
+      <c r="N21" s="603"/>
+      <c r="O21" s="603">
         <v>50</v>
       </c>
-      <c r="P21" s="540"/>
-      <c r="Q21" s="540"/>
-      <c r="R21" s="540">
+      <c r="P21" s="603"/>
+      <c r="Q21" s="603"/>
+      <c r="R21" s="603">
         <v>62</v>
       </c>
-      <c r="S21" s="540"/>
-      <c r="T21" s="540">
+      <c r="S21" s="603"/>
+      <c r="T21" s="603">
         <v>0</v>
       </c>
-      <c r="U21" s="540"/>
-      <c r="V21" s="540">
+      <c r="U21" s="603"/>
+      <c r="V21" s="603">
         <v>10</v>
       </c>
-      <c r="W21" s="546"/>
-      <c r="X21" s="540">
+      <c r="W21" s="605"/>
+      <c r="X21" s="603">
         <v>11</v>
       </c>
-      <c r="Y21" s="576"/>
+      <c r="Y21" s="604"/>
       <c r="Z21" s="96"/>
       <c r="AA21" s="119"/>
     </row>
@@ -28938,41 +28938,41 @@
       </c>
       <c r="E22" s="233"/>
       <c r="F22" s="105"/>
-      <c r="G22" s="544" t="s">
+      <c r="G22" s="627" t="s">
         <v>404</v>
       </c>
-      <c r="H22" s="545"/>
-      <c r="I22" s="546">
+      <c r="H22" s="628"/>
+      <c r="I22" s="605">
         <v>1</v>
       </c>
-      <c r="J22" s="547"/>
-      <c r="K22" s="548"/>
-      <c r="L22" s="540">
+      <c r="J22" s="629"/>
+      <c r="K22" s="630"/>
+      <c r="L22" s="603">
         <v>2</v>
       </c>
-      <c r="M22" s="540"/>
-      <c r="N22" s="540"/>
-      <c r="O22" s="540">
+      <c r="M22" s="603"/>
+      <c r="N22" s="603"/>
+      <c r="O22" s="603">
         <v>4</v>
       </c>
-      <c r="P22" s="540"/>
-      <c r="Q22" s="540"/>
-      <c r="R22" s="540">
+      <c r="P22" s="603"/>
+      <c r="Q22" s="603"/>
+      <c r="R22" s="603">
         <v>6</v>
       </c>
-      <c r="S22" s="540"/>
-      <c r="T22" s="540">
+      <c r="S22" s="603"/>
+      <c r="T22" s="603">
         <v>0</v>
       </c>
-      <c r="U22" s="540"/>
-      <c r="V22" s="540">
+      <c r="U22" s="603"/>
+      <c r="V22" s="603">
         <v>0</v>
       </c>
-      <c r="W22" s="546"/>
-      <c r="X22" s="540">
+      <c r="W22" s="605"/>
+      <c r="X22" s="603">
         <v>3</v>
       </c>
-      <c r="Y22" s="576"/>
+      <c r="Y22" s="604"/>
       <c r="Z22" s="96"/>
       <c r="AA22" s="119"/>
     </row>
@@ -28989,48 +28989,48 @@
       </c>
       <c r="E23" s="234"/>
       <c r="F23" s="105"/>
-      <c r="G23" s="587" t="s">
+      <c r="G23" s="615" t="s">
         <v>145</v>
       </c>
-      <c r="H23" s="579"/>
-      <c r="I23" s="579">
+      <c r="H23" s="607"/>
+      <c r="I23" s="607">
         <f>SUM(I14:K22)</f>
         <v>68</v>
       </c>
-      <c r="J23" s="579"/>
-      <c r="K23" s="579"/>
-      <c r="L23" s="579">
+      <c r="J23" s="607"/>
+      <c r="K23" s="607"/>
+      <c r="L23" s="607">
         <f>SUM(L14:N22)</f>
         <v>187</v>
       </c>
-      <c r="M23" s="579"/>
-      <c r="N23" s="579"/>
-      <c r="O23" s="584">
+      <c r="M23" s="607"/>
+      <c r="N23" s="607"/>
+      <c r="O23" s="612">
         <f>SUM(O14:Q22)</f>
         <v>473</v>
       </c>
-      <c r="P23" s="585"/>
-      <c r="Q23" s="586"/>
-      <c r="R23" s="584">
+      <c r="P23" s="613"/>
+      <c r="Q23" s="614"/>
+      <c r="R23" s="612">
         <f>SUM(R14:S22)</f>
         <v>526</v>
       </c>
-      <c r="S23" s="586"/>
-      <c r="T23" s="584">
+      <c r="S23" s="614"/>
+      <c r="T23" s="612">
         <f>SUM(T14:U22)</f>
         <v>28</v>
       </c>
-      <c r="U23" s="586"/>
-      <c r="V23" s="584">
+      <c r="U23" s="614"/>
+      <c r="V23" s="612">
         <f>SUM(V14:W22)</f>
         <v>33</v>
       </c>
-      <c r="W23" s="585"/>
-      <c r="X23" s="579">
+      <c r="W23" s="613"/>
+      <c r="X23" s="607">
         <f>SUM(X14:Y22)</f>
         <v>36</v>
       </c>
-      <c r="Y23" s="580"/>
+      <c r="Y23" s="608"/>
       <c r="Z23" s="96"/>
       <c r="AA23" s="119"/>
     </row>
@@ -29100,28 +29100,28 @@
       <c r="E26" s="98"/>
       <c r="F26" s="95"/>
       <c r="G26" s="161"/>
-      <c r="H26" s="624" t="s">
+      <c r="H26" s="570" t="s">
         <v>160</v>
       </c>
-      <c r="I26" s="625"/>
-      <c r="J26" s="626"/>
+      <c r="I26" s="571"/>
+      <c r="J26" s="572"/>
       <c r="K26" s="105"/>
-      <c r="L26" s="630" t="s">
+      <c r="L26" s="579" t="s">
         <v>153</v>
       </c>
-      <c r="M26" s="631"/>
-      <c r="N26" s="631"/>
-      <c r="O26" s="631"/>
-      <c r="P26" s="631"/>
-      <c r="Q26" s="631"/>
-      <c r="R26" s="631"/>
-      <c r="S26" s="631"/>
-      <c r="T26" s="631"/>
-      <c r="U26" s="631"/>
-      <c r="V26" s="631"/>
-      <c r="W26" s="631"/>
-      <c r="X26" s="631"/>
-      <c r="Y26" s="632"/>
+      <c r="M26" s="580"/>
+      <c r="N26" s="580"/>
+      <c r="O26" s="580"/>
+      <c r="P26" s="580"/>
+      <c r="Q26" s="580"/>
+      <c r="R26" s="580"/>
+      <c r="S26" s="580"/>
+      <c r="T26" s="580"/>
+      <c r="U26" s="580"/>
+      <c r="V26" s="580"/>
+      <c r="W26" s="580"/>
+      <c r="X26" s="580"/>
+      <c r="Y26" s="581"/>
       <c r="Z26" s="96"/>
       <c r="AA26" s="119"/>
     </row>
@@ -29133,41 +29133,41 @@
       <c r="E27" s="98"/>
       <c r="F27" s="95"/>
       <c r="G27" s="162"/>
-      <c r="H27" s="621">
+      <c r="H27" s="552">
         <f>Y38</f>
         <v>64</v>
       </c>
-      <c r="I27" s="622"/>
-      <c r="J27" s="623"/>
+      <c r="I27" s="553"/>
+      <c r="J27" s="554"/>
       <c r="K27" s="105"/>
-      <c r="L27" s="595" t="s">
+      <c r="L27" s="601" t="s">
         <v>137</v>
       </c>
-      <c r="M27" s="543"/>
-      <c r="N27" s="543"/>
-      <c r="O27" s="543" t="s">
+      <c r="M27" s="575"/>
+      <c r="N27" s="575"/>
+      <c r="O27" s="575" t="s">
         <v>154</v>
       </c>
-      <c r="P27" s="543"/>
-      <c r="Q27" s="543" t="s">
+      <c r="P27" s="575"/>
+      <c r="Q27" s="575" t="s">
         <v>155</v>
       </c>
-      <c r="R27" s="543"/>
-      <c r="S27" s="543" t="s">
+      <c r="R27" s="575"/>
+      <c r="S27" s="575" t="s">
         <v>156</v>
       </c>
-      <c r="T27" s="543" t="s">
+      <c r="T27" s="575" t="s">
         <v>157</v>
       </c>
-      <c r="U27" s="543"/>
-      <c r="V27" s="543" t="s">
+      <c r="U27" s="575"/>
+      <c r="V27" s="575" t="s">
         <v>158</v>
       </c>
-      <c r="W27" s="543" t="s">
+      <c r="W27" s="575" t="s">
         <v>159</v>
       </c>
-      <c r="X27" s="543"/>
-      <c r="Y27" s="564" t="s">
+      <c r="X27" s="575"/>
+      <c r="Y27" s="606" t="s">
         <v>145</v>
       </c>
       <c r="Z27" s="96"/>
@@ -29185,20 +29185,20 @@
       <c r="I28" s="98"/>
       <c r="J28" s="193"/>
       <c r="K28" s="105"/>
-      <c r="L28" s="595"/>
-      <c r="M28" s="543"/>
-      <c r="N28" s="543"/>
-      <c r="O28" s="543"/>
-      <c r="P28" s="543"/>
-      <c r="Q28" s="543"/>
-      <c r="R28" s="543"/>
-      <c r="S28" s="543"/>
-      <c r="T28" s="543"/>
-      <c r="U28" s="543"/>
-      <c r="V28" s="543"/>
-      <c r="W28" s="543"/>
-      <c r="X28" s="543"/>
-      <c r="Y28" s="564"/>
+      <c r="L28" s="601"/>
+      <c r="M28" s="575"/>
+      <c r="N28" s="575"/>
+      <c r="O28" s="575"/>
+      <c r="P28" s="575"/>
+      <c r="Q28" s="575"/>
+      <c r="R28" s="575"/>
+      <c r="S28" s="575"/>
+      <c r="T28" s="575"/>
+      <c r="U28" s="575"/>
+      <c r="V28" s="575"/>
+      <c r="W28" s="575"/>
+      <c r="X28" s="575"/>
+      <c r="Y28" s="606"/>
       <c r="Z28" s="96"/>
       <c r="AA28" s="119"/>
     </row>
@@ -29214,33 +29214,33 @@
       <c r="I29" s="194"/>
       <c r="J29" s="164"/>
       <c r="K29" s="105"/>
-      <c r="L29" s="592" t="s">
+      <c r="L29" s="587" t="s">
         <v>18</v>
       </c>
-      <c r="M29" s="593"/>
-      <c r="N29" s="593"/>
-      <c r="O29" s="593">
+      <c r="M29" s="555"/>
+      <c r="N29" s="555"/>
+      <c r="O29" s="555">
         <v>3</v>
       </c>
-      <c r="P29" s="593"/>
-      <c r="Q29" s="593">
+      <c r="P29" s="555"/>
+      <c r="Q29" s="555">
         <v>1</v>
       </c>
-      <c r="R29" s="593"/>
+      <c r="R29" s="555"/>
       <c r="S29" s="87">
         <v>0</v>
       </c>
-      <c r="T29" s="593">
+      <c r="T29" s="555">
         <v>0</v>
       </c>
-      <c r="U29" s="593"/>
+      <c r="U29" s="555"/>
       <c r="V29" s="87">
         <v>3</v>
       </c>
-      <c r="W29" s="593">
+      <c r="W29" s="555">
         <v>0</v>
       </c>
-      <c r="X29" s="594"/>
+      <c r="X29" s="556"/>
       <c r="Y29" s="227">
         <v>6</v>
       </c>
@@ -29259,33 +29259,33 @@
       <c r="I30" s="125"/>
       <c r="J30" s="125"/>
       <c r="K30" s="95"/>
-      <c r="L30" s="592" t="s">
+      <c r="L30" s="587" t="s">
         <v>16</v>
       </c>
-      <c r="M30" s="593"/>
-      <c r="N30" s="593"/>
-      <c r="O30" s="593">
+      <c r="M30" s="555"/>
+      <c r="N30" s="555"/>
+      <c r="O30" s="555">
         <v>0</v>
       </c>
-      <c r="P30" s="593"/>
-      <c r="Q30" s="593">
+      <c r="P30" s="555"/>
+      <c r="Q30" s="555">
         <v>0</v>
       </c>
-      <c r="R30" s="593"/>
+      <c r="R30" s="555"/>
       <c r="S30" s="87">
         <v>9</v>
       </c>
-      <c r="T30" s="593">
+      <c r="T30" s="555">
         <v>3</v>
       </c>
-      <c r="U30" s="593"/>
+      <c r="U30" s="555"/>
       <c r="V30" s="87">
         <v>2</v>
       </c>
-      <c r="W30" s="593">
+      <c r="W30" s="555">
         <v>1</v>
       </c>
-      <c r="X30" s="594"/>
+      <c r="X30" s="556"/>
       <c r="Y30" s="227">
         <v>11</v>
       </c>
@@ -29300,39 +29300,39 @@
       <c r="E31" s="98"/>
       <c r="F31" s="95"/>
       <c r="G31" s="161"/>
-      <c r="H31" s="627" t="s">
+      <c r="H31" s="576" t="s">
         <v>150</v>
       </c>
-      <c r="I31" s="628"/>
-      <c r="J31" s="629"/>
+      <c r="I31" s="577"/>
+      <c r="J31" s="578"/>
       <c r="K31" s="105"/>
-      <c r="L31" s="592" t="s">
+      <c r="L31" s="587" t="s">
         <v>19</v>
       </c>
-      <c r="M31" s="593"/>
-      <c r="N31" s="593"/>
-      <c r="O31" s="593">
+      <c r="M31" s="555"/>
+      <c r="N31" s="555"/>
+      <c r="O31" s="555">
         <v>1</v>
       </c>
-      <c r="P31" s="593"/>
-      <c r="Q31" s="593">
+      <c r="P31" s="555"/>
+      <c r="Q31" s="555">
         <v>0</v>
       </c>
-      <c r="R31" s="593"/>
+      <c r="R31" s="555"/>
       <c r="S31" s="87">
         <v>3</v>
       </c>
-      <c r="T31" s="593">
+      <c r="T31" s="555">
         <v>4</v>
       </c>
-      <c r="U31" s="593"/>
+      <c r="U31" s="555"/>
       <c r="V31" s="87">
         <v>2</v>
       </c>
-      <c r="W31" s="593">
+      <c r="W31" s="555">
         <v>0</v>
       </c>
-      <c r="X31" s="594"/>
+      <c r="X31" s="556"/>
       <c r="Y31" s="227">
         <v>6</v>
       </c>
@@ -29351,33 +29351,33 @@
       <c r="I32" s="98"/>
       <c r="J32" s="193"/>
       <c r="K32" s="105"/>
-      <c r="L32" s="592" t="s">
+      <c r="L32" s="587" t="s">
         <v>17</v>
       </c>
-      <c r="M32" s="593"/>
-      <c r="N32" s="593"/>
-      <c r="O32" s="593">
+      <c r="M32" s="555"/>
+      <c r="N32" s="555"/>
+      <c r="O32" s="555">
         <v>2</v>
       </c>
-      <c r="P32" s="593"/>
-      <c r="Q32" s="593">
+      <c r="P32" s="555"/>
+      <c r="Q32" s="555">
         <v>0</v>
       </c>
-      <c r="R32" s="593"/>
+      <c r="R32" s="555"/>
       <c r="S32" s="87">
         <v>4</v>
       </c>
-      <c r="T32" s="593">
+      <c r="T32" s="555">
         <v>2</v>
       </c>
-      <c r="U32" s="593"/>
+      <c r="U32" s="555"/>
       <c r="V32" s="87">
         <v>9</v>
       </c>
-      <c r="W32" s="593">
+      <c r="W32" s="555">
         <v>2</v>
       </c>
-      <c r="X32" s="594"/>
+      <c r="X32" s="556"/>
       <c r="Y32" s="227">
         <v>15</v>
       </c>
@@ -29392,40 +29392,40 @@
       <c r="E33" s="98"/>
       <c r="F33" s="95"/>
       <c r="G33" s="162"/>
-      <c r="H33" s="621">
+      <c r="H33" s="552">
         <f>O38</f>
         <v>13</v>
       </c>
-      <c r="I33" s="622"/>
-      <c r="J33" s="623"/>
+      <c r="I33" s="553"/>
+      <c r="J33" s="554"/>
       <c r="K33" s="105"/>
-      <c r="L33" s="592" t="s">
+      <c r="L33" s="587" t="s">
         <v>402</v>
       </c>
-      <c r="M33" s="593"/>
-      <c r="N33" s="593"/>
-      <c r="O33" s="593">
+      <c r="M33" s="555"/>
+      <c r="N33" s="555"/>
+      <c r="O33" s="555">
         <v>2</v>
       </c>
-      <c r="P33" s="593"/>
-      <c r="Q33" s="593">
+      <c r="P33" s="555"/>
+      <c r="Q33" s="555">
         <v>2</v>
       </c>
-      <c r="R33" s="593"/>
+      <c r="R33" s="555"/>
       <c r="S33" s="87">
         <v>0</v>
       </c>
-      <c r="T33" s="593">
+      <c r="T33" s="555">
         <v>0</v>
       </c>
-      <c r="U33" s="593"/>
+      <c r="U33" s="555"/>
       <c r="V33" s="87">
         <v>1</v>
       </c>
-      <c r="W33" s="593">
+      <c r="W33" s="555">
         <v>1</v>
       </c>
-      <c r="X33" s="594"/>
+      <c r="X33" s="556"/>
       <c r="Y33" s="227">
         <v>3</v>
       </c>
@@ -29444,33 +29444,33 @@
       <c r="I34" s="98"/>
       <c r="J34" s="193"/>
       <c r="K34" s="105"/>
-      <c r="L34" s="592" t="s">
+      <c r="L34" s="587" t="s">
         <v>403</v>
       </c>
-      <c r="M34" s="593"/>
-      <c r="N34" s="593"/>
-      <c r="O34" s="593">
+      <c r="M34" s="555"/>
+      <c r="N34" s="555"/>
+      <c r="O34" s="555">
         <v>1</v>
       </c>
-      <c r="P34" s="593"/>
-      <c r="Q34" s="593">
+      <c r="P34" s="555"/>
+      <c r="Q34" s="555">
         <v>0</v>
       </c>
-      <c r="R34" s="593"/>
+      <c r="R34" s="555"/>
       <c r="S34" s="87">
         <v>0</v>
       </c>
-      <c r="T34" s="593">
+      <c r="T34" s="555">
         <v>0</v>
       </c>
-      <c r="U34" s="593"/>
+      <c r="U34" s="555"/>
       <c r="V34" s="87">
         <v>4</v>
       </c>
-      <c r="W34" s="593">
+      <c r="W34" s="555">
         <v>0</v>
       </c>
-      <c r="X34" s="594"/>
+      <c r="X34" s="556"/>
       <c r="Y34" s="227">
         <v>5</v>
       </c>
@@ -29489,33 +29489,33 @@
       <c r="I35" s="194"/>
       <c r="J35" s="164"/>
       <c r="K35" s="105"/>
-      <c r="L35" s="592" t="s">
+      <c r="L35" s="587" t="s">
         <v>22</v>
       </c>
-      <c r="M35" s="593"/>
-      <c r="N35" s="593"/>
-      <c r="O35" s="596">
+      <c r="M35" s="555"/>
+      <c r="N35" s="555"/>
+      <c r="O35" s="582">
         <v>0</v>
       </c>
-      <c r="P35" s="596"/>
-      <c r="Q35" s="596">
+      <c r="P35" s="582"/>
+      <c r="Q35" s="582">
         <v>0</v>
       </c>
-      <c r="R35" s="596"/>
+      <c r="R35" s="582"/>
       <c r="S35" s="190">
         <v>0</v>
       </c>
-      <c r="T35" s="596">
+      <c r="T35" s="582">
         <v>0</v>
       </c>
-      <c r="U35" s="596"/>
+      <c r="U35" s="582"/>
       <c r="V35" s="190">
         <v>5</v>
       </c>
-      <c r="W35" s="596">
+      <c r="W35" s="582">
         <v>0</v>
       </c>
-      <c r="X35" s="597"/>
+      <c r="X35" s="602"/>
       <c r="Y35" s="227">
         <v>5</v>
       </c>
@@ -29534,33 +29534,33 @@
       <c r="I36" s="125"/>
       <c r="J36" s="125"/>
       <c r="K36" s="95"/>
-      <c r="L36" s="592" t="s">
+      <c r="L36" s="587" t="s">
         <v>20</v>
       </c>
-      <c r="M36" s="593"/>
-      <c r="N36" s="594"/>
-      <c r="O36" s="598">
+      <c r="M36" s="555"/>
+      <c r="N36" s="556"/>
+      <c r="O36" s="559">
         <v>4</v>
       </c>
-      <c r="P36" s="598"/>
-      <c r="Q36" s="598">
+      <c r="P36" s="559"/>
+      <c r="Q36" s="559">
         <v>1</v>
       </c>
-      <c r="R36" s="598"/>
+      <c r="R36" s="559"/>
       <c r="S36" s="191">
         <v>0</v>
       </c>
-      <c r="T36" s="598">
+      <c r="T36" s="559">
         <v>0</v>
       </c>
-      <c r="U36" s="598"/>
+      <c r="U36" s="559"/>
       <c r="V36" s="191">
         <v>6</v>
       </c>
-      <c r="W36" s="598">
+      <c r="W36" s="559">
         <v>1</v>
       </c>
-      <c r="X36" s="599"/>
+      <c r="X36" s="583"/>
       <c r="Y36" s="227">
         <v>10</v>
       </c>
@@ -29575,39 +29575,39 @@
       <c r="E37" s="98"/>
       <c r="F37" s="95"/>
       <c r="G37" s="161"/>
-      <c r="H37" s="627" t="s">
+      <c r="H37" s="576" t="s">
         <v>149</v>
       </c>
-      <c r="I37" s="628"/>
-      <c r="J37" s="629"/>
+      <c r="I37" s="577"/>
+      <c r="J37" s="578"/>
       <c r="K37" s="105"/>
-      <c r="L37" s="592" t="s">
+      <c r="L37" s="587" t="s">
         <v>404</v>
       </c>
-      <c r="M37" s="593"/>
-      <c r="N37" s="594"/>
-      <c r="O37" s="598">
+      <c r="M37" s="555"/>
+      <c r="N37" s="556"/>
+      <c r="O37" s="559">
         <v>0</v>
       </c>
-      <c r="P37" s="598"/>
-      <c r="Q37" s="598">
+      <c r="P37" s="559"/>
+      <c r="Q37" s="559">
         <v>0</v>
       </c>
-      <c r="R37" s="598"/>
+      <c r="R37" s="559"/>
       <c r="S37" s="191">
         <v>0</v>
       </c>
-      <c r="T37" s="598">
+      <c r="T37" s="559">
         <v>0</v>
       </c>
-      <c r="U37" s="598"/>
+      <c r="U37" s="559"/>
       <c r="V37" s="191">
         <v>3</v>
       </c>
-      <c r="W37" s="598">
+      <c r="W37" s="559">
         <v>3</v>
       </c>
-      <c r="X37" s="599"/>
+      <c r="X37" s="583"/>
       <c r="Y37" s="227">
         <v>3</v>
       </c>
@@ -29625,39 +29625,39 @@
       <c r="I38" s="98"/>
       <c r="J38" s="193"/>
       <c r="K38" s="105"/>
-      <c r="L38" s="611" t="s">
+      <c r="L38" s="595" t="s">
         <v>145</v>
       </c>
-      <c r="M38" s="612"/>
-      <c r="N38" s="613"/>
-      <c r="O38" s="600">
+      <c r="M38" s="596"/>
+      <c r="N38" s="597"/>
+      <c r="O38" s="560">
         <f>SUM(O29:P37)</f>
         <v>13</v>
       </c>
-      <c r="P38" s="600"/>
-      <c r="Q38" s="600">
+      <c r="P38" s="560"/>
+      <c r="Q38" s="560">
         <f>SUM(Q29:R37)</f>
         <v>4</v>
       </c>
-      <c r="R38" s="600"/>
+      <c r="R38" s="560"/>
       <c r="S38" s="228">
         <f>SUM(S29:S37)</f>
         <v>16</v>
       </c>
-      <c r="T38" s="600">
+      <c r="T38" s="560">
         <f>SUM(T29:U37)</f>
         <v>9</v>
       </c>
-      <c r="U38" s="600"/>
+      <c r="U38" s="560"/>
       <c r="V38" s="228">
         <f>SUM(V29:V37)</f>
         <v>35</v>
       </c>
-      <c r="W38" s="600">
+      <c r="W38" s="560">
         <f>SUM(W29:X37)</f>
         <v>8</v>
       </c>
-      <c r="X38" s="600"/>
+      <c r="X38" s="560"/>
       <c r="Y38" s="229">
         <f>SUM(Y29:Y37)</f>
         <v>64</v>
@@ -29673,26 +29673,26 @@
       <c r="E39" s="98"/>
       <c r="F39" s="95"/>
       <c r="G39" s="162"/>
-      <c r="H39" s="621">
+      <c r="H39" s="552">
         <f>S38</f>
         <v>16</v>
       </c>
-      <c r="I39" s="622"/>
-      <c r="J39" s="623"/>
+      <c r="I39" s="553"/>
+      <c r="J39" s="554"/>
       <c r="K39" s="105"/>
-      <c r="L39" s="606"/>
-      <c r="M39" s="614"/>
-      <c r="N39" s="615"/>
-      <c r="O39" s="606"/>
-      <c r="P39" s="607"/>
-      <c r="Q39" s="619"/>
-      <c r="R39" s="620"/>
+      <c r="L39" s="590"/>
+      <c r="M39" s="598"/>
+      <c r="N39" s="599"/>
+      <c r="O39" s="590"/>
+      <c r="P39" s="591"/>
+      <c r="Q39" s="573"/>
+      <c r="R39" s="574"/>
       <c r="S39" s="123"/>
-      <c r="T39" s="647"/>
-      <c r="U39" s="647"/>
+      <c r="T39" s="561"/>
+      <c r="U39" s="561"/>
       <c r="V39" s="123"/>
-      <c r="W39" s="647"/>
-      <c r="X39" s="647"/>
+      <c r="W39" s="561"/>
+      <c r="X39" s="561"/>
       <c r="Y39" s="154"/>
       <c r="Z39" s="98"/>
       <c r="AA39" s="95"/>
@@ -29709,19 +29709,19 @@
       <c r="I40" s="98"/>
       <c r="J40" s="193"/>
       <c r="K40" s="105"/>
-      <c r="L40" s="616"/>
-      <c r="M40" s="617"/>
-      <c r="N40" s="618"/>
-      <c r="O40" s="608"/>
-      <c r="P40" s="605"/>
-      <c r="Q40" s="604"/>
-      <c r="R40" s="605"/>
+      <c r="L40" s="563"/>
+      <c r="M40" s="600"/>
+      <c r="N40" s="564"/>
+      <c r="O40" s="592"/>
+      <c r="P40" s="589"/>
+      <c r="Q40" s="588"/>
+      <c r="R40" s="589"/>
       <c r="S40" s="98"/>
-      <c r="T40" s="648"/>
-      <c r="U40" s="648"/>
+      <c r="T40" s="562"/>
+      <c r="U40" s="562"/>
       <c r="V40" s="98"/>
-      <c r="W40" s="648"/>
-      <c r="X40" s="648"/>
+      <c r="W40" s="562"/>
+      <c r="X40" s="562"/>
       <c r="Y40" s="166"/>
       <c r="Z40" s="98"/>
     </row>
@@ -29737,19 +29737,19 @@
       <c r="I41" s="194"/>
       <c r="J41" s="164"/>
       <c r="K41" s="105"/>
-      <c r="L41" s="616"/>
-      <c r="M41" s="617"/>
-      <c r="N41" s="618"/>
-      <c r="O41" s="609"/>
-      <c r="P41" s="610"/>
-      <c r="Q41" s="616"/>
-      <c r="R41" s="618"/>
+      <c r="L41" s="563"/>
+      <c r="M41" s="600"/>
+      <c r="N41" s="564"/>
+      <c r="O41" s="593"/>
+      <c r="P41" s="594"/>
+      <c r="Q41" s="563"/>
+      <c r="R41" s="564"/>
       <c r="S41" s="98"/>
-      <c r="T41" s="616"/>
-      <c r="U41" s="618"/>
+      <c r="T41" s="563"/>
+      <c r="U41" s="564"/>
       <c r="V41" s="98"/>
-      <c r="W41" s="616"/>
-      <c r="X41" s="618"/>
+      <c r="W41" s="563"/>
+      <c r="X41" s="564"/>
       <c r="Y41" s="166"/>
       <c r="Z41" s="98"/>
       <c r="AA41" s="119"/>
@@ -29766,21 +29766,21 @@
       <c r="I42" s="125"/>
       <c r="J42" s="125"/>
       <c r="K42" s="95"/>
-      <c r="L42" s="601"/>
-      <c r="M42" s="602"/>
-      <c r="N42" s="603"/>
-      <c r="O42" s="619"/>
-      <c r="P42" s="620"/>
+      <c r="L42" s="584"/>
+      <c r="M42" s="585"/>
+      <c r="N42" s="586"/>
+      <c r="O42" s="573"/>
+      <c r="P42" s="574"/>
       <c r="Q42" s="98"/>
-      <c r="R42" s="645" t="s">
+      <c r="R42" s="557" t="s">
         <v>204</v>
       </c>
-      <c r="S42" s="646"/>
+      <c r="S42" s="558"/>
       <c r="T42" s="124"/>
-      <c r="U42" s="649"/>
-      <c r="V42" s="650"/>
-      <c r="W42" s="649"/>
-      <c r="X42" s="650"/>
+      <c r="U42" s="565"/>
+      <c r="V42" s="566"/>
+      <c r="W42" s="565"/>
+      <c r="X42" s="566"/>
       <c r="Y42" s="166"/>
       <c r="Z42" s="98"/>
       <c r="AA42" s="95"/>
@@ -29793,19 +29793,19 @@
       <c r="E43" s="98"/>
       <c r="F43" s="95"/>
       <c r="G43" s="161"/>
-      <c r="H43" s="652" t="s">
+      <c r="H43" s="568" t="s">
         <v>161</v>
       </c>
-      <c r="I43" s="652"/>
-      <c r="J43" s="653"/>
+      <c r="I43" s="568"/>
+      <c r="J43" s="569"/>
       <c r="K43" s="105"/>
       <c r="L43" s="161"/>
       <c r="M43" s="192"/>
-      <c r="N43" s="636" t="s">
+      <c r="N43" s="543" t="s">
         <v>151</v>
       </c>
-      <c r="O43" s="637"/>
-      <c r="P43" s="638"/>
+      <c r="O43" s="544"/>
+      <c r="P43" s="545"/>
       <c r="Q43" s="162"/>
       <c r="R43" s="348" t="s">
         <v>205</v>
@@ -29859,21 +29859,21 @@
       <c r="E45" s="98"/>
       <c r="F45" s="95"/>
       <c r="G45" s="162"/>
-      <c r="H45" s="621">
+      <c r="H45" s="552">
         <f>SUM(V38)</f>
         <v>35</v>
       </c>
-      <c r="I45" s="622"/>
-      <c r="J45" s="623"/>
+      <c r="I45" s="553"/>
+      <c r="J45" s="554"/>
       <c r="K45" s="105"/>
       <c r="L45" s="162"/>
       <c r="M45" s="98"/>
       <c r="N45" s="98"/>
-      <c r="O45" s="639">
+      <c r="O45" s="546">
         <f>SUM(Q38,T38,W38)</f>
         <v>21</v>
       </c>
-      <c r="P45" s="640"/>
+      <c r="P45" s="547"/>
       <c r="Q45" s="162"/>
       <c r="R45" s="349" t="s">
         <v>206</v>
@@ -29905,8 +29905,8 @@
       <c r="L46" s="162"/>
       <c r="M46" s="98"/>
       <c r="N46" s="98"/>
-      <c r="O46" s="641"/>
-      <c r="P46" s="642"/>
+      <c r="O46" s="548"/>
+      <c r="P46" s="549"/>
       <c r="Q46" s="162"/>
       <c r="R46" s="350"/>
       <c r="S46" s="365"/>
@@ -30017,9 +30017,9 @@
       <c r="E50" s="98"/>
       <c r="F50" s="95"/>
       <c r="G50" s="195"/>
-      <c r="H50" s="643"/>
-      <c r="I50" s="643"/>
-      <c r="J50" s="644"/>
+      <c r="H50" s="550"/>
+      <c r="I50" s="550"/>
+      <c r="J50" s="551"/>
       <c r="K50" s="96"/>
       <c r="L50" s="123"/>
       <c r="M50" s="123"/>
@@ -30074,9 +30074,9 @@
       <c r="E52" s="98"/>
       <c r="F52" s="98"/>
       <c r="G52" s="98"/>
-      <c r="H52" s="651"/>
-      <c r="I52" s="651"/>
-      <c r="J52" s="651"/>
+      <c r="H52" s="567"/>
+      <c r="I52" s="567"/>
+      <c r="J52" s="567"/>
       <c r="K52" s="98"/>
       <c r="L52" s="98"/>
       <c r="M52" s="98"/>
@@ -30177,11 +30177,11 @@
       <c r="U55" s="95"/>
       <c r="V55" s="98"/>
       <c r="W55" s="98"/>
-      <c r="X55" s="633"/>
-      <c r="Y55" s="634"/>
-      <c r="Z55" s="634"/>
-      <c r="AA55" s="634"/>
-      <c r="AB55" s="635"/>
+      <c r="X55" s="540"/>
+      <c r="Y55" s="541"/>
+      <c r="Z55" s="541"/>
+      <c r="AA55" s="541"/>
+      <c r="AB55" s="542"/>
     </row>
     <row r="56" spans="1:28" ht="23.25" hidden="1">
       <c r="A56" s="98"/>
@@ -30397,11 +30397,11 @@
       <c r="P63" s="98"/>
       <c r="Q63" s="95"/>
       <c r="R63" s="95"/>
-      <c r="U63" s="633"/>
-      <c r="V63" s="634"/>
-      <c r="W63" s="634"/>
-      <c r="X63" s="634"/>
-      <c r="Y63" s="635"/>
+      <c r="U63" s="540"/>
+      <c r="V63" s="541"/>
+      <c r="W63" s="541"/>
+      <c r="X63" s="541"/>
+      <c r="Y63" s="542"/>
       <c r="Z63" s="98"/>
     </row>
     <row r="64" spans="1:28" ht="23.25">
@@ -30837,6 +30837,178 @@
     </row>
   </sheetData>
   <mergeCells count="196">
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="V12:W13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="B1:Y1"/>
+    <mergeCell ref="B3:Y3"/>
+    <mergeCell ref="B4:Y4"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="X12:Y13"/>
+    <mergeCell ref="R11:Y11"/>
+    <mergeCell ref="G10:Y10"/>
+    <mergeCell ref="G11:H13"/>
+    <mergeCell ref="I11:K13"/>
+    <mergeCell ref="L11:N13"/>
+    <mergeCell ref="O11:Q13"/>
+    <mergeCell ref="R12:S13"/>
+    <mergeCell ref="T12:U13"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="W27:X28"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="V27:V28"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Y27:Y28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="W29:X29"/>
+    <mergeCell ref="T27:U28"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="L27:N28"/>
+    <mergeCell ref="W31:X31"/>
+    <mergeCell ref="W32:X32"/>
+    <mergeCell ref="W33:X33"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="W35:X35"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="W38:X38"/>
+    <mergeCell ref="L42:N42"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="L40:N40"/>
+    <mergeCell ref="L41:N41"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="O27:P28"/>
+    <mergeCell ref="Q27:R28"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="L26:Y26"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="T32:U32"/>
+    <mergeCell ref="T33:U33"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="Q36:R36"/>
     <mergeCell ref="U63:Y63"/>
     <mergeCell ref="X55:AB55"/>
     <mergeCell ref="N43:P43"/>
@@ -30861,178 +31033,6 @@
     <mergeCell ref="W41:X41"/>
     <mergeCell ref="W42:X42"/>
     <mergeCell ref="H43:J43"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="O42:P42"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="O27:P28"/>
-    <mergeCell ref="Q27:R28"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="L26:Y26"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="T32:U32"/>
-    <mergeCell ref="T33:U33"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="W37:X37"/>
-    <mergeCell ref="W38:X38"/>
-    <mergeCell ref="L42:N42"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="L40:N40"/>
-    <mergeCell ref="L41:N41"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="W29:X29"/>
-    <mergeCell ref="T27:U28"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="L27:N28"/>
-    <mergeCell ref="W31:X31"/>
-    <mergeCell ref="W32:X32"/>
-    <mergeCell ref="W33:X33"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="W35:X35"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Y27:Y28"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="V27:V28"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="W27:X28"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="X15:Y15"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="V12:W13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="B1:Y1"/>
-    <mergeCell ref="B3:Y3"/>
-    <mergeCell ref="B4:Y4"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="X12:Y13"/>
-    <mergeCell ref="R11:Y11"/>
-    <mergeCell ref="G10:Y10"/>
-    <mergeCell ref="G11:H13"/>
-    <mergeCell ref="I11:K13"/>
-    <mergeCell ref="L11:N13"/>
-    <mergeCell ref="O11:Q13"/>
-    <mergeCell ref="R12:S13"/>
-    <mergeCell ref="T12:U13"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="T16:U16"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:E15">
     <cfRule type="expression" dxfId="5" priority="10">
@@ -31827,57 +31827,57 @@
   <sheetData>
     <row r="1" spans="1:21" ht="21">
       <c r="A1" s="98"/>
-      <c r="B1" s="662" t="s">
+      <c r="B1" s="697" t="s">
         <v>176</v>
       </c>
-      <c r="C1" s="663"/>
-      <c r="D1" s="663"/>
-      <c r="E1" s="663"/>
-      <c r="F1" s="663"/>
-      <c r="G1" s="663"/>
-      <c r="H1" s="663"/>
-      <c r="I1" s="663"/>
-      <c r="J1" s="663"/>
-      <c r="K1" s="663"/>
-      <c r="L1" s="663"/>
-      <c r="M1" s="663"/>
-      <c r="N1" s="663"/>
-      <c r="O1" s="663"/>
-      <c r="P1" s="664"/>
+      <c r="C1" s="698"/>
+      <c r="D1" s="698"/>
+      <c r="E1" s="698"/>
+      <c r="F1" s="698"/>
+      <c r="G1" s="698"/>
+      <c r="H1" s="698"/>
+      <c r="I1" s="698"/>
+      <c r="J1" s="698"/>
+      <c r="K1" s="698"/>
+      <c r="L1" s="698"/>
+      <c r="M1" s="698"/>
+      <c r="N1" s="698"/>
+      <c r="O1" s="698"/>
+      <c r="P1" s="699"/>
       <c r="Q1" s="98"/>
       <c r="R1" s="98"/>
       <c r="S1" s="98"/>
       <c r="T1" s="98"/>
       <c r="U1" s="98"/>
     </row>
-    <row r="2" spans="1:21" ht="30.75" customHeight="1">
+    <row r="2" spans="1:21" ht="18.75" customHeight="1">
       <c r="A2" s="98"/>
-      <c r="B2" s="658" t="s">
+      <c r="B2" s="693" t="s">
         <v>177</v>
       </c>
-      <c r="C2" s="659"/>
-      <c r="D2" s="659"/>
-      <c r="E2" s="659"/>
-      <c r="F2" s="659"/>
-      <c r="G2" s="660" t="s">
+      <c r="C2" s="694"/>
+      <c r="D2" s="694"/>
+      <c r="E2" s="694"/>
+      <c r="F2" s="694"/>
+      <c r="G2" s="695" t="s">
         <v>221</v>
       </c>
-      <c r="H2" s="660"/>
-      <c r="I2" s="660"/>
-      <c r="J2" s="660"/>
-      <c r="K2" s="660"/>
-      <c r="L2" s="660"/>
-      <c r="M2" s="660"/>
-      <c r="N2" s="660"/>
-      <c r="O2" s="660"/>
-      <c r="P2" s="661"/>
+      <c r="H2" s="695"/>
+      <c r="I2" s="695"/>
+      <c r="J2" s="695"/>
+      <c r="K2" s="695"/>
+      <c r="L2" s="695"/>
+      <c r="M2" s="695"/>
+      <c r="N2" s="695"/>
+      <c r="O2" s="695"/>
+      <c r="P2" s="696"/>
       <c r="Q2" s="98"/>
       <c r="R2" s="98"/>
       <c r="S2" s="98"/>
       <c r="T2" s="98"/>
       <c r="U2" s="98"/>
     </row>
-    <row r="3" spans="1:21" ht="18.75" customHeight="1">
+    <row r="3" spans="1:21" ht="6" customHeight="1">
       <c r="A3" s="98"/>
       <c r="B3" s="245"/>
       <c r="C3" s="249"/>
@@ -31911,14 +31911,14 @@
       <c r="H4" s="96"/>
       <c r="I4" s="104"/>
       <c r="J4" s="251"/>
-      <c r="K4" s="677" t="s">
+      <c r="K4" s="686" t="s">
         <v>217</v>
       </c>
-      <c r="L4" s="677"/>
-      <c r="M4" s="677"/>
-      <c r="N4" s="677"/>
-      <c r="O4" s="677"/>
-      <c r="P4" s="677"/>
+      <c r="L4" s="686"/>
+      <c r="M4" s="686"/>
+      <c r="N4" s="686"/>
+      <c r="O4" s="686"/>
+      <c r="P4" s="686"/>
       <c r="Q4" s="98"/>
       <c r="R4" s="98"/>
       <c r="S4" s="98"/>
@@ -31931,18 +31931,18 @@
       <c r="H5" s="95"/>
       <c r="I5" s="98"/>
       <c r="J5" s="252"/>
-      <c r="K5" s="673" t="s">
+      <c r="K5" s="704" t="s">
         <v>179</v>
       </c>
-      <c r="L5" s="673"/>
-      <c r="M5" s="673" t="s">
+      <c r="L5" s="704"/>
+      <c r="M5" s="704" t="s">
         <v>182</v>
       </c>
-      <c r="N5" s="673"/>
-      <c r="O5" s="673" t="s">
+      <c r="N5" s="704"/>
+      <c r="O5" s="704" t="s">
         <v>183</v>
       </c>
-      <c r="P5" s="673"/>
+      <c r="P5" s="704"/>
       <c r="Q5" s="96"/>
       <c r="R5" s="98"/>
       <c r="S5" s="98"/>
@@ -31955,18 +31955,18 @@
       <c r="H6" s="95"/>
       <c r="I6" s="98"/>
       <c r="J6" s="95"/>
-      <c r="K6" s="688" t="s">
+      <c r="K6" s="682" t="s">
         <v>194</v>
       </c>
-      <c r="L6" s="669"/>
-      <c r="M6" s="668" t="s">
+      <c r="L6" s="683"/>
+      <c r="M6" s="703" t="s">
         <v>407</v>
       </c>
-      <c r="N6" s="669"/>
-      <c r="O6" s="668" t="s">
+      <c r="N6" s="683"/>
+      <c r="O6" s="703" t="s">
         <v>156</v>
       </c>
-      <c r="P6" s="674"/>
+      <c r="P6" s="705"/>
       <c r="Q6" s="96"/>
       <c r="R6" s="98"/>
       <c r="S6" s="98"/>
@@ -31977,24 +31977,24 @@
       <c r="A7" s="98"/>
       <c r="C7" s="98"/>
       <c r="D7" s="98"/>
-      <c r="E7" s="675"/>
-      <c r="F7" s="676"/>
-      <c r="G7" s="676"/>
-      <c r="H7" s="676"/>
+      <c r="E7" s="684"/>
+      <c r="F7" s="685"/>
+      <c r="G7" s="685"/>
+      <c r="H7" s="685"/>
       <c r="I7" s="98"/>
       <c r="J7" s="119"/>
       <c r="K7" s="678" t="s">
         <v>194</v>
       </c>
-      <c r="L7" s="671"/>
-      <c r="M7" s="670" t="s">
+      <c r="L7" s="675"/>
+      <c r="M7" s="674" t="s">
         <v>408</v>
       </c>
-      <c r="N7" s="671"/>
-      <c r="O7" s="670" t="s">
+      <c r="N7" s="675"/>
+      <c r="O7" s="674" t="s">
         <v>156</v>
       </c>
-      <c r="P7" s="672"/>
+      <c r="P7" s="681"/>
       <c r="Q7" s="96"/>
       <c r="R7" s="98"/>
       <c r="S7" s="98"/>
@@ -32011,15 +32011,15 @@
       <c r="K8" s="678" t="s">
         <v>193</v>
       </c>
-      <c r="L8" s="671"/>
-      <c r="M8" s="670" t="s">
+      <c r="L8" s="675"/>
+      <c r="M8" s="674" t="s">
         <v>409</v>
       </c>
-      <c r="N8" s="671"/>
-      <c r="O8" s="670" t="s">
+      <c r="N8" s="675"/>
+      <c r="O8" s="674" t="s">
         <v>156</v>
       </c>
-      <c r="P8" s="672"/>
+      <c r="P8" s="681"/>
       <c r="Q8" s="96"/>
       <c r="R8" s="98"/>
       <c r="S8" s="98"/>
@@ -32036,15 +32036,15 @@
       <c r="K9" s="678" t="s">
         <v>193</v>
       </c>
-      <c r="L9" s="671"/>
-      <c r="M9" s="670" t="s">
+      <c r="L9" s="675"/>
+      <c r="M9" s="674" t="s">
         <v>410</v>
       </c>
-      <c r="N9" s="671"/>
-      <c r="O9" s="670" t="s">
+      <c r="N9" s="675"/>
+      <c r="O9" s="674" t="s">
         <v>156</v>
       </c>
-      <c r="P9" s="672"/>
+      <c r="P9" s="681"/>
       <c r="Q9" s="96"/>
       <c r="R9" s="98"/>
       <c r="S9" s="98"/>
@@ -32061,15 +32061,15 @@
       <c r="K10" s="678" t="s">
         <v>193</v>
       </c>
-      <c r="L10" s="671"/>
-      <c r="M10" s="670" t="s">
+      <c r="L10" s="675"/>
+      <c r="M10" s="674" t="s">
         <v>411</v>
       </c>
-      <c r="N10" s="671"/>
-      <c r="O10" s="670" t="s">
+      <c r="N10" s="675"/>
+      <c r="O10" s="674" t="s">
         <v>156</v>
       </c>
-      <c r="P10" s="672"/>
+      <c r="P10" s="681"/>
       <c r="Q10" s="96"/>
       <c r="R10" s="98"/>
       <c r="S10" s="98"/>
@@ -32081,26 +32081,26 @@
       <c r="B11" s="98"/>
       <c r="C11" s="98"/>
       <c r="D11" s="95"/>
-      <c r="E11" s="665" t="s">
+      <c r="E11" s="700" t="s">
         <v>181</v>
       </c>
-      <c r="F11" s="666"/>
-      <c r="G11" s="666"/>
-      <c r="H11" s="667"/>
+      <c r="F11" s="701"/>
+      <c r="G11" s="701"/>
+      <c r="H11" s="702"/>
       <c r="I11" s="96"/>
       <c r="J11" s="119"/>
       <c r="K11" s="678" t="s">
         <v>405</v>
       </c>
-      <c r="L11" s="671"/>
-      <c r="M11" s="670" t="s">
+      <c r="L11" s="675"/>
+      <c r="M11" s="674" t="s">
         <v>412</v>
       </c>
-      <c r="N11" s="671"/>
-      <c r="O11" s="670" t="s">
+      <c r="N11" s="675"/>
+      <c r="O11" s="674" t="s">
         <v>156</v>
       </c>
-      <c r="P11" s="672"/>
+      <c r="P11" s="681"/>
       <c r="Q11" s="96"/>
       <c r="R11" s="98"/>
       <c r="S11" s="98"/>
@@ -32112,11 +32112,11 @@
       <c r="B12" s="98"/>
       <c r="C12" s="98"/>
       <c r="D12" s="95"/>
-      <c r="E12" s="679" t="s">
+      <c r="E12" s="687" t="s">
         <v>179</v>
       </c>
-      <c r="F12" s="680"/>
-      <c r="G12" s="681"/>
+      <c r="F12" s="688"/>
+      <c r="G12" s="689"/>
       <c r="H12" s="453" t="s">
         <v>180</v>
       </c>
@@ -32125,15 +32125,15 @@
       <c r="K12" s="678" t="s">
         <v>405</v>
       </c>
-      <c r="L12" s="671"/>
-      <c r="M12" s="670" t="s">
+      <c r="L12" s="675"/>
+      <c r="M12" s="674" t="s">
         <v>413</v>
       </c>
-      <c r="N12" s="671"/>
-      <c r="O12" s="670" t="s">
+      <c r="N12" s="675"/>
+      <c r="O12" s="674" t="s">
         <v>420</v>
       </c>
-      <c r="P12" s="672"/>
+      <c r="P12" s="681"/>
       <c r="Q12" s="96"/>
       <c r="R12" s="98"/>
       <c r="S12" s="98"/>
@@ -32145,11 +32145,11 @@
       <c r="B13" s="98"/>
       <c r="C13" s="98"/>
       <c r="D13" s="95"/>
-      <c r="E13" s="682" t="s">
+      <c r="E13" s="690" t="s">
         <v>196</v>
       </c>
-      <c r="F13" s="683"/>
-      <c r="G13" s="684"/>
+      <c r="F13" s="691"/>
+      <c r="G13" s="692"/>
       <c r="H13" s="311">
         <v>2</v>
       </c>
@@ -32158,15 +32158,15 @@
       <c r="K13" s="678" t="s">
         <v>406</v>
       </c>
-      <c r="L13" s="671"/>
-      <c r="M13" s="670" t="s">
+      <c r="L13" s="675"/>
+      <c r="M13" s="674" t="s">
         <v>414</v>
       </c>
-      <c r="N13" s="671"/>
-      <c r="O13" s="670" t="s">
+      <c r="N13" s="675"/>
+      <c r="O13" s="674" t="s">
         <v>156</v>
       </c>
-      <c r="P13" s="672"/>
+      <c r="P13" s="681"/>
       <c r="Q13" s="96"/>
       <c r="R13" s="98"/>
       <c r="S13" s="98"/>
@@ -32178,11 +32178,11 @@
       <c r="B14" s="98"/>
       <c r="C14" s="98"/>
       <c r="D14" s="95"/>
-      <c r="E14" s="685" t="s">
+      <c r="E14" s="664" t="s">
         <v>194</v>
       </c>
-      <c r="F14" s="686"/>
-      <c r="G14" s="687"/>
+      <c r="F14" s="665"/>
+      <c r="G14" s="666"/>
       <c r="H14" s="312">
         <v>26</v>
       </c>
@@ -32191,15 +32191,15 @@
       <c r="K14" s="678" t="s">
         <v>406</v>
       </c>
-      <c r="L14" s="671"/>
-      <c r="M14" s="670" t="s">
+      <c r="L14" s="675"/>
+      <c r="M14" s="674" t="s">
         <v>415</v>
       </c>
-      <c r="N14" s="671"/>
-      <c r="O14" s="670" t="s">
+      <c r="N14" s="675"/>
+      <c r="O14" s="674" t="s">
         <v>156</v>
       </c>
-      <c r="P14" s="672"/>
+      <c r="P14" s="681"/>
       <c r="Q14" s="96"/>
       <c r="R14" s="98"/>
       <c r="S14" s="98"/>
@@ -32211,11 +32211,11 @@
       <c r="B15" s="98"/>
       <c r="C15" s="98"/>
       <c r="D15" s="95"/>
-      <c r="E15" s="685" t="s">
+      <c r="E15" s="664" t="s">
         <v>195</v>
       </c>
-      <c r="F15" s="686"/>
-      <c r="G15" s="687"/>
+      <c r="F15" s="665"/>
+      <c r="G15" s="666"/>
       <c r="H15" s="312">
         <v>5</v>
       </c>
@@ -32224,15 +32224,15 @@
       <c r="K15" s="678" t="s">
         <v>193</v>
       </c>
-      <c r="L15" s="671"/>
-      <c r="M15" s="670" t="s">
+      <c r="L15" s="675"/>
+      <c r="M15" s="674" t="s">
         <v>416</v>
       </c>
-      <c r="N15" s="671"/>
-      <c r="O15" s="670" t="s">
+      <c r="N15" s="675"/>
+      <c r="O15" s="674" t="s">
         <v>156</v>
       </c>
-      <c r="P15" s="672"/>
+      <c r="P15" s="681"/>
       <c r="Q15" s="96"/>
       <c r="R15" s="98"/>
       <c r="S15" s="98"/>
@@ -32244,11 +32244,11 @@
       <c r="B16" s="98"/>
       <c r="C16" s="98"/>
       <c r="D16" s="95"/>
-      <c r="E16" s="685" t="s">
+      <c r="E16" s="664" t="s">
         <v>197</v>
       </c>
-      <c r="F16" s="686"/>
-      <c r="G16" s="687"/>
+      <c r="F16" s="665"/>
+      <c r="G16" s="666"/>
       <c r="H16" s="312">
         <v>29</v>
       </c>
@@ -32257,15 +32257,15 @@
       <c r="K16" s="678" t="s">
         <v>193</v>
       </c>
-      <c r="L16" s="671"/>
-      <c r="M16" s="670" t="s">
+      <c r="L16" s="675"/>
+      <c r="M16" s="674" t="s">
         <v>417</v>
       </c>
-      <c r="N16" s="671"/>
-      <c r="O16" s="670" t="s">
+      <c r="N16" s="675"/>
+      <c r="O16" s="674" t="s">
         <v>156</v>
       </c>
-      <c r="P16" s="672"/>
+      <c r="P16" s="681"/>
       <c r="Q16" s="96"/>
       <c r="R16" s="98"/>
       <c r="S16" s="98"/>
@@ -32275,11 +32275,11 @@
     <row r="17" spans="1:21" ht="66" customHeight="1">
       <c r="A17" s="95"/>
       <c r="D17" s="114"/>
-      <c r="E17" s="685" t="s">
+      <c r="E17" s="664" t="s">
         <v>198</v>
       </c>
-      <c r="F17" s="686"/>
-      <c r="G17" s="687"/>
+      <c r="F17" s="665"/>
+      <c r="G17" s="666"/>
       <c r="H17" s="312">
         <v>6</v>
       </c>
@@ -32288,15 +32288,15 @@
       <c r="K17" s="678" t="s">
         <v>195</v>
       </c>
-      <c r="L17" s="671"/>
-      <c r="M17" s="670" t="s">
+      <c r="L17" s="675"/>
+      <c r="M17" s="674" t="s">
         <v>418</v>
       </c>
-      <c r="N17" s="671"/>
-      <c r="O17" s="670" t="s">
+      <c r="N17" s="675"/>
+      <c r="O17" s="674" t="s">
         <v>420</v>
       </c>
-      <c r="P17" s="672"/>
+      <c r="P17" s="681"/>
       <c r="Q17" s="96"/>
       <c r="R17" s="98"/>
       <c r="S17" s="98"/>
@@ -32307,28 +32307,28 @@
       <c r="A18" s="95"/>
       <c r="C18" s="123"/>
       <c r="D18" s="95"/>
-      <c r="E18" s="697" t="s">
+      <c r="E18" s="667" t="s">
         <v>199</v>
       </c>
-      <c r="F18" s="698"/>
-      <c r="G18" s="699"/>
+      <c r="F18" s="668"/>
+      <c r="G18" s="669"/>
       <c r="H18" s="313">
         <v>25</v>
       </c>
       <c r="I18" s="96"/>
       <c r="J18" s="95"/>
-      <c r="K18" s="705" t="s">
+      <c r="K18" s="679" t="s">
         <v>195</v>
       </c>
-      <c r="L18" s="704"/>
-      <c r="M18" s="689" t="s">
+      <c r="L18" s="677"/>
+      <c r="M18" s="676" t="s">
         <v>419</v>
       </c>
-      <c r="N18" s="704"/>
-      <c r="O18" s="689" t="s">
+      <c r="N18" s="677"/>
+      <c r="O18" s="676" t="s">
         <v>420</v>
       </c>
-      <c r="P18" s="690"/>
+      <c r="P18" s="680"/>
       <c r="Q18" s="96"/>
       <c r="R18" s="98"/>
       <c r="S18" s="95"/>
@@ -32419,10 +32419,10 @@
         <v>181</v>
       </c>
       <c r="G22" s="290"/>
-      <c r="H22" s="700" t="s">
+      <c r="H22" s="670" t="s">
         <v>184</v>
       </c>
-      <c r="I22" s="701"/>
+      <c r="I22" s="671"/>
       <c r="J22" s="299"/>
       <c r="K22" s="306"/>
       <c r="L22" s="287"/>
@@ -32533,17 +32533,17 @@
       <c r="F26" s="309" t="s">
         <v>185</v>
       </c>
-      <c r="H26" s="702" t="s">
+      <c r="H26" s="672" t="s">
         <v>213</v>
       </c>
-      <c r="I26" s="703"/>
+      <c r="I26" s="673"/>
       <c r="J26" s="388"/>
-      <c r="K26" s="691" t="s">
+      <c r="K26" s="658" t="s">
         <v>216</v>
       </c>
-      <c r="L26" s="692"/>
-      <c r="M26" s="692"/>
-      <c r="N26" s="693"/>
+      <c r="L26" s="659"/>
+      <c r="M26" s="659"/>
+      <c r="N26" s="660"/>
       <c r="O26" s="96"/>
       <c r="P26" s="193"/>
       <c r="Q26" s="96"/>
@@ -32571,12 +32571,12 @@
       </c>
       <c r="I27" s="255"/>
       <c r="J27" s="253"/>
-      <c r="K27" s="694" t="s">
+      <c r="K27" s="661" t="s">
         <v>215</v>
       </c>
-      <c r="L27" s="695"/>
-      <c r="M27" s="695"/>
-      <c r="N27" s="696"/>
+      <c r="L27" s="662"/>
+      <c r="M27" s="662"/>
+      <c r="N27" s="663"/>
       <c r="O27" s="194"/>
       <c r="P27" s="164"/>
       <c r="Q27" s="96"/>
@@ -33023,33 +33023,22 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:P2"/>
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="M10:N10"/>
     <mergeCell ref="M11:N11"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="K4:P4"/>
@@ -33066,22 +33055,33 @@
     <mergeCell ref="K12:L12"/>
     <mergeCell ref="K13:L13"/>
     <mergeCell ref="K14:L14"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G2:P2"/>
-    <mergeCell ref="B1:P1"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K15:L15"/>
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -33355,14 +33355,14 @@
       <c r="G2" s="316"/>
       <c r="H2" s="316"/>
       <c r="I2" s="316"/>
-      <c r="J2" s="470" t="s">
+      <c r="J2" s="480" t="s">
         <v>203</v>
       </c>
-      <c r="K2" s="470"/>
-      <c r="L2" s="470"/>
-      <c r="M2" s="470"/>
-      <c r="N2" s="470"/>
-      <c r="O2" s="470"/>
+      <c r="K2" s="480"/>
+      <c r="L2" s="480"/>
+      <c r="M2" s="480"/>
+      <c r="N2" s="480"/>
+      <c r="O2" s="480"/>
       <c r="P2" s="316"/>
       <c r="Q2" s="316"/>
       <c r="R2" s="316"/>
@@ -33403,14 +33403,14 @@
       <c r="I4" s="317" t="s">
         <v>201</v>
       </c>
-      <c r="J4" s="469" t="s">
+      <c r="J4" s="479" t="s">
         <v>202</v>
       </c>
-      <c r="K4" s="469"/>
-      <c r="L4" s="469"/>
-      <c r="M4" s="469"/>
-      <c r="N4" s="469"/>
-      <c r="O4" s="469"/>
+      <c r="K4" s="479"/>
+      <c r="L4" s="479"/>
+      <c r="M4" s="479"/>
+      <c r="N4" s="479"/>
+      <c r="O4" s="479"/>
       <c r="P4" s="235"/>
       <c r="Q4" s="235"/>
       <c r="R4" s="236"/>
@@ -33426,17 +33426,17 @@
       <c r="G5" s="318"/>
       <c r="H5" s="318"/>
       <c r="I5" s="320"/>
-      <c r="J5" s="480" t="s">
+      <c r="J5" s="472" t="s">
         <v>174</v>
       </c>
-      <c r="K5" s="480"/>
-      <c r="L5" s="480"/>
-      <c r="M5" s="480"/>
-      <c r="N5" s="477" t="s">
+      <c r="K5" s="472"/>
+      <c r="L5" s="472"/>
+      <c r="M5" s="472"/>
+      <c r="N5" s="484" t="s">
         <v>221</v>
       </c>
-      <c r="O5" s="477"/>
-      <c r="P5" s="477"/>
+      <c r="O5" s="484"/>
+      <c r="P5" s="484"/>
       <c r="Q5" s="319"/>
       <c r="R5" s="319"/>
       <c r="S5" s="28"/>
@@ -33467,12 +33467,12 @@
     </row>
     <row r="8" spans="1:19" ht="45.75" customHeight="1" thickBot="1">
       <c r="A8" s="29"/>
-      <c r="C8" s="481" t="str">
+      <c r="C8" s="475" t="str">
         <f>_xlfn.CONCAT("PERIODO ", N5)</f>
         <v>PERIODO ABRIL - 2025</v>
       </c>
-      <c r="D8" s="482"/>
-      <c r="E8" s="483"/>
+      <c r="D8" s="476"/>
+      <c r="E8" s="477"/>
       <c r="G8" s="66" t="s">
         <v>1</v>
       </c>
@@ -33515,11 +33515,11 @@
     </row>
     <row r="10" spans="1:19" ht="42" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="C10" s="484" t="s">
+      <c r="C10" s="478" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="484"/>
-      <c r="E10" s="484"/>
+      <c r="D10" s="478"/>
+      <c r="E10" s="478"/>
       <c r="G10" s="92" t="s">
         <v>8</v>
       </c>
@@ -33693,11 +33693,11 @@
       <c r="C15" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="479">
+      <c r="D15" s="470">
         <f>R14</f>
         <v>122</v>
       </c>
-      <c r="E15" s="479"/>
+      <c r="E15" s="470"/>
       <c r="H15" s="45"/>
       <c r="M15" s="45"/>
       <c r="N15" s="45"/>
@@ -33740,11 +33740,11 @@
     </row>
     <row r="24" spans="1:19" ht="50.25" customHeight="1">
       <c r="A24" s="29"/>
-      <c r="C24" s="472" t="s">
+      <c r="C24" s="481" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="473"/>
-      <c r="E24" s="474"/>
+      <c r="D24" s="482"/>
+      <c r="E24" s="483"/>
       <c r="S24" s="28"/>
     </row>
     <row r="25" spans="1:19" ht="32.25" customHeight="1">
@@ -33752,11 +33752,11 @@
       <c r="C25" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="475">
+      <c r="D25" s="473">
         <f>SUM(M13:O13)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="476"/>
+      <c r="E25" s="474"/>
       <c r="S25" s="28"/>
     </row>
     <row r="26" spans="1:19" ht="33.75" customHeight="1">
@@ -33764,11 +33764,11 @@
       <c r="C26" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="475">
+      <c r="D26" s="473">
         <f>SUM(M12:O12)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="476"/>
+      <c r="E26" s="474"/>
       <c r="S26" s="28"/>
     </row>
     <row r="27" spans="1:19" ht="38.25" customHeight="1">
@@ -33800,11 +33800,11 @@
       <c r="C29" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="478">
+      <c r="D29" s="469">
         <f>SUM(M14:O14)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="478"/>
+      <c r="E29" s="469"/>
       <c r="S29" s="28"/>
     </row>
     <row r="30" spans="1:19">
@@ -33918,6 +33918,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="J4:O4"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="N5:P5"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D27:E27"/>
@@ -33929,12 +33935,6 @@
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="D11:E11"/>
-    <mergeCell ref="J4:O4"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="N5:P5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -40394,9 +40394,9 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27" customHeight="1">
       <c r="A1" s="114"/>
-      <c r="B1" s="529"/>
-      <c r="C1" s="530"/>
-      <c r="D1" s="531"/>
+      <c r="B1" s="531"/>
+      <c r="C1" s="532"/>
+      <c r="D1" s="533"/>
       <c r="E1" s="95"/>
       <c r="F1" s="98"/>
       <c r="G1" s="96"/>
@@ -40418,10 +40418,10 @@
       <c r="E2" s="104"/>
       <c r="G2" s="106"/>
       <c r="H2" s="98"/>
-      <c r="I2" s="538" t="s">
+      <c r="I2" s="527" t="s">
         <v>387</v>
       </c>
-      <c r="J2" s="539"/>
+      <c r="J2" s="528"/>
       <c r="K2" s="109"/>
       <c r="L2" s="98"/>
       <c r="M2" s="106"/>
@@ -40474,10 +40474,10 @@
       <c r="B5" s="157" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="532" t="s">
+      <c r="C5" s="534" t="s">
         <v>107</v>
       </c>
-      <c r="D5" s="533"/>
+      <c r="D5" s="535"/>
       <c r="E5" s="239" t="s">
         <v>109</v>
       </c>
@@ -40507,10 +40507,10 @@
       <c r="B6" s="266" t="s">
         <v>113</v>
       </c>
-      <c r="C6" s="534">
+      <c r="C6" s="536">
         <v>44725</v>
       </c>
-      <c r="D6" s="535"/>
+      <c r="D6" s="537"/>
       <c r="E6" s="458">
         <v>44908</v>
       </c>
@@ -40542,10 +40542,10 @@
       <c r="B7" s="267" t="s">
         <v>114</v>
       </c>
-      <c r="C7" s="536">
+      <c r="C7" s="538">
         <v>44789</v>
       </c>
-      <c r="D7" s="537"/>
+      <c r="D7" s="539"/>
       <c r="E7" s="459">
         <v>44608</v>
       </c>
@@ -40575,10 +40575,10 @@
       <c r="B8" s="267" t="s">
         <v>115</v>
       </c>
-      <c r="C8" s="536">
+      <c r="C8" s="538">
         <v>44868</v>
       </c>
-      <c r="D8" s="537"/>
+      <c r="D8" s="539"/>
       <c r="E8" s="459">
         <v>45049</v>
       </c>
@@ -40609,10 +40609,10 @@
       <c r="B9" s="267" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="536">
+      <c r="C9" s="538">
         <v>45439</v>
       </c>
-      <c r="D9" s="537"/>
+      <c r="D9" s="539"/>
       <c r="E9" s="459">
         <v>45623</v>
       </c>
@@ -40644,10 +40644,10 @@
       <c r="B10" s="267" t="s">
         <v>117</v>
       </c>
-      <c r="C10" s="536">
+      <c r="C10" s="538">
         <v>44900</v>
       </c>
-      <c r="D10" s="537"/>
+      <c r="D10" s="539"/>
       <c r="E10" s="459">
         <v>45082</v>
       </c>
@@ -40678,10 +40678,10 @@
       <c r="B11" s="267" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="536">
+      <c r="C11" s="538">
         <v>44930</v>
       </c>
-      <c r="D11" s="537"/>
+      <c r="D11" s="539"/>
       <c r="E11" s="459">
         <v>45111</v>
       </c>
@@ -40712,10 +40712,10 @@
       <c r="B12" s="268" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="524">
+      <c r="C12" s="529">
         <v>44958</v>
       </c>
-      <c r="D12" s="525"/>
+      <c r="D12" s="530"/>
       <c r="E12" s="460">
         <v>45139</v>
       </c>
@@ -40806,14 +40806,14 @@
       <c r="D16" s="382" t="s">
         <v>113</v>
       </c>
-      <c r="E16" s="526" t="s">
+      <c r="E16" s="524" t="s">
         <v>381</v>
       </c>
-      <c r="F16" s="527"/>
-      <c r="G16" s="527"/>
-      <c r="H16" s="527"/>
-      <c r="I16" s="527"/>
-      <c r="J16" s="528"/>
+      <c r="F16" s="525"/>
+      <c r="G16" s="525"/>
+      <c r="H16" s="525"/>
+      <c r="I16" s="525"/>
+      <c r="J16" s="526"/>
       <c r="K16" s="399"/>
       <c r="L16" s="134"/>
       <c r="M16" s="132"/>
@@ -40829,14 +40829,14 @@
       <c r="D17" s="382" t="s">
         <v>114</v>
       </c>
-      <c r="E17" s="526" t="s">
+      <c r="E17" s="524" t="s">
         <v>382</v>
       </c>
-      <c r="F17" s="527"/>
-      <c r="G17" s="527"/>
-      <c r="H17" s="527"/>
-      <c r="I17" s="527"/>
-      <c r="J17" s="528"/>
+      <c r="F17" s="525"/>
+      <c r="G17" s="525"/>
+      <c r="H17" s="525"/>
+      <c r="I17" s="525"/>
+      <c r="J17" s="526"/>
       <c r="K17" s="162"/>
       <c r="L17" s="145"/>
       <c r="M17" s="134"/>
@@ -40853,14 +40853,14 @@
       <c r="D18" s="383" t="s">
         <v>115</v>
       </c>
-      <c r="E18" s="526" t="s">
+      <c r="E18" s="524" t="s">
         <v>383</v>
       </c>
-      <c r="F18" s="527"/>
-      <c r="G18" s="527"/>
-      <c r="H18" s="527"/>
-      <c r="I18" s="527"/>
-      <c r="J18" s="528"/>
+      <c r="F18" s="525"/>
+      <c r="G18" s="525"/>
+      <c r="H18" s="525"/>
+      <c r="I18" s="525"/>
+      <c r="J18" s="526"/>
       <c r="L18" s="134"/>
       <c r="M18" s="130"/>
       <c r="N18" s="129"/>
@@ -40874,14 +40874,14 @@
       <c r="D19" s="384" t="s">
         <v>116</v>
       </c>
-      <c r="E19" s="526" t="s">
+      <c r="E19" s="524" t="s">
         <v>384</v>
       </c>
-      <c r="F19" s="527"/>
-      <c r="G19" s="527"/>
-      <c r="H19" s="527"/>
-      <c r="I19" s="527"/>
-      <c r="J19" s="528"/>
+      <c r="F19" s="525"/>
+      <c r="G19" s="525"/>
+      <c r="H19" s="525"/>
+      <c r="I19" s="525"/>
+      <c r="J19" s="526"/>
       <c r="K19" s="162"/>
       <c r="L19" s="145"/>
       <c r="M19" s="130"/>
@@ -40895,14 +40895,14 @@
       <c r="D20" s="383" t="s">
         <v>117</v>
       </c>
-      <c r="E20" s="526" t="s">
+      <c r="E20" s="524" t="s">
         <v>385</v>
       </c>
-      <c r="F20" s="527"/>
-      <c r="G20" s="527"/>
-      <c r="H20" s="527"/>
-      <c r="I20" s="527"/>
-      <c r="J20" s="528"/>
+      <c r="F20" s="525"/>
+      <c r="G20" s="525"/>
+      <c r="H20" s="525"/>
+      <c r="I20" s="525"/>
+      <c r="J20" s="526"/>
       <c r="K20" s="400"/>
       <c r="L20" s="385"/>
       <c r="M20" s="133"/>
@@ -40915,14 +40915,14 @@
       <c r="D21" s="386" t="s">
         <v>118</v>
       </c>
-      <c r="E21" s="526" t="s">
+      <c r="E21" s="524" t="s">
         <v>385</v>
       </c>
-      <c r="F21" s="527"/>
-      <c r="G21" s="527"/>
-      <c r="H21" s="527"/>
-      <c r="I21" s="527"/>
-      <c r="J21" s="528"/>
+      <c r="F21" s="525"/>
+      <c r="G21" s="525"/>
+      <c r="H21" s="525"/>
+      <c r="I21" s="525"/>
+      <c r="J21" s="526"/>
       <c r="K21" s="401"/>
       <c r="L21" s="68"/>
       <c r="M21" s="131"/>
@@ -40936,14 +40936,14 @@
       <c r="D22" s="402" t="s">
         <v>119</v>
       </c>
-      <c r="E22" s="526" t="s">
+      <c r="E22" s="524" t="s">
         <v>386</v>
       </c>
-      <c r="F22" s="527"/>
-      <c r="G22" s="527"/>
-      <c r="H22" s="527"/>
-      <c r="I22" s="527"/>
-      <c r="J22" s="528"/>
+      <c r="F22" s="525"/>
+      <c r="G22" s="525"/>
+      <c r="H22" s="525"/>
+      <c r="I22" s="525"/>
+      <c r="J22" s="526"/>
       <c r="L22" s="131"/>
       <c r="M22" s="134"/>
       <c r="N22" s="134"/>
@@ -41361,11 +41361,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="E21:J21"/>
-    <mergeCell ref="E16:J16"/>
-    <mergeCell ref="E17:J17"/>
-    <mergeCell ref="I2:J2"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="E20:J20"/>
     <mergeCell ref="E19:J19"/>
@@ -41378,6 +41373,11 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="E21:J21"/>
+    <mergeCell ref="E16:J16"/>
+    <mergeCell ref="E17:J17"/>
+    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="5" scale="47" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -41395,17 +41395,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010039E554BA5E2FA5449283D399C0FD5B7C" ma:contentTypeVersion="18" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="dd0678842d65e4207392abd035356b9c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xmlns:ns3="954542bb-2825-439d-9db6-a5c04d3b21fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d84746cc30da1fe182e7a313d44b54c" ns2:_="" ns3:_="">
     <xsd:import namespace="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
@@ -41660,6 +41649,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6AC9645-B568-450E-BF2C-C54CDA88D1C4}">
   <ds:schemaRefs>
@@ -41669,23 +41669,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83E8CA1-0683-49D4-9501-EE88776F2630}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
-    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE64779-B9F2-4AEC-A5E9-E8076DA89A71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41702,4 +41685,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83E8CA1-0683-49D4-9501-EE88776F2630}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
+    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Backend/output/informe_final.xlsx
+++ b/Backend/output/informe_final.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA6D9497-34AA-4219-A48B-9233A978051F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F1AC8CA-8FF1-4ECE-BCD3-4C0B18A0F6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" tabRatio="719" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" tabRatio="719" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="194">
   <si>
     <t>SUBSECRETARÍA DE EDUCACIÓN</t>
   </si>
@@ -626,6 +626,15 @@
     <t>Detalles de Cumplimiento -Planes de Tratamiento de Riesgos</t>
   </si>
   <si>
+    <t>ABRIL - 2025</t>
+  </si>
+  <si>
+    <t>Acum ABRIL - 2025</t>
+  </si>
+  <si>
+    <t>Hitos ADP ocurridos al 20 de ABRIL</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ciberseguridad </t>
   </si>
   <si>
@@ -669,6 +678,9 @@
   </si>
   <si>
     <t>Señales de alerta</t>
+  </si>
+  <si>
+    <t>Primer Trimestre -2025</t>
   </si>
   <si>
     <t>No implementados</t>
@@ -746,842 +758,6 @@
   </si>
   <si>
     <t>JUNIO - 2025</t>
-  </si>
-  <si>
-    <t>Gabinete Ministerio</t>
-  </si>
-  <si>
-    <t>Gabinete Subsecretaría</t>
-  </si>
-  <si>
-    <t>División Jurídica</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de Auditorías del Plan Anual de Auditoría efectivamente realizadas en el año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Número de documentos publicados en la web del Centro de Estudios en el año t.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de solicitudes de información respondidas oportunamente en el año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de solicitudes de certificados de estudio no disponibles en línea, derivadas a registro curriculares o la Unidad Nacional de Registro Curricular, que son resueltas en un plazo inferior o igual a 10 días hábiles en el año t.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sistema Calidad de Servicio y Experiencia Usuaria</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Medidas de Equidad de Género</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de participación de estudiantes, directivos, docentes, asistentes, coordinadores/as de informática y/o profesionales de la educación de establecimientos educacionales en acciones formativas del Centro de Innovación en el año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Cumplimiento de hito asociado a la entrega de fondos para compra de  equipamiento por parte de la Secretaría Ejecutiva EMTP</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Elaborar un Informe con recopilación y análisis de los procesos de formación docente generado a partir de la Red maestros de Maestros en el año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de provincias que 
-participan de las acciones del CPEIP 
-para la difusión del Marco para la 
-Buena Enseñanza (MBE) al año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de Establecimientos educativos que reciben formación en Bienestar Docente en el año t.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Elaborar un Informe financiero preliminar para proyecto de ley de Carrera Directiva entregado en el año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de comunas que 
-cuentan con una evaluación de 
-resultados de implementación del 
-Programa "A convivir se Aprende" en 
-el año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de personas jóvenes y adultas que se encuentran fuera del sistema escolar que se inscriben para iniciar, continuar y/o completar sus estudios de educación básica y/o su educación media a través de servicios educativos en el año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de ciudadanos que se examinan en los procesos de examinación de validación de estudios en el año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de acciones del Plan de difusión de adhesión de establecimientos educacionales al PIE, implementadas en el año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de tiempo en que los sistemas definidos como críticos por la institución están habilitados en el año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de sitios web con certificados de sitio seguro</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de tickets de atención resueltos oportunamente en el año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sistema Transformación Digital</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Concentración del Gasto Subtítulos 22 y 29</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de establecimientos subvencionados vigentes que declaran asistencia vía SIGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de transacciones realizadas a través del sistema SIGPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de procesos documentados de la Unidad de Reconocimiento y Admisión Escolar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de solicitudes de beneficios y/o préstamos otorgados por el Servicio de Bienestar pagados oportunamente</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de Expedientes de compras de Tratos Directos enviados oportunamente a la División Jurídica por parte del Departamento de Compras y Licitaciones</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sistema Estado Verde</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sistema de Riesgos Psicosociales laborales</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de cierres contables oportunos</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de contratos nuevos a honorarios de nivel central enviados oportunamente a firma de la autoridad por el Departamento de Gestión y Desarrollo de Personas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de ejecución del plan asociado al Centro de Recursos de Lectura, Aprendizaje y Bibliotecas Escolar CRA en el año t.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de ejecución del plan estratégico de Desarrollo Curricular en el año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de ejecución del plan de difusión de instrumentos curriculares, evaluativos y estrategias pedagógicas para Directivos, Jefe de UTP, Profesores, Supervisores Técnicos, Apoderados, Encargados de Bibliotecas Escolares, Seremi y Deprov en el año t.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de ejecución del plan de Evaluación y Estándares en el año t.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de ejecución del plan estratégico de la modernización de textos escolares en el año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de Textos Escolares entregados a los establecimientos educacionales subvencionados a la fecha comprometida.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de Kit evaluativo 
-entregados a los establecimientos 
-educacionales subvencionados dentro 
-del año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de actos administrativos que Adjudican una Licitación Pública, elaborados oportunamente en el año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de  actos administrativos que Aprueban Bases Administrativas y Técnicas de Licitación Pública, elaborados oportunamente en el año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de propuestas de convenios o reformulación tramitadas oportunamente en el año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de actos administrativos que transfieren recursos financieros tramitados oportunamente en el año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de actos administrativos que transfieren recursos financieros en el marco del artículo 11 de la Ley N°20.159 tramitados oportunamente en el año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de recursos de apelación, reclamación, jerárquico y/o extraordinarios de revisión tramitados oportunamente en el año t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Porcentaje de defensas a recursos de protección elaborados, presentados y cerrados en Sistema de Gestión Documental oportunamente en el año t</t>
-  </si>
-  <si>
-    <t>I16_002</t>
-  </si>
-  <si>
-    <t>I20_013</t>
-  </si>
-  <si>
-    <t>I20_014</t>
-  </si>
-  <si>
-    <t>I19_026</t>
-  </si>
-  <si>
-    <t>I23_015</t>
-  </si>
-  <si>
-    <t>I21_001</t>
-  </si>
-  <si>
-    <t>I24_001</t>
-  </si>
-  <si>
-    <t>I24_002</t>
-  </si>
-  <si>
-    <t>I25_002</t>
-  </si>
-  <si>
-    <t>I23_018</t>
-  </si>
-  <si>
-    <t>I25_003</t>
-  </si>
-  <si>
-    <t>I25_001</t>
-  </si>
-  <si>
-    <t>I25_011</t>
-  </si>
-  <si>
-    <t>I17_001</t>
-  </si>
-  <si>
-    <t>I23_004</t>
-  </si>
-  <si>
-    <t>I24_009</t>
-  </si>
-  <si>
-    <t>I16_043</t>
-  </si>
-  <si>
-    <t>I20_011</t>
-  </si>
-  <si>
-    <t>I20_012</t>
-  </si>
-  <si>
-    <t>I25_012</t>
-  </si>
-  <si>
-    <t>I21_002</t>
-  </si>
-  <si>
-    <t>I16_054</t>
-  </si>
-  <si>
-    <t>I19_012</t>
-  </si>
-  <si>
-    <t>I25_005</t>
-  </si>
-  <si>
-    <t>I21_007</t>
-  </si>
-  <si>
-    <t>I25_004</t>
-  </si>
-  <si>
-    <t>I23_019</t>
-  </si>
-  <si>
-    <t>I25_013</t>
-  </si>
-  <si>
-    <t>I20_006</t>
-  </si>
-  <si>
-    <t>I20_005</t>
-  </si>
-  <si>
-    <t>I19_020</t>
-  </si>
-  <si>
-    <t>I21_011</t>
-  </si>
-  <si>
-    <t>I21_012</t>
-  </si>
-  <si>
-    <t>I22_006</t>
-  </si>
-  <si>
-    <t>I19_019</t>
-  </si>
-  <si>
-    <t>I16_062</t>
-  </si>
-  <si>
-    <t>I25_010</t>
-  </si>
-  <si>
-    <t>I16_052</t>
-  </si>
-  <si>
-    <t>I24_004</t>
-  </si>
-  <si>
-    <t>I23_007</t>
-  </si>
-  <si>
-    <t>I22_008</t>
-  </si>
-  <si>
-    <t>I24_011</t>
-  </si>
-  <si>
-    <t>I24_003</t>
-  </si>
-  <si>
-    <t>I16_053</t>
-  </si>
-  <si>
-    <t>I23_014</t>
-  </si>
-  <si>
-    <t>I16_066</t>
-  </si>
-  <si>
-    <t>I25_007</t>
-  </si>
-  <si>
-    <t>I16_056</t>
-  </si>
-  <si>
-    <t>I25_006</t>
-  </si>
-  <si>
-    <t>I23_014-SECREDUC 01</t>
-  </si>
-  <si>
-    <t>I23_014-SECREDUC 02</t>
-  </si>
-  <si>
-    <t>I23_014-SECREDUC 03</t>
-  </si>
-  <si>
-    <t>I23_014-SECREDUC 04</t>
-  </si>
-  <si>
-    <t>I23_014-SECREDUC 05</t>
-  </si>
-  <si>
-    <t>I23_014-SECREDUC 06</t>
-  </si>
-  <si>
-    <t>I23_014-SECREDUC 07</t>
-  </si>
-  <si>
-    <t>I23_014-SECREDUC 08</t>
-  </si>
-  <si>
-    <t>I23_014-SECREDUC 09</t>
-  </si>
-  <si>
-    <t>I23_014-SECREDUC 10</t>
-  </si>
-  <si>
-    <t>I23_014-SECREDUC 11</t>
-  </si>
-  <si>
-    <t>I23_014-SECREDUC 12</t>
-  </si>
-  <si>
-    <t>I23_014-SECREDUC 13</t>
-  </si>
-  <si>
-    <t>I23_014-SECREDUC 14</t>
-  </si>
-  <si>
-    <t>I23_014-SECREDUC 15</t>
-  </si>
-  <si>
-    <t>I23_014-SECREDUC 16</t>
-  </si>
-  <si>
-    <t>I16_066-SECREDUC 01</t>
-  </si>
-  <si>
-    <t>I16_066-SECREDUC 02</t>
-  </si>
-  <si>
-    <t>I16_066-SECREDUC 03</t>
-  </si>
-  <si>
-    <t>I16_066-SECREDUC 04</t>
-  </si>
-  <si>
-    <t>I16_066-SECREDUC 05</t>
-  </si>
-  <si>
-    <t>I16_066-SECREDUC 06</t>
-  </si>
-  <si>
-    <t>I16_066-SECREDUC 07</t>
-  </si>
-  <si>
-    <t>I16_066-SECREDUC 08</t>
-  </si>
-  <si>
-    <t>I16_066-SECREDUC 09</t>
-  </si>
-  <si>
-    <t>I16_066-SECREDUC 10</t>
-  </si>
-  <si>
-    <t>I16_066-SECREDUC 11</t>
-  </si>
-  <si>
-    <t>I16_066-SECREDUC 12</t>
-  </si>
-  <si>
-    <t>I16_066-SECREDUC 13</t>
-  </si>
-  <si>
-    <t>I16_066-SECREDUC 14</t>
-  </si>
-  <si>
-    <t>I16_066-SECREDUC 15</t>
-  </si>
-  <si>
-    <t>I16_066-SECREDUC 16</t>
-  </si>
-  <si>
-    <t>I25_007-SECREDUC 01</t>
-  </si>
-  <si>
-    <t>I25_007-SECREDUC 02</t>
-  </si>
-  <si>
-    <t>I25_007-SECREDUC 03</t>
-  </si>
-  <si>
-    <t>I25_007-SECREDUC 04</t>
-  </si>
-  <si>
-    <t>I25_007-SECREDUC 05</t>
-  </si>
-  <si>
-    <t>I25_007-SECREDUC 06</t>
-  </si>
-  <si>
-    <t>I25_007-SECREDUC 07</t>
-  </si>
-  <si>
-    <t>I25_007-SECREDUC 08</t>
-  </si>
-  <si>
-    <t>I25_007-SECREDUC 09</t>
-  </si>
-  <si>
-    <t>I25_007-SECREDUC 10</t>
-  </si>
-  <si>
-    <t>I25_007-SECREDUC 11</t>
-  </si>
-  <si>
-    <t>I25_007-SECREDUC 12</t>
-  </si>
-  <si>
-    <t>I25_007-SECREDUC 13</t>
-  </si>
-  <si>
-    <t>I25_007-SECREDUC 14</t>
-  </si>
-  <si>
-    <t>I25_007-SECREDUC 15</t>
-  </si>
-  <si>
-    <t>I25_007-SECREDUC 16</t>
-  </si>
-  <si>
-    <t>I16_056-SECREDUC 01</t>
-  </si>
-  <si>
-    <t>I16_056-SECREDUC 02</t>
-  </si>
-  <si>
-    <t>I16_056-SECREDUC 03</t>
-  </si>
-  <si>
-    <t>I16_056-SECREDUC 04</t>
-  </si>
-  <si>
-    <t>I16_056-SECREDUC 05</t>
-  </si>
-  <si>
-    <t>I16_056-SECREDUC 06</t>
-  </si>
-  <si>
-    <t>I16_056-SECREDUC 07</t>
-  </si>
-  <si>
-    <t>I16_056-SECREDUC 08</t>
-  </si>
-  <si>
-    <t>I16_056-SECREDUC 09</t>
-  </si>
-  <si>
-    <t>I16_056-SECREDUC 10</t>
-  </si>
-  <si>
-    <t>I16_056-SECREDUC 11</t>
-  </si>
-  <si>
-    <t>I16_056-SECREDUC 12</t>
-  </si>
-  <si>
-    <t>I16_056-SECREDUC 13</t>
-  </si>
-  <si>
-    <t>I16_056-SECREDUC 14</t>
-  </si>
-  <si>
-    <t>I16_056-SECREDUC 15</t>
-  </si>
-  <si>
-    <t>I16_056-SECREDUC 16</t>
-  </si>
-  <si>
-    <t>I25_006-SECREDUC 01</t>
-  </si>
-  <si>
-    <t>I25_006-SECREDUC 02</t>
-  </si>
-  <si>
-    <t>I25_006-SECREDUC 03</t>
-  </si>
-  <si>
-    <t>I25_006-SECREDUC 04</t>
-  </si>
-  <si>
-    <t>I25_006-SECREDUC 05</t>
-  </si>
-  <si>
-    <t>I25_006-SECREDUC 06</t>
-  </si>
-  <si>
-    <t>I25_006-SECREDUC 07</t>
-  </si>
-  <si>
-    <t>I25_006-SECREDUC 08</t>
-  </si>
-  <si>
-    <t>I25_006-SECREDUC 09</t>
-  </si>
-  <si>
-    <t>I25_006-SECREDUC 10</t>
-  </si>
-  <si>
-    <t>I25_006-SECREDUC 11</t>
-  </si>
-  <si>
-    <t>I25_006-SECREDUC 12</t>
-  </si>
-  <si>
-    <t>I25_006-SECREDUC 13</t>
-  </si>
-  <si>
-    <t>I25_006-SECREDUC 14</t>
-  </si>
-  <si>
-    <t>I25_006-SECREDUC 15</t>
-  </si>
-  <si>
-    <t>I25_006-SECREDUC 16</t>
-  </si>
-  <si>
-    <t>La Araucanía</t>
-  </si>
-  <si>
-    <t>CNT</t>
-  </si>
-  <si>
-    <t>Recursos Financieros</t>
-  </si>
-  <si>
-    <t>Subvenciones</t>
-  </si>
-  <si>
-    <t>URAE</t>
-  </si>
-  <si>
-    <t>JURID</t>
-  </si>
-  <si>
-    <t>GABMIN</t>
-  </si>
-  <si>
-    <t>Auditoria</t>
-  </si>
-  <si>
-    <t>Estudios</t>
-  </si>
-  <si>
-    <t>Ayuda Mineduc</t>
-  </si>
-  <si>
-    <t>Innovación</t>
-  </si>
-  <si>
-    <t>TP</t>
-  </si>
-  <si>
-    <t>CRUCH</t>
-  </si>
-  <si>
-    <t>JUNAEB</t>
-  </si>
-  <si>
-    <t>Agencia de Calidad</t>
-  </si>
-  <si>
-    <t>DEP</t>
-  </si>
-  <si>
-    <t>Superintendencia de Educación</t>
-  </si>
-  <si>
-    <t>JUNJI</t>
-  </si>
-  <si>
-    <t>Superintendencia de Educación Superior</t>
-  </si>
-  <si>
-    <t>En enero 2025 se envió mediante mail del Jefe del Gabinete del Ministro, el resultado del monitoreo del tercer año de gestión.</t>
-  </si>
-  <si>
-    <t>En marzo 2025 se envió mediante mail del Jefe del Gabinete del Ministro, el resultado del monitoreo del tercer año de gestión.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En mayo 2025 se inició el monitoreo del tercer año de gestión
-</t>
-  </si>
-  <si>
-    <t>En mayo 2025 se inició el proceso de evaluación del primer año de gestión.</t>
-  </si>
-  <si>
-    <t>En mayo 2025 se envió a tramitación el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio del segundo año de gestión.</t>
-  </si>
-  <si>
-    <t>En febrero 2025 se tramitó totalmente el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio del segundo año de gestión.</t>
-  </si>
-  <si>
-    <t>En abril 2025 se tramitó totalmente el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio del segundo año de gestión.</t>
-  </si>
-  <si>
-    <t>Acum JUNIO - 2025</t>
-  </si>
-  <si>
-    <t>Hitos ADP ocurridos al 30 de JUNIO</t>
-  </si>
-  <si>
-    <t>SLEP Gabriela Mistral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLEP Chiloé </t>
-  </si>
-  <si>
-    <t>Se envía solicitud de informe de monitoreo para el segundo año de gestión, el cual debe enviarse a más tardar el 01 de junio de 2025.</t>
-  </si>
-  <si>
-    <t>Se nombra a Director Ejecutivo el 24 de febrero, por lo que no corresponde al Ministro, hacer seguimiento al II nivel, ya que finaliza la subrogancia.</t>
-  </si>
-  <si>
-    <t>Política de Gestión de Riesgos</t>
-  </si>
-  <si>
-    <t>Ranking de Procesos</t>
-  </si>
-  <si>
-    <t>Matriz de Riesgos</t>
-  </si>
-  <si>
-    <t>Ranking de Riesgos</t>
-  </si>
-  <si>
-    <t>Señales de Alerta - Asociadas a MR</t>
-  </si>
-  <si>
-    <t>Señales de Alerta - No Asociadas a MR</t>
-  </si>
-  <si>
-    <t>Plan de Tratamiento de Riesgos</t>
-  </si>
-  <si>
-    <t>Plan de Comunicaciones y Consulta</t>
-  </si>
-  <si>
-    <t>Pendiente actualizar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actualizado </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Institucionales </t>
-  </si>
-  <si>
-    <t>Señales de Alerta no asociadas a MR</t>
-  </si>
-  <si>
-    <t>Se hizo envío del 1° monitoreo al CAIGG, el 30/04</t>
-  </si>
-  <si>
-    <t>Segundo Trimestre - 2025</t>
-  </si>
-  <si>
-    <t>DPCG</t>
-  </si>
-  <si>
-    <t>Gabinete DIPLAP</t>
-  </si>
-  <si>
-    <t>Seguridad de la Información</t>
-  </si>
-  <si>
-    <t>Dirección de Educación Pública</t>
-  </si>
-  <si>
-    <t>Junta Nacional de Auxilio Escolar y Becas</t>
-  </si>
-  <si>
-    <t>Junta Nacional de Jardines Infantiles</t>
-  </si>
-  <si>
-    <t>Subsecretaria de Educación</t>
-  </si>
-  <si>
-    <t>Subsecretaría Educación Parvularia</t>
-  </si>
-  <si>
-    <t>Subsecretaría Educación Superior</t>
-  </si>
-  <si>
-    <t>Subsecretaría de Educación Parvularia</t>
-  </si>
-  <si>
-    <t>Subsecretaría de Educación Superior</t>
-  </si>
-  <si>
-    <t>Hogares y Residencias Estudiantiles (Hogares Insulares V Región)</t>
-  </si>
-  <si>
-    <t>Beca Integración Territorial (Programa Especial Beca Art. 56 Ley N° 18.681)</t>
-  </si>
-  <si>
-    <t>Beca Polimetales Arica</t>
-  </si>
-  <si>
-    <t>Programa de Bienestar Socioemocional y Educación Integral</t>
-  </si>
-  <si>
-    <t>Subvención Gratuidad
-*Se ha definido iniciar el desarrollo de las nuevas fichas con los grupos correspondientes a Carrera Docente y Gratuidad, dada su importancia estructural dentro del sistema de subvenciones escolares. Ambas representan pilares centrales de las reformas educativas de los últimos años, al abordar dimensiones clave como la equidad en el acceso y la profesionalización del cuerpo docente. Además de su relevancia técnica y programática, estas subvenciones tienen un peso presupuestario significativo, ya que en conjunto representan aproximadamente el 70% del gasto total actualmente contenido en la ficha "Otras Subvenciones Escolares". Por tanto, su priorización permite avanzar en una primera etapa con los componentes de mayor impacto financiero y estratégico del sistema.</t>
-  </si>
-  <si>
-    <t>Carrera Docente
-*Se ha definido iniciar el desarrollo de las nuevas fichas con los grupos correspondientes a Carrera Docente y Gratuidad, dada su importancia estructural dentro del sistema de subvenciones escolares. Ambas representan pilares centrales de las reformas educativas de los últimos años, al abordar dimensiones clave como la equidad en el acceso y la profesionalización del cuerpo docente. Además de su relevancia técnica y programática, estas subvenciones tienen un peso presupuestario significativo, ya que en conjunto representan aproximadamente el 70% del gasto total actualmente contenido en la ficha "Otras Subvenciones Escolares". Por tanto, su priorización permite avanzar en una primera etapa con los componentes de mayor impacto financiero y estratégico del sistema.</t>
-  </si>
-  <si>
-    <t>Fonoinfancia</t>
-  </si>
-  <si>
-    <t>Jardines Infantiles y Salas Cuna Modalidad Convencional
-*Ingresa para Reformulación programática En Ante 2026, debido a que se incorporará dentro de su diseño los programas "Programa de Extensión Horaria" y "Programa Vacaciones en mi Jardín"</t>
-  </si>
-  <si>
-    <t>Beca Reparacióin</t>
-  </si>
-  <si>
-    <t>Programa de Acompañamiento y Acceso Efectivo a la Educación Superior (PACE) (PATP ingresaría como parte de PACE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programa Educativo Alternativo de Atención del Párvulo </t>
-  </si>
-  <si>
-    <t>Jardín Infantil Clásico de Administración Directa</t>
-  </si>
-  <si>
-    <t>Jardín Infantil Clásico de Administración VTF</t>
-  </si>
-  <si>
-    <t>Infraestructura y equipamiento para la Educación Pública del siglo XXI (incluirá Contingencia para Mantención y Reparación de Infraestructura Escolar (Plan de Reactivación Educativa)</t>
-  </si>
-  <si>
-    <t>Fondo de Apoyo a la Educación Pública (incluirá Financiamiento de la Educación Pública (Fondo de Incentivo para la Gestión Administrativa de los SLEP)</t>
-  </si>
-  <si>
-    <t>Fondo para la Reactivación Educativa (Plan de Reactivación Educativa)</t>
-  </si>
-  <si>
-    <t>En evaluación. Primer informe de evaluación recibido con calificación OT al 09/06</t>
-  </si>
-  <si>
-    <t>En evaluación. Primer informe de evaluación recibido con calificación OT al 12/06</t>
-  </si>
-  <si>
-    <t>En evaluación. Primer informe de evaluación recibido con calificación OT al 19/06</t>
-  </si>
-  <si>
-    <t>En evaluación. Primer informe de evaluación recibido con calificación OT al 11/06</t>
-  </si>
-  <si>
-    <t>En evaluación. Primer informe de evaluación recibido con calificación OT al 13/06</t>
-  </si>
-  <si>
-    <t>En evaluación. Primer informe de evaluación recibido con calificación OT al 05/06</t>
-  </si>
-  <si>
-    <t>En evaluación. Primer informe de evaluación recibido con calificación FI al 30/05</t>
-  </si>
-  <si>
-    <t>En evaluación. Primer informe de evaluación recibido con calificación OT al 06/06</t>
-  </si>
-  <si>
-    <t>En evaluación. Primer informe de evaluación recibido con calificación OT al 10/06</t>
-  </si>
-  <si>
-    <t>Inicio Monitoreo 2024
-ejecución año t-1</t>
-  </si>
-  <si>
-    <t>Envío de orientaciones
-a contrapartes internas</t>
-  </si>
-  <si>
-    <t>Evaluación
-MDSyF</t>
-  </si>
-  <si>
-    <t>Reporte en
-plataforma</t>
-  </si>
-  <si>
-    <t>Inicio Ex ante</t>
-  </si>
-  <si>
-    <t>Envío de
-lineamientos
-internos</t>
-  </si>
-  <si>
-    <t>Ingreso máximo ex ante</t>
-  </si>
-  <si>
-    <t>Iteración 1</t>
-  </si>
-  <si>
-    <t>Iteración 2</t>
-  </si>
-  <si>
-    <t>Iteración 3</t>
-  </si>
-  <si>
-    <t>Iteración 4</t>
-  </si>
-  <si>
-    <t>Publicación
-de informes
-de monitoreo</t>
-  </si>
-  <si>
-    <t>Cierre
-ex ante</t>
   </si>
 </sst>
 </file>
@@ -14877,15 +14053,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -15000,15 +14167,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>38</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -15123,15 +14281,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -15495,9 +14644,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>4</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -15598,9 +14744,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -15701,9 +14844,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>4</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -15898,6 +15038,14 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10697682406354191"/>
+          <c:y val="4.1212112034207132E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -15934,8 +15082,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="4.0125577630341101E-2"/>
-          <c:y val="0.22576923538662858"/>
+          <c:x val="5.4958833954806087E-2"/>
+          <c:y val="0.22576931318592031"/>
           <c:w val="0.91300096501850747"/>
           <c:h val="0.57180930885866232"/>
         </c:manualLayout>
@@ -16077,10 +15225,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>62</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -16304,11 +15452,6 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{19CC5CE4-8008-44CA-804B-4352D72FAB58}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -16322,7 +15465,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -16338,11 +15480,6 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{51DCDCB1-945D-4A85-9D4C-0EB8F4E3DA23}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -16356,7 +15493,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -16372,11 +15508,6 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{498A27AC-35BD-415F-B019-9AC8DE13CFCB}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -16390,7 +15521,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -16406,11 +15536,6 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5C4FD578-ED24-411F-8707-A8CBD236E848}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -16424,7 +15549,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -16452,17 +15576,6 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{DC3ABDF9-0378-464A-A503-69CFF3C6B18F}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr>
-                        <a:defRPr sz="1400">
-                          <a:solidFill>
-                            <a:schemeClr val="lt1"/>
-                          </a:solidFill>
-                        </a:defRPr>
-                      </a:pPr>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -16517,7 +15630,6 @@
                       <a:noFill/>
                     </a:ln>
                   </c15:spPr>
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -16545,17 +15657,6 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{946987A8-F513-487B-9954-E6747EE0AD23}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr>
-                        <a:defRPr sz="1400">
-                          <a:solidFill>
-                            <a:schemeClr val="lt1"/>
-                          </a:solidFill>
-                        </a:defRPr>
-                      </a:pPr>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -16610,7 +15711,6 @@
                       <a:noFill/>
                     </a:ln>
                   </c15:spPr>
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -16638,17 +15738,6 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{34000DD1-9854-40E5-8949-47B66506F84A}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr>
-                        <a:defRPr sz="1400">
-                          <a:solidFill>
-                            <a:schemeClr val="lt1"/>
-                          </a:solidFill>
-                        </a:defRPr>
-                      </a:pPr>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -16703,7 +15792,6 @@
                       <a:noFill/>
                     </a:ln>
                   </c15:spPr>
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -16719,11 +15807,6 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7282BB45-61DF-4AF7-B28A-C79F724B2905}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -16737,7 +15820,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -16765,17 +15847,6 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{048D8428-BD57-4F4F-B341-30CEAF14FBE0}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr>
-                        <a:defRPr sz="1400">
-                          <a:solidFill>
-                            <a:schemeClr val="lt1"/>
-                          </a:solidFill>
-                        </a:defRPr>
-                      </a:pPr>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -16830,7 +15901,6 @@
                       <a:noFill/>
                     </a:ln>
                   </c15:spPr>
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -16858,17 +15928,6 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{D47FBD07-B600-4647-9AC3-DDD5C16D4A1B}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr>
-                        <a:defRPr sz="1400">
-                          <a:solidFill>
-                            <a:schemeClr val="lt1"/>
-                          </a:solidFill>
-                        </a:defRPr>
-                      </a:pPr>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -16923,7 +15982,6 @@
                       <a:noFill/>
                     </a:ln>
                   </c15:spPr>
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -17049,17 +16107,6 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{5AAF0EFF-FCAD-47CA-8164-271E9630B9AA}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr>
-                        <a:defRPr sz="1400">
-                          <a:solidFill>
-                            <a:schemeClr val="lt1"/>
-                          </a:solidFill>
-                        </a:defRPr>
-                      </a:pPr>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -17114,7 +16161,6 @@
                       <a:noFill/>
                     </a:ln>
                   </c15:spPr>
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -17315,100 +16361,6 @@
           <c:cat>
             <c:multiLvlStrRef>
               <c:f>datos_graficos!$A$3:$B$15</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="13"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Inicio Monitoreo 2024
-ejecución año t-1</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>Envío de orientaciones
-a contrapartes internas</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>Evaluación
-MDSyF</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>Reporte en
-plataforma</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>Inicio Ex ante</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>Envío de
-lineamientos
-internos</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>Ingreso máximo ex ante</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>Iteración 1</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>Iteración 2</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>Iteración 3</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>Iteración 4</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>Publicación
-de informes
-de monitoreo</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>Cierre
-ex ante</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>20-dic</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>03-ene</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>20-ene</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>26-ene</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>06-may</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>14-may</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>30-may</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>06-jun</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>13-jun</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>20-jun</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>27-jun</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>30-jun</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>02-jul</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
             </c:multiLvlStrRef>
           </c:cat>
           <c:val>
@@ -17417,45 +16369,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-1</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>-1</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -17466,54 +16379,6 @@
                 <c15:f>datos_graficos!$B$3:$B$15</c15:f>
                 <c15:dlblRangeCache>
                   <c:ptCount val="13"/>
-                  <c:pt idx="0">
-                    <c:v>Inicio Monitoreo 2024
-ejecución año t-1</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>Envío de orientaciones
-a contrapartes internas</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>Evaluación
-MDSyF</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>Reporte en
-plataforma</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>Inicio Ex ante</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>Envío de
-lineamientos
-internos</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>Ingreso máximo ex ante</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>Iteración 1</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>Iteración 2</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>Iteración 3</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>Iteración 4</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>Publicación
-de informes
-de monitoreo</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>Cierre
-ex ante</c:v>
-                  </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
             </c:ext>
@@ -17607,11 +16472,6 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B639E17C-F927-4ABF-B89A-77B055BAB1D7}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -17625,7 +16485,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -17641,11 +16500,6 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4D28ED35-9A2A-48AF-8C6D-423FF60A1C65}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -17659,7 +16513,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -17675,11 +16528,6 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{899A2D70-95A4-497F-99FF-8EC11ACA35BE}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -17693,7 +16541,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -17709,11 +16556,6 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B2310557-98E6-4B50-8554-DD50F2EB44C7}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -17727,7 +16569,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -17743,11 +16584,6 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8C3F5409-B6CB-4CA9-8B92-7FE59F72C15B}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -17761,7 +16597,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -17777,11 +16612,6 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{383B4AB5-977F-4F81-9B0A-A0AAC8BAD3C3}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -17795,7 +16625,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -17811,11 +16640,6 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{43BD0955-07F8-4958-8942-AEA9B8E65028}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -17829,7 +16653,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -17845,11 +16668,6 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DFBB97ED-3FBC-4B85-A216-0DD6C424513F}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -17863,7 +16681,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -17879,11 +16696,6 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C4426DDB-D8A7-4B7E-BAF9-D2A46DAAD060}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -17897,7 +16709,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -17913,11 +16724,6 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{ECF57E5A-9DA1-4EAE-8E6C-4274E53BC516}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -17931,7 +16737,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -17947,11 +16752,6 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{25F58EE6-9B21-44CC-8A61-D1DAF2A8C778}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -17965,7 +16765,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -17981,11 +16780,6 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DF326976-AC91-4342-A618-B98376739230}" type="CELLRANGE">
-                      <a:rPr lang="es-CL"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
                     <a:endParaRPr lang="es-CL"/>
                   </a:p>
                 </c:rich>
@@ -17999,7 +16793,6 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
                   <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
@@ -18081,100 +16874,6 @@
           <c:cat>
             <c:multiLvlStrRef>
               <c:f>datos_graficos!$A$3:$B$15</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="13"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Inicio Monitoreo 2024
-ejecución año t-1</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>Envío de orientaciones
-a contrapartes internas</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>Evaluación
-MDSyF</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>Reporte en
-plataforma</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>Inicio Ex ante</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>Envío de
-lineamientos
-internos</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>Ingreso máximo ex ante</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>Iteración 1</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>Iteración 2</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>Iteración 3</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>Iteración 4</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>Publicación
-de informes
-de monitoreo</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>Cierre
-ex ante</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>20-dic</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>03-ene</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>20-ene</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>26-ene</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>06-may</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>14-may</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>30-may</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>06-jun</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>13-jun</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>20-jun</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>27-jun</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>30-jun</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>02-jul</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
             </c:multiLvlStrRef>
           </c:cat>
           <c:val>
@@ -18183,45 +16882,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -18232,45 +16892,6 @@
                 <c15:f>datos_graficos!$A$3:$A$15</c15:f>
                 <c15:dlblRangeCache>
                   <c:ptCount val="13"/>
-                  <c:pt idx="0">
-                    <c:v>20-dic</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>03-ene</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>20-ene</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>26-ene</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>06-may</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>14-may</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>30-may</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>06-jun</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>13-jun</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>20-jun</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>27-jun</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>30-jun</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>02-jul</c:v>
-                  </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
             </c:ext>
@@ -18638,30 +17259,13 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'programas sociales'!$B$16:$B$21</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>Dirección de Educación Pública</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Junta Nacional de Auxilio Escolar y Becas</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Junta Nacional de Jardines Infantiles</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Subsecretaria de Educación</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Subsecretaría Educación Parvularia</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Subsecretaría Educación Superior</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -18669,24 +17273,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>25</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -25477,13 +24063,13 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>440379</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>294657</xdr:rowOff>
+      <xdr:rowOff>225384</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>467591</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>246847</xdr:rowOff>
+      <xdr:rowOff>177574</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -25498,7 +24084,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6744197" y="5559384"/>
+          <a:off x="6744197" y="5490111"/>
           <a:ext cx="6261758" cy="437099"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -25556,13 +24142,13 @@
       <xdr:col>12</xdr:col>
       <xdr:colOff>622218</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>283971</xdr:rowOff>
+      <xdr:rowOff>232017</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>5645728</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>218949</xdr:rowOff>
+      <xdr:rowOff>166995</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -25577,7 +24163,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13160582" y="5548698"/>
+          <a:off x="13160582" y="5496744"/>
           <a:ext cx="9612828" cy="419887"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -25650,15 +24236,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>350076</xdr:colOff>
+      <xdr:colOff>277091</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>178131</xdr:rowOff>
+      <xdr:rowOff>34636</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>439140</xdr:colOff>
+      <xdr:colOff>421821</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>178130</xdr:rowOff>
+      <xdr:rowOff>22265</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -25673,8 +24259,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6653894" y="10620995"/>
-          <a:ext cx="6323610" cy="380999"/>
+          <a:off x="6580909" y="10477500"/>
+          <a:ext cx="6379276" cy="368629"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -25729,15 +24315,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>623454</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>-1</xdr:rowOff>
+      <xdr:colOff>640772</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>34636</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>5559136</xdr:colOff>
+      <xdr:colOff>5645727</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>173182</xdr:rowOff>
+      <xdr:rowOff>17319</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -25752,8 +24338,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13161818" y="10633363"/>
-          <a:ext cx="9525000" cy="363683"/>
+          <a:off x="13179136" y="10477500"/>
+          <a:ext cx="9594273" cy="363683"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -26078,21 +24664,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>311727</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>69272</xdr:rowOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>155864</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>415637</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>80020</xdr:rowOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>32635</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="11" name="Imagen 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EA48795-0D10-D86B-EB71-F63889910CEC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B36164D6-912F-B3CF-146B-AB97567626D2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -26114,8 +24700,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6607752" y="11070647"/>
-          <a:ext cx="6333260" cy="3820748"/>
+          <a:off x="6607752" y="10966739"/>
+          <a:ext cx="6333260" cy="3543896"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -26127,22 +24713,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>606137</xdr:colOff>
+      <xdr:colOff>640772</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>69274</xdr:rowOff>
+      <xdr:rowOff>17317</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>5583585</xdr:colOff>
+      <xdr:colOff>5645727</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>467957</xdr:rowOff>
+      <xdr:rowOff>491484</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="9" name="Imagen 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3C56B4B-9014-6A19-28C3-A37CE962C64A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEFFF53B-C9D2-B8C2-A1DB-98A97071CE68}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -26164,8 +24750,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13131512" y="11070649"/>
-          <a:ext cx="9578023" cy="3218083"/>
+          <a:off x="13166147" y="11018692"/>
+          <a:ext cx="9605530" cy="3293567"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -26177,22 +24763,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>623453</xdr:colOff>
+      <xdr:colOff>623454</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>329046</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>161585</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>5628410</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>147620</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="10" name="Imagen 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A42BCCCA-AD9C-F81D-9817-E1D1BA2DA650}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A628396-D2DF-AB8F-D5BE-4305D8D852D3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -26214,8 +24800,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13148828" y="6091671"/>
-          <a:ext cx="9644497" cy="4118789"/>
+          <a:off x="13148829" y="6091671"/>
+          <a:ext cx="9605531" cy="3685724"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -26227,22 +24813,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>450272</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>51955</xdr:rowOff>
+      <xdr:colOff>450273</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>259775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>467590</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>147824</xdr:rowOff>
+      <xdr:colOff>381001</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>95304</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="8" name="Imagen 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC2EFB7C-D73E-8D5E-4A00-D9DA610BBE5D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76054679-59D2-C8F9-141E-79EEABEE7C33}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -26264,8 +24850,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6746297" y="6157480"/>
-          <a:ext cx="6246668" cy="4420219"/>
+          <a:off x="6746298" y="6022400"/>
+          <a:ext cx="6160078" cy="4121779"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -27646,7 +26232,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s326892"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s327302"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -27711,7 +26297,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s326893"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s327303"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -27828,7 +26414,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s326894"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s327304"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -27893,7 +26479,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s326895"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s327305"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -27958,7 +26544,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s326896"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s327306"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -28023,7 +26609,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s326897"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s327307"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -28088,7 +26674,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s326898"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s327308"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -28153,7 +26739,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s326899"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s327309"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -28218,7 +26804,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s326900"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s327310"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -28283,7 +26869,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s326901"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s327311"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -31029,7 +29615,7 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="14" name="Gráfico 13">
+        <xdr:cNvPr id="14" name="signals_chart">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25950EC3-1590-32C4-829D-B644D554DDF0}"/>
@@ -31053,19 +29639,19 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>44822</xdr:colOff>
+      <xdr:colOff>717176</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>291354</xdr:rowOff>
+      <xdr:rowOff>112059</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>235323</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1008529</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="15" name="Gráfico 14">
+        <xdr:cNvPr id="15" name="ptr_chart">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44FBD140-EB46-B47C-FF82-ACD6C1641FD5}"/>
@@ -31683,7 +30269,7 @@
       <c r="D12" s="82"/>
       <c r="E12" s="225"/>
       <c r="F12" s="591" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G12" s="592"/>
       <c r="H12" s="82"/>
@@ -32492,7 +31078,7 @@
     </row>
     <row r="2" spans="1:17" ht="36">
       <c r="B2" s="120" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C2" s="120"/>
       <c r="D2" s="82"/>
@@ -32500,7 +31086,7 @@
       <c r="G2" s="90"/>
       <c r="H2" s="82"/>
       <c r="I2" s="651" t="s">
-        <v>392</v>
+        <v>165</v>
       </c>
       <c r="J2" s="652"/>
       <c r="K2" s="93"/>
@@ -32514,7 +31100,7 @@
     <row r="3" spans="1:17" s="59" customFormat="1" ht="22.5" customHeight="1">
       <c r="A3" s="85"/>
       <c r="B3" s="59" t="s">
-        <v>393</v>
+        <v>166</v>
       </c>
       <c r="D3" s="91"/>
       <c r="E3" s="84"/>
@@ -32556,7 +31142,7 @@
         <v>58</v>
       </c>
       <c r="C5" s="658" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D5" s="659"/>
       <c r="E5" s="579" t="s">
@@ -32586,31 +31172,15 @@
     </row>
     <row r="6" spans="1:17" ht="29.25" thickBot="1">
       <c r="A6" s="79"/>
-      <c r="B6" s="582" t="s">
-        <v>394</v>
-      </c>
-      <c r="C6" s="665">
-        <v>45231</v>
-      </c>
+      <c r="B6" s="582"/>
+      <c r="C6" s="665"/>
       <c r="D6" s="666"/>
-      <c r="E6" s="583">
-        <v>45413</v>
-      </c>
-      <c r="F6" s="583">
-        <v>45597</v>
-      </c>
-      <c r="G6" s="583">
-        <v>45778</v>
-      </c>
-      <c r="H6" s="583">
-        <v>45962</v>
-      </c>
-      <c r="I6" s="583">
-        <v>46143</v>
-      </c>
-      <c r="J6" s="584">
-        <v>46327</v>
-      </c>
+      <c r="E6" s="583"/>
+      <c r="F6" s="583"/>
+      <c r="G6" s="583"/>
+      <c r="H6" s="583"/>
+      <c r="I6" s="583"/>
+      <c r="J6" s="584"/>
       <c r="K6" s="78"/>
       <c r="L6" s="82"/>
       <c r="M6" s="82"/>
@@ -32735,12 +31305,8 @@
         <v>145</v>
       </c>
       <c r="C13" s="493"/>
-      <c r="D13" s="294" t="s">
-        <v>394</v>
-      </c>
-      <c r="E13" s="648" t="s">
-        <v>396</v>
-      </c>
+      <c r="D13" s="294"/>
+      <c r="E13" s="648"/>
       <c r="F13" s="649"/>
       <c r="G13" s="649"/>
       <c r="H13" s="649"/>
@@ -32759,12 +31325,8 @@
         <v>65</v>
       </c>
       <c r="C14" s="492"/>
-      <c r="D14" s="294" t="s">
-        <v>395</v>
-      </c>
-      <c r="E14" s="648" t="s">
-        <v>397</v>
-      </c>
+      <c r="D14" s="294"/>
+      <c r="E14" s="648"/>
       <c r="F14" s="649"/>
       <c r="G14" s="649"/>
       <c r="H14" s="649"/>
@@ -33428,7 +31990,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="766" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="C4" s="767"/>
       <c r="D4" s="767"/>
@@ -33542,7 +32104,7 @@
       <c r="G7" s="116"/>
       <c r="H7" s="747">
         <f>I23</f>
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="I7" s="749"/>
       <c r="J7" s="749"/>
@@ -33551,7 +32113,7 @@
       <c r="M7" s="116"/>
       <c r="N7" s="753">
         <f>L23</f>
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="O7" s="754"/>
       <c r="P7" s="755"/>
@@ -33559,7 +32121,7 @@
       <c r="R7" s="152"/>
       <c r="S7" s="747">
         <f>O23</f>
-        <v>473</v>
+        <v>0</v>
       </c>
       <c r="T7" s="748"/>
       <c r="U7" s="89"/>
@@ -33567,7 +32129,7 @@
       <c r="W7" s="82"/>
       <c r="X7" s="747">
         <f>R23</f>
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="748"/>
       <c r="Z7" s="141"/>
@@ -33575,15 +32137,9 @@
     </row>
     <row r="8" spans="1:28" ht="21.75" customHeight="1" thickBot="1">
       <c r="A8" s="181"/>
-      <c r="B8" s="189" t="s">
-        <v>398</v>
-      </c>
-      <c r="C8" s="184" t="s">
-        <v>406</v>
-      </c>
-      <c r="D8" s="182">
-        <v>2019</v>
-      </c>
+      <c r="B8" s="189"/>
+      <c r="C8" s="184"/>
+      <c r="D8" s="182"/>
       <c r="E8" s="198"/>
       <c r="F8" s="89"/>
       <c r="G8" s="144"/>
@@ -33610,15 +32166,9 @@
     </row>
     <row r="9" spans="1:28" ht="18" customHeight="1" thickBot="1">
       <c r="A9" s="183"/>
-      <c r="B9" s="189" t="s">
-        <v>399</v>
-      </c>
-      <c r="C9" s="185" t="s">
-        <v>407</v>
-      </c>
-      <c r="D9" s="134">
-        <v>2024</v>
-      </c>
+      <c r="B9" s="189"/>
+      <c r="C9" s="185"/>
+      <c r="D9" s="134"/>
       <c r="E9" s="199"/>
       <c r="F9" s="80"/>
       <c r="G9" s="106"/>
@@ -33645,15 +32195,9 @@
     </row>
     <row r="10" spans="1:28" ht="21" customHeight="1">
       <c r="A10" s="81"/>
-      <c r="B10" s="189" t="s">
-        <v>400</v>
-      </c>
-      <c r="C10" s="185" t="s">
-        <v>407</v>
-      </c>
-      <c r="D10" s="134">
-        <v>2024</v>
-      </c>
+      <c r="B10" s="189"/>
+      <c r="C10" s="185"/>
+      <c r="D10" s="134"/>
       <c r="E10" s="199"/>
       <c r="F10" s="89"/>
       <c r="G10" s="779" t="s">
@@ -33682,15 +32226,9 @@
     </row>
     <row r="11" spans="1:28" ht="19.5" customHeight="1">
       <c r="A11" s="79"/>
-      <c r="B11" s="189" t="s">
-        <v>401</v>
-      </c>
-      <c r="C11" s="188" t="s">
-        <v>407</v>
-      </c>
-      <c r="D11" s="134">
-        <v>2024</v>
-      </c>
+      <c r="B11" s="189"/>
+      <c r="C11" s="188"/>
+      <c r="D11" s="134"/>
       <c r="E11" s="199"/>
       <c r="F11" s="89"/>
       <c r="G11" s="782" t="s">
@@ -33727,15 +32265,9 @@
     </row>
     <row r="12" spans="1:28" ht="17.25" customHeight="1">
       <c r="A12" s="79"/>
-      <c r="B12" s="190" t="s">
-        <v>402</v>
-      </c>
-      <c r="C12" s="192" t="s">
-        <v>407</v>
-      </c>
-      <c r="D12" s="185">
-        <v>2024</v>
-      </c>
+      <c r="B12" s="190"/>
+      <c r="C12" s="192"/>
+      <c r="D12" s="185"/>
       <c r="E12" s="199"/>
       <c r="F12" s="89"/>
       <c r="G12" s="782"/>
@@ -33770,15 +32302,9 @@
     </row>
     <row r="13" spans="1:28" ht="18.75" customHeight="1">
       <c r="A13" s="79"/>
-      <c r="B13" s="189" t="s">
-        <v>403</v>
-      </c>
-      <c r="C13" s="184" t="s">
-        <v>407</v>
-      </c>
-      <c r="D13" s="134">
-        <v>2024</v>
-      </c>
+      <c r="B13" s="189"/>
+      <c r="C13" s="184"/>
+      <c r="D13" s="134"/>
       <c r="E13" s="199"/>
       <c r="F13" s="89"/>
       <c r="G13" s="782"/>
@@ -33805,101 +32331,61 @@
     </row>
     <row r="14" spans="1:28" ht="18.75" customHeight="1">
       <c r="A14" s="79"/>
-      <c r="B14" s="189" t="s">
-        <v>404</v>
-      </c>
-      <c r="C14" s="185" t="s">
-        <v>407</v>
-      </c>
-      <c r="D14" s="134">
-        <v>2024</v>
-      </c>
+      <c r="B14" s="189"/>
+      <c r="C14" s="185"/>
+      <c r="D14" s="134"/>
       <c r="E14" s="199"/>
       <c r="F14" s="89"/>
       <c r="G14" s="756" t="s">
         <v>18</v>
       </c>
       <c r="H14" s="757"/>
-      <c r="I14" s="734">
-        <v>4</v>
-      </c>
+      <c r="I14" s="734"/>
       <c r="J14" s="758"/>
       <c r="K14" s="759"/>
-      <c r="L14" s="732">
-        <v>8</v>
-      </c>
+      <c r="L14" s="732"/>
       <c r="M14" s="732"/>
       <c r="N14" s="732"/>
-      <c r="O14" s="732">
-        <v>30</v>
-      </c>
+      <c r="O14" s="732"/>
       <c r="P14" s="732"/>
       <c r="Q14" s="732"/>
-      <c r="R14" s="732">
-        <v>53</v>
-      </c>
+      <c r="R14" s="732"/>
       <c r="S14" s="732"/>
-      <c r="T14" s="732">
-        <v>0</v>
-      </c>
+      <c r="T14" s="732"/>
       <c r="U14" s="732"/>
-      <c r="V14" s="732">
-        <v>8</v>
-      </c>
+      <c r="V14" s="732"/>
       <c r="W14" s="734"/>
-      <c r="X14" s="732">
-        <v>2</v>
-      </c>
+      <c r="X14" s="732"/>
       <c r="Y14" s="733"/>
       <c r="Z14" s="80"/>
     </row>
     <row r="15" spans="1:28" ht="19.5" customHeight="1" thickBot="1">
       <c r="A15" s="79"/>
-      <c r="B15" s="191" t="s">
-        <v>405</v>
-      </c>
-      <c r="C15" s="187" t="s">
-        <v>407</v>
-      </c>
-      <c r="D15" s="186">
-        <v>2024</v>
-      </c>
+      <c r="B15" s="191"/>
+      <c r="C15" s="187"/>
+      <c r="D15" s="186"/>
       <c r="E15" s="200"/>
       <c r="F15" s="89"/>
       <c r="G15" s="756" t="s">
         <v>16</v>
       </c>
       <c r="H15" s="757"/>
-      <c r="I15" s="734">
-        <v>11</v>
-      </c>
+      <c r="I15" s="734"/>
       <c r="J15" s="758"/>
       <c r="K15" s="759"/>
-      <c r="L15" s="732">
-        <v>30</v>
-      </c>
+      <c r="L15" s="732"/>
       <c r="M15" s="732"/>
       <c r="N15" s="732"/>
-      <c r="O15" s="732">
-        <v>105</v>
-      </c>
+      <c r="O15" s="732"/>
       <c r="P15" s="732"/>
       <c r="Q15" s="732"/>
-      <c r="R15" s="732">
-        <v>105</v>
-      </c>
+      <c r="R15" s="732"/>
       <c r="S15" s="732"/>
-      <c r="T15" s="732">
-        <v>8</v>
-      </c>
+      <c r="T15" s="732"/>
       <c r="U15" s="732"/>
-      <c r="V15" s="732">
-        <v>0</v>
-      </c>
+      <c r="V15" s="732"/>
       <c r="W15" s="734"/>
-      <c r="X15" s="732">
-        <v>4</v>
-      </c>
+      <c r="X15" s="732"/>
       <c r="Y15" s="733"/>
       <c r="Z15" s="80"/>
       <c r="AA15" s="103"/>
@@ -33915,36 +32401,22 @@
         <v>19</v>
       </c>
       <c r="H16" s="757"/>
-      <c r="I16" s="734">
-        <v>19</v>
-      </c>
+      <c r="I16" s="734"/>
       <c r="J16" s="758"/>
       <c r="K16" s="759"/>
-      <c r="L16" s="732">
-        <v>58</v>
-      </c>
+      <c r="L16" s="732"/>
       <c r="M16" s="732"/>
       <c r="N16" s="732"/>
-      <c r="O16" s="732">
-        <v>99</v>
-      </c>
+      <c r="O16" s="732"/>
       <c r="P16" s="732"/>
       <c r="Q16" s="732"/>
-      <c r="R16" s="732">
-        <v>107</v>
-      </c>
+      <c r="R16" s="732"/>
       <c r="S16" s="732"/>
-      <c r="T16" s="732">
-        <v>8</v>
-      </c>
+      <c r="T16" s="732"/>
       <c r="U16" s="732"/>
-      <c r="V16" s="732">
-        <v>6</v>
-      </c>
+      <c r="V16" s="732"/>
       <c r="W16" s="734"/>
-      <c r="X16" s="732">
-        <v>7</v>
-      </c>
+      <c r="X16" s="732"/>
       <c r="Y16" s="733"/>
       <c r="Z16" s="80"/>
       <c r="AA16" s="103"/>
@@ -33963,36 +32435,22 @@
         <v>17</v>
       </c>
       <c r="H17" s="757"/>
-      <c r="I17" s="734">
-        <v>15</v>
-      </c>
+      <c r="I17" s="734"/>
       <c r="J17" s="758"/>
       <c r="K17" s="759"/>
-      <c r="L17" s="732">
-        <v>49</v>
-      </c>
+      <c r="L17" s="732"/>
       <c r="M17" s="732"/>
       <c r="N17" s="732"/>
-      <c r="O17" s="732">
-        <v>127</v>
-      </c>
+      <c r="O17" s="732"/>
       <c r="P17" s="732"/>
       <c r="Q17" s="732"/>
-      <c r="R17" s="732">
-        <v>134</v>
-      </c>
+      <c r="R17" s="732"/>
       <c r="S17" s="732"/>
-      <c r="T17" s="732">
-        <v>12</v>
-      </c>
+      <c r="T17" s="732"/>
       <c r="U17" s="732"/>
-      <c r="V17" s="732">
-        <v>5</v>
-      </c>
+      <c r="V17" s="732"/>
       <c r="W17" s="734"/>
-      <c r="X17" s="732">
-        <v>7</v>
-      </c>
+      <c r="X17" s="732"/>
       <c r="Y17" s="733"/>
       <c r="Z17" s="80"/>
       <c r="AA17" s="103"/>
@@ -34013,258 +32471,158 @@
       </c>
       <c r="F18" s="89"/>
       <c r="G18" s="756" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H18" s="757"/>
-      <c r="I18" s="734">
-        <v>1</v>
-      </c>
+      <c r="I18" s="734"/>
       <c r="J18" s="758"/>
       <c r="K18" s="759"/>
-      <c r="L18" s="732">
-        <v>2</v>
-      </c>
+      <c r="L18" s="732"/>
       <c r="M18" s="732"/>
       <c r="N18" s="732"/>
-      <c r="O18" s="732">
-        <v>4</v>
-      </c>
+      <c r="O18" s="732"/>
       <c r="P18" s="732"/>
       <c r="Q18" s="732"/>
-      <c r="R18" s="732">
-        <v>4</v>
-      </c>
+      <c r="R18" s="732"/>
       <c r="S18" s="732"/>
-      <c r="T18" s="732">
-        <v>0</v>
-      </c>
+      <c r="T18" s="732"/>
       <c r="U18" s="732"/>
-      <c r="V18" s="732">
-        <v>2</v>
-      </c>
+      <c r="V18" s="732"/>
       <c r="W18" s="734"/>
-      <c r="X18" s="732">
-        <v>2</v>
-      </c>
+      <c r="X18" s="732"/>
       <c r="Y18" s="733"/>
       <c r="Z18" s="80"/>
       <c r="AA18" s="103"/>
     </row>
     <row r="19" spans="1:27" ht="45" customHeight="1">
       <c r="A19" s="79"/>
-      <c r="B19" s="157" t="s">
-        <v>92</v>
-      </c>
-      <c r="C19" s="134">
-        <v>16</v>
-      </c>
-      <c r="D19" s="554" t="s">
-        <v>410</v>
-      </c>
+      <c r="B19" s="157"/>
+      <c r="C19" s="134"/>
+      <c r="D19" s="554"/>
       <c r="E19" s="201"/>
       <c r="F19" s="89"/>
       <c r="G19" s="756" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H19" s="757"/>
-      <c r="I19" s="734">
-        <v>5</v>
-      </c>
+      <c r="I19" s="734"/>
       <c r="J19" s="758"/>
       <c r="K19" s="759"/>
-      <c r="L19" s="732">
-        <v>8</v>
-      </c>
+      <c r="L19" s="732"/>
       <c r="M19" s="732"/>
       <c r="N19" s="732"/>
-      <c r="O19" s="732">
-        <v>22</v>
-      </c>
+      <c r="O19" s="732"/>
       <c r="P19" s="732"/>
       <c r="Q19" s="732"/>
-      <c r="R19" s="732">
-        <v>22</v>
-      </c>
+      <c r="R19" s="732"/>
       <c r="S19" s="732"/>
-      <c r="T19" s="732">
-        <v>0</v>
-      </c>
+      <c r="T19" s="732"/>
       <c r="U19" s="732"/>
-      <c r="V19" s="732">
-        <v>2</v>
-      </c>
+      <c r="V19" s="732"/>
       <c r="W19" s="734"/>
-      <c r="X19" s="732">
-        <v>0</v>
-      </c>
+      <c r="X19" s="732"/>
       <c r="Y19" s="733"/>
       <c r="Z19" s="80"/>
       <c r="AA19" s="103"/>
     </row>
     <row r="20" spans="1:27" ht="41.25" customHeight="1">
       <c r="A20" s="79"/>
-      <c r="B20" s="157" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" s="139">
-        <v>13</v>
-      </c>
-      <c r="D20" s="554" t="s">
-        <v>410</v>
-      </c>
+      <c r="B20" s="157"/>
+      <c r="C20" s="139"/>
+      <c r="D20" s="554"/>
       <c r="E20" s="201"/>
       <c r="F20" s="89"/>
       <c r="G20" s="756" t="s">
         <v>22</v>
       </c>
       <c r="H20" s="757"/>
-      <c r="I20" s="734">
-        <v>9</v>
-      </c>
+      <c r="I20" s="734"/>
       <c r="J20" s="758"/>
       <c r="K20" s="759"/>
-      <c r="L20" s="732">
-        <v>22</v>
-      </c>
+      <c r="L20" s="732"/>
       <c r="M20" s="732"/>
       <c r="N20" s="732"/>
-      <c r="O20" s="732">
-        <v>32</v>
-      </c>
+      <c r="O20" s="732"/>
       <c r="P20" s="732"/>
       <c r="Q20" s="732"/>
-      <c r="R20" s="732">
-        <v>33</v>
-      </c>
+      <c r="R20" s="732"/>
       <c r="S20" s="732"/>
-      <c r="T20" s="732">
-        <v>0</v>
-      </c>
+      <c r="T20" s="732"/>
       <c r="U20" s="732"/>
-      <c r="V20" s="732">
-        <v>0</v>
-      </c>
+      <c r="V20" s="732"/>
       <c r="W20" s="734"/>
-      <c r="X20" s="732">
-        <v>0</v>
-      </c>
+      <c r="X20" s="732"/>
       <c r="Y20" s="733"/>
       <c r="Z20" s="80"/>
       <c r="AA20" s="103"/>
     </row>
     <row r="21" spans="1:27" ht="45" customHeight="1">
       <c r="A21" s="79"/>
-      <c r="B21" s="157" t="s">
-        <v>408</v>
-      </c>
-      <c r="C21" s="139">
-        <v>35</v>
-      </c>
-      <c r="D21" s="554" t="s">
-        <v>410</v>
-      </c>
+      <c r="B21" s="157"/>
+      <c r="C21" s="139"/>
+      <c r="D21" s="554"/>
       <c r="E21" s="201"/>
       <c r="F21" s="89"/>
       <c r="G21" s="756" t="s">
         <v>20</v>
       </c>
       <c r="H21" s="757"/>
-      <c r="I21" s="734">
-        <v>3</v>
-      </c>
+      <c r="I21" s="734"/>
       <c r="J21" s="758"/>
       <c r="K21" s="759"/>
-      <c r="L21" s="732">
-        <v>8</v>
-      </c>
+      <c r="L21" s="732"/>
       <c r="M21" s="732"/>
       <c r="N21" s="732"/>
-      <c r="O21" s="732">
-        <v>50</v>
-      </c>
+      <c r="O21" s="732"/>
       <c r="P21" s="732"/>
       <c r="Q21" s="732"/>
-      <c r="R21" s="732">
-        <v>62</v>
-      </c>
+      <c r="R21" s="732"/>
       <c r="S21" s="732"/>
-      <c r="T21" s="732">
-        <v>0</v>
-      </c>
+      <c r="T21" s="732"/>
       <c r="U21" s="732"/>
-      <c r="V21" s="732">
-        <v>10</v>
-      </c>
+      <c r="V21" s="732"/>
       <c r="W21" s="734"/>
-      <c r="X21" s="732">
-        <v>11</v>
-      </c>
+      <c r="X21" s="732"/>
       <c r="Y21" s="733"/>
       <c r="Z21" s="80"/>
       <c r="AA21" s="103"/>
     </row>
     <row r="22" spans="1:27" ht="50.25" customHeight="1">
       <c r="A22" s="79"/>
-      <c r="B22" s="157" t="s">
-        <v>94</v>
-      </c>
-      <c r="C22" s="139">
-        <v>21</v>
-      </c>
-      <c r="D22" s="554" t="s">
-        <v>410</v>
-      </c>
+      <c r="B22" s="157"/>
+      <c r="C22" s="139"/>
+      <c r="D22" s="554"/>
       <c r="E22" s="201"/>
       <c r="F22" s="89"/>
       <c r="G22" s="756" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H22" s="757"/>
-      <c r="I22" s="734">
-        <v>1</v>
-      </c>
+      <c r="I22" s="734"/>
       <c r="J22" s="758"/>
       <c r="K22" s="759"/>
-      <c r="L22" s="732">
-        <v>2</v>
-      </c>
+      <c r="L22" s="732"/>
       <c r="M22" s="732"/>
       <c r="N22" s="732"/>
-      <c r="O22" s="732">
-        <v>4</v>
-      </c>
+      <c r="O22" s="732"/>
       <c r="P22" s="732"/>
       <c r="Q22" s="732"/>
-      <c r="R22" s="732">
-        <v>6</v>
-      </c>
+      <c r="R22" s="732"/>
       <c r="S22" s="732"/>
-      <c r="T22" s="732">
-        <v>0</v>
-      </c>
+      <c r="T22" s="732"/>
       <c r="U22" s="732"/>
-      <c r="V22" s="732">
-        <v>0</v>
-      </c>
+      <c r="V22" s="732"/>
       <c r="W22" s="734"/>
-      <c r="X22" s="732">
-        <v>3</v>
-      </c>
+      <c r="X22" s="732"/>
       <c r="Y22" s="733"/>
       <c r="Z22" s="80"/>
       <c r="AA22" s="103"/>
     </row>
     <row r="23" spans="1:27" ht="42" customHeight="1" thickBot="1">
       <c r="A23" s="79"/>
-      <c r="B23" s="158" t="s">
-        <v>409</v>
-      </c>
-      <c r="C23" s="159">
-        <v>2</v>
-      </c>
-      <c r="D23" s="555" t="s">
-        <v>410</v>
-      </c>
+      <c r="B23" s="158"/>
+      <c r="C23" s="159"/>
+      <c r="D23" s="555"/>
       <c r="E23" s="202"/>
       <c r="F23" s="89"/>
       <c r="G23" s="744" t="s">
@@ -34273,40 +32631,40 @@
       <c r="H23" s="736"/>
       <c r="I23" s="736">
         <f>SUM(I14:K22)</f>
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="J23" s="736"/>
       <c r="K23" s="736"/>
       <c r="L23" s="736">
         <f>SUM(L14:N22)</f>
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="M23" s="736"/>
       <c r="N23" s="736"/>
       <c r="O23" s="741">
         <f>SUM(O14:Q22)</f>
-        <v>473</v>
+        <v>0</v>
       </c>
       <c r="P23" s="742"/>
       <c r="Q23" s="743"/>
       <c r="R23" s="741">
         <f>SUM(R14:S22)</f>
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="S23" s="743"/>
       <c r="T23" s="741">
         <f>SUM(T14:U22)</f>
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="U23" s="743"/>
       <c r="V23" s="741">
         <f>SUM(V14:W22)</f>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="W23" s="742"/>
       <c r="X23" s="736">
         <f>SUM(X14:Y22)</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="737"/>
       <c r="Z23" s="80"/>
@@ -34413,7 +32771,7 @@
       <c r="G27" s="136"/>
       <c r="H27" s="681">
         <f>Y38</f>
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="I27" s="682"/>
       <c r="J27" s="683"/>
@@ -34497,31 +32855,17 @@
       </c>
       <c r="M29" s="684"/>
       <c r="N29" s="684"/>
-      <c r="O29" s="684">
-        <v>3</v>
-      </c>
+      <c r="O29" s="684"/>
       <c r="P29" s="684"/>
-      <c r="Q29" s="684">
-        <v>1</v>
-      </c>
+      <c r="Q29" s="684"/>
       <c r="R29" s="684"/>
-      <c r="S29" s="71">
-        <v>0</v>
-      </c>
-      <c r="T29" s="684">
-        <v>0</v>
-      </c>
+      <c r="S29" s="71"/>
+      <c r="T29" s="684"/>
       <c r="U29" s="684"/>
-      <c r="V29" s="71">
-        <v>3</v>
-      </c>
-      <c r="W29" s="684">
-        <v>0</v>
-      </c>
+      <c r="V29" s="71"/>
+      <c r="W29" s="684"/>
       <c r="X29" s="685"/>
-      <c r="Y29" s="195">
-        <v>6</v>
-      </c>
+      <c r="Y29" s="195"/>
       <c r="Z29" s="80"/>
       <c r="AA29" s="103"/>
     </row>
@@ -34542,31 +32886,17 @@
       </c>
       <c r="M30" s="684"/>
       <c r="N30" s="684"/>
-      <c r="O30" s="684">
-        <v>0</v>
-      </c>
+      <c r="O30" s="684"/>
       <c r="P30" s="684"/>
-      <c r="Q30" s="684">
-        <v>0</v>
-      </c>
+      <c r="Q30" s="684"/>
       <c r="R30" s="684"/>
-      <c r="S30" s="71">
-        <v>9</v>
-      </c>
-      <c r="T30" s="684">
-        <v>3</v>
-      </c>
+      <c r="S30" s="71"/>
+      <c r="T30" s="684"/>
       <c r="U30" s="684"/>
-      <c r="V30" s="71">
-        <v>2</v>
-      </c>
-      <c r="W30" s="684">
-        <v>1</v>
-      </c>
+      <c r="V30" s="71"/>
+      <c r="W30" s="684"/>
       <c r="X30" s="685"/>
-      <c r="Y30" s="195">
-        <v>11</v>
-      </c>
+      <c r="Y30" s="195"/>
       <c r="Z30" s="80"/>
       <c r="AA30" s="79"/>
     </row>
@@ -34589,31 +32919,17 @@
       </c>
       <c r="M31" s="684"/>
       <c r="N31" s="684"/>
-      <c r="O31" s="684">
-        <v>1</v>
-      </c>
+      <c r="O31" s="684"/>
       <c r="P31" s="684"/>
-      <c r="Q31" s="684">
-        <v>0</v>
-      </c>
+      <c r="Q31" s="684"/>
       <c r="R31" s="684"/>
-      <c r="S31" s="71">
-        <v>3</v>
-      </c>
-      <c r="T31" s="684">
-        <v>4</v>
-      </c>
+      <c r="S31" s="71"/>
+      <c r="T31" s="684"/>
       <c r="U31" s="684"/>
-      <c r="V31" s="71">
-        <v>2</v>
-      </c>
-      <c r="W31" s="684">
-        <v>0</v>
-      </c>
+      <c r="V31" s="71"/>
+      <c r="W31" s="684"/>
       <c r="X31" s="685"/>
-      <c r="Y31" s="195">
-        <v>6</v>
-      </c>
+      <c r="Y31" s="195"/>
       <c r="Z31" s="80"/>
       <c r="AA31" s="79"/>
     </row>
@@ -34634,31 +32950,17 @@
       </c>
       <c r="M32" s="684"/>
       <c r="N32" s="684"/>
-      <c r="O32" s="684">
-        <v>2</v>
-      </c>
+      <c r="O32" s="684"/>
       <c r="P32" s="684"/>
-      <c r="Q32" s="684">
-        <v>0</v>
-      </c>
+      <c r="Q32" s="684"/>
       <c r="R32" s="684"/>
-      <c r="S32" s="71">
-        <v>4</v>
-      </c>
-      <c r="T32" s="684">
-        <v>2</v>
-      </c>
+      <c r="S32" s="71"/>
+      <c r="T32" s="684"/>
       <c r="U32" s="684"/>
-      <c r="V32" s="71">
-        <v>9</v>
-      </c>
-      <c r="W32" s="684">
-        <v>2</v>
-      </c>
+      <c r="V32" s="71"/>
+      <c r="W32" s="684"/>
       <c r="X32" s="685"/>
-      <c r="Y32" s="195">
-        <v>15</v>
-      </c>
+      <c r="Y32" s="195"/>
       <c r="Z32" s="80"/>
       <c r="AA32" s="79"/>
     </row>
@@ -34672,41 +32974,27 @@
       <c r="G33" s="136"/>
       <c r="H33" s="681">
         <f>O38</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I33" s="682"/>
       <c r="J33" s="683"/>
       <c r="K33" s="89"/>
       <c r="L33" s="716" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="M33" s="684"/>
       <c r="N33" s="684"/>
-      <c r="O33" s="684">
-        <v>2</v>
-      </c>
+      <c r="O33" s="684"/>
       <c r="P33" s="684"/>
-      <c r="Q33" s="684">
-        <v>2</v>
-      </c>
+      <c r="Q33" s="684"/>
       <c r="R33" s="684"/>
-      <c r="S33" s="71">
-        <v>0</v>
-      </c>
-      <c r="T33" s="684">
-        <v>0</v>
-      </c>
+      <c r="S33" s="71"/>
+      <c r="T33" s="684"/>
       <c r="U33" s="684"/>
-      <c r="V33" s="71">
-        <v>1</v>
-      </c>
-      <c r="W33" s="684">
-        <v>1</v>
-      </c>
+      <c r="V33" s="71"/>
+      <c r="W33" s="684"/>
       <c r="X33" s="685"/>
-      <c r="Y33" s="195">
-        <v>3</v>
-      </c>
+      <c r="Y33" s="195"/>
       <c r="Z33" s="80"/>
       <c r="AA33" s="193"/>
     </row>
@@ -34723,35 +33011,21 @@
       <c r="J34" s="165"/>
       <c r="K34" s="89"/>
       <c r="L34" s="716" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="M34" s="684"/>
       <c r="N34" s="684"/>
-      <c r="O34" s="684">
-        <v>1</v>
-      </c>
+      <c r="O34" s="684"/>
       <c r="P34" s="684"/>
-      <c r="Q34" s="684">
-        <v>0</v>
-      </c>
+      <c r="Q34" s="684"/>
       <c r="R34" s="684"/>
-      <c r="S34" s="71">
-        <v>0</v>
-      </c>
-      <c r="T34" s="684">
-        <v>0</v>
-      </c>
+      <c r="S34" s="71"/>
+      <c r="T34" s="684"/>
       <c r="U34" s="684"/>
-      <c r="V34" s="71">
-        <v>4</v>
-      </c>
-      <c r="W34" s="684">
-        <v>0</v>
-      </c>
+      <c r="V34" s="71"/>
+      <c r="W34" s="684"/>
       <c r="X34" s="685"/>
-      <c r="Y34" s="195">
-        <v>5</v>
-      </c>
+      <c r="Y34" s="195"/>
       <c r="Z34" s="80"/>
       <c r="AA34" s="79"/>
     </row>
@@ -34772,31 +33046,17 @@
       </c>
       <c r="M35" s="684"/>
       <c r="N35" s="684"/>
-      <c r="O35" s="711">
-        <v>0</v>
-      </c>
+      <c r="O35" s="711"/>
       <c r="P35" s="711"/>
-      <c r="Q35" s="711">
-        <v>0</v>
-      </c>
+      <c r="Q35" s="711"/>
       <c r="R35" s="711"/>
-      <c r="S35" s="162">
-        <v>0</v>
-      </c>
-      <c r="T35" s="711">
-        <v>0</v>
-      </c>
+      <c r="S35" s="162"/>
+      <c r="T35" s="711"/>
       <c r="U35" s="711"/>
-      <c r="V35" s="162">
-        <v>5</v>
-      </c>
-      <c r="W35" s="711">
-        <v>0</v>
-      </c>
+      <c r="V35" s="162"/>
+      <c r="W35" s="711"/>
       <c r="X35" s="731"/>
-      <c r="Y35" s="195">
-        <v>5</v>
-      </c>
+      <c r="Y35" s="195"/>
       <c r="Z35" s="80"/>
       <c r="AA35" s="103"/>
     </row>
@@ -34817,31 +33077,17 @@
       </c>
       <c r="M36" s="684"/>
       <c r="N36" s="685"/>
-      <c r="O36" s="688">
-        <v>4</v>
-      </c>
+      <c r="O36" s="688"/>
       <c r="P36" s="688"/>
-      <c r="Q36" s="688">
-        <v>1</v>
-      </c>
+      <c r="Q36" s="688"/>
       <c r="R36" s="688"/>
-      <c r="S36" s="163">
-        <v>0</v>
-      </c>
-      <c r="T36" s="688">
-        <v>0</v>
-      </c>
+      <c r="S36" s="163"/>
+      <c r="T36" s="688"/>
       <c r="U36" s="688"/>
-      <c r="V36" s="163">
-        <v>6</v>
-      </c>
-      <c r="W36" s="688">
-        <v>1</v>
-      </c>
+      <c r="V36" s="163"/>
+      <c r="W36" s="688"/>
       <c r="X36" s="712"/>
-      <c r="Y36" s="195">
-        <v>10</v>
-      </c>
+      <c r="Y36" s="195"/>
       <c r="Z36" s="80"/>
       <c r="AA36" s="79"/>
     </row>
@@ -34860,35 +33106,21 @@
       <c r="J37" s="707"/>
       <c r="K37" s="89"/>
       <c r="L37" s="716" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M37" s="684"/>
       <c r="N37" s="685"/>
-      <c r="O37" s="688">
-        <v>0</v>
-      </c>
+      <c r="O37" s="688"/>
       <c r="P37" s="688"/>
-      <c r="Q37" s="688">
-        <v>0</v>
-      </c>
+      <c r="Q37" s="688"/>
       <c r="R37" s="688"/>
-      <c r="S37" s="163">
-        <v>0</v>
-      </c>
-      <c r="T37" s="688">
-        <v>0</v>
-      </c>
+      <c r="S37" s="163"/>
+      <c r="T37" s="688"/>
       <c r="U37" s="688"/>
-      <c r="V37" s="163">
-        <v>3</v>
-      </c>
-      <c r="W37" s="688">
-        <v>3</v>
-      </c>
+      <c r="V37" s="163"/>
+      <c r="W37" s="688"/>
       <c r="X37" s="712"/>
-      <c r="Y37" s="195">
-        <v>3</v>
-      </c>
+      <c r="Y37" s="195"/>
       <c r="Z37" s="80"/>
     </row>
     <row r="38" spans="1:27" ht="14.25" customHeight="1" thickBot="1">
@@ -34910,35 +33142,35 @@
       <c r="N38" s="726"/>
       <c r="O38" s="689">
         <f>SUM(O29:P37)</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P38" s="689"/>
       <c r="Q38" s="689">
         <f>SUM(Q29:R37)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R38" s="689"/>
       <c r="S38" s="196">
         <f>SUM(S29:S37)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="T38" s="689">
         <f>SUM(T29:U37)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="U38" s="689"/>
       <c r="V38" s="196">
         <f>SUM(V29:V37)</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="W38" s="689">
         <f>SUM(W29:X37)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X38" s="689"/>
       <c r="Y38" s="197">
         <f>SUM(Y29:Y37)</f>
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="Z38" s="80"/>
       <c r="AA38" s="103"/>
@@ -34953,7 +33185,7 @@
       <c r="G39" s="136"/>
       <c r="H39" s="681">
         <f>S38</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I39" s="682"/>
       <c r="J39" s="683"/>
@@ -35139,7 +33371,7 @@
       <c r="G45" s="136"/>
       <c r="H45" s="681">
         <f>SUM(V38)</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I45" s="682"/>
       <c r="J45" s="683"/>
@@ -35149,7 +33381,7 @@
       <c r="N45" s="82"/>
       <c r="O45" s="675">
         <f>SUM(Q38,T38,W38)</f>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="P45" s="676"/>
       <c r="Q45" s="136"/>
@@ -37156,7 +35388,7 @@
     </row>
     <row r="4" spans="1:15" ht="24" customHeight="1" thickBot="1">
       <c r="A4" s="799" t="s">
-        <v>411</v>
+        <v>182</v>
       </c>
       <c r="B4" s="799"/>
       <c r="C4" s="799"/>
@@ -37213,7 +35445,7 @@
       <c r="L6" s="517"/>
       <c r="M6" s="135"/>
       <c r="N6" s="522" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="O6" s="232"/>
     </row>
@@ -37221,13 +35453,13 @@
       <c r="A7" s="137"/>
       <c r="B7" s="523">
         <f>SUM(E13:E15)</f>
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="C7" s="89"/>
       <c r="D7" s="137"/>
       <c r="E7" s="523">
         <f>E13</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F7" s="89"/>
       <c r="G7" s="137"/>
@@ -37238,13 +35470,13 @@
       <c r="J7" s="525"/>
       <c r="K7" s="523">
         <f>E15</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L7" s="518"/>
       <c r="M7" s="137"/>
       <c r="N7" s="523">
         <f>F25</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O7" s="406"/>
     </row>
@@ -37309,7 +35541,7 @@
         <v>152</v>
       </c>
       <c r="C11" s="832" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D11" s="834" t="s">
         <v>154</v>
@@ -37349,18 +35581,12 @@
       <c r="A13" s="563" t="s">
         <v>92</v>
       </c>
-      <c r="B13" s="564">
-        <v>2</v>
-      </c>
-      <c r="C13" s="564">
-        <v>14</v>
-      </c>
-      <c r="D13" s="565">
-        <v>0</v>
-      </c>
+      <c r="B13" s="564"/>
+      <c r="C13" s="564"/>
+      <c r="D13" s="565"/>
       <c r="E13" s="825">
         <f>SUM(B13:D13)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F13" s="826"/>
       <c r="G13" s="80"/>
@@ -37377,18 +35603,12 @@
       <c r="A14" s="507" t="s">
         <v>93</v>
       </c>
-      <c r="B14" s="506">
-        <v>0</v>
-      </c>
-      <c r="C14" s="506">
-        <v>10</v>
-      </c>
-      <c r="D14" s="566">
-        <v>0</v>
-      </c>
+      <c r="B14" s="506"/>
+      <c r="C14" s="506"/>
+      <c r="D14" s="566"/>
       <c r="E14" s="827">
         <f>SUM(B14:D14)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F14" s="828"/>
       <c r="G14" s="80"/>
@@ -37405,18 +35625,12 @@
       <c r="A15" s="508" t="s">
         <v>104</v>
       </c>
-      <c r="B15" s="509">
-        <v>0</v>
-      </c>
-      <c r="C15" s="509">
-        <v>38</v>
-      </c>
-      <c r="D15" s="510">
-        <v>0</v>
-      </c>
+      <c r="B15" s="509"/>
+      <c r="C15" s="509"/>
+      <c r="D15" s="510"/>
       <c r="E15" s="837">
         <f>SUM(B15:D15)</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F15" s="838"/>
       <c r="G15" s="80"/>
@@ -37490,7 +35704,7 @@
       <c r="F19" s="105"/>
       <c r="H19" s="193"/>
       <c r="I19" s="533" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J19" s="527"/>
       <c r="K19" s="528"/>
@@ -37504,10 +35718,10 @@
         <v>152</v>
       </c>
       <c r="B20" s="530" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C20" s="503" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D20" s="82"/>
       <c r="E20" s="83"/>
@@ -37516,7 +35730,7 @@
         <v>50</v>
       </c>
       <c r="I20" s="542" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J20" s="543" t="s">
         <v>51</v>
@@ -37534,11 +35748,11 @@
     <row r="21" spans="1:15" ht="22.5" customHeight="1">
       <c r="A21" s="503">
         <f>SUM(B13:B15)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B21" s="532">
         <f>SUM(C13:C15)</f>
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="C21" s="503">
         <f>SUM(D13:D15)</f>
@@ -37548,21 +35762,11 @@
       <c r="E21" s="82"/>
       <c r="F21" s="82"/>
       <c r="G21" s="78"/>
-      <c r="H21" s="549" t="s">
-        <v>18</v>
-      </c>
-      <c r="I21" s="547">
-        <v>1</v>
-      </c>
-      <c r="J21" s="547">
-        <v>1</v>
-      </c>
-      <c r="K21" s="547">
-        <v>1</v>
-      </c>
-      <c r="L21" s="813">
-        <v>1</v>
-      </c>
+      <c r="H21" s="549"/>
+      <c r="I21" s="547"/>
+      <c r="J21" s="547"/>
+      <c r="K21" s="547"/>
+      <c r="L21" s="813"/>
       <c r="M21" s="814"/>
       <c r="N21" s="80"/>
       <c r="O21" s="165"/>
@@ -37575,21 +35779,11 @@
       <c r="E22" s="106"/>
       <c r="F22" s="106"/>
       <c r="G22" s="78"/>
-      <c r="H22" s="550" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="546">
-        <v>1</v>
-      </c>
-      <c r="J22" s="546">
-        <v>1</v>
-      </c>
-      <c r="K22" s="546">
-        <v>1</v>
-      </c>
-      <c r="L22" s="787">
-        <v>1</v>
-      </c>
+      <c r="H22" s="550"/>
+      <c r="I22" s="546"/>
+      <c r="J22" s="546"/>
+      <c r="K22" s="546"/>
+      <c r="L22" s="787"/>
       <c r="M22" s="788"/>
       <c r="N22" s="80"/>
       <c r="O22" s="165"/>
@@ -37604,21 +35798,11 @@
       <c r="E23" s="809"/>
       <c r="F23" s="810"/>
       <c r="G23" s="78"/>
-      <c r="H23" s="550" t="s">
-        <v>19</v>
-      </c>
-      <c r="I23" s="546">
-        <v>1</v>
-      </c>
-      <c r="J23" s="546">
-        <v>1</v>
-      </c>
-      <c r="K23" s="546">
-        <v>1</v>
-      </c>
-      <c r="L23" s="787">
-        <v>1</v>
-      </c>
+      <c r="H23" s="550"/>
+      <c r="I23" s="546"/>
+      <c r="J23" s="546"/>
+      <c r="K23" s="546"/>
+      <c r="L23" s="787"/>
       <c r="M23" s="788"/>
       <c r="N23" s="80"/>
       <c r="O23" s="165"/>
@@ -37628,34 +35812,24 @@
         <v>158</v>
       </c>
       <c r="B24" s="806" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C24" s="807"/>
       <c r="D24" s="560" t="s">
         <v>161</v>
       </c>
       <c r="E24" s="561" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F24" s="562" t="s">
         <v>88</v>
       </c>
       <c r="G24" s="78"/>
-      <c r="H24" s="550" t="s">
-        <v>17</v>
-      </c>
-      <c r="I24" s="546">
-        <v>1</v>
-      </c>
-      <c r="J24" s="546">
-        <v>1</v>
-      </c>
-      <c r="K24" s="546">
-        <v>1</v>
-      </c>
-      <c r="L24" s="787">
-        <v>1</v>
-      </c>
+      <c r="H24" s="550"/>
+      <c r="I24" s="546"/>
+      <c r="J24" s="546"/>
+      <c r="K24" s="546"/>
+      <c r="L24" s="787"/>
       <c r="M24" s="788"/>
       <c r="N24" s="80"/>
       <c r="O24" s="165"/>
@@ -37664,36 +35838,20 @@
       <c r="A25" s="505" t="s">
         <v>94</v>
       </c>
-      <c r="B25" s="829">
-        <v>4</v>
-      </c>
+      <c r="B25" s="829"/>
       <c r="C25" s="829"/>
-      <c r="D25" s="512">
-        <v>16</v>
-      </c>
-      <c r="E25" s="512">
-        <v>4</v>
-      </c>
+      <c r="D25" s="512"/>
+      <c r="E25" s="512"/>
       <c r="F25" s="511">
         <f>SUM(B25:D25)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G25" s="78"/>
-      <c r="H25" s="551" t="s">
-        <v>367</v>
-      </c>
-      <c r="I25" s="546">
-        <v>1</v>
-      </c>
-      <c r="J25" s="546">
-        <v>1</v>
-      </c>
-      <c r="K25" s="546">
-        <v>1</v>
-      </c>
-      <c r="L25" s="787">
-        <v>1</v>
-      </c>
+      <c r="H25" s="551"/>
+      <c r="I25" s="546"/>
+      <c r="J25" s="546"/>
+      <c r="K25" s="546"/>
+      <c r="L25" s="787"/>
       <c r="M25" s="788"/>
       <c r="N25" s="80"/>
       <c r="O25" s="165"/>
@@ -37703,21 +35861,11 @@
       <c r="C26" s="496"/>
       <c r="F26" s="497"/>
       <c r="G26" s="103"/>
-      <c r="H26" s="551" t="s">
-        <v>412</v>
-      </c>
-      <c r="I26" s="546">
-        <v>1</v>
-      </c>
-      <c r="J26" s="546">
-        <v>1</v>
-      </c>
-      <c r="K26" s="546">
-        <v>1</v>
-      </c>
-      <c r="L26" s="787">
-        <v>1</v>
-      </c>
+      <c r="H26" s="551"/>
+      <c r="I26" s="546"/>
+      <c r="J26" s="546"/>
+      <c r="K26" s="546"/>
+      <c r="L26" s="787"/>
       <c r="M26" s="788"/>
       <c r="N26" s="80"/>
       <c r="O26" s="165"/>
@@ -37730,21 +35878,11 @@
       <c r="E27" s="499"/>
       <c r="F27" s="502"/>
       <c r="G27" s="89"/>
-      <c r="H27" s="551" t="s">
-        <v>413</v>
-      </c>
-      <c r="I27" s="546">
-        <v>1</v>
-      </c>
-      <c r="J27" s="546">
-        <v>1</v>
-      </c>
-      <c r="K27" s="546">
-        <v>1</v>
-      </c>
-      <c r="L27" s="787">
-        <v>1</v>
-      </c>
+      <c r="H27" s="551"/>
+      <c r="I27" s="546"/>
+      <c r="J27" s="546"/>
+      <c r="K27" s="546"/>
+      <c r="L27" s="787"/>
       <c r="M27" s="788"/>
       <c r="N27" s="80"/>
       <c r="O27" s="165"/>
@@ -37757,21 +35895,11 @@
       <c r="E28" s="82"/>
       <c r="F28" s="82"/>
       <c r="G28" s="89"/>
-      <c r="H28" s="551" t="s">
-        <v>368</v>
-      </c>
-      <c r="I28" s="546">
-        <v>1</v>
-      </c>
-      <c r="J28" s="546">
-        <v>1</v>
-      </c>
-      <c r="K28" s="546">
-        <v>1</v>
-      </c>
-      <c r="L28" s="787">
-        <v>1</v>
-      </c>
+      <c r="H28" s="551"/>
+      <c r="I28" s="546"/>
+      <c r="J28" s="546"/>
+      <c r="K28" s="546"/>
+      <c r="L28" s="787"/>
       <c r="M28" s="788"/>
       <c r="N28" s="105"/>
       <c r="O28" s="165"/>
@@ -37783,21 +35911,11 @@
       <c r="D29" s="82"/>
       <c r="E29" s="82"/>
       <c r="F29" s="82"/>
-      <c r="H29" s="551" t="s">
-        <v>369</v>
-      </c>
-      <c r="I29" s="546">
-        <v>1</v>
-      </c>
-      <c r="J29" s="546">
-        <v>1</v>
-      </c>
-      <c r="K29" s="546">
-        <v>1</v>
-      </c>
-      <c r="L29" s="787">
-        <v>1</v>
-      </c>
+      <c r="H29" s="551"/>
+      <c r="I29" s="546"/>
+      <c r="J29" s="546"/>
+      <c r="K29" s="546"/>
+      <c r="L29" s="787"/>
       <c r="M29" s="788"/>
       <c r="N29" s="80"/>
       <c r="O29" s="165"/>
@@ -37810,21 +35928,11 @@
       <c r="E30" s="82"/>
       <c r="F30" s="82"/>
       <c r="G30" s="78"/>
-      <c r="H30" s="551" t="s">
-        <v>370</v>
-      </c>
-      <c r="I30" s="546">
-        <v>1</v>
-      </c>
-      <c r="J30" s="546">
-        <v>1</v>
-      </c>
-      <c r="K30" s="546">
-        <v>1</v>
-      </c>
-      <c r="L30" s="787">
-        <v>1</v>
-      </c>
+      <c r="H30" s="551"/>
+      <c r="I30" s="546"/>
+      <c r="J30" s="546"/>
+      <c r="K30" s="546"/>
+      <c r="L30" s="787"/>
       <c r="M30" s="788"/>
       <c r="N30" s="80"/>
       <c r="O30" s="165"/>
@@ -37837,21 +35945,11 @@
       <c r="E31" s="82"/>
       <c r="F31" s="82"/>
       <c r="G31" s="78"/>
-      <c r="H31" s="550" t="s">
-        <v>371</v>
-      </c>
-      <c r="I31" s="546">
-        <v>0.8</v>
-      </c>
-      <c r="J31" s="546">
-        <v>1</v>
-      </c>
-      <c r="K31" s="546">
-        <v>1</v>
-      </c>
-      <c r="L31" s="787">
-        <v>0.4</v>
-      </c>
+      <c r="H31" s="550"/>
+      <c r="I31" s="546"/>
+      <c r="J31" s="546"/>
+      <c r="K31" s="546"/>
+      <c r="L31" s="787"/>
       <c r="M31" s="788"/>
       <c r="N31" s="80"/>
       <c r="O31" s="165"/>
@@ -37864,21 +35962,11 @@
       <c r="E32" s="82"/>
       <c r="F32" s="82"/>
       <c r="G32" s="78"/>
-      <c r="H32" s="550" t="s">
-        <v>372</v>
-      </c>
-      <c r="I32" s="546">
-        <v>1</v>
-      </c>
-      <c r="J32" s="546">
-        <v>1</v>
-      </c>
-      <c r="K32" s="546">
-        <v>1</v>
-      </c>
-      <c r="L32" s="787">
-        <v>1</v>
-      </c>
+      <c r="H32" s="550"/>
+      <c r="I32" s="546"/>
+      <c r="J32" s="546"/>
+      <c r="K32" s="546"/>
+      <c r="L32" s="787"/>
       <c r="M32" s="788"/>
       <c r="N32" s="80"/>
       <c r="O32" s="165"/>
@@ -37891,21 +35979,11 @@
       <c r="E33" s="82"/>
       <c r="F33" s="82"/>
       <c r="G33" s="78"/>
-      <c r="H33" s="557" t="s">
-        <v>374</v>
-      </c>
-      <c r="I33" s="546">
-        <v>1</v>
-      </c>
-      <c r="J33" s="546">
-        <v>1</v>
-      </c>
-      <c r="K33" s="546">
-        <v>1</v>
-      </c>
-      <c r="L33" s="787">
-        <v>1</v>
-      </c>
+      <c r="H33" s="557"/>
+      <c r="I33" s="546"/>
+      <c r="J33" s="546"/>
+      <c r="K33" s="546"/>
+      <c r="L33" s="787"/>
       <c r="M33" s="788"/>
       <c r="N33" s="80"/>
       <c r="O33" s="165"/>
@@ -37918,21 +35996,11 @@
       <c r="E34" s="82"/>
       <c r="F34" s="82"/>
       <c r="G34" s="78"/>
-      <c r="H34" s="557" t="s">
-        <v>414</v>
-      </c>
-      <c r="I34" s="546">
-        <v>1</v>
-      </c>
-      <c r="J34" s="546">
-        <v>1</v>
-      </c>
-      <c r="K34" s="546">
-        <v>1</v>
-      </c>
-      <c r="L34" s="787">
-        <v>1</v>
-      </c>
+      <c r="H34" s="557"/>
+      <c r="I34" s="546"/>
+      <c r="J34" s="546"/>
+      <c r="K34" s="546"/>
+      <c r="L34" s="787"/>
       <c r="M34" s="788"/>
       <c r="N34" s="80"/>
       <c r="O34" s="165"/>
@@ -37945,21 +36013,11 @@
       <c r="E35" s="82"/>
       <c r="F35" s="82"/>
       <c r="G35" s="89"/>
-      <c r="H35" s="550" t="s">
-        <v>191</v>
-      </c>
-      <c r="I35" s="546">
-        <v>1</v>
-      </c>
-      <c r="J35" s="546">
-        <v>1</v>
-      </c>
-      <c r="K35" s="546">
-        <v>1</v>
-      </c>
-      <c r="L35" s="787">
-        <v>1</v>
-      </c>
+      <c r="H35" s="550"/>
+      <c r="I35" s="546"/>
+      <c r="J35" s="546"/>
+      <c r="K35" s="546"/>
+      <c r="L35" s="787"/>
       <c r="M35" s="788"/>
       <c r="N35" s="80"/>
       <c r="O35" s="165"/>
@@ -37971,21 +36029,11 @@
       <c r="D36" s="82"/>
       <c r="E36" s="82"/>
       <c r="F36" s="82"/>
-      <c r="H36" s="556" t="s">
-        <v>375</v>
-      </c>
-      <c r="I36" s="546">
-        <v>1</v>
-      </c>
-      <c r="J36" s="546">
-        <v>1</v>
-      </c>
-      <c r="K36" s="546">
-        <v>1</v>
-      </c>
-      <c r="L36" s="787">
-        <v>1</v>
-      </c>
+      <c r="H36" s="556"/>
+      <c r="I36" s="546"/>
+      <c r="J36" s="546"/>
+      <c r="K36" s="546"/>
+      <c r="L36" s="787"/>
       <c r="M36" s="788"/>
       <c r="N36" s="80"/>
       <c r="O36" s="165"/>
@@ -37998,21 +36046,11 @@
       <c r="E37" s="82"/>
       <c r="F37" s="82"/>
       <c r="G37" s="78"/>
-      <c r="H37" s="552" t="s">
-        <v>20</v>
-      </c>
-      <c r="I37" s="548">
-        <v>0.67</v>
-      </c>
-      <c r="J37" s="548">
-        <v>1</v>
-      </c>
-      <c r="K37" s="548">
-        <v>1</v>
-      </c>
-      <c r="L37" s="789">
-        <v>0</v>
-      </c>
+      <c r="H37" s="552"/>
+      <c r="I37" s="548"/>
+      <c r="J37" s="548"/>
+      <c r="K37" s="548"/>
+      <c r="L37" s="789"/>
       <c r="M37" s="790"/>
       <c r="N37" s="80"/>
       <c r="O37" s="165"/>
@@ -38129,7 +36167,7 @@
       <c r="E2" s="861"/>
       <c r="F2" s="861"/>
       <c r="G2" s="862" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="H2" s="862"/>
       <c r="I2" s="862"/>
@@ -38148,7 +36186,7 @@
     <row r="3" spans="1:20" ht="28.5" customHeight="1" thickBot="1">
       <c r="A3" s="82"/>
       <c r="B3" s="864" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C3" s="865"/>
       <c r="D3" s="865"/>
@@ -38181,7 +36219,7 @@
       <c r="I4" s="88"/>
       <c r="J4" s="103"/>
       <c r="K4" s="882" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="L4" s="883"/>
       <c r="M4" s="883"/>
@@ -38204,7 +36242,7 @@
       </c>
       <c r="L5" s="878"/>
       <c r="M5" s="878" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="N5" s="878"/>
       <c r="O5" s="534" t="s">
@@ -38222,17 +36260,11 @@
       <c r="H6" s="79"/>
       <c r="I6" s="82"/>
       <c r="J6" s="79"/>
-      <c r="K6" s="885" t="s">
-        <v>416</v>
-      </c>
+      <c r="K6" s="885"/>
       <c r="L6" s="886"/>
-      <c r="M6" s="876" t="s">
-        <v>423</v>
-      </c>
+      <c r="M6" s="876"/>
       <c r="N6" s="877"/>
-      <c r="O6" s="572" t="s">
-        <v>439</v>
-      </c>
+      <c r="O6" s="572"/>
       <c r="P6" s="80"/>
       <c r="Q6" s="82"/>
       <c r="R6" s="82"/>
@@ -38249,17 +36281,11 @@
       <c r="H7" s="881"/>
       <c r="I7" s="82"/>
       <c r="J7" s="103"/>
-      <c r="K7" s="841" t="s">
-        <v>416</v>
-      </c>
+      <c r="K7" s="841"/>
       <c r="L7" s="842"/>
-      <c r="M7" s="839" t="s">
-        <v>424</v>
-      </c>
+      <c r="M7" s="839"/>
       <c r="N7" s="840"/>
-      <c r="O7" s="573" t="s">
-        <v>440</v>
-      </c>
+      <c r="O7" s="573"/>
       <c r="P7" s="80"/>
       <c r="Q7" s="82"/>
       <c r="R7" s="82"/>
@@ -38273,17 +36299,11 @@
       <c r="D8" s="82"/>
       <c r="I8" s="82"/>
       <c r="J8" s="79"/>
-      <c r="K8" s="841" t="s">
-        <v>416</v>
-      </c>
+      <c r="K8" s="841"/>
       <c r="L8" s="842"/>
-      <c r="M8" s="839" t="s">
-        <v>425</v>
-      </c>
+      <c r="M8" s="839"/>
       <c r="N8" s="840"/>
-      <c r="O8" s="573" t="s">
-        <v>439</v>
-      </c>
+      <c r="O8" s="573"/>
       <c r="P8" s="80"/>
       <c r="Q8" s="82"/>
       <c r="R8" s="82"/>
@@ -38297,17 +36317,11 @@
       <c r="D9" s="82"/>
       <c r="I9" s="82"/>
       <c r="J9" s="103"/>
-      <c r="K9" s="841" t="s">
-        <v>131</v>
-      </c>
+      <c r="K9" s="841"/>
       <c r="L9" s="842"/>
-      <c r="M9" s="839" t="s">
-        <v>426</v>
-      </c>
+      <c r="M9" s="839"/>
       <c r="N9" s="840"/>
-      <c r="O9" s="573" t="s">
-        <v>441</v>
-      </c>
+      <c r="O9" s="573"/>
       <c r="P9" s="80"/>
       <c r="Q9" s="82"/>
       <c r="R9" s="82"/>
@@ -38318,22 +36332,16 @@
       <c r="A10" s="79"/>
       <c r="B10" s="568"/>
       <c r="C10" s="569" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D10" s="80"/>
       <c r="I10" s="82"/>
       <c r="J10" s="79"/>
-      <c r="K10" s="841" t="s">
-        <v>131</v>
-      </c>
+      <c r="K10" s="841"/>
       <c r="L10" s="842"/>
-      <c r="M10" s="839" t="s">
-        <v>427</v>
-      </c>
+      <c r="M10" s="839"/>
       <c r="N10" s="840"/>
-      <c r="O10" s="573" t="s">
-        <v>441</v>
-      </c>
+      <c r="O10" s="573"/>
       <c r="P10" s="80"/>
       <c r="Q10" s="82"/>
       <c r="R10" s="82"/>
@@ -38344,24 +36352,18 @@
       <c r="A11" s="79"/>
       <c r="B11" s="570"/>
       <c r="C11" s="571" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D11" s="89"/>
       <c r="F11" s="89"/>
       <c r="H11" s="87"/>
       <c r="I11" s="80"/>
       <c r="J11" s="103"/>
-      <c r="K11" s="841" t="s">
-        <v>131</v>
-      </c>
+      <c r="K11" s="841"/>
       <c r="L11" s="842"/>
-      <c r="M11" s="839" t="s">
-        <v>428</v>
-      </c>
+      <c r="M11" s="839"/>
       <c r="N11" s="840"/>
-      <c r="O11" s="573" t="s">
-        <v>442</v>
-      </c>
+      <c r="O11" s="573"/>
       <c r="P11" s="80"/>
       <c r="Q11" s="82"/>
       <c r="R11" s="82"/>
@@ -38376,17 +36378,11 @@
       <c r="G12" s="89"/>
       <c r="I12" s="80"/>
       <c r="J12" s="103"/>
-      <c r="K12" s="841" t="s">
-        <v>421</v>
-      </c>
+      <c r="K12" s="841"/>
       <c r="L12" s="842"/>
-      <c r="M12" s="839" t="s">
-        <v>429</v>
-      </c>
+      <c r="M12" s="839"/>
       <c r="N12" s="840"/>
-      <c r="O12" s="573" t="s">
-        <v>441</v>
-      </c>
+      <c r="O12" s="573"/>
       <c r="P12" s="80"/>
       <c r="Q12" s="82"/>
       <c r="R12" s="82"/>
@@ -38397,24 +36393,18 @@
       <c r="A13" s="79"/>
       <c r="D13" s="89"/>
       <c r="E13" s="875" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F13" s="875"/>
       <c r="G13" s="875"/>
       <c r="H13" s="875"/>
       <c r="I13" s="80"/>
       <c r="J13" s="103"/>
-      <c r="K13" s="841" t="s">
-        <v>421</v>
-      </c>
+      <c r="K13" s="841"/>
       <c r="L13" s="842"/>
-      <c r="M13" s="839" t="s">
-        <v>430</v>
-      </c>
+      <c r="M13" s="839"/>
       <c r="N13" s="840"/>
-      <c r="O13" s="573" t="s">
-        <v>443</v>
-      </c>
+      <c r="O13" s="573"/>
       <c r="P13" s="80"/>
       <c r="Q13" s="82"/>
       <c r="R13" s="82"/>
@@ -38424,7 +36414,7 @@
     <row r="14" spans="1:20" ht="47.25" customHeight="1">
       <c r="A14" s="79"/>
       <c r="B14" s="851" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C14" s="851"/>
       <c r="D14" s="89"/>
@@ -38438,17 +36428,11 @@
       </c>
       <c r="I14" s="80"/>
       <c r="J14" s="103"/>
-      <c r="K14" s="841" t="s">
-        <v>422</v>
-      </c>
+      <c r="K14" s="841"/>
       <c r="L14" s="842"/>
-      <c r="M14" s="839" t="s">
-        <v>431</v>
-      </c>
+      <c r="M14" s="839"/>
       <c r="N14" s="840"/>
-      <c r="O14" s="573" t="s">
-        <v>444</v>
-      </c>
+      <c r="O14" s="573"/>
       <c r="P14" s="80"/>
       <c r="Q14" s="82"/>
       <c r="R14" s="82"/>
@@ -38461,30 +36445,20 @@
         <v>121</v>
       </c>
       <c r="C15" s="474" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D15" s="89"/>
-      <c r="E15" s="855" t="s">
-        <v>415</v>
-      </c>
+      <c r="E15" s="855"/>
       <c r="F15" s="855"/>
       <c r="G15" s="855"/>
-      <c r="H15" s="476">
-        <v>2</v>
-      </c>
+      <c r="H15" s="476"/>
       <c r="I15" s="80"/>
       <c r="J15" s="103"/>
-      <c r="K15" s="841" t="s">
-        <v>422</v>
-      </c>
+      <c r="K15" s="841"/>
       <c r="L15" s="842"/>
-      <c r="M15" s="839" t="s">
-        <v>432</v>
-      </c>
+      <c r="M15" s="839"/>
       <c r="N15" s="840"/>
-      <c r="O15" s="573" t="s">
-        <v>445</v>
-      </c>
+      <c r="O15" s="573"/>
       <c r="P15" s="80"/>
       <c r="Q15" s="82"/>
       <c r="R15" s="82"/>
@@ -38493,34 +36467,20 @@
     </row>
     <row r="16" spans="1:20" ht="47.25" customHeight="1">
       <c r="A16" s="79"/>
-      <c r="B16" s="475" t="s">
-        <v>415</v>
-      </c>
-      <c r="C16" s="475">
-        <v>4</v>
-      </c>
+      <c r="B16" s="475"/>
+      <c r="C16" s="475"/>
       <c r="D16" s="89"/>
-      <c r="E16" s="855" t="s">
-        <v>416</v>
-      </c>
+      <c r="E16" s="855"/>
       <c r="F16" s="855"/>
       <c r="G16" s="855"/>
-      <c r="H16" s="476">
-        <v>26</v>
-      </c>
+      <c r="H16" s="476"/>
       <c r="I16" s="80"/>
       <c r="J16" s="103"/>
-      <c r="K16" s="841" t="s">
-        <v>417</v>
-      </c>
+      <c r="K16" s="841"/>
       <c r="L16" s="842"/>
-      <c r="M16" s="839" t="s">
-        <v>433</v>
-      </c>
+      <c r="M16" s="839"/>
       <c r="N16" s="840"/>
-      <c r="O16" s="573" t="s">
-        <v>443</v>
-      </c>
+      <c r="O16" s="573"/>
       <c r="P16" s="80"/>
       <c r="Q16" s="82"/>
       <c r="R16" s="82"/>
@@ -38529,34 +36489,20 @@
     </row>
     <row r="17" spans="1:20" ht="46.5" customHeight="1">
       <c r="A17" s="79"/>
-      <c r="B17" s="475" t="s">
-        <v>416</v>
-      </c>
-      <c r="C17" s="475">
-        <v>26</v>
-      </c>
+      <c r="B17" s="475"/>
+      <c r="C17" s="475"/>
       <c r="D17" s="89"/>
-      <c r="E17" s="855" t="s">
-        <v>417</v>
-      </c>
+      <c r="E17" s="855"/>
       <c r="F17" s="855"/>
       <c r="G17" s="855"/>
-      <c r="H17" s="476">
-        <v>5</v>
-      </c>
+      <c r="H17" s="476"/>
       <c r="I17" s="80"/>
       <c r="J17" s="79"/>
-      <c r="K17" s="841" t="s">
-        <v>417</v>
-      </c>
+      <c r="K17" s="841"/>
       <c r="L17" s="842"/>
-      <c r="M17" s="839" t="s">
-        <v>434</v>
-      </c>
+      <c r="M17" s="839"/>
       <c r="N17" s="840"/>
-      <c r="O17" s="573" t="s">
-        <v>446</v>
-      </c>
+      <c r="O17" s="573"/>
       <c r="P17" s="80"/>
       <c r="Q17" s="82"/>
       <c r="R17" s="82"/>
@@ -38565,34 +36511,20 @@
     </row>
     <row r="18" spans="1:20" ht="54.75" customHeight="1" thickBot="1">
       <c r="A18" s="79"/>
-      <c r="B18" s="475" t="s">
-        <v>417</v>
-      </c>
-      <c r="C18" s="475">
-        <v>5</v>
-      </c>
+      <c r="B18" s="475"/>
+      <c r="C18" s="475"/>
       <c r="D18" s="89"/>
-      <c r="E18" s="855" t="s">
-        <v>418</v>
-      </c>
+      <c r="E18" s="855"/>
       <c r="F18" s="855"/>
       <c r="G18" s="855"/>
-      <c r="H18" s="476">
-        <v>31</v>
-      </c>
+      <c r="H18" s="476"/>
       <c r="I18" s="80"/>
       <c r="J18" s="87"/>
-      <c r="K18" s="858" t="s">
-        <v>417</v>
-      </c>
+      <c r="K18" s="858"/>
       <c r="L18" s="859"/>
-      <c r="M18" s="846" t="s">
-        <v>435</v>
-      </c>
+      <c r="M18" s="846"/>
       <c r="N18" s="847"/>
-      <c r="O18" s="573" t="s">
-        <v>447</v>
-      </c>
+      <c r="O18" s="573"/>
       <c r="P18" s="80"/>
       <c r="Q18" s="82"/>
       <c r="R18" s="82"/>
@@ -38601,33 +36533,19 @@
     </row>
     <row r="19" spans="1:20" ht="42" customHeight="1" thickBot="1">
       <c r="A19" s="79"/>
-      <c r="B19" s="475" t="s">
-        <v>418</v>
-      </c>
-      <c r="C19" s="475">
-        <v>31</v>
-      </c>
+      <c r="B19" s="475"/>
+      <c r="C19" s="475"/>
       <c r="D19" s="89"/>
-      <c r="E19" s="855" t="s">
-        <v>419</v>
-      </c>
+      <c r="E19" s="855"/>
       <c r="F19" s="855"/>
       <c r="G19" s="855"/>
-      <c r="H19" s="476">
-        <v>6</v>
-      </c>
+      <c r="H19" s="476"/>
       <c r="I19" s="80"/>
       <c r="J19" s="79"/>
-      <c r="K19" s="230" t="s">
-        <v>415</v>
-      </c>
-      <c r="M19" s="846" t="s">
-        <v>436</v>
-      </c>
+      <c r="K19" s="230"/>
+      <c r="M19" s="846"/>
       <c r="N19" s="847"/>
-      <c r="O19" s="573" t="s">
-        <v>439</v>
-      </c>
+      <c r="O19" s="573"/>
       <c r="P19" s="80"/>
       <c r="Q19" s="82"/>
       <c r="R19" s="82"/>
@@ -38636,33 +36554,19 @@
     </row>
     <row r="20" spans="1:20" ht="33.75" customHeight="1" thickBot="1">
       <c r="A20" s="79"/>
-      <c r="B20" s="475" t="s">
-        <v>419</v>
-      </c>
-      <c r="C20" s="475">
-        <v>6</v>
-      </c>
+      <c r="B20" s="475"/>
+      <c r="C20" s="475"/>
       <c r="D20" s="89"/>
-      <c r="E20" s="856" t="s">
-        <v>420</v>
-      </c>
+      <c r="E20" s="856"/>
       <c r="F20" s="856"/>
       <c r="G20" s="856"/>
-      <c r="H20" s="477">
-        <v>25</v>
-      </c>
+      <c r="H20" s="477"/>
       <c r="I20" s="80"/>
       <c r="J20" s="103"/>
-      <c r="K20" s="230" t="s">
-        <v>415</v>
-      </c>
-      <c r="M20" s="846" t="s">
-        <v>437</v>
-      </c>
+      <c r="K20" s="230"/>
+      <c r="M20" s="846"/>
       <c r="N20" s="847"/>
-      <c r="O20" s="573" t="s">
-        <v>443</v>
-      </c>
+      <c r="O20" s="573"/>
       <c r="P20" s="80"/>
       <c r="Q20" s="82"/>
       <c r="R20" s="82"/>
@@ -38671,12 +36575,8 @@
     </row>
     <row r="21" spans="1:20" ht="46.5" customHeight="1" thickBot="1">
       <c r="A21" s="79"/>
-      <c r="B21" s="475" t="s">
-        <v>420</v>
-      </c>
-      <c r="C21" s="475">
-        <v>25</v>
-      </c>
+      <c r="B21" s="475"/>
+      <c r="C21" s="475"/>
       <c r="D21" s="98"/>
       <c r="E21" s="867" t="s">
         <v>10</v>
@@ -38685,20 +36585,14 @@
       <c r="G21" s="867"/>
       <c r="H21" s="478">
         <f>SUM(H15:H20)</f>
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="I21" s="80"/>
       <c r="J21" s="103"/>
-      <c r="K21" s="230" t="s">
-        <v>415</v>
-      </c>
-      <c r="M21" s="846" t="s">
-        <v>438</v>
-      </c>
+      <c r="K21" s="230"/>
+      <c r="M21" s="846"/>
       <c r="N21" s="847"/>
-      <c r="O21" s="573" t="s">
-        <v>443</v>
-      </c>
+      <c r="O21" s="573"/>
       <c r="P21" s="80"/>
       <c r="Q21" s="82"/>
       <c r="R21" s="82"/>
@@ -38712,11 +36606,11 @@
       </c>
       <c r="C22" s="478">
         <f>SUM(C16:C21)</f>
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D22" s="89"/>
       <c r="E22" s="843" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F22" s="844"/>
       <c r="G22" s="844"/>
@@ -38795,7 +36689,7 @@
       <c r="I26" s="857"/>
       <c r="J26" s="468"/>
       <c r="K26" s="852" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="L26" s="853"/>
       <c r="M26" s="853"/>
@@ -38817,7 +36711,7 @@
       <c r="I27" s="473"/>
       <c r="J27" s="211"/>
       <c r="K27" s="848" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="L27" s="849"/>
       <c r="M27" s="849"/>
@@ -38832,7 +36726,7 @@
       <c r="A28" s="79"/>
       <c r="J28" s="78"/>
       <c r="K28" s="869" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L28" s="870"/>
       <c r="M28" s="870"/>
@@ -42133,186 +40027,82 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
-      <c r="A3" s="343">
-        <v>45646</v>
-      </c>
-      <c r="B3" s="455" t="s">
-        <v>448</v>
-      </c>
-      <c r="C3" s="344">
-        <v>2</v>
-      </c>
-      <c r="D3" s="344">
-        <v>0</v>
-      </c>
+      <c r="A3" s="343"/>
+      <c r="B3" s="455"/>
+      <c r="C3" s="344"/>
+      <c r="D3" s="344"/>
     </row>
     <row r="4" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A4" s="343">
-        <v>45660</v>
-      </c>
-      <c r="B4" s="455" t="s">
-        <v>449</v>
-      </c>
-      <c r="C4" s="344">
-        <v>-1</v>
-      </c>
-      <c r="D4" s="344">
-        <v>0</v>
-      </c>
+      <c r="A4" s="343"/>
+      <c r="B4" s="455"/>
+      <c r="C4" s="344"/>
+      <c r="D4" s="344"/>
     </row>
     <row r="5" spans="1:4" ht="26.25" customHeight="1">
-      <c r="A5" s="343">
-        <v>45677</v>
-      </c>
-      <c r="B5" s="455" t="s">
-        <v>450</v>
-      </c>
-      <c r="C5" s="344">
-        <v>1</v>
-      </c>
-      <c r="D5" s="344">
-        <v>0</v>
-      </c>
+      <c r="A5" s="343"/>
+      <c r="B5" s="455"/>
+      <c r="C5" s="344"/>
+      <c r="D5" s="344"/>
     </row>
     <row r="6" spans="1:4" ht="24" customHeight="1">
-      <c r="A6" s="343">
-        <v>45683</v>
-      </c>
-      <c r="B6" s="455" t="s">
-        <v>451</v>
-      </c>
-      <c r="C6" s="344">
-        <v>-1</v>
-      </c>
-      <c r="D6" s="344">
-        <v>0</v>
-      </c>
+      <c r="A6" s="343"/>
+      <c r="B6" s="455"/>
+      <c r="C6" s="344"/>
+      <c r="D6" s="344"/>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A7" s="343">
-        <v>45783</v>
-      </c>
-      <c r="B7" s="455" t="s">
-        <v>452</v>
-      </c>
-      <c r="C7" s="344">
-        <v>2</v>
-      </c>
-      <c r="D7" s="344">
-        <v>0</v>
-      </c>
+      <c r="A7" s="343"/>
+      <c r="B7" s="455"/>
+      <c r="C7" s="344"/>
+      <c r="D7" s="344"/>
     </row>
     <row r="8" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A8" s="343">
-        <v>45791</v>
-      </c>
-      <c r="B8" s="455" t="s">
-        <v>453</v>
-      </c>
-      <c r="C8" s="344">
-        <v>-1</v>
-      </c>
-      <c r="D8" s="344">
-        <v>0</v>
-      </c>
+      <c r="A8" s="343"/>
+      <c r="B8" s="455"/>
+      <c r="C8" s="344"/>
+      <c r="D8" s="344"/>
     </row>
     <row r="9" spans="1:4" ht="24.75" customHeight="1">
-      <c r="A9" s="343">
-        <v>45807</v>
-      </c>
-      <c r="B9" s="455" t="s">
-        <v>454</v>
-      </c>
-      <c r="C9" s="344">
-        <v>2</v>
-      </c>
-      <c r="D9" s="344">
-        <v>0</v>
-      </c>
+      <c r="A9" s="343"/>
+      <c r="B9" s="455"/>
+      <c r="C9" s="344"/>
+      <c r="D9" s="344"/>
     </row>
     <row r="10" spans="1:4" ht="33.75" customHeight="1">
-      <c r="A10" s="343">
-        <v>45814</v>
-      </c>
-      <c r="B10" s="342" t="s">
-        <v>455</v>
-      </c>
-      <c r="C10" s="344">
-        <v>-1</v>
-      </c>
-      <c r="D10" s="344">
-        <v>0</v>
-      </c>
+      <c r="A10" s="343"/>
+      <c r="B10" s="342"/>
+      <c r="C10" s="344"/>
+      <c r="D10" s="344"/>
     </row>
     <row r="11" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A11" s="343">
-        <v>45821</v>
-      </c>
-      <c r="B11" s="455" t="s">
-        <v>456</v>
-      </c>
-      <c r="C11" s="344">
-        <v>1</v>
-      </c>
-      <c r="D11" s="344">
-        <v>0</v>
-      </c>
+      <c r="A11" s="343"/>
+      <c r="B11" s="455"/>
+      <c r="C11" s="344"/>
+      <c r="D11" s="344"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="343">
-        <v>45828</v>
-      </c>
-      <c r="B12" s="455" t="s">
-        <v>457</v>
-      </c>
-      <c r="C12" s="344">
-        <v>-1</v>
-      </c>
-      <c r="D12" s="344">
-        <v>0</v>
-      </c>
+      <c r="A12" s="343"/>
+      <c r="B12" s="455"/>
+      <c r="C12" s="344"/>
+      <c r="D12" s="344"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="343">
-        <v>45835</v>
-      </c>
-      <c r="B13" s="455" t="s">
-        <v>458</v>
-      </c>
-      <c r="C13" s="344">
-        <v>1</v>
-      </c>
-      <c r="D13" s="344">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="45">
-      <c r="A14" s="453">
-        <v>45838</v>
-      </c>
-      <c r="B14" s="457" t="s">
-        <v>459</v>
-      </c>
-      <c r="C14" s="454">
-        <v>-1</v>
-      </c>
-      <c r="D14" s="454">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="30">
-      <c r="A15" s="458">
-        <v>45840</v>
-      </c>
-      <c r="B15" s="456" t="s">
-        <v>460</v>
-      </c>
-      <c r="C15" s="71">
-        <v>2</v>
-      </c>
-      <c r="D15" s="71">
-        <v>0</v>
-      </c>
+      <c r="A13" s="343"/>
+      <c r="B13" s="455"/>
+      <c r="C13" s="344"/>
+      <c r="D13" s="344"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="453"/>
+      <c r="B14" s="457"/>
+      <c r="C14" s="454"/>
+      <c r="D14" s="454"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="458"/>
+      <c r="B15" s="456"/>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -42462,7 +40252,7 @@
       <c r="L5" s="596"/>
       <c r="M5" s="596"/>
       <c r="N5" s="608" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="O5" s="608"/>
       <c r="P5" s="608"/>
@@ -43345,7 +41135,7 @@
       <c r="R2" s="610"/>
       <c r="S2" s="610"/>
       <c r="T2" s="611" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="U2" s="611"/>
       <c r="V2" s="611"/>
@@ -45135,7 +42925,7 @@
     </row>
     <row r="2" spans="1:21" ht="19.5" thickBot="1">
       <c r="A2" s="615" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="B2" s="616"/>
       <c r="C2" s="616"/>
@@ -45236,33 +43026,33 @@
         <v>23</v>
       </c>
       <c r="C6" s="319"/>
-      <c r="D6" s="320">
+      <c r="D6" s="320" t="str">
         <f>IF(data_status_reg!$E4="bajo",0,IF(data_status_reg!$E4="medio",0.5,IF(data_status_reg!$E4="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="E6" s="321"/>
       <c r="F6" s="321"/>
-      <c r="G6" s="320">
+      <c r="G6" s="320" t="str">
         <f>IF(data_status_reg!$E20="bajo",0,IF(data_status_reg!$E20="medio",0.5,IF(data_status_reg!$E20="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="H6" s="321"/>
       <c r="I6" s="321"/>
-      <c r="J6" s="320">
+      <c r="J6" s="320" t="str">
         <f>IF(data_status_reg!$E36="bajo",0,IF(data_status_reg!$E36="medio",0.5,IF(data_status_reg!$E36="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="K6" s="321"/>
       <c r="L6" s="321"/>
-      <c r="M6" s="320">
+      <c r="M6" s="320" t="str">
         <f>IF(data_status_reg!$E52="bajo",0,IF(data_status_reg!$E52="medio",0.5,IF(data_status_reg!$E52="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="N6" s="322"/>
       <c r="O6" s="336"/>
-      <c r="P6" s="320">
+      <c r="P6" s="320" t="str">
         <f>IF(data_status_reg!$E68="bajo",0,IF(data_status_reg!$E68="medio",0.5,IF(data_status_reg!$E68="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="Q6" s="323"/>
       <c r="R6" s="314"/>
@@ -45273,33 +43063,33 @@
         <v>24</v>
       </c>
       <c r="C7" s="324"/>
-      <c r="D7" s="309">
+      <c r="D7" s="309" t="str">
         <f>IF(data_status_reg!$E5="bajo",0,IF(data_status_reg!$E5="medio",0.5,IF(data_status_reg!$E5="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="E7" s="310"/>
       <c r="F7" s="310"/>
-      <c r="G7" s="309">
+      <c r="G7" s="309" t="str">
         <f>IF(data_status_reg!$E21="bajo",0,IF(data_status_reg!$E21="medio",0.5,IF(data_status_reg!$E21="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="H7" s="310"/>
       <c r="I7" s="310"/>
-      <c r="J7" s="309">
+      <c r="J7" s="309" t="str">
         <f>IF(data_status_reg!$E37="bajo",0,IF(data_status_reg!$E37="medio",0.5,IF(data_status_reg!$E37="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="K7" s="310"/>
       <c r="L7" s="310"/>
-      <c r="M7" s="309">
+      <c r="M7" s="309" t="str">
         <f>IF(data_status_reg!$E53="bajo",0,IF(data_status_reg!$E53="medio",0.5,IF(data_status_reg!$E53="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="N7" s="307"/>
       <c r="O7" s="337"/>
-      <c r="P7" s="309">
+      <c r="P7" s="309" t="str">
         <f>IF(data_status_reg!$E69="bajo",0,IF(data_status_reg!$E69="medio",0.5,IF(data_status_reg!$E69="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="Q7" s="325"/>
       <c r="R7" s="3"/>
@@ -45310,33 +43100,33 @@
         <v>25</v>
       </c>
       <c r="C8" s="324"/>
-      <c r="D8" s="309">
+      <c r="D8" s="309" t="str">
         <f>IF(data_status_reg!$E6="bajo",0,IF(data_status_reg!$E6="medio",0.5,IF(data_status_reg!$E6="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="E8" s="310"/>
       <c r="F8" s="310"/>
-      <c r="G8" s="309">
+      <c r="G8" s="309" t="str">
         <f>IF(data_status_reg!$E22="bajo",0,IF(data_status_reg!$E22="medio",0.5,IF(data_status_reg!$E22="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="H8" s="310"/>
       <c r="I8" s="310"/>
-      <c r="J8" s="309">
+      <c r="J8" s="309" t="str">
         <f>IF(data_status_reg!$E38="bajo",0,IF(data_status_reg!$E38="medio",0.5,IF(data_status_reg!$E38="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="K8" s="310"/>
       <c r="L8" s="310"/>
-      <c r="M8" s="309">
+      <c r="M8" s="309" t="str">
         <f>IF(data_status_reg!$E54="bajo",0,IF(data_status_reg!$E54="medio",0.5,IF(data_status_reg!$E54="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="N8" s="307"/>
       <c r="O8" s="337"/>
-      <c r="P8" s="309">
+      <c r="P8" s="309" t="str">
         <f>IF(data_status_reg!$E70="bajo",0,IF(data_status_reg!$E70="medio",0.5,IF(data_status_reg!$E70="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="Q8" s="325"/>
       <c r="R8" s="3"/>
@@ -45347,33 +43137,33 @@
         <v>26</v>
       </c>
       <c r="C9" s="324"/>
-      <c r="D9" s="309">
+      <c r="D9" s="309" t="str">
         <f>IF(data_status_reg!$E7="bajo",0,IF(data_status_reg!$E7="medio",0.5,IF(data_status_reg!$E7="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="E9" s="310"/>
       <c r="F9" s="310"/>
-      <c r="G9" s="309">
+      <c r="G9" s="309" t="str">
         <f>IF(data_status_reg!$E23="bajo",0,IF(data_status_reg!$E23="medio",0.5,IF(data_status_reg!$E23="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="H9" s="310"/>
       <c r="I9" s="310"/>
-      <c r="J9" s="309">
+      <c r="J9" s="309" t="str">
         <f>IF(data_status_reg!$E39="bajo",0,IF(data_status_reg!$E39="medio",0.5,IF(data_status_reg!$E39="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="K9" s="310"/>
       <c r="L9" s="310"/>
-      <c r="M9" s="309">
+      <c r="M9" s="309" t="str">
         <f>IF(data_status_reg!$E55="bajo",0,IF(data_status_reg!$E55="medio",0.5,IF(data_status_reg!$E55="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="N9" s="307"/>
       <c r="O9" s="337"/>
-      <c r="P9" s="309">
+      <c r="P9" s="309" t="str">
         <f>IF(data_status_reg!$E71="bajo",0,IF(data_status_reg!$E71="medio",0.5,IF(data_status_reg!$E71="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="Q9" s="325"/>
       <c r="R9" s="3"/>
@@ -45384,33 +43174,33 @@
         <v>27</v>
       </c>
       <c r="C10" s="324"/>
-      <c r="D10" s="309">
+      <c r="D10" s="309" t="str">
         <f>IF(data_status_reg!$E8="bajo",0,IF(data_status_reg!$E8="medio",0.5,IF(data_status_reg!$E8="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="E10" s="310"/>
       <c r="F10" s="310"/>
-      <c r="G10" s="309">
+      <c r="G10" s="309" t="str">
         <f>IF(data_status_reg!$E24="bajo",0,IF(data_status_reg!$E24="medio",0.5,IF(data_status_reg!$E24="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="H10" s="310"/>
       <c r="I10" s="310"/>
-      <c r="J10" s="309">
+      <c r="J10" s="309" t="str">
         <f>IF(data_status_reg!$E40="bajo",0,IF(data_status_reg!$E40="medio",0.5,IF(data_status_reg!$E40="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="K10" s="310"/>
       <c r="L10" s="310"/>
-      <c r="M10" s="309">
+      <c r="M10" s="309" t="str">
         <f>IF(data_status_reg!$E56="bajo",0,IF(data_status_reg!$E56="medio",0.5,IF(data_status_reg!$E56="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="N10" s="307"/>
       <c r="O10" s="337"/>
-      <c r="P10" s="309">
+      <c r="P10" s="309" t="str">
         <f>IF(data_status_reg!$E72="bajo",0,IF(data_status_reg!$E72="medio",0.5,IF(data_status_reg!$E72="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="Q10" s="325"/>
       <c r="R10" s="3"/>
@@ -45421,33 +43211,33 @@
         <v>28</v>
       </c>
       <c r="C11" s="324"/>
-      <c r="D11" s="309">
+      <c r="D11" s="309" t="str">
         <f>IF(data_status_reg!$E9="bajo",0,IF(data_status_reg!$E9="medio",0.5,IF(data_status_reg!$E9="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="E11" s="310"/>
       <c r="F11" s="310"/>
-      <c r="G11" s="309">
+      <c r="G11" s="309" t="str">
         <f>IF(data_status_reg!$E25="bajo",0,IF(data_status_reg!$E25="medio",0.5,IF(data_status_reg!$E25="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="H11" s="310"/>
       <c r="I11" s="310"/>
-      <c r="J11" s="309">
+      <c r="J11" s="309" t="str">
         <f>IF(data_status_reg!$E41="bajo",0,IF(data_status_reg!$E41="medio",0.5,IF(data_status_reg!$E41="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="K11" s="310"/>
       <c r="L11" s="310"/>
-      <c r="M11" s="309">
+      <c r="M11" s="309" t="str">
         <f>IF(data_status_reg!$E57="bajo",0,IF(data_status_reg!$E57="medio",0.5,IF(data_status_reg!$E57="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="N11" s="307"/>
       <c r="O11" s="337"/>
-      <c r="P11" s="309">
+      <c r="P11" s="309" t="str">
         <f>IF(data_status_reg!$E73="bajo",0,IF(data_status_reg!$E73="medio",0.5,IF(data_status_reg!$E73="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="Q11" s="325"/>
       <c r="R11" s="3"/>
@@ -45458,33 +43248,33 @@
         <v>29</v>
       </c>
       <c r="C12" s="324"/>
-      <c r="D12" s="309">
+      <c r="D12" s="309" t="str">
         <f>IF(data_status_reg!$E10="bajo",0,IF(data_status_reg!$E10="medio",0.5,IF(data_status_reg!$E10="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="E12" s="310"/>
       <c r="F12" s="310"/>
-      <c r="G12" s="309">
+      <c r="G12" s="309" t="str">
         <f>IF(data_status_reg!$E26="bajo",0,IF(data_status_reg!$E26="medio",0.5,IF(data_status_reg!$E26="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="H12" s="310"/>
       <c r="I12" s="311"/>
-      <c r="J12" s="309">
+      <c r="J12" s="309" t="str">
         <f>IF(data_status_reg!$E42="bajo",0,IF(data_status_reg!$E42="medio",0.5,IF(data_status_reg!$E42="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="K12" s="311"/>
       <c r="L12" s="311"/>
-      <c r="M12" s="309">
+      <c r="M12" s="309" t="str">
         <f>IF(data_status_reg!$E58="bajo",0,IF(data_status_reg!$E58="medio",0.5,IF(data_status_reg!$E58="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="N12" s="308"/>
       <c r="O12" s="338"/>
-      <c r="P12" s="309">
+      <c r="P12" s="309" t="str">
         <f>IF(data_status_reg!$E74="bajo",0,IF(data_status_reg!$E74="medio",0.5,IF(data_status_reg!$E74="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="Q12" s="325"/>
       <c r="R12" s="3"/>
@@ -45495,33 +43285,33 @@
         <v>30</v>
       </c>
       <c r="C13" s="324"/>
-      <c r="D13" s="309">
+      <c r="D13" s="309" t="str">
         <f>IF(data_status_reg!$E11="bajo",0,IF(data_status_reg!$E11="medio",0.5,IF(data_status_reg!$E11="alto",1,"falta riesgo")))</f>
-        <v>0.5</v>
+        <v>falta riesgo</v>
       </c>
       <c r="E13" s="310"/>
       <c r="F13" s="310"/>
-      <c r="G13" s="309">
+      <c r="G13" s="309" t="str">
         <f>IF(data_status_reg!$E27="bajo",0,IF(data_status_reg!$E27="medio",0.5,IF(data_status_reg!$E27="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="H13" s="310"/>
       <c r="I13" s="310"/>
-      <c r="J13" s="309">
+      <c r="J13" s="309" t="str">
         <f>IF(data_status_reg!$E43="bajo",0,IF(data_status_reg!$E43="medio",0.5,IF(data_status_reg!$E43="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="K13" s="310"/>
       <c r="L13" s="310"/>
-      <c r="M13" s="309">
+      <c r="M13" s="309" t="str">
         <f>IF(data_status_reg!$E59="bajo",0,IF(data_status_reg!$E59="medio",0.5,IF(data_status_reg!$E59="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="N13" s="307"/>
       <c r="O13" s="337"/>
-      <c r="P13" s="309">
+      <c r="P13" s="309" t="str">
         <f>IF(data_status_reg!$E75="bajo",0,IF(data_status_reg!$E75="medio",0.5,IF(data_status_reg!$E75="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="Q13" s="325"/>
       <c r="R13" s="3"/>
@@ -45533,33 +43323,33 @@
         <v>31</v>
       </c>
       <c r="C14" s="324"/>
-      <c r="D14" s="309">
+      <c r="D14" s="309" t="str">
         <f>IF(data_status_reg!$E12="bajo",0,IF(data_status_reg!$E12="medio",0.5,IF(data_status_reg!$E12="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="E14" s="310"/>
       <c r="F14" s="310"/>
-      <c r="G14" s="309">
+      <c r="G14" s="309" t="str">
         <f>IF(data_status_reg!$E28="bajo",0,IF(data_status_reg!$E28="medio",0.5,IF(data_status_reg!$E28="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="H14" s="310"/>
       <c r="I14" s="310"/>
-      <c r="J14" s="309">
+      <c r="J14" s="309" t="str">
         <f>IF(data_status_reg!$E44="bajo",0,IF(data_status_reg!$E44="medio",0.5,IF(data_status_reg!$E44="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="K14" s="310"/>
       <c r="L14" s="310"/>
-      <c r="M14" s="309">
+      <c r="M14" s="309" t="str">
         <f>IF(data_status_reg!$E60="bajo",0,IF(data_status_reg!$E60="medio",0.5,IF(data_status_reg!$E60="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="N14" s="307"/>
       <c r="O14" s="337"/>
-      <c r="P14" s="309">
+      <c r="P14" s="309" t="str">
         <f>IF(data_status_reg!$E76="bajo",0,IF(data_status_reg!$E76="medio",0.5,IF(data_status_reg!$E76="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="Q14" s="325"/>
       <c r="R14" s="3"/>
@@ -45570,33 +43360,33 @@
         <v>32</v>
       </c>
       <c r="C15" s="324"/>
-      <c r="D15" s="309">
+      <c r="D15" s="309" t="str">
         <f>IF(data_status_reg!$E13="bajo",0,IF(data_status_reg!$E13="medio",0.5,IF(data_status_reg!$E13="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="E15" s="310"/>
       <c r="F15" s="310"/>
-      <c r="G15" s="309">
+      <c r="G15" s="309" t="str">
         <f>IF(data_status_reg!$E29="bajo",0,IF(data_status_reg!$E29="medio",0.5,IF(data_status_reg!$E29="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="H15" s="310"/>
       <c r="I15" s="311"/>
-      <c r="J15" s="309">
+      <c r="J15" s="309" t="str">
         <f>IF(data_status_reg!$E45="bajo",0,IF(data_status_reg!$E45="medio",0.5,IF(data_status_reg!$E45="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="K15" s="311"/>
       <c r="L15" s="311"/>
-      <c r="M15" s="309">
+      <c r="M15" s="309" t="str">
         <f>IF(data_status_reg!$E61="bajo",0,IF(data_status_reg!$E61="medio",0.5,IF(data_status_reg!$E61="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="N15" s="308"/>
       <c r="O15" s="338"/>
-      <c r="P15" s="309">
+      <c r="P15" s="309" t="str">
         <f>IF(data_status_reg!$E77="bajo",0,IF(data_status_reg!$E77="medio",0.5,IF(data_status_reg!$E77="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="Q15" s="325"/>
       <c r="R15" s="3"/>
@@ -45607,33 +43397,33 @@
         <v>33</v>
       </c>
       <c r="C16" s="324"/>
-      <c r="D16" s="309">
+      <c r="D16" s="309" t="str">
         <f>IF(data_status_reg!$E14="bajo",0,IF(data_status_reg!$E14="medio",0.5,IF(data_status_reg!$E14="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="E16" s="310"/>
       <c r="F16" s="310"/>
-      <c r="G16" s="309">
+      <c r="G16" s="309" t="str">
         <f>IF(data_status_reg!$E30="bajo",0,IF(data_status_reg!$E30="medio",0.5,IF(data_status_reg!$E30="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="H16" s="310"/>
       <c r="I16" s="310"/>
-      <c r="J16" s="309">
+      <c r="J16" s="309" t="str">
         <f>IF(data_status_reg!$E46="bajo",0,IF(data_status_reg!$E46="medio",0.5,IF(data_status_reg!$E46="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="K16" s="310"/>
       <c r="L16" s="310"/>
-      <c r="M16" s="309">
+      <c r="M16" s="309" t="str">
         <f>IF(data_status_reg!$E62="bajo",0,IF(data_status_reg!$E62="medio",0.5,IF(data_status_reg!$E62="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="N16" s="307"/>
       <c r="O16" s="337"/>
-      <c r="P16" s="309">
+      <c r="P16" s="309" t="str">
         <f>IF(data_status_reg!$E78="bajo",0,IF(data_status_reg!$E78="medio",0.5,IF(data_status_reg!$E78="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="Q16" s="325"/>
       <c r="R16" s="3"/>
@@ -45644,33 +43434,33 @@
         <v>34</v>
       </c>
       <c r="C17" s="324"/>
-      <c r="D17" s="309">
+      <c r="D17" s="309" t="str">
         <f>IF(data_status_reg!$E15="bajo",0,IF(data_status_reg!$E15="medio",0.5,IF(data_status_reg!$E15="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="E17" s="310"/>
       <c r="F17" s="310"/>
-      <c r="G17" s="309">
+      <c r="G17" s="309" t="str">
         <f>IF(data_status_reg!$E31="bajo",0,IF(data_status_reg!$E31="medio",0.5,IF(data_status_reg!$E31="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="H17" s="310"/>
       <c r="I17" s="310"/>
-      <c r="J17" s="309">
+      <c r="J17" s="309" t="str">
         <f>IF(data_status_reg!$E47="bajo",0,IF(data_status_reg!$E47="medio",0.5,IF(data_status_reg!$E47="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="K17" s="310"/>
       <c r="L17" s="310"/>
-      <c r="M17" s="309">
+      <c r="M17" s="309" t="str">
         <f>IF(data_status_reg!$E63="bajo",0,IF(data_status_reg!$E63="medio",0.5,IF(data_status_reg!$E63="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="N17" s="307"/>
       <c r="O17" s="337"/>
-      <c r="P17" s="309">
+      <c r="P17" s="309" t="str">
         <f>IF(data_status_reg!$E79="bajo",0,IF(data_status_reg!$E79="medio",0.5,IF(data_status_reg!$E79="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="Q17" s="325"/>
       <c r="R17" s="3"/>
@@ -45681,9 +43471,9 @@
         <v>35</v>
       </c>
       <c r="C18" s="324"/>
-      <c r="D18" s="309">
+      <c r="D18" s="309" t="str">
         <f>IF(data_status_reg!$E16="bajo",0,IF(data_status_reg!$E16="medio",0.5,IF(data_status_reg!$E16="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="E18" s="310"/>
       <c r="F18" s="310"/>
@@ -45692,20 +43482,20 @@
       </c>
       <c r="H18" s="310"/>
       <c r="I18" s="310"/>
-      <c r="J18" s="309">
+      <c r="J18" s="309" t="str">
         <f>IF(data_status_reg!$E48="bajo",0,IF(data_status_reg!$E48="medio",0.5,IF(data_status_reg!$E48="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="K18" s="310"/>
-      <c r="M18" s="309">
+      <c r="M18" s="309" t="str">
         <f>IF(data_status_reg!$E64="bajo",0,IF(data_status_reg!$E64="medio",0.5,IF(data_status_reg!$E64="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="N18" s="308"/>
       <c r="O18" s="338"/>
-      <c r="P18" s="309">
+      <c r="P18" s="309" t="str">
         <f>IF(data_status_reg!$E80="bajo",0,IF(data_status_reg!$E80="medio",0.5,IF(data_status_reg!$E80="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="Q18" s="325"/>
       <c r="R18" s="3"/>
@@ -45716,33 +43506,33 @@
         <v>36</v>
       </c>
       <c r="C19" s="324"/>
-      <c r="D19" s="309">
+      <c r="D19" s="309" t="str">
         <f>IF(data_status_reg!$E17="bajo",0,IF(data_status_reg!$E17="medio",0.5,IF(data_status_reg!$E17="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="E19" s="310"/>
       <c r="F19" s="310"/>
-      <c r="G19" s="309">
+      <c r="G19" s="309" t="str">
         <f>IF(data_status_reg!$E33="bajo",0,IF(data_status_reg!$E33="medio",0.5,IF(data_status_reg!$E33="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="H19" s="310"/>
       <c r="I19" s="310"/>
-      <c r="J19" s="309">
+      <c r="J19" s="309" t="str">
         <f>IF(data_status_reg!$E49="bajo",0,IF(data_status_reg!$E49="medio",0.5,IF(data_status_reg!$E49="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="K19" s="310"/>
       <c r="L19" s="310"/>
-      <c r="M19" s="309">
+      <c r="M19" s="309" t="str">
         <f>IF(data_status_reg!$E65="bajo",0,IF(data_status_reg!$E65="medio",0.5,IF(data_status_reg!$E65="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="N19" s="307"/>
       <c r="O19" s="337"/>
-      <c r="P19" s="309">
+      <c r="P19" s="309" t="str">
         <f>IF(data_status_reg!$E81="bajo",0,IF(data_status_reg!$E81="medio",0.5,IF(data_status_reg!$E81="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="Q19" s="325"/>
       <c r="R19" s="3"/>
@@ -45753,33 +43543,33 @@
         <v>37</v>
       </c>
       <c r="C20" s="324"/>
-      <c r="D20" s="309">
+      <c r="D20" s="309" t="str">
         <f>IF(data_status_reg!$E18="bajo",0,IF(data_status_reg!$E18="medio",0.5,IF(data_status_reg!$E18="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="E20" s="310"/>
       <c r="F20" s="310"/>
-      <c r="G20" s="309">
+      <c r="G20" s="309" t="str">
         <f>IF(data_status_reg!$E34="bajo",0,IF(data_status_reg!$E34="medio",0.5,IF(data_status_reg!$E34="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="H20" s="310"/>
       <c r="I20" s="310"/>
-      <c r="J20" s="309">
+      <c r="J20" s="309" t="str">
         <f>IF(data_status_reg!$E50="bajo",0,IF(data_status_reg!$E50="medio",0.5,IF(data_status_reg!$E50="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="K20" s="310"/>
       <c r="L20" s="310"/>
-      <c r="M20" s="309">
+      <c r="M20" s="309" t="str">
         <f>IF(data_status_reg!$E66="bajo",0,IF(data_status_reg!$E66="medio",0.5,IF(data_status_reg!$E66="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="N20" s="307"/>
       <c r="O20" s="337"/>
-      <c r="P20" s="309">
+      <c r="P20" s="309" t="str">
         <f>IF(data_status_reg!$E82="bajo",0,IF(data_status_reg!$E82="medio",0.5,IF(data_status_reg!$E82="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="Q20" s="325"/>
       <c r="R20" s="3"/>
@@ -45790,9 +43580,9 @@
         <v>38</v>
       </c>
       <c r="C21" s="326"/>
-      <c r="D21" s="327">
+      <c r="D21" s="327" t="str">
         <f>IF(data_status_reg!$E19="bajo",0,IF(data_status_reg!$E19="medio",0.5,IF(data_status_reg!$E19="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="E21" s="328"/>
       <c r="F21" s="328"/>
@@ -45801,21 +43591,21 @@
       </c>
       <c r="H21" s="328"/>
       <c r="I21" s="328"/>
-      <c r="J21" s="327">
+      <c r="J21" s="327" t="str">
         <f>IF(data_status_reg!$E51="bajo",0,IF(data_status_reg!$E51="medio",0.5,IF(data_status_reg!$E51="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="K21" s="328"/>
       <c r="L21" s="329"/>
-      <c r="M21" s="330">
+      <c r="M21" s="330" t="str">
         <f>IF(data_status_reg!$E67="bajo",0,IF(data_status_reg!$E67="medio",0.5,IF(data_status_reg!$E67="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="N21" s="331"/>
       <c r="O21" s="339"/>
-      <c r="P21" s="327">
+      <c r="P21" s="327" t="str">
         <f>IF(data_status_reg!$E83="bajo",0,IF(data_status_reg!$E83="medio",0.5,IF(data_status_reg!$E83="alto",1,"falta riesgo")))</f>
-        <v>0</v>
+        <v>falta riesgo</v>
       </c>
       <c r="Q21" s="332"/>
       <c r="R21" s="3"/>
@@ -46122,7 +43912,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A2:G53"/>
+  <dimension ref="B2:C53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="39.7109375" customWidth="1"/>
@@ -46131,1109 +43921,449 @@
     <col min="5" max="5" width="74.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="18" customHeight="1"/>
-    <row r="3" spans="1:7" ht="18" customHeight="1">
-      <c r="A3" t="s">
-        <v>190</v>
-      </c>
+    <row r="2" spans="2:3" ht="18" customHeight="1"/>
+    <row r="3" spans="2:3" ht="18" customHeight="1">
       <c r="B3" s="541" t="str">
         <f>_xlfn.CONCAT($D3,":"," ","Auditorías del Plan Anual de Auditoría")</f>
-        <v>CDC: Auditorías del Plan Anual de Auditoría</v>
+        <v>: Auditorías del Plan Anual de Auditoría</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C46" si="0">IF($F3="bajo",0,IF($F3="medio",2,IF($F3="alto",3,4)))</f>
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>193</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18" customHeight="1">
-      <c r="A4" t="s">
-        <v>190</v>
-      </c>
+        <f>IF($G3="bajo",0,IF($G3="medio",2,IF($G3="alto",3,4)))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="18" customHeight="1">
       <c r="B4" s="541" t="str">
         <f>_xlfn.CONCAT($D4,":"," ","Documentos publicados en web Centro de Estudios")</f>
-        <v>CDC: Documentos publicados en web Centro de Estudios</v>
+        <v>: Documentos publicados en web Centro de Estudios</v>
       </c>
       <c r="C4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>194</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="18" customHeight="1">
-      <c r="A5" t="s">
-        <v>190</v>
-      </c>
+        <f t="shared" ref="C4:C46" si="0">IF($G4="bajo",0,IF($G4="medio",2,IF($G4="alto",3,4)))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="18" customHeight="1">
       <c r="B5" s="541" t="str">
         <f>_xlfn.CONCAT($D5,":"," ","Solicitudes de información respondidas")</f>
-        <v>CDC: Solicitudes de información respondidas</v>
+        <v>: Solicitudes de información respondidas</v>
       </c>
       <c r="C5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>195</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18" customHeight="1">
-      <c r="A6" t="s">
-        <v>191</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="18" customHeight="1">
       <c r="B6" s="541" t="str">
         <f>_xlfn.CONCAT($D6,":"," ","Solicitudes de certificados de estudio")</f>
-        <v>CDC: Solicitudes de certificados de estudio</v>
+        <v>: Solicitudes de certificados de estudio</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>196</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="18" customHeight="1">
-      <c r="A7" t="s">
-        <v>191</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="18" customHeight="1">
       <c r="B7" s="541" t="str">
         <f>_xlfn.CONCAT($D7,":"," ","Sistema Calidad de Servicio y Experiencia")</f>
-        <v>PMG: Sistema Calidad de Servicio y Experiencia</v>
+        <v>: Sistema Calidad de Servicio y Experiencia</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" t="s">
-        <v>197</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1">
-      <c r="A8" t="s">
-        <v>191</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="18" customHeight="1">
       <c r="B8" s="541" t="str">
         <f>_xlfn.CONCAT($D8,":"," ","Medidas de Equidad y Género")</f>
-        <v>PMG: Medidas de Equidad y Género</v>
+        <v>: Medidas de Equidad y Género</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" t="s">
-        <v>198</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="18" customHeight="1">
-      <c r="A9" t="s">
-        <v>191</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="18" customHeight="1">
       <c r="B9" s="541" t="str">
         <f>_xlfn.CONCAT($D9,":"," ","Acciones formativas del Centro de Innovación")</f>
-        <v>CDC: Acciones formativas del Centro de Innovación</v>
+        <v>: Acciones formativas del Centro de Innovación</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" t="s">
-        <v>199</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18" customHeight="1">
-      <c r="A10" t="s">
-        <v>191</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="18" customHeight="1">
       <c r="B10" s="541" t="str">
         <f>_xlfn.CONCAT($D10,":"," ","Compra de equipamiento")</f>
-        <v>CDC: Compra de equipamiento</v>
+        <v>: Compra de equipamiento</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" t="s">
-        <v>200</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="18" customHeight="1">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="18" customHeight="1">
       <c r="B11" s="541" t="str">
         <f>_xlfn.CONCAT($D11,":"," ","Elaboración de informe formación docente")</f>
-        <v>CDC: Elaboración de informe formación docente</v>
+        <v>: Elaboración de informe formación docente</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" t="s">
-        <v>201</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="18" customHeight="1">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="18" customHeight="1">
       <c r="B12" s="541" t="str">
         <f>_xlfn.CONCAT($D12,":"," ","Provincias que participan de acciones de CPEIP")</f>
-        <v>H: Provincias que participan de acciones de CPEIP</v>
+        <v>: Provincias que participan de acciones de CPEIP</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="F12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="18" customHeight="1">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" ht="18" customHeight="1">
       <c r="B13" s="541" t="str">
         <f>_xlfn.CONCAT($D13,":"," ","Formación de bienestar docente")</f>
-        <v>CDC: Formación de bienestar docente</v>
+        <v>: Formación de bienestar docente</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" t="s">
-        <v>203</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="18" customHeight="1">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="18" customHeight="1">
       <c r="B14" s="541" t="str">
         <f>_xlfn.CONCAT($D14,":"," ","Informe proyecto de ley carrera directiva")</f>
-        <v>CDC: Informe proyecto de ley carrera directiva</v>
+        <v>: Informe proyecto de ley carrera directiva</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" t="s">
-        <v>204</v>
-      </c>
-      <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="18" customHeight="1">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="18" customHeight="1">
       <c r="B15" s="541" t="str">
         <f>_xlfn.CONCAT($D15,":"," ","Implementación del Programa 'A convivir se Aprende'")</f>
-        <v>H: Implementación del Programa 'A convivir se Aprende'</v>
+        <v>: Implementación del Programa 'A convivir se Aprende'</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D15" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="F15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" ht="19.5" customHeight="1">
       <c r="B16" s="541" t="str">
         <f>_xlfn.CONCAT($D16,":"," ","Inscipción para completar los estudios")</f>
-        <v>CDC: Inscipción para completar los estudios</v>
+        <v>: Inscipción para completar los estudios</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" t="s">
-        <v>206</v>
-      </c>
-      <c r="F16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="18" customHeight="1">
-      <c r="A17" t="s">
-        <v>19</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="18" customHeight="1">
       <c r="B17" s="541" t="str">
         <f>_xlfn.CONCAT($D17,":"," ","Procesos de validación de estudios")</f>
-        <v>CDC: Procesos de validación de estudios</v>
+        <v>: Procesos de validación de estudios</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" t="s">
-        <v>207</v>
-      </c>
-      <c r="F17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="18" customHeight="1">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="18" customHeight="1">
       <c r="B18" s="541" t="str">
         <f>_xlfn.CONCAT($D18,":"," ","Acciones plan de difusión")</f>
-        <v>CDC: Acciones plan de difusión</v>
+        <v>: Acciones plan de difusión</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" t="s">
-        <v>208</v>
-      </c>
-      <c r="F18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="18" customHeight="1">
-      <c r="A19" t="s">
-        <v>130</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="18" customHeight="1">
       <c r="B19" s="541" t="str">
         <f>_xlfn.CONCAT($D19,":"," ","Sistemas definidos como críticos")</f>
-        <v>CDC: Sistemas definidos como críticos</v>
+        <v>: Sistemas definidos como críticos</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D19" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" t="s">
-        <v>209</v>
-      </c>
-      <c r="F19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="18" customHeight="1">
-      <c r="A20" t="s">
-        <v>130</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" ht="18" customHeight="1">
       <c r="B20" s="541" t="str">
         <f>_xlfn.CONCAT($D20,":"," ","Sitios web con certificados de sitio seguro")</f>
-        <v>CDC: Sitios web con certificados de sitio seguro</v>
+        <v>: Sitios web con certificados de sitio seguro</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D20" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" t="s">
-        <v>210</v>
-      </c>
-      <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="18" customHeight="1">
-      <c r="A21" t="s">
-        <v>130</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="18" customHeight="1">
       <c r="B21" s="541" t="str">
         <f>_xlfn.CONCAT($D21,":"," ","Tickets de atención resueltos")</f>
-        <v>CDC: Tickets de atención resueltos</v>
+        <v>: Tickets de atención resueltos</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D21" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" t="s">
-        <v>211</v>
-      </c>
-      <c r="F21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="18" customHeight="1">
-      <c r="A22" t="s">
-        <v>130</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" ht="18" customHeight="1">
       <c r="B22" s="541" t="str">
         <f>_xlfn.CONCAT($D22,":"," ","Transformación Digital")</f>
-        <v>PMG: Transformación Digital</v>
+        <v>: Transformación Digital</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D22" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" t="s">
-        <v>212</v>
-      </c>
-      <c r="F22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="18" customHeight="1">
-      <c r="A23" t="s">
-        <v>130</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" ht="18" customHeight="1">
       <c r="B23" s="541" t="str">
         <f>_xlfn.CONCAT($D23,":"," ","Concentración del Gasto")</f>
-        <v>PMG: Concentración del Gasto</v>
+        <v>: Concentración del Gasto</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D23" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" t="s">
-        <v>213</v>
-      </c>
-      <c r="F23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A24" t="s">
-        <v>130</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="22.5" customHeight="1">
       <c r="B24" s="541" t="str">
         <f>_xlfn.CONCAT($D24,":"," ","Asistencia vía SIGE")</f>
-        <v>CDC: Asistencia vía SIGE</v>
+        <v>: Asistencia vía SIGE</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D24" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" t="s">
-        <v>214</v>
-      </c>
-      <c r="F24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="18" customHeight="1">
-      <c r="A25" t="s">
-        <v>130</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" ht="18" customHeight="1">
       <c r="B25" s="541" t="str">
         <f>_xlfn.CONCAT($D25,":"," ","Transacciones a través del sistema SIGPA")</f>
-        <v>CDC: Transacciones a través del sistema SIGPA</v>
+        <v>: Transacciones a través del sistema SIGPA</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D25" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" t="s">
-        <v>215</v>
-      </c>
-      <c r="F25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="18" customHeight="1">
-      <c r="A26" t="s">
-        <v>130</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" ht="18" customHeight="1">
       <c r="B26" s="541" t="str">
         <f>_xlfn.CONCAT($D26,":"," ","Procesos documentados URAE")</f>
-        <v>CDC: Procesos documentados URAE</v>
+        <v>: Procesos documentados URAE</v>
       </c>
       <c r="C26">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D26" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" t="s">
-        <v>216</v>
-      </c>
-      <c r="F26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="18" customHeight="1">
-      <c r="A27" t="s">
-        <v>16</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" ht="18" customHeight="1">
       <c r="B27" s="541" t="str">
         <f>_xlfn.CONCAT($D27,":"," ","Solicitudes de beneficios y/o préstamos")</f>
-        <v>CDC: Solicitudes de beneficios y/o préstamos</v>
+        <v>: Solicitudes de beneficios y/o préstamos</v>
       </c>
       <c r="C27">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D27" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" t="s">
-        <v>217</v>
-      </c>
-      <c r="F27" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="18" customHeight="1">
-      <c r="A28" t="s">
-        <v>16</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" ht="18" customHeight="1">
       <c r="B28" s="541" t="str">
         <f>_xlfn.CONCAT($D28,":"," ","Expedientes de compras")</f>
-        <v>CDC: Expedientes de compras</v>
+        <v>: Expedientes de compras</v>
       </c>
       <c r="C28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D28" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" t="s">
-        <v>218</v>
-      </c>
-      <c r="F28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="18" customHeight="1">
-      <c r="A29" t="s">
-        <v>16</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" ht="18" customHeight="1">
       <c r="B29" s="541" t="str">
         <f>_xlfn.CONCAT($D29,":"," ","Sistema Estado Verde")</f>
-        <v>PMG: Sistema Estado Verde</v>
+        <v>: Sistema Estado Verde</v>
       </c>
       <c r="C29">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D29" t="s">
-        <v>6</v>
-      </c>
-      <c r="E29" t="s">
-        <v>219</v>
-      </c>
-      <c r="F29" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="18" customHeight="1">
-      <c r="A30" t="s">
-        <v>16</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" ht="18" customHeight="1">
       <c r="B30" s="541" t="str">
         <f>_xlfn.CONCAT($D30,":"," ","Sistema de Riesgos Psicosociales laborales")</f>
-        <v>PMG: Sistema de Riesgos Psicosociales laborales</v>
+        <v>: Sistema de Riesgos Psicosociales laborales</v>
       </c>
       <c r="C30">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D30" t="s">
-        <v>6</v>
-      </c>
-      <c r="E30" t="s">
-        <v>220</v>
-      </c>
-      <c r="F30" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="18" customHeight="1">
-      <c r="A31" t="s">
-        <v>16</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" ht="18" customHeight="1">
       <c r="B31" s="541" t="str">
         <f>_xlfn.CONCAT($D31,":"," ","Cierres contables oportunos")</f>
-        <v>CDC: Cierres contables oportunos</v>
+        <v>: Cierres contables oportunos</v>
       </c>
       <c r="C31">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D31" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" t="s">
-        <v>221</v>
-      </c>
-      <c r="F31" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="18" customHeight="1">
-      <c r="A32" t="s">
-        <v>16</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" ht="18" customHeight="1">
       <c r="B32" s="541" t="str">
         <f>_xlfn.CONCAT($D32,":"," ","Contratos nuevos a honorarios NC")</f>
-        <v>CDC: Contratos nuevos a honorarios NC</v>
+        <v>: Contratos nuevos a honorarios NC</v>
       </c>
       <c r="C32">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" t="s">
-        <v>222</v>
-      </c>
-      <c r="F32" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="18" customHeight="1">
-      <c r="A33" t="s">
-        <v>20</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="18" customHeight="1">
       <c r="B33" s="541" t="str">
         <f>_xlfn.CONCAT($D33,":"," ","Recursos de Lectura, Aprendizaje y Bibliotecas")</f>
-        <v>CDC: Recursos de Lectura, Aprendizaje y Bibliotecas</v>
+        <v>: Recursos de Lectura, Aprendizaje y Bibliotecas</v>
       </c>
       <c r="C33">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D33" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" t="s">
-        <v>223</v>
-      </c>
-      <c r="F33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="18" customHeight="1">
-      <c r="A34" t="s">
-        <v>20</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" ht="18" customHeight="1">
       <c r="B34" s="541" t="str">
         <f>_xlfn.CONCAT($D34,":"," ","Ejecución del plan de Desarrollo Curricular")</f>
-        <v>CDC: Ejecución del plan de Desarrollo Curricular</v>
+        <v>: Ejecución del plan de Desarrollo Curricular</v>
       </c>
       <c r="C34">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D34" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" t="s">
-        <v>224</v>
-      </c>
-      <c r="F34" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="18" customHeight="1">
-      <c r="A35" t="s">
-        <v>20</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" ht="18" customHeight="1">
       <c r="B35" s="541" t="str">
         <f>_xlfn.CONCAT($D35,":"," ","Difusión de instrumentos curriculares")</f>
-        <v>CDC: Difusión de instrumentos curriculares</v>
+        <v>: Difusión de instrumentos curriculares</v>
       </c>
       <c r="C35">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D35" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" t="s">
-        <v>225</v>
-      </c>
-      <c r="F35" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="18" customHeight="1">
-      <c r="A36" t="s">
-        <v>20</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" ht="18" customHeight="1">
       <c r="B36" s="541" t="str">
         <f>_xlfn.CONCAT($D36,":"," ","Ejecución del plan de Evaluación y Estándares")</f>
-        <v>CDC: Ejecución del plan de Evaluación y Estándares</v>
+        <v>: Ejecución del plan de Evaluación y Estándares</v>
       </c>
       <c r="C36">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D36" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" t="s">
-        <v>226</v>
-      </c>
-      <c r="F36" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="21" customHeight="1">
-      <c r="A37" t="s">
-        <v>20</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" ht="21" customHeight="1">
       <c r="B37" s="541" t="str">
         <f>_xlfn.CONCAT($D37,":"," ","Modernización de textos escolares")</f>
-        <v>CDC: Modernización de textos escolares</v>
+        <v>: Modernización de textos escolares</v>
       </c>
       <c r="C37">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D37" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" t="s">
-        <v>227</v>
-      </c>
-      <c r="F37" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="21" customHeight="1">
-      <c r="A38" t="s">
-        <v>20</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" ht="21" customHeight="1">
       <c r="B38" s="541" t="str">
         <f>_xlfn.CONCAT($D38,":"," ","Textos Escolares entregados")</f>
-        <v>H: Textos Escolares entregados</v>
+        <v>: Textos Escolares entregados</v>
       </c>
       <c r="C38">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D38" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" t="s">
-        <v>228</v>
-      </c>
-      <c r="F38" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="18" customHeight="1">
-      <c r="A39" t="s">
-        <v>20</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" ht="18" customHeight="1">
       <c r="B39" s="541" t="str">
         <f>_xlfn.CONCAT($D39,":"," ","Entrega de Kit evaluativo de los EE subvencionados")</f>
-        <v>H: Entrega de Kit evaluativo de los EE subvencionados</v>
+        <v>: Entrega de Kit evaluativo de los EE subvencionados</v>
       </c>
       <c r="C39">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D39" t="s">
-        <v>7</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="F39" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="18" customHeight="1">
-      <c r="A40" t="s">
-        <v>192</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" ht="18" customHeight="1">
       <c r="B40" s="541" t="str">
         <f>_xlfn.CONCAT($D40,":"," ","Actos administrativos con una Licitación Pública ")</f>
-        <v xml:space="preserve">CDC: Actos administrativos con una Licitación Pública </v>
+        <v xml:space="preserve">: Actos administrativos con una Licitación Pública </v>
       </c>
       <c r="C40">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D40" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" t="s">
-        <v>230</v>
-      </c>
-      <c r="F40" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="18" customHeight="1">
-      <c r="A41" t="s">
-        <v>192</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" ht="18" customHeight="1">
       <c r="B41" s="541" t="str">
         <f>_xlfn.CONCAT($D41,":"," ","Actos administrativos Bases Admin. y Técnicas")</f>
-        <v>CDC: Actos administrativos Bases Admin. y Técnicas</v>
+        <v>: Actos administrativos Bases Admin. y Técnicas</v>
       </c>
       <c r="C41">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D41" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" t="s">
-        <v>231</v>
-      </c>
-      <c r="F41" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="18" customHeight="1">
-      <c r="A42" t="s">
-        <v>192</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" ht="18" customHeight="1">
       <c r="B42" s="541" t="str">
         <f>_xlfn.CONCAT($D42,":"," ","Propuestas de convenios o reformulación")</f>
-        <v>CDC: Propuestas de convenios o reformulación</v>
+        <v>: Propuestas de convenios o reformulación</v>
       </c>
       <c r="C42">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D42" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42" t="s">
-        <v>232</v>
-      </c>
-      <c r="F42" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="18" customHeight="1">
-      <c r="A43" t="s">
-        <v>192</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" ht="18" customHeight="1">
       <c r="B43" s="541" t="str">
         <f>_xlfn.CONCAT($D43,":"," ","Actos administrativos que transfieren recursos")</f>
-        <v>CDC: Actos administrativos que transfieren recursos</v>
+        <v>: Actos administrativos que transfieren recursos</v>
       </c>
       <c r="C43">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D43" t="s">
-        <v>21</v>
-      </c>
-      <c r="E43" t="s">
-        <v>233</v>
-      </c>
-      <c r="F43" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="18" customHeight="1">
-      <c r="A44" t="s">
-        <v>192</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" ht="18" customHeight="1">
       <c r="B44" s="541" t="str">
         <f>_xlfn.CONCAT($D44,":"," ","Actos administrativos artículo 11 de la Ley N°20.159")</f>
-        <v>CDC: Actos administrativos artículo 11 de la Ley N°20.159</v>
+        <v>: Actos administrativos artículo 11 de la Ley N°20.159</v>
       </c>
       <c r="C44">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D44" t="s">
-        <v>21</v>
-      </c>
-      <c r="E44" t="s">
-        <v>234</v>
-      </c>
-      <c r="F44" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="20.25" customHeight="1">
-      <c r="A45" t="s">
-        <v>192</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" ht="20.25" customHeight="1">
       <c r="B45" s="541" t="str">
         <f>_xlfn.CONCAT($D45,":"," ","Recursos de apelación, reclamación")</f>
-        <v>CDC: Recursos de apelación, reclamación</v>
+        <v>: Recursos de apelación, reclamación</v>
       </c>
       <c r="C45">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D45" t="s">
-        <v>21</v>
-      </c>
-      <c r="E45" t="s">
-        <v>235</v>
-      </c>
-      <c r="F45" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="18" customHeight="1">
-      <c r="A46" t="s">
-        <v>192</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" ht="18" customHeight="1">
       <c r="B46" s="541" t="str">
         <f>_xlfn.CONCAT($D46,":"," ","Defensas a recursos de protección")</f>
-        <v>CDC: Defensas a recursos de protección</v>
+        <v>: Defensas a recursos de protección</v>
       </c>
       <c r="C46">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D46" t="s">
-        <v>21</v>
-      </c>
-      <c r="E46" t="s">
-        <v>236</v>
-      </c>
-      <c r="F46" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="18" customHeight="1"/>
-    <row r="48" spans="1:7" ht="18" customHeight="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" ht="18" customHeight="1"/>
+    <row r="48" spans="2:3" ht="18" customHeight="1"/>
     <row r="49" ht="18" customHeight="1"/>
     <row r="50" ht="18" customHeight="1"/>
     <row r="51" ht="18" customHeight="1"/>
@@ -47299,1124 +44429,484 @@
       </c>
     </row>
     <row r="4" spans="2:5">
-      <c r="B4" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="73"/>
     </row>
     <row r="5" spans="2:5">
-      <c r="B5" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="73"/>
     </row>
     <row r="6" spans="2:5">
-      <c r="B6" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="73"/>
     </row>
     <row r="7" spans="2:5">
-      <c r="B7" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="73"/>
     </row>
     <row r="8" spans="2:5">
-      <c r="B8" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="73"/>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="73"/>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="73"/>
     </row>
     <row r="11" spans="2:5">
-      <c r="B11" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="73" t="s">
-        <v>14</v>
-      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="73"/>
     </row>
     <row r="12" spans="2:5">
-      <c r="B12" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E12" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="73"/>
     </row>
     <row r="13" spans="2:5">
-      <c r="B13" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="73"/>
     </row>
     <row r="14" spans="2:5">
-      <c r="B14" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="73"/>
     </row>
     <row r="15" spans="2:5">
-      <c r="B15" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="73"/>
     </row>
     <row r="16" spans="2:5">
-      <c r="B16" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="73"/>
     </row>
     <row r="17" spans="2:5">
-      <c r="B17" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="73"/>
     </row>
     <row r="18" spans="2:5">
-      <c r="B18" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="73"/>
     </row>
     <row r="19" spans="2:5">
-      <c r="B19" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="73"/>
     </row>
     <row r="20" spans="2:5">
-      <c r="B20" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="C20" s="74" t="s">
-        <v>302</v>
-      </c>
-      <c r="D20" s="74" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B20" s="74"/>
+      <c r="C20" s="74"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="73"/>
     </row>
     <row r="21" spans="2:5">
-      <c r="B21" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="C21" s="74" t="s">
-        <v>303</v>
-      </c>
-      <c r="D21" s="74" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B21" s="74"/>
+      <c r="C21" s="74"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="73"/>
     </row>
     <row r="22" spans="2:5">
-      <c r="B22" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="C22" s="74" t="s">
-        <v>304</v>
-      </c>
-      <c r="D22" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B22" s="74"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="73"/>
     </row>
     <row r="23" spans="2:5">
-      <c r="B23" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="C23" s="74" t="s">
-        <v>305</v>
-      </c>
-      <c r="D23" s="74" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B23" s="74"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="73"/>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="C24" s="74" t="s">
-        <v>306</v>
-      </c>
-      <c r="D24" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B24" s="74"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="73"/>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="C25" s="74" t="s">
-        <v>307</v>
-      </c>
-      <c r="D25" s="74" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B25" s="74"/>
+      <c r="C25" s="74"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="73"/>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="C26" s="74" t="s">
-        <v>308</v>
-      </c>
-      <c r="D26" s="74" t="s">
-        <v>29</v>
-      </c>
-      <c r="E26" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B26" s="74"/>
+      <c r="C26" s="74"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="73"/>
     </row>
     <row r="27" spans="2:5">
-      <c r="B27" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="C27" s="74" t="s">
-        <v>309</v>
-      </c>
-      <c r="D27" s="74" t="s">
-        <v>30</v>
-      </c>
-      <c r="E27" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B27" s="74"/>
+      <c r="C27" s="74"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="73"/>
     </row>
     <row r="28" spans="2:5">
-      <c r="B28" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="C28" s="74" t="s">
-        <v>310</v>
-      </c>
-      <c r="D28" s="74" t="s">
-        <v>366</v>
-      </c>
-      <c r="E28" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B28" s="74"/>
+      <c r="C28" s="74"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="73"/>
     </row>
     <row r="29" spans="2:5">
-      <c r="B29" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="C29" s="74" t="s">
-        <v>311</v>
-      </c>
-      <c r="D29" s="74" t="s">
-        <v>32</v>
-      </c>
-      <c r="E29" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B29" s="74"/>
+      <c r="C29" s="74"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="73"/>
     </row>
     <row r="30" spans="2:5">
-      <c r="B30" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="C30" s="74" t="s">
-        <v>312</v>
-      </c>
-      <c r="D30" s="74" t="s">
-        <v>33</v>
-      </c>
-      <c r="E30" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B30" s="74"/>
+      <c r="C30" s="74"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="73"/>
     </row>
     <row r="31" spans="2:5">
-      <c r="B31" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="C31" s="74" t="s">
-        <v>313</v>
-      </c>
-      <c r="D31" s="74" t="s">
-        <v>34</v>
-      </c>
-      <c r="E31" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B31" s="74"/>
+      <c r="C31" s="74"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="73"/>
     </row>
     <row r="32" spans="2:5">
-      <c r="B32" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="C32" s="74" t="s">
-        <v>314</v>
-      </c>
-      <c r="D32" s="74" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" s="73" t="s">
-        <v>45</v>
-      </c>
+      <c r="B32" s="74"/>
+      <c r="C32" s="74"/>
+      <c r="D32" s="74"/>
+      <c r="E32" s="73"/>
     </row>
     <row r="33" spans="2:5">
-      <c r="B33" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="C33" s="74" t="s">
-        <v>315</v>
-      </c>
-      <c r="D33" s="74" t="s">
-        <v>36</v>
-      </c>
-      <c r="E33" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B33" s="74"/>
+      <c r="C33" s="74"/>
+      <c r="D33" s="74"/>
+      <c r="E33" s="73"/>
     </row>
     <row r="34" spans="2:5">
-      <c r="B34" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="C34" s="74" t="s">
-        <v>316</v>
-      </c>
-      <c r="D34" s="74" t="s">
-        <v>37</v>
-      </c>
-      <c r="E34" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B34" s="74"/>
+      <c r="C34" s="74"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="73"/>
     </row>
     <row r="35" spans="2:5">
-      <c r="B35" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="C35" s="74" t="s">
-        <v>317</v>
-      </c>
-      <c r="D35" s="74" t="s">
-        <v>38</v>
-      </c>
-      <c r="E35" s="73" t="s">
-        <v>45</v>
-      </c>
+      <c r="B35" s="74"/>
+      <c r="C35" s="74"/>
+      <c r="D35" s="74"/>
+      <c r="E35" s="73"/>
     </row>
     <row r="36" spans="2:5">
-      <c r="B36" s="71" t="s">
-        <v>283</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E36" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B36" s="71"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="73"/>
     </row>
     <row r="37" spans="2:5">
-      <c r="B37" s="71" t="s">
-        <v>283</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B37" s="71"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="73"/>
     </row>
     <row r="38" spans="2:5">
-      <c r="B38" s="71" t="s">
-        <v>283</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E38" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B38" s="71"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="73"/>
     </row>
     <row r="39" spans="2:5">
-      <c r="B39" s="71" t="s">
-        <v>283</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E39" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B39" s="71"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="73"/>
     </row>
     <row r="40" spans="2:5">
-      <c r="B40" s="71" t="s">
-        <v>283</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E40" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B40" s="71"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="73"/>
     </row>
     <row r="41" spans="2:5">
-      <c r="B41" s="71" t="s">
-        <v>283</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E41" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B41" s="71"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="73"/>
     </row>
     <row r="42" spans="2:5">
-      <c r="B42" s="71" t="s">
-        <v>283</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E42" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B42" s="71"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="73"/>
     </row>
     <row r="43" spans="2:5">
-      <c r="B43" s="71" t="s">
-        <v>283</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E43" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B43" s="71"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="73"/>
     </row>
     <row r="44" spans="2:5">
-      <c r="B44" s="71" t="s">
-        <v>283</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E44" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B44" s="71"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="73"/>
     </row>
     <row r="45" spans="2:5">
-      <c r="B45" s="71" t="s">
-        <v>283</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E45" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B45" s="71"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="73"/>
     </row>
     <row r="46" spans="2:5">
-      <c r="B46" s="71" t="s">
-        <v>283</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E46" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B46" s="71"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="73"/>
     </row>
     <row r="47" spans="2:5">
-      <c r="B47" s="71" t="s">
-        <v>283</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E47" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B47" s="71"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="73"/>
     </row>
     <row r="48" spans="2:5">
-      <c r="B48" s="71" t="s">
-        <v>283</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E48" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B48" s="71"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="73"/>
     </row>
     <row r="49" spans="2:5">
-      <c r="B49" s="71" t="s">
-        <v>283</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E49" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B49" s="71"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="73"/>
     </row>
     <row r="50" spans="2:5">
-      <c r="B50" s="71" t="s">
-        <v>283</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E50" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B50" s="71"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="73"/>
     </row>
     <row r="51" spans="2:5">
-      <c r="B51" s="71" t="s">
-        <v>283</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E51" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B51" s="71"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="73"/>
     </row>
     <row r="52" spans="2:5">
-      <c r="B52" s="71" t="s">
-        <v>284</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="D52" s="75" t="s">
-        <v>23</v>
-      </c>
-      <c r="E52" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B52" s="71"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="75"/>
+      <c r="E52" s="73"/>
     </row>
     <row r="53" spans="2:5">
-      <c r="B53" s="71" t="s">
-        <v>284</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="D53" s="75" t="s">
-        <v>24</v>
-      </c>
-      <c r="E53" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B53" s="71"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="75"/>
+      <c r="E53" s="73"/>
     </row>
     <row r="54" spans="2:5">
-      <c r="B54" s="71" t="s">
-        <v>284</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D54" s="75" t="s">
-        <v>25</v>
-      </c>
-      <c r="E54" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B54" s="71"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="75"/>
+      <c r="E54" s="73"/>
     </row>
     <row r="55" spans="2:5">
-      <c r="B55" s="71" t="s">
-        <v>284</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="D55" s="75" t="s">
-        <v>26</v>
-      </c>
-      <c r="E55" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B55" s="71"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="75"/>
+      <c r="E55" s="73"/>
     </row>
     <row r="56" spans="2:5">
-      <c r="B56" s="71" t="s">
-        <v>284</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="D56" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="E56" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B56" s="71"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="75"/>
+      <c r="E56" s="73"/>
     </row>
     <row r="57" spans="2:5">
-      <c r="B57" s="71" t="s">
-        <v>284</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="D57" s="75" t="s">
-        <v>28</v>
-      </c>
-      <c r="E57" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B57" s="71"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="75"/>
+      <c r="E57" s="73"/>
     </row>
     <row r="58" spans="2:5">
-      <c r="B58" s="71" t="s">
-        <v>284</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D58" s="75" t="s">
-        <v>29</v>
-      </c>
-      <c r="E58" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B58" s="71"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="75"/>
+      <c r="E58" s="73"/>
     </row>
     <row r="59" spans="2:5">
-      <c r="B59" s="71" t="s">
-        <v>284</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="D59" s="75" t="s">
-        <v>30</v>
-      </c>
-      <c r="E59" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B59" s="71"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="75"/>
+      <c r="E59" s="73"/>
     </row>
     <row r="60" spans="2:5">
-      <c r="B60" s="71" t="s">
-        <v>284</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="D60" s="75" t="s">
-        <v>366</v>
-      </c>
-      <c r="E60" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B60" s="71"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="75"/>
+      <c r="E60" s="73"/>
     </row>
     <row r="61" spans="2:5">
-      <c r="B61" s="71" t="s">
-        <v>284</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="D61" s="75" t="s">
-        <v>32</v>
-      </c>
-      <c r="E61" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B61" s="71"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="75"/>
+      <c r="E61" s="73"/>
     </row>
     <row r="62" spans="2:5">
-      <c r="B62" s="71" t="s">
-        <v>284</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D62" s="75" t="s">
-        <v>33</v>
-      </c>
-      <c r="E62" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B62" s="71"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="75"/>
+      <c r="E62" s="73"/>
     </row>
     <row r="63" spans="2:5">
-      <c r="B63" s="71" t="s">
-        <v>284</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="D63" s="75" t="s">
-        <v>34</v>
-      </c>
-      <c r="E63" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B63" s="71"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="75"/>
+      <c r="E63" s="73"/>
     </row>
     <row r="64" spans="2:5">
-      <c r="B64" s="71" t="s">
-        <v>284</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D64" s="75" t="s">
-        <v>35</v>
-      </c>
-      <c r="E64" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B64" s="71"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="75"/>
+      <c r="E64" s="73"/>
     </row>
     <row r="65" spans="2:5">
-      <c r="B65" s="71" t="s">
-        <v>284</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D65" s="75" t="s">
-        <v>36</v>
-      </c>
-      <c r="E65" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B65" s="71"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="75"/>
+      <c r="E65" s="73"/>
     </row>
     <row r="66" spans="2:5">
-      <c r="B66" s="71" t="s">
-        <v>284</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="D66" s="75" t="s">
-        <v>37</v>
-      </c>
-      <c r="E66" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B66" s="71"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="75"/>
+      <c r="E66" s="73"/>
     </row>
     <row r="67" spans="2:5">
-      <c r="B67" s="71" t="s">
-        <v>284</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D67" s="75" t="s">
-        <v>38</v>
-      </c>
-      <c r="E67" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B67" s="71"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="75"/>
+      <c r="E67" s="73"/>
     </row>
     <row r="68" spans="2:5">
-      <c r="B68" s="71" t="s">
-        <v>285</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D68" s="75" t="s">
-        <v>23</v>
-      </c>
-      <c r="E68" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B68" s="71"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="75"/>
+      <c r="E68" s="73"/>
     </row>
     <row r="69" spans="2:5">
-      <c r="B69" s="71" t="s">
-        <v>285</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="D69" s="75" t="s">
-        <v>24</v>
-      </c>
-      <c r="E69" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B69" s="71"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="75"/>
+      <c r="E69" s="73"/>
     </row>
     <row r="70" spans="2:5">
-      <c r="B70" s="71" t="s">
-        <v>285</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="D70" s="75" t="s">
-        <v>25</v>
-      </c>
-      <c r="E70" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B70" s="71"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="75"/>
+      <c r="E70" s="73"/>
     </row>
     <row r="71" spans="2:5">
-      <c r="B71" s="71" t="s">
-        <v>285</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="D71" s="75" t="s">
-        <v>26</v>
-      </c>
-      <c r="E71" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B71" s="71"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="75"/>
+      <c r="E71" s="73"/>
     </row>
     <row r="72" spans="2:5">
-      <c r="B72" s="71" t="s">
-        <v>285</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D72" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="E72" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B72" s="71"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="75"/>
+      <c r="E72" s="73"/>
     </row>
     <row r="73" spans="2:5">
-      <c r="B73" s="71" t="s">
-        <v>285</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="D73" s="75" t="s">
-        <v>28</v>
-      </c>
-      <c r="E73" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B73" s="71"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="75"/>
+      <c r="E73" s="73"/>
     </row>
     <row r="74" spans="2:5">
-      <c r="B74" s="71" t="s">
-        <v>285</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D74" s="75" t="s">
-        <v>29</v>
-      </c>
-      <c r="E74" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B74" s="71"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="75"/>
+      <c r="E74" s="73"/>
     </row>
     <row r="75" spans="2:5">
-      <c r="B75" s="71" t="s">
-        <v>285</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D75" s="75" t="s">
-        <v>30</v>
-      </c>
-      <c r="E75" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B75" s="71"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="75"/>
+      <c r="E75" s="73"/>
     </row>
     <row r="76" spans="2:5">
-      <c r="B76" s="71" t="s">
-        <v>285</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D76" s="75" t="s">
-        <v>366</v>
-      </c>
-      <c r="E76" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B76" s="71"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="75"/>
+      <c r="E76" s="73"/>
     </row>
     <row r="77" spans="2:5">
-      <c r="B77" s="71" t="s">
-        <v>285</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D77" s="75" t="s">
-        <v>32</v>
-      </c>
-      <c r="E77" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B77" s="71"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="75"/>
+      <c r="E77" s="73"/>
     </row>
     <row r="78" spans="2:5">
-      <c r="B78" s="71" t="s">
-        <v>285</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D78" s="75" t="s">
-        <v>33</v>
-      </c>
-      <c r="E78" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B78" s="71"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="75"/>
+      <c r="E78" s="73"/>
     </row>
     <row r="79" spans="2:5">
-      <c r="B79" s="71" t="s">
-        <v>285</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D79" s="75" t="s">
-        <v>34</v>
-      </c>
-      <c r="E79" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B79" s="71"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="75"/>
+      <c r="E79" s="73"/>
     </row>
     <row r="80" spans="2:5">
-      <c r="B80" s="71" t="s">
-        <v>285</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D80" s="75" t="s">
-        <v>35</v>
-      </c>
-      <c r="E80" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B80" s="71"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="75"/>
+      <c r="E80" s="73"/>
     </row>
     <row r="81" spans="2:5">
-      <c r="B81" s="71" t="s">
-        <v>285</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D81" s="75" t="s">
-        <v>36</v>
-      </c>
-      <c r="E81" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B81" s="71"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="75"/>
+      <c r="E81" s="73"/>
     </row>
     <row r="82" spans="2:5">
-      <c r="B82" s="71" t="s">
-        <v>285</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="D82" s="75" t="s">
-        <v>37</v>
-      </c>
-      <c r="E82" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B82" s="71"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="75"/>
+      <c r="E82" s="73"/>
     </row>
     <row r="83" spans="2:5">
-      <c r="B83" s="71" t="s">
-        <v>285</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D83" s="75" t="s">
-        <v>38</v>
-      </c>
-      <c r="E83" s="73" t="s">
-        <v>13</v>
-      </c>
+      <c r="B83" s="71"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="75"/>
+      <c r="E83" s="73"/>
     </row>
   </sheetData>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -48618,617 +45108,277 @@
     <row r="11" spans="1:16" ht="18.75">
       <c r="A11" s="242"/>
       <c r="B11" s="247"/>
-      <c r="C11" s="65" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="345">
-        <v>1</v>
-      </c>
-      <c r="E11" s="345">
-        <v>1</v>
-      </c>
-      <c r="F11" s="345">
-        <v>1</v>
-      </c>
-      <c r="G11" s="346">
-        <v>1</v>
-      </c>
-      <c r="I11" s="575" t="s">
-        <v>23</v>
-      </c>
-      <c r="J11" s="345">
-        <v>1</v>
-      </c>
-      <c r="K11" s="345">
-        <v>1</v>
-      </c>
-      <c r="L11" s="345">
-        <v>1</v>
-      </c>
-      <c r="M11" s="346">
-        <v>1</v>
-      </c>
+      <c r="C11" s="65"/>
+      <c r="D11" s="345"/>
+      <c r="E11" s="345"/>
+      <c r="F11" s="345"/>
+      <c r="G11" s="346"/>
+      <c r="I11" s="575"/>
+      <c r="J11" s="345"/>
+      <c r="K11" s="345"/>
+      <c r="L11" s="345"/>
+      <c r="M11" s="346"/>
       <c r="O11" s="256"/>
     </row>
     <row r="12" spans="1:16" ht="18.75">
       <c r="A12" s="32"/>
       <c r="B12" s="247"/>
-      <c r="C12" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="347">
-        <v>1</v>
-      </c>
-      <c r="E12" s="347">
-        <v>1</v>
-      </c>
-      <c r="F12" s="347">
-        <v>1</v>
-      </c>
-      <c r="G12" s="348">
-        <v>1</v>
-      </c>
-      <c r="I12" s="576" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="347">
-        <v>0.93</v>
-      </c>
-      <c r="K12" s="347">
-        <v>1</v>
-      </c>
-      <c r="L12" s="347">
-        <v>1</v>
-      </c>
-      <c r="M12" s="348">
-        <v>0.8</v>
-      </c>
+      <c r="C12" s="34"/>
+      <c r="D12" s="347"/>
+      <c r="E12" s="347"/>
+      <c r="F12" s="347"/>
+      <c r="G12" s="348"/>
+      <c r="I12" s="576"/>
+      <c r="J12" s="347"/>
+      <c r="K12" s="347"/>
+      <c r="L12" s="347"/>
+      <c r="M12" s="348"/>
       <c r="N12" s="257"/>
       <c r="O12" s="248"/>
     </row>
     <row r="13" spans="1:16" ht="18.75">
       <c r="A13" s="32"/>
       <c r="B13" s="247"/>
-      <c r="C13" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="347">
-        <v>1</v>
-      </c>
-      <c r="E13" s="347">
-        <v>1</v>
-      </c>
-      <c r="F13" s="347">
-        <v>1</v>
-      </c>
-      <c r="G13" s="348">
-        <v>1</v>
-      </c>
-      <c r="I13" s="576" t="s">
-        <v>25</v>
-      </c>
-      <c r="J13" s="347">
-        <v>0.93</v>
-      </c>
-      <c r="K13" s="347">
-        <v>1</v>
-      </c>
-      <c r="L13" s="347">
-        <v>1</v>
-      </c>
-      <c r="M13" s="348">
-        <v>0.8</v>
-      </c>
+      <c r="C13" s="34"/>
+      <c r="D13" s="347"/>
+      <c r="E13" s="347"/>
+      <c r="F13" s="347"/>
+      <c r="G13" s="348"/>
+      <c r="I13" s="576"/>
+      <c r="J13" s="347"/>
+      <c r="K13" s="347"/>
+      <c r="L13" s="347"/>
+      <c r="M13" s="348"/>
       <c r="N13" s="257"/>
       <c r="O13" s="248"/>
     </row>
     <row r="14" spans="1:16" ht="18.75">
       <c r="A14" s="243"/>
       <c r="B14" s="247"/>
-      <c r="C14" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="347">
-        <v>0.75</v>
-      </c>
-      <c r="E14" s="347">
-        <v>0.75</v>
-      </c>
-      <c r="F14" s="347">
-        <v>0.75</v>
-      </c>
-      <c r="G14" s="348">
-        <v>0.75</v>
-      </c>
-      <c r="I14" s="576" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="347">
-        <v>1</v>
-      </c>
-      <c r="K14" s="347">
-        <v>1</v>
-      </c>
-      <c r="L14" s="347">
-        <v>1</v>
-      </c>
-      <c r="M14" s="348">
-        <v>1</v>
-      </c>
+      <c r="C14" s="34"/>
+      <c r="D14" s="347"/>
+      <c r="E14" s="347"/>
+      <c r="F14" s="347"/>
+      <c r="G14" s="348"/>
+      <c r="I14" s="576"/>
+      <c r="J14" s="347"/>
+      <c r="K14" s="347"/>
+      <c r="L14" s="347"/>
+      <c r="M14" s="348"/>
       <c r="N14" s="257"/>
       <c r="O14" s="248"/>
     </row>
     <row r="15" spans="1:16" ht="18.75">
       <c r="A15" s="32"/>
       <c r="B15" s="247"/>
-      <c r="C15" s="57" t="s">
-        <v>367</v>
-      </c>
-      <c r="D15" s="347">
-        <v>1</v>
-      </c>
-      <c r="E15" s="347">
-        <v>1</v>
-      </c>
-      <c r="F15" s="347">
-        <v>1</v>
-      </c>
-      <c r="G15" s="348">
-        <v>1</v>
-      </c>
-      <c r="I15" s="576" t="s">
-        <v>27</v>
-      </c>
-      <c r="J15" s="347">
-        <v>0.93</v>
-      </c>
-      <c r="K15" s="347">
-        <v>1</v>
-      </c>
-      <c r="L15" s="347">
-        <v>0.8</v>
-      </c>
-      <c r="M15" s="348">
-        <v>1</v>
-      </c>
+      <c r="C15" s="57"/>
+      <c r="D15" s="347"/>
+      <c r="E15" s="347"/>
+      <c r="F15" s="347"/>
+      <c r="G15" s="348"/>
+      <c r="I15" s="576"/>
+      <c r="J15" s="347"/>
+      <c r="K15" s="347"/>
+      <c r="L15" s="347"/>
+      <c r="M15" s="348"/>
       <c r="N15" s="257"/>
       <c r="O15" s="248"/>
     </row>
     <row r="16" spans="1:16" ht="18.75">
       <c r="A16" s="32"/>
       <c r="B16" s="247"/>
-      <c r="C16" s="57" t="s">
-        <v>368</v>
-      </c>
-      <c r="D16" s="347">
-        <v>1</v>
-      </c>
-      <c r="E16" s="347">
-        <v>1</v>
-      </c>
-      <c r="F16" s="347">
-        <v>1</v>
-      </c>
-      <c r="G16" s="348">
-        <v>1</v>
-      </c>
-      <c r="I16" s="576" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" s="347">
-        <v>0.73</v>
-      </c>
-      <c r="K16" s="347">
-        <v>1</v>
-      </c>
-      <c r="L16" s="347">
-        <v>0.6</v>
-      </c>
-      <c r="M16" s="348">
-        <v>0.6</v>
-      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="347"/>
+      <c r="E16" s="347"/>
+      <c r="F16" s="347"/>
+      <c r="G16" s="348"/>
+      <c r="I16" s="576"/>
+      <c r="J16" s="347"/>
+      <c r="K16" s="347"/>
+      <c r="L16" s="347"/>
+      <c r="M16" s="348"/>
       <c r="N16" s="257"/>
       <c r="O16" s="248"/>
     </row>
     <row r="17" spans="1:15" ht="18.75">
       <c r="A17" s="32"/>
       <c r="B17" s="247"/>
-      <c r="C17" s="57" t="s">
-        <v>369</v>
-      </c>
-      <c r="D17" s="347">
-        <v>1</v>
-      </c>
-      <c r="E17" s="347">
-        <v>1</v>
-      </c>
-      <c r="F17" s="347">
-        <v>1</v>
-      </c>
-      <c r="G17" s="348">
-        <v>1</v>
-      </c>
-      <c r="I17" s="576" t="s">
-        <v>29</v>
-      </c>
-      <c r="J17" s="347">
-        <v>0.73</v>
-      </c>
-      <c r="K17" s="347">
-        <v>1</v>
-      </c>
-      <c r="L17" s="347">
-        <v>0.6</v>
-      </c>
-      <c r="M17" s="348">
-        <v>0.6</v>
-      </c>
+      <c r="C17" s="57"/>
+      <c r="D17" s="347"/>
+      <c r="E17" s="347"/>
+      <c r="F17" s="347"/>
+      <c r="G17" s="348"/>
+      <c r="I17" s="576"/>
+      <c r="J17" s="347"/>
+      <c r="K17" s="347"/>
+      <c r="L17" s="347"/>
+      <c r="M17" s="348"/>
       <c r="N17" s="257"/>
       <c r="O17" s="248"/>
     </row>
     <row r="18" spans="1:15" ht="18.75">
       <c r="A18" s="32"/>
       <c r="B18" s="247"/>
-      <c r="C18" s="57" t="s">
-        <v>370</v>
-      </c>
-      <c r="D18" s="347">
-        <v>0</v>
-      </c>
-      <c r="E18" s="347">
-        <v>0</v>
-      </c>
-      <c r="F18" s="347">
-        <v>0</v>
-      </c>
-      <c r="G18" s="348">
-        <v>0</v>
-      </c>
-      <c r="I18" s="576" t="s">
-        <v>30</v>
-      </c>
-      <c r="J18" s="347">
-        <v>1</v>
-      </c>
-      <c r="K18" s="347">
-        <v>1</v>
-      </c>
-      <c r="L18" s="347">
-        <v>1</v>
-      </c>
-      <c r="M18" s="348">
-        <v>1</v>
-      </c>
+      <c r="C18" s="57"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
+      <c r="G18" s="348"/>
+      <c r="I18" s="576"/>
+      <c r="J18" s="347"/>
+      <c r="K18" s="347"/>
+      <c r="L18" s="347"/>
+      <c r="M18" s="348"/>
       <c r="N18" s="257"/>
       <c r="O18" s="248"/>
     </row>
     <row r="19" spans="1:15" ht="18.75">
       <c r="A19" s="32"/>
       <c r="B19" s="247"/>
-      <c r="C19" s="34" t="s">
-        <v>371</v>
-      </c>
-      <c r="D19" s="347">
-        <v>1</v>
-      </c>
-      <c r="E19" s="347">
-        <v>1</v>
-      </c>
-      <c r="F19" s="347">
-        <v>1</v>
-      </c>
-      <c r="G19" s="348">
-        <v>1</v>
-      </c>
-      <c r="I19" s="576" t="s">
-        <v>366</v>
-      </c>
-      <c r="J19" s="347">
-        <v>1</v>
-      </c>
-      <c r="K19" s="347">
-        <v>1</v>
-      </c>
-      <c r="L19" s="347">
-        <v>1</v>
-      </c>
-      <c r="M19" s="348">
-        <v>1</v>
-      </c>
+      <c r="C19" s="34"/>
+      <c r="D19" s="347"/>
+      <c r="E19" s="347"/>
+      <c r="F19" s="347"/>
+      <c r="G19" s="348"/>
+      <c r="I19" s="576"/>
+      <c r="J19" s="347"/>
+      <c r="K19" s="347"/>
+      <c r="L19" s="347"/>
+      <c r="M19" s="348"/>
       <c r="N19" s="257"/>
       <c r="O19" s="248"/>
     </row>
     <row r="20" spans="1:15" ht="18.75">
       <c r="A20" s="32"/>
       <c r="B20" s="247"/>
-      <c r="C20" s="34" t="s">
-        <v>372</v>
-      </c>
-      <c r="D20" s="347">
-        <v>1</v>
-      </c>
-      <c r="E20" s="347">
-        <v>1</v>
-      </c>
-      <c r="F20" s="347">
-        <v>1</v>
-      </c>
-      <c r="G20" s="348">
-        <v>1</v>
-      </c>
-      <c r="I20" s="576" t="s">
-        <v>32</v>
-      </c>
-      <c r="J20" s="347">
-        <v>0.87</v>
-      </c>
-      <c r="K20" s="347">
-        <v>1</v>
-      </c>
-      <c r="L20" s="347">
-        <v>0.8</v>
-      </c>
-      <c r="M20" s="348">
-        <v>0.8</v>
-      </c>
+      <c r="C20" s="34"/>
+      <c r="D20" s="347"/>
+      <c r="E20" s="347"/>
+      <c r="F20" s="347"/>
+      <c r="G20" s="348"/>
+      <c r="I20" s="576"/>
+      <c r="J20" s="347"/>
+      <c r="K20" s="347"/>
+      <c r="L20" s="347"/>
+      <c r="M20" s="348"/>
       <c r="N20" s="257"/>
       <c r="O20" s="248"/>
     </row>
     <row r="21" spans="1:15" ht="18.75">
       <c r="A21" s="32"/>
       <c r="B21" s="247"/>
-      <c r="C21" s="33" t="s">
-        <v>373</v>
-      </c>
-      <c r="D21" s="347">
-        <v>1</v>
-      </c>
-      <c r="E21" s="347">
-        <v>1</v>
-      </c>
-      <c r="F21" s="347">
-        <v>1</v>
-      </c>
-      <c r="G21" s="348">
-        <v>1</v>
-      </c>
-      <c r="I21" s="576" t="s">
-        <v>33</v>
-      </c>
-      <c r="J21" s="347">
-        <v>1</v>
-      </c>
-      <c r="K21" s="347">
-        <v>1</v>
-      </c>
-      <c r="L21" s="347">
-        <v>1</v>
-      </c>
-      <c r="M21" s="348">
-        <v>1</v>
-      </c>
+      <c r="C21" s="33"/>
+      <c r="D21" s="347"/>
+      <c r="E21" s="347"/>
+      <c r="F21" s="347"/>
+      <c r="G21" s="348"/>
+      <c r="I21" s="576"/>
+      <c r="J21" s="347"/>
+      <c r="K21" s="347"/>
+      <c r="L21" s="347"/>
+      <c r="M21" s="348"/>
       <c r="N21" s="257"/>
       <c r="O21" s="248"/>
     </row>
     <row r="22" spans="1:15" ht="18.75">
       <c r="A22" s="32"/>
       <c r="B22" s="247"/>
-      <c r="C22" s="33" t="s">
-        <v>374</v>
-      </c>
-      <c r="D22" s="347">
-        <v>1</v>
-      </c>
-      <c r="E22" s="347">
-        <v>1</v>
-      </c>
-      <c r="F22" s="347">
-        <v>1</v>
-      </c>
-      <c r="G22" s="348">
-        <v>1</v>
-      </c>
-      <c r="I22" s="576" t="s">
-        <v>34</v>
-      </c>
-      <c r="J22" s="347">
-        <v>1</v>
-      </c>
-      <c r="K22" s="347">
-        <v>1</v>
-      </c>
-      <c r="L22" s="347">
-        <v>1</v>
-      </c>
-      <c r="M22" s="348">
-        <v>1</v>
-      </c>
+      <c r="C22" s="33"/>
+      <c r="D22" s="347"/>
+      <c r="E22" s="347"/>
+      <c r="F22" s="347"/>
+      <c r="G22" s="348"/>
+      <c r="I22" s="576"/>
+      <c r="J22" s="347"/>
+      <c r="K22" s="347"/>
+      <c r="L22" s="347"/>
+      <c r="M22" s="348"/>
       <c r="N22" s="257"/>
       <c r="O22" s="248"/>
     </row>
     <row r="23" spans="1:15" ht="18.75">
       <c r="A23" s="32"/>
       <c r="B23" s="247"/>
-      <c r="C23" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="D23" s="347">
-        <v>0.83</v>
-      </c>
-      <c r="E23" s="347">
-        <v>0.75</v>
-      </c>
-      <c r="F23" s="347">
-        <v>1</v>
-      </c>
-      <c r="G23" s="348">
-        <v>0.75</v>
-      </c>
-      <c r="I23" s="576" t="s">
-        <v>35</v>
-      </c>
-      <c r="J23" s="347">
-        <v>1</v>
-      </c>
-      <c r="K23" s="347">
-        <v>1</v>
-      </c>
-      <c r="L23" s="347">
-        <v>1</v>
-      </c>
-      <c r="M23" s="348">
-        <v>1</v>
-      </c>
+      <c r="C23" s="34"/>
+      <c r="D23" s="347"/>
+      <c r="E23" s="347"/>
+      <c r="F23" s="347"/>
+      <c r="G23" s="348"/>
+      <c r="I23" s="576"/>
+      <c r="J23" s="347"/>
+      <c r="K23" s="347"/>
+      <c r="L23" s="347"/>
+      <c r="M23" s="348"/>
       <c r="N23" s="257"/>
       <c r="O23" s="248"/>
     </row>
     <row r="24" spans="1:15" ht="18.75">
       <c r="A24" s="32"/>
       <c r="B24" s="247"/>
-      <c r="C24" s="33" t="s">
-        <v>375</v>
-      </c>
-      <c r="D24" s="347">
-        <v>1</v>
-      </c>
-      <c r="E24" s="347">
-        <v>1</v>
-      </c>
-      <c r="F24" s="347">
-        <v>1</v>
-      </c>
-      <c r="G24" s="348">
-        <v>1</v>
-      </c>
-      <c r="I24" s="576" t="s">
-        <v>36</v>
-      </c>
-      <c r="J24" s="347">
-        <v>1</v>
-      </c>
-      <c r="K24" s="347">
-        <v>1</v>
-      </c>
-      <c r="L24" s="347">
-        <v>1</v>
-      </c>
-      <c r="M24" s="348">
-        <v>1</v>
-      </c>
+      <c r="C24" s="33"/>
+      <c r="D24" s="347"/>
+      <c r="E24" s="347"/>
+      <c r="F24" s="347"/>
+      <c r="G24" s="348"/>
+      <c r="I24" s="576"/>
+      <c r="J24" s="347"/>
+      <c r="K24" s="347"/>
+      <c r="L24" s="347"/>
+      <c r="M24" s="348"/>
       <c r="N24" s="257"/>
       <c r="O24" s="248"/>
     </row>
     <row r="25" spans="1:15" ht="18.75">
       <c r="A25" s="32"/>
       <c r="B25" s="247"/>
-      <c r="C25" s="33" t="s">
-        <v>191</v>
-      </c>
-      <c r="D25" s="347">
-        <v>1</v>
-      </c>
-      <c r="E25" s="347">
-        <v>1</v>
-      </c>
-      <c r="F25" s="347">
-        <v>1</v>
-      </c>
-      <c r="G25" s="348">
-        <v>1</v>
-      </c>
-      <c r="I25" s="576" t="s">
-        <v>37</v>
-      </c>
-      <c r="J25" s="347">
-        <v>0.87</v>
-      </c>
-      <c r="K25" s="347">
-        <v>1</v>
-      </c>
-      <c r="L25" s="347">
-        <v>0.6</v>
-      </c>
-      <c r="M25" s="348">
-        <v>1</v>
-      </c>
+      <c r="C25" s="33"/>
+      <c r="D25" s="347"/>
+      <c r="E25" s="347"/>
+      <c r="F25" s="347"/>
+      <c r="G25" s="348"/>
+      <c r="I25" s="576"/>
+      <c r="J25" s="347"/>
+      <c r="K25" s="347"/>
+      <c r="L25" s="347"/>
+      <c r="M25" s="348"/>
       <c r="N25" s="257"/>
       <c r="O25" s="248"/>
     </row>
     <row r="26" spans="1:15" ht="19.5" thickBot="1">
       <c r="A26" s="32"/>
       <c r="B26" s="247"/>
-      <c r="C26" s="33" t="s">
-        <v>376</v>
-      </c>
-      <c r="D26" s="347">
-        <v>1</v>
-      </c>
-      <c r="E26" s="347">
-        <v>1</v>
-      </c>
-      <c r="F26" s="347">
-        <v>1</v>
-      </c>
-      <c r="G26" s="348">
-        <v>1</v>
-      </c>
-      <c r="I26" s="577" t="s">
-        <v>38</v>
-      </c>
-      <c r="J26" s="349">
-        <v>0.83</v>
-      </c>
-      <c r="K26" s="349">
-        <v>1</v>
-      </c>
-      <c r="L26" s="349">
-        <v>0.5</v>
-      </c>
-      <c r="M26" s="350">
-        <v>1</v>
-      </c>
+      <c r="C26" s="33"/>
+      <c r="D26" s="347"/>
+      <c r="E26" s="347"/>
+      <c r="F26" s="347"/>
+      <c r="G26" s="348"/>
+      <c r="I26" s="577"/>
+      <c r="J26" s="349"/>
+      <c r="K26" s="349"/>
+      <c r="L26" s="349"/>
+      <c r="M26" s="350"/>
       <c r="N26" s="257"/>
       <c r="O26" s="248"/>
     </row>
     <row r="27" spans="1:15" ht="23.25" customHeight="1">
       <c r="A27" s="32"/>
       <c r="B27" s="247"/>
-      <c r="C27" s="33" t="s">
-        <v>377</v>
-      </c>
-      <c r="D27" s="347">
-        <v>0.33</v>
-      </c>
-      <c r="E27" s="347">
-        <v>0</v>
-      </c>
-      <c r="F27" s="347">
-        <v>1</v>
-      </c>
-      <c r="G27" s="348">
-        <v>0</v>
-      </c>
+      <c r="C27" s="33"/>
+      <c r="D27" s="347"/>
+      <c r="E27" s="347"/>
+      <c r="F27" s="347"/>
+      <c r="G27" s="348"/>
       <c r="N27" s="257"/>
       <c r="O27" s="248"/>
     </row>
     <row r="28" spans="1:15" ht="23.25" customHeight="1" thickBot="1">
       <c r="A28" s="32"/>
       <c r="B28" s="247"/>
-      <c r="C28" s="306" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="349">
-        <v>1</v>
-      </c>
-      <c r="E28" s="349">
-        <v>1</v>
-      </c>
-      <c r="F28" s="349">
-        <v>1</v>
-      </c>
-      <c r="G28" s="350">
-        <v>1</v>
-      </c>
+      <c r="C28" s="306"/>
+      <c r="D28" s="349"/>
+      <c r="E28" s="349"/>
+      <c r="F28" s="349"/>
+      <c r="G28" s="350"/>
       <c r="I28" s="574"/>
       <c r="J28" s="574"/>
       <c r="N28" s="257"/>
@@ -49408,7 +45558,7 @@
     </row>
     <row r="2" spans="1:17" ht="36">
       <c r="B2" s="120" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C2" s="120"/>
       <c r="D2" s="82"/>
@@ -49416,7 +45566,7 @@
       <c r="G2" s="90"/>
       <c r="H2" s="82"/>
       <c r="I2" s="651" t="s">
-        <v>392</v>
+        <v>165</v>
       </c>
       <c r="J2" s="652"/>
       <c r="K2" s="93"/>
@@ -49430,7 +45580,7 @@
     <row r="3" spans="1:17" s="59" customFormat="1" ht="22.5" customHeight="1">
       <c r="A3" s="85"/>
       <c r="B3" s="59" t="s">
-        <v>393</v>
+        <v>166</v>
       </c>
       <c r="D3" s="91"/>
       <c r="E3" s="84"/>
@@ -49472,7 +45622,7 @@
         <v>58</v>
       </c>
       <c r="C5" s="658" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D5" s="659"/>
       <c r="E5" s="375" t="s">
@@ -49501,31 +45651,15 @@
       <c r="P5" s="104"/>
     </row>
     <row r="6" spans="1:17" ht="51" customHeight="1">
-      <c r="B6" s="215" t="s">
-        <v>378</v>
-      </c>
-      <c r="C6" s="660">
-        <v>44725</v>
-      </c>
+      <c r="B6" s="215"/>
+      <c r="C6" s="660"/>
       <c r="D6" s="661"/>
-      <c r="E6" s="459">
-        <v>44908</v>
-      </c>
-      <c r="F6" s="459">
-        <v>45090</v>
-      </c>
-      <c r="G6" s="459">
-        <v>45273</v>
-      </c>
-      <c r="H6" s="459">
-        <v>45456</v>
-      </c>
-      <c r="I6" s="459">
-        <v>45639</v>
-      </c>
-      <c r="J6" s="462">
-        <v>45821</v>
-      </c>
+      <c r="E6" s="459"/>
+      <c r="F6" s="459"/>
+      <c r="G6" s="459"/>
+      <c r="H6" s="459"/>
+      <c r="I6" s="459"/>
+      <c r="J6" s="462"/>
       <c r="K6" s="116"/>
       <c r="L6" s="82"/>
       <c r="M6" s="82"/>
@@ -49536,31 +45670,15 @@
     </row>
     <row r="7" spans="1:17" ht="45.75" customHeight="1">
       <c r="A7" s="99"/>
-      <c r="B7" s="216" t="s">
-        <v>379</v>
-      </c>
-      <c r="C7" s="662">
-        <v>37484</v>
-      </c>
+      <c r="B7" s="216"/>
+      <c r="C7" s="662"/>
       <c r="D7" s="663"/>
-      <c r="E7" s="460">
-        <v>44608</v>
-      </c>
-      <c r="F7" s="460">
-        <v>45154</v>
-      </c>
-      <c r="G7" s="460">
-        <v>45338</v>
-      </c>
-      <c r="H7" s="460">
-        <v>45520</v>
-      </c>
-      <c r="I7" s="460">
-        <v>45704</v>
-      </c>
-      <c r="J7" s="463">
-        <v>45885</v>
-      </c>
+      <c r="E7" s="460"/>
+      <c r="F7" s="460"/>
+      <c r="G7" s="460"/>
+      <c r="H7" s="460"/>
+      <c r="I7" s="460"/>
+      <c r="J7" s="463"/>
       <c r="L7" s="82"/>
       <c r="M7" s="82"/>
       <c r="N7" s="82"/>
@@ -49569,31 +45687,15 @@
     </row>
     <row r="8" spans="1:17" ht="44.25" customHeight="1">
       <c r="A8" s="100"/>
-      <c r="B8" s="216" t="s">
-        <v>380</v>
-      </c>
-      <c r="C8" s="662">
-        <v>44868</v>
-      </c>
+      <c r="B8" s="216"/>
+      <c r="C8" s="662"/>
       <c r="D8" s="663"/>
-      <c r="E8" s="460">
-        <v>45049</v>
-      </c>
-      <c r="F8" s="460">
-        <v>45233</v>
-      </c>
-      <c r="G8" s="460">
-        <v>45415</v>
-      </c>
-      <c r="H8" s="460">
-        <v>45599</v>
-      </c>
-      <c r="I8" s="460">
-        <v>45780</v>
-      </c>
-      <c r="J8" s="463">
-        <v>45964</v>
-      </c>
+      <c r="E8" s="460"/>
+      <c r="F8" s="460"/>
+      <c r="G8" s="460"/>
+      <c r="H8" s="460"/>
+      <c r="I8" s="460"/>
+      <c r="J8" s="463"/>
       <c r="K8" s="206"/>
       <c r="L8" s="82"/>
       <c r="M8" s="82"/>
@@ -49603,31 +45705,15 @@
     </row>
     <row r="9" spans="1:17" ht="39.75" customHeight="1">
       <c r="A9" s="100"/>
-      <c r="B9" s="216" t="s">
-        <v>381</v>
-      </c>
-      <c r="C9" s="662">
-        <v>45439</v>
-      </c>
+      <c r="B9" s="216"/>
+      <c r="C9" s="662"/>
       <c r="D9" s="663"/>
-      <c r="E9" s="460">
-        <v>45623</v>
-      </c>
-      <c r="F9" s="460">
-        <v>45804</v>
-      </c>
-      <c r="G9" s="460">
-        <v>45988</v>
-      </c>
-      <c r="H9" s="460">
-        <v>46169</v>
-      </c>
-      <c r="I9" s="460">
-        <v>46353</v>
-      </c>
-      <c r="J9" s="463">
-        <v>46534</v>
-      </c>
+      <c r="E9" s="460"/>
+      <c r="F9" s="460"/>
+      <c r="G9" s="460"/>
+      <c r="H9" s="460"/>
+      <c r="I9" s="460"/>
+      <c r="J9" s="463"/>
       <c r="K9" s="152"/>
       <c r="L9" s="82"/>
       <c r="M9" s="82"/>
@@ -49638,31 +45724,15 @@
     </row>
     <row r="10" spans="1:17" ht="55.5" customHeight="1">
       <c r="A10" s="102"/>
-      <c r="B10" s="216" t="s">
-        <v>382</v>
-      </c>
-      <c r="C10" s="662">
-        <v>45017</v>
-      </c>
+      <c r="B10" s="216"/>
+      <c r="C10" s="662"/>
       <c r="D10" s="663"/>
-      <c r="E10" s="460">
-        <v>45200</v>
-      </c>
-      <c r="F10" s="460">
-        <v>45383</v>
-      </c>
-      <c r="G10" s="460">
-        <v>45566</v>
-      </c>
-      <c r="H10" s="460">
-        <v>45748</v>
-      </c>
-      <c r="I10" s="460">
-        <v>45931</v>
-      </c>
-      <c r="J10" s="463">
-        <v>46113</v>
-      </c>
+      <c r="E10" s="460"/>
+      <c r="F10" s="460"/>
+      <c r="G10" s="460"/>
+      <c r="H10" s="460"/>
+      <c r="I10" s="460"/>
+      <c r="J10" s="463"/>
       <c r="K10" s="116"/>
       <c r="L10" s="82"/>
       <c r="M10" s="82"/>
@@ -49672,31 +45742,15 @@
     </row>
     <row r="11" spans="1:17" ht="44.25" customHeight="1">
       <c r="A11" s="101"/>
-      <c r="B11" s="216" t="s">
-        <v>383</v>
-      </c>
-      <c r="C11" s="662">
-        <v>44930</v>
-      </c>
+      <c r="B11" s="216"/>
+      <c r="C11" s="662"/>
       <c r="D11" s="663"/>
-      <c r="E11" s="460">
-        <v>45111</v>
-      </c>
-      <c r="F11" s="460">
-        <v>45295</v>
-      </c>
-      <c r="G11" s="460">
-        <v>45477</v>
-      </c>
-      <c r="H11" s="460">
-        <v>45661</v>
-      </c>
-      <c r="I11" s="460">
-        <v>45842</v>
-      </c>
-      <c r="J11" s="463">
-        <v>46026</v>
-      </c>
+      <c r="E11" s="460"/>
+      <c r="F11" s="460"/>
+      <c r="G11" s="460"/>
+      <c r="H11" s="460"/>
+      <c r="I11" s="460"/>
+      <c r="J11" s="463"/>
       <c r="L11" s="82"/>
       <c r="M11" s="90"/>
       <c r="N11" s="82"/>
@@ -49706,31 +45760,15 @@
     </row>
     <row r="12" spans="1:17" ht="66.75" customHeight="1" thickBot="1">
       <c r="A12" s="100"/>
-      <c r="B12" s="217" t="s">
-        <v>384</v>
-      </c>
-      <c r="C12" s="653">
-        <v>44958</v>
-      </c>
+      <c r="B12" s="217"/>
+      <c r="C12" s="653"/>
       <c r="D12" s="654"/>
-      <c r="E12" s="461">
-        <v>45139</v>
-      </c>
-      <c r="F12" s="461">
-        <v>45323</v>
-      </c>
-      <c r="G12" s="461">
-        <v>45505</v>
-      </c>
-      <c r="H12" s="461">
-        <v>45689</v>
-      </c>
-      <c r="I12" s="461">
-        <v>45870</v>
-      </c>
-      <c r="J12" s="464">
-        <v>46054</v>
-      </c>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
+      <c r="G12" s="461"/>
+      <c r="H12" s="461"/>
+      <c r="I12" s="461"/>
+      <c r="J12" s="464"/>
       <c r="K12" s="206"/>
       <c r="L12" s="82"/>
       <c r="M12" s="82"/>
@@ -49800,12 +45838,8 @@
         <v>145</v>
       </c>
       <c r="C16" s="483"/>
-      <c r="D16" s="294" t="s">
-        <v>378</v>
-      </c>
-      <c r="E16" s="648" t="s">
-        <v>385</v>
-      </c>
+      <c r="D16" s="294"/>
+      <c r="E16" s="648"/>
       <c r="F16" s="649"/>
       <c r="G16" s="649"/>
       <c r="H16" s="649"/>
@@ -49823,12 +45857,8 @@
         <v>65</v>
       </c>
       <c r="C17" s="485"/>
-      <c r="D17" s="294" t="s">
-        <v>379</v>
-      </c>
-      <c r="E17" s="648" t="s">
-        <v>386</v>
-      </c>
+      <c r="D17" s="294"/>
+      <c r="E17" s="648"/>
       <c r="F17" s="649"/>
       <c r="G17" s="649"/>
       <c r="H17" s="649"/>
@@ -49847,12 +45877,8 @@
         <v>66</v>
       </c>
       <c r="C18" s="485"/>
-      <c r="D18" s="295" t="s">
-        <v>380</v>
-      </c>
-      <c r="E18" s="648" t="s">
-        <v>387</v>
-      </c>
+      <c r="D18" s="295"/>
+      <c r="E18" s="648"/>
       <c r="F18" s="649"/>
       <c r="G18" s="649"/>
       <c r="H18" s="649"/>
@@ -49868,12 +45894,8 @@
       <c r="A19" s="82"/>
       <c r="B19" s="87"/>
       <c r="C19" s="87"/>
-      <c r="D19" s="296" t="s">
-        <v>381</v>
-      </c>
-      <c r="E19" s="648" t="s">
-        <v>388</v>
-      </c>
+      <c r="D19" s="296"/>
+      <c r="E19" s="648"/>
       <c r="F19" s="649"/>
       <c r="G19" s="649"/>
       <c r="H19" s="649"/>
@@ -49889,12 +45911,8 @@
     <row r="20" spans="1:16" ht="108" customHeight="1" thickBot="1">
       <c r="A20" s="79"/>
       <c r="B20" s="90"/>
-      <c r="D20" s="295" t="s">
-        <v>382</v>
-      </c>
-      <c r="E20" s="648" t="s">
-        <v>389</v>
-      </c>
+      <c r="D20" s="295"/>
+      <c r="E20" s="648"/>
       <c r="F20" s="649"/>
       <c r="G20" s="649"/>
       <c r="H20" s="649"/>
@@ -49909,12 +45927,8 @@
     <row r="21" spans="1:16" s="226" customFormat="1" ht="81.75" customHeight="1" thickBot="1">
       <c r="B21" s="227"/>
       <c r="C21" s="228"/>
-      <c r="D21" s="298" t="s">
-        <v>383</v>
-      </c>
-      <c r="E21" s="648" t="s">
-        <v>390</v>
-      </c>
+      <c r="D21" s="298"/>
+      <c r="E21" s="648"/>
       <c r="F21" s="649"/>
       <c r="G21" s="649"/>
       <c r="H21" s="649"/>
@@ -49930,12 +45944,8 @@
       <c r="A22" s="83"/>
       <c r="B22" s="106"/>
       <c r="C22" s="87"/>
-      <c r="D22" s="305" t="s">
-        <v>384</v>
-      </c>
-      <c r="E22" s="648" t="s">
-        <v>391</v>
-      </c>
+      <c r="D22" s="305"/>
+      <c r="E22" s="648"/>
       <c r="F22" s="649"/>
       <c r="G22" s="649"/>
       <c r="H22" s="649"/>

--- a/Backend/output/informe_final.xlsx
+++ b/Backend/output/informe_final.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E49289CB-97DE-4E6F-953E-91796A052946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B7A293D-A636-4E73-8F47-52C20065CF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="719" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13960,7 +13960,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E0EDC16B-B33A-4819-A1E5-8085C57B4A85}" type="CELLRANGE">
+                    <a:fld id="{F4C8493B-D265-497E-BB27-ACE19CA0B718}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13994,7 +13994,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{ACCF0333-BA45-43DE-BC85-7CE6FCE16207}" type="CELLRANGE">
+                    <a:fld id="{3C44E438-0C1B-4694-B2FA-B21309D53CD9}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14028,7 +14028,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{60EA9538-0E03-4E09-B3AB-DB3704A72498}" type="CELLRANGE">
+                    <a:fld id="{18145A7C-3543-430A-8CE8-49A8D5F19703}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14062,7 +14062,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F0B94245-2459-4CBF-A194-0D7AC9829BA5}" type="CELLRANGE">
+                    <a:fld id="{1F69AF2A-E6E2-4737-A5B9-0C537E3012D2}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14108,7 +14108,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{8D032169-9674-4F93-A70F-C63FF9575E39}" type="CELLRANGE">
+                    <a:fld id="{BA6B5383-5236-438B-B75C-09F30FAC5566}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr>
                         <a:defRPr sz="1400">
@@ -14201,7 +14201,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{E11B26A9-F28D-4F5C-847B-4AD03411BD4B}" type="CELLRANGE">
+                    <a:fld id="{406D18E1-D49E-49B0-BDC2-F5DEC5C25D3B}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr>
                         <a:defRPr sz="1400">
@@ -14294,7 +14294,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{5A9AE8B8-7DAE-4ACE-8714-D7F73DCCE476}" type="CELLRANGE">
+                    <a:fld id="{6B9CAAD9-0633-45E3-B8BD-19E9F71A36AD}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr>
                         <a:defRPr sz="1400">
@@ -14375,7 +14375,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E1AF6B6D-6C74-4353-A836-DA56FDE52297}" type="CELLRANGE">
+                    <a:fld id="{ACCF0283-D294-44B4-AC02-8CE588908A24}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14421,7 +14421,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{8DE1050F-6679-48BC-9C08-FDB8CDD80D7A}" type="CELLRANGE">
+                    <a:fld id="{E7A3F590-9074-400A-B35F-9C68764127E5}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr>
                         <a:defRPr sz="1400">
@@ -14514,7 +14514,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{19AA92C3-C618-4F6D-8369-169E0489903C}" type="CELLRANGE">
+                    <a:fld id="{D47A2140-2321-4D74-A3F0-72D1B3405838}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr>
                         <a:defRPr sz="1400">
@@ -14705,7 +14705,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{B96E770C-386E-4276-B0C9-5CC0BFEF6803}" type="CELLRANGE">
+                    <a:fld id="{4612769D-2E5D-44F6-AE28-DA639819A571}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr>
                         <a:defRPr sz="1400">
@@ -15263,7 +15263,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2F8F739D-12FD-4A95-8FB7-82BB6D67E361}" type="CELLRANGE">
+                    <a:fld id="{B0321A0A-EBAD-464D-90FA-2777D8A3405D}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15297,7 +15297,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{80270F3F-C83B-4B57-8C65-ACECAAF49B36}" type="CELLRANGE">
+                    <a:fld id="{120BE1BF-08BE-4356-ADA4-94F99DB8AE25}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15331,7 +15331,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{53A8FCAC-C03D-4F9A-B7F1-2F28B23302A7}" type="CELLRANGE">
+                    <a:fld id="{D39D4D92-0EA3-47C3-A62F-CEC949093CBB}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15365,7 +15365,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{13D0D107-518F-49D9-AF8A-E3D549AF464B}" type="CELLRANGE">
+                    <a:fld id="{42E9044F-4E67-478B-BB5E-8B1CF5A45201}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15399,7 +15399,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F01703ED-6FF1-410C-A936-747C30ED51B0}" type="CELLRANGE">
+                    <a:fld id="{D3639BB2-C3AD-4EAF-A90D-E203D191F668}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15433,7 +15433,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8C76335C-08B7-4440-93DC-EFBFA37CD9AC}" type="CELLRANGE">
+                    <a:fld id="{651C1975-94BB-442B-812B-9D2404E9391E}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15467,7 +15467,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{67606BAE-4529-47A5-9779-6AD05E0CE283}" type="CELLRANGE">
+                    <a:fld id="{D1FE5970-4A72-4C74-9263-67D2B7D11E1D}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15501,7 +15501,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FAC14235-A8C5-4182-A6DD-3DE5C91992CE}" type="CELLRANGE">
+                    <a:fld id="{A7E22677-3C9B-46F5-88A9-1E170F70BEA0}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15535,7 +15535,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DC945C86-6314-440F-9284-951584BEFCFA}" type="CELLRANGE">
+                    <a:fld id="{BF96E584-6DBE-44BA-B716-C9135E50B4F3}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15569,7 +15569,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{68091A2C-9FF6-448F-B85A-73D3214EE0A4}" type="CELLRANGE">
+                    <a:fld id="{0E7924D7-344D-47BC-B4CF-FB2B8AC61F1E}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15603,7 +15603,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2317415D-9D10-4B12-9718-86A868E4308E}" type="CELLRANGE">
+                    <a:fld id="{CDA642CB-5542-4A2C-9FEF-BAEF3994E0CB}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15637,7 +15637,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8A6FE61E-EB5A-43BB-9B9A-12FA548FEA7D}" type="CELLRANGE">
+                    <a:fld id="{EAD1F672-080A-4911-8DDC-81775E861560}" type="CELLRANGE">
                       <a:rPr lang="es-CL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -22910,7 +22910,7 @@
         <xdr:cNvPr id="11" name="Imagen 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F8AA139-533B-A9F0-7D10-A311F9D4218E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{607F6107-A714-5C1E-D974-1E72C24CFDF9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22960,7 +22960,7 @@
         <xdr:cNvPr id="9" name="Imagen 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D0891E5-2A57-F2C7-5220-0089AED2A017}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{741C9EC1-6D28-8D03-C732-0299EB5B7E93}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23010,7 +23010,7 @@
         <xdr:cNvPr id="10" name="Imagen 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24CFB45C-FA37-DDE4-CFD2-0AC90EA33EAE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19B291BF-E706-A475-E6EF-BFA5F9EBD359}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23060,7 +23060,7 @@
         <xdr:cNvPr id="8" name="Imagen 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{229DA649-3181-FDBA-9305-3473DC208C55}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B366094E-BED3-01EE-8108-FF734886A173}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -24464,7 +24464,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341804"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341824"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -24529,7 +24529,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341805"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341825"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -24646,7 +24646,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s341806"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s341826"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -24711,7 +24711,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s341807"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s341827"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -24776,7 +24776,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s341808"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s341828"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -24841,7 +24841,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s341809"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s341829"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -24906,7 +24906,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s341810"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s341830"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -24971,7 +24971,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s341811"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s341831"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25036,7 +25036,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s341812"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s341832"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25101,7 +25101,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s341813"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s341833"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -27814,7 +27814,7 @@
         <xdr:cNvPr id="4" name="Imagen 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{038614B9-0B50-0A69-CE1C-F1EDFC5C14D7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B7DF340-9331-D733-62B4-FEEC3FB74C92}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -27864,7 +27864,7 @@
         <xdr:cNvPr id="5" name="Imagen 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{764121B3-4FEF-AD81-313F-D5BF30922BF7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{628FDEDF-C317-9AEF-1363-60D2862E010A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -27914,7 +27914,7 @@
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A631DDF3-5EA5-E466-85CB-2D101F75E75B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A9CF92F-AE4F-087C-A9E3-D0378A2F9265}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
